--- a/test-case-example.xlsx
+++ b/test-case-example.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ptmyx\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\sports-field-booking-management\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CDE14F4-F661-4EF3-B7FE-8E051F78F63F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="821" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450" tabRatio="821" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="97" r:id="rId1"/>
     <sheet name="Samples" sheetId="122" r:id="rId2"/>
     <sheet name="Test Report" sheetId="107" r:id="rId3"/>
+    <sheet name="Cancel Booking" sheetId="123" r:id="rId4"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId4"/>
+    <externalReference r:id="rId5"/>
   </externalReferences>
   <definedNames>
     <definedName name="Access">[1]Validation!$E$2:$E$223</definedName>
@@ -30,12 +30,12 @@
     <definedName name="Port">[1]Validation!$F$2:$F$40</definedName>
     <definedName name="VancoProducts">[1]Validation!$B$2:$B$4</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="161">
   <si>
     <r>
       <t>Don't see</t>
@@ -497,11 +497,159 @@
   <si>
     <t>SPORT-BOOKING-01</t>
   </si>
+  <si>
+    <t>HỦY ĐẶT SÂN</t>
+  </si>
+  <si>
+    <t>CR200 - CANCEL BOOKING</t>
+  </si>
+  <si>
+    <t>1. Chỉ người đặt mới được hủy</t>
+  </si>
+  <si>
+    <t>TC2-01</t>
+  </si>
+  <si>
+    <t>Hủy sân sau khi đặt sân trong cùng một tài khoản</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1: Truy cập vào trang và đăng nhập tài khoản thành công.
+2: Chuyển tab "Sân đã đặt" nhấn "HỦY SÂN" cần hủy.
+</t>
+  </si>
+  <si>
+    <t>Hệ thống tự động tải lại trang, tab "Sân đã đặt" không còn sân vừa hủy.</t>
+  </si>
+  <si>
+    <t>TC2-02</t>
+  </si>
+  <si>
+    <t>Hủy sân của một user khác</t>
+  </si>
+  <si>
+    <t>1: Truy cập vào trang và đăng nhập user A thành công.
+2: Đặt lịch ở user A rồi đăng nhập vào user B.
+3: Chuyển tab "Sân đã đặt" để kiểm tra.</t>
+  </si>
+  <si>
+    <t>Không thấy sân đã đặt lịch ở user A</t>
+  </si>
+  <si>
+    <t>2. Không hủy khi còn &lt;2 giờ trước giờ chơi</t>
+  </si>
+  <si>
+    <t>TC2-03</t>
+  </si>
+  <si>
+    <t>Huỷ một sân trước 3 giờ trước hạn chót</t>
+  </si>
+  <si>
+    <t>Booking #1 có giờ bắt đầu là 14:00 hôm nay. Thời gian hiện tại là 11:00:
+1: Truy cập vào trang và đăng nhập tài khoản thành công.
+2: Chuyển sang tab "Sân đã đặt".
+3: Nhấn "HỦY SÂN" ở booking #1.</t>
+  </si>
+  <si>
+    <t>Hệ thống tự động tải lại trang, tab "Sân đã đặt" không còn booking #1.</t>
+  </si>
+  <si>
+    <t>TC2-04</t>
+  </si>
+  <si>
+    <t>Hủy một sân 1 phút ngay trước hạn chót</t>
+  </si>
+  <si>
+    <t>Booking #1 có giờ bắt đầu là 14:00 hôm nay. Thời gian hiện tại là 11:59:
+1: Truy cập vào trang và đăng nhập tài khoản thành công.
+2: Chuyển sang tab "Sân đã đặt".
+3: Nhấn "HỦY SÂN" ở booking #1.</t>
+  </si>
+  <si>
+    <t>TC2-05</t>
+  </si>
+  <si>
+    <t>Huỷ một sân đúng ngay hạn chót</t>
+  </si>
+  <si>
+    <t>Booking #1 có giờ bắt đầu là 14:00 hôm nay. Thời gian hiện tại là 12:00:
+1: Truy cập vào trang và đăng nhập tài khoản thành công.
+2: Chuyển sang tab "Sân đã đặt".
+3: Nhấn "HỦY SÂN" ở booking #1.</t>
+  </si>
+  <si>
+    <t>Hệ thống từ chối huỷ sân, hiển thị thông báo "Sân sắp đá, không được huỷ!"</t>
+  </si>
+  <si>
+    <t>TC2-06</t>
+  </si>
+  <si>
+    <t>Huỷ một sân đã quá 1 phút sau hạn chót</t>
+  </si>
+  <si>
+    <t>Booking #1 có giờ bắt đầu là 14:00 hôm nay. Thời gian hiện tại là 12:01:
+1: Truy cập vào trang và đăng nhập tài khoản thành công.
+2: Chuyển sang tab "Sân đã đặt".
+3: Nhấn "HỦY SÂN" ở booking #1.</t>
+  </si>
+  <si>
+    <t>TC2-07</t>
+  </si>
+  <si>
+    <t>Huỷ một sân đã qua hạn chót 1 giờ.</t>
+  </si>
+  <si>
+    <t>Booking #1 có giờ bắt đầu là 14:00 hôm nay. Thời gian hiện tại là 13:00:
+1: Truy cập vào trang và đăng nhập tài khoản thành công.
+2: Chuyển sang tab "Sân đã đặt".
+3: Nhấn "HỦY SÂN" ở booking #1.</t>
+  </si>
+  <si>
+    <t>3. Không hủy khi đang chơi</t>
+  </si>
+  <si>
+    <t>TC2-08</t>
+  </si>
+  <si>
+    <t>Hủy một sân đang trong thời gian sử dụng</t>
+  </si>
+  <si>
+    <t>1: Truy cập vào trang và đăng nhập tài khoản thành công.
+2: Chuyển sang tab "Sân đã đặt".
+3: Nhấn "HỦY SÂN" ở booking đang trong thời gian sử dụng.</t>
+  </si>
+  <si>
+    <t>Hệ thống có thông báo "Sân đang trong giờ sử dụng, bạn không thể hủy lúc này!"</t>
+  </si>
+  <si>
+    <t>TC2-09</t>
+  </si>
+  <si>
+    <t>Hủy một sân ngay khi vừa thi đấu xong</t>
+  </si>
+  <si>
+    <t>1: Truy cập vào trang và đăng nhập tài khoản thành công.
+2: Chuyển sang tab "Sân đã đặt".
+3:  Nhấn "HỦY SÂN" ở booking vừa mới thi đấu xong.</t>
+  </si>
+  <si>
+    <t>TC2-10</t>
+  </si>
+  <si>
+    <t>Hủy một sân sau khi vừa thi đấu xong 15 phút.</t>
+  </si>
+  <si>
+    <t>1: Truy cập vào trang và đăng nhập tài khoản thành công.
+2: Chuyển sang tab "Sân đã đặt".
+3:  Nhấn "HỦY SÂN" ở booking đã qua thời gian sử dụng 15 phút.</t>
+  </si>
+  <si>
+    <t>Hệ thống có thông báo "Sân này đã thi đấu xong, không thể hủy!"</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
@@ -747,7 +895,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="35">
+  <borders count="38">
     <border>
       <left/>
       <right/>
@@ -1209,6 +1357,37 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1217,7 +1396,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="125">
+  <cellXfs count="146">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1407,60 +1586,12 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="23" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="33" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="24" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="4" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1468,52 +1599,7 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="24" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="30" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="4"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="34" xfId="4" applyFont="1" applyBorder="1"/>
@@ -1539,17 +1625,173 @@
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="4" applyFont="1"/>
     <xf numFmtId="0" fontId="32" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="4" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="24" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="23" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="24" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="33" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="30" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="4" xr:uid="{4A15C362-BE0B-457A-AAD2-047D68D09160}"/>
-    <cellStyle name="Normal_Functional Test Case v1.0" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
-    <cellStyle name="Normal_Sheet1_Vanco_CR022a1_TestCase_v0.1" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
-    <cellStyle name="標準_結合試験(AllOvertheWorld)" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="Normal 2" xfId="4"/>
+    <cellStyle name="Normal_Functional Test Case v1.0" xfId="1"/>
+    <cellStyle name="Normal_Sheet1_Vanco_CR022a1_TestCase_v0.1" xfId="2"/>
+    <cellStyle name="標準_結合試験(AllOvertheWorld)" xfId="3"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Table Style 1" pivot="0" count="0" xr9:uid="{CD416BC6-D49C-4959-BC12-9304ACEFBA0D}"/>
+    <tableStyle name="Table Style 1" pivot="0" count="0"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1563,7 +1805,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Validation"/>
@@ -1576,9 +1818,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1616,9 +1858,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1653,7 +1895,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1688,7 +1930,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1861,24 +2103,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A2:I26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="19.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.5" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="52" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="28.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="31.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="31.625" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" ht="24.6">
+    <row r="2" spans="1:9" ht="25.5">
       <c r="A2" s="23"/>
-      <c r="B2" s="123" t="s">
+      <c r="B2" s="92" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="23"/>
@@ -1887,453 +2129,453 @@
       <c r="F2" s="23"/>
       <c r="G2" s="23"/>
     </row>
-    <row r="3" spans="1:9" ht="16.8">
+    <row r="3" spans="1:9" ht="16.5">
       <c r="A3" s="23"/>
-      <c r="B3" s="121" t="s">
+      <c r="B3" s="90" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="124" t="s">
+      <c r="C3" s="93" t="s">
         <v>101</v>
       </c>
-      <c r="D3" s="111"/>
-      <c r="E3" s="111"/>
-      <c r="F3" s="111"/>
-      <c r="G3" s="111"/>
-      <c r="H3" s="111"/>
-      <c r="I3" s="111"/>
-    </row>
-    <row r="4" spans="1:9" ht="16.8">
+      <c r="D3" s="80"/>
+      <c r="E3" s="80"/>
+      <c r="F3" s="80"/>
+      <c r="G3" s="80"/>
+      <c r="H3" s="80"/>
+      <c r="I3" s="80"/>
+    </row>
+    <row r="4" spans="1:9" ht="16.5">
       <c r="A4" s="23"/>
-      <c r="B4" s="121" t="s">
+      <c r="B4" s="90" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="124" t="s">
+      <c r="C4" s="93" t="s">
         <v>117</v>
       </c>
-      <c r="D4" s="111"/>
-      <c r="E4" s="111"/>
-      <c r="F4" s="111"/>
-      <c r="G4" s="111"/>
-      <c r="H4" s="111"/>
-      <c r="I4" s="111"/>
-    </row>
-    <row r="5" spans="1:9" ht="16.8">
+      <c r="D4" s="80"/>
+      <c r="E4" s="80"/>
+      <c r="F4" s="80"/>
+      <c r="G4" s="80"/>
+      <c r="H4" s="80"/>
+      <c r="I4" s="80"/>
+    </row>
+    <row r="5" spans="1:9" ht="16.5">
       <c r="A5" s="23"/>
-      <c r="B5" s="121"/>
-      <c r="C5" s="111"/>
-      <c r="D5" s="111"/>
-      <c r="E5" s="111"/>
-      <c r="F5" s="111"/>
-      <c r="G5" s="111"/>
-      <c r="H5" s="111"/>
-      <c r="I5" s="111"/>
+      <c r="B5" s="90"/>
+      <c r="C5" s="80"/>
+      <c r="D5" s="80"/>
+      <c r="E5" s="80"/>
+      <c r="F5" s="80"/>
+      <c r="G5" s="80"/>
+      <c r="H5" s="80"/>
+      <c r="I5" s="80"/>
     </row>
     <row r="6" spans="1:9" ht="14.25" customHeight="1">
       <c r="A6" s="23"/>
-      <c r="B6" s="121" t="s">
+      <c r="B6" s="90" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="112" t="s">
+      <c r="C6" s="81" t="s">
         <v>118</v>
       </c>
-      <c r="D6" s="111"/>
-      <c r="E6" s="122"/>
-      <c r="F6" s="111"/>
-      <c r="G6" s="111"/>
-      <c r="H6" s="111"/>
-      <c r="I6" s="111"/>
-    </row>
-    <row r="7" spans="1:9" ht="13.8" customHeight="1">
+      <c r="D6" s="80"/>
+      <c r="E6" s="91"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
+    </row>
+    <row r="7" spans="1:9" ht="13.9" customHeight="1">
       <c r="A7" s="23"/>
-      <c r="B7" s="121" t="s">
+      <c r="B7" s="90" t="s">
         <v>35</v>
       </c>
-      <c r="C7" s="112" t="s">
+      <c r="C7" s="81" t="s">
         <v>119</v>
       </c>
-      <c r="D7" s="111"/>
-      <c r="E7" s="111"/>
-      <c r="F7" s="111"/>
-      <c r="G7" s="111"/>
-      <c r="H7" s="111"/>
-      <c r="I7" s="111"/>
-    </row>
-    <row r="8" spans="1:9" ht="16.8">
+      <c r="D7" s="80"/>
+      <c r="E7" s="80"/>
+      <c r="F7" s="80"/>
+      <c r="G7" s="80"/>
+      <c r="H7" s="80"/>
+      <c r="I7" s="80"/>
+    </row>
+    <row r="8" spans="1:9" ht="16.5">
       <c r="A8" s="23"/>
-      <c r="B8" s="121"/>
+      <c r="B8" s="90"/>
       <c r="C8" s="23"/>
       <c r="D8" s="23"/>
       <c r="E8" s="23"/>
       <c r="F8" s="23"/>
       <c r="G8" s="23"/>
     </row>
-    <row r="9" spans="1:9" ht="16.8">
+    <row r="9" spans="1:9" ht="16.5">
       <c r="A9" s="23"/>
-      <c r="B9" s="113"/>
+      <c r="B9" s="82"/>
       <c r="C9" s="17"/>
       <c r="D9" s="17"/>
       <c r="E9" s="17"/>
       <c r="F9" s="23"/>
       <c r="G9" s="23"/>
     </row>
-    <row r="10" spans="1:9" ht="16.8">
-      <c r="B10" s="114" t="s">
+    <row r="10" spans="1:9" ht="16.5">
+      <c r="B10" s="83" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="115"/>
-      <c r="D10" s="115"/>
-      <c r="E10" s="115"/>
-      <c r="F10" s="115"/>
-      <c r="G10" s="115"/>
-      <c r="H10" s="115"/>
-    </row>
-    <row r="11" spans="1:9" s="29" customFormat="1" ht="50.4">
-      <c r="B11" s="116" t="s">
+      <c r="C10" s="84"/>
+      <c r="D10" s="84"/>
+      <c r="E10" s="84"/>
+      <c r="F10" s="84"/>
+      <c r="G10" s="84"/>
+      <c r="H10" s="84"/>
+    </row>
+    <row r="11" spans="1:9" s="29" customFormat="1" ht="33">
+      <c r="B11" s="85" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="117" t="s">
+      <c r="C11" s="86" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="117" t="s">
+      <c r="D11" s="86" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="117" t="s">
+      <c r="E11" s="86" t="s">
         <v>10</v>
       </c>
-      <c r="F11" s="117" t="s">
+      <c r="F11" s="86" t="s">
         <v>15</v>
       </c>
-      <c r="G11" s="118" t="s">
+      <c r="G11" s="87" t="s">
         <v>14</v>
       </c>
-      <c r="H11" s="119" t="s">
+      <c r="H11" s="88" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:9" s="29" customFormat="1" ht="49.95" customHeight="1">
-      <c r="B12" s="120" t="s">
+    <row r="12" spans="1:9" s="29" customFormat="1" ht="49.9" customHeight="1">
+      <c r="B12" s="89" t="s">
         <v>58</v>
       </c>
-      <c r="C12" s="120" t="s">
+      <c r="C12" s="89" t="s">
         <v>40</v>
       </c>
-      <c r="D12" s="120"/>
-      <c r="E12" s="120" t="s">
+      <c r="D12" s="89"/>
+      <c r="E12" s="89" t="s">
         <v>59</v>
       </c>
-      <c r="F12" s="120" t="s">
+      <c r="F12" s="89" t="s">
         <v>60</v>
       </c>
-      <c r="G12" s="120"/>
-      <c r="H12" s="120" t="s">
+      <c r="G12" s="89"/>
+      <c r="H12" s="89" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="13" spans="1:9" s="29" customFormat="1" ht="49.95" customHeight="1">
-      <c r="B13" s="120" t="s">
+    <row r="13" spans="1:9" s="29" customFormat="1" ht="49.9" customHeight="1">
+      <c r="B13" s="89" t="s">
         <v>62</v>
       </c>
-      <c r="C13" s="120" t="s">
+      <c r="C13" s="89" t="s">
         <v>46</v>
       </c>
-      <c r="D13" s="120" t="s">
+      <c r="D13" s="89" t="s">
         <v>63</v>
       </c>
-      <c r="E13" s="120" t="s">
+      <c r="E13" s="89" t="s">
         <v>64</v>
       </c>
-      <c r="F13" s="120" t="s">
+      <c r="F13" s="89" t="s">
         <v>60</v>
       </c>
-      <c r="G13" s="120"/>
-      <c r="H13" s="120" t="s">
+      <c r="G13" s="89"/>
+      <c r="H13" s="89" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="14" spans="1:9" s="30" customFormat="1" ht="49.95" customHeight="1">
-      <c r="B14" s="120" t="s">
+    <row r="14" spans="1:9" s="30" customFormat="1" ht="49.9" customHeight="1">
+      <c r="B14" s="89" t="s">
         <v>66</v>
       </c>
-      <c r="C14" s="120" t="s">
+      <c r="C14" s="89" t="s">
         <v>46</v>
       </c>
-      <c r="D14" s="120" t="s">
+      <c r="D14" s="89" t="s">
         <v>67</v>
       </c>
-      <c r="E14" s="120" t="s">
+      <c r="E14" s="89" t="s">
         <v>68</v>
       </c>
-      <c r="F14" s="120" t="s">
+      <c r="F14" s="89" t="s">
         <v>60</v>
       </c>
-      <c r="G14" s="120"/>
-      <c r="H14" s="120" t="s">
+      <c r="G14" s="89"/>
+      <c r="H14" s="89" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="15" spans="1:9" s="30" customFormat="1" ht="49.95" customHeight="1">
-      <c r="B15" s="120" t="s">
+    <row r="15" spans="1:9" s="30" customFormat="1" ht="49.9" customHeight="1">
+      <c r="B15" s="89" t="s">
         <v>70</v>
       </c>
-      <c r="C15" s="120" t="s">
+      <c r="C15" s="89" t="s">
         <v>47</v>
       </c>
-      <c r="D15" s="120" t="s">
+      <c r="D15" s="89" t="s">
         <v>71</v>
       </c>
-      <c r="E15" s="120" t="s">
+      <c r="E15" s="89" t="s">
         <v>72</v>
       </c>
-      <c r="F15" s="120" t="s">
+      <c r="F15" s="89" t="s">
         <v>73</v>
       </c>
-      <c r="G15" s="120"/>
-      <c r="H15" s="120" t="s">
+      <c r="G15" s="89"/>
+      <c r="H15" s="89" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="16" spans="1:9" s="29" customFormat="1" ht="49.95" customHeight="1">
-      <c r="B16" s="120" t="s">
+    <row r="16" spans="1:9" s="29" customFormat="1" ht="49.9" customHeight="1">
+      <c r="B16" s="89" t="s">
         <v>75</v>
       </c>
-      <c r="C16" s="120" t="s">
+      <c r="C16" s="89" t="s">
         <v>47</v>
       </c>
-      <c r="D16" s="120" t="s">
+      <c r="D16" s="89" t="s">
         <v>76</v>
       </c>
-      <c r="E16" s="120" t="s">
+      <c r="E16" s="89" t="s">
         <v>77</v>
       </c>
-      <c r="F16" s="120" t="s">
+      <c r="F16" s="89" t="s">
         <v>78</v>
       </c>
-      <c r="G16" s="120" t="s">
+      <c r="G16" s="89" t="s">
         <v>60</v>
       </c>
-      <c r="H16" s="120" t="s">
+      <c r="H16" s="89" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="17" spans="2:8" s="29" customFormat="1" ht="49.95" customHeight="1">
-      <c r="B17" s="120" t="s">
+    <row r="17" spans="2:8" s="29" customFormat="1" ht="49.9" customHeight="1">
+      <c r="B17" s="89" t="s">
         <v>80</v>
       </c>
-      <c r="C17" s="120" t="s">
+      <c r="C17" s="89" t="s">
         <v>47</v>
       </c>
-      <c r="D17" s="120" t="s">
+      <c r="D17" s="89" t="s">
         <v>81</v>
       </c>
-      <c r="E17" s="120" t="s">
+      <c r="E17" s="89" t="s">
         <v>82</v>
       </c>
-      <c r="F17" s="120" t="s">
+      <c r="F17" s="89" t="s">
         <v>60</v>
       </c>
-      <c r="G17" s="120"/>
-      <c r="H17" s="120" t="s">
+      <c r="G17" s="89"/>
+      <c r="H17" s="89" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="18" spans="2:8" s="29" customFormat="1" ht="49.95" customHeight="1">
-      <c r="B18" s="120" t="s">
+    <row r="18" spans="2:8" s="29" customFormat="1" ht="49.9" customHeight="1">
+      <c r="B18" s="89" t="s">
         <v>84</v>
       </c>
-      <c r="C18" s="120" t="s">
+      <c r="C18" s="89" t="s">
         <v>85</v>
       </c>
-      <c r="D18" s="120" t="s">
+      <c r="D18" s="89" t="s">
         <v>86</v>
       </c>
-      <c r="E18" s="120" t="s">
+      <c r="E18" s="89" t="s">
         <v>87</v>
       </c>
-      <c r="F18" s="120" t="s">
+      <c r="F18" s="89" t="s">
         <v>88</v>
       </c>
-      <c r="G18" s="120" t="s">
+      <c r="G18" s="89" t="s">
         <v>60</v>
       </c>
-      <c r="H18" s="120" t="s">
+      <c r="H18" s="89" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="19" spans="2:8" s="29" customFormat="1" ht="49.95" customHeight="1">
-      <c r="B19" s="120" t="s">
+    <row r="19" spans="2:8" s="29" customFormat="1" ht="49.9" customHeight="1">
+      <c r="B19" s="89" t="s">
         <v>84</v>
       </c>
-      <c r="C19" s="120" t="s">
+      <c r="C19" s="89" t="s">
         <v>85</v>
       </c>
-      <c r="D19" s="120" t="s">
+      <c r="D19" s="89" t="s">
         <v>90</v>
       </c>
-      <c r="E19" s="120" t="s">
+      <c r="E19" s="89" t="s">
         <v>91</v>
       </c>
-      <c r="F19" s="120" t="s">
+      <c r="F19" s="89" t="s">
         <v>78</v>
       </c>
-      <c r="G19" s="120" t="s">
+      <c r="G19" s="89" t="s">
         <v>60</v>
       </c>
-      <c r="H19" s="120" t="s">
+      <c r="H19" s="89" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="20" spans="2:8" s="29" customFormat="1" ht="49.95" customHeight="1">
-      <c r="B20" s="120" t="s">
+    <row r="20" spans="2:8" s="29" customFormat="1" ht="49.9" customHeight="1">
+      <c r="B20" s="89" t="s">
         <v>93</v>
       </c>
-      <c r="C20" s="120" t="s">
+      <c r="C20" s="89" t="s">
         <v>85</v>
       </c>
-      <c r="D20" s="120" t="s">
+      <c r="D20" s="89" t="s">
         <v>94</v>
       </c>
-      <c r="E20" s="120" t="s">
+      <c r="E20" s="89" t="s">
         <v>95</v>
       </c>
-      <c r="F20" s="120" t="s">
+      <c r="F20" s="89" t="s">
         <v>60</v>
       </c>
-      <c r="G20" s="120"/>
-      <c r="H20" s="120" t="s">
+      <c r="G20" s="89"/>
+      <c r="H20" s="89" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="21" spans="2:8" s="29" customFormat="1" ht="49.95" customHeight="1">
-      <c r="B21" s="120" t="s">
+    <row r="21" spans="2:8" s="29" customFormat="1" ht="49.9" customHeight="1">
+      <c r="B21" s="89" t="s">
         <v>97</v>
       </c>
-      <c r="C21" s="120" t="s">
+      <c r="C21" s="89" t="s">
         <v>85</v>
       </c>
-      <c r="D21" s="120" t="s">
+      <c r="D21" s="89" t="s">
         <v>98</v>
       </c>
-      <c r="E21" s="120" t="s">
+      <c r="E21" s="89" t="s">
         <v>99</v>
       </c>
-      <c r="F21" s="120" t="s">
+      <c r="F21" s="89" t="s">
         <v>60</v>
       </c>
-      <c r="G21" s="120"/>
-      <c r="H21" s="120" t="s">
+      <c r="G21" s="89"/>
+      <c r="H21" s="89" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="22" spans="2:8" s="29" customFormat="1" ht="49.95" customHeight="1">
-      <c r="B22" s="120" t="s">
+    <row r="22" spans="2:8" s="29" customFormat="1" ht="49.9" customHeight="1">
+      <c r="B22" s="89" t="s">
         <v>97</v>
       </c>
-      <c r="C22" s="120" t="s">
+      <c r="C22" s="89" t="s">
         <v>101</v>
       </c>
-      <c r="D22" s="120" t="s">
+      <c r="D22" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="E22" s="120" t="s">
+      <c r="E22" s="89" t="s">
         <v>103</v>
       </c>
-      <c r="F22" s="120" t="s">
+      <c r="F22" s="89" t="s">
         <v>78</v>
       </c>
-      <c r="G22" s="120" t="s">
+      <c r="G22" s="89" t="s">
         <v>60</v>
       </c>
-      <c r="H22" s="120" t="s">
+      <c r="H22" s="89" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="23" spans="2:8" s="29" customFormat="1" ht="49.95" customHeight="1">
-      <c r="B23" s="120" t="s">
+    <row r="23" spans="2:8" s="29" customFormat="1" ht="49.9" customHeight="1">
+      <c r="B23" s="89" t="s">
         <v>105</v>
       </c>
-      <c r="C23" s="120" t="s">
+      <c r="C23" s="89" t="s">
         <v>101</v>
       </c>
-      <c r="D23" s="120" t="s">
+      <c r="D23" s="89" t="s">
         <v>86</v>
       </c>
-      <c r="E23" s="120" t="s">
+      <c r="E23" s="89" t="s">
         <v>106</v>
       </c>
-      <c r="F23" s="120" t="s">
+      <c r="F23" s="89" t="s">
         <v>60</v>
       </c>
-      <c r="G23" s="120"/>
-      <c r="H23" s="120" t="s">
+      <c r="G23" s="89"/>
+      <c r="H23" s="89" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="24" spans="2:8" ht="49.95" customHeight="1">
-      <c r="B24" s="120" t="s">
+    <row r="24" spans="2:8" ht="49.9" customHeight="1">
+      <c r="B24" s="89" t="s">
         <v>105</v>
       </c>
-      <c r="C24" s="120" t="s">
+      <c r="C24" s="89" t="s">
         <v>101</v>
       </c>
-      <c r="D24" s="120" t="s">
+      <c r="D24" s="89" t="s">
         <v>108</v>
       </c>
-      <c r="E24" s="120" t="s">
+      <c r="E24" s="89" t="s">
         <v>109</v>
       </c>
-      <c r="F24" s="120" t="s">
+      <c r="F24" s="89" t="s">
         <v>88</v>
       </c>
-      <c r="G24" s="120" t="s">
+      <c r="G24" s="89" t="s">
         <v>60</v>
       </c>
-      <c r="H24" s="120" t="s">
+      <c r="H24" s="89" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="25" spans="2:8" ht="49.95" customHeight="1">
-      <c r="B25" s="120" t="s">
+    <row r="25" spans="2:8" ht="49.9" customHeight="1">
+      <c r="B25" s="89" t="s">
         <v>105</v>
       </c>
-      <c r="C25" s="120" t="s">
+      <c r="C25" s="89" t="s">
         <v>101</v>
       </c>
-      <c r="D25" s="120" t="s">
+      <c r="D25" s="89" t="s">
         <v>94</v>
       </c>
-      <c r="E25" s="120" t="s">
+      <c r="E25" s="89" t="s">
         <v>111</v>
       </c>
-      <c r="F25" s="120" t="s">
+      <c r="F25" s="89" t="s">
         <v>78</v>
       </c>
-      <c r="G25" s="120" t="s">
+      <c r="G25" s="89" t="s">
         <v>60</v>
       </c>
-      <c r="H25" s="120" t="s">
+      <c r="H25" s="89" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="49.95" customHeight="1">
-      <c r="B26" s="120" t="s">
+    <row r="26" spans="2:8" ht="49.9" customHeight="1">
+      <c r="B26" s="89" t="s">
         <v>113</v>
       </c>
-      <c r="C26" s="120" t="s">
+      <c r="C26" s="89" t="s">
         <v>101</v>
       </c>
-      <c r="D26" s="120" t="s">
+      <c r="D26" s="89" t="s">
         <v>114</v>
       </c>
-      <c r="E26" s="120" t="s">
+      <c r="E26" s="89" t="s">
         <v>115</v>
       </c>
-      <c r="F26" s="120" t="s">
+      <c r="F26" s="89" t="s">
         <v>60</v>
       </c>
-      <c r="G26" s="120" t="s">
+      <c r="G26" s="89" t="s">
         <v>60</v>
       </c>
-      <c r="H26" s="120" t="s">
+      <c r="H26" s="89" t="s">
         <v>116</v>
       </c>
     </row>
@@ -2348,20 +2590,20 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:L55"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.8" outlineLevelRow="1"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14.25" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" customWidth="1"/>
-    <col min="2" max="2" width="18.109375" customWidth="1"/>
-    <col min="3" max="3" width="42.109375" customWidth="1"/>
-    <col min="6" max="6" width="23.6640625" customWidth="1"/>
-    <col min="7" max="7" width="18.44140625" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="15.625" customWidth="1"/>
+    <col min="2" max="2" width="18.125" customWidth="1"/>
+    <col min="3" max="3" width="42.125" customWidth="1"/>
+    <col min="6" max="6" width="23.625" customWidth="1"/>
+    <col min="7" max="7" width="18.5" hidden="1" customWidth="1"/>
     <col min="8" max="8" width="38" customWidth="1"/>
-    <col min="9" max="9" width="17.109375" customWidth="1"/>
+    <col min="9" max="9" width="17.125" customWidth="1"/>
     <col min="10" max="10" width="9" style="17"/>
     <col min="11" max="11" width="18" customWidth="1"/>
   </cols>
@@ -2370,9 +2612,9 @@
       <c r="A1" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="86"/>
-      <c r="C1" s="86"/>
-      <c r="D1" s="86"/>
+      <c r="B1" s="94"/>
+      <c r="C1" s="94"/>
+      <c r="D1" s="94"/>
       <c r="E1" s="5"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
@@ -2384,9 +2626,9 @@
     </row>
     <row r="2" spans="1:12" s="2" customFormat="1" ht="11.25" customHeight="1" thickBot="1">
       <c r="A2" s="6"/>
-      <c r="B2" s="87"/>
-      <c r="C2" s="87"/>
-      <c r="D2" s="87"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
+      <c r="D2" s="95"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
@@ -2400,54 +2642,54 @@
       <c r="A3" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="B3" s="75" t="s">
+      <c r="B3" s="105" t="s">
         <v>48</v>
       </c>
-      <c r="C3" s="75"/>
-      <c r="D3" s="76"/>
+      <c r="C3" s="105"/>
+      <c r="D3" s="106"/>
       <c r="E3" s="43"/>
       <c r="F3" s="43"/>
       <c r="G3" s="43"/>
       <c r="H3" s="43"/>
-      <c r="I3" s="96"/>
-      <c r="J3" s="96"/>
-      <c r="K3" s="96"/>
+      <c r="I3" s="104"/>
+      <c r="J3" s="104"/>
+      <c r="K3" s="104"/>
       <c r="L3" s="8"/>
     </row>
-    <row r="4" spans="1:12" s="3" customFormat="1" ht="13.2">
+    <row r="4" spans="1:12" s="3" customFormat="1" ht="12.75">
       <c r="A4" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="B4" s="97" t="s">
+      <c r="B4" s="109" t="s">
         <v>49</v>
       </c>
-      <c r="C4" s="98"/>
-      <c r="D4" s="99"/>
+      <c r="C4" s="110"/>
+      <c r="D4" s="111"/>
       <c r="E4" s="43"/>
       <c r="F4" s="43"/>
       <c r="G4" s="43"/>
       <c r="H4" s="43"/>
-      <c r="I4" s="96"/>
-      <c r="J4" s="96"/>
-      <c r="K4" s="96"/>
+      <c r="I4" s="104"/>
+      <c r="J4" s="104"/>
+      <c r="K4" s="104"/>
       <c r="L4" s="8"/>
     </row>
-    <row r="5" spans="1:12" s="53" customFormat="1" ht="26.4">
+    <row r="5" spans="1:12" s="53" customFormat="1" ht="25.5">
       <c r="A5" s="45" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="89" t="s">
+      <c r="B5" s="97" t="s">
         <v>50</v>
       </c>
-      <c r="C5" s="90"/>
-      <c r="D5" s="91"/>
+      <c r="C5" s="98"/>
+      <c r="D5" s="99"/>
       <c r="E5" s="51"/>
       <c r="F5" s="51"/>
       <c r="G5" s="51"/>
       <c r="H5" s="51"/>
-      <c r="I5" s="95"/>
-      <c r="J5" s="95"/>
-      <c r="K5" s="95"/>
+      <c r="I5" s="103"/>
+      <c r="J5" s="103"/>
+      <c r="K5" s="103"/>
       <c r="L5" s="52"/>
     </row>
     <row r="6" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1">
@@ -2469,9 +2711,9 @@
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
       <c r="H6" s="7"/>
-      <c r="I6" s="96"/>
-      <c r="J6" s="96"/>
-      <c r="K6" s="96"/>
+      <c r="I6" s="104"/>
+      <c r="J6" s="104"/>
+      <c r="K6" s="104"/>
       <c r="L6" s="8"/>
     </row>
     <row r="7" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" thickBot="1">
@@ -2493,16 +2735,16 @@
       <c r="F7" s="44"/>
       <c r="G7" s="44"/>
       <c r="H7" s="44"/>
-      <c r="I7" s="96"/>
-      <c r="J7" s="96"/>
-      <c r="K7" s="96"/>
+      <c r="I7" s="104"/>
+      <c r="J7" s="104"/>
+      <c r="K7" s="104"/>
       <c r="L7" s="8"/>
     </row>
     <row r="8" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1">
-      <c r="A8" s="88"/>
-      <c r="B8" s="88"/>
-      <c r="C8" s="88"/>
-      <c r="D8" s="88"/>
+      <c r="A8" s="96"/>
+      <c r="B8" s="96"/>
+      <c r="C8" s="96"/>
+      <c r="D8" s="96"/>
       <c r="E8" s="7"/>
       <c r="F8" s="7"/>
       <c r="G8" s="7"/>
@@ -2513,78 +2755,78 @@
       <c r="L8" s="8"/>
     </row>
     <row r="9" spans="1:12" s="55" customFormat="1" ht="12" customHeight="1">
-      <c r="A9" s="78" t="s">
+      <c r="A9" s="108" t="s">
         <v>31</v>
       </c>
-      <c r="B9" s="103" t="s">
+      <c r="B9" s="115" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="78" t="s">
+      <c r="C9" s="108" t="s">
         <v>17</v>
       </c>
-      <c r="D9" s="105" t="s">
+      <c r="D9" s="124" t="s">
         <v>55</v>
       </c>
-      <c r="E9" s="106"/>
-      <c r="F9" s="106"/>
-      <c r="G9" s="107"/>
-      <c r="H9" s="83" t="s">
+      <c r="E9" s="125"/>
+      <c r="F9" s="125"/>
+      <c r="G9" s="126"/>
+      <c r="H9" s="121" t="s">
         <v>56</v>
       </c>
-      <c r="I9" s="77" t="s">
+      <c r="I9" s="107" t="s">
         <v>28</v>
       </c>
-      <c r="J9" s="77" t="s">
+      <c r="J9" s="107" t="s">
         <v>57</v>
       </c>
-      <c r="K9" s="77" t="s">
+      <c r="K9" s="107" t="s">
         <v>32</v>
       </c>
       <c r="L9" s="54"/>
     </row>
     <row r="10" spans="1:12" s="3" customFormat="1" ht="12" customHeight="1">
-      <c r="A10" s="102"/>
-      <c r="B10" s="104"/>
-      <c r="C10" s="102"/>
-      <c r="D10" s="108"/>
-      <c r="E10" s="109"/>
-      <c r="F10" s="109"/>
-      <c r="G10" s="110"/>
-      <c r="H10" s="78"/>
-      <c r="I10" s="78"/>
-      <c r="J10" s="78"/>
-      <c r="K10" s="78"/>
+      <c r="A10" s="114"/>
+      <c r="B10" s="116"/>
+      <c r="C10" s="114"/>
+      <c r="D10" s="127"/>
+      <c r="E10" s="128"/>
+      <c r="F10" s="128"/>
+      <c r="G10" s="129"/>
+      <c r="H10" s="108"/>
+      <c r="I10" s="108"/>
+      <c r="J10" s="108"/>
+      <c r="K10" s="108"/>
       <c r="L10" s="8"/>
     </row>
     <row r="11" spans="1:12" s="56" customFormat="1" ht="15">
-      <c r="A11" s="100"/>
-      <c r="B11" s="100"/>
-      <c r="C11" s="100"/>
-      <c r="D11" s="100"/>
-      <c r="E11" s="100"/>
-      <c r="F11" s="100"/>
-      <c r="G11" s="100"/>
-      <c r="H11" s="100"/>
-      <c r="I11" s="100"/>
-      <c r="J11" s="100"/>
-      <c r="K11" s="101"/>
-    </row>
-    <row r="12" spans="1:12" s="4" customFormat="1" ht="13.2">
-      <c r="A12" s="92" t="s">
+      <c r="A11" s="112"/>
+      <c r="B11" s="112"/>
+      <c r="C11" s="112"/>
+      <c r="D11" s="112"/>
+      <c r="E11" s="112"/>
+      <c r="F11" s="112"/>
+      <c r="G11" s="112"/>
+      <c r="H11" s="112"/>
+      <c r="I11" s="112"/>
+      <c r="J11" s="112"/>
+      <c r="K11" s="113"/>
+    </row>
+    <row r="12" spans="1:12" s="4" customFormat="1" ht="12.75">
+      <c r="A12" s="100" t="s">
         <v>51</v>
       </c>
-      <c r="B12" s="93"/>
-      <c r="C12" s="93"/>
-      <c r="D12" s="93"/>
-      <c r="E12" s="93"/>
-      <c r="F12" s="93"/>
-      <c r="G12" s="93"/>
-      <c r="H12" s="93"/>
-      <c r="I12" s="93"/>
-      <c r="J12" s="93"/>
-      <c r="K12" s="94"/>
-    </row>
-    <row r="13" spans="1:12" s="4" customFormat="1" ht="79.2" outlineLevel="1">
+      <c r="B12" s="101"/>
+      <c r="C12" s="101"/>
+      <c r="D12" s="101"/>
+      <c r="E12" s="101"/>
+      <c r="F12" s="101"/>
+      <c r="G12" s="101"/>
+      <c r="H12" s="101"/>
+      <c r="I12" s="101"/>
+      <c r="J12" s="101"/>
+      <c r="K12" s="102"/>
+    </row>
+    <row r="13" spans="1:12" s="4" customFormat="1" ht="76.5" outlineLevel="1">
       <c r="A13" s="60" t="s">
         <v>2</v>
       </c>
@@ -2594,11 +2836,11 @@
       <c r="C13" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="D13" s="85" t="s">
+      <c r="D13" s="123" t="s">
         <v>43</v>
       </c>
-      <c r="E13" s="84"/>
-      <c r="F13" s="84"/>
+      <c r="E13" s="122"/>
+      <c r="F13" s="122"/>
       <c r="G13" s="58"/>
       <c r="H13" s="73"/>
       <c r="I13" s="69"/>
@@ -2607,12 +2849,12 @@
       </c>
       <c r="K13" s="57"/>
     </row>
-    <row r="14" spans="1:12" s="4" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A14" s="79" t="s">
+    <row r="14" spans="1:12" s="4" customFormat="1" ht="12.75" outlineLevel="1">
+      <c r="A14" s="117" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="80"/>
-      <c r="C14" s="80"/>
+      <c r="B14" s="118"/>
+      <c r="C14" s="118"/>
       <c r="D14" s="67"/>
       <c r="E14" s="67"/>
       <c r="F14" s="67"/>
@@ -2632,11 +2874,11 @@
       <c r="C15" s="66" t="s">
         <v>53</v>
       </c>
-      <c r="D15" s="81" t="s">
+      <c r="D15" s="119" t="s">
         <v>1</v>
       </c>
-      <c r="E15" s="84"/>
-      <c r="F15" s="84"/>
+      <c r="E15" s="122"/>
+      <c r="F15" s="122"/>
       <c r="G15" s="58"/>
       <c r="H15" s="73"/>
       <c r="I15" s="64"/>
@@ -2645,12 +2887,12 @@
       </c>
       <c r="K15" s="57"/>
     </row>
-    <row r="16" spans="1:12" s="4" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A16" s="79" t="s">
+    <row r="16" spans="1:12" s="4" customFormat="1" ht="12.75" outlineLevel="1">
+      <c r="A16" s="117" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="80"/>
-      <c r="C16" s="80"/>
+      <c r="B16" s="118"/>
+      <c r="C16" s="118"/>
       <c r="D16" s="67"/>
       <c r="E16" s="67"/>
       <c r="F16" s="67"/>
@@ -2670,11 +2912,11 @@
       <c r="C17" s="59" t="s">
         <v>54</v>
       </c>
-      <c r="D17" s="81" t="s">
+      <c r="D17" s="119" t="s">
         <v>0</v>
       </c>
-      <c r="E17" s="82"/>
-      <c r="F17" s="82"/>
+      <c r="E17" s="120"/>
+      <c r="F17" s="120"/>
       <c r="G17" s="58"/>
       <c r="H17" s="73"/>
       <c r="I17" s="64"/>
@@ -2723,6 +2965,15 @@
     <row r="55" ht="12" customHeight="1"/>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="H9:H10"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D9:G10"/>
+    <mergeCell ref="A14:C14"/>
     <mergeCell ref="B1:D2"/>
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="B5:D5"/>
@@ -2739,15 +2990,6 @@
     <mergeCell ref="A11:K11"/>
     <mergeCell ref="A9:A10"/>
     <mergeCell ref="B9:B10"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="H9:H10"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D9:G10"/>
-    <mergeCell ref="A14:C14"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2757,15 +2999,15 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="13.5"/>
   <cols>
-    <col min="3" max="3" width="22.77734375" customWidth="1"/>
-    <col min="7" max="7" width="18.77734375" customWidth="1"/>
+    <col min="3" max="3" width="22.75" customWidth="1"/>
+    <col min="7" max="7" width="18.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="22.2">
+    <row r="1" spans="1:7" ht="22.5">
       <c r="A1" s="13" t="s">
         <v>12</v>
       </c>
@@ -2785,7 +3027,7 @@
       <c r="F2" s="15"/>
       <c r="G2" s="16"/>
     </row>
-    <row r="3" spans="1:7" ht="13.8">
+    <row r="3" spans="1:7" ht="14.25">
       <c r="B3" s="17" t="s">
         <v>11</v>
       </c>
@@ -2795,7 +3037,7 @@
       <c r="F3" s="15"/>
       <c r="G3" s="16"/>
     </row>
-    <row r="4" spans="1:7" ht="13.8">
+    <row r="4" spans="1:7" ht="14.25">
       <c r="B4" s="17" t="s">
         <v>6</v>
       </c>
@@ -2805,7 +3047,7 @@
       <c r="F4" s="17"/>
       <c r="G4" s="17"/>
     </row>
-    <row r="5" spans="1:7" ht="13.8">
+    <row r="5" spans="1:7" ht="14.25">
       <c r="A5" s="17"/>
       <c r="B5" s="17"/>
       <c r="C5" s="17"/>
@@ -2814,7 +3056,7 @@
       <c r="F5" s="17"/>
       <c r="G5" s="17"/>
     </row>
-    <row r="6" spans="1:7" ht="13.8">
+    <row r="6" spans="1:7" ht="14.25">
       <c r="A6" s="17"/>
       <c r="B6" s="17"/>
       <c r="C6" s="17"/>
@@ -2823,7 +3065,7 @@
       <c r="F6" s="17"/>
       <c r="G6" s="17"/>
     </row>
-    <row r="7" spans="1:7" ht="26.4">
+    <row r="7" spans="1:7" ht="25.5">
       <c r="A7" s="17"/>
       <c r="B7" s="31" t="s">
         <v>18</v>
@@ -2844,7 +3086,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:7" s="42" customFormat="1" ht="13.8">
+    <row r="8" spans="1:7" s="42" customFormat="1" ht="14.25">
       <c r="A8" s="46"/>
       <c r="B8" s="47">
         <v>1</v>
@@ -2870,7 +3112,7 @@
         <v>-9</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="13.8">
+    <row r="9" spans="1:7" ht="14.25">
       <c r="A9" s="17"/>
       <c r="B9" s="27"/>
       <c r="C9" s="26"/>
@@ -2879,7 +3121,7 @@
       <c r="F9" s="25"/>
       <c r="G9" s="28"/>
     </row>
-    <row r="10" spans="1:7" ht="13.8">
+    <row r="10" spans="1:7" ht="14.25">
       <c r="A10" s="17"/>
       <c r="B10" s="35"/>
       <c r="C10" s="36" t="s">
@@ -2902,7 +3144,7 @@
         <v>-9</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="13.8">
+    <row r="11" spans="1:7" ht="14.25">
       <c r="A11" s="17"/>
       <c r="B11" s="18"/>
       <c r="C11" s="17"/>
@@ -2911,7 +3153,7 @@
       <c r="F11" s="20"/>
       <c r="G11" s="20"/>
     </row>
-    <row r="12" spans="1:7" ht="13.8">
+    <row r="12" spans="1:7" ht="14.25">
       <c r="A12" s="17"/>
       <c r="B12" s="17"/>
       <c r="C12" s="17" t="s">
@@ -2927,7 +3169,7 @@
       </c>
       <c r="G12" s="22"/>
     </row>
-    <row r="13" spans="1:7" ht="13.8">
+    <row r="13" spans="1:7" ht="14.25">
       <c r="A13" s="17"/>
       <c r="B13" s="17"/>
       <c r="C13" s="17" t="s">
@@ -2951,4 +3193,523 @@
     <oddFooter>&amp;L&amp;"Tahoma,Regular"&amp;8 02ae-BM/PM/HDCV/FSOFT v1/0</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K24"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="18.25" customWidth="1"/>
+    <col min="2" max="2" width="26.625" customWidth="1"/>
+    <col min="3" max="3" width="33.5" customWidth="1"/>
+    <col min="6" max="6" width="17.625" customWidth="1"/>
+    <col min="7" max="7" width="0.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="14.25">
+      <c r="A1" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="94"/>
+      <c r="C1" s="94"/>
+      <c r="D1" s="94"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="71"/>
+      <c r="K1" s="5"/>
+    </row>
+    <row r="2" spans="1:11" ht="15" thickBot="1">
+      <c r="A2" s="6"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
+      <c r="D2" s="95"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="71"/>
+      <c r="K2" s="5"/>
+    </row>
+    <row r="3" spans="1:11" ht="14.25">
+      <c r="A3" s="144" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" s="105" t="s">
+        <v>120</v>
+      </c>
+      <c r="C3" s="105"/>
+      <c r="D3" s="106"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="43"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="43"/>
+      <c r="I3" s="104"/>
+      <c r="J3" s="104"/>
+      <c r="K3" s="104"/>
+    </row>
+    <row r="4" spans="1:11" ht="14.25">
+      <c r="A4" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="109" t="s">
+        <v>121</v>
+      </c>
+      <c r="C4" s="110"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="43"/>
+      <c r="F4" s="43"/>
+      <c r="G4" s="43"/>
+      <c r="H4" s="43"/>
+      <c r="I4" s="104"/>
+      <c r="J4" s="104"/>
+      <c r="K4" s="104"/>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="145" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="97" t="s">
+        <v>50</v>
+      </c>
+      <c r="C5" s="98"/>
+      <c r="D5" s="99"/>
+      <c r="E5" s="51"/>
+      <c r="F5" s="51"/>
+      <c r="G5" s="51"/>
+      <c r="H5" s="51"/>
+      <c r="I5" s="103"/>
+      <c r="J5" s="103"/>
+      <c r="K5" s="103"/>
+    </row>
+    <row r="6" spans="1:11" ht="14.25">
+      <c r="A6" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" s="61">
+        <f>COUNTIF(J12:J23,"Pass")</f>
+        <v>0</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" s="11">
+        <f>COUNTIF(J10:J741,"Pending")</f>
+        <v>10</v>
+      </c>
+      <c r="E6" s="79"/>
+      <c r="F6" s="79"/>
+      <c r="G6" s="79"/>
+      <c r="H6" s="79"/>
+      <c r="I6" s="104"/>
+      <c r="J6" s="104"/>
+      <c r="K6" s="104"/>
+    </row>
+    <row r="7" spans="1:11" ht="15" thickBot="1">
+      <c r="A7" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="62">
+        <f>COUNTIF(J12:J23,"Fail")</f>
+        <v>0</v>
+      </c>
+      <c r="C7" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="41">
+        <f>COUNTA(A12:A24)-3</f>
+        <v>10</v>
+      </c>
+      <c r="E7" s="44"/>
+      <c r="F7" s="44"/>
+      <c r="G7" s="44"/>
+      <c r="H7" s="44"/>
+      <c r="I7" s="104"/>
+      <c r="J7" s="104"/>
+      <c r="K7" s="104"/>
+    </row>
+    <row r="8" spans="1:11" ht="14.25">
+      <c r="A8" s="96"/>
+      <c r="B8" s="96"/>
+      <c r="C8" s="96"/>
+      <c r="D8" s="96"/>
+      <c r="E8" s="79"/>
+      <c r="F8" s="79"/>
+      <c r="G8" s="79"/>
+      <c r="H8" s="79"/>
+      <c r="I8" s="79"/>
+      <c r="J8" s="72"/>
+      <c r="K8" s="72"/>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="108" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" s="115" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="108" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="124" t="s">
+        <v>55</v>
+      </c>
+      <c r="E9" s="125"/>
+      <c r="F9" s="125"/>
+      <c r="G9" s="126"/>
+      <c r="H9" s="121" t="s">
+        <v>56</v>
+      </c>
+      <c r="I9" s="107" t="s">
+        <v>28</v>
+      </c>
+      <c r="J9" s="107" t="s">
+        <v>57</v>
+      </c>
+      <c r="K9" s="107" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="114"/>
+      <c r="B10" s="116"/>
+      <c r="C10" s="114"/>
+      <c r="D10" s="127"/>
+      <c r="E10" s="128"/>
+      <c r="F10" s="128"/>
+      <c r="G10" s="129"/>
+      <c r="H10" s="108"/>
+      <c r="I10" s="108"/>
+      <c r="J10" s="108"/>
+      <c r="K10" s="108"/>
+    </row>
+    <row r="11" spans="1:11" ht="15">
+      <c r="A11" s="112"/>
+      <c r="B11" s="112"/>
+      <c r="C11" s="112"/>
+      <c r="D11" s="112"/>
+      <c r="E11" s="112"/>
+      <c r="F11" s="112"/>
+      <c r="G11" s="112"/>
+      <c r="H11" s="112"/>
+      <c r="I11" s="112"/>
+      <c r="J11" s="112"/>
+      <c r="K11" s="113"/>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="100" t="s">
+        <v>122</v>
+      </c>
+      <c r="B12" s="101"/>
+      <c r="C12" s="101"/>
+      <c r="D12" s="101"/>
+      <c r="E12" s="101"/>
+      <c r="F12" s="101"/>
+      <c r="G12" s="101"/>
+      <c r="H12" s="101"/>
+      <c r="I12" s="101"/>
+      <c r="J12" s="101"/>
+      <c r="K12" s="102"/>
+    </row>
+    <row r="13" spans="1:11" ht="55.5" customHeight="1">
+      <c r="A13" s="60" t="s">
+        <v>123</v>
+      </c>
+      <c r="B13" s="63" t="s">
+        <v>124</v>
+      </c>
+      <c r="C13" s="59" t="s">
+        <v>125</v>
+      </c>
+      <c r="D13" s="130" t="s">
+        <v>126</v>
+      </c>
+      <c r="E13" s="131"/>
+      <c r="F13" s="131"/>
+      <c r="G13" s="132"/>
+      <c r="H13" s="75"/>
+      <c r="I13" s="69"/>
+      <c r="J13" s="59" t="s">
+        <v>39</v>
+      </c>
+      <c r="K13" s="57"/>
+    </row>
+    <row r="14" spans="1:11" ht="54" customHeight="1">
+      <c r="A14" s="60" t="s">
+        <v>127</v>
+      </c>
+      <c r="B14" s="63" t="s">
+        <v>128</v>
+      </c>
+      <c r="C14" s="76" t="s">
+        <v>129</v>
+      </c>
+      <c r="D14" s="123" t="s">
+        <v>130</v>
+      </c>
+      <c r="E14" s="122"/>
+      <c r="F14" s="122"/>
+      <c r="G14" s="58"/>
+      <c r="H14" s="58"/>
+      <c r="I14" s="133"/>
+      <c r="J14" s="59" t="s">
+        <v>39</v>
+      </c>
+      <c r="K14" s="57"/>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" s="100" t="s">
+        <v>131</v>
+      </c>
+      <c r="B15" s="101"/>
+      <c r="C15" s="101"/>
+      <c r="D15" s="134"/>
+      <c r="E15" s="134"/>
+      <c r="F15" s="134"/>
+      <c r="G15" s="134"/>
+      <c r="H15" s="77"/>
+      <c r="I15" s="77"/>
+      <c r="J15" s="77"/>
+      <c r="K15" s="78"/>
+    </row>
+    <row r="16" spans="1:11" ht="77.25" customHeight="1">
+      <c r="A16" s="60" t="s">
+        <v>132</v>
+      </c>
+      <c r="B16" s="59" t="s">
+        <v>133</v>
+      </c>
+      <c r="C16" s="76" t="s">
+        <v>134</v>
+      </c>
+      <c r="D16" s="123" t="s">
+        <v>135</v>
+      </c>
+      <c r="E16" s="122"/>
+      <c r="F16" s="122"/>
+      <c r="G16" s="135"/>
+      <c r="H16" s="58"/>
+      <c r="I16" s="59"/>
+      <c r="J16" s="59" t="s">
+        <v>39</v>
+      </c>
+      <c r="K16" s="57"/>
+    </row>
+    <row r="17" spans="1:11" ht="78" customHeight="1">
+      <c r="A17" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="B17" s="66" t="s">
+        <v>137</v>
+      </c>
+      <c r="C17" s="66" t="s">
+        <v>138</v>
+      </c>
+      <c r="D17" s="130" t="s">
+        <v>135</v>
+      </c>
+      <c r="E17" s="131"/>
+      <c r="F17" s="131"/>
+      <c r="G17" s="132"/>
+      <c r="H17" s="75"/>
+      <c r="I17" s="76"/>
+      <c r="J17" s="59" t="s">
+        <v>39</v>
+      </c>
+      <c r="K17" s="57"/>
+    </row>
+    <row r="18" spans="1:11" ht="79.5" customHeight="1">
+      <c r="A18" s="60" t="s">
+        <v>139</v>
+      </c>
+      <c r="B18" s="59" t="s">
+        <v>140</v>
+      </c>
+      <c r="C18" s="76" t="s">
+        <v>141</v>
+      </c>
+      <c r="D18" s="123" t="s">
+        <v>142</v>
+      </c>
+      <c r="E18" s="122"/>
+      <c r="F18" s="122"/>
+      <c r="G18" s="58"/>
+      <c r="H18" s="58"/>
+      <c r="I18" s="59"/>
+      <c r="J18" s="59" t="s">
+        <v>39</v>
+      </c>
+      <c r="K18" s="57"/>
+    </row>
+    <row r="19" spans="1:11" ht="78.75" customHeight="1">
+      <c r="A19" s="60" t="s">
+        <v>143</v>
+      </c>
+      <c r="B19" s="59" t="s">
+        <v>144</v>
+      </c>
+      <c r="C19" s="76" t="s">
+        <v>145</v>
+      </c>
+      <c r="D19" s="123" t="s">
+        <v>142</v>
+      </c>
+      <c r="E19" s="122"/>
+      <c r="F19" s="122"/>
+      <c r="G19" s="58"/>
+      <c r="H19" s="58"/>
+      <c r="I19" s="59"/>
+      <c r="J19" s="59" t="s">
+        <v>39</v>
+      </c>
+      <c r="K19" s="57"/>
+    </row>
+    <row r="20" spans="1:11" ht="78.75" customHeight="1">
+      <c r="A20" s="136" t="s">
+        <v>146</v>
+      </c>
+      <c r="B20" s="137" t="s">
+        <v>147</v>
+      </c>
+      <c r="C20" s="138" t="s">
+        <v>148</v>
+      </c>
+      <c r="D20" s="139" t="s">
+        <v>142</v>
+      </c>
+      <c r="E20" s="140"/>
+      <c r="F20" s="140"/>
+      <c r="G20" s="141"/>
+      <c r="H20" s="142"/>
+      <c r="I20" s="142"/>
+      <c r="J20" s="142" t="s">
+        <v>39</v>
+      </c>
+      <c r="K20" s="142"/>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" s="100" t="s">
+        <v>149</v>
+      </c>
+      <c r="B21" s="101"/>
+      <c r="C21" s="101"/>
+      <c r="D21" s="134"/>
+      <c r="E21" s="134"/>
+      <c r="F21" s="134"/>
+      <c r="G21" s="134"/>
+      <c r="H21" s="77"/>
+      <c r="I21" s="77"/>
+      <c r="J21" s="77"/>
+      <c r="K21" s="78"/>
+    </row>
+    <row r="22" spans="1:11" ht="66" customHeight="1">
+      <c r="A22" s="60" t="s">
+        <v>150</v>
+      </c>
+      <c r="B22" s="66" t="s">
+        <v>151</v>
+      </c>
+      <c r="C22" s="66" t="s">
+        <v>152</v>
+      </c>
+      <c r="D22" s="123" t="s">
+        <v>153</v>
+      </c>
+      <c r="E22" s="122"/>
+      <c r="F22" s="122"/>
+      <c r="G22" s="58"/>
+      <c r="H22" s="75"/>
+      <c r="I22" s="76"/>
+      <c r="J22" s="59" t="s">
+        <v>39</v>
+      </c>
+      <c r="K22" s="57"/>
+    </row>
+    <row r="23" spans="1:11" ht="65.25" customHeight="1">
+      <c r="A23" s="143" t="s">
+        <v>154</v>
+      </c>
+      <c r="B23" s="59" t="s">
+        <v>155</v>
+      </c>
+      <c r="C23" s="59" t="s">
+        <v>156</v>
+      </c>
+      <c r="D23" s="123" t="s">
+        <v>160</v>
+      </c>
+      <c r="E23" s="122"/>
+      <c r="F23" s="122"/>
+      <c r="G23" s="58"/>
+      <c r="H23" s="59"/>
+      <c r="I23" s="59"/>
+      <c r="J23" s="59" t="s">
+        <v>39</v>
+      </c>
+      <c r="K23" s="57"/>
+    </row>
+    <row r="24" spans="1:11" ht="67.5" customHeight="1">
+      <c r="A24" s="143" t="s">
+        <v>157</v>
+      </c>
+      <c r="B24" s="59" t="s">
+        <v>158</v>
+      </c>
+      <c r="C24" s="59" t="s">
+        <v>159</v>
+      </c>
+      <c r="D24" s="123" t="s">
+        <v>160</v>
+      </c>
+      <c r="E24" s="122"/>
+      <c r="F24" s="122"/>
+      <c r="G24" s="58"/>
+      <c r="H24" s="59"/>
+      <c r="I24" s="59"/>
+      <c r="J24" s="59" t="s">
+        <v>39</v>
+      </c>
+      <c r="K24" s="57"/>
+    </row>
+  </sheetData>
+  <mergeCells count="32">
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="K9:K10"/>
+    <mergeCell ref="A11:K11"/>
+    <mergeCell ref="A12:K12"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D9:G10"/>
+    <mergeCell ref="H9:H10"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="B1:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="I5:K5"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/test-case-example.xlsx
+++ b/test-case-example.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sports-field-booking-management\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D8C809D-0D5F-4D1D-A227-99701DE534BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E87223E6-2BF4-4C3E-BF43-8693D5468A09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="821" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="97" r:id="rId1"/>
     <sheet name="Samples" sheetId="122" r:id="rId2"/>
-    <sheet name="Booking" sheetId="124" r:id="rId3"/>
-    <sheet name="Cancel Booking" sheetId="123" r:id="rId4"/>
-    <sheet name="Test Report" sheetId="107" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="125" r:id="rId3"/>
+    <sheet name="Booking" sheetId="124" r:id="rId4"/>
+    <sheet name="Cancel Booking" sheetId="123" r:id="rId5"/>
+    <sheet name="Test Report" sheetId="107" r:id="rId6"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId6"/>
+    <externalReference r:id="rId7"/>
   </externalReferences>
   <definedNames>
     <definedName name="Access">[1]Validation!$E$2:$E$223</definedName>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="177">
   <si>
     <t>TEST CASE</t>
   </si>
@@ -45,9 +46,6 @@
     <t>Version:</t>
   </si>
   <si>
-    <t>1.4</t>
-  </si>
-  <si>
     <t>Issue date:</t>
   </si>
   <si>
@@ -67,9 +65,6 @@
   </si>
   <si>
     <t>Record of change:</t>
-  </si>
-  <si>
-    <t>Effective Date</t>
   </si>
   <si>
     <t>Version</t>
@@ -89,132 +84,6 @@
   </si>
   <si>
     <t>Reference</t>
-  </si>
-  <si>
-    <t>09/03/2026</t>
-  </si>
-  <si>
-    <t>1.0</t>
-  </si>
-  <si>
-    <t>Initial commit – Tạo project, README.md</t>
-  </si>
-  <si>
-    <t>16/03/2026</t>
-  </si>
-  <si>
-    <t>1.1</t>
-  </si>
-  <si>
-    <t>models.py, seed.py</t>
-  </si>
-  <si>
-    <t>Tạo project cấu trúc ban đầu, định nghĩa models &amp; seed data</t>
-  </si>
-  <si>
-    <t>25/03/2026</t>
-  </si>
-  <si>
-    <t>README.md</t>
-  </si>
-  <si>
-    <t>Cập nhật README, tạo nhánh chính</t>
-  </si>
-  <si>
-    <t>29/03/2026</t>
-  </si>
-  <si>
-    <t>1.2</t>
-  </si>
-  <si>
-    <t>index.html (FE)</t>
-  </si>
-  <si>
-    <t>FE KhamPha – Thiết kế trang khám phá sân</t>
-  </si>
-  <si>
-    <t>02/04/2026</t>
-  </si>
-  <si>
-    <t>featured.html</t>
-  </si>
-  <si>
-    <t>Thiết kế trang Featured Page (nổi bật)</t>
-  </si>
-  <si>
-    <t>04/04/2026</t>
-  </si>
-  <si>
-    <t>seed.py, models.py</t>
-  </si>
-  <si>
-    <t>Cập nhật dữ liệu mẫu (update data)</t>
-  </si>
-  <si>
-    <t>05/04/2026</t>
-  </si>
-  <si>
-    <t>1.3</t>
-  </si>
-  <si>
-    <t>admin.py</t>
-  </si>
-  <si>
-    <t>Long-administrator: Xây dựng trang Admin quản lý sân</t>
-  </si>
-  <si>
-    <t>base.html, footer</t>
-  </si>
-  <si>
-    <t>Cập nhật footer (update fe_footer)</t>
-  </si>
-  <si>
-    <t>06/04/2026</t>
-  </si>
-  <si>
-    <t>index.py</t>
-  </si>
-  <si>
-    <t>Chỉnh sửa tabs điều hướng (edit tabs)</t>
-  </si>
-  <si>
-    <t>10/04/2026</t>
-  </si>
-  <si>
-    <t>dao.py, index.py</t>
-  </si>
-  <si>
-    <t>API-BOOKING: Xây dựng API đặt sân, hủy sân</t>
-  </si>
-  <si>
-    <t>dao.py, models.py</t>
-  </si>
-  <si>
-    <t>Hoàn tất tích hợp code Xuyên + Quyên, giữ giao diện</t>
-  </si>
-  <si>
-    <t>11/04/2026</t>
-  </si>
-  <si>
-    <t>Chỉnh sửa file admin – cập nhật validation</t>
-  </si>
-  <si>
-    <t>admin.py, dao.py</t>
-  </si>
-  <si>
-    <t>LONG/feature/CRUD-validation: Thêm ràng buộc CRUD</t>
-  </si>
-  <si>
-    <t>cancel-booking API: Hoàn thiện API hủy đặt sân</t>
-  </si>
-  <si>
-    <t>12/04/2026</t>
-  </si>
-  <si>
-    <t>index.html</t>
-  </si>
-  <si>
-    <t>index.html: Cập nhật giao diện trang chủ, ràng buộc UI</t>
   </si>
   <si>
     <r>
@@ -852,105 +721,82 @@
     <t xml:space="preserve">Huỷ một sân trước 3 giờ trước hạn chót </t>
   </si>
   <si>
-    <t>UC-00: Khởi tạo hệ thống</t>
-  </si>
-  <si>
-    <t>UC-01: Quản lý dữ liệu sân
-UC-02: Quản lý người dùng</t>
-  </si>
-  <si>
-    <t>Tài liệu dự án – README v1.1</t>
-  </si>
-  <si>
-    <t>UC-03: Tìm kiếm &amp; khám phá sân
-Yêu cầu FE – Trang Explore</t>
-  </si>
-  <si>
-    <t>UC-04: Xem sân nổi bật
-Yêu cầu FE – Trang Featured</t>
-  </si>
-  <si>
-    <t>UC-01: Quản lý dữ liệu sân
-(Cập nhật seed data thực tế)</t>
-  </si>
-  <si>
-    <t>UC-08: Quản lý Admin
-Yêu cầu: CRUD Category, Product, User</t>
-  </si>
-  <si>
-    <t>Yêu cầu FE – Footer &amp; Navigation
-Issue #8 feature/fe_footer</t>
-  </si>
-  <si>
-    <t>Yêu cầu FE – Điều hướng trang
-UC-03: Khám phá sân</t>
-  </si>
-  <si>
-    <t>UC-05: Đặt sân
-UC-06: Hủy đặt sân
-Issue #9 feature/API-booking</t>
-  </si>
-  <si>
-    <t>UC-05: Đặt sân
-UC-07: Đánh giá &amp; Yêu thích</t>
-  </si>
-  <si>
-    <t>UC-08: Quản lý Admin
-Yêu cầu: Validation dữ liệu Admin</t>
-  </si>
-  <si>
-    <t>UC-08: Quản lý Admin
-Yêu cầu: Không xóa sân đang có lịch đặt
-Issue #10 CRUD-validation</t>
-  </si>
-  <si>
-    <t>UC-06: Hủy đặt sân
-Yêu cầu: Ràng buộc thời gian hủy</t>
-  </si>
-  <si>
-    <t>UC-05: Đặt sân
-UC-06: Hủy đặt sân
-Yêu cầu FE – Constraint UI trang chủ
-Issue #14 feature/constraints1</t>
-  </si>
-  <si>
     <t>Mỹ Xuyên</t>
   </si>
   <si>
     <t>Đại Long</t>
   </si>
   <si>
-    <t>Đại Long / Thúy Quyên</t>
-  </si>
-  <si>
     <t>Thúy Quyên</t>
   </si>
   <si>
-    <t>Thùy Quyên</t>
-  </si>
-  <si>
-    <t>16/04/2026</t>
-  </si>
-  <si>
-    <t>frontend (FE)</t>
-  </si>
-  <si>
-    <t>Cập nhật giao diện FE</t>
-  </si>
-  <si>
-    <t>17/04/2026</t>
-  </si>
-  <si>
-    <t>dao.py, API-booking</t>
-  </si>
-  <si>
-    <t>Hoàn thiện API booking</t>
-  </si>
-  <si>
-    <t>UC-09: Giao diện trang chủ</t>
-  </si>
-  <si>
-    <t>UC-05: Đặt sân</t>
+    <t>S</t>
+  </si>
+  <si>
+    <t>CR300 - AUTH</t>
+  </si>
+  <si>
+    <t>Sheet Booking</t>
+  </si>
+  <si>
+    <t>Sheet Cancel Booking</t>
+  </si>
+  <si>
+    <t>Update testcase</t>
+  </si>
+  <si>
+    <t>Chia modeul để thiết kế testcase</t>
+  </si>
+  <si>
+    <t>1. 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tạo sheet booking và bắt đầu thiết kế </t>
+  </si>
+  <si>
+    <t>Create file</t>
+  </si>
+  <si>
+    <t>CR100-Booking</t>
+  </si>
+  <si>
+    <t>CR200-Cancel-Booking</t>
+  </si>
+  <si>
+    <t>CR300-Auth</t>
+  </si>
+  <si>
+    <t>Sheet Auth</t>
+  </si>
+  <si>
+    <t>Sheet Admin</t>
+  </si>
+  <si>
+    <t>tạo sheet Auth và bắt đầu thiết kế</t>
+  </si>
+  <si>
+    <t>tạo sheet cancel-booking và bắt đầu thiết kế</t>
+  </si>
+  <si>
+    <t>tạo sheet Admin bắt đầu thiết kế</t>
+  </si>
+  <si>
+    <t>CR400-Admin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">thêm tc 3 - tc 5 </t>
+  </si>
+  <si>
+    <t>thêm tc 5 - tc10</t>
+  </si>
+  <si>
+    <t>19/4/2026</t>
+  </si>
+  <si>
+    <t>Sheet Auth - Sheet Admin</t>
+  </si>
+  <si>
+    <t>CR300-Auth, CR400-Admin</t>
   </si>
 </sst>
 </file>
@@ -1064,65 +910,11 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="20"/>
-      <name val="Tahoma"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color indexed="60"/>
-      <name val="Tahoma"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="13"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="20"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="13"/>
-      <name val="Tahoma"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color indexed="60"/>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="13"/>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color indexed="9"/>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
@@ -1159,9 +951,63 @@
       <name val="ＭＳ Ｐゴシック"/>
     </font>
     <font>
-      <sz val="13"/>
+      <b/>
+      <sz val="19"/>
+      <color indexed="9"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="19"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="21"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="19"/>
+      <color indexed="60"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="19"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="19"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="19"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="19"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="19"/>
+      <color indexed="60"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="9">
@@ -1723,12 +1569,12 @@
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="163">
+  <cellXfs count="164">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1962,31 +1808,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="26" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="7" borderId="36" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="8" fillId="8" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -2006,7 +1827,91 @@
     <xf numFmtId="0" fontId="3" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="17" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="17" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="15" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="16" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="32" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="25" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="25" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="28" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="29" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="24" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -2025,96 +1930,12 @@
     <xf numFmtId="0" fontId="11" fillId="6" borderId="16" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="15" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="16" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="32" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="25" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="25" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="28" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="29" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="24" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="17" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="17" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -2136,29 +1957,59 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="7" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="24" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="7" borderId="38" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="26" fillId="7" borderId="36" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="7" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="36" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="38" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -2483,528 +2334,438 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:I28"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="9" style="88"/>
     <col min="2" max="2" width="29.77734375" style="88" customWidth="1"/>
     <col min="3" max="3" width="23.109375" style="88" customWidth="1"/>
-    <col min="4" max="4" width="18.44140625" style="88" customWidth="1"/>
-    <col min="5" max="5" width="52" style="88" customWidth="1"/>
-    <col min="6" max="6" width="34.109375" style="88" customWidth="1"/>
-    <col min="7" max="7" width="25.44140625" style="88" customWidth="1"/>
-    <col min="8" max="8" width="61.77734375" style="88" customWidth="1"/>
+    <col min="4" max="4" width="66.77734375" style="88" customWidth="1"/>
+    <col min="5" max="5" width="141.33203125" style="88" customWidth="1"/>
+    <col min="6" max="7" width="31.109375" style="88" customWidth="1"/>
+    <col min="8" max="8" width="174.5546875" style="88" customWidth="1"/>
     <col min="9" max="16384" width="9" style="88"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" ht="24.6">
-      <c r="A2" s="89"/>
-      <c r="B2" s="90" t="s">
+    <row r="1" spans="1:9" s="155" customFormat="1" ht="24"/>
+    <row r="2" spans="1:9" s="155" customFormat="1" ht="24">
+      <c r="A2" s="156"/>
+      <c r="B2" s="157" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="89"/>
-      <c r="D2" s="89"/>
-      <c r="E2" s="89"/>
-      <c r="F2" s="89"/>
-      <c r="G2" s="89"/>
-    </row>
-    <row r="3" spans="1:9" ht="16.8">
-      <c r="A3" s="89"/>
-      <c r="B3" s="91" t="s">
+      <c r="C2" s="156"/>
+      <c r="D2" s="156"/>
+      <c r="E2" s="156"/>
+      <c r="F2" s="156"/>
+      <c r="G2" s="156"/>
+    </row>
+    <row r="3" spans="1:9" s="155" customFormat="1" ht="25.2">
+      <c r="A3" s="156"/>
+      <c r="B3" s="154" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="92" t="s">
+      <c r="C3" s="158">
+        <v>1.2</v>
+      </c>
+      <c r="D3" s="159"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="159"/>
+      <c r="G3" s="159"/>
+      <c r="H3" s="159"/>
+      <c r="I3" s="159"/>
+    </row>
+    <row r="4" spans="1:9" s="155" customFormat="1" ht="25.2">
+      <c r="A4" s="156"/>
+      <c r="B4" s="154" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="93"/>
-      <c r="E3" s="93"/>
-      <c r="F3" s="93"/>
-      <c r="G3" s="93"/>
-      <c r="H3" s="93"/>
-      <c r="I3" s="93"/>
-    </row>
-    <row r="4" spans="1:9" ht="16.8">
-      <c r="A4" s="89"/>
-      <c r="B4" s="91" t="s">
+      <c r="C4" s="158" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="92" t="s">
+      <c r="D4" s="159"/>
+      <c r="E4" s="159"/>
+      <c r="F4" s="159"/>
+      <c r="G4" s="159"/>
+      <c r="H4" s="159"/>
+      <c r="I4" s="159"/>
+    </row>
+    <row r="5" spans="1:9" s="155" customFormat="1" ht="25.2">
+      <c r="A5" s="156"/>
+      <c r="B5" s="154"/>
+      <c r="C5" s="159"/>
+      <c r="D5" s="159"/>
+      <c r="E5" s="159"/>
+      <c r="F5" s="159"/>
+      <c r="G5" s="159"/>
+      <c r="H5" s="159"/>
+      <c r="I5" s="159"/>
+    </row>
+    <row r="6" spans="1:9" s="155" customFormat="1" ht="47.4" customHeight="1">
+      <c r="A6" s="156"/>
+      <c r="B6" s="154" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="93"/>
-      <c r="E4" s="93"/>
-      <c r="F4" s="93"/>
-      <c r="G4" s="93"/>
-      <c r="H4" s="93"/>
-      <c r="I4" s="93"/>
-    </row>
-    <row r="5" spans="1:9" ht="16.8">
-      <c r="A5" s="89"/>
-      <c r="B5" s="91"/>
-      <c r="C5" s="93"/>
-      <c r="D5" s="93"/>
-      <c r="E5" s="93"/>
-      <c r="F5" s="93"/>
-      <c r="G5" s="93"/>
-      <c r="H5" s="93"/>
-      <c r="I5" s="93"/>
-    </row>
-    <row r="6" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A6" s="89"/>
-      <c r="B6" s="91" t="s">
+      <c r="C6" s="160" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="94" t="s">
+      <c r="D6" s="159"/>
+      <c r="E6" s="159"/>
+      <c r="F6" s="159"/>
+      <c r="G6" s="159"/>
+      <c r="H6" s="159"/>
+      <c r="I6" s="159"/>
+    </row>
+    <row r="7" spans="1:9" s="155" customFormat="1" ht="27" customHeight="1">
+      <c r="A7" s="156"/>
+      <c r="B7" s="154" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="93"/>
-      <c r="E6" s="95"/>
-      <c r="F6" s="93"/>
-      <c r="G6" s="93"/>
-      <c r="H6" s="93"/>
-      <c r="I6" s="93"/>
-    </row>
-    <row r="7" spans="1:9" ht="13.95" customHeight="1">
-      <c r="A7" s="89"/>
-      <c r="B7" s="91" t="s">
+      <c r="C7" s="160" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="94" t="s">
+      <c r="D7" s="159"/>
+      <c r="E7" s="159"/>
+      <c r="F7" s="159"/>
+      <c r="G7" s="159"/>
+      <c r="H7" s="159"/>
+      <c r="I7" s="159"/>
+    </row>
+    <row r="8" spans="1:9" s="155" customFormat="1" ht="24">
+      <c r="A8" s="156"/>
+      <c r="B8" s="154"/>
+      <c r="C8" s="156"/>
+      <c r="D8" s="156"/>
+      <c r="E8" s="156"/>
+      <c r="F8" s="156"/>
+      <c r="G8" s="156"/>
+    </row>
+    <row r="9" spans="1:9" s="155" customFormat="1" ht="24">
+      <c r="A9" s="156"/>
+      <c r="F9" s="156"/>
+      <c r="G9" s="156"/>
+    </row>
+    <row r="10" spans="1:9" s="155" customFormat="1" ht="24.6">
+      <c r="B10" s="161" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="93"/>
-      <c r="E7" s="93"/>
-      <c r="F7" s="93"/>
-      <c r="G7" s="93"/>
-      <c r="H7" s="93"/>
-      <c r="I7" s="93"/>
-    </row>
-    <row r="8" spans="1:9" ht="16.8">
-      <c r="A8" s="89"/>
-      <c r="B8" s="91"/>
-      <c r="C8" s="89"/>
-      <c r="D8" s="89"/>
-      <c r="E8" s="89"/>
-      <c r="F8" s="89"/>
-      <c r="G8" s="89"/>
-    </row>
-    <row r="9" spans="1:9" ht="16.8">
-      <c r="A9" s="89"/>
-      <c r="B9" s="96"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="89"/>
-      <c r="G9" s="89"/>
-    </row>
-    <row r="10" spans="1:9" ht="16.8">
-      <c r="B10" s="97" t="s">
+      <c r="C10" s="162"/>
+      <c r="D10" s="162"/>
+      <c r="E10" s="162"/>
+      <c r="F10" s="162"/>
+      <c r="G10" s="162"/>
+      <c r="H10" s="162"/>
+    </row>
+    <row r="11" spans="1:9" s="163" customFormat="1" ht="63.6" customHeight="1">
+      <c r="B11" s="144"/>
+      <c r="C11" s="145" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="98"/>
-      <c r="D10" s="98"/>
-      <c r="E10" s="98"/>
-      <c r="F10" s="98"/>
-      <c r="G10" s="98"/>
-      <c r="H10" s="98"/>
-    </row>
-    <row r="11" spans="1:9" s="86" customFormat="1" ht="50.4">
-      <c r="B11" s="99" t="s">
+      <c r="D11" s="145" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="100" t="s">
+      <c r="E11" s="145" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="100" t="s">
+      <c r="F11" s="145" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="100" t="s">
+      <c r="G11" s="146" t="s">
         <v>13</v>
       </c>
-      <c r="F11" s="100" t="s">
+      <c r="H11" s="147" t="s">
         <v>14</v>
       </c>
-      <c r="G11" s="101" t="s">
-        <v>15</v>
-      </c>
-      <c r="H11" s="102" t="s">
-        <v>16</v>
-      </c>
     </row>
     <row r="12" spans="1:9" s="86" customFormat="1" ht="49.95" customHeight="1">
-      <c r="B12" s="103" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" s="103" t="s">
-        <v>18</v>
-      </c>
-      <c r="D12" s="103"/>
-      <c r="E12" s="103" t="s">
-        <v>19</v>
-      </c>
-      <c r="F12" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="G12" s="103"/>
-      <c r="H12" s="159" t="s">
-        <v>195</v>
+      <c r="B12" s="148">
+        <v>46268</v>
+      </c>
+      <c r="C12" s="149" t="s">
+        <v>160</v>
+      </c>
+      <c r="D12" s="149" t="s">
+        <v>158</v>
+      </c>
+      <c r="E12" s="149" t="s">
+        <v>159</v>
+      </c>
+      <c r="F12" s="149" t="s">
+        <v>151</v>
+      </c>
+      <c r="G12" s="149" t="s">
+        <v>151</v>
+      </c>
+      <c r="H12" s="150" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="13" spans="1:9" s="86" customFormat="1" ht="49.95" customHeight="1">
-      <c r="B13" s="103" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13" s="103" t="s">
-        <v>21</v>
-      </c>
-      <c r="D13" s="103" t="s">
-        <v>22</v>
-      </c>
-      <c r="E13" s="103" t="s">
-        <v>23</v>
-      </c>
-      <c r="F13" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="G13" s="103"/>
-      <c r="H13" s="159" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" s="87" customFormat="1" ht="49.95" customHeight="1">
-      <c r="B14" s="103" t="s">
-        <v>24</v>
-      </c>
-      <c r="C14" s="103" t="s">
-        <v>21</v>
-      </c>
-      <c r="D14" s="103" t="s">
-        <v>25</v>
-      </c>
-      <c r="E14" s="103" t="s">
-        <v>26</v>
-      </c>
-      <c r="F14" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="G14" s="103"/>
-      <c r="H14" s="159" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" s="87" customFormat="1" ht="49.95" customHeight="1">
-      <c r="B15" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="C15" s="103" t="s">
-        <v>28</v>
-      </c>
-      <c r="D15" s="103" t="s">
-        <v>29</v>
-      </c>
-      <c r="E15" s="103" t="s">
-        <v>30</v>
-      </c>
-      <c r="F15" s="103" t="s">
-        <v>212</v>
-      </c>
-      <c r="G15" s="103"/>
-      <c r="H15" s="159" t="s">
-        <v>198</v>
+      <c r="B13" s="148">
+        <v>46116</v>
+      </c>
+      <c r="C13" s="149">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D13" s="149" t="s">
+        <v>156</v>
+      </c>
+      <c r="E13" s="149" t="s">
+        <v>161</v>
+      </c>
+      <c r="F13" s="149" t="s">
+        <v>153</v>
+      </c>
+      <c r="G13" s="149" t="s">
+        <v>151</v>
+      </c>
+      <c r="H13" s="150" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" s="86" customFormat="1" ht="49.95" customHeight="1">
+      <c r="B14" s="148">
+        <v>46116</v>
+      </c>
+      <c r="C14" s="149">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D14" s="149" t="s">
+        <v>157</v>
+      </c>
+      <c r="E14" s="149" t="s">
+        <v>169</v>
+      </c>
+      <c r="F14" s="149" t="s">
+        <v>152</v>
+      </c>
+      <c r="G14" s="149" t="s">
+        <v>151</v>
+      </c>
+      <c r="H14" s="150" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" s="86" customFormat="1" ht="49.95" customHeight="1">
+      <c r="B15" s="148">
+        <v>46116</v>
+      </c>
+      <c r="C15" s="149">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D15" s="149" t="s">
+        <v>166</v>
+      </c>
+      <c r="E15" s="149" t="s">
+        <v>168</v>
+      </c>
+      <c r="F15" s="149" t="s">
+        <v>151</v>
+      </c>
+      <c r="G15" s="149" t="s">
+        <v>151</v>
+      </c>
+      <c r="H15" s="150" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="16" spans="1:9" s="86" customFormat="1" ht="49.95" customHeight="1">
-      <c r="B16" s="103" t="s">
-        <v>31</v>
-      </c>
-      <c r="C16" s="103" t="s">
-        <v>28</v>
-      </c>
-      <c r="D16" s="103" t="s">
-        <v>32</v>
-      </c>
-      <c r="E16" s="103" t="s">
-        <v>33</v>
-      </c>
-      <c r="F16" s="103" t="s">
-        <v>213</v>
-      </c>
-      <c r="G16" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="H16" s="159" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="17" spans="2:8" s="86" customFormat="1" ht="49.95" customHeight="1">
-      <c r="B17" s="103" t="s">
-        <v>34</v>
-      </c>
-      <c r="C17" s="103" t="s">
-        <v>28</v>
-      </c>
-      <c r="D17" s="103" t="s">
-        <v>35</v>
-      </c>
-      <c r="E17" s="103" t="s">
-        <v>36</v>
-      </c>
-      <c r="F17" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="G17" s="103"/>
-      <c r="H17" s="159" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="18" spans="2:8" s="86" customFormat="1" ht="49.95" customHeight="1">
-      <c r="B18" s="103" t="s">
-        <v>37</v>
-      </c>
-      <c r="C18" s="103" t="s">
-        <v>38</v>
-      </c>
-      <c r="D18" s="103" t="s">
-        <v>39</v>
-      </c>
-      <c r="E18" s="103" t="s">
-        <v>40</v>
-      </c>
-      <c r="F18" s="103" t="s">
-        <v>211</v>
-      </c>
-      <c r="G18" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="H18" s="159" t="s">
-        <v>201</v>
+      <c r="B16" s="148">
+        <v>46116</v>
+      </c>
+      <c r="C16" s="149">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D16" s="149" t="s">
+        <v>167</v>
+      </c>
+      <c r="E16" s="149" t="s">
+        <v>170</v>
+      </c>
+      <c r="F16" s="149" t="s">
+        <v>151</v>
+      </c>
+      <c r="G16" s="149" t="s">
+        <v>151</v>
+      </c>
+      <c r="H16" s="150" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" s="87" customFormat="1" ht="49.95" customHeight="1">
+      <c r="B17" s="148">
+        <v>46330</v>
+      </c>
+      <c r="C17" s="149">
+        <v>1.2</v>
+      </c>
+      <c r="D17" s="149" t="s">
+        <v>156</v>
+      </c>
+      <c r="E17" s="149" t="s">
+        <v>172</v>
+      </c>
+      <c r="F17" s="149" t="s">
+        <v>153</v>
+      </c>
+      <c r="G17" s="149" t="s">
+        <v>151</v>
+      </c>
+      <c r="H17" s="150" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" s="87" customFormat="1" ht="49.95" customHeight="1">
+      <c r="B18" s="148">
+        <v>46330</v>
+      </c>
+      <c r="C18" s="149">
+        <v>1.2</v>
+      </c>
+      <c r="D18" s="149" t="s">
+        <v>157</v>
+      </c>
+      <c r="E18" s="149" t="s">
+        <v>173</v>
+      </c>
+      <c r="F18" s="149" t="s">
+        <v>152</v>
+      </c>
+      <c r="G18" s="149" t="s">
+        <v>151</v>
+      </c>
+      <c r="H18" s="150" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="19" spans="2:8" s="86" customFormat="1" ht="49.95" customHeight="1">
-      <c r="B19" s="103" t="s">
-        <v>37</v>
-      </c>
-      <c r="C19" s="103" t="s">
-        <v>38</v>
-      </c>
-      <c r="D19" s="103" t="s">
-        <v>41</v>
-      </c>
-      <c r="E19" s="103" t="s">
-        <v>42</v>
-      </c>
-      <c r="F19" s="103" t="s">
-        <v>213</v>
-      </c>
-      <c r="G19" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="H19" s="159" t="s">
-        <v>202</v>
+      <c r="B19" s="149" t="s">
+        <v>174</v>
+      </c>
+      <c r="C19" s="149">
+        <v>1.2</v>
+      </c>
+      <c r="D19" s="149" t="s">
+        <v>175</v>
+      </c>
+      <c r="E19" s="149"/>
+      <c r="F19" s="149" t="s">
+        <v>151</v>
+      </c>
+      <c r="G19" s="149"/>
+      <c r="H19" s="150" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="20" spans="2:8" s="86" customFormat="1" ht="49.95" customHeight="1">
-      <c r="B20" s="103" t="s">
-        <v>43</v>
-      </c>
-      <c r="C20" s="103" t="s">
-        <v>38</v>
-      </c>
-      <c r="D20" s="103" t="s">
-        <v>44</v>
-      </c>
-      <c r="E20" s="103" t="s">
-        <v>45</v>
-      </c>
-      <c r="F20" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="G20" s="103"/>
-      <c r="H20" s="159" t="s">
-        <v>203</v>
-      </c>
+      <c r="B20" s="149"/>
+      <c r="C20" s="149"/>
+      <c r="D20" s="149"/>
+      <c r="E20" s="149"/>
+      <c r="F20" s="149"/>
+      <c r="G20" s="149"/>
+      <c r="H20" s="150"/>
     </row>
     <row r="21" spans="2:8" s="86" customFormat="1" ht="49.95" customHeight="1">
-      <c r="B21" s="103" t="s">
-        <v>46</v>
-      </c>
-      <c r="C21" s="103" t="s">
-        <v>38</v>
-      </c>
-      <c r="D21" s="103" t="s">
-        <v>47</v>
-      </c>
-      <c r="E21" s="103" t="s">
-        <v>48</v>
-      </c>
-      <c r="F21" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="G21" s="103"/>
-      <c r="H21" s="159" t="s">
-        <v>204</v>
-      </c>
+      <c r="B21" s="149"/>
+      <c r="C21" s="149"/>
+      <c r="D21" s="149"/>
+      <c r="E21" s="149"/>
+      <c r="F21" s="149"/>
+      <c r="G21" s="149"/>
+      <c r="H21" s="150"/>
     </row>
     <row r="22" spans="2:8" s="86" customFormat="1" ht="49.95" customHeight="1">
-      <c r="B22" s="103" t="s">
-        <v>46</v>
-      </c>
-      <c r="C22" s="103" t="s">
-        <v>2</v>
-      </c>
-      <c r="D22" s="103" t="s">
-        <v>49</v>
-      </c>
-      <c r="E22" s="103" t="s">
-        <v>50</v>
-      </c>
-      <c r="F22" s="103" t="s">
-        <v>213</v>
-      </c>
-      <c r="G22" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="H22" s="159" t="s">
-        <v>205</v>
-      </c>
+      <c r="B22" s="149"/>
+      <c r="C22" s="149"/>
+      <c r="D22" s="149"/>
+      <c r="E22" s="149"/>
+      <c r="F22" s="149"/>
+      <c r="G22" s="149"/>
+      <c r="H22" s="150"/>
     </row>
     <row r="23" spans="2:8" s="86" customFormat="1" ht="49.95" customHeight="1">
-      <c r="B23" s="103" t="s">
-        <v>51</v>
-      </c>
-      <c r="C23" s="103" t="s">
-        <v>2</v>
-      </c>
-      <c r="D23" s="103" t="s">
-        <v>39</v>
-      </c>
-      <c r="E23" s="103" t="s">
-        <v>52</v>
-      </c>
-      <c r="F23" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="G23" s="103"/>
-      <c r="H23" s="159" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="24" spans="2:8" ht="49.95" customHeight="1">
-      <c r="B24" s="103" t="s">
-        <v>51</v>
-      </c>
-      <c r="C24" s="103" t="s">
-        <v>2</v>
-      </c>
-      <c r="D24" s="103" t="s">
-        <v>53</v>
-      </c>
-      <c r="E24" s="103" t="s">
-        <v>54</v>
-      </c>
-      <c r="F24" s="103" t="s">
-        <v>211</v>
-      </c>
-      <c r="G24" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="H24" s="159" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="25" spans="2:8" ht="49.95" customHeight="1">
-      <c r="B25" s="103" t="s">
-        <v>51</v>
-      </c>
-      <c r="C25" s="103" t="s">
-        <v>2</v>
-      </c>
-      <c r="D25" s="103" t="s">
-        <v>44</v>
-      </c>
-      <c r="E25" s="103" t="s">
-        <v>55</v>
-      </c>
-      <c r="F25" s="103" t="s">
-        <v>213</v>
-      </c>
-      <c r="G25" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="H25" s="159" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="26" spans="2:8" ht="49.95" customHeight="1">
-      <c r="B26" s="160" t="s">
-        <v>56</v>
-      </c>
-      <c r="C26" s="160" t="s">
-        <v>2</v>
-      </c>
-      <c r="D26" s="160" t="s">
-        <v>57</v>
-      </c>
-      <c r="E26" s="160" t="s">
-        <v>58</v>
-      </c>
-      <c r="F26" s="160" t="s">
-        <v>210</v>
-      </c>
-      <c r="G26" s="160" t="s">
-        <v>210</v>
-      </c>
-      <c r="H26" s="161" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="27" spans="2:8" ht="44.4" customHeight="1">
-      <c r="B27" s="162" t="s">
-        <v>215</v>
-      </c>
-      <c r="C27" s="162">
-        <v>1.4</v>
-      </c>
-      <c r="D27" s="162" t="s">
-        <v>216</v>
-      </c>
-      <c r="E27" s="162" t="s">
-        <v>217</v>
-      </c>
-      <c r="F27" s="162" t="s">
-        <v>214</v>
-      </c>
-      <c r="G27" s="162" t="s">
-        <v>210</v>
-      </c>
-      <c r="H27" s="162" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="28" spans="2:8" ht="39" customHeight="1">
-      <c r="B28" s="162" t="s">
-        <v>218</v>
-      </c>
-      <c r="C28" s="162">
-        <v>1.4</v>
-      </c>
-      <c r="D28" s="162" t="s">
-        <v>219</v>
-      </c>
-      <c r="E28" s="162" t="s">
-        <v>220</v>
-      </c>
-      <c r="F28" s="162" t="s">
-        <v>210</v>
-      </c>
-      <c r="G28" s="162" t="s">
-        <v>210</v>
-      </c>
-      <c r="H28" s="162" t="s">
-        <v>222</v>
-      </c>
+      <c r="B23" s="149"/>
+      <c r="C23" s="149"/>
+      <c r="D23" s="149"/>
+      <c r="E23" s="149"/>
+      <c r="F23" s="149"/>
+      <c r="G23" s="149"/>
+      <c r="H23" s="150"/>
+    </row>
+    <row r="24" spans="2:8" s="86" customFormat="1" ht="49.95" customHeight="1">
+      <c r="B24" s="149"/>
+      <c r="C24" s="149"/>
+      <c r="D24" s="149"/>
+      <c r="E24" s="149"/>
+      <c r="F24" s="149"/>
+      <c r="G24" s="149"/>
+      <c r="H24" s="150"/>
+    </row>
+    <row r="25" spans="2:8" s="86" customFormat="1" ht="49.95" customHeight="1">
+      <c r="B25" s="149"/>
+      <c r="C25" s="149"/>
+      <c r="D25" s="149"/>
+      <c r="E25" s="149"/>
+      <c r="F25" s="149"/>
+      <c r="G25" s="149"/>
+      <c r="H25" s="150"/>
+    </row>
+    <row r="26" spans="2:8" s="86" customFormat="1" ht="49.95" customHeight="1">
+      <c r="B26" s="149"/>
+      <c r="C26" s="149"/>
+      <c r="D26" s="149"/>
+      <c r="E26" s="149"/>
+      <c r="F26" s="149"/>
+      <c r="G26" s="149"/>
+      <c r="H26" s="150"/>
+    </row>
+    <row r="27" spans="2:8" ht="49.95" customHeight="1">
+      <c r="B27" s="149"/>
+      <c r="C27" s="149"/>
+      <c r="D27" s="149"/>
+      <c r="E27" s="149"/>
+      <c r="F27" s="149"/>
+      <c r="G27" s="149"/>
+      <c r="H27" s="150"/>
+    </row>
+    <row r="28" spans="2:8" ht="49.95" customHeight="1">
+      <c r="B28" s="149"/>
+      <c r="C28" s="149"/>
+      <c r="D28" s="149"/>
+      <c r="E28" s="149"/>
+      <c r="F28" s="149"/>
+      <c r="G28" s="149"/>
+      <c r="H28" s="150"/>
+    </row>
+    <row r="29" spans="2:8" ht="49.95" customHeight="1">
+      <c r="B29" s="151"/>
+      <c r="C29" s="151"/>
+      <c r="D29" s="151"/>
+      <c r="E29" s="151"/>
+      <c r="F29" s="151"/>
+      <c r="G29" s="151"/>
+      <c r="H29" s="152"/>
+    </row>
+    <row r="30" spans="2:8" ht="44.4" customHeight="1">
+      <c r="B30" s="153"/>
+      <c r="C30" s="153"/>
+      <c r="D30" s="153"/>
+      <c r="E30" s="153"/>
+      <c r="F30" s="153"/>
+      <c r="G30" s="153"/>
+      <c r="H30" s="153"/>
+    </row>
+    <row r="31" spans="2:8" ht="39" customHeight="1">
+      <c r="B31" s="153"/>
+      <c r="C31" s="153"/>
+      <c r="D31" s="153"/>
+      <c r="E31" s="153"/>
+      <c r="F31" s="153"/>
+      <c r="G31" s="153"/>
+      <c r="H31" s="153"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="33" type="noConversion"/>
   <pageMargins left="0.37" right="0.47" top="0.5" bottom="0.38" header="0.5" footer="0.17"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="96" verticalDpi="96"/>
   <headerFooter alignWithMargins="0">
@@ -3036,9 +2797,9 @@
       <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="112"/>
-      <c r="C1" s="112"/>
-      <c r="D1" s="112"/>
+      <c r="B1" s="125"/>
+      <c r="C1" s="125"/>
+      <c r="D1" s="125"/>
       <c r="E1" s="31"/>
       <c r="F1" s="31"/>
       <c r="G1" s="31"/>
@@ -3050,9 +2811,9 @@
     </row>
     <row r="2" spans="1:12" s="75" customFormat="1" ht="11.25" customHeight="1">
       <c r="A2" s="33"/>
-      <c r="B2" s="113"/>
-      <c r="C2" s="113"/>
-      <c r="D2" s="113"/>
+      <c r="B2" s="126"/>
+      <c r="C2" s="126"/>
+      <c r="D2" s="126"/>
       <c r="E2" s="31"/>
       <c r="F2" s="31"/>
       <c r="G2" s="31"/>
@@ -3064,68 +2825,68 @@
     </row>
     <row r="3" spans="1:12" s="76" customFormat="1" ht="15" customHeight="1">
       <c r="A3" s="71" t="s">
-        <v>59</v>
-      </c>
-      <c r="B3" s="139" t="s">
-        <v>60</v>
-      </c>
-      <c r="C3" s="139"/>
-      <c r="D3" s="140"/>
+        <v>15</v>
+      </c>
+      <c r="B3" s="131" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="131"/>
+      <c r="D3" s="132"/>
       <c r="E3" s="35"/>
       <c r="F3" s="35"/>
       <c r="G3" s="35"/>
       <c r="H3" s="35"/>
-      <c r="I3" s="120"/>
-      <c r="J3" s="120"/>
-      <c r="K3" s="120"/>
+      <c r="I3" s="97"/>
+      <c r="J3" s="97"/>
+      <c r="K3" s="97"/>
       <c r="L3" s="81"/>
     </row>
     <row r="4" spans="1:12" s="76" customFormat="1" ht="13.2">
       <c r="A4" s="37" t="s">
-        <v>61</v>
-      </c>
-      <c r="B4" s="141" t="s">
-        <v>62</v>
-      </c>
-      <c r="C4" s="142"/>
-      <c r="D4" s="143"/>
+        <v>17</v>
+      </c>
+      <c r="B4" s="98" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="99"/>
+      <c r="D4" s="100"/>
       <c r="E4" s="35"/>
       <c r="F4" s="35"/>
       <c r="G4" s="35"/>
       <c r="H4" s="35"/>
-      <c r="I4" s="120"/>
-      <c r="J4" s="120"/>
-      <c r="K4" s="120"/>
+      <c r="I4" s="97"/>
+      <c r="J4" s="97"/>
+      <c r="K4" s="97"/>
       <c r="L4" s="81"/>
     </row>
     <row r="5" spans="1:12" s="77" customFormat="1" ht="26.4">
       <c r="A5" s="37" t="s">
-        <v>63</v>
-      </c>
-      <c r="B5" s="144" t="s">
-        <v>64</v>
-      </c>
-      <c r="C5" s="145"/>
-      <c r="D5" s="146"/>
+        <v>19</v>
+      </c>
+      <c r="B5" s="101" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="102"/>
+      <c r="D5" s="103"/>
       <c r="E5" s="39"/>
       <c r="F5" s="39"/>
       <c r="G5" s="39"/>
       <c r="H5" s="39"/>
-      <c r="I5" s="147"/>
-      <c r="J5" s="147"/>
-      <c r="K5" s="147"/>
+      <c r="I5" s="104"/>
+      <c r="J5" s="104"/>
+      <c r="K5" s="104"/>
       <c r="L5" s="82"/>
     </row>
     <row r="6" spans="1:12" s="76" customFormat="1" ht="15" customHeight="1">
       <c r="A6" s="40" t="s">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="B6" s="41">
         <f>COUNTIF(J12:J17,"Pass")</f>
         <v>3</v>
       </c>
       <c r="C6" s="42" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="D6" s="43">
         <f>COUNTIF(J10:J736,"Pending")</f>
@@ -3135,21 +2896,21 @@
       <c r="F6" s="36"/>
       <c r="G6" s="36"/>
       <c r="H6" s="36"/>
-      <c r="I6" s="120"/>
-      <c r="J6" s="120"/>
-      <c r="K6" s="120"/>
+      <c r="I6" s="97"/>
+      <c r="J6" s="97"/>
+      <c r="K6" s="97"/>
       <c r="L6" s="81"/>
     </row>
     <row r="7" spans="1:12" s="76" customFormat="1" ht="15" customHeight="1">
       <c r="A7" s="44" t="s">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="B7" s="45">
         <f>COUNTIF(J12:J17,"Fail")</f>
         <v>0</v>
       </c>
       <c r="C7" s="46" t="s">
-        <v>68</v>
+        <v>24</v>
       </c>
       <c r="D7" s="47">
         <f>COUNTA(A12:A17)-15</f>
@@ -3159,16 +2920,16 @@
       <c r="F7" s="48"/>
       <c r="G7" s="48"/>
       <c r="H7" s="48"/>
-      <c r="I7" s="120"/>
-      <c r="J7" s="120"/>
-      <c r="K7" s="120"/>
+      <c r="I7" s="97"/>
+      <c r="J7" s="97"/>
+      <c r="K7" s="97"/>
       <c r="L7" s="81"/>
     </row>
     <row r="8" spans="1:12" s="76" customFormat="1" ht="15" customHeight="1">
-      <c r="A8" s="121"/>
-      <c r="B8" s="121"/>
-      <c r="C8" s="121"/>
-      <c r="D8" s="121"/>
+      <c r="A8" s="107"/>
+      <c r="B8" s="107"/>
+      <c r="C8" s="107"/>
+      <c r="D8" s="107"/>
       <c r="E8" s="36"/>
       <c r="F8" s="36"/>
       <c r="G8" s="36"/>
@@ -3179,106 +2940,106 @@
       <c r="L8" s="81"/>
     </row>
     <row r="9" spans="1:12" s="78" customFormat="1" ht="12" customHeight="1">
-      <c r="A9" s="127" t="s">
-        <v>69</v>
-      </c>
-      <c r="B9" s="129" t="s">
-        <v>70</v>
-      </c>
-      <c r="C9" s="127" t="s">
-        <v>71</v>
-      </c>
-      <c r="D9" s="133" t="s">
-        <v>72</v>
-      </c>
-      <c r="E9" s="134"/>
-      <c r="F9" s="134"/>
-      <c r="G9" s="135"/>
-      <c r="H9" s="131" t="s">
-        <v>73</v>
-      </c>
-      <c r="I9" s="132" t="s">
-        <v>74</v>
-      </c>
-      <c r="J9" s="132" t="s">
-        <v>75</v>
-      </c>
-      <c r="K9" s="132" t="s">
-        <v>76</v>
+      <c r="A9" s="113" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="115" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="119" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" s="120"/>
+      <c r="F9" s="120"/>
+      <c r="G9" s="121"/>
+      <c r="H9" s="117" t="s">
+        <v>29</v>
+      </c>
+      <c r="I9" s="118" t="s">
+        <v>30</v>
+      </c>
+      <c r="J9" s="118" t="s">
+        <v>31</v>
+      </c>
+      <c r="K9" s="118" t="s">
+        <v>32</v>
       </c>
       <c r="L9" s="83"/>
     </row>
     <row r="10" spans="1:12" s="76" customFormat="1" ht="12" customHeight="1">
-      <c r="A10" s="128"/>
-      <c r="B10" s="130"/>
-      <c r="C10" s="128"/>
-      <c r="D10" s="136"/>
-      <c r="E10" s="137"/>
-      <c r="F10" s="137"/>
-      <c r="G10" s="138"/>
-      <c r="H10" s="127"/>
-      <c r="I10" s="127"/>
-      <c r="J10" s="127"/>
-      <c r="K10" s="127"/>
+      <c r="A10" s="114"/>
+      <c r="B10" s="116"/>
+      <c r="C10" s="114"/>
+      <c r="D10" s="122"/>
+      <c r="E10" s="123"/>
+      <c r="F10" s="123"/>
+      <c r="G10" s="124"/>
+      <c r="H10" s="113"/>
+      <c r="I10" s="113"/>
+      <c r="J10" s="113"/>
+      <c r="K10" s="113"/>
       <c r="L10" s="81"/>
     </row>
     <row r="11" spans="1:12" s="79" customFormat="1" ht="15">
-      <c r="A11" s="122"/>
-      <c r="B11" s="122"/>
-      <c r="C11" s="122"/>
-      <c r="D11" s="122"/>
-      <c r="E11" s="122"/>
-      <c r="F11" s="122"/>
-      <c r="G11" s="122"/>
-      <c r="H11" s="122"/>
-      <c r="I11" s="122"/>
-      <c r="J11" s="122"/>
-      <c r="K11" s="123"/>
+      <c r="A11" s="108"/>
+      <c r="B11" s="108"/>
+      <c r="C11" s="108"/>
+      <c r="D11" s="108"/>
+      <c r="E11" s="108"/>
+      <c r="F11" s="108"/>
+      <c r="G11" s="108"/>
+      <c r="H11" s="108"/>
+      <c r="I11" s="108"/>
+      <c r="J11" s="108"/>
+      <c r="K11" s="109"/>
     </row>
     <row r="12" spans="1:12" s="80" customFormat="1" ht="13.2">
-      <c r="A12" s="124" t="s">
-        <v>77</v>
-      </c>
-      <c r="B12" s="125"/>
-      <c r="C12" s="125"/>
-      <c r="D12" s="125"/>
-      <c r="E12" s="125"/>
-      <c r="F12" s="125"/>
-      <c r="G12" s="125"/>
-      <c r="H12" s="125"/>
-      <c r="I12" s="125"/>
-      <c r="J12" s="125"/>
-      <c r="K12" s="126"/>
+      <c r="A12" s="110" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="111"/>
+      <c r="C12" s="111"/>
+      <c r="D12" s="111"/>
+      <c r="E12" s="111"/>
+      <c r="F12" s="111"/>
+      <c r="G12" s="111"/>
+      <c r="H12" s="111"/>
+      <c r="I12" s="111"/>
+      <c r="J12" s="111"/>
+      <c r="K12" s="112"/>
     </row>
     <row r="13" spans="1:12" s="80" customFormat="1" ht="79.2" outlineLevel="1">
       <c r="A13" s="52" t="s">
-        <v>78</v>
+        <v>34</v>
       </c>
       <c r="B13" s="53" t="s">
-        <v>79</v>
+        <v>35</v>
       </c>
       <c r="C13" s="54" t="s">
-        <v>80</v>
-      </c>
-      <c r="D13" s="114" t="s">
-        <v>81</v>
-      </c>
-      <c r="E13" s="115"/>
-      <c r="F13" s="115"/>
+        <v>36</v>
+      </c>
+      <c r="D13" s="127" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" s="128"/>
+      <c r="F13" s="128"/>
       <c r="G13" s="59"/>
       <c r="H13" s="56"/>
       <c r="I13" s="57"/>
       <c r="J13" s="54" t="s">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="K13" s="54"/>
     </row>
     <row r="14" spans="1:12" s="80" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A14" s="116" t="s">
-        <v>82</v>
-      </c>
-      <c r="B14" s="117"/>
-      <c r="C14" s="117"/>
+      <c r="A14" s="129" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="130"/>
+      <c r="C14" s="130"/>
       <c r="D14" s="50"/>
       <c r="E14" s="50"/>
       <c r="F14" s="50"/>
@@ -3290,33 +3051,33 @@
     </row>
     <row r="15" spans="1:12" s="80" customFormat="1" ht="63.75" customHeight="1" outlineLevel="1">
       <c r="A15" s="52" t="s">
-        <v>83</v>
+        <v>39</v>
       </c>
       <c r="B15" s="84" t="s">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="C15" s="63" t="s">
-        <v>85</v>
-      </c>
-      <c r="D15" s="118" t="s">
-        <v>86</v>
-      </c>
-      <c r="E15" s="115"/>
-      <c r="F15" s="115"/>
+        <v>41</v>
+      </c>
+      <c r="D15" s="105" t="s">
+        <v>42</v>
+      </c>
+      <c r="E15" s="128"/>
+      <c r="F15" s="128"/>
       <c r="G15" s="59"/>
       <c r="H15" s="56"/>
       <c r="I15" s="58"/>
       <c r="J15" s="54" t="s">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="K15" s="54"/>
     </row>
     <row r="16" spans="1:12" s="80" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A16" s="116" t="s">
-        <v>87</v>
-      </c>
-      <c r="B16" s="117"/>
-      <c r="C16" s="117"/>
+      <c r="A16" s="129" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="130"/>
+      <c r="C16" s="130"/>
       <c r="D16" s="50"/>
       <c r="E16" s="50"/>
       <c r="F16" s="50"/>
@@ -3328,24 +3089,24 @@
     </row>
     <row r="17" spans="1:11" s="80" customFormat="1" ht="63.75" customHeight="1" outlineLevel="1">
       <c r="A17" s="52" t="s">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="B17" s="85" t="s">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="C17" s="54" t="s">
-        <v>89</v>
-      </c>
-      <c r="D17" s="118" t="s">
-        <v>90</v>
-      </c>
-      <c r="E17" s="119"/>
-      <c r="F17" s="119"/>
+        <v>45</v>
+      </c>
+      <c r="D17" s="105" t="s">
+        <v>46</v>
+      </c>
+      <c r="E17" s="106"/>
+      <c r="F17" s="106"/>
       <c r="G17" s="59"/>
       <c r="H17" s="56"/>
       <c r="I17" s="58"/>
       <c r="J17" s="54" t="s">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="K17" s="54"/>
     </row>
@@ -3389,11 +3150,12 @@
     <row r="55" ht="12" customHeight="1"/>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="B1:D2"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="B3:D3"/>
     <mergeCell ref="D17:F17"/>
     <mergeCell ref="I6:K6"/>
     <mergeCell ref="I7:K7"/>
@@ -3408,12 +3170,11 @@
     <mergeCell ref="J9:J10"/>
     <mergeCell ref="K9:K10"/>
     <mergeCell ref="D9:G10"/>
-    <mergeCell ref="B1:D2"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="I5:K5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -3422,6 +3183,405 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6899EEAB-D6EB-4EA8-B404-49C0A5FE4EB8}">
+  <dimension ref="A1:L55"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.8" outlineLevelRow="1"/>
+  <cols>
+    <col min="1" max="1" width="15.6640625" customWidth="1"/>
+    <col min="2" max="2" width="18.109375" customWidth="1"/>
+    <col min="3" max="3" width="42.109375" customWidth="1"/>
+    <col min="6" max="6" width="23.6640625" customWidth="1"/>
+    <col min="7" max="7" width="18.44140625" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="38" customWidth="1"/>
+    <col min="9" max="9" width="17.109375" customWidth="1"/>
+    <col min="10" max="10" width="8.77734375" style="6"/>
+    <col min="11" max="11" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" s="75" customFormat="1" ht="12.75" customHeight="1">
+      <c r="A1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="125"/>
+      <c r="C1" s="125"/>
+      <c r="D1" s="125"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="31"/>
+      <c r="L1" s="33"/>
+    </row>
+    <row r="2" spans="1:12" s="75" customFormat="1" ht="11.25" customHeight="1" thickBot="1">
+      <c r="A2" s="33"/>
+      <c r="B2" s="126"/>
+      <c r="C2" s="126"/>
+      <c r="D2" s="126"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="31"/>
+      <c r="L2" s="33"/>
+    </row>
+    <row r="3" spans="1:12" s="76" customFormat="1" ht="15" customHeight="1">
+      <c r="A3" s="71" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="131" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="131"/>
+      <c r="D3" s="132"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="97"/>
+      <c r="J3" s="97"/>
+      <c r="K3" s="97"/>
+      <c r="L3" s="81"/>
+    </row>
+    <row r="4" spans="1:12" s="76" customFormat="1" ht="13.2" customHeight="1">
+      <c r="A4" s="37" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="98" t="s">
+        <v>155</v>
+      </c>
+      <c r="C4" s="99"/>
+      <c r="D4" s="100"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="35"/>
+      <c r="I4" s="97"/>
+      <c r="J4" s="97"/>
+      <c r="K4" s="97"/>
+      <c r="L4" s="81"/>
+    </row>
+    <row r="5" spans="1:12" s="77" customFormat="1" ht="26.4">
+      <c r="A5" s="37" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="101" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="102"/>
+      <c r="D5" s="103"/>
+      <c r="E5" s="39"/>
+      <c r="F5" s="39"/>
+      <c r="G5" s="39"/>
+      <c r="H5" s="39"/>
+      <c r="I5" s="104"/>
+      <c r="J5" s="104"/>
+      <c r="K5" s="104"/>
+      <c r="L5" s="82"/>
+    </row>
+    <row r="6" spans="1:12" s="76" customFormat="1" ht="15" customHeight="1">
+      <c r="A6" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="41">
+        <v>0</v>
+      </c>
+      <c r="C6" s="42" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="43">
+        <v>5</v>
+      </c>
+      <c r="E6" s="36"/>
+      <c r="F6" s="36"/>
+      <c r="G6" s="36"/>
+      <c r="H6" s="36"/>
+      <c r="I6" s="97"/>
+      <c r="J6" s="97"/>
+      <c r="K6" s="97"/>
+      <c r="L6" s="81"/>
+    </row>
+    <row r="7" spans="1:12" s="76" customFormat="1" ht="15" customHeight="1" thickBot="1">
+      <c r="A7" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="45">
+        <v>0</v>
+      </c>
+      <c r="C7" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="47">
+        <v>10</v>
+      </c>
+      <c r="E7" s="48"/>
+      <c r="F7" s="48"/>
+      <c r="G7" s="48"/>
+      <c r="H7" s="48"/>
+      <c r="I7" s="97"/>
+      <c r="J7" s="97"/>
+      <c r="K7" s="97"/>
+      <c r="L7" s="81"/>
+    </row>
+    <row r="8" spans="1:12" s="76" customFormat="1" ht="15" customHeight="1">
+      <c r="A8" s="107"/>
+      <c r="B8" s="107"/>
+      <c r="C8" s="107"/>
+      <c r="D8" s="107"/>
+      <c r="E8" s="36"/>
+      <c r="F8" s="36"/>
+      <c r="G8" s="36"/>
+      <c r="H8" s="36"/>
+      <c r="I8" s="36"/>
+      <c r="J8" s="49"/>
+      <c r="K8" s="49"/>
+      <c r="L8" s="81"/>
+    </row>
+    <row r="9" spans="1:12" s="78" customFormat="1" ht="12" customHeight="1">
+      <c r="A9" s="113" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="115" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="119" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" s="120"/>
+      <c r="F9" s="120"/>
+      <c r="G9" s="121"/>
+      <c r="H9" s="117" t="s">
+        <v>29</v>
+      </c>
+      <c r="I9" s="118" t="s">
+        <v>30</v>
+      </c>
+      <c r="J9" s="118" t="s">
+        <v>31</v>
+      </c>
+      <c r="K9" s="118" t="s">
+        <v>32</v>
+      </c>
+      <c r="L9" s="83"/>
+    </row>
+    <row r="10" spans="1:12" s="76" customFormat="1" ht="12" customHeight="1">
+      <c r="A10" s="114"/>
+      <c r="B10" s="116"/>
+      <c r="C10" s="114"/>
+      <c r="D10" s="122"/>
+      <c r="E10" s="123"/>
+      <c r="F10" s="123"/>
+      <c r="G10" s="124"/>
+      <c r="H10" s="113"/>
+      <c r="I10" s="113"/>
+      <c r="J10" s="113"/>
+      <c r="K10" s="113"/>
+      <c r="L10" s="81"/>
+    </row>
+    <row r="11" spans="1:12" s="79" customFormat="1" ht="15">
+      <c r="A11" s="108"/>
+      <c r="B11" s="108"/>
+      <c r="C11" s="108"/>
+      <c r="D11" s="108"/>
+      <c r="E11" s="108"/>
+      <c r="F11" s="108"/>
+      <c r="G11" s="108"/>
+      <c r="H11" s="108"/>
+      <c r="I11" s="108"/>
+      <c r="J11" s="108"/>
+      <c r="K11" s="109"/>
+    </row>
+    <row r="12" spans="1:12" s="80" customFormat="1" ht="13.2">
+      <c r="A12" s="110" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="111"/>
+      <c r="C12" s="111"/>
+      <c r="D12" s="111"/>
+      <c r="E12" s="111"/>
+      <c r="F12" s="111"/>
+      <c r="G12" s="111"/>
+      <c r="H12" s="111"/>
+      <c r="I12" s="111"/>
+      <c r="J12" s="111"/>
+      <c r="K12" s="112"/>
+    </row>
+    <row r="13" spans="1:12" s="80" customFormat="1" ht="79.2" outlineLevel="1">
+      <c r="A13" s="52" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="53" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" s="54" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" s="127" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" s="128"/>
+      <c r="F13" s="128"/>
+      <c r="G13" s="59"/>
+      <c r="H13" s="56"/>
+      <c r="I13" s="57"/>
+      <c r="J13" s="54" t="s">
+        <v>21</v>
+      </c>
+      <c r="K13" s="54"/>
+    </row>
+    <row r="14" spans="1:12" s="80" customFormat="1" ht="13.2" outlineLevel="1">
+      <c r="A14" s="129" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="130"/>
+      <c r="C14" s="130"/>
+      <c r="D14" s="50"/>
+      <c r="E14" s="50"/>
+      <c r="F14" s="50"/>
+      <c r="G14" s="50"/>
+      <c r="H14" s="50"/>
+      <c r="I14" s="50"/>
+      <c r="J14" s="50"/>
+      <c r="K14" s="51"/>
+    </row>
+    <row r="15" spans="1:12" s="80" customFormat="1" ht="63.75" customHeight="1" outlineLevel="1">
+      <c r="A15" s="52" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="84" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" s="63" t="s">
+        <v>41</v>
+      </c>
+      <c r="D15" s="105" t="s">
+        <v>42</v>
+      </c>
+      <c r="E15" s="128"/>
+      <c r="F15" s="128"/>
+      <c r="G15" s="59"/>
+      <c r="H15" s="56"/>
+      <c r="I15" s="58"/>
+      <c r="J15" s="54" t="s">
+        <v>21</v>
+      </c>
+      <c r="K15" s="54"/>
+    </row>
+    <row r="16" spans="1:12" s="80" customFormat="1" ht="13.2" outlineLevel="1">
+      <c r="A16" s="129" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="130"/>
+      <c r="C16" s="130"/>
+      <c r="D16" s="50"/>
+      <c r="E16" s="50"/>
+      <c r="F16" s="50"/>
+      <c r="G16" s="50"/>
+      <c r="H16" s="50"/>
+      <c r="I16" s="50"/>
+      <c r="J16" s="50"/>
+      <c r="K16" s="51"/>
+    </row>
+    <row r="17" spans="1:11" s="80" customFormat="1" ht="63.75" customHeight="1" outlineLevel="1">
+      <c r="A17" s="52" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="85" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" s="54" t="s">
+        <v>45</v>
+      </c>
+      <c r="D17" s="105" t="s">
+        <v>46</v>
+      </c>
+      <c r="E17" s="106"/>
+      <c r="F17" s="106"/>
+      <c r="G17" s="59"/>
+      <c r="H17" s="56"/>
+      <c r="I17" s="58"/>
+      <c r="J17" s="54" t="s">
+        <v>21</v>
+      </c>
+      <c r="K17" s="54"/>
+    </row>
+    <row r="18" spans="1:11" ht="12" customHeight="1"/>
+    <row r="19" spans="1:11" ht="12" customHeight="1"/>
+    <row r="20" spans="1:11" ht="12" customHeight="1"/>
+    <row r="21" spans="1:11" ht="12" customHeight="1"/>
+    <row r="22" spans="1:11" ht="12" customHeight="1"/>
+    <row r="23" spans="1:11" ht="12" customHeight="1"/>
+    <row r="24" spans="1:11" ht="12" customHeight="1"/>
+    <row r="25" spans="1:11" ht="12" customHeight="1"/>
+    <row r="26" spans="1:11" ht="12" customHeight="1"/>
+    <row r="27" spans="1:11" ht="12" customHeight="1"/>
+    <row r="28" spans="1:11" ht="12" customHeight="1"/>
+    <row r="29" spans="1:11" ht="12" customHeight="1"/>
+    <row r="30" spans="1:11" ht="12" customHeight="1"/>
+    <row r="31" spans="1:11" ht="12" customHeight="1"/>
+    <row r="32" spans="1:11" ht="12" customHeight="1"/>
+    <row r="33" ht="12" customHeight="1"/>
+    <row r="34" ht="12" customHeight="1"/>
+    <row r="35" ht="12" customHeight="1"/>
+    <row r="36" ht="12" customHeight="1"/>
+    <row r="37" ht="12" customHeight="1"/>
+    <row r="38" ht="12" customHeight="1"/>
+    <row r="39" ht="12" customHeight="1"/>
+    <row r="40" ht="12" customHeight="1"/>
+    <row r="41" ht="12" customHeight="1"/>
+    <row r="42" ht="12" customHeight="1"/>
+    <row r="43" ht="12" customHeight="1"/>
+    <row r="44" ht="12" customHeight="1"/>
+    <row r="45" ht="12" customHeight="1"/>
+    <row r="46" ht="12" customHeight="1"/>
+    <row r="47" ht="12" customHeight="1"/>
+    <row r="48" ht="12" customHeight="1"/>
+    <row r="49" ht="12" customHeight="1"/>
+    <row r="50" ht="12" customHeight="1"/>
+    <row r="51" ht="12" customHeight="1"/>
+    <row r="52" ht="12" customHeight="1"/>
+    <row r="53" ht="12" customHeight="1"/>
+    <row r="54" ht="12" customHeight="1"/>
+    <row r="55" ht="12" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="25">
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="K9:K10"/>
+    <mergeCell ref="A11:K11"/>
+    <mergeCell ref="A12:K12"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D9:G10"/>
+    <mergeCell ref="H9:H10"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="B1:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="I5:K5"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K36"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.2"/>
@@ -3436,7 +3596,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="69" t="s">
-        <v>91</v>
+        <v>47</v>
       </c>
       <c r="C1" s="69"/>
       <c r="D1" s="69"/>
@@ -3463,64 +3623,64 @@
     </row>
     <row r="3" spans="1:11" ht="13.8">
       <c r="A3" s="71" t="s">
-        <v>59</v>
-      </c>
-      <c r="B3" s="139" t="s">
-        <v>92</v>
-      </c>
-      <c r="C3" s="139"/>
-      <c r="D3" s="140"/>
+        <v>15</v>
+      </c>
+      <c r="B3" s="131" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="131"/>
+      <c r="D3" s="132"/>
       <c r="E3" s="35"/>
       <c r="F3" s="35"/>
       <c r="G3" s="35"/>
       <c r="H3" s="35"/>
-      <c r="I3" s="120"/>
-      <c r="J3" s="120"/>
-      <c r="K3" s="120"/>
+      <c r="I3" s="97"/>
+      <c r="J3" s="97"/>
+      <c r="K3" s="97"/>
     </row>
     <row r="4" spans="1:11" ht="13.8">
       <c r="A4" s="37" t="s">
-        <v>61</v>
-      </c>
-      <c r="B4" s="141" t="s">
-        <v>93</v>
-      </c>
-      <c r="C4" s="142"/>
-      <c r="D4" s="143"/>
+        <v>17</v>
+      </c>
+      <c r="B4" s="98" t="s">
+        <v>49</v>
+      </c>
+      <c r="C4" s="99"/>
+      <c r="D4" s="100"/>
       <c r="E4" s="35"/>
       <c r="F4" s="35"/>
       <c r="G4" s="35"/>
       <c r="H4" s="35"/>
-      <c r="I4" s="120"/>
-      <c r="J4" s="120"/>
-      <c r="K4" s="120"/>
+      <c r="I4" s="97"/>
+      <c r="J4" s="97"/>
+      <c r="K4" s="97"/>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="37" t="s">
-        <v>63</v>
-      </c>
-      <c r="B5" s="144" t="s">
-        <v>64</v>
-      </c>
-      <c r="C5" s="145"/>
-      <c r="D5" s="146"/>
+        <v>19</v>
+      </c>
+      <c r="B5" s="101" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="102"/>
+      <c r="D5" s="103"/>
       <c r="E5" s="39"/>
       <c r="F5" s="39"/>
       <c r="G5" s="39"/>
       <c r="H5" s="39"/>
-      <c r="I5" s="147"/>
-      <c r="J5" s="147"/>
-      <c r="K5" s="147"/>
+      <c r="I5" s="104"/>
+      <c r="J5" s="104"/>
+      <c r="K5" s="104"/>
     </row>
     <row r="6" spans="1:11" ht="13.8">
       <c r="A6" s="40" t="s">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="B6" s="41">
         <v>0</v>
       </c>
       <c r="C6" s="42" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="D6" s="43">
         <v>5</v>
@@ -3529,19 +3689,19 @@
       <c r="F6" s="36"/>
       <c r="G6" s="36"/>
       <c r="H6" s="36"/>
-      <c r="I6" s="120"/>
-      <c r="J6" s="120"/>
-      <c r="K6" s="120"/>
+      <c r="I6" s="97"/>
+      <c r="J6" s="97"/>
+      <c r="K6" s="97"/>
     </row>
     <row r="7" spans="1:11" ht="13.8">
       <c r="A7" s="44" t="s">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="B7" s="45">
         <v>0</v>
       </c>
       <c r="C7" s="46" t="s">
-        <v>68</v>
+        <v>24</v>
       </c>
       <c r="D7" s="47">
         <v>10</v>
@@ -3550,15 +3710,15 @@
       <c r="F7" s="48"/>
       <c r="G7" s="48"/>
       <c r="H7" s="48"/>
-      <c r="I7" s="120"/>
-      <c r="J7" s="120"/>
-      <c r="K7" s="120"/>
+      <c r="I7" s="97"/>
+      <c r="J7" s="97"/>
+      <c r="K7" s="97"/>
     </row>
     <row r="8" spans="1:11" ht="13.8">
-      <c r="A8" s="121"/>
-      <c r="B8" s="121"/>
-      <c r="C8" s="121"/>
-      <c r="D8" s="121"/>
+      <c r="A8" s="107"/>
+      <c r="B8" s="107"/>
+      <c r="C8" s="107"/>
+      <c r="D8" s="107"/>
       <c r="E8" s="36"/>
       <c r="F8" s="36"/>
       <c r="G8" s="36"/>
@@ -3568,142 +3728,142 @@
       <c r="K8" s="49"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="127" t="s">
-        <v>69</v>
-      </c>
-      <c r="B9" s="129" t="s">
-        <v>70</v>
-      </c>
-      <c r="C9" s="127" t="s">
-        <v>71</v>
-      </c>
-      <c r="D9" s="133" t="s">
-        <v>72</v>
-      </c>
-      <c r="E9" s="134"/>
-      <c r="F9" s="134"/>
-      <c r="G9" s="135"/>
-      <c r="H9" s="131" t="s">
-        <v>73</v>
-      </c>
-      <c r="I9" s="132" t="s">
-        <v>74</v>
-      </c>
-      <c r="J9" s="132" t="s">
-        <v>75</v>
-      </c>
-      <c r="K9" s="132" t="s">
-        <v>76</v>
+      <c r="A9" s="113" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="115" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="119" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" s="120"/>
+      <c r="F9" s="120"/>
+      <c r="G9" s="121"/>
+      <c r="H9" s="117" t="s">
+        <v>29</v>
+      </c>
+      <c r="I9" s="118" t="s">
+        <v>30</v>
+      </c>
+      <c r="J9" s="118" t="s">
+        <v>31</v>
+      </c>
+      <c r="K9" s="118" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="128"/>
-      <c r="B10" s="130"/>
-      <c r="C10" s="128"/>
-      <c r="D10" s="136"/>
-      <c r="E10" s="137"/>
-      <c r="F10" s="137"/>
-      <c r="G10" s="138"/>
-      <c r="H10" s="127"/>
-      <c r="I10" s="127"/>
-      <c r="J10" s="127"/>
-      <c r="K10" s="127"/>
+      <c r="A10" s="114"/>
+      <c r="B10" s="116"/>
+      <c r="C10" s="114"/>
+      <c r="D10" s="122"/>
+      <c r="E10" s="123"/>
+      <c r="F10" s="123"/>
+      <c r="G10" s="124"/>
+      <c r="H10" s="113"/>
+      <c r="I10" s="113"/>
+      <c r="J10" s="113"/>
+      <c r="K10" s="113"/>
     </row>
     <row r="11" spans="1:11" ht="15">
-      <c r="A11" s="122"/>
-      <c r="B11" s="122"/>
-      <c r="C11" s="122"/>
-      <c r="D11" s="122"/>
-      <c r="E11" s="122"/>
-      <c r="F11" s="122"/>
-      <c r="G11" s="122"/>
-      <c r="H11" s="122"/>
-      <c r="I11" s="122"/>
-      <c r="J11" s="122"/>
-      <c r="K11" s="123"/>
+      <c r="A11" s="108"/>
+      <c r="B11" s="108"/>
+      <c r="C11" s="108"/>
+      <c r="D11" s="108"/>
+      <c r="E11" s="108"/>
+      <c r="F11" s="108"/>
+      <c r="G11" s="108"/>
+      <c r="H11" s="108"/>
+      <c r="I11" s="108"/>
+      <c r="J11" s="108"/>
+      <c r="K11" s="109"/>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="124" t="s">
-        <v>94</v>
-      </c>
-      <c r="B12" s="125"/>
-      <c r="C12" s="125"/>
-      <c r="D12" s="125"/>
-      <c r="E12" s="125"/>
-      <c r="F12" s="125"/>
-      <c r="G12" s="125"/>
-      <c r="H12" s="125"/>
-      <c r="I12" s="125"/>
-      <c r="J12" s="125"/>
-      <c r="K12" s="126"/>
+      <c r="A12" s="110" t="s">
+        <v>50</v>
+      </c>
+      <c r="B12" s="111"/>
+      <c r="C12" s="111"/>
+      <c r="D12" s="111"/>
+      <c r="E12" s="111"/>
+      <c r="F12" s="111"/>
+      <c r="G12" s="111"/>
+      <c r="H12" s="111"/>
+      <c r="I12" s="111"/>
+      <c r="J12" s="111"/>
+      <c r="K12" s="112"/>
     </row>
     <row r="13" spans="1:11" ht="105.6">
       <c r="A13" s="52" t="s">
-        <v>78</v>
+        <v>34</v>
       </c>
       <c r="B13" s="54" t="s">
-        <v>95</v>
+        <v>51</v>
       </c>
       <c r="C13" s="54" t="s">
-        <v>96</v>
-      </c>
-      <c r="D13" s="149" t="s">
-        <v>97</v>
-      </c>
-      <c r="E13" s="115"/>
-      <c r="F13" s="115"/>
-      <c r="G13" s="148"/>
+        <v>52</v>
+      </c>
+      <c r="D13" s="134" t="s">
+        <v>53</v>
+      </c>
+      <c r="E13" s="128"/>
+      <c r="F13" s="128"/>
+      <c r="G13" s="133"/>
       <c r="H13" s="56"/>
       <c r="I13" s="57"/>
       <c r="J13" s="54" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="K13" s="54"/>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="124" t="s">
-        <v>98</v>
-      </c>
-      <c r="B14" s="125"/>
-      <c r="C14" s="125"/>
-      <c r="D14" s="125"/>
-      <c r="E14" s="125"/>
-      <c r="F14" s="125"/>
-      <c r="G14" s="125"/>
-      <c r="H14" s="125"/>
-      <c r="I14" s="125"/>
-      <c r="J14" s="125"/>
-      <c r="K14" s="126"/>
+      <c r="A14" s="110" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" s="111"/>
+      <c r="C14" s="111"/>
+      <c r="D14" s="111"/>
+      <c r="E14" s="111"/>
+      <c r="F14" s="111"/>
+      <c r="G14" s="111"/>
+      <c r="H14" s="111"/>
+      <c r="I14" s="111"/>
+      <c r="J14" s="111"/>
+      <c r="K14" s="112"/>
     </row>
     <row r="15" spans="1:11" ht="92.4">
       <c r="A15" s="72" t="s">
-        <v>83</v>
+        <v>39</v>
       </c>
       <c r="B15" s="72" t="s">
-        <v>99</v>
+        <v>55</v>
       </c>
       <c r="C15" s="72" t="s">
-        <v>100</v>
-      </c>
-      <c r="D15" s="150" t="s">
-        <v>101</v>
-      </c>
-      <c r="E15" s="151"/>
-      <c r="F15" s="151"/>
-      <c r="G15" s="152"/>
+        <v>56</v>
+      </c>
+      <c r="D15" s="135" t="s">
+        <v>57</v>
+      </c>
+      <c r="E15" s="136"/>
+      <c r="F15" s="136"/>
+      <c r="G15" s="137"/>
       <c r="H15" s="73"/>
       <c r="I15" s="73"/>
       <c r="J15" s="74" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="K15" s="73"/>
     </row>
     <row r="16" spans="1:11">
-      <c r="A16" s="124" t="s">
-        <v>102</v>
-      </c>
-      <c r="B16" s="125"/>
-      <c r="C16" s="125"/>
+      <c r="A16" s="110" t="s">
+        <v>58</v>
+      </c>
+      <c r="B16" s="111"/>
+      <c r="C16" s="111"/>
       <c r="D16" s="50"/>
       <c r="E16" s="50"/>
       <c r="F16" s="50"/>
@@ -3715,33 +3875,33 @@
     </row>
     <row r="17" spans="1:11" ht="26.4">
       <c r="A17" s="52" t="s">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="B17" s="63" t="s">
-        <v>103</v>
+        <v>59</v>
       </c>
       <c r="C17" s="63" t="s">
-        <v>104</v>
-      </c>
-      <c r="D17" s="149" t="s">
-        <v>105</v>
-      </c>
-      <c r="E17" s="153"/>
-      <c r="F17" s="153"/>
-      <c r="G17" s="154"/>
+        <v>60</v>
+      </c>
+      <c r="D17" s="134" t="s">
+        <v>61</v>
+      </c>
+      <c r="E17" s="138"/>
+      <c r="F17" s="138"/>
+      <c r="G17" s="139"/>
       <c r="H17" s="56"/>
       <c r="I17" s="58"/>
       <c r="J17" s="54" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="K17" s="54"/>
     </row>
     <row r="18" spans="1:11">
-      <c r="A18" s="124" t="s">
-        <v>106</v>
-      </c>
-      <c r="B18" s="125"/>
-      <c r="C18" s="125"/>
+      <c r="A18" s="110" t="s">
+        <v>62</v>
+      </c>
+      <c r="B18" s="111"/>
+      <c r="C18" s="111"/>
       <c r="D18" s="50"/>
       <c r="E18" s="50"/>
       <c r="F18" s="50"/>
@@ -3753,33 +3913,33 @@
     </row>
     <row r="19" spans="1:11" ht="39.6">
       <c r="A19" s="52" t="s">
-        <v>107</v>
+        <v>63</v>
       </c>
       <c r="B19" s="54" t="s">
-        <v>108</v>
+        <v>64</v>
       </c>
       <c r="C19" s="54" t="s">
-        <v>109</v>
-      </c>
-      <c r="D19" s="114" t="s">
-        <v>110</v>
-      </c>
-      <c r="E19" s="115"/>
-      <c r="F19" s="115"/>
-      <c r="G19" s="148"/>
+        <v>65</v>
+      </c>
+      <c r="D19" s="127" t="s">
+        <v>66</v>
+      </c>
+      <c r="E19" s="128"/>
+      <c r="F19" s="128"/>
+      <c r="G19" s="133"/>
       <c r="H19" s="56"/>
       <c r="I19" s="58"/>
       <c r="J19" s="54" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="K19" s="54"/>
     </row>
     <row r="20" spans="1:11">
-      <c r="A20" s="124" t="s">
-        <v>111</v>
-      </c>
-      <c r="B20" s="125"/>
-      <c r="C20" s="125"/>
+      <c r="A20" s="110" t="s">
+        <v>67</v>
+      </c>
+      <c r="B20" s="111"/>
+      <c r="C20" s="111"/>
       <c r="D20" s="50"/>
       <c r="E20" s="50"/>
       <c r="F20" s="50"/>
@@ -3791,122 +3951,110 @@
     </row>
     <row r="21" spans="1:11" ht="66">
       <c r="A21" s="52" t="s">
-        <v>112</v>
+        <v>68</v>
       </c>
       <c r="B21" s="54" t="s">
-        <v>113</v>
+        <v>69</v>
       </c>
       <c r="C21" s="54" t="s">
-        <v>114</v>
-      </c>
-      <c r="D21" s="114" t="s">
-        <v>115</v>
-      </c>
-      <c r="E21" s="115"/>
-      <c r="F21" s="115"/>
-      <c r="G21" s="148"/>
+        <v>70</v>
+      </c>
+      <c r="D21" s="127" t="s">
+        <v>71</v>
+      </c>
+      <c r="E21" s="128"/>
+      <c r="F21" s="128"/>
+      <c r="G21" s="133"/>
       <c r="H21" s="56"/>
       <c r="I21" s="58"/>
       <c r="J21" s="54" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="K21" s="54"/>
     </row>
     <row r="22" spans="1:11">
       <c r="A22" s="64" t="s">
-        <v>165</v>
+        <v>121</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" s="64" t="s">
-        <v>166</v>
+        <v>122</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="A24" s="64" t="s">
-        <v>167</v>
+        <v>123</v>
       </c>
     </row>
     <row r="25" spans="1:11">
       <c r="A25" s="64" t="s">
-        <v>168</v>
+        <v>124</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="26.4">
       <c r="A26" s="64" t="s">
-        <v>169</v>
+        <v>125</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="39.6">
       <c r="A27" s="64" t="s">
-        <v>170</v>
+        <v>126</v>
+      </c>
+      <c r="C27" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" s="64" t="s">
-        <v>171</v>
+        <v>127</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="26.4">
       <c r="A29" s="64" t="s">
-        <v>172</v>
+        <v>128</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="26.4">
       <c r="A30" s="64" t="s">
-        <v>173</v>
+        <v>129</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="39.6">
       <c r="A31" s="64" t="s">
-        <v>174</v>
+        <v>130</v>
       </c>
     </row>
     <row r="32" spans="1:11">
-      <c r="A32" s="104" t="s">
-        <v>175</v>
+      <c r="A32" s="89" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="66">
-      <c r="A33" s="104" t="s">
-        <v>176</v>
+      <c r="A33" s="89" t="s">
+        <v>132</v>
       </c>
       <c r="B33" t="s">
-        <v>180</v>
+        <v>136</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="26.4">
-      <c r="A34" s="104" t="s">
-        <v>177</v>
+      <c r="A34" s="89" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="26.4">
-      <c r="A35" s="104" t="s">
-        <v>178</v>
+      <c r="A35" s="89" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="26.4">
-      <c r="A36" s="104" t="s">
-        <v>179</v>
+      <c r="A36" s="89" t="s">
+        <v>135</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A11:K11"/>
-    <mergeCell ref="A12:K12"/>
-    <mergeCell ref="H9:H10"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="K9:K10"/>
     <mergeCell ref="A18:C18"/>
     <mergeCell ref="D19:G19"/>
     <mergeCell ref="A20:C20"/>
@@ -3920,12 +4068,27 @@
     <mergeCell ref="D15:G15"/>
     <mergeCell ref="A16:C16"/>
     <mergeCell ref="D17:G17"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A11:K11"/>
+    <mergeCell ref="A12:K12"/>
+    <mergeCell ref="H9:H10"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="K9:K10"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="I5:K5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:K39"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.2"/>
@@ -3941,9 +4104,9 @@
       <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="112"/>
-      <c r="C1" s="112"/>
-      <c r="D1" s="112"/>
+      <c r="B1" s="125"/>
+      <c r="C1" s="125"/>
+      <c r="D1" s="125"/>
       <c r="E1" s="31"/>
       <c r="F1" s="31"/>
       <c r="G1" s="31"/>
@@ -3954,9 +4117,9 @@
     </row>
     <row r="2" spans="1:11" ht="13.8">
       <c r="A2" s="33"/>
-      <c r="B2" s="113"/>
-      <c r="C2" s="113"/>
-      <c r="D2" s="113"/>
+      <c r="B2" s="126"/>
+      <c r="C2" s="126"/>
+      <c r="D2" s="126"/>
       <c r="E2" s="31"/>
       <c r="F2" s="31"/>
       <c r="G2" s="31"/>
@@ -3967,65 +4130,65 @@
     </row>
     <row r="3" spans="1:11" ht="13.8">
       <c r="A3" s="34" t="s">
-        <v>59</v>
-      </c>
-      <c r="B3" s="139" t="s">
-        <v>116</v>
-      </c>
-      <c r="C3" s="139"/>
-      <c r="D3" s="140"/>
+        <v>15</v>
+      </c>
+      <c r="B3" s="131" t="s">
+        <v>72</v>
+      </c>
+      <c r="C3" s="131"/>
+      <c r="D3" s="132"/>
       <c r="E3" s="35"/>
       <c r="F3" s="35"/>
       <c r="G3" s="35"/>
       <c r="H3" s="35"/>
-      <c r="I3" s="120"/>
-      <c r="J3" s="120"/>
-      <c r="K3" s="120"/>
+      <c r="I3" s="97"/>
+      <c r="J3" s="97"/>
+      <c r="K3" s="97"/>
     </row>
     <row r="4" spans="1:11" ht="13.8">
       <c r="A4" s="37" t="s">
-        <v>61</v>
-      </c>
-      <c r="B4" s="141" t="s">
-        <v>117</v>
-      </c>
-      <c r="C4" s="142"/>
-      <c r="D4" s="143"/>
+        <v>17</v>
+      </c>
+      <c r="B4" s="98" t="s">
+        <v>73</v>
+      </c>
+      <c r="C4" s="99"/>
+      <c r="D4" s="100"/>
       <c r="E4" s="35"/>
       <c r="F4" s="35"/>
       <c r="G4" s="35"/>
       <c r="H4" s="35"/>
-      <c r="I4" s="120"/>
-      <c r="J4" s="120"/>
-      <c r="K4" s="120"/>
+      <c r="I4" s="97"/>
+      <c r="J4" s="97"/>
+      <c r="K4" s="97"/>
     </row>
     <row r="5" spans="1:11" ht="26.4">
       <c r="A5" s="38" t="s">
-        <v>63</v>
-      </c>
-      <c r="B5" s="144" t="s">
-        <v>64</v>
-      </c>
-      <c r="C5" s="145"/>
-      <c r="D5" s="146"/>
+        <v>19</v>
+      </c>
+      <c r="B5" s="101" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="102"/>
+      <c r="D5" s="103"/>
       <c r="E5" s="39"/>
       <c r="F5" s="39"/>
       <c r="G5" s="39"/>
       <c r="H5" s="39"/>
-      <c r="I5" s="147"/>
-      <c r="J5" s="147"/>
-      <c r="K5" s="147"/>
+      <c r="I5" s="104"/>
+      <c r="J5" s="104"/>
+      <c r="K5" s="104"/>
     </row>
     <row r="6" spans="1:11" ht="13.8">
       <c r="A6" s="40" t="s">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="B6" s="41">
         <f>COUNTIF(J12:J23,"Pass")</f>
         <v>0</v>
       </c>
       <c r="C6" s="42" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="D6" s="43">
         <f>COUNTIF(J10:J741,"Pending")</f>
@@ -4035,20 +4198,20 @@
       <c r="F6" s="36"/>
       <c r="G6" s="36"/>
       <c r="H6" s="36"/>
-      <c r="I6" s="120"/>
-      <c r="J6" s="120"/>
-      <c r="K6" s="120"/>
+      <c r="I6" s="97"/>
+      <c r="J6" s="97"/>
+      <c r="K6" s="97"/>
     </row>
     <row r="7" spans="1:11" ht="13.8">
       <c r="A7" s="44" t="s">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="B7" s="45">
         <f>COUNTIF(J12:J23,"Fail")</f>
         <v>0</v>
       </c>
       <c r="C7" s="46" t="s">
-        <v>68</v>
+        <v>24</v>
       </c>
       <c r="D7" s="47">
         <f>COUNTA(A12:A24)-3</f>
@@ -4058,15 +4221,15 @@
       <c r="F7" s="48"/>
       <c r="G7" s="48"/>
       <c r="H7" s="48"/>
-      <c r="I7" s="120"/>
-      <c r="J7" s="120"/>
-      <c r="K7" s="120"/>
+      <c r="I7" s="97"/>
+      <c r="J7" s="97"/>
+      <c r="K7" s="97"/>
     </row>
     <row r="8" spans="1:11" ht="13.8">
-      <c r="A8" s="121"/>
-      <c r="B8" s="121"/>
-      <c r="C8" s="121"/>
-      <c r="D8" s="121"/>
+      <c r="A8" s="107"/>
+      <c r="B8" s="107"/>
+      <c r="C8" s="107"/>
+      <c r="D8" s="107"/>
       <c r="E8" s="36"/>
       <c r="F8" s="36"/>
       <c r="G8" s="36"/>
@@ -4076,127 +4239,127 @@
       <c r="K8" s="49"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="127" t="s">
-        <v>69</v>
-      </c>
-      <c r="B9" s="129" t="s">
-        <v>70</v>
-      </c>
-      <c r="C9" s="127" t="s">
-        <v>71</v>
-      </c>
-      <c r="D9" s="133" t="s">
-        <v>72</v>
-      </c>
-      <c r="E9" s="134"/>
-      <c r="F9" s="134"/>
-      <c r="G9" s="135"/>
-      <c r="H9" s="131" t="s">
-        <v>73</v>
-      </c>
-      <c r="I9" s="132" t="s">
+      <c r="A9" s="113" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="115" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="119" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" s="120"/>
+      <c r="F9" s="120"/>
+      <c r="G9" s="121"/>
+      <c r="H9" s="117" t="s">
+        <v>29</v>
+      </c>
+      <c r="I9" s="118" t="s">
+        <v>30</v>
+      </c>
+      <c r="J9" s="118" t="s">
+        <v>31</v>
+      </c>
+      <c r="K9" s="118" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="114"/>
+      <c r="B10" s="116"/>
+      <c r="C10" s="114"/>
+      <c r="D10" s="122"/>
+      <c r="E10" s="123"/>
+      <c r="F10" s="123"/>
+      <c r="G10" s="124"/>
+      <c r="H10" s="113"/>
+      <c r="I10" s="113"/>
+      <c r="J10" s="113"/>
+      <c r="K10" s="113"/>
+    </row>
+    <row r="11" spans="1:11" ht="15">
+      <c r="A11" s="108"/>
+      <c r="B11" s="108"/>
+      <c r="C11" s="108"/>
+      <c r="D11" s="108"/>
+      <c r="E11" s="108"/>
+      <c r="F11" s="108"/>
+      <c r="G11" s="108"/>
+      <c r="H11" s="108"/>
+      <c r="I11" s="108"/>
+      <c r="J11" s="108"/>
+      <c r="K11" s="109"/>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="110" t="s">
         <v>74</v>
       </c>
-      <c r="J9" s="132" t="s">
-        <v>75</v>
-      </c>
-      <c r="K9" s="132" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="A10" s="128"/>
-      <c r="B10" s="130"/>
-      <c r="C10" s="128"/>
-      <c r="D10" s="136"/>
-      <c r="E10" s="137"/>
-      <c r="F10" s="137"/>
-      <c r="G10" s="138"/>
-      <c r="H10" s="127"/>
-      <c r="I10" s="127"/>
-      <c r="J10" s="127"/>
-      <c r="K10" s="127"/>
-    </row>
-    <row r="11" spans="1:11" ht="15">
-      <c r="A11" s="122"/>
-      <c r="B11" s="122"/>
-      <c r="C11" s="122"/>
-      <c r="D11" s="122"/>
-      <c r="E11" s="122"/>
-      <c r="F11" s="122"/>
-      <c r="G11" s="122"/>
-      <c r="H11" s="122"/>
-      <c r="I11" s="122"/>
-      <c r="J11" s="122"/>
-      <c r="K11" s="123"/>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12" s="124" t="s">
-        <v>118</v>
-      </c>
-      <c r="B12" s="125"/>
-      <c r="C12" s="125"/>
-      <c r="D12" s="125"/>
-      <c r="E12" s="125"/>
-      <c r="F12" s="125"/>
-      <c r="G12" s="125"/>
-      <c r="H12" s="125"/>
-      <c r="I12" s="125"/>
-      <c r="J12" s="125"/>
-      <c r="K12" s="126"/>
+      <c r="B12" s="111"/>
+      <c r="C12" s="111"/>
+      <c r="D12" s="111"/>
+      <c r="E12" s="111"/>
+      <c r="F12" s="111"/>
+      <c r="G12" s="111"/>
+      <c r="H12" s="111"/>
+      <c r="I12" s="111"/>
+      <c r="J12" s="111"/>
+      <c r="K12" s="112"/>
     </row>
     <row r="13" spans="1:11" ht="55.5" customHeight="1">
       <c r="A13" s="52" t="s">
-        <v>119</v>
+        <v>75</v>
       </c>
       <c r="B13" s="53" t="s">
-        <v>120</v>
+        <v>76</v>
       </c>
       <c r="C13" s="54" t="s">
-        <v>121</v>
-      </c>
-      <c r="D13" s="157" t="s">
-        <v>122</v>
-      </c>
-      <c r="E13" s="158"/>
-      <c r="F13" s="158"/>
+        <v>77</v>
+      </c>
+      <c r="D13" s="140" t="s">
+        <v>78</v>
+      </c>
+      <c r="E13" s="141"/>
+      <c r="F13" s="141"/>
       <c r="G13" s="55"/>
       <c r="H13" s="56"/>
       <c r="I13" s="57"/>
       <c r="J13" s="54" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="K13" s="54"/>
     </row>
     <row r="14" spans="1:11" ht="54" customHeight="1">
       <c r="A14" s="52" t="s">
-        <v>123</v>
+        <v>79</v>
       </c>
       <c r="B14" s="53" t="s">
-        <v>124</v>
+        <v>80</v>
       </c>
       <c r="C14" s="58" t="s">
-        <v>125</v>
-      </c>
-      <c r="D14" s="114" t="s">
-        <v>126</v>
-      </c>
-      <c r="E14" s="115"/>
-      <c r="F14" s="115"/>
+        <v>81</v>
+      </c>
+      <c r="D14" s="127" t="s">
+        <v>82</v>
+      </c>
+      <c r="E14" s="128"/>
+      <c r="F14" s="128"/>
       <c r="G14" s="59"/>
       <c r="H14" s="59"/>
       <c r="I14" s="60"/>
       <c r="J14" s="54" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="K14" s="54"/>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="124" t="s">
-        <v>127</v>
-      </c>
-      <c r="B15" s="125"/>
-      <c r="C15" s="125"/>
+      <c r="A15" s="110" t="s">
+        <v>83</v>
+      </c>
+      <c r="B15" s="111"/>
+      <c r="C15" s="111"/>
       <c r="D15" s="61"/>
       <c r="E15" s="61"/>
       <c r="F15" s="61"/>
@@ -4208,125 +4371,125 @@
     </row>
     <row r="16" spans="1:11" ht="77.25" customHeight="1">
       <c r="A16" s="52" t="s">
-        <v>128</v>
-      </c>
-      <c r="B16" s="108" t="s">
-        <v>194</v>
+        <v>84</v>
+      </c>
+      <c r="B16" s="93" t="s">
+        <v>150</v>
       </c>
       <c r="C16" s="58" t="s">
-        <v>129</v>
-      </c>
-      <c r="D16" s="114" t="s">
-        <v>130</v>
-      </c>
-      <c r="E16" s="115"/>
-      <c r="F16" s="115"/>
+        <v>85</v>
+      </c>
+      <c r="D16" s="127" t="s">
+        <v>86</v>
+      </c>
+      <c r="E16" s="128"/>
+      <c r="F16" s="128"/>
       <c r="G16" s="62"/>
       <c r="H16" s="59"/>
       <c r="I16" s="54"/>
       <c r="J16" s="54" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="K16" s="54"/>
     </row>
     <row r="17" spans="1:11" ht="78" customHeight="1">
       <c r="A17" s="52" t="s">
-        <v>131</v>
-      </c>
-      <c r="B17" s="109" t="s">
-        <v>132</v>
+        <v>87</v>
+      </c>
+      <c r="B17" s="94" t="s">
+        <v>88</v>
       </c>
       <c r="C17" s="63" t="s">
-        <v>133</v>
-      </c>
-      <c r="D17" s="157" t="s">
-        <v>130</v>
-      </c>
-      <c r="E17" s="158"/>
-      <c r="F17" s="158"/>
+        <v>89</v>
+      </c>
+      <c r="D17" s="140" t="s">
+        <v>86</v>
+      </c>
+      <c r="E17" s="141"/>
+      <c r="F17" s="141"/>
       <c r="G17" s="55"/>
       <c r="H17" s="56"/>
       <c r="I17" s="58"/>
       <c r="J17" s="54" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="K17" s="54"/>
     </row>
     <row r="18" spans="1:11" ht="79.5" customHeight="1">
       <c r="A18" s="52" t="s">
-        <v>134</v>
-      </c>
-      <c r="B18" s="108" t="s">
-        <v>192</v>
+        <v>90</v>
+      </c>
+      <c r="B18" s="93" t="s">
+        <v>148</v>
       </c>
       <c r="C18" s="58" t="s">
-        <v>135</v>
-      </c>
-      <c r="D18" s="114" t="s">
-        <v>136</v>
-      </c>
-      <c r="E18" s="115"/>
-      <c r="F18" s="115"/>
+        <v>91</v>
+      </c>
+      <c r="D18" s="127" t="s">
+        <v>92</v>
+      </c>
+      <c r="E18" s="128"/>
+      <c r="F18" s="128"/>
       <c r="G18" s="59"/>
       <c r="H18" s="59"/>
       <c r="I18" s="54"/>
       <c r="J18" s="54" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="K18" s="54"/>
     </row>
     <row r="19" spans="1:11" ht="78.75" customHeight="1">
       <c r="A19" s="52" t="s">
-        <v>137</v>
-      </c>
-      <c r="B19" s="108" t="s">
-        <v>138</v>
+        <v>93</v>
+      </c>
+      <c r="B19" s="93" t="s">
+        <v>94</v>
       </c>
       <c r="C19" s="58" t="s">
-        <v>139</v>
-      </c>
-      <c r="D19" s="114" t="s">
-        <v>136</v>
-      </c>
-      <c r="E19" s="115"/>
-      <c r="F19" s="115"/>
+        <v>95</v>
+      </c>
+      <c r="D19" s="127" t="s">
+        <v>92</v>
+      </c>
+      <c r="E19" s="128"/>
+      <c r="F19" s="128"/>
       <c r="G19" s="59"/>
       <c r="H19" s="59"/>
       <c r="I19" s="54"/>
       <c r="J19" s="54" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="K19" s="54"/>
     </row>
     <row r="20" spans="1:11" ht="78.75" customHeight="1">
       <c r="A20" s="64" t="s">
-        <v>140</v>
-      </c>
-      <c r="B20" s="110" t="s">
-        <v>141</v>
+        <v>96</v>
+      </c>
+      <c r="B20" s="95" t="s">
+        <v>97</v>
       </c>
       <c r="C20" s="65" t="s">
-        <v>142</v>
-      </c>
-      <c r="D20" s="155" t="s">
-        <v>136</v>
-      </c>
-      <c r="E20" s="156"/>
-      <c r="F20" s="156"/>
+        <v>98</v>
+      </c>
+      <c r="D20" s="142" t="s">
+        <v>92</v>
+      </c>
+      <c r="E20" s="143"/>
+      <c r="F20" s="143"/>
       <c r="G20" s="66"/>
       <c r="H20" s="67"/>
       <c r="I20" s="67"/>
       <c r="J20" s="67" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="K20" s="67"/>
     </row>
     <row r="21" spans="1:11">
-      <c r="A21" s="124" t="s">
-        <v>143</v>
-      </c>
-      <c r="B21" s="125"/>
-      <c r="C21" s="125"/>
+      <c r="A21" s="110" t="s">
+        <v>99</v>
+      </c>
+      <c r="B21" s="111"/>
+      <c r="C21" s="111"/>
       <c r="D21" s="61"/>
       <c r="E21" s="61"/>
       <c r="F21" s="61"/>
@@ -4338,159 +4501,143 @@
     </row>
     <row r="22" spans="1:11" ht="66" customHeight="1">
       <c r="A22" s="52" t="s">
-        <v>144</v>
+        <v>100</v>
       </c>
       <c r="B22" s="63" t="s">
-        <v>145</v>
+        <v>101</v>
       </c>
       <c r="C22" s="63" t="s">
-        <v>146</v>
-      </c>
-      <c r="D22" s="114" t="s">
-        <v>147</v>
-      </c>
-      <c r="E22" s="115"/>
-      <c r="F22" s="115"/>
+        <v>102</v>
+      </c>
+      <c r="D22" s="127" t="s">
+        <v>103</v>
+      </c>
+      <c r="E22" s="128"/>
+      <c r="F22" s="128"/>
       <c r="G22" s="59"/>
       <c r="H22" s="56"/>
       <c r="I22" s="58"/>
       <c r="J22" s="54" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="K22" s="54"/>
     </row>
     <row r="23" spans="1:11" ht="65.25" customHeight="1">
       <c r="A23" s="68" t="s">
-        <v>148</v>
+        <v>104</v>
       </c>
       <c r="B23" s="54" t="s">
-        <v>149</v>
+        <v>105</v>
       </c>
       <c r="C23" s="54" t="s">
-        <v>150</v>
-      </c>
-      <c r="D23" s="114" t="s">
-        <v>151</v>
-      </c>
-      <c r="E23" s="115"/>
-      <c r="F23" s="115"/>
+        <v>106</v>
+      </c>
+      <c r="D23" s="127" t="s">
+        <v>107</v>
+      </c>
+      <c r="E23" s="128"/>
+      <c r="F23" s="128"/>
       <c r="G23" s="59"/>
       <c r="H23" s="54"/>
       <c r="I23" s="54"/>
       <c r="J23" s="54" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="K23" s="54"/>
     </row>
     <row r="24" spans="1:11" ht="67.5" customHeight="1">
       <c r="A24" s="68" t="s">
-        <v>152</v>
+        <v>108</v>
       </c>
       <c r="B24" s="54" t="s">
-        <v>153</v>
+        <v>109</v>
       </c>
       <c r="C24" s="54" t="s">
-        <v>154</v>
-      </c>
-      <c r="D24" s="114" t="s">
-        <v>151</v>
-      </c>
-      <c r="E24" s="115"/>
-      <c r="F24" s="115"/>
+        <v>110</v>
+      </c>
+      <c r="D24" s="127" t="s">
+        <v>107</v>
+      </c>
+      <c r="E24" s="128"/>
+      <c r="F24" s="128"/>
       <c r="G24" s="59"/>
       <c r="H24" s="54"/>
       <c r="I24" s="54"/>
       <c r="J24" s="54" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="K24" s="54"/>
     </row>
     <row r="25" spans="1:11">
-      <c r="A25" s="107" t="s">
-        <v>181</v>
+      <c r="A25" s="92" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="26" spans="1:11">
-      <c r="A26" s="107" t="s">
-        <v>182</v>
+      <c r="A26" s="92" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="27" spans="1:11">
-      <c r="A27" s="105"/>
+      <c r="A27" s="90"/>
     </row>
     <row r="28" spans="1:11" ht="26.4">
-      <c r="A28" s="106" t="s">
-        <v>183</v>
+      <c r="A28" s="91" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="26.4">
-      <c r="A29" s="106" t="s">
-        <v>184</v>
+      <c r="A29" s="91" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="30" spans="1:11">
-      <c r="A30" s="105"/>
+      <c r="A30" s="90"/>
     </row>
     <row r="31" spans="1:11" ht="26.4">
-      <c r="A31" s="106" t="s">
-        <v>185</v>
-      </c>
-      <c r="C31" s="111" t="s">
-        <v>193</v>
+      <c r="A31" s="91" t="s">
+        <v>141</v>
+      </c>
+      <c r="C31" s="96" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="32" spans="1:11">
-      <c r="A32" s="105"/>
+      <c r="A32" s="90"/>
     </row>
     <row r="33" spans="1:2" ht="26.4">
-      <c r="A33" s="106" t="s">
-        <v>186</v>
+      <c r="A33" s="91" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" s="105" t="s">
-        <v>187</v>
+      <c r="A34" s="90" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="52.8">
-      <c r="A35" s="106" t="s">
-        <v>188</v>
+      <c r="A35" s="91" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="105" t="s">
-        <v>189</v>
+      <c r="A36" s="90" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="26.4">
-      <c r="A37" s="106" t="s">
-        <v>190</v>
-      </c>
-      <c r="B37" s="105"/>
+      <c r="A37" s="91" t="s">
+        <v>146</v>
+      </c>
+      <c r="B37" s="90"/>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="105" t="s">
-        <v>191</v>
+      <c r="A39" s="90" t="s">
+        <v>147</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A11:K11"/>
-    <mergeCell ref="A12:K12"/>
-    <mergeCell ref="H9:H10"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="K9:K10"/>
     <mergeCell ref="B1:D2"/>
     <mergeCell ref="D23:F23"/>
     <mergeCell ref="D24:F24"/>
@@ -4507,12 +4654,28 @@
     <mergeCell ref="D14:F14"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="D16:F16"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A11:K11"/>
+    <mergeCell ref="A12:K12"/>
+    <mergeCell ref="H9:H10"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="K9:K10"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="I5:K5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:G13"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.2"/>
@@ -4523,7 +4686,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="22.2">
       <c r="A1" s="2" t="s">
-        <v>155</v>
+        <v>111</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="4"/>
@@ -4543,7 +4706,7 @@
     </row>
     <row r="3" spans="1:7" ht="13.8">
       <c r="B3" s="6" t="s">
-        <v>156</v>
+        <v>112</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
@@ -4553,7 +4716,7 @@
     </row>
     <row r="4" spans="1:7" ht="13.8">
       <c r="B4" s="6" t="s">
-        <v>157</v>
+        <v>113</v>
       </c>
       <c r="C4" s="7"/>
       <c r="D4" s="6"/>
@@ -4582,22 +4745,22 @@
     <row r="7" spans="1:7" ht="26.4">
       <c r="A7" s="6"/>
       <c r="B7" s="8" t="s">
-        <v>158</v>
+        <v>114</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>159</v>
+        <v>115</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>160</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:7" s="1" customFormat="1" ht="13.8">
@@ -4639,7 +4802,7 @@
       <c r="A10" s="6"/>
       <c r="B10" s="21"/>
       <c r="C10" s="22" t="s">
-        <v>161</v>
+        <v>117</v>
       </c>
       <c r="D10" s="23">
         <f>SUM(D6:D9)</f>
@@ -4671,7 +4834,7 @@
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
       <c r="C12" s="6" t="s">
-        <v>162</v>
+        <v>118</v>
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="28">
@@ -4679,7 +4842,7 @@
         <v>-33.3333333333333</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>163</v>
+        <v>119</v>
       </c>
       <c r="G12" s="29"/>
     </row>
@@ -4687,7 +4850,7 @@
       <c r="A13" s="6"/>
       <c r="B13" s="6"/>
       <c r="C13" s="6" t="s">
-        <v>164</v>
+        <v>120</v>
       </c>
       <c r="D13" s="6"/>
       <c r="E13" s="28">
@@ -4695,7 +4858,7 @@
         <v>-33.3333333333333</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>163</v>
+        <v>119</v>
       </c>
       <c r="G13" s="29"/>
     </row>

--- a/test-case-example.xlsx
+++ b/test-case-example.xlsx
@@ -1,27 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sports-field-booking-management\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\sports-field-booking-management\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E87223E6-2BF4-4C3E-BF43-8693D5468A09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="821" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450" tabRatio="821" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="97" r:id="rId1"/>
-    <sheet name="Samples" sheetId="122" r:id="rId2"/>
-    <sheet name="Sheet1" sheetId="125" r:id="rId3"/>
-    <sheet name="Booking" sheetId="124" r:id="rId4"/>
-    <sheet name="Cancel Booking" sheetId="123" r:id="rId5"/>
-    <sheet name="Test Report" sheetId="107" r:id="rId6"/>
+    <sheet name="Favorite" sheetId="126" r:id="rId2"/>
+    <sheet name="Samples" sheetId="122" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="125" r:id="rId4"/>
+    <sheet name="Booking" sheetId="124" r:id="rId5"/>
+    <sheet name="Cancel Booking" sheetId="123" r:id="rId6"/>
+    <sheet name="Test Report" sheetId="107" r:id="rId7"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId7"/>
+    <externalReference r:id="rId8"/>
   </externalReferences>
   <definedNames>
     <definedName name="Access">[1]Validation!$E$2:$E$223</definedName>
@@ -33,12 +33,12 @@
     <definedName name="Port">[1]Validation!$F$2:$F$40</definedName>
     <definedName name="VancoProducts">[1]Validation!$B$2:$B$4</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="202">
   <si>
     <t>TEST CASE</t>
   </si>
@@ -459,16 +459,10 @@
     <t>Cho phép người dùng đặt thành công 3 sân trong cùng 1 ngày, khi đặt tiếp thì nhận thông báo hệ thống "Bạn đã đạt giới hạn đặt sân trong ngày!"</t>
   </si>
   <si>
-    <t>HỦY ĐẶT SÂN</t>
-  </si>
-  <si>
     <t>CR200 - CANCEL BOOKING</t>
   </si>
   <si>
     <t>1. Chỉ người đặt mới được hủy</t>
-  </si>
-  <si>
-    <t>TC2-01</t>
   </si>
   <si>
     <t>Hủy sân sau khi đặt sân trong cùng một tài khoản</t>
@@ -482,9 +476,6 @@
     <t>Hệ thống tự động tải lại trang, tab "Sân đã đặt" không còn sân vừa hủy.</t>
   </si>
   <si>
-    <t>TC2-02</t>
-  </si>
-  <si>
     <t>Hủy sân của một user khác</t>
   </si>
   <si>
@@ -499,22 +490,7 @@
     <t>2. Không hủy khi còn &lt;2 giờ trước giờ chơi</t>
   </si>
   <si>
-    <t>TC2-03</t>
-  </si>
-  <si>
-    <t>Booking #1 có giờ bắt đầu là 14:00 hôm nay. Thời gian hiện tại là 11:00:
-1: Truy cập vào trang và đăng nhập tài khoản thành công.
-2: Chuyển sang tab "Sân đã đặt".
-3: Nhấn "HỦY SÂN" ở booking #1.</t>
-  </si>
-  <si>
     <t>Hệ thống tự động tải lại trang, tab "Sân đã đặt" không còn booking #1.</t>
-  </si>
-  <si>
-    <t>TC2-04</t>
-  </si>
-  <si>
-    <t>Hủy một sân 1 phút ngay trước hạn chót</t>
   </si>
   <si>
     <t>Booking #1 có giờ bắt đầu là 14:00 hôm nay. Thời gian hiện tại là 11:59:
@@ -523,9 +499,6 @@
 3: Nhấn "HỦY SÂN" ở booking #1.</t>
   </si>
   <si>
-    <t>TC2-05</t>
-  </si>
-  <si>
     <t>Booking #1 có giờ bắt đầu là 14:00 hôm nay. Thời gian hiện tại là 12:00:
 1: Truy cập vào trang và đăng nhập tài khoản thành công.
 2: Chuyển sang tab "Sân đã đặt".
@@ -535,34 +508,13 @@
     <t>Hệ thống từ chối huỷ sân, hiển thị thông báo "Sân sắp đá, không được huỷ!"</t>
   </si>
   <si>
-    <t>TC2-06</t>
-  </si>
-  <si>
-    <t>Huỷ một sân đã quá 1 phút sau hạn chót</t>
-  </si>
-  <si>
     <t>Booking #1 có giờ bắt đầu là 14:00 hôm nay. Thời gian hiện tại là 12:01:
 1: Truy cập vào trang và đăng nhập tài khoản thành công.
 2: Chuyển sang tab "Sân đã đặt".
 3: Nhấn "HỦY SÂN" ở booking #1.</t>
   </si>
   <si>
-    <t>TC2-07</t>
-  </si>
-  <si>
-    <t>Huỷ một sân đã qua hạn chót 1 giờ.</t>
-  </si>
-  <si>
-    <t>Booking #1 có giờ bắt đầu là 14:00 hôm nay. Thời gian hiện tại là 13:00:
-1: Truy cập vào trang và đăng nhập tài khoản thành công.
-2: Chuyển sang tab "Sân đã đặt".
-3: Nhấn "HỦY SÂN" ở booking #1.</t>
-  </si>
-  <si>
     <t>3. Không hủy khi đang chơi</t>
-  </si>
-  <si>
-    <t>TC2-08</t>
   </si>
   <si>
     <t>Hủy một sân đang trong thời gian sử dụng</t>
@@ -576,9 +528,6 @@
     <t>Hệ thống có thông báo "Sân đang trong giờ sử dụng, bạn không thể hủy lúc này!"</t>
   </si>
   <si>
-    <t>TC2-09</t>
-  </si>
-  <si>
     <t>Hủy một sân ngay khi vừa thi đấu xong</t>
   </si>
   <si>
@@ -590,9 +539,6 @@
     <t>Hệ thống có thông báo "Sân này đã thi đấu xong, không thể hủy!"</t>
   </si>
   <si>
-    <t>TC2-10</t>
-  </si>
-  <si>
     <t>Hủy một sân sau khi vừa thi đấu xong 15 phút.</t>
   </si>
   <si>
@@ -679,48 +625,6 @@
     <t xml:space="preserve">test API - dữ liệu </t>
   </si>
   <si>
-    <t>2.  &lt; 2 giờ chơi</t>
-  </si>
-  <si>
-    <t>tc1 : hủy &lt; 2 h</t>
-  </si>
-  <si>
-    <t>tc2 : hủy còn đúng 2h</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tc3 : hủy khi dang sử dụng </t>
-  </si>
-  <si>
-    <t xml:space="preserve">tc4 : hủy sau khi đã sử dụng xong </t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 . Các trương hợp khác </t>
-  </si>
-  <si>
-    <t xml:space="preserve">tc1 . Sau khi hủy , slot đó hiển thị là trống lại </t>
-  </si>
-  <si>
-    <t>tc2 . Booking bị xóa hoàn toàn (ko chuyển sang cancelled)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tc3 , hủy khi chưa đăng nhập </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. chỉ người đặt mới hủy </t>
-  </si>
-  <si>
-    <t xml:space="preserve">tc1 :hủy booking ko tồn tại </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Huỷ một sân đúng ngay hạn chót .  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">sửa lại những cái tô vàng . Đặt lại tên testcsce cho đúng . Hạn chot là hạn gì . </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Huỷ một sân trước 3 giờ trước hạn chót </t>
-  </si>
-  <si>
     <t>Mỹ Xuyên</t>
   </si>
   <si>
@@ -797,17 +701,208 @@
   </si>
   <si>
     <t>CR300-Auth, CR400-Admin</t>
+  </si>
+  <si>
+    <t>Huỷ một booking không tồn tại.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1: Truy cập vào trang và đăng nhập tài khoản thành công.
+2: Gửi yêu cầu POST api/cancel-booking/99999
+</t>
+  </si>
+  <si>
+    <t>Flash thông báo: "Không tìm thấy hoặc bạn không có quyền!"</t>
+  </si>
+  <si>
+    <t>Hủy một sân khi còn 2 giờ 1 phút trước giờ chơi</t>
+  </si>
+  <si>
+    <t>Huỷ một sân khi còn đúng 2 giờ trước giờ chơi</t>
+  </si>
+  <si>
+    <t>TC6</t>
+  </si>
+  <si>
+    <t>Huỷ một sân khi còn 1 giờ 59 phút trước giờ chơi</t>
+  </si>
+  <si>
+    <t>TC7</t>
+  </si>
+  <si>
+    <t>TC8</t>
+  </si>
+  <si>
+    <t>TC9</t>
+  </si>
+  <si>
+    <t>4. Những trường hợp khác</t>
+  </si>
+  <si>
+    <t>TC10</t>
+  </si>
+  <si>
+    <t>Sau khi huỷ, slot đó đó hiển thị là trống trở lại.</t>
+  </si>
+  <si>
+    <t>1: Truy cập vào trang và đăng nhập tài khoản thành công.
+2: Chuyển sang tab "Sân đã đặt".
+3:  Nhấn "HỦY SÂN" ở một sân có status = confirmed trong bảng Booking trong database.
+4: Kiểm tra lại trang chi tiết sân vừa huỷ.</t>
+  </si>
+  <si>
+    <t>Khung thời gian trùng với khung thời gian của sân vừa huỷ không còn bị mờ đi nữa.</t>
+  </si>
+  <si>
+    <t>TC11</t>
+  </si>
+  <si>
+    <t>Booking bị xoá hoàn toàn</t>
+  </si>
+  <si>
+    <t>1: Truy cập vào trang và đăng nhập tài khoản thành công.
+2: Chuyển sang tab "Sân đã đặt".
+3:  Nhấn "HỦY SÂN" ở một sân có status = confirmed trong bảng Booking trong database.
+4: Kiểm tra lại bảng Booking trong database.</t>
+  </si>
+  <si>
+    <t>Sân vừa huỷ không còn trong bảng Booking nữa.</t>
+  </si>
+  <si>
+    <t>TC12</t>
+  </si>
+  <si>
+    <t>Huỷ sân khi chưa đăng nhập</t>
+  </si>
+  <si>
+    <t>1: Truy cập vào trang ở trạng thái chưa đăng nhập.
+2: Chuyển sang tab "Sân đã đặt".</t>
+  </si>
+  <si>
+    <t>Tab "Sân đã đặt" trống.</t>
+  </si>
+  <si>
+    <t>Sheet Cancel Booking - Sheet Favorite</t>
+  </si>
+  <si>
+    <t>thêm tc 11 - tc 12 ở sheet cancel-booking, tạo sheet favorite và bắt đầu thiết kế</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Toggle Favorite - Thêm và xoá </t>
+  </si>
+  <si>
+    <t>Gọi POST api/favorite/1 khi chưa nhấn yêu thích.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1: Truy cập trang và đăng nhập thành công.
+2: Nhấn yêu thích sân có product_id = 1.
+3: Gửi POST api/favorite/1
+4: Kiểm tra kết quả.
+</t>
+  </si>
+  <si>
+    <t>api trả về {added: false; ok: true}</t>
+  </si>
+  <si>
+    <t>Gọi POST api/favorite/1 khi vừa nhấn yêu thích.</t>
+  </si>
+  <si>
+    <t>api trả về {added: true; ok: true}</t>
+  </si>
+  <si>
+    <t>2. Hiển thị và đồng bộ favorite</t>
+  </si>
+  <si>
+    <t>Kiểm tra Tab "Yêu thích" khi nhấn "Yêu thích" 3 sản phẩm.</t>
+  </si>
+  <si>
+    <t>1: Truy cập trang và đăng nhập thành công.
+2: Nhấn trái tim màu xám ở phía góc trên bên phải của 3 sản phẩm bất kỳ.
+3: Chuyển sang tab "Yêu thích".
+4: Kiểm tra các sản phẩm trong tab "Yêu thích"</t>
+  </si>
+  <si>
+    <t>Tab "Yêu thích" hiển thị đầy đủ thông tin tên sân, giá cả, trái tim trên góc phải của sản phẩm chuyển thành màu đỏ.</t>
+  </si>
+  <si>
+    <t>Kiểm tra Tab "Yêu thích" khi chưa đăng nhập.</t>
+  </si>
+  <si>
+    <t>1: Truy cập trang và đăng nhập thành công.
+2: Chuyển sang tab "Yêu thích".</t>
+  </si>
+  <si>
+    <t>Tab "Yêu thích" rỗng, có thông báo "Bạn chưa có sân nào trong danh sách yêu thích."</t>
+  </si>
+  <si>
+    <t>Huỷ yêu thích một sản phẩm ở tab "Yêu thích".</t>
+  </si>
+  <si>
+    <t>1: Truy cập trang và đăng nhập thành công.
+2: Chuyển sang tab "Yêu thích".
+3: Nhấn trái tim màu đỏ ở phía trên góc phải của sản phẩm để huỷ yêu thích.</t>
+  </si>
+  <si>
+    <t>Sản phẩm đó biến mất ngay lập tức khỏi tab "Yêu thích".</t>
+  </si>
+  <si>
+    <t>Kiểm tra sự đồng bộ giữa</t>
+  </si>
+  <si>
+    <t>1: Truy cập trang và mở thêm 1 tab trình duyệt, đăng nhập thành công cùng 1 tài khoản.
+2: Tab A để trang "Danh sách sân" và tab B để trang "Yêu thích.
+3: Tại Tab A, nhấn vào trái tim xám trên góc phải của một sản phẩm..
+4: Kiểm tra danh sách "Yêu thích" ở tab B.</t>
+  </si>
+  <si>
+    <t>1. Sản phẩm vừa nhấn yêu thích chưa hiển thị bên tab B ngay lập tức.
+2: Tải lại trang, tab B hiển thị sân vừa nhấn yêu thích với thông tin chính xác.</t>
+  </si>
+  <si>
+    <t>3. Các trường hợp đặc biệt</t>
+  </si>
+  <si>
+    <t>Yêu thích một sân khi chưa đăng nhập</t>
+  </si>
+  <si>
+    <t>1: Truy cập trang ở trạng thái chưa đăng nhập.
+2: Nhấn vào trái tim xám phía trên một sản phẩm.
+3: Quan sát thông báo.</t>
+  </si>
+  <si>
+    <t>Flash hiển thị thông báo "Bạn cần đăng nhập!".</t>
+  </si>
+  <si>
+    <t>Yêu thích một sân không tồn tại trong cơ sở dữ liệu.</t>
+  </si>
+  <si>
+    <t>1: Truy cập trang và đăng nhập thành công.
+2: Gửi yêu cầu POST api/favorite/9999</t>
+  </si>
+  <si>
+    <t>HTTP 404. Server không bị crash</t>
+  </si>
+  <si>
+    <t>CANCEL BOOKING</t>
+  </si>
+  <si>
+    <t>FAVORITE</t>
+  </si>
+  <si>
+    <t>CR200-Cancel-Booking, CR500-Favorite</t>
+  </si>
+  <si>
+    <t>CR500 - Favorite</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="34">
+  <fonts count="40">
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -1009,6 +1104,44 @@
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="128"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color indexed="9"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color indexed="9"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color indexed="8"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color indexed="8"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color indexed="10"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -1574,7 +1707,7 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="164">
+  <cellXfs count="208">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1720,9 +1853,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1735,31 +1865,10 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="24" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1811,163 +1920,9 @@
     <xf numFmtId="165" fontId="8" fillId="8" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="165" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="8" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="17" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="17" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="15" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="16" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="32" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="25" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="25" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="28" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="29" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="24" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="15" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="16" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="24" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2011,17 +1966,327 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="37" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="6" borderId="24" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="6" borderId="16" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="6" borderId="32" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="7" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="37" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="16" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="32" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="37" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="6" borderId="15" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="16" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="29" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="25" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="15" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="16" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="32" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="15" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="25" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="24" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="28" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="3" borderId="12" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="17" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="17" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="15" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="16" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="6" borderId="15" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="6" borderId="16" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="6" borderId="32" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="4" borderId="28" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="4" borderId="25" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="4" borderId="29" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="6" borderId="16" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="4" borderId="18" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="4" borderId="25" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="4" borderId="18" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="4" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="4" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="4" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="4" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="4" borderId="24" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="4" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
-    <cellStyle name="Normal_Functional Test Case v1.0" xfId="2" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
-    <cellStyle name="Normal_Sheet1_Vanco_CR022a1_TestCase_v0.1" xfId="3" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
-    <cellStyle name="標準_結合試験(AllOvertheWorld)" xfId="4" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
+    <cellStyle name="Normal 2" xfId="1"/>
+    <cellStyle name="Normal_Functional Test Case v1.0" xfId="2"/>
+    <cellStyle name="Normal_Sheet1_Vanco_CR022a1_TestCase_v0.1" xfId="3"/>
+    <cellStyle name="標準_結合試験(AllOvertheWorld)" xfId="4"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Table Style 1" pivot="0" count="0" xr9:uid="{F7E00C52-7677-4CF7-8502-45BEFC62BBA4}"/>
+    <tableStyle name="Table Style 1" pivot="0" count="0"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2035,7 +2300,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Validation"/>
@@ -2090,7 +2355,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2125,7 +2390,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2333,436 +2598,446 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="9" style="88"/>
-    <col min="2" max="2" width="29.77734375" style="88" customWidth="1"/>
-    <col min="3" max="3" width="23.109375" style="88" customWidth="1"/>
-    <col min="4" max="4" width="66.77734375" style="88" customWidth="1"/>
-    <col min="5" max="5" width="141.33203125" style="88" customWidth="1"/>
-    <col min="6" max="7" width="31.109375" style="88" customWidth="1"/>
-    <col min="8" max="8" width="174.5546875" style="88" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="88"/>
+    <col min="1" max="1" width="9" style="80"/>
+    <col min="2" max="2" width="29.75" style="80" customWidth="1"/>
+    <col min="3" max="3" width="23.125" style="80" customWidth="1"/>
+    <col min="4" max="4" width="66.75" style="80" customWidth="1"/>
+    <col min="5" max="5" width="141.375" style="80" customWidth="1"/>
+    <col min="6" max="7" width="31.125" style="80" customWidth="1"/>
+    <col min="8" max="8" width="174.5" style="80" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="80"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="155" customFormat="1" ht="24"/>
-    <row r="2" spans="1:9" s="155" customFormat="1" ht="24">
-      <c r="A2" s="156"/>
-      <c r="B2" s="157" t="s">
+    <row r="1" spans="1:9" s="95" customFormat="1" ht="23.25"/>
+    <row r="2" spans="1:9" s="95" customFormat="1" ht="23.25">
+      <c r="A2" s="96"/>
+      <c r="B2" s="97" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="156"/>
-      <c r="D2" s="156"/>
-      <c r="E2" s="156"/>
-      <c r="F2" s="156"/>
-      <c r="G2" s="156"/>
-    </row>
-    <row r="3" spans="1:9" s="155" customFormat="1" ht="25.2">
-      <c r="A3" s="156"/>
-      <c r="B3" s="154" t="s">
+      <c r="C2" s="96"/>
+      <c r="D2" s="96"/>
+      <c r="E2" s="96"/>
+      <c r="F2" s="96"/>
+      <c r="G2" s="96"/>
+    </row>
+    <row r="3" spans="1:9" s="95" customFormat="1" ht="24.75">
+      <c r="A3" s="96"/>
+      <c r="B3" s="94" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="158">
+      <c r="C3" s="98">
         <v>1.2</v>
       </c>
-      <c r="D3" s="159"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="159"/>
-      <c r="G3" s="159"/>
-      <c r="H3" s="159"/>
-      <c r="I3" s="159"/>
-    </row>
-    <row r="4" spans="1:9" s="155" customFormat="1" ht="25.2">
-      <c r="A4" s="156"/>
-      <c r="B4" s="154" t="s">
+      <c r="D3" s="99"/>
+      <c r="E3" s="99"/>
+      <c r="F3" s="99"/>
+      <c r="G3" s="99"/>
+      <c r="H3" s="99"/>
+      <c r="I3" s="99"/>
+    </row>
+    <row r="4" spans="1:9" s="95" customFormat="1" ht="24.75">
+      <c r="A4" s="96"/>
+      <c r="B4" s="94" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="158" t="s">
+      <c r="C4" s="98" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="159"/>
-      <c r="E4" s="159"/>
-      <c r="F4" s="159"/>
-      <c r="G4" s="159"/>
-      <c r="H4" s="159"/>
-      <c r="I4" s="159"/>
-    </row>
-    <row r="5" spans="1:9" s="155" customFormat="1" ht="25.2">
-      <c r="A5" s="156"/>
-      <c r="B5" s="154"/>
-      <c r="C5" s="159"/>
-      <c r="D5" s="159"/>
-      <c r="E5" s="159"/>
-      <c r="F5" s="159"/>
-      <c r="G5" s="159"/>
-      <c r="H5" s="159"/>
-      <c r="I5" s="159"/>
-    </row>
-    <row r="6" spans="1:9" s="155" customFormat="1" ht="47.4" customHeight="1">
-      <c r="A6" s="156"/>
-      <c r="B6" s="154" t="s">
+      <c r="D4" s="99"/>
+      <c r="E4" s="99"/>
+      <c r="F4" s="99"/>
+      <c r="G4" s="99"/>
+      <c r="H4" s="99"/>
+      <c r="I4" s="99"/>
+    </row>
+    <row r="5" spans="1:9" s="95" customFormat="1" ht="24.75">
+      <c r="A5" s="96"/>
+      <c r="B5" s="94"/>
+      <c r="C5" s="99"/>
+      <c r="D5" s="99"/>
+      <c r="E5" s="99"/>
+      <c r="F5" s="99"/>
+      <c r="G5" s="99"/>
+      <c r="H5" s="99"/>
+      <c r="I5" s="99"/>
+    </row>
+    <row r="6" spans="1:9" s="95" customFormat="1" ht="47.45" customHeight="1">
+      <c r="A6" s="96"/>
+      <c r="B6" s="94" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="160" t="s">
+      <c r="C6" s="100" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="159"/>
-      <c r="E6" s="159"/>
-      <c r="F6" s="159"/>
-      <c r="G6" s="159"/>
-      <c r="H6" s="159"/>
-      <c r="I6" s="159"/>
-    </row>
-    <row r="7" spans="1:9" s="155" customFormat="1" ht="27" customHeight="1">
-      <c r="A7" s="156"/>
-      <c r="B7" s="154" t="s">
+      <c r="D6" s="99"/>
+      <c r="E6" s="99"/>
+      <c r="F6" s="99"/>
+      <c r="G6" s="99"/>
+      <c r="H6" s="99"/>
+      <c r="I6" s="99"/>
+    </row>
+    <row r="7" spans="1:9" s="95" customFormat="1" ht="27" customHeight="1">
+      <c r="A7" s="96"/>
+      <c r="B7" s="94" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="160" t="s">
+      <c r="C7" s="100" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="159"/>
-      <c r="E7" s="159"/>
-      <c r="F7" s="159"/>
-      <c r="G7" s="159"/>
-      <c r="H7" s="159"/>
-      <c r="I7" s="159"/>
-    </row>
-    <row r="8" spans="1:9" s="155" customFormat="1" ht="24">
-      <c r="A8" s="156"/>
-      <c r="B8" s="154"/>
-      <c r="C8" s="156"/>
-      <c r="D8" s="156"/>
-      <c r="E8" s="156"/>
-      <c r="F8" s="156"/>
-      <c r="G8" s="156"/>
-    </row>
-    <row r="9" spans="1:9" s="155" customFormat="1" ht="24">
-      <c r="A9" s="156"/>
-      <c r="F9" s="156"/>
-      <c r="G9" s="156"/>
-    </row>
-    <row r="10" spans="1:9" s="155" customFormat="1" ht="24.6">
-      <c r="B10" s="161" t="s">
+      <c r="D7" s="99"/>
+      <c r="E7" s="99"/>
+      <c r="F7" s="99"/>
+      <c r="G7" s="99"/>
+      <c r="H7" s="99"/>
+      <c r="I7" s="99"/>
+    </row>
+    <row r="8" spans="1:9" s="95" customFormat="1" ht="23.25">
+      <c r="A8" s="96"/>
+      <c r="B8" s="94"/>
+      <c r="C8" s="96"/>
+      <c r="D8" s="96"/>
+      <c r="E8" s="96"/>
+      <c r="F8" s="96"/>
+      <c r="G8" s="96"/>
+    </row>
+    <row r="9" spans="1:9" s="95" customFormat="1" ht="23.25">
+      <c r="A9" s="96"/>
+      <c r="F9" s="96"/>
+      <c r="G9" s="96"/>
+    </row>
+    <row r="10" spans="1:9" s="95" customFormat="1" ht="24">
+      <c r="B10" s="101" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="162"/>
-      <c r="D10" s="162"/>
-      <c r="E10" s="162"/>
-      <c r="F10" s="162"/>
-      <c r="G10" s="162"/>
-      <c r="H10" s="162"/>
-    </row>
-    <row r="11" spans="1:9" s="163" customFormat="1" ht="63.6" customHeight="1">
-      <c r="B11" s="144"/>
-      <c r="C11" s="145" t="s">
+      <c r="C10" s="102"/>
+      <c r="D10" s="102"/>
+      <c r="E10" s="102"/>
+      <c r="F10" s="102"/>
+      <c r="G10" s="102"/>
+      <c r="H10" s="102"/>
+    </row>
+    <row r="11" spans="1:9" s="103" customFormat="1" ht="63.6" customHeight="1">
+      <c r="B11" s="84"/>
+      <c r="C11" s="85" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="145" t="s">
+      <c r="D11" s="85" t="s">
         <v>10</v>
       </c>
-      <c r="E11" s="145" t="s">
+      <c r="E11" s="85" t="s">
         <v>11</v>
       </c>
-      <c r="F11" s="145" t="s">
+      <c r="F11" s="85" t="s">
         <v>12</v>
       </c>
-      <c r="G11" s="146" t="s">
+      <c r="G11" s="86" t="s">
         <v>13</v>
       </c>
-      <c r="H11" s="147" t="s">
+      <c r="H11" s="87" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:9" s="86" customFormat="1" ht="49.95" customHeight="1">
-      <c r="B12" s="148">
+    <row r="12" spans="1:9" s="78" customFormat="1" ht="49.9" customHeight="1">
+      <c r="B12" s="88">
         <v>46268</v>
       </c>
-      <c r="C12" s="149" t="s">
-        <v>160</v>
-      </c>
-      <c r="D12" s="149" t="s">
-        <v>158</v>
-      </c>
-      <c r="E12" s="149" t="s">
-        <v>159</v>
-      </c>
-      <c r="F12" s="149" t="s">
-        <v>151</v>
-      </c>
-      <c r="G12" s="149" t="s">
-        <v>151</v>
-      </c>
-      <c r="H12" s="150" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" s="86" customFormat="1" ht="49.95" customHeight="1">
-      <c r="B13" s="148">
+      <c r="C12" s="89" t="s">
+        <v>130</v>
+      </c>
+      <c r="D12" s="89" t="s">
+        <v>128</v>
+      </c>
+      <c r="E12" s="89" t="s">
+        <v>129</v>
+      </c>
+      <c r="F12" s="89" t="s">
+        <v>121</v>
+      </c>
+      <c r="G12" s="89" t="s">
+        <v>121</v>
+      </c>
+      <c r="H12" s="90" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" s="78" customFormat="1" ht="49.9" customHeight="1">
+      <c r="B13" s="88">
         <v>46116</v>
       </c>
-      <c r="C13" s="149">
+      <c r="C13" s="89">
         <v>1.1000000000000001</v>
       </c>
-      <c r="D13" s="149" t="s">
-        <v>156</v>
-      </c>
-      <c r="E13" s="149" t="s">
-        <v>161</v>
-      </c>
-      <c r="F13" s="149" t="s">
-        <v>153</v>
-      </c>
-      <c r="G13" s="149" t="s">
-        <v>151</v>
-      </c>
-      <c r="H13" s="150" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" s="86" customFormat="1" ht="49.95" customHeight="1">
-      <c r="B14" s="148">
+      <c r="D13" s="89" t="s">
+        <v>126</v>
+      </c>
+      <c r="E13" s="89" t="s">
+        <v>131</v>
+      </c>
+      <c r="F13" s="89" t="s">
+        <v>123</v>
+      </c>
+      <c r="G13" s="89" t="s">
+        <v>121</v>
+      </c>
+      <c r="H13" s="90" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" s="78" customFormat="1" ht="49.9" customHeight="1">
+      <c r="B14" s="88">
         <v>46116</v>
       </c>
-      <c r="C14" s="149">
+      <c r="C14" s="89">
         <v>1.1000000000000001</v>
       </c>
-      <c r="D14" s="149" t="s">
-        <v>157</v>
-      </c>
-      <c r="E14" s="149" t="s">
-        <v>169</v>
-      </c>
-      <c r="F14" s="149" t="s">
-        <v>152</v>
-      </c>
-      <c r="G14" s="149" t="s">
-        <v>151</v>
-      </c>
-      <c r="H14" s="150" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" s="86" customFormat="1" ht="49.95" customHeight="1">
-      <c r="B15" s="148">
+      <c r="D14" s="89" t="s">
+        <v>127</v>
+      </c>
+      <c r="E14" s="89" t="s">
+        <v>139</v>
+      </c>
+      <c r="F14" s="89" t="s">
+        <v>122</v>
+      </c>
+      <c r="G14" s="89" t="s">
+        <v>121</v>
+      </c>
+      <c r="H14" s="90" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" s="78" customFormat="1" ht="49.9" customHeight="1">
+      <c r="B15" s="88">
         <v>46116</v>
       </c>
-      <c r="C15" s="149">
+      <c r="C15" s="89">
         <v>1.1000000000000001</v>
       </c>
-      <c r="D15" s="149" t="s">
-        <v>166</v>
-      </c>
-      <c r="E15" s="149" t="s">
-        <v>168</v>
-      </c>
-      <c r="F15" s="149" t="s">
-        <v>151</v>
-      </c>
-      <c r="G15" s="149" t="s">
-        <v>151</v>
-      </c>
-      <c r="H15" s="150" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" s="86" customFormat="1" ht="49.95" customHeight="1">
-      <c r="B16" s="148">
+      <c r="D15" s="89" t="s">
+        <v>136</v>
+      </c>
+      <c r="E15" s="89" t="s">
+        <v>138</v>
+      </c>
+      <c r="F15" s="89" t="s">
+        <v>121</v>
+      </c>
+      <c r="G15" s="89" t="s">
+        <v>121</v>
+      </c>
+      <c r="H15" s="90" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" s="78" customFormat="1" ht="49.9" customHeight="1">
+      <c r="B16" s="88">
         <v>46116</v>
       </c>
-      <c r="C16" s="149">
+      <c r="C16" s="89">
         <v>1.1000000000000001</v>
       </c>
-      <c r="D16" s="149" t="s">
-        <v>167</v>
-      </c>
-      <c r="E16" s="149" t="s">
+      <c r="D16" s="89" t="s">
+        <v>137</v>
+      </c>
+      <c r="E16" s="89" t="s">
+        <v>140</v>
+      </c>
+      <c r="F16" s="89" t="s">
+        <v>121</v>
+      </c>
+      <c r="G16" s="89" t="s">
+        <v>121</v>
+      </c>
+      <c r="H16" s="90" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" s="79" customFormat="1" ht="49.9" customHeight="1">
+      <c r="B17" s="88">
+        <v>46330</v>
+      </c>
+      <c r="C17" s="89">
+        <v>1.2</v>
+      </c>
+      <c r="D17" s="89" t="s">
+        <v>126</v>
+      </c>
+      <c r="E17" s="89" t="s">
+        <v>142</v>
+      </c>
+      <c r="F17" s="89" t="s">
+        <v>123</v>
+      </c>
+      <c r="G17" s="89" t="s">
+        <v>121</v>
+      </c>
+      <c r="H17" s="90" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" s="79" customFormat="1" ht="49.9" customHeight="1">
+      <c r="B18" s="88">
+        <v>46330</v>
+      </c>
+      <c r="C18" s="89">
+        <v>1.2</v>
+      </c>
+      <c r="D18" s="89" t="s">
+        <v>127</v>
+      </c>
+      <c r="E18" s="89" t="s">
+        <v>143</v>
+      </c>
+      <c r="F18" s="89" t="s">
+        <v>122</v>
+      </c>
+      <c r="G18" s="89" t="s">
+        <v>121</v>
+      </c>
+      <c r="H18" s="90" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" s="78" customFormat="1" ht="49.9" customHeight="1">
+      <c r="B19" s="89" t="s">
+        <v>144</v>
+      </c>
+      <c r="C19" s="89">
+        <v>1.2</v>
+      </c>
+      <c r="D19" s="89" t="s">
+        <v>145</v>
+      </c>
+      <c r="E19" s="89"/>
+      <c r="F19" s="89" t="s">
+        <v>121</v>
+      </c>
+      <c r="G19" s="89"/>
+      <c r="H19" s="90" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" s="78" customFormat="1" ht="49.9" customHeight="1">
+      <c r="B20" s="88">
+        <v>46133</v>
+      </c>
+      <c r="C20" s="89"/>
+      <c r="D20" s="89" t="s">
         <v>170</v>
       </c>
-      <c r="F16" s="149" t="s">
-        <v>151</v>
-      </c>
-      <c r="G16" s="149" t="s">
-        <v>151</v>
-      </c>
-      <c r="H16" s="150" t="s">
+      <c r="E20" s="89" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="17" spans="2:8" s="87" customFormat="1" ht="49.95" customHeight="1">
-      <c r="B17" s="148">
-        <v>46330</v>
-      </c>
-      <c r="C17" s="149">
-        <v>1.2</v>
-      </c>
-      <c r="D17" s="149" t="s">
-        <v>156</v>
-      </c>
-      <c r="E17" s="149" t="s">
-        <v>172</v>
-      </c>
-      <c r="F17" s="149" t="s">
-        <v>153</v>
-      </c>
-      <c r="G17" s="149" t="s">
-        <v>151</v>
-      </c>
-      <c r="H17" s="150" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="18" spans="2:8" s="87" customFormat="1" ht="49.95" customHeight="1">
-      <c r="B18" s="148">
-        <v>46330</v>
-      </c>
-      <c r="C18" s="149">
-        <v>1.2</v>
-      </c>
-      <c r="D18" s="149" t="s">
-        <v>157</v>
-      </c>
-      <c r="E18" s="149" t="s">
-        <v>173</v>
-      </c>
-      <c r="F18" s="149" t="s">
-        <v>152</v>
-      </c>
-      <c r="G18" s="149" t="s">
-        <v>151</v>
-      </c>
-      <c r="H18" s="150" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" s="86" customFormat="1" ht="49.95" customHeight="1">
-      <c r="B19" s="149" t="s">
-        <v>174</v>
-      </c>
-      <c r="C19" s="149">
-        <v>1.2</v>
-      </c>
-      <c r="D19" s="149" t="s">
-        <v>175</v>
-      </c>
-      <c r="E19" s="149"/>
-      <c r="F19" s="149" t="s">
-        <v>151</v>
-      </c>
-      <c r="G19" s="149"/>
-      <c r="H19" s="150" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="20" spans="2:8" s="86" customFormat="1" ht="49.95" customHeight="1">
-      <c r="B20" s="149"/>
-      <c r="C20" s="149"/>
-      <c r="D20" s="149"/>
-      <c r="E20" s="149"/>
-      <c r="F20" s="149"/>
-      <c r="G20" s="149"/>
-      <c r="H20" s="150"/>
-    </row>
-    <row r="21" spans="2:8" s="86" customFormat="1" ht="49.95" customHeight="1">
-      <c r="B21" s="149"/>
-      <c r="C21" s="149"/>
-      <c r="D21" s="149"/>
-      <c r="E21" s="149"/>
-      <c r="F21" s="149"/>
-      <c r="G21" s="149"/>
-      <c r="H21" s="150"/>
-    </row>
-    <row r="22" spans="2:8" s="86" customFormat="1" ht="49.95" customHeight="1">
-      <c r="B22" s="149"/>
-      <c r="C22" s="149"/>
-      <c r="D22" s="149"/>
-      <c r="E22" s="149"/>
-      <c r="F22" s="149"/>
-      <c r="G22" s="149"/>
-      <c r="H22" s="150"/>
-    </row>
-    <row r="23" spans="2:8" s="86" customFormat="1" ht="49.95" customHeight="1">
-      <c r="B23" s="149"/>
-      <c r="C23" s="149"/>
-      <c r="D23" s="149"/>
-      <c r="E23" s="149"/>
-      <c r="F23" s="149"/>
-      <c r="G23" s="149"/>
-      <c r="H23" s="150"/>
-    </row>
-    <row r="24" spans="2:8" s="86" customFormat="1" ht="49.95" customHeight="1">
-      <c r="B24" s="149"/>
-      <c r="C24" s="149"/>
-      <c r="D24" s="149"/>
-      <c r="E24" s="149"/>
-      <c r="F24" s="149"/>
-      <c r="G24" s="149"/>
-      <c r="H24" s="150"/>
-    </row>
-    <row r="25" spans="2:8" s="86" customFormat="1" ht="49.95" customHeight="1">
-      <c r="B25" s="149"/>
-      <c r="C25" s="149"/>
-      <c r="D25" s="149"/>
-      <c r="E25" s="149"/>
-      <c r="F25" s="149"/>
-      <c r="G25" s="149"/>
-      <c r="H25" s="150"/>
-    </row>
-    <row r="26" spans="2:8" s="86" customFormat="1" ht="49.95" customHeight="1">
-      <c r="B26" s="149"/>
-      <c r="C26" s="149"/>
-      <c r="D26" s="149"/>
-      <c r="E26" s="149"/>
-      <c r="F26" s="149"/>
-      <c r="G26" s="149"/>
-      <c r="H26" s="150"/>
-    </row>
-    <row r="27" spans="2:8" ht="49.95" customHeight="1">
-      <c r="B27" s="149"/>
-      <c r="C27" s="149"/>
-      <c r="D27" s="149"/>
-      <c r="E27" s="149"/>
-      <c r="F27" s="149"/>
-      <c r="G27" s="149"/>
-      <c r="H27" s="150"/>
-    </row>
-    <row r="28" spans="2:8" ht="49.95" customHeight="1">
-      <c r="B28" s="149"/>
-      <c r="C28" s="149"/>
-      <c r="D28" s="149"/>
-      <c r="E28" s="149"/>
-      <c r="F28" s="149"/>
-      <c r="G28" s="149"/>
-      <c r="H28" s="150"/>
-    </row>
-    <row r="29" spans="2:8" ht="49.95" customHeight="1">
-      <c r="B29" s="151"/>
-      <c r="C29" s="151"/>
-      <c r="D29" s="151"/>
-      <c r="E29" s="151"/>
-      <c r="F29" s="151"/>
-      <c r="G29" s="151"/>
-      <c r="H29" s="152"/>
-    </row>
-    <row r="30" spans="2:8" ht="44.4" customHeight="1">
-      <c r="B30" s="153"/>
-      <c r="C30" s="153"/>
-      <c r="D30" s="153"/>
-      <c r="E30" s="153"/>
-      <c r="F30" s="153"/>
-      <c r="G30" s="153"/>
-      <c r="H30" s="153"/>
+      <c r="F20" s="89" t="s">
+        <v>122</v>
+      </c>
+      <c r="G20" s="89"/>
+      <c r="H20" s="90" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" s="78" customFormat="1" ht="49.9" customHeight="1">
+      <c r="B21" s="89"/>
+      <c r="C21" s="89"/>
+      <c r="D21" s="89"/>
+      <c r="E21" s="89"/>
+      <c r="F21" s="89"/>
+      <c r="G21" s="89"/>
+      <c r="H21" s="90"/>
+    </row>
+    <row r="22" spans="2:8" s="78" customFormat="1" ht="49.9" customHeight="1">
+      <c r="B22" s="89"/>
+      <c r="C22" s="89"/>
+      <c r="D22" s="89"/>
+      <c r="E22" s="89"/>
+      <c r="F22" s="89"/>
+      <c r="G22" s="89"/>
+      <c r="H22" s="90"/>
+    </row>
+    <row r="23" spans="2:8" s="78" customFormat="1" ht="49.9" customHeight="1">
+      <c r="B23" s="89"/>
+      <c r="C23" s="89"/>
+      <c r="D23" s="89"/>
+      <c r="E23" s="89"/>
+      <c r="F23" s="89"/>
+      <c r="G23" s="89"/>
+      <c r="H23" s="90"/>
+    </row>
+    <row r="24" spans="2:8" s="78" customFormat="1" ht="49.9" customHeight="1">
+      <c r="B24" s="89"/>
+      <c r="C24" s="89"/>
+      <c r="D24" s="89"/>
+      <c r="E24" s="89"/>
+      <c r="F24" s="89"/>
+      <c r="G24" s="89"/>
+      <c r="H24" s="90"/>
+    </row>
+    <row r="25" spans="2:8" s="78" customFormat="1" ht="49.9" customHeight="1">
+      <c r="B25" s="89"/>
+      <c r="C25" s="89"/>
+      <c r="D25" s="89"/>
+      <c r="E25" s="89"/>
+      <c r="F25" s="89"/>
+      <c r="G25" s="89"/>
+      <c r="H25" s="90"/>
+    </row>
+    <row r="26" spans="2:8" s="78" customFormat="1" ht="49.9" customHeight="1">
+      <c r="B26" s="89"/>
+      <c r="C26" s="89"/>
+      <c r="D26" s="89"/>
+      <c r="E26" s="89"/>
+      <c r="F26" s="89"/>
+      <c r="G26" s="89"/>
+      <c r="H26" s="90"/>
+    </row>
+    <row r="27" spans="2:8" ht="49.9" customHeight="1">
+      <c r="B27" s="89"/>
+      <c r="C27" s="89"/>
+      <c r="D27" s="89"/>
+      <c r="E27" s="89"/>
+      <c r="F27" s="89"/>
+      <c r="G27" s="89"/>
+      <c r="H27" s="90"/>
+    </row>
+    <row r="28" spans="2:8" ht="49.9" customHeight="1">
+      <c r="B28" s="89"/>
+      <c r="C28" s="89"/>
+      <c r="D28" s="89"/>
+      <c r="E28" s="89"/>
+      <c r="F28" s="89"/>
+      <c r="G28" s="89"/>
+      <c r="H28" s="90"/>
+    </row>
+    <row r="29" spans="2:8" ht="49.9" customHeight="1">
+      <c r="B29" s="91"/>
+      <c r="C29" s="91"/>
+      <c r="D29" s="91"/>
+      <c r="E29" s="91"/>
+      <c r="F29" s="91"/>
+      <c r="G29" s="91"/>
+      <c r="H29" s="92"/>
+    </row>
+    <row r="30" spans="2:8" ht="44.45" customHeight="1">
+      <c r="B30" s="93"/>
+      <c r="C30" s="93"/>
+      <c r="D30" s="93"/>
+      <c r="E30" s="93"/>
+      <c r="F30" s="93"/>
+      <c r="G30" s="93"/>
+      <c r="H30" s="93"/>
     </row>
     <row r="31" spans="2:8" ht="39" customHeight="1">
-      <c r="B31" s="153"/>
-      <c r="C31" s="153"/>
-      <c r="D31" s="153"/>
-      <c r="E31" s="153"/>
-      <c r="F31" s="153"/>
-      <c r="G31" s="153"/>
-      <c r="H31" s="153"/>
+      <c r="B31" s="93"/>
+      <c r="C31" s="93"/>
+      <c r="D31" s="93"/>
+      <c r="E31" s="93"/>
+      <c r="F31" s="93"/>
+      <c r="G31" s="93"/>
+      <c r="H31" s="93"/>
     </row>
   </sheetData>
   <phoneticPr fontId="33" type="noConversion"/>
@@ -2775,31 +3050,504 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K22"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="15.625" customWidth="1"/>
+    <col min="2" max="2" width="27.5" customWidth="1"/>
+    <col min="3" max="3" width="33" customWidth="1"/>
+    <col min="6" max="6" width="12.875" customWidth="1"/>
+    <col min="7" max="7" width="0.875" customWidth="1"/>
+    <col min="9" max="9" width="7.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="14.25">
+      <c r="A1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="131" t="s">
+        <v>199</v>
+      </c>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="31"/>
+    </row>
+    <row r="2" spans="1:11" ht="15" thickBot="1">
+      <c r="A2" s="33"/>
+      <c r="B2" s="130"/>
+      <c r="C2" s="130"/>
+      <c r="D2" s="130"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="31"/>
+    </row>
+    <row r="3" spans="1:11" ht="14.25" customHeight="1">
+      <c r="A3" s="63" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="158" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="159"/>
+      <c r="D3" s="160"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="146"/>
+      <c r="J3" s="146"/>
+      <c r="K3" s="146"/>
+    </row>
+    <row r="4" spans="1:11" ht="13.5" customHeight="1">
+      <c r="A4" s="37" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="161" t="s">
+        <v>201</v>
+      </c>
+      <c r="C4" s="162"/>
+      <c r="D4" s="163"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="35"/>
+      <c r="I4" s="146"/>
+      <c r="J4" s="146"/>
+      <c r="K4" s="146"/>
+    </row>
+    <row r="5" spans="1:11" ht="12.75" customHeight="1">
+      <c r="A5" s="37" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="164" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="165"/>
+      <c r="D5" s="166"/>
+      <c r="E5" s="39"/>
+      <c r="F5" s="39"/>
+      <c r="G5" s="39"/>
+      <c r="H5" s="39"/>
+      <c r="I5" s="167"/>
+      <c r="J5" s="167"/>
+      <c r="K5" s="167"/>
+    </row>
+    <row r="6" spans="1:11" ht="14.25">
+      <c r="A6" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="41">
+        <f>COUNTIF(J12:J21,"Pass")</f>
+        <v>0</v>
+      </c>
+      <c r="C6" s="42" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="43">
+        <f>COUNTIF(J10:J740,"Pending")</f>
+        <v>8</v>
+      </c>
+      <c r="E6" s="83"/>
+      <c r="F6" s="83"/>
+      <c r="G6" s="83"/>
+      <c r="H6" s="83"/>
+      <c r="I6" s="146"/>
+      <c r="J6" s="146"/>
+      <c r="K6" s="146"/>
+    </row>
+    <row r="7" spans="1:11" ht="15" thickBot="1">
+      <c r="A7" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="45">
+        <f>COUNTIF(J12:J21,"Fail")</f>
+        <v>0</v>
+      </c>
+      <c r="C7" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="47">
+        <f>COUNTA(A12:A22)-3</f>
+        <v>8</v>
+      </c>
+      <c r="E7" s="48"/>
+      <c r="F7" s="48"/>
+      <c r="G7" s="48"/>
+      <c r="H7" s="48"/>
+      <c r="I7" s="146"/>
+      <c r="J7" s="146"/>
+      <c r="K7" s="146"/>
+    </row>
+    <row r="8" spans="1:11" ht="14.25">
+      <c r="A8" s="147"/>
+      <c r="B8" s="147"/>
+      <c r="C8" s="147"/>
+      <c r="D8" s="147"/>
+      <c r="E8" s="83"/>
+      <c r="F8" s="83"/>
+      <c r="G8" s="83"/>
+      <c r="H8" s="83"/>
+      <c r="I8" s="83"/>
+      <c r="J8" s="49"/>
+      <c r="K8" s="49"/>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="138" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="149" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="138" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="151" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" s="152"/>
+      <c r="F9" s="152"/>
+      <c r="G9" s="153"/>
+      <c r="H9" s="157" t="s">
+        <v>29</v>
+      </c>
+      <c r="I9" s="137" t="s">
+        <v>30</v>
+      </c>
+      <c r="J9" s="137" t="s">
+        <v>31</v>
+      </c>
+      <c r="K9" s="137" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="148"/>
+      <c r="B10" s="150"/>
+      <c r="C10" s="148"/>
+      <c r="D10" s="154"/>
+      <c r="E10" s="155"/>
+      <c r="F10" s="155"/>
+      <c r="G10" s="156"/>
+      <c r="H10" s="138"/>
+      <c r="I10" s="138"/>
+      <c r="J10" s="138"/>
+      <c r="K10" s="138"/>
+    </row>
+    <row r="11" spans="1:11" ht="15">
+      <c r="A11" s="139"/>
+      <c r="B11" s="139"/>
+      <c r="C11" s="139"/>
+      <c r="D11" s="139"/>
+      <c r="E11" s="139"/>
+      <c r="F11" s="139"/>
+      <c r="G11" s="139"/>
+      <c r="H11" s="139"/>
+      <c r="I11" s="139"/>
+      <c r="J11" s="139"/>
+      <c r="K11" s="140"/>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="141" t="s">
+        <v>172</v>
+      </c>
+      <c r="B12" s="142"/>
+      <c r="C12" s="142"/>
+      <c r="D12" s="142"/>
+      <c r="E12" s="142"/>
+      <c r="F12" s="142"/>
+      <c r="G12" s="142"/>
+      <c r="H12" s="142"/>
+      <c r="I12" s="142"/>
+      <c r="J12" s="142"/>
+      <c r="K12" s="143"/>
+    </row>
+    <row r="13" spans="1:11" ht="52.5" customHeight="1">
+      <c r="A13" s="120" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="53" t="s">
+        <v>173</v>
+      </c>
+      <c r="C13" s="53" t="s">
+        <v>174</v>
+      </c>
+      <c r="D13" s="144" t="s">
+        <v>175</v>
+      </c>
+      <c r="E13" s="134"/>
+      <c r="F13" s="134"/>
+      <c r="G13" s="121"/>
+      <c r="H13" s="122"/>
+      <c r="I13" s="123"/>
+      <c r="J13" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="K13" s="53"/>
+    </row>
+    <row r="14" spans="1:11" ht="57" customHeight="1">
+      <c r="A14" s="120" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="53" t="s">
+        <v>176</v>
+      </c>
+      <c r="C14" s="53" t="s">
+        <v>174</v>
+      </c>
+      <c r="D14" s="144" t="s">
+        <v>177</v>
+      </c>
+      <c r="E14" s="134"/>
+      <c r="F14" s="134"/>
+      <c r="G14" s="121"/>
+      <c r="H14" s="122"/>
+      <c r="I14" s="123"/>
+      <c r="J14" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="K14" s="53"/>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" s="145" t="s">
+        <v>178</v>
+      </c>
+      <c r="B15" s="136"/>
+      <c r="C15" s="136"/>
+      <c r="D15" s="124"/>
+      <c r="E15" s="124"/>
+      <c r="F15" s="124"/>
+      <c r="G15" s="124"/>
+      <c r="H15" s="124"/>
+      <c r="I15" s="124"/>
+      <c r="J15" s="124"/>
+      <c r="K15" s="125"/>
+    </row>
+    <row r="16" spans="1:11" ht="78" customHeight="1">
+      <c r="A16" s="120" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" s="126" t="s">
+        <v>179</v>
+      </c>
+      <c r="C16" s="127" t="s">
+        <v>180</v>
+      </c>
+      <c r="D16" s="132" t="s">
+        <v>181</v>
+      </c>
+      <c r="E16" s="134"/>
+      <c r="F16" s="134"/>
+      <c r="G16" s="121"/>
+      <c r="H16" s="122"/>
+      <c r="I16" s="128"/>
+      <c r="J16" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="K16" s="53"/>
+    </row>
+    <row r="17" spans="1:11" ht="40.5" customHeight="1">
+      <c r="A17" s="120" t="s">
+        <v>63</v>
+      </c>
+      <c r="B17" s="127" t="s">
+        <v>182</v>
+      </c>
+      <c r="C17" s="127" t="s">
+        <v>183</v>
+      </c>
+      <c r="D17" s="132" t="s">
+        <v>184</v>
+      </c>
+      <c r="E17" s="134"/>
+      <c r="F17" s="134"/>
+      <c r="G17" s="121"/>
+      <c r="H17" s="122"/>
+      <c r="I17" s="128"/>
+      <c r="J17" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="K17" s="53"/>
+    </row>
+    <row r="18" spans="1:11" ht="54.75" customHeight="1">
+      <c r="A18" s="120" t="s">
+        <v>68</v>
+      </c>
+      <c r="B18" s="127" t="s">
+        <v>185</v>
+      </c>
+      <c r="C18" s="127" t="s">
+        <v>186</v>
+      </c>
+      <c r="D18" s="132" t="s">
+        <v>187</v>
+      </c>
+      <c r="E18" s="134"/>
+      <c r="F18" s="134"/>
+      <c r="G18" s="121"/>
+      <c r="H18" s="122"/>
+      <c r="I18" s="128"/>
+      <c r="J18" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="K18" s="53"/>
+    </row>
+    <row r="19" spans="1:11" ht="105.75" customHeight="1">
+      <c r="A19" s="120" t="s">
+        <v>152</v>
+      </c>
+      <c r="B19" s="127" t="s">
+        <v>188</v>
+      </c>
+      <c r="C19" s="127" t="s">
+        <v>189</v>
+      </c>
+      <c r="D19" s="132" t="s">
+        <v>190</v>
+      </c>
+      <c r="E19" s="134"/>
+      <c r="F19" s="134"/>
+      <c r="G19" s="121"/>
+      <c r="H19" s="122"/>
+      <c r="I19" s="128"/>
+      <c r="J19" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="K19" s="53"/>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" s="135" t="s">
+        <v>191</v>
+      </c>
+      <c r="B20" s="136"/>
+      <c r="C20" s="136"/>
+      <c r="D20" s="124"/>
+      <c r="E20" s="124"/>
+      <c r="F20" s="124"/>
+      <c r="G20" s="124"/>
+      <c r="H20" s="124"/>
+      <c r="I20" s="124"/>
+      <c r="J20" s="124"/>
+      <c r="K20" s="125"/>
+    </row>
+    <row r="21" spans="1:11" ht="65.25" customHeight="1">
+      <c r="A21" s="129" t="s">
+        <v>154</v>
+      </c>
+      <c r="B21" s="105" t="s">
+        <v>192</v>
+      </c>
+      <c r="C21" s="105" t="s">
+        <v>193</v>
+      </c>
+      <c r="D21" s="132" t="s">
+        <v>194</v>
+      </c>
+      <c r="E21" s="133"/>
+      <c r="F21" s="133"/>
+      <c r="G21" s="121"/>
+      <c r="H21" s="122"/>
+      <c r="I21" s="128"/>
+      <c r="J21" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="K21" s="53"/>
+    </row>
+    <row r="22" spans="1:11" ht="30" customHeight="1">
+      <c r="A22" s="129" t="s">
+        <v>155</v>
+      </c>
+      <c r="B22" s="105" t="s">
+        <v>195</v>
+      </c>
+      <c r="C22" s="105" t="s">
+        <v>196</v>
+      </c>
+      <c r="D22" s="132" t="s">
+        <v>197</v>
+      </c>
+      <c r="E22" s="133"/>
+      <c r="F22" s="133"/>
+      <c r="G22" s="121"/>
+      <c r="H22" s="122"/>
+      <c r="I22" s="128"/>
+      <c r="J22" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="K22" s="53"/>
+    </row>
+  </sheetData>
+  <mergeCells count="29">
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D9:G10"/>
+    <mergeCell ref="H9:H10"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="K9:K10"/>
+    <mergeCell ref="A11:K11"/>
+    <mergeCell ref="A12:K12"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D19:F19"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:L55"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.8" outlineLevelRow="1"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14.25" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" customWidth="1"/>
-    <col min="2" max="2" width="18.109375" customWidth="1"/>
-    <col min="3" max="3" width="42.109375" customWidth="1"/>
-    <col min="6" max="6" width="23.6640625" customWidth="1"/>
-    <col min="7" max="7" width="18.44140625" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="15.625" customWidth="1"/>
+    <col min="2" max="2" width="18.125" customWidth="1"/>
+    <col min="3" max="3" width="42.125" customWidth="1"/>
+    <col min="6" max="6" width="23.625" customWidth="1"/>
+    <col min="7" max="7" width="18.5" hidden="1" customWidth="1"/>
     <col min="8" max="8" width="38" customWidth="1"/>
-    <col min="9" max="9" width="17.109375" customWidth="1"/>
+    <col min="9" max="9" width="17.125" customWidth="1"/>
     <col min="10" max="10" width="9" style="6"/>
     <col min="11" max="11" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="75" customFormat="1" ht="12.75" customHeight="1">
+    <row r="1" spans="1:12" s="67" customFormat="1" ht="12.75" customHeight="1">
       <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="125"/>
-      <c r="C1" s="125"/>
-      <c r="D1" s="125"/>
+      <c r="B1" s="170"/>
+      <c r="C1" s="170"/>
+      <c r="D1" s="170"/>
       <c r="E1" s="31"/>
       <c r="F1" s="31"/>
       <c r="G1" s="31"/>
@@ -2809,11 +3557,11 @@
       <c r="K1" s="31"/>
       <c r="L1" s="33"/>
     </row>
-    <row r="2" spans="1:12" s="75" customFormat="1" ht="11.25" customHeight="1">
+    <row r="2" spans="1:12" s="67" customFormat="1" ht="11.25" customHeight="1">
       <c r="A2" s="33"/>
-      <c r="B2" s="126"/>
-      <c r="C2" s="126"/>
-      <c r="D2" s="126"/>
+      <c r="B2" s="171"/>
+      <c r="C2" s="171"/>
+      <c r="D2" s="171"/>
       <c r="E2" s="31"/>
       <c r="F2" s="31"/>
       <c r="G2" s="31"/>
@@ -2823,61 +3571,61 @@
       <c r="K2" s="31"/>
       <c r="L2" s="33"/>
     </row>
-    <row r="3" spans="1:12" s="76" customFormat="1" ht="15" customHeight="1">
-      <c r="A3" s="71" t="s">
+    <row r="3" spans="1:12" s="68" customFormat="1" ht="15" customHeight="1">
+      <c r="A3" s="63" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="131" t="s">
+      <c r="B3" s="159" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="131"/>
-      <c r="D3" s="132"/>
+      <c r="C3" s="159"/>
+      <c r="D3" s="160"/>
       <c r="E3" s="35"/>
       <c r="F3" s="35"/>
       <c r="G3" s="35"/>
       <c r="H3" s="35"/>
-      <c r="I3" s="97"/>
-      <c r="J3" s="97"/>
-      <c r="K3" s="97"/>
-      <c r="L3" s="81"/>
-    </row>
-    <row r="4" spans="1:12" s="76" customFormat="1" ht="13.2">
+      <c r="I3" s="146"/>
+      <c r="J3" s="146"/>
+      <c r="K3" s="146"/>
+      <c r="L3" s="73"/>
+    </row>
+    <row r="4" spans="1:12" s="68" customFormat="1" ht="12.75">
       <c r="A4" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="98" t="s">
+      <c r="B4" s="161" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="99"/>
-      <c r="D4" s="100"/>
+      <c r="C4" s="162"/>
+      <c r="D4" s="163"/>
       <c r="E4" s="35"/>
       <c r="F4" s="35"/>
       <c r="G4" s="35"/>
       <c r="H4" s="35"/>
-      <c r="I4" s="97"/>
-      <c r="J4" s="97"/>
-      <c r="K4" s="97"/>
-      <c r="L4" s="81"/>
-    </row>
-    <row r="5" spans="1:12" s="77" customFormat="1" ht="26.4">
+      <c r="I4" s="146"/>
+      <c r="J4" s="146"/>
+      <c r="K4" s="146"/>
+      <c r="L4" s="73"/>
+    </row>
+    <row r="5" spans="1:12" s="69" customFormat="1" ht="25.5">
       <c r="A5" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="101" t="s">
+      <c r="B5" s="164" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="102"/>
-      <c r="D5" s="103"/>
+      <c r="C5" s="165"/>
+      <c r="D5" s="166"/>
       <c r="E5" s="39"/>
       <c r="F5" s="39"/>
       <c r="G5" s="39"/>
       <c r="H5" s="39"/>
-      <c r="I5" s="104"/>
-      <c r="J5" s="104"/>
-      <c r="K5" s="104"/>
-      <c r="L5" s="82"/>
-    </row>
-    <row r="6" spans="1:12" s="76" customFormat="1" ht="15" customHeight="1">
+      <c r="I5" s="167"/>
+      <c r="J5" s="167"/>
+      <c r="K5" s="167"/>
+      <c r="L5" s="74"/>
+    </row>
+    <row r="6" spans="1:12" s="68" customFormat="1" ht="15" customHeight="1">
       <c r="A6" s="40" t="s">
         <v>21</v>
       </c>
@@ -2896,12 +3644,12 @@
       <c r="F6" s="36"/>
       <c r="G6" s="36"/>
       <c r="H6" s="36"/>
-      <c r="I6" s="97"/>
-      <c r="J6" s="97"/>
-      <c r="K6" s="97"/>
-      <c r="L6" s="81"/>
-    </row>
-    <row r="7" spans="1:12" s="76" customFormat="1" ht="15" customHeight="1">
+      <c r="I6" s="146"/>
+      <c r="J6" s="146"/>
+      <c r="K6" s="146"/>
+      <c r="L6" s="73"/>
+    </row>
+    <row r="7" spans="1:12" s="68" customFormat="1" ht="15" customHeight="1">
       <c r="A7" s="44" t="s">
         <v>23</v>
       </c>
@@ -2920,16 +3668,16 @@
       <c r="F7" s="48"/>
       <c r="G7" s="48"/>
       <c r="H7" s="48"/>
-      <c r="I7" s="97"/>
-      <c r="J7" s="97"/>
-      <c r="K7" s="97"/>
-      <c r="L7" s="81"/>
-    </row>
-    <row r="8" spans="1:12" s="76" customFormat="1" ht="15" customHeight="1">
-      <c r="A8" s="107"/>
-      <c r="B8" s="107"/>
-      <c r="C8" s="107"/>
-      <c r="D8" s="107"/>
+      <c r="I7" s="146"/>
+      <c r="J7" s="146"/>
+      <c r="K7" s="146"/>
+      <c r="L7" s="73"/>
+    </row>
+    <row r="8" spans="1:12" s="68" customFormat="1" ht="15" customHeight="1">
+      <c r="A8" s="147"/>
+      <c r="B8" s="147"/>
+      <c r="C8" s="147"/>
+      <c r="D8" s="147"/>
       <c r="E8" s="36"/>
       <c r="F8" s="36"/>
       <c r="G8" s="36"/>
@@ -2937,81 +3685,81 @@
       <c r="I8" s="36"/>
       <c r="J8" s="49"/>
       <c r="K8" s="49"/>
-      <c r="L8" s="81"/>
-    </row>
-    <row r="9" spans="1:12" s="78" customFormat="1" ht="12" customHeight="1">
-      <c r="A9" s="113" t="s">
+      <c r="L8" s="73"/>
+    </row>
+    <row r="9" spans="1:12" s="70" customFormat="1" ht="12" customHeight="1">
+      <c r="A9" s="138" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="115" t="s">
+      <c r="B9" s="149" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="113" t="s">
+      <c r="C9" s="138" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="119" t="s">
+      <c r="D9" s="151" t="s">
         <v>28</v>
       </c>
-      <c r="E9" s="120"/>
-      <c r="F9" s="120"/>
-      <c r="G9" s="121"/>
-      <c r="H9" s="117" t="s">
+      <c r="E9" s="152"/>
+      <c r="F9" s="152"/>
+      <c r="G9" s="153"/>
+      <c r="H9" s="157" t="s">
         <v>29</v>
       </c>
-      <c r="I9" s="118" t="s">
+      <c r="I9" s="137" t="s">
         <v>30</v>
       </c>
-      <c r="J9" s="118" t="s">
+      <c r="J9" s="137" t="s">
         <v>31</v>
       </c>
-      <c r="K9" s="118" t="s">
+      <c r="K9" s="137" t="s">
         <v>32</v>
       </c>
-      <c r="L9" s="83"/>
-    </row>
-    <row r="10" spans="1:12" s="76" customFormat="1" ht="12" customHeight="1">
-      <c r="A10" s="114"/>
-      <c r="B10" s="116"/>
-      <c r="C10" s="114"/>
-      <c r="D10" s="122"/>
-      <c r="E10" s="123"/>
-      <c r="F10" s="123"/>
-      <c r="G10" s="124"/>
-      <c r="H10" s="113"/>
-      <c r="I10" s="113"/>
-      <c r="J10" s="113"/>
-      <c r="K10" s="113"/>
-      <c r="L10" s="81"/>
-    </row>
-    <row r="11" spans="1:12" s="79" customFormat="1" ht="15">
-      <c r="A11" s="108"/>
-      <c r="B11" s="108"/>
-      <c r="C11" s="108"/>
-      <c r="D11" s="108"/>
-      <c r="E11" s="108"/>
-      <c r="F11" s="108"/>
-      <c r="G11" s="108"/>
-      <c r="H11" s="108"/>
-      <c r="I11" s="108"/>
-      <c r="J11" s="108"/>
-      <c r="K11" s="109"/>
-    </row>
-    <row r="12" spans="1:12" s="80" customFormat="1" ht="13.2">
-      <c r="A12" s="110" t="s">
+      <c r="L9" s="75"/>
+    </row>
+    <row r="10" spans="1:12" s="68" customFormat="1" ht="12" customHeight="1">
+      <c r="A10" s="148"/>
+      <c r="B10" s="150"/>
+      <c r="C10" s="148"/>
+      <c r="D10" s="154"/>
+      <c r="E10" s="155"/>
+      <c r="F10" s="155"/>
+      <c r="G10" s="156"/>
+      <c r="H10" s="138"/>
+      <c r="I10" s="138"/>
+      <c r="J10" s="138"/>
+      <c r="K10" s="138"/>
+      <c r="L10" s="73"/>
+    </row>
+    <row r="11" spans="1:12" s="71" customFormat="1" ht="15">
+      <c r="A11" s="139"/>
+      <c r="B11" s="139"/>
+      <c r="C11" s="139"/>
+      <c r="D11" s="139"/>
+      <c r="E11" s="139"/>
+      <c r="F11" s="139"/>
+      <c r="G11" s="139"/>
+      <c r="H11" s="139"/>
+      <c r="I11" s="139"/>
+      <c r="J11" s="139"/>
+      <c r="K11" s="140"/>
+    </row>
+    <row r="12" spans="1:12" s="72" customFormat="1" ht="12.75">
+      <c r="A12" s="141" t="s">
         <v>33</v>
       </c>
-      <c r="B12" s="111"/>
-      <c r="C12" s="111"/>
-      <c r="D12" s="111"/>
-      <c r="E12" s="111"/>
-      <c r="F12" s="111"/>
-      <c r="G12" s="111"/>
-      <c r="H12" s="111"/>
-      <c r="I12" s="111"/>
-      <c r="J12" s="111"/>
-      <c r="K12" s="112"/>
-    </row>
-    <row r="13" spans="1:12" s="80" customFormat="1" ht="79.2" outlineLevel="1">
+      <c r="B12" s="142"/>
+      <c r="C12" s="142"/>
+      <c r="D12" s="142"/>
+      <c r="E12" s="142"/>
+      <c r="F12" s="142"/>
+      <c r="G12" s="142"/>
+      <c r="H12" s="142"/>
+      <c r="I12" s="142"/>
+      <c r="J12" s="142"/>
+      <c r="K12" s="143"/>
+    </row>
+    <row r="13" spans="1:12" s="72" customFormat="1" ht="76.5" outlineLevel="1">
       <c r="A13" s="52" t="s">
         <v>34</v>
       </c>
@@ -3021,25 +3769,25 @@
       <c r="C13" s="54" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="127" t="s">
+      <c r="D13" s="172" t="s">
         <v>37</v>
       </c>
-      <c r="E13" s="128"/>
-      <c r="F13" s="128"/>
-      <c r="G13" s="59"/>
-      <c r="H13" s="56"/>
-      <c r="I13" s="57"/>
+      <c r="E13" s="173"/>
+      <c r="F13" s="173"/>
+      <c r="G13" s="58"/>
+      <c r="H13" s="55"/>
+      <c r="I13" s="56"/>
       <c r="J13" s="54" t="s">
         <v>21</v>
       </c>
       <c r="K13" s="54"/>
     </row>
-    <row r="14" spans="1:12" s="80" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A14" s="129" t="s">
+    <row r="14" spans="1:12" s="72" customFormat="1" ht="12.75" outlineLevel="1">
+      <c r="A14" s="174" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="130"/>
-      <c r="C14" s="130"/>
+      <c r="B14" s="175"/>
+      <c r="C14" s="175"/>
       <c r="D14" s="50"/>
       <c r="E14" s="50"/>
       <c r="F14" s="50"/>
@@ -3049,35 +3797,35 @@
       <c r="J14" s="50"/>
       <c r="K14" s="51"/>
     </row>
-    <row r="15" spans="1:12" s="80" customFormat="1" ht="63.75" customHeight="1" outlineLevel="1">
+    <row r="15" spans="1:12" s="72" customFormat="1" ht="63.75" customHeight="1" outlineLevel="1">
       <c r="A15" s="52" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="84" t="s">
+      <c r="B15" s="76" t="s">
         <v>40</v>
       </c>
-      <c r="C15" s="63" t="s">
+      <c r="C15" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="D15" s="105" t="s">
+      <c r="D15" s="168" t="s">
         <v>42</v>
       </c>
-      <c r="E15" s="128"/>
-      <c r="F15" s="128"/>
-      <c r="G15" s="59"/>
-      <c r="H15" s="56"/>
-      <c r="I15" s="58"/>
+      <c r="E15" s="173"/>
+      <c r="F15" s="173"/>
+      <c r="G15" s="58"/>
+      <c r="H15" s="55"/>
+      <c r="I15" s="57"/>
       <c r="J15" s="54" t="s">
         <v>21</v>
       </c>
       <c r="K15" s="54"/>
     </row>
-    <row r="16" spans="1:12" s="80" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A16" s="129" t="s">
+    <row r="16" spans="1:12" s="72" customFormat="1" ht="12.75" outlineLevel="1">
+      <c r="A16" s="174" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="130"/>
-      <c r="C16" s="130"/>
+      <c r="B16" s="175"/>
+      <c r="C16" s="175"/>
       <c r="D16" s="50"/>
       <c r="E16" s="50"/>
       <c r="F16" s="50"/>
@@ -3087,24 +3835,24 @@
       <c r="J16" s="50"/>
       <c r="K16" s="51"/>
     </row>
-    <row r="17" spans="1:11" s="80" customFormat="1" ht="63.75" customHeight="1" outlineLevel="1">
+    <row r="17" spans="1:11" s="72" customFormat="1" ht="63.75" customHeight="1" outlineLevel="1">
       <c r="A17" s="52" t="s">
         <v>44</v>
       </c>
-      <c r="B17" s="85" t="s">
+      <c r="B17" s="77" t="s">
         <v>40</v>
       </c>
       <c r="C17" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="D17" s="105" t="s">
+      <c r="D17" s="168" t="s">
         <v>46</v>
       </c>
-      <c r="E17" s="106"/>
-      <c r="F17" s="106"/>
-      <c r="G17" s="59"/>
-      <c r="H17" s="56"/>
-      <c r="I17" s="58"/>
+      <c r="E17" s="169"/>
+      <c r="F17" s="169"/>
+      <c r="G17" s="58"/>
+      <c r="H17" s="55"/>
+      <c r="I17" s="57"/>
       <c r="J17" s="54" t="s">
         <v>21</v>
       </c>
@@ -3182,29 +3930,29 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6899EEAB-D6EB-4EA8-B404-49C0A5FE4EB8}">
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L55"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.8" outlineLevelRow="1"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14.25" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" customWidth="1"/>
-    <col min="2" max="2" width="18.109375" customWidth="1"/>
-    <col min="3" max="3" width="42.109375" customWidth="1"/>
-    <col min="6" max="6" width="23.6640625" customWidth="1"/>
-    <col min="7" max="7" width="18.44140625" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="15.625" customWidth="1"/>
+    <col min="2" max="2" width="18.125" customWidth="1"/>
+    <col min="3" max="3" width="42.125" customWidth="1"/>
+    <col min="6" max="6" width="23.625" customWidth="1"/>
+    <col min="7" max="7" width="18.5" hidden="1" customWidth="1"/>
     <col min="8" max="8" width="38" customWidth="1"/>
-    <col min="9" max="9" width="17.109375" customWidth="1"/>
-    <col min="10" max="10" width="8.77734375" style="6"/>
+    <col min="9" max="9" width="17.125" customWidth="1"/>
+    <col min="10" max="10" width="8.75" style="6"/>
     <col min="11" max="11" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="75" customFormat="1" ht="12.75" customHeight="1">
+    <row r="1" spans="1:12" s="67" customFormat="1" ht="12.75" customHeight="1">
       <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="125"/>
-      <c r="C1" s="125"/>
-      <c r="D1" s="125"/>
+      <c r="B1" s="170"/>
+      <c r="C1" s="170"/>
+      <c r="D1" s="170"/>
       <c r="E1" s="31"/>
       <c r="F1" s="31"/>
       <c r="G1" s="31"/>
@@ -3214,11 +3962,11 @@
       <c r="K1" s="31"/>
       <c r="L1" s="33"/>
     </row>
-    <row r="2" spans="1:12" s="75" customFormat="1" ht="11.25" customHeight="1" thickBot="1">
+    <row r="2" spans="1:12" s="67" customFormat="1" ht="11.25" customHeight="1" thickBot="1">
       <c r="A2" s="33"/>
-      <c r="B2" s="126"/>
-      <c r="C2" s="126"/>
-      <c r="D2" s="126"/>
+      <c r="B2" s="171"/>
+      <c r="C2" s="171"/>
+      <c r="D2" s="171"/>
       <c r="E2" s="31"/>
       <c r="F2" s="31"/>
       <c r="G2" s="31"/>
@@ -3228,61 +3976,61 @@
       <c r="K2" s="31"/>
       <c r="L2" s="33"/>
     </row>
-    <row r="3" spans="1:12" s="76" customFormat="1" ht="15" customHeight="1">
-      <c r="A3" s="71" t="s">
+    <row r="3" spans="1:12" s="68" customFormat="1" ht="15" customHeight="1">
+      <c r="A3" s="63" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="131" t="s">
+      <c r="B3" s="159" t="s">
         <v>48</v>
       </c>
-      <c r="C3" s="131"/>
-      <c r="D3" s="132"/>
+      <c r="C3" s="159"/>
+      <c r="D3" s="160"/>
       <c r="E3" s="35"/>
       <c r="F3" s="35"/>
       <c r="G3" s="35"/>
       <c r="H3" s="35"/>
-      <c r="I3" s="97"/>
-      <c r="J3" s="97"/>
-      <c r="K3" s="97"/>
-      <c r="L3" s="81"/>
-    </row>
-    <row r="4" spans="1:12" s="76" customFormat="1" ht="13.2" customHeight="1">
+      <c r="I3" s="146"/>
+      <c r="J3" s="146"/>
+      <c r="K3" s="146"/>
+      <c r="L3" s="73"/>
+    </row>
+    <row r="4" spans="1:12" s="68" customFormat="1" ht="13.15" customHeight="1">
       <c r="A4" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="98" t="s">
-        <v>155</v>
-      </c>
-      <c r="C4" s="99"/>
-      <c r="D4" s="100"/>
+      <c r="B4" s="161" t="s">
+        <v>125</v>
+      </c>
+      <c r="C4" s="162"/>
+      <c r="D4" s="163"/>
       <c r="E4" s="35"/>
       <c r="F4" s="35"/>
       <c r="G4" s="35"/>
       <c r="H4" s="35"/>
-      <c r="I4" s="97"/>
-      <c r="J4" s="97"/>
-      <c r="K4" s="97"/>
-      <c r="L4" s="81"/>
-    </row>
-    <row r="5" spans="1:12" s="77" customFormat="1" ht="26.4">
+      <c r="I4" s="146"/>
+      <c r="J4" s="146"/>
+      <c r="K4" s="146"/>
+      <c r="L4" s="73"/>
+    </row>
+    <row r="5" spans="1:12" s="69" customFormat="1" ht="12.75">
       <c r="A5" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="101" t="s">
+      <c r="B5" s="164" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="102"/>
-      <c r="D5" s="103"/>
+      <c r="C5" s="165"/>
+      <c r="D5" s="166"/>
       <c r="E5" s="39"/>
       <c r="F5" s="39"/>
       <c r="G5" s="39"/>
       <c r="H5" s="39"/>
-      <c r="I5" s="104"/>
-      <c r="J5" s="104"/>
-      <c r="K5" s="104"/>
-      <c r="L5" s="82"/>
-    </row>
-    <row r="6" spans="1:12" s="76" customFormat="1" ht="15" customHeight="1">
+      <c r="I5" s="167"/>
+      <c r="J5" s="167"/>
+      <c r="K5" s="167"/>
+      <c r="L5" s="74"/>
+    </row>
+    <row r="6" spans="1:12" s="68" customFormat="1" ht="15" customHeight="1">
       <c r="A6" s="40" t="s">
         <v>21</v>
       </c>
@@ -3299,12 +4047,12 @@
       <c r="F6" s="36"/>
       <c r="G6" s="36"/>
       <c r="H6" s="36"/>
-      <c r="I6" s="97"/>
-      <c r="J6" s="97"/>
-      <c r="K6" s="97"/>
-      <c r="L6" s="81"/>
-    </row>
-    <row r="7" spans="1:12" s="76" customFormat="1" ht="15" customHeight="1" thickBot="1">
+      <c r="I6" s="146"/>
+      <c r="J6" s="146"/>
+      <c r="K6" s="146"/>
+      <c r="L6" s="73"/>
+    </row>
+    <row r="7" spans="1:12" s="68" customFormat="1" ht="15" customHeight="1" thickBot="1">
       <c r="A7" s="44" t="s">
         <v>23</v>
       </c>
@@ -3321,16 +4069,16 @@
       <c r="F7" s="48"/>
       <c r="G7" s="48"/>
       <c r="H7" s="48"/>
-      <c r="I7" s="97"/>
-      <c r="J7" s="97"/>
-      <c r="K7" s="97"/>
-      <c r="L7" s="81"/>
-    </row>
-    <row r="8" spans="1:12" s="76" customFormat="1" ht="15" customHeight="1">
-      <c r="A8" s="107"/>
-      <c r="B8" s="107"/>
-      <c r="C8" s="107"/>
-      <c r="D8" s="107"/>
+      <c r="I7" s="146"/>
+      <c r="J7" s="146"/>
+      <c r="K7" s="146"/>
+      <c r="L7" s="73"/>
+    </row>
+    <row r="8" spans="1:12" s="68" customFormat="1" ht="15" customHeight="1">
+      <c r="A8" s="147"/>
+      <c r="B8" s="147"/>
+      <c r="C8" s="147"/>
+      <c r="D8" s="147"/>
       <c r="E8" s="36"/>
       <c r="F8" s="36"/>
       <c r="G8" s="36"/>
@@ -3338,81 +4086,81 @@
       <c r="I8" s="36"/>
       <c r="J8" s="49"/>
       <c r="K8" s="49"/>
-      <c r="L8" s="81"/>
-    </row>
-    <row r="9" spans="1:12" s="78" customFormat="1" ht="12" customHeight="1">
-      <c r="A9" s="113" t="s">
+      <c r="L8" s="73"/>
+    </row>
+    <row r="9" spans="1:12" s="70" customFormat="1" ht="12" customHeight="1">
+      <c r="A9" s="138" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="115" t="s">
+      <c r="B9" s="149" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="113" t="s">
+      <c r="C9" s="138" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="119" t="s">
+      <c r="D9" s="151" t="s">
         <v>28</v>
       </c>
-      <c r="E9" s="120"/>
-      <c r="F9" s="120"/>
-      <c r="G9" s="121"/>
-      <c r="H9" s="117" t="s">
+      <c r="E9" s="152"/>
+      <c r="F9" s="152"/>
+      <c r="G9" s="153"/>
+      <c r="H9" s="157" t="s">
         <v>29</v>
       </c>
-      <c r="I9" s="118" t="s">
+      <c r="I9" s="137" t="s">
         <v>30</v>
       </c>
-      <c r="J9" s="118" t="s">
+      <c r="J9" s="137" t="s">
         <v>31</v>
       </c>
-      <c r="K9" s="118" t="s">
+      <c r="K9" s="137" t="s">
         <v>32</v>
       </c>
-      <c r="L9" s="83"/>
-    </row>
-    <row r="10" spans="1:12" s="76" customFormat="1" ht="12" customHeight="1">
-      <c r="A10" s="114"/>
-      <c r="B10" s="116"/>
-      <c r="C10" s="114"/>
-      <c r="D10" s="122"/>
-      <c r="E10" s="123"/>
-      <c r="F10" s="123"/>
-      <c r="G10" s="124"/>
-      <c r="H10" s="113"/>
-      <c r="I10" s="113"/>
-      <c r="J10" s="113"/>
-      <c r="K10" s="113"/>
-      <c r="L10" s="81"/>
-    </row>
-    <row r="11" spans="1:12" s="79" customFormat="1" ht="15">
-      <c r="A11" s="108"/>
-      <c r="B11" s="108"/>
-      <c r="C11" s="108"/>
-      <c r="D11" s="108"/>
-      <c r="E11" s="108"/>
-      <c r="F11" s="108"/>
-      <c r="G11" s="108"/>
-      <c r="H11" s="108"/>
-      <c r="I11" s="108"/>
-      <c r="J11" s="108"/>
-      <c r="K11" s="109"/>
-    </row>
-    <row r="12" spans="1:12" s="80" customFormat="1" ht="13.2">
-      <c r="A12" s="110" t="s">
+      <c r="L9" s="75"/>
+    </row>
+    <row r="10" spans="1:12" s="68" customFormat="1" ht="12" customHeight="1">
+      <c r="A10" s="148"/>
+      <c r="B10" s="150"/>
+      <c r="C10" s="148"/>
+      <c r="D10" s="154"/>
+      <c r="E10" s="155"/>
+      <c r="F10" s="155"/>
+      <c r="G10" s="156"/>
+      <c r="H10" s="138"/>
+      <c r="I10" s="138"/>
+      <c r="J10" s="138"/>
+      <c r="K10" s="138"/>
+      <c r="L10" s="73"/>
+    </row>
+    <row r="11" spans="1:12" s="71" customFormat="1" ht="15">
+      <c r="A11" s="139"/>
+      <c r="B11" s="139"/>
+      <c r="C11" s="139"/>
+      <c r="D11" s="139"/>
+      <c r="E11" s="139"/>
+      <c r="F11" s="139"/>
+      <c r="G11" s="139"/>
+      <c r="H11" s="139"/>
+      <c r="I11" s="139"/>
+      <c r="J11" s="139"/>
+      <c r="K11" s="140"/>
+    </row>
+    <row r="12" spans="1:12" s="72" customFormat="1" ht="12.75">
+      <c r="A12" s="141" t="s">
         <v>33</v>
       </c>
-      <c r="B12" s="111"/>
-      <c r="C12" s="111"/>
-      <c r="D12" s="111"/>
-      <c r="E12" s="111"/>
-      <c r="F12" s="111"/>
-      <c r="G12" s="111"/>
-      <c r="H12" s="111"/>
-      <c r="I12" s="111"/>
-      <c r="J12" s="111"/>
-      <c r="K12" s="112"/>
-    </row>
-    <row r="13" spans="1:12" s="80" customFormat="1" ht="79.2" outlineLevel="1">
+      <c r="B12" s="142"/>
+      <c r="C12" s="142"/>
+      <c r="D12" s="142"/>
+      <c r="E12" s="142"/>
+      <c r="F12" s="142"/>
+      <c r="G12" s="142"/>
+      <c r="H12" s="142"/>
+      <c r="I12" s="142"/>
+      <c r="J12" s="142"/>
+      <c r="K12" s="143"/>
+    </row>
+    <row r="13" spans="1:12" s="72" customFormat="1" ht="76.5" outlineLevel="1">
       <c r="A13" s="52" t="s">
         <v>34</v>
       </c>
@@ -3422,25 +4170,25 @@
       <c r="C13" s="54" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="127" t="s">
+      <c r="D13" s="172" t="s">
         <v>37</v>
       </c>
-      <c r="E13" s="128"/>
-      <c r="F13" s="128"/>
-      <c r="G13" s="59"/>
-      <c r="H13" s="56"/>
-      <c r="I13" s="57"/>
+      <c r="E13" s="173"/>
+      <c r="F13" s="173"/>
+      <c r="G13" s="58"/>
+      <c r="H13" s="55"/>
+      <c r="I13" s="56"/>
       <c r="J13" s="54" t="s">
         <v>21</v>
       </c>
       <c r="K13" s="54"/>
     </row>
-    <row r="14" spans="1:12" s="80" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A14" s="129" t="s">
+    <row r="14" spans="1:12" s="72" customFormat="1" ht="12.75" outlineLevel="1">
+      <c r="A14" s="174" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="130"/>
-      <c r="C14" s="130"/>
+      <c r="B14" s="175"/>
+      <c r="C14" s="175"/>
       <c r="D14" s="50"/>
       <c r="E14" s="50"/>
       <c r="F14" s="50"/>
@@ -3450,35 +4198,35 @@
       <c r="J14" s="50"/>
       <c r="K14" s="51"/>
     </row>
-    <row r="15" spans="1:12" s="80" customFormat="1" ht="63.75" customHeight="1" outlineLevel="1">
+    <row r="15" spans="1:12" s="72" customFormat="1" ht="63.75" customHeight="1" outlineLevel="1">
       <c r="A15" s="52" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="84" t="s">
+      <c r="B15" s="76" t="s">
         <v>40</v>
       </c>
-      <c r="C15" s="63" t="s">
+      <c r="C15" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="D15" s="105" t="s">
+      <c r="D15" s="168" t="s">
         <v>42</v>
       </c>
-      <c r="E15" s="128"/>
-      <c r="F15" s="128"/>
-      <c r="G15" s="59"/>
-      <c r="H15" s="56"/>
-      <c r="I15" s="58"/>
+      <c r="E15" s="173"/>
+      <c r="F15" s="173"/>
+      <c r="G15" s="58"/>
+      <c r="H15" s="55"/>
+      <c r="I15" s="57"/>
       <c r="J15" s="54" t="s">
         <v>21</v>
       </c>
       <c r="K15" s="54"/>
     </row>
-    <row r="16" spans="1:12" s="80" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A16" s="129" t="s">
+    <row r="16" spans="1:12" s="72" customFormat="1" ht="12.75" outlineLevel="1">
+      <c r="A16" s="174" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="130"/>
-      <c r="C16" s="130"/>
+      <c r="B16" s="175"/>
+      <c r="C16" s="175"/>
       <c r="D16" s="50"/>
       <c r="E16" s="50"/>
       <c r="F16" s="50"/>
@@ -3488,24 +4236,24 @@
       <c r="J16" s="50"/>
       <c r="K16" s="51"/>
     </row>
-    <row r="17" spans="1:11" s="80" customFormat="1" ht="63.75" customHeight="1" outlineLevel="1">
+    <row r="17" spans="1:11" s="72" customFormat="1" ht="63.75" customHeight="1" outlineLevel="1">
       <c r="A17" s="52" t="s">
         <v>44</v>
       </c>
-      <c r="B17" s="85" t="s">
+      <c r="B17" s="77" t="s">
         <v>40</v>
       </c>
       <c r="C17" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="D17" s="105" t="s">
+      <c r="D17" s="168" t="s">
         <v>46</v>
       </c>
-      <c r="E17" s="106"/>
-      <c r="F17" s="106"/>
-      <c r="G17" s="59"/>
-      <c r="H17" s="56"/>
-      <c r="I17" s="58"/>
+      <c r="E17" s="169"/>
+      <c r="F17" s="169"/>
+      <c r="G17" s="58"/>
+      <c r="H17" s="55"/>
+      <c r="I17" s="57"/>
       <c r="J17" s="54" t="s">
         <v>21</v>
       </c>
@@ -3569,37 +4317,37 @@
     <mergeCell ref="H9:H10"/>
     <mergeCell ref="I9:I10"/>
     <mergeCell ref="J9:J10"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="I5:K5"/>
     <mergeCell ref="B1:D2"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="I3:K3"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="I4:K4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="I5:K5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K36"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="22.5546875" customWidth="1"/>
+    <col min="1" max="1" width="22.5" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="32.44140625" customWidth="1"/>
+    <col min="3" max="3" width="32.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="13.8">
+    <row r="1" spans="1:11" ht="14.25">
       <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="69" t="s">
+      <c r="B1" s="61" t="s">
         <v>47</v>
       </c>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
       <c r="E1" s="31"/>
       <c r="F1" s="31"/>
       <c r="G1" s="31"/>
@@ -3608,11 +4356,11 @@
       <c r="J1" s="32"/>
       <c r="K1" s="31"/>
     </row>
-    <row r="2" spans="1:11" ht="13.8">
+    <row r="2" spans="1:11" ht="14.25">
       <c r="A2" s="33"/>
-      <c r="B2" s="70"/>
-      <c r="C2" s="70"/>
-      <c r="D2" s="70"/>
+      <c r="B2" s="62"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
       <c r="E2" s="31"/>
       <c r="F2" s="31"/>
       <c r="G2" s="31"/>
@@ -3621,58 +4369,58 @@
       <c r="J2" s="32"/>
       <c r="K2" s="31"/>
     </row>
-    <row r="3" spans="1:11" ht="13.8">
-      <c r="A3" s="71" t="s">
+    <row r="3" spans="1:11" ht="14.25">
+      <c r="A3" s="63" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="131" t="s">
+      <c r="B3" s="159" t="s">
         <v>48</v>
       </c>
-      <c r="C3" s="131"/>
-      <c r="D3" s="132"/>
+      <c r="C3" s="159"/>
+      <c r="D3" s="160"/>
       <c r="E3" s="35"/>
       <c r="F3" s="35"/>
       <c r="G3" s="35"/>
       <c r="H3" s="35"/>
-      <c r="I3" s="97"/>
-      <c r="J3" s="97"/>
-      <c r="K3" s="97"/>
-    </row>
-    <row r="4" spans="1:11" ht="13.8">
+      <c r="I3" s="146"/>
+      <c r="J3" s="146"/>
+      <c r="K3" s="146"/>
+    </row>
+    <row r="4" spans="1:11" ht="14.25">
       <c r="A4" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="98" t="s">
+      <c r="B4" s="161" t="s">
         <v>49</v>
       </c>
-      <c r="C4" s="99"/>
-      <c r="D4" s="100"/>
+      <c r="C4" s="162"/>
+      <c r="D4" s="163"/>
       <c r="E4" s="35"/>
       <c r="F4" s="35"/>
       <c r="G4" s="35"/>
       <c r="H4" s="35"/>
-      <c r="I4" s="97"/>
-      <c r="J4" s="97"/>
-      <c r="K4" s="97"/>
+      <c r="I4" s="146"/>
+      <c r="J4" s="146"/>
+      <c r="K4" s="146"/>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="101" t="s">
+      <c r="B5" s="164" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="102"/>
-      <c r="D5" s="103"/>
+      <c r="C5" s="165"/>
+      <c r="D5" s="166"/>
       <c r="E5" s="39"/>
       <c r="F5" s="39"/>
       <c r="G5" s="39"/>
       <c r="H5" s="39"/>
-      <c r="I5" s="104"/>
-      <c r="J5" s="104"/>
-      <c r="K5" s="104"/>
-    </row>
-    <row r="6" spans="1:11" ht="13.8">
+      <c r="I5" s="167"/>
+      <c r="J5" s="167"/>
+      <c r="K5" s="167"/>
+    </row>
+    <row r="6" spans="1:11" ht="14.25">
       <c r="A6" s="40" t="s">
         <v>21</v>
       </c>
@@ -3689,11 +4437,11 @@
       <c r="F6" s="36"/>
       <c r="G6" s="36"/>
       <c r="H6" s="36"/>
-      <c r="I6" s="97"/>
-      <c r="J6" s="97"/>
-      <c r="K6" s="97"/>
-    </row>
-    <row r="7" spans="1:11" ht="13.8">
+      <c r="I6" s="146"/>
+      <c r="J6" s="146"/>
+      <c r="K6" s="146"/>
+    </row>
+    <row r="7" spans="1:11" ht="14.25">
       <c r="A7" s="44" t="s">
         <v>23</v>
       </c>
@@ -3710,15 +4458,15 @@
       <c r="F7" s="48"/>
       <c r="G7" s="48"/>
       <c r="H7" s="48"/>
-      <c r="I7" s="97"/>
-      <c r="J7" s="97"/>
-      <c r="K7" s="97"/>
-    </row>
-    <row r="8" spans="1:11" ht="13.8">
-      <c r="A8" s="107"/>
-      <c r="B8" s="107"/>
-      <c r="C8" s="107"/>
-      <c r="D8" s="107"/>
+      <c r="I7" s="146"/>
+      <c r="J7" s="146"/>
+      <c r="K7" s="146"/>
+    </row>
+    <row r="8" spans="1:11" ht="14.25">
+      <c r="A8" s="147"/>
+      <c r="B8" s="147"/>
+      <c r="C8" s="147"/>
+      <c r="D8" s="147"/>
       <c r="E8" s="36"/>
       <c r="F8" s="36"/>
       <c r="G8" s="36"/>
@@ -3728,76 +4476,76 @@
       <c r="K8" s="49"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="113" t="s">
+      <c r="A9" s="138" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="115" t="s">
+      <c r="B9" s="149" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="113" t="s">
+      <c r="C9" s="138" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="119" t="s">
+      <c r="D9" s="151" t="s">
         <v>28</v>
       </c>
-      <c r="E9" s="120"/>
-      <c r="F9" s="120"/>
-      <c r="G9" s="121"/>
-      <c r="H9" s="117" t="s">
+      <c r="E9" s="152"/>
+      <c r="F9" s="152"/>
+      <c r="G9" s="153"/>
+      <c r="H9" s="157" t="s">
         <v>29</v>
       </c>
-      <c r="I9" s="118" t="s">
+      <c r="I9" s="137" t="s">
         <v>30</v>
       </c>
-      <c r="J9" s="118" t="s">
+      <c r="J9" s="137" t="s">
         <v>31</v>
       </c>
-      <c r="K9" s="118" t="s">
+      <c r="K9" s="137" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="114"/>
-      <c r="B10" s="116"/>
-      <c r="C10" s="114"/>
-      <c r="D10" s="122"/>
-      <c r="E10" s="123"/>
-      <c r="F10" s="123"/>
-      <c r="G10" s="124"/>
-      <c r="H10" s="113"/>
-      <c r="I10" s="113"/>
-      <c r="J10" s="113"/>
-      <c r="K10" s="113"/>
+      <c r="A10" s="148"/>
+      <c r="B10" s="150"/>
+      <c r="C10" s="148"/>
+      <c r="D10" s="154"/>
+      <c r="E10" s="155"/>
+      <c r="F10" s="155"/>
+      <c r="G10" s="156"/>
+      <c r="H10" s="138"/>
+      <c r="I10" s="138"/>
+      <c r="J10" s="138"/>
+      <c r="K10" s="138"/>
     </row>
     <row r="11" spans="1:11" ht="15">
-      <c r="A11" s="108"/>
-      <c r="B11" s="108"/>
-      <c r="C11" s="108"/>
-      <c r="D11" s="108"/>
-      <c r="E11" s="108"/>
-      <c r="F11" s="108"/>
-      <c r="G11" s="108"/>
-      <c r="H11" s="108"/>
-      <c r="I11" s="108"/>
-      <c r="J11" s="108"/>
-      <c r="K11" s="109"/>
+      <c r="A11" s="139"/>
+      <c r="B11" s="139"/>
+      <c r="C11" s="139"/>
+      <c r="D11" s="139"/>
+      <c r="E11" s="139"/>
+      <c r="F11" s="139"/>
+      <c r="G11" s="139"/>
+      <c r="H11" s="139"/>
+      <c r="I11" s="139"/>
+      <c r="J11" s="139"/>
+      <c r="K11" s="140"/>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="110" t="s">
+      <c r="A12" s="141" t="s">
         <v>50</v>
       </c>
-      <c r="B12" s="111"/>
-      <c r="C12" s="111"/>
-      <c r="D12" s="111"/>
-      <c r="E12" s="111"/>
-      <c r="F12" s="111"/>
-      <c r="G12" s="111"/>
-      <c r="H12" s="111"/>
-      <c r="I12" s="111"/>
-      <c r="J12" s="111"/>
-      <c r="K12" s="112"/>
-    </row>
-    <row r="13" spans="1:11" ht="105.6">
+      <c r="B12" s="142"/>
+      <c r="C12" s="142"/>
+      <c r="D12" s="142"/>
+      <c r="E12" s="142"/>
+      <c r="F12" s="142"/>
+      <c r="G12" s="142"/>
+      <c r="H12" s="142"/>
+      <c r="I12" s="142"/>
+      <c r="J12" s="142"/>
+      <c r="K12" s="143"/>
+    </row>
+    <row r="13" spans="1:11" ht="63.75">
       <c r="A13" s="52" t="s">
         <v>34</v>
       </c>
@@ -3807,63 +4555,63 @@
       <c r="C13" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="D13" s="134" t="s">
+      <c r="D13" s="177" t="s">
         <v>53</v>
       </c>
-      <c r="E13" s="128"/>
-      <c r="F13" s="128"/>
-      <c r="G13" s="133"/>
-      <c r="H13" s="56"/>
-      <c r="I13" s="57"/>
+      <c r="E13" s="173"/>
+      <c r="F13" s="173"/>
+      <c r="G13" s="176"/>
+      <c r="H13" s="55"/>
+      <c r="I13" s="56"/>
       <c r="J13" s="54" t="s">
         <v>22</v>
       </c>
       <c r="K13" s="54"/>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="110" t="s">
+      <c r="A14" s="141" t="s">
         <v>54</v>
       </c>
-      <c r="B14" s="111"/>
-      <c r="C14" s="111"/>
-      <c r="D14" s="111"/>
-      <c r="E14" s="111"/>
-      <c r="F14" s="111"/>
-      <c r="G14" s="111"/>
-      <c r="H14" s="111"/>
-      <c r="I14" s="111"/>
-      <c r="J14" s="111"/>
-      <c r="K14" s="112"/>
-    </row>
-    <row r="15" spans="1:11" ht="92.4">
-      <c r="A15" s="72" t="s">
+      <c r="B14" s="142"/>
+      <c r="C14" s="142"/>
+      <c r="D14" s="142"/>
+      <c r="E14" s="142"/>
+      <c r="F14" s="142"/>
+      <c r="G14" s="142"/>
+      <c r="H14" s="142"/>
+      <c r="I14" s="142"/>
+      <c r="J14" s="142"/>
+      <c r="K14" s="143"/>
+    </row>
+    <row r="15" spans="1:11" ht="63.75">
+      <c r="A15" s="64" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="72" t="s">
+      <c r="B15" s="64" t="s">
         <v>55</v>
       </c>
-      <c r="C15" s="72" t="s">
+      <c r="C15" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="D15" s="135" t="s">
+      <c r="D15" s="178" t="s">
         <v>57</v>
       </c>
-      <c r="E15" s="136"/>
-      <c r="F15" s="136"/>
-      <c r="G15" s="137"/>
-      <c r="H15" s="73"/>
-      <c r="I15" s="73"/>
-      <c r="J15" s="74" t="s">
+      <c r="E15" s="179"/>
+      <c r="F15" s="179"/>
+      <c r="G15" s="180"/>
+      <c r="H15" s="65"/>
+      <c r="I15" s="65"/>
+      <c r="J15" s="66" t="s">
         <v>22</v>
       </c>
-      <c r="K15" s="73"/>
+      <c r="K15" s="65"/>
     </row>
     <row r="16" spans="1:11">
-      <c r="A16" s="110" t="s">
+      <c r="A16" s="141" t="s">
         <v>58</v>
       </c>
-      <c r="B16" s="111"/>
-      <c r="C16" s="111"/>
+      <c r="B16" s="142"/>
+      <c r="C16" s="142"/>
       <c r="D16" s="50"/>
       <c r="E16" s="50"/>
       <c r="F16" s="50"/>
@@ -3873,35 +4621,35 @@
       <c r="J16" s="50"/>
       <c r="K16" s="51"/>
     </row>
-    <row r="17" spans="1:11" ht="26.4">
+    <row r="17" spans="1:11">
       <c r="A17" s="52" t="s">
         <v>44</v>
       </c>
-      <c r="B17" s="63" t="s">
+      <c r="B17" s="59" t="s">
         <v>59</v>
       </c>
-      <c r="C17" s="63" t="s">
+      <c r="C17" s="59" t="s">
         <v>60</v>
       </c>
-      <c r="D17" s="134" t="s">
+      <c r="D17" s="177" t="s">
         <v>61</v>
       </c>
-      <c r="E17" s="138"/>
-      <c r="F17" s="138"/>
-      <c r="G17" s="139"/>
-      <c r="H17" s="56"/>
-      <c r="I17" s="58"/>
+      <c r="E17" s="181"/>
+      <c r="F17" s="181"/>
+      <c r="G17" s="182"/>
+      <c r="H17" s="55"/>
+      <c r="I17" s="57"/>
       <c r="J17" s="54" t="s">
         <v>22</v>
       </c>
       <c r="K17" s="54"/>
     </row>
     <row r="18" spans="1:11">
-      <c r="A18" s="110" t="s">
+      <c r="A18" s="141" t="s">
         <v>62</v>
       </c>
-      <c r="B18" s="111"/>
-      <c r="C18" s="111"/>
+      <c r="B18" s="142"/>
+      <c r="C18" s="142"/>
       <c r="D18" s="50"/>
       <c r="E18" s="50"/>
       <c r="F18" s="50"/>
@@ -3911,7 +4659,7 @@
       <c r="J18" s="50"/>
       <c r="K18" s="51"/>
     </row>
-    <row r="19" spans="1:11" ht="39.6">
+    <row r="19" spans="1:11" ht="38.25">
       <c r="A19" s="52" t="s">
         <v>63</v>
       </c>
@@ -3921,25 +4669,25 @@
       <c r="C19" s="54" t="s">
         <v>65</v>
       </c>
-      <c r="D19" s="127" t="s">
+      <c r="D19" s="172" t="s">
         <v>66</v>
       </c>
-      <c r="E19" s="128"/>
-      <c r="F19" s="128"/>
-      <c r="G19" s="133"/>
-      <c r="H19" s="56"/>
-      <c r="I19" s="58"/>
+      <c r="E19" s="173"/>
+      <c r="F19" s="173"/>
+      <c r="G19" s="176"/>
+      <c r="H19" s="55"/>
+      <c r="I19" s="57"/>
       <c r="J19" s="54" t="s">
         <v>22</v>
       </c>
       <c r="K19" s="54"/>
     </row>
     <row r="20" spans="1:11">
-      <c r="A20" s="110" t="s">
+      <c r="A20" s="141" t="s">
         <v>67</v>
       </c>
-      <c r="B20" s="111"/>
-      <c r="C20" s="111"/>
+      <c r="B20" s="142"/>
+      <c r="C20" s="142"/>
       <c r="D20" s="50"/>
       <c r="E20" s="50"/>
       <c r="F20" s="50"/>
@@ -3949,7 +4697,7 @@
       <c r="J20" s="50"/>
       <c r="K20" s="51"/>
     </row>
-    <row r="21" spans="1:11" ht="66">
+    <row r="21" spans="1:11" ht="63.75">
       <c r="A21" s="52" t="s">
         <v>68</v>
       </c>
@@ -3959,98 +4707,98 @@
       <c r="C21" s="54" t="s">
         <v>70</v>
       </c>
-      <c r="D21" s="127" t="s">
+      <c r="D21" s="172" t="s">
         <v>71</v>
       </c>
-      <c r="E21" s="128"/>
-      <c r="F21" s="128"/>
-      <c r="G21" s="133"/>
-      <c r="H21" s="56"/>
-      <c r="I21" s="58"/>
+      <c r="E21" s="173"/>
+      <c r="F21" s="173"/>
+      <c r="G21" s="176"/>
+      <c r="H21" s="55"/>
+      <c r="I21" s="57"/>
       <c r="J21" s="54" t="s">
         <v>22</v>
       </c>
       <c r="K21" s="54"/>
     </row>
     <row r="22" spans="1:11">
-      <c r="A22" s="64" t="s">
-        <v>121</v>
+      <c r="A22" s="60" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="23" spans="1:11">
-      <c r="A23" s="64" t="s">
-        <v>122</v>
+      <c r="A23" s="60" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="24" spans="1:11">
-      <c r="A24" s="64" t="s">
-        <v>123</v>
+      <c r="A24" s="60" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="25" spans="1:11">
-      <c r="A25" s="64" t="s">
+      <c r="A25" s="60" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="25.5">
+      <c r="A26" s="60" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="25.5">
+      <c r="A27" s="60" t="s">
+        <v>110</v>
+      </c>
+      <c r="C27" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="26.4">
-      <c r="A26" s="64" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" ht="39.6">
-      <c r="A27" s="64" t="s">
-        <v>126</v>
-      </c>
-      <c r="C27" t="s">
-        <v>154</v>
-      </c>
-    </row>
     <row r="28" spans="1:11">
-      <c r="A28" s="64" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" ht="26.4">
-      <c r="A29" s="64" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" ht="26.4">
-      <c r="A30" s="64" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" ht="39.6">
-      <c r="A31" s="64" t="s">
-        <v>130</v>
+      <c r="A28" s="60" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="25.5">
+      <c r="A29" s="60" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="25.5">
+      <c r="A30" s="60" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="38.25">
+      <c r="A31" s="60" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="32" spans="1:11">
-      <c r="A32" s="89" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" ht="66">
-      <c r="A33" s="89" t="s">
-        <v>132</v>
+      <c r="A32" s="81" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="63.75">
+      <c r="A33" s="81" t="s">
+        <v>116</v>
       </c>
       <c r="B33" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" ht="26.4">
-      <c r="A34" s="89" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" ht="26.4">
-      <c r="A35" s="89" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" ht="26.4">
-      <c r="A36" s="89" t="s">
-        <v>135</v>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="25.5">
+      <c r="A34" s="81" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="25.5">
+      <c r="A35" s="81" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="25.5">
+      <c r="A36" s="81" t="s">
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -4088,25 +4836,27 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:K39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.2"/>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K40"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="18.21875" customWidth="1"/>
-    <col min="2" max="2" width="26.6640625" customWidth="1"/>
-    <col min="3" max="3" width="33.44140625" customWidth="1"/>
-    <col min="6" max="6" width="17.6640625" customWidth="1"/>
-    <col min="7" max="7" width="0.88671875" customWidth="1"/>
+    <col min="1" max="1" width="18.25" customWidth="1"/>
+    <col min="2" max="2" width="26.625" customWidth="1"/>
+    <col min="3" max="3" width="35.5" customWidth="1"/>
+    <col min="6" max="6" width="17.625" customWidth="1"/>
+    <col min="7" max="7" width="0.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="13.8">
+    <row r="1" spans="1:11" ht="14.25">
       <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="125"/>
-      <c r="C1" s="125"/>
-      <c r="D1" s="125"/>
+      <c r="B1" s="131" t="s">
+        <v>198</v>
+      </c>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
       <c r="E1" s="31"/>
       <c r="F1" s="31"/>
       <c r="G1" s="31"/>
@@ -4115,11 +4865,11 @@
       <c r="J1" s="32"/>
       <c r="K1" s="31"/>
     </row>
-    <row r="2" spans="1:11" ht="13.8">
+    <row r="2" spans="1:11" ht="14.25">
       <c r="A2" s="33"/>
-      <c r="B2" s="126"/>
-      <c r="C2" s="126"/>
-      <c r="D2" s="126"/>
+      <c r="B2" s="130"/>
+      <c r="C2" s="130"/>
+      <c r="D2" s="130"/>
       <c r="E2" s="31"/>
       <c r="F2" s="31"/>
       <c r="G2" s="31"/>
@@ -4128,58 +4878,58 @@
       <c r="J2" s="32"/>
       <c r="K2" s="31"/>
     </row>
-    <row r="3" spans="1:11" ht="13.8">
+    <row r="3" spans="1:11" ht="14.25">
       <c r="A3" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="131" t="s">
-        <v>72</v>
-      </c>
-      <c r="C3" s="131"/>
-      <c r="D3" s="132"/>
+      <c r="B3" s="158" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="159"/>
+      <c r="D3" s="160"/>
       <c r="E3" s="35"/>
       <c r="F3" s="35"/>
       <c r="G3" s="35"/>
       <c r="H3" s="35"/>
-      <c r="I3" s="97"/>
-      <c r="J3" s="97"/>
-      <c r="K3" s="97"/>
-    </row>
-    <row r="4" spans="1:11" ht="13.8">
+      <c r="I3" s="146"/>
+      <c r="J3" s="146"/>
+      <c r="K3" s="146"/>
+    </row>
+    <row r="4" spans="1:11" ht="14.25">
       <c r="A4" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="98" t="s">
-        <v>73</v>
-      </c>
-      <c r="C4" s="99"/>
-      <c r="D4" s="100"/>
+      <c r="B4" s="161" t="s">
+        <v>72</v>
+      </c>
+      <c r="C4" s="162"/>
+      <c r="D4" s="163"/>
       <c r="E4" s="35"/>
       <c r="F4" s="35"/>
       <c r="G4" s="35"/>
       <c r="H4" s="35"/>
-      <c r="I4" s="97"/>
-      <c r="J4" s="97"/>
-      <c r="K4" s="97"/>
-    </row>
-    <row r="5" spans="1:11" ht="26.4">
+      <c r="I4" s="146"/>
+      <c r="J4" s="146"/>
+      <c r="K4" s="146"/>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="101" t="s">
+      <c r="B5" s="164" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="102"/>
-      <c r="D5" s="103"/>
+      <c r="C5" s="165"/>
+      <c r="D5" s="166"/>
       <c r="E5" s="39"/>
       <c r="F5" s="39"/>
       <c r="G5" s="39"/>
       <c r="H5" s="39"/>
-      <c r="I5" s="104"/>
-      <c r="J5" s="104"/>
-      <c r="K5" s="104"/>
-    </row>
-    <row r="6" spans="1:11" ht="13.8">
+      <c r="I5" s="167"/>
+      <c r="J5" s="167"/>
+      <c r="K5" s="167"/>
+    </row>
+    <row r="6" spans="1:11" ht="14.25">
       <c r="A6" s="40" t="s">
         <v>21</v>
       </c>
@@ -4192,17 +4942,17 @@
       </c>
       <c r="D6" s="43">
         <f>COUNTIF(J10:J741,"Pending")</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E6" s="36"/>
       <c r="F6" s="36"/>
       <c r="G6" s="36"/>
       <c r="H6" s="36"/>
-      <c r="I6" s="97"/>
-      <c r="J6" s="97"/>
-      <c r="K6" s="97"/>
-    </row>
-    <row r="7" spans="1:11" ht="13.8">
+      <c r="I6" s="146"/>
+      <c r="J6" s="146"/>
+      <c r="K6" s="146"/>
+    </row>
+    <row r="7" spans="1:11" ht="14.25">
       <c r="A7" s="44" t="s">
         <v>23</v>
       </c>
@@ -4214,22 +4964,22 @@
         <v>24</v>
       </c>
       <c r="D7" s="47">
-        <f>COUNTA(A12:A24)-3</f>
-        <v>10</v>
+        <f>COUNTA(A12:A27)-4</f>
+        <v>12</v>
       </c>
       <c r="E7" s="48"/>
       <c r="F7" s="48"/>
       <c r="G7" s="48"/>
       <c r="H7" s="48"/>
-      <c r="I7" s="97"/>
-      <c r="J7" s="97"/>
-      <c r="K7" s="97"/>
-    </row>
-    <row r="8" spans="1:11" ht="13.8">
-      <c r="A8" s="107"/>
-      <c r="B8" s="107"/>
-      <c r="C8" s="107"/>
-      <c r="D8" s="107"/>
+      <c r="I7" s="146"/>
+      <c r="J7" s="146"/>
+      <c r="K7" s="146"/>
+    </row>
+    <row r="8" spans="1:11" ht="14.25">
+      <c r="A8" s="147"/>
+      <c r="B8" s="147"/>
+      <c r="C8" s="147"/>
+      <c r="D8" s="147"/>
       <c r="E8" s="36"/>
       <c r="F8" s="36"/>
       <c r="G8" s="36"/>
@@ -4238,422 +4988,457 @@
       <c r="J8" s="49"/>
       <c r="K8" s="49"/>
     </row>
-    <row r="9" spans="1:11">
-      <c r="A9" s="113" t="s">
+    <row r="9" spans="1:11" ht="13.5" customHeight="1">
+      <c r="A9" s="194" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="115" t="s">
+      <c r="B9" s="198" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="113" t="s">
+      <c r="C9" s="194" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="119" t="s">
+      <c r="D9" s="200" t="s">
         <v>28</v>
       </c>
-      <c r="E9" s="120"/>
-      <c r="F9" s="120"/>
-      <c r="G9" s="121"/>
-      <c r="H9" s="117" t="s">
+      <c r="E9" s="201"/>
+      <c r="F9" s="201"/>
+      <c r="G9" s="202"/>
+      <c r="H9" s="193" t="s">
         <v>29</v>
       </c>
-      <c r="I9" s="118" t="s">
+      <c r="I9" s="195" t="s">
         <v>30</v>
       </c>
-      <c r="J9" s="118" t="s">
+      <c r="J9" s="195" t="s">
         <v>31</v>
       </c>
-      <c r="K9" s="118" t="s">
+      <c r="K9" s="195" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="114"/>
-      <c r="B10" s="116"/>
-      <c r="C10" s="114"/>
-      <c r="D10" s="122"/>
-      <c r="E10" s="123"/>
-      <c r="F10" s="123"/>
-      <c r="G10" s="124"/>
-      <c r="H10" s="113"/>
-      <c r="I10" s="113"/>
-      <c r="J10" s="113"/>
-      <c r="K10" s="113"/>
+      <c r="A10" s="197"/>
+      <c r="B10" s="199"/>
+      <c r="C10" s="197"/>
+      <c r="D10" s="203"/>
+      <c r="E10" s="204"/>
+      <c r="F10" s="204"/>
+      <c r="G10" s="205"/>
+      <c r="H10" s="194"/>
+      <c r="I10" s="194"/>
+      <c r="J10" s="194"/>
+      <c r="K10" s="194"/>
     </row>
     <row r="11" spans="1:11" ht="15">
-      <c r="A11" s="108"/>
-      <c r="B11" s="108"/>
-      <c r="C11" s="108"/>
-      <c r="D11" s="108"/>
-      <c r="E11" s="108"/>
-      <c r="F11" s="108"/>
-      <c r="G11" s="108"/>
-      <c r="H11" s="108"/>
-      <c r="I11" s="108"/>
-      <c r="J11" s="108"/>
-      <c r="K11" s="109"/>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12" s="110" t="s">
+      <c r="A11" s="190"/>
+      <c r="B11" s="190"/>
+      <c r="C11" s="190"/>
+      <c r="D11" s="190"/>
+      <c r="E11" s="190"/>
+      <c r="F11" s="190"/>
+      <c r="G11" s="190"/>
+      <c r="H11" s="190"/>
+      <c r="I11" s="190"/>
+      <c r="J11" s="190"/>
+      <c r="K11" s="191"/>
+    </row>
+    <row r="12" spans="1:11" ht="16.5" customHeight="1">
+      <c r="A12" s="185" t="s">
+        <v>73</v>
+      </c>
+      <c r="B12" s="186"/>
+      <c r="C12" s="186"/>
+      <c r="D12" s="186"/>
+      <c r="E12" s="186"/>
+      <c r="F12" s="186"/>
+      <c r="G12" s="186"/>
+      <c r="H12" s="186"/>
+      <c r="I12" s="186"/>
+      <c r="J12" s="186"/>
+      <c r="K12" s="192"/>
+    </row>
+    <row r="13" spans="1:11" ht="54" customHeight="1">
+      <c r="A13" s="104" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="105" t="s">
         <v>74</v>
       </c>
-      <c r="B12" s="111"/>
-      <c r="C12" s="111"/>
-      <c r="D12" s="111"/>
-      <c r="E12" s="111"/>
-      <c r="F12" s="111"/>
-      <c r="G12" s="111"/>
-      <c r="H12" s="111"/>
-      <c r="I12" s="111"/>
-      <c r="J12" s="111"/>
-      <c r="K12" s="112"/>
-    </row>
-    <row r="13" spans="1:11" ht="55.5" customHeight="1">
-      <c r="A13" s="52" t="s">
+      <c r="C13" s="106" t="s">
         <v>75</v>
       </c>
-      <c r="B13" s="53" t="s">
+      <c r="D13" s="188" t="s">
         <v>76</v>
       </c>
-      <c r="C13" s="54" t="s">
+      <c r="E13" s="189"/>
+      <c r="F13" s="189"/>
+      <c r="G13" s="107"/>
+      <c r="H13" s="108"/>
+      <c r="I13" s="109"/>
+      <c r="J13" s="106" t="s">
+        <v>22</v>
+      </c>
+      <c r="K13" s="106"/>
+    </row>
+    <row r="14" spans="1:11" ht="54.75" customHeight="1">
+      <c r="A14" s="104" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="105" t="s">
+        <v>147</v>
+      </c>
+      <c r="C14" s="106" t="s">
+        <v>148</v>
+      </c>
+      <c r="D14" s="184" t="s">
+        <v>149</v>
+      </c>
+      <c r="E14" s="187"/>
+      <c r="F14" s="187"/>
+      <c r="G14" s="107"/>
+      <c r="H14" s="108"/>
+      <c r="I14" s="109"/>
+      <c r="J14" s="106" t="s">
+        <v>22</v>
+      </c>
+      <c r="K14" s="106"/>
+    </row>
+    <row r="15" spans="1:11" ht="58.5" customHeight="1">
+      <c r="A15" s="104" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" s="105" t="s">
         <v>77</v>
       </c>
-      <c r="D13" s="140" t="s">
+      <c r="C15" s="110" t="s">
         <v>78</v>
       </c>
-      <c r="E13" s="141"/>
-      <c r="F13" s="141"/>
-      <c r="G13" s="55"/>
-      <c r="H13" s="56"/>
-      <c r="I13" s="57"/>
-      <c r="J13" s="54" t="s">
+      <c r="D15" s="184" t="s">
+        <v>79</v>
+      </c>
+      <c r="E15" s="187"/>
+      <c r="F15" s="187"/>
+      <c r="G15" s="111"/>
+      <c r="H15" s="111"/>
+      <c r="I15" s="112"/>
+      <c r="J15" s="106" t="s">
         <v>22</v>
       </c>
-      <c r="K13" s="54"/>
-    </row>
-    <row r="14" spans="1:11" ht="54" customHeight="1">
-      <c r="A14" s="52" t="s">
-        <v>79</v>
-      </c>
-      <c r="B14" s="53" t="s">
+      <c r="K15" s="106"/>
+    </row>
+    <row r="16" spans="1:11" ht="18" customHeight="1">
+      <c r="A16" s="185" t="s">
         <v>80</v>
       </c>
-      <c r="C14" s="58" t="s">
+      <c r="B16" s="186"/>
+      <c r="C16" s="186"/>
+      <c r="D16" s="113"/>
+      <c r="E16" s="113"/>
+      <c r="F16" s="113"/>
+      <c r="G16" s="113"/>
+      <c r="H16" s="114"/>
+      <c r="I16" s="114"/>
+      <c r="J16" s="114"/>
+      <c r="K16" s="115"/>
+    </row>
+    <row r="17" spans="1:11" ht="78" customHeight="1">
+      <c r="A17" s="104" t="s">
+        <v>63</v>
+      </c>
+      <c r="B17" s="116" t="s">
+        <v>150</v>
+      </c>
+      <c r="C17" s="117" t="s">
+        <v>82</v>
+      </c>
+      <c r="D17" s="188" t="s">
         <v>81</v>
       </c>
-      <c r="D14" s="127" t="s">
-        <v>82</v>
-      </c>
-      <c r="E14" s="128"/>
-      <c r="F14" s="128"/>
-      <c r="G14" s="59"/>
-      <c r="H14" s="59"/>
-      <c r="I14" s="60"/>
-      <c r="J14" s="54" t="s">
+      <c r="E17" s="189"/>
+      <c r="F17" s="189"/>
+      <c r="G17" s="107"/>
+      <c r="H17" s="108"/>
+      <c r="I17" s="110"/>
+      <c r="J17" s="106" t="s">
         <v>22</v>
       </c>
-      <c r="K14" s="54"/>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="A15" s="110" t="s">
+      <c r="K17" s="106"/>
+    </row>
+    <row r="18" spans="1:11" ht="79.5" customHeight="1">
+      <c r="A18" s="104" t="s">
+        <v>68</v>
+      </c>
+      <c r="B18" s="118" t="s">
+        <v>151</v>
+      </c>
+      <c r="C18" s="110" t="s">
         <v>83</v>
       </c>
-      <c r="B15" s="111"/>
-      <c r="C15" s="111"/>
-      <c r="D15" s="61"/>
-      <c r="E15" s="61"/>
-      <c r="F15" s="61"/>
-      <c r="G15" s="61"/>
-      <c r="H15" s="50"/>
-      <c r="I15" s="50"/>
-      <c r="J15" s="50"/>
-      <c r="K15" s="51"/>
-    </row>
-    <row r="16" spans="1:11" ht="77.25" customHeight="1">
-      <c r="A16" s="52" t="s">
+      <c r="D18" s="184" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="93" t="s">
-        <v>150</v>
-      </c>
-      <c r="C16" s="58" t="s">
+      <c r="E18" s="187"/>
+      <c r="F18" s="187"/>
+      <c r="G18" s="111"/>
+      <c r="H18" s="111"/>
+      <c r="I18" s="106"/>
+      <c r="J18" s="106" t="s">
+        <v>22</v>
+      </c>
+      <c r="K18" s="106"/>
+    </row>
+    <row r="19" spans="1:11" ht="78.75" customHeight="1">
+      <c r="A19" s="104" t="s">
+        <v>152</v>
+      </c>
+      <c r="B19" s="118" t="s">
+        <v>153</v>
+      </c>
+      <c r="C19" s="110" t="s">
         <v>85</v>
       </c>
-      <c r="D16" s="127" t="s">
+      <c r="D19" s="184" t="s">
+        <v>84</v>
+      </c>
+      <c r="E19" s="187"/>
+      <c r="F19" s="187"/>
+      <c r="G19" s="111"/>
+      <c r="H19" s="111"/>
+      <c r="I19" s="106"/>
+      <c r="J19" s="106" t="s">
+        <v>22</v>
+      </c>
+      <c r="K19" s="106"/>
+    </row>
+    <row r="20" spans="1:11" ht="19.5" customHeight="1">
+      <c r="A20" s="185" t="s">
         <v>86</v>
       </c>
-      <c r="E16" s="128"/>
-      <c r="F16" s="128"/>
-      <c r="G16" s="62"/>
-      <c r="H16" s="59"/>
-      <c r="I16" s="54"/>
-      <c r="J16" s="54" t="s">
+      <c r="B20" s="186"/>
+      <c r="C20" s="186"/>
+      <c r="D20" s="113"/>
+      <c r="E20" s="113"/>
+      <c r="F20" s="113"/>
+      <c r="G20" s="113"/>
+      <c r="H20" s="114"/>
+      <c r="I20" s="114"/>
+      <c r="J20" s="114"/>
+      <c r="K20" s="115"/>
+    </row>
+    <row r="21" spans="1:11" ht="66" customHeight="1">
+      <c r="A21" s="104" t="s">
+        <v>154</v>
+      </c>
+      <c r="B21" s="117" t="s">
+        <v>87</v>
+      </c>
+      <c r="C21" s="117" t="s">
+        <v>88</v>
+      </c>
+      <c r="D21" s="184" t="s">
+        <v>89</v>
+      </c>
+      <c r="E21" s="187"/>
+      <c r="F21" s="187"/>
+      <c r="G21" s="111"/>
+      <c r="H21" s="108"/>
+      <c r="I21" s="110"/>
+      <c r="J21" s="106" t="s">
         <v>22</v>
       </c>
-      <c r="K16" s="54"/>
-    </row>
-    <row r="17" spans="1:11" ht="78" customHeight="1">
-      <c r="A17" s="52" t="s">
-        <v>87</v>
-      </c>
-      <c r="B17" s="94" t="s">
-        <v>88</v>
-      </c>
-      <c r="C17" s="63" t="s">
-        <v>89</v>
-      </c>
-      <c r="D17" s="140" t="s">
-        <v>86</v>
-      </c>
-      <c r="E17" s="141"/>
-      <c r="F17" s="141"/>
-      <c r="G17" s="55"/>
-      <c r="H17" s="56"/>
-      <c r="I17" s="58"/>
-      <c r="J17" s="54" t="s">
+      <c r="K21" s="106"/>
+    </row>
+    <row r="22" spans="1:11" ht="66.75" customHeight="1">
+      <c r="A22" s="104" t="s">
+        <v>155</v>
+      </c>
+      <c r="B22" s="106" t="s">
+        <v>90</v>
+      </c>
+      <c r="C22" s="106" t="s">
+        <v>91</v>
+      </c>
+      <c r="D22" s="184" t="s">
+        <v>92</v>
+      </c>
+      <c r="E22" s="187"/>
+      <c r="F22" s="187"/>
+      <c r="G22" s="111"/>
+      <c r="H22" s="106"/>
+      <c r="I22" s="106"/>
+      <c r="J22" s="106" t="s">
         <v>22</v>
       </c>
-      <c r="K17" s="54"/>
-    </row>
-    <row r="18" spans="1:11" ht="79.5" customHeight="1">
-      <c r="A18" s="52" t="s">
-        <v>90</v>
-      </c>
-      <c r="B18" s="93" t="s">
-        <v>148</v>
-      </c>
-      <c r="C18" s="58" t="s">
-        <v>91</v>
-      </c>
-      <c r="D18" s="127" t="s">
+      <c r="K22" s="106"/>
+    </row>
+    <row r="23" spans="1:11" ht="65.25" customHeight="1">
+      <c r="A23" s="104" t="s">
+        <v>156</v>
+      </c>
+      <c r="B23" s="106" t="s">
+        <v>93</v>
+      </c>
+      <c r="C23" s="106" t="s">
+        <v>94</v>
+      </c>
+      <c r="D23" s="188" t="s">
         <v>92</v>
       </c>
-      <c r="E18" s="128"/>
-      <c r="F18" s="128"/>
-      <c r="G18" s="59"/>
-      <c r="H18" s="59"/>
-      <c r="I18" s="54"/>
-      <c r="J18" s="54" t="s">
+      <c r="E23" s="189"/>
+      <c r="F23" s="189"/>
+      <c r="G23" s="107"/>
+      <c r="H23" s="117"/>
+      <c r="I23" s="117"/>
+      <c r="J23" s="117" t="s">
         <v>22</v>
       </c>
-      <c r="K18" s="54"/>
-    </row>
-    <row r="19" spans="1:11" ht="78.75" customHeight="1">
-      <c r="A19" s="52" t="s">
-        <v>93</v>
-      </c>
-      <c r="B19" s="93" t="s">
-        <v>94</v>
-      </c>
-      <c r="C19" s="58" t="s">
-        <v>95</v>
-      </c>
-      <c r="D19" s="127" t="s">
-        <v>92</v>
-      </c>
-      <c r="E19" s="128"/>
-      <c r="F19" s="128"/>
-      <c r="G19" s="59"/>
-      <c r="H19" s="59"/>
-      <c r="I19" s="54"/>
-      <c r="J19" s="54" t="s">
+      <c r="K23" s="117"/>
+    </row>
+    <row r="24" spans="1:11" ht="18" customHeight="1">
+      <c r="A24" s="185" t="s">
+        <v>157</v>
+      </c>
+      <c r="B24" s="186"/>
+      <c r="C24" s="186"/>
+      <c r="D24" s="196"/>
+      <c r="E24" s="196"/>
+      <c r="F24" s="196"/>
+      <c r="G24" s="114"/>
+      <c r="H24" s="114"/>
+      <c r="I24" s="114"/>
+      <c r="J24" s="114"/>
+      <c r="K24" s="115"/>
+    </row>
+    <row r="25" spans="1:11" ht="79.5" customHeight="1">
+      <c r="A25" s="119" t="s">
+        <v>158</v>
+      </c>
+      <c r="B25" s="106" t="s">
+        <v>159</v>
+      </c>
+      <c r="C25" s="106" t="s">
+        <v>160</v>
+      </c>
+      <c r="D25" s="188" t="s">
+        <v>161</v>
+      </c>
+      <c r="E25" s="189"/>
+      <c r="F25" s="189"/>
+      <c r="G25" s="107"/>
+      <c r="H25" s="117"/>
+      <c r="I25" s="117"/>
+      <c r="J25" s="117" t="s">
         <v>22</v>
       </c>
-      <c r="K19" s="54"/>
-    </row>
-    <row r="20" spans="1:11" ht="78.75" customHeight="1">
-      <c r="A20" s="64" t="s">
-        <v>96</v>
-      </c>
-      <c r="B20" s="95" t="s">
-        <v>97</v>
-      </c>
-      <c r="C20" s="65" t="s">
-        <v>98</v>
-      </c>
-      <c r="D20" s="142" t="s">
-        <v>92</v>
-      </c>
-      <c r="E20" s="143"/>
-      <c r="F20" s="143"/>
-      <c r="G20" s="66"/>
-      <c r="H20" s="67"/>
-      <c r="I20" s="67"/>
-      <c r="J20" s="67" t="s">
+      <c r="K25" s="117"/>
+    </row>
+    <row r="26" spans="1:11" ht="81.75" customHeight="1">
+      <c r="A26" s="119" t="s">
+        <v>162</v>
+      </c>
+      <c r="B26" s="106" t="s">
+        <v>163</v>
+      </c>
+      <c r="C26" s="106" t="s">
+        <v>164</v>
+      </c>
+      <c r="D26" s="183" t="s">
+        <v>165</v>
+      </c>
+      <c r="E26" s="183"/>
+      <c r="F26" s="184"/>
+      <c r="G26" s="111"/>
+      <c r="H26" s="111"/>
+      <c r="I26" s="106"/>
+      <c r="J26" s="106" t="s">
         <v>22</v>
       </c>
-      <c r="K20" s="67"/>
-    </row>
-    <row r="21" spans="1:11">
-      <c r="A21" s="110" t="s">
-        <v>99</v>
-      </c>
-      <c r="B21" s="111"/>
-      <c r="C21" s="111"/>
-      <c r="D21" s="61"/>
-      <c r="E21" s="61"/>
-      <c r="F21" s="61"/>
-      <c r="G21" s="61"/>
-      <c r="H21" s="50"/>
-      <c r="I21" s="50"/>
-      <c r="J21" s="50"/>
-      <c r="K21" s="51"/>
-    </row>
-    <row r="22" spans="1:11" ht="66" customHeight="1">
-      <c r="A22" s="52" t="s">
-        <v>100</v>
-      </c>
-      <c r="B22" s="63" t="s">
-        <v>101</v>
-      </c>
-      <c r="C22" s="63" t="s">
-        <v>102</v>
-      </c>
-      <c r="D22" s="127" t="s">
-        <v>103</v>
-      </c>
-      <c r="E22" s="128"/>
-      <c r="F22" s="128"/>
-      <c r="G22" s="59"/>
-      <c r="H22" s="56"/>
-      <c r="I22" s="58"/>
-      <c r="J22" s="54" t="s">
+      <c r="K26" s="106"/>
+    </row>
+    <row r="27" spans="1:11" ht="42" customHeight="1">
+      <c r="A27" s="119" t="s">
+        <v>166</v>
+      </c>
+      <c r="B27" s="106" t="s">
+        <v>167</v>
+      </c>
+      <c r="C27" s="106" t="s">
+        <v>168</v>
+      </c>
+      <c r="D27" s="183" t="s">
+        <v>169</v>
+      </c>
+      <c r="E27" s="183"/>
+      <c r="F27" s="184"/>
+      <c r="G27" s="111"/>
+      <c r="H27" s="106"/>
+      <c r="I27" s="106"/>
+      <c r="J27" s="106" t="s">
         <v>22</v>
       </c>
-      <c r="K22" s="54"/>
-    </row>
-    <row r="23" spans="1:11" ht="65.25" customHeight="1">
-      <c r="A23" s="68" t="s">
-        <v>104</v>
-      </c>
-      <c r="B23" s="54" t="s">
-        <v>105</v>
-      </c>
-      <c r="C23" s="54" t="s">
-        <v>106</v>
-      </c>
-      <c r="D23" s="127" t="s">
-        <v>107</v>
-      </c>
-      <c r="E23" s="128"/>
-      <c r="F23" s="128"/>
-      <c r="G23" s="59"/>
-      <c r="H23" s="54"/>
-      <c r="I23" s="54"/>
-      <c r="J23" s="54" t="s">
-        <v>22</v>
-      </c>
-      <c r="K23" s="54"/>
-    </row>
-    <row r="24" spans="1:11" ht="67.5" customHeight="1">
-      <c r="A24" s="68" t="s">
-        <v>108</v>
-      </c>
-      <c r="B24" s="54" t="s">
-        <v>109</v>
-      </c>
-      <c r="C24" s="54" t="s">
-        <v>110</v>
-      </c>
-      <c r="D24" s="127" t="s">
-        <v>107</v>
-      </c>
-      <c r="E24" s="128"/>
-      <c r="F24" s="128"/>
-      <c r="G24" s="59"/>
-      <c r="H24" s="54"/>
-      <c r="I24" s="54"/>
-      <c r="J24" s="54" t="s">
-        <v>22</v>
-      </c>
-      <c r="K24" s="54"/>
-    </row>
-    <row r="25" spans="1:11">
-      <c r="A25" s="92" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11">
-      <c r="A26" s="92" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11">
-      <c r="A27" s="90"/>
-    </row>
-    <row r="28" spans="1:11" ht="26.4">
-      <c r="A28" s="91" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" ht="26.4">
-      <c r="A29" s="91" t="s">
-        <v>140</v>
-      </c>
+      <c r="K27" s="106"/>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" s="206"/>
+      <c r="B28" s="207"/>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" s="206"/>
+      <c r="B29" s="207"/>
     </row>
     <row r="30" spans="1:11">
-      <c r="A30" s="90"/>
-    </row>
-    <row r="31" spans="1:11" ht="26.4">
-      <c r="A31" s="91" t="s">
-        <v>141</v>
-      </c>
-      <c r="C31" s="96" t="s">
-        <v>149</v>
-      </c>
+      <c r="A30" s="207"/>
+      <c r="B30" s="207"/>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" s="206"/>
+      <c r="B31" s="207"/>
+      <c r="C31" s="82"/>
     </row>
     <row r="32" spans="1:11">
-      <c r="A32" s="90"/>
-    </row>
-    <row r="33" spans="1:2" ht="26.4">
-      <c r="A33" s="91" t="s">
-        <v>142</v>
-      </c>
+      <c r="A32" s="206"/>
+      <c r="B32" s="207"/>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="207"/>
+      <c r="B33" s="207"/>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" s="90" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" ht="52.8">
-      <c r="A35" s="91" t="s">
-        <v>144</v>
-      </c>
+      <c r="A34" s="206"/>
+      <c r="B34" s="207"/>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" s="206"/>
+      <c r="B35" s="207"/>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="90" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" ht="26.4">
-      <c r="A37" s="91" t="s">
-        <v>146</v>
-      </c>
-      <c r="B37" s="90"/>
+      <c r="A36" s="207"/>
+      <c r="B36" s="207"/>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="206"/>
+      <c r="B37" s="207"/>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" s="206"/>
+      <c r="B38" s="207"/>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="90" t="s">
-        <v>147</v>
-      </c>
+      <c r="A39" s="207"/>
+      <c r="B39" s="207"/>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" s="207"/>
+      <c r="B40" s="207"/>
     </row>
   </sheetData>
-  <mergeCells count="32">
-    <mergeCell ref="B1:D2"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D9:G10"/>
+  <mergeCells count="35">
     <mergeCell ref="D18:F18"/>
     <mergeCell ref="D19:F19"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="A21:C21"/>
     <mergeCell ref="D22:F22"/>
     <mergeCell ref="D13:F13"/>
     <mergeCell ref="D14:F14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D16:F16"/>
     <mergeCell ref="D17:F17"/>
     <mergeCell ref="I6:K6"/>
     <mergeCell ref="I7:K7"/>
@@ -4664,29 +5449,44 @@
     <mergeCell ref="I9:I10"/>
     <mergeCell ref="J9:J10"/>
     <mergeCell ref="K9:K10"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D9:G10"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="I3:K3"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="I4:K4"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="I5:K5"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D24:F24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="13.5"/>
   <cols>
-    <col min="3" max="3" width="22.77734375" customWidth="1"/>
-    <col min="7" max="7" width="18.77734375" customWidth="1"/>
+    <col min="3" max="3" width="22.75" customWidth="1"/>
+    <col min="7" max="7" width="18.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="22.2">
+    <row r="1" spans="1:7" ht="22.5">
       <c r="A1" s="2" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="4"/>
@@ -4704,9 +5504,9 @@
       <c r="F2" s="4"/>
       <c r="G2" s="5"/>
     </row>
-    <row r="3" spans="1:7" ht="13.8">
+    <row r="3" spans="1:7" ht="14.25">
       <c r="B3" s="6" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
@@ -4714,9 +5514,9 @@
       <c r="F3" s="4"/>
       <c r="G3" s="5"/>
     </row>
-    <row r="4" spans="1:7" ht="13.8">
+    <row r="4" spans="1:7" ht="14.25">
       <c r="B4" s="6" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="C4" s="7"/>
       <c r="D4" s="6"/>
@@ -4724,7 +5524,7 @@
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
     </row>
-    <row r="5" spans="1:7" ht="13.8">
+    <row r="5" spans="1:7" ht="14.25">
       <c r="A5" s="6"/>
       <c r="B5" s="6"/>
       <c r="C5" s="6"/>
@@ -4733,7 +5533,7 @@
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
     </row>
-    <row r="6" spans="1:7" ht="13.8">
+    <row r="6" spans="1:7" ht="14.25">
       <c r="A6" s="6"/>
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
@@ -4742,13 +5542,13 @@
       <c r="F6" s="6"/>
       <c r="G6" s="6"/>
     </row>
-    <row r="7" spans="1:7" ht="26.4">
+    <row r="7" spans="1:7" ht="25.5">
       <c r="A7" s="6"/>
       <c r="B7" s="8" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="D7" s="10" t="s">
         <v>21</v>
@@ -4760,10 +5560,10 @@
         <v>22</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" s="1" customFormat="1" ht="13.8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" s="1" customFormat="1" ht="14.25">
       <c r="A8" s="12"/>
       <c r="B8" s="13">
         <v>1</v>
@@ -4789,7 +5589,7 @@
         <v>-9</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="13.8">
+    <row r="9" spans="1:7" ht="14.25">
       <c r="A9" s="6"/>
       <c r="B9" s="16"/>
       <c r="C9" s="17"/>
@@ -4798,11 +5598,11 @@
       <c r="F9" s="19"/>
       <c r="G9" s="20"/>
     </row>
-    <row r="10" spans="1:7" ht="13.8">
+    <row r="10" spans="1:7" ht="14.25">
       <c r="A10" s="6"/>
       <c r="B10" s="21"/>
       <c r="C10" s="22" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="D10" s="23">
         <f>SUM(D6:D9)</f>
@@ -4821,7 +5621,7 @@
         <v>-9</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="13.8">
+    <row r="11" spans="1:7" ht="14.25">
       <c r="A11" s="6"/>
       <c r="B11" s="25"/>
       <c r="C11" s="6"/>
@@ -4830,11 +5630,11 @@
       <c r="F11" s="27"/>
       <c r="G11" s="27"/>
     </row>
-    <row r="12" spans="1:7" ht="13.8">
+    <row r="12" spans="1:7" ht="14.25">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
       <c r="C12" s="6" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="28">
@@ -4842,15 +5642,15 @@
         <v>-33.3333333333333</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="G12" s="29"/>
     </row>
-    <row r="13" spans="1:7" ht="13.8">
+    <row r="13" spans="1:7" ht="14.25">
       <c r="A13" s="6"/>
       <c r="B13" s="6"/>
       <c r="C13" s="6" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="D13" s="6"/>
       <c r="E13" s="28">
@@ -4858,7 +5658,7 @@
         <v>-33.3333333333333</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="G13" s="29"/>
     </row>

--- a/test-case-example.xlsx
+++ b/test-case-example.xlsx
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="977" uniqueCount="586">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="977" uniqueCount="585">
   <si>
     <t>TEST CASE</t>
   </si>
@@ -2312,9 +2312,6 @@
     <t>Related</t>
   </si>
   <si>
-    <t>28/4/2026</t>
-  </si>
-  <si>
     <t>__init__.py</t>
   </si>
   <si>
@@ -2362,9 +2359,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="3">
-    <numFmt numFmtId="168" formatCode="[$-409]d\-mmm\-yy;@"/>
-    <numFmt numFmtId="169" formatCode="0.000"/>
-    <numFmt numFmtId="170" formatCode="dd/mm/yyyy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
   <fonts count="47">
     <font>
@@ -3551,11 +3548,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3679,8 +3676,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3781,7 +3778,7 @@
     <xf numFmtId="0" fontId="18" fillId="9" borderId="56" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="13" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3847,7 +3844,7 @@
     <xf numFmtId="0" fontId="9" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="13" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3874,7 +3871,7 @@
     <xf numFmtId="0" fontId="26" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="13" fillId="12" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="13" fillId="12" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="12" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3895,10 +3892,10 @@
     <xf numFmtId="0" fontId="13" fillId="12" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="13" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3908,7 +3905,7 @@
     <xf numFmtId="0" fontId="28" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3921,7 +3918,7 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="169" fontId="13" fillId="0" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3945,17 +3942,17 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="170" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="170" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="31" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="170" fontId="33" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="170" fontId="34" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="33" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="34" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="61" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="37" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="37" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="170" fontId="39" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="39" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3967,7 +3964,7 @@
     <xf numFmtId="0" fontId="39" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="40" fillId="12" borderId="61" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="40" fillId="12" borderId="61" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="12" borderId="61" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3976,7 +3973,7 @@
     <xf numFmtId="0" fontId="40" fillId="12" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="40" fillId="12" borderId="63" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="40" fillId="12" borderId="63" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="12" borderId="63" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3985,21 +3982,135 @@
     <xf numFmtId="0" fontId="40" fillId="12" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="40" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="40" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="58" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="59" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="60" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="40" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="56" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="39" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="40" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="56" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="39" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="40" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="56" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="49" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="42" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="49" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="42" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="52" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="53" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="50" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="51" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="54" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="48" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="55" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="36" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="37" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="39" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -4021,117 +4132,6 @@
     <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="39" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="40" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="56" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="39" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="40" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="56" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="58" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="59" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="60" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="40" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="56" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="49" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="42" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="49" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="42" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="52" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="53" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="50" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="51" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="54" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="48" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="55" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -4150,6 +4150,15 @@
     <xf numFmtId="0" fontId="18" fillId="9" borderId="40" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="39" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="25" fillId="9" borderId="39" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -4159,15 +4168,6 @@
     <xf numFmtId="0" fontId="25" fillId="9" borderId="56" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="39" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="9" borderId="40" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -4195,14 +4195,44 @@
     <xf numFmtId="0" fontId="13" fillId="6" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="9" borderId="39" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="10" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -4210,41 +4240,8 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="1" fontId="8" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="10" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -5182,11 +5179,11 @@
       <c r="A3" s="70" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="170" t="s">
+      <c r="B3" s="209" t="s">
         <v>62</v>
       </c>
-      <c r="C3" s="170"/>
-      <c r="D3" s="171"/>
+      <c r="C3" s="209"/>
+      <c r="D3" s="210"/>
       <c r="E3" s="71"/>
       <c r="F3" s="71"/>
       <c r="G3" s="71"/>
@@ -5195,11 +5192,11 @@
       <c r="A4" s="74" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="173" t="s">
+      <c r="B4" s="211" t="s">
         <v>488</v>
       </c>
-      <c r="C4" s="174"/>
-      <c r="D4" s="175"/>
+      <c r="C4" s="212"/>
+      <c r="D4" s="213"/>
       <c r="E4" s="71"/>
       <c r="F4" s="71"/>
       <c r="G4" s="71"/>
@@ -5208,11 +5205,11 @@
       <c r="A5" s="74" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="176" t="s">
+      <c r="B5" s="214" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="177"/>
-      <c r="D5" s="178"/>
+      <c r="C5" s="215"/>
+      <c r="D5" s="216"/>
       <c r="E5" s="75"/>
       <c r="F5" s="75"/>
       <c r="G5" s="75"/>
@@ -5252,83 +5249,83 @@
       <c r="G7" s="85"/>
     </row>
     <row r="8" spans="1:11" ht="14.25">
-      <c r="A8" s="237"/>
-      <c r="B8" s="237"/>
-      <c r="C8" s="237"/>
-      <c r="D8" s="237"/>
+      <c r="A8" s="238"/>
+      <c r="B8" s="238"/>
+      <c r="C8" s="238"/>
+      <c r="D8" s="238"/>
       <c r="E8" s="72"/>
       <c r="F8" s="72"/>
       <c r="G8" s="72"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="205" t="s">
+      <c r="A9" s="197" t="s">
         <v>71</v>
       </c>
-      <c r="B9" s="207" t="s">
+      <c r="B9" s="199" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="205" t="s">
+      <c r="C9" s="197" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="211" t="s">
+      <c r="D9" s="203" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="212"/>
-      <c r="F9" s="212"/>
-      <c r="G9" s="213"/>
-      <c r="H9" s="209" t="s">
+      <c r="E9" s="204"/>
+      <c r="F9" s="204"/>
+      <c r="G9" s="205"/>
+      <c r="H9" s="201" t="s">
         <v>75</v>
       </c>
-      <c r="I9" s="210" t="s">
+      <c r="I9" s="202" t="s">
         <v>76</v>
       </c>
-      <c r="J9" s="210" t="s">
+      <c r="J9" s="202" t="s">
         <v>77</v>
       </c>
-      <c r="K9" s="210" t="s">
+      <c r="K9" s="202" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="206"/>
-      <c r="B10" s="208"/>
-      <c r="C10" s="206"/>
-      <c r="D10" s="214"/>
-      <c r="E10" s="215"/>
-      <c r="F10" s="215"/>
-      <c r="G10" s="216"/>
-      <c r="H10" s="205"/>
-      <c r="I10" s="205"/>
-      <c r="J10" s="205"/>
-      <c r="K10" s="205"/>
+      <c r="A10" s="198"/>
+      <c r="B10" s="200"/>
+      <c r="C10" s="198"/>
+      <c r="D10" s="206"/>
+      <c r="E10" s="207"/>
+      <c r="F10" s="207"/>
+      <c r="G10" s="208"/>
+      <c r="H10" s="197"/>
+      <c r="I10" s="197"/>
+      <c r="J10" s="197"/>
+      <c r="K10" s="197"/>
     </row>
     <row r="11" spans="1:11" ht="15">
-      <c r="A11" s="181"/>
-      <c r="B11" s="181"/>
-      <c r="C11" s="181"/>
-      <c r="D11" s="181"/>
-      <c r="E11" s="181"/>
-      <c r="F11" s="181"/>
-      <c r="G11" s="181"/>
-      <c r="H11" s="181"/>
-      <c r="I11" s="181"/>
-      <c r="J11" s="181"/>
-      <c r="K11" s="182"/>
+      <c r="A11" s="195"/>
+      <c r="B11" s="195"/>
+      <c r="C11" s="195"/>
+      <c r="D11" s="195"/>
+      <c r="E11" s="195"/>
+      <c r="F11" s="195"/>
+      <c r="G11" s="195"/>
+      <c r="H11" s="195"/>
+      <c r="I11" s="195"/>
+      <c r="J11" s="195"/>
+      <c r="K11" s="196"/>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="183" t="s">
+      <c r="A12" s="184" t="s">
         <v>489</v>
       </c>
-      <c r="B12" s="184"/>
-      <c r="C12" s="184"/>
-      <c r="D12" s="184"/>
-      <c r="E12" s="184"/>
-      <c r="F12" s="184"/>
-      <c r="G12" s="184"/>
-      <c r="H12" s="184"/>
-      <c r="I12" s="184"/>
-      <c r="J12" s="184"/>
-      <c r="K12" s="185"/>
+      <c r="B12" s="185"/>
+      <c r="C12" s="185"/>
+      <c r="D12" s="185"/>
+      <c r="E12" s="185"/>
+      <c r="F12" s="185"/>
+      <c r="G12" s="185"/>
+      <c r="H12" s="185"/>
+      <c r="I12" s="185"/>
+      <c r="J12" s="185"/>
+      <c r="K12" s="186"/>
     </row>
     <row r="13" spans="1:11" ht="38.25">
       <c r="A13" s="90" t="s">
@@ -5340,12 +5337,12 @@
       <c r="C13" s="92" t="s">
         <v>491</v>
       </c>
-      <c r="D13" s="186" t="s">
+      <c r="D13" s="187" t="s">
         <v>492</v>
       </c>
-      <c r="E13" s="187"/>
-      <c r="F13" s="187"/>
-      <c r="G13" s="188"/>
+      <c r="E13" s="176"/>
+      <c r="F13" s="176"/>
+      <c r="G13" s="177"/>
       <c r="H13" s="94"/>
       <c r="I13" s="96"/>
       <c r="J13" s="92" t="s">
@@ -5354,19 +5351,19 @@
       <c r="K13" s="92"/>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="183" t="s">
+      <c r="A14" s="184" t="s">
         <v>493</v>
       </c>
-      <c r="B14" s="184"/>
-      <c r="C14" s="184"/>
-      <c r="D14" s="184"/>
-      <c r="E14" s="184"/>
-      <c r="F14" s="184"/>
-      <c r="G14" s="184"/>
-      <c r="H14" s="184"/>
-      <c r="I14" s="184"/>
-      <c r="J14" s="184"/>
-      <c r="K14" s="185"/>
+      <c r="B14" s="185"/>
+      <c r="C14" s="185"/>
+      <c r="D14" s="185"/>
+      <c r="E14" s="185"/>
+      <c r="F14" s="185"/>
+      <c r="G14" s="185"/>
+      <c r="H14" s="185"/>
+      <c r="I14" s="185"/>
+      <c r="J14" s="185"/>
+      <c r="K14" s="186"/>
     </row>
     <row r="15" spans="1:11" ht="25.5">
       <c r="A15" s="102" t="s">
@@ -5378,12 +5375,12 @@
       <c r="C15" s="102" t="s">
         <v>495</v>
       </c>
-      <c r="D15" s="189" t="s">
+      <c r="D15" s="188" t="s">
         <v>496</v>
       </c>
-      <c r="E15" s="190"/>
-      <c r="F15" s="190"/>
-      <c r="G15" s="191"/>
+      <c r="E15" s="189"/>
+      <c r="F15" s="189"/>
+      <c r="G15" s="190"/>
       <c r="H15" s="103"/>
       <c r="I15" s="103"/>
       <c r="J15" s="104" t="s">
@@ -5392,19 +5389,19 @@
       <c r="K15" s="103"/>
     </row>
     <row r="16" spans="1:11">
-      <c r="A16" s="183" t="s">
+      <c r="A16" s="184" t="s">
         <v>497</v>
       </c>
-      <c r="B16" s="184"/>
-      <c r="C16" s="184"/>
-      <c r="D16" s="184"/>
-      <c r="E16" s="184"/>
-      <c r="F16" s="184"/>
-      <c r="G16" s="184"/>
-      <c r="H16" s="184"/>
-      <c r="I16" s="184"/>
-      <c r="J16" s="184"/>
-      <c r="K16" s="185"/>
+      <c r="B16" s="185"/>
+      <c r="C16" s="185"/>
+      <c r="D16" s="185"/>
+      <c r="E16" s="185"/>
+      <c r="F16" s="185"/>
+      <c r="G16" s="185"/>
+      <c r="H16" s="185"/>
+      <c r="I16" s="185"/>
+      <c r="J16" s="185"/>
+      <c r="K16" s="186"/>
     </row>
     <row r="17" spans="1:11" ht="38.25">
       <c r="A17" s="102" t="s">
@@ -5416,12 +5413,12 @@
       <c r="C17" s="102" t="s">
         <v>499</v>
       </c>
-      <c r="D17" s="189" t="s">
+      <c r="D17" s="188" t="s">
         <v>500</v>
       </c>
-      <c r="E17" s="190"/>
-      <c r="F17" s="190"/>
-      <c r="G17" s="191"/>
+      <c r="E17" s="189"/>
+      <c r="F17" s="189"/>
+      <c r="G17" s="190"/>
       <c r="H17" s="103"/>
       <c r="I17" s="103"/>
       <c r="J17" s="104" t="s">
@@ -5430,19 +5427,19 @@
       <c r="K17" s="103"/>
     </row>
     <row r="18" spans="1:11">
-      <c r="A18" s="183" t="s">
+      <c r="A18" s="184" t="s">
         <v>501</v>
       </c>
-      <c r="B18" s="184"/>
-      <c r="C18" s="184"/>
-      <c r="D18" s="184"/>
-      <c r="E18" s="184"/>
-      <c r="F18" s="184"/>
-      <c r="G18" s="184"/>
-      <c r="H18" s="184"/>
-      <c r="I18" s="184"/>
-      <c r="J18" s="184"/>
-      <c r="K18" s="185"/>
+      <c r="B18" s="185"/>
+      <c r="C18" s="185"/>
+      <c r="D18" s="185"/>
+      <c r="E18" s="185"/>
+      <c r="F18" s="185"/>
+      <c r="G18" s="185"/>
+      <c r="H18" s="185"/>
+      <c r="I18" s="185"/>
+      <c r="J18" s="185"/>
+      <c r="K18" s="186"/>
     </row>
     <row r="19" spans="1:11" ht="38.25">
       <c r="A19" s="102" t="s">
@@ -5454,12 +5451,12 @@
       <c r="C19" s="102" t="s">
         <v>503</v>
       </c>
-      <c r="D19" s="189" t="s">
+      <c r="D19" s="188" t="s">
         <v>504</v>
       </c>
-      <c r="E19" s="190"/>
-      <c r="F19" s="190"/>
-      <c r="G19" s="191"/>
+      <c r="E19" s="189"/>
+      <c r="F19" s="189"/>
+      <c r="G19" s="190"/>
       <c r="H19" s="103"/>
       <c r="I19" s="103"/>
       <c r="J19" s="104" t="s">
@@ -5468,19 +5465,19 @@
       <c r="K19" s="103"/>
     </row>
     <row r="20" spans="1:11">
-      <c r="A20" s="183" t="s">
+      <c r="A20" s="184" t="s">
         <v>505</v>
       </c>
-      <c r="B20" s="184"/>
-      <c r="C20" s="184"/>
-      <c r="D20" s="184"/>
-      <c r="E20" s="184"/>
-      <c r="F20" s="184"/>
-      <c r="G20" s="184"/>
-      <c r="H20" s="184"/>
-      <c r="I20" s="184"/>
-      <c r="J20" s="184"/>
-      <c r="K20" s="185"/>
+      <c r="B20" s="185"/>
+      <c r="C20" s="185"/>
+      <c r="D20" s="185"/>
+      <c r="E20" s="185"/>
+      <c r="F20" s="185"/>
+      <c r="G20" s="185"/>
+      <c r="H20" s="185"/>
+      <c r="I20" s="185"/>
+      <c r="J20" s="185"/>
+      <c r="K20" s="186"/>
     </row>
     <row r="21" spans="1:11" ht="38.25">
       <c r="A21" s="102" t="s">
@@ -5492,12 +5489,12 @@
       <c r="C21" s="102" t="s">
         <v>507</v>
       </c>
-      <c r="D21" s="189" t="s">
+      <c r="D21" s="188" t="s">
         <v>508</v>
       </c>
-      <c r="E21" s="190"/>
-      <c r="F21" s="190"/>
-      <c r="G21" s="191"/>
+      <c r="E21" s="189"/>
+      <c r="F21" s="189"/>
+      <c r="G21" s="190"/>
       <c r="H21" s="103"/>
       <c r="I21" s="103"/>
       <c r="J21" s="104" t="s">
@@ -5506,19 +5503,19 @@
       <c r="K21" s="103"/>
     </row>
     <row r="22" spans="1:11">
-      <c r="A22" s="183" t="s">
+      <c r="A22" s="184" t="s">
         <v>509</v>
       </c>
-      <c r="B22" s="184"/>
-      <c r="C22" s="184"/>
-      <c r="D22" s="184"/>
-      <c r="E22" s="184"/>
-      <c r="F22" s="184"/>
-      <c r="G22" s="184"/>
-      <c r="H22" s="184"/>
-      <c r="I22" s="184"/>
-      <c r="J22" s="184"/>
-      <c r="K22" s="185"/>
+      <c r="B22" s="185"/>
+      <c r="C22" s="185"/>
+      <c r="D22" s="185"/>
+      <c r="E22" s="185"/>
+      <c r="F22" s="185"/>
+      <c r="G22" s="185"/>
+      <c r="H22" s="185"/>
+      <c r="I22" s="185"/>
+      <c r="J22" s="185"/>
+      <c r="K22" s="186"/>
     </row>
     <row r="23" spans="1:11" ht="38.25">
       <c r="A23" s="102" t="s">
@@ -5530,12 +5527,12 @@
       <c r="C23" s="102" t="s">
         <v>511</v>
       </c>
-      <c r="D23" s="189" t="s">
+      <c r="D23" s="188" t="s">
         <v>512</v>
       </c>
-      <c r="E23" s="190"/>
-      <c r="F23" s="190"/>
-      <c r="G23" s="191"/>
+      <c r="E23" s="189"/>
+      <c r="F23" s="189"/>
+      <c r="G23" s="190"/>
       <c r="H23" s="103"/>
       <c r="I23" s="103"/>
       <c r="J23" s="104" t="s">
@@ -5544,19 +5541,19 @@
       <c r="K23" s="103"/>
     </row>
     <row r="24" spans="1:11">
-      <c r="A24" s="183" t="s">
+      <c r="A24" s="184" t="s">
         <v>513</v>
       </c>
-      <c r="B24" s="184"/>
-      <c r="C24" s="184"/>
-      <c r="D24" s="184"/>
-      <c r="E24" s="184"/>
-      <c r="F24" s="184"/>
-      <c r="G24" s="184"/>
-      <c r="H24" s="184"/>
-      <c r="I24" s="184"/>
-      <c r="J24" s="184"/>
-      <c r="K24" s="185"/>
+      <c r="B24" s="185"/>
+      <c r="C24" s="185"/>
+      <c r="D24" s="185"/>
+      <c r="E24" s="185"/>
+      <c r="F24" s="185"/>
+      <c r="G24" s="185"/>
+      <c r="H24" s="185"/>
+      <c r="I24" s="185"/>
+      <c r="J24" s="185"/>
+      <c r="K24" s="186"/>
     </row>
     <row r="25" spans="1:11" ht="38.25">
       <c r="A25" s="102" t="s">
@@ -5568,12 +5565,12 @@
       <c r="C25" s="102" t="s">
         <v>515</v>
       </c>
-      <c r="D25" s="189" t="s">
+      <c r="D25" s="188" t="s">
         <v>516</v>
       </c>
-      <c r="E25" s="190"/>
-      <c r="F25" s="190"/>
-      <c r="G25" s="191"/>
+      <c r="E25" s="189"/>
+      <c r="F25" s="189"/>
+      <c r="G25" s="190"/>
       <c r="H25" s="103"/>
       <c r="I25" s="103"/>
       <c r="J25" s="104" t="s">
@@ -5582,19 +5579,19 @@
       <c r="K25" s="103"/>
     </row>
     <row r="26" spans="1:11">
-      <c r="A26" s="183" t="s">
+      <c r="A26" s="184" t="s">
         <v>517</v>
       </c>
-      <c r="B26" s="184"/>
-      <c r="C26" s="184"/>
-      <c r="D26" s="184"/>
-      <c r="E26" s="184"/>
-      <c r="F26" s="184"/>
-      <c r="G26" s="184"/>
-      <c r="H26" s="184"/>
-      <c r="I26" s="184"/>
-      <c r="J26" s="184"/>
-      <c r="K26" s="185"/>
+      <c r="B26" s="185"/>
+      <c r="C26" s="185"/>
+      <c r="D26" s="185"/>
+      <c r="E26" s="185"/>
+      <c r="F26" s="185"/>
+      <c r="G26" s="185"/>
+      <c r="H26" s="185"/>
+      <c r="I26" s="185"/>
+      <c r="J26" s="185"/>
+      <c r="K26" s="186"/>
     </row>
     <row r="27" spans="1:11" ht="38.25">
       <c r="A27" s="102" t="s">
@@ -5606,12 +5603,12 @@
       <c r="C27" s="102" t="s">
         <v>519</v>
       </c>
-      <c r="D27" s="189" t="s">
+      <c r="D27" s="188" t="s">
         <v>520</v>
       </c>
-      <c r="E27" s="190"/>
-      <c r="F27" s="190"/>
-      <c r="G27" s="191"/>
+      <c r="E27" s="189"/>
+      <c r="F27" s="189"/>
+      <c r="G27" s="190"/>
       <c r="H27" s="103"/>
       <c r="I27" s="103"/>
       <c r="J27" s="104" t="s">
@@ -5620,19 +5617,19 @@
       <c r="K27" s="103"/>
     </row>
     <row r="28" spans="1:11">
-      <c r="A28" s="183" t="s">
+      <c r="A28" s="184" t="s">
         <v>521</v>
       </c>
-      <c r="B28" s="184"/>
-      <c r="C28" s="184"/>
-      <c r="D28" s="184"/>
-      <c r="E28" s="184"/>
-      <c r="F28" s="184"/>
-      <c r="G28" s="184"/>
-      <c r="H28" s="184"/>
-      <c r="I28" s="184"/>
-      <c r="J28" s="184"/>
-      <c r="K28" s="185"/>
+      <c r="B28" s="185"/>
+      <c r="C28" s="185"/>
+      <c r="D28" s="185"/>
+      <c r="E28" s="185"/>
+      <c r="F28" s="185"/>
+      <c r="G28" s="185"/>
+      <c r="H28" s="185"/>
+      <c r="I28" s="185"/>
+      <c r="J28" s="185"/>
+      <c r="K28" s="186"/>
     </row>
     <row r="29" spans="1:11" ht="38.25">
       <c r="A29" s="102" t="s">
@@ -5644,12 +5641,12 @@
       <c r="C29" s="102" t="s">
         <v>523</v>
       </c>
-      <c r="D29" s="189" t="s">
+      <c r="D29" s="188" t="s">
         <v>524</v>
       </c>
-      <c r="E29" s="190"/>
-      <c r="F29" s="190"/>
-      <c r="G29" s="191"/>
+      <c r="E29" s="189"/>
+      <c r="F29" s="189"/>
+      <c r="G29" s="190"/>
       <c r="H29" s="103"/>
       <c r="I29" s="103"/>
       <c r="J29" s="104" t="s">
@@ -5658,19 +5655,19 @@
       <c r="K29" s="103"/>
     </row>
     <row r="30" spans="1:11">
-      <c r="A30" s="183" t="s">
+      <c r="A30" s="184" t="s">
         <v>525</v>
       </c>
-      <c r="B30" s="184"/>
-      <c r="C30" s="184"/>
-      <c r="D30" s="184"/>
-      <c r="E30" s="184"/>
-      <c r="F30" s="184"/>
-      <c r="G30" s="184"/>
-      <c r="H30" s="184"/>
-      <c r="I30" s="184"/>
-      <c r="J30" s="184"/>
-      <c r="K30" s="185"/>
+      <c r="B30" s="185"/>
+      <c r="C30" s="185"/>
+      <c r="D30" s="185"/>
+      <c r="E30" s="185"/>
+      <c r="F30" s="185"/>
+      <c r="G30" s="185"/>
+      <c r="H30" s="185"/>
+      <c r="I30" s="185"/>
+      <c r="J30" s="185"/>
+      <c r="K30" s="186"/>
     </row>
     <row r="31" spans="1:11" ht="38.25">
       <c r="A31" s="102" t="s">
@@ -5682,12 +5679,12 @@
       <c r="C31" s="102" t="s">
         <v>527</v>
       </c>
-      <c r="D31" s="189" t="s">
+      <c r="D31" s="188" t="s">
         <v>528</v>
       </c>
-      <c r="E31" s="190"/>
-      <c r="F31" s="190"/>
-      <c r="G31" s="191"/>
+      <c r="E31" s="189"/>
+      <c r="F31" s="189"/>
+      <c r="G31" s="190"/>
       <c r="H31" s="103"/>
       <c r="I31" s="103"/>
       <c r="J31" s="104" t="s">
@@ -5696,19 +5693,19 @@
       <c r="K31" s="103"/>
     </row>
     <row r="32" spans="1:11">
-      <c r="A32" s="183" t="s">
+      <c r="A32" s="184" t="s">
         <v>529</v>
       </c>
-      <c r="B32" s="184"/>
-      <c r="C32" s="184"/>
-      <c r="D32" s="184"/>
-      <c r="E32" s="184"/>
-      <c r="F32" s="184"/>
-      <c r="G32" s="184"/>
-      <c r="H32" s="184"/>
-      <c r="I32" s="184"/>
-      <c r="J32" s="184"/>
-      <c r="K32" s="185"/>
+      <c r="B32" s="185"/>
+      <c r="C32" s="185"/>
+      <c r="D32" s="185"/>
+      <c r="E32" s="185"/>
+      <c r="F32" s="185"/>
+      <c r="G32" s="185"/>
+      <c r="H32" s="185"/>
+      <c r="I32" s="185"/>
+      <c r="J32" s="185"/>
+      <c r="K32" s="186"/>
     </row>
     <row r="33" spans="1:11" ht="38.25">
       <c r="A33" s="102" t="s">
@@ -5720,12 +5717,12 @@
       <c r="C33" s="102" t="s">
         <v>531</v>
       </c>
-      <c r="D33" s="189" t="s">
+      <c r="D33" s="188" t="s">
         <v>524</v>
       </c>
-      <c r="E33" s="190"/>
-      <c r="F33" s="190"/>
-      <c r="G33" s="191"/>
+      <c r="E33" s="189"/>
+      <c r="F33" s="189"/>
+      <c r="G33" s="190"/>
       <c r="H33" s="103"/>
       <c r="I33" s="103"/>
       <c r="J33" s="104" t="s">
@@ -5735,6 +5732,25 @@
     </row>
   </sheetData>
   <mergeCells count="35">
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A11:K11"/>
+    <mergeCell ref="A12:K12"/>
+    <mergeCell ref="D13:G13"/>
+    <mergeCell ref="A14:K14"/>
+    <mergeCell ref="D15:G15"/>
+    <mergeCell ref="A16:K16"/>
+    <mergeCell ref="D23:G23"/>
+    <mergeCell ref="A24:K24"/>
+    <mergeCell ref="D25:G25"/>
+    <mergeCell ref="A26:K26"/>
+    <mergeCell ref="D17:G17"/>
+    <mergeCell ref="A18:K18"/>
+    <mergeCell ref="D19:G19"/>
+    <mergeCell ref="A20:K20"/>
+    <mergeCell ref="D21:G21"/>
     <mergeCell ref="A32:K32"/>
     <mergeCell ref="D33:G33"/>
     <mergeCell ref="A9:A10"/>
@@ -5751,25 +5767,6 @@
     <mergeCell ref="A30:K30"/>
     <mergeCell ref="D31:G31"/>
     <mergeCell ref="A22:K22"/>
-    <mergeCell ref="D23:G23"/>
-    <mergeCell ref="A24:K24"/>
-    <mergeCell ref="D25:G25"/>
-    <mergeCell ref="A26:K26"/>
-    <mergeCell ref="D17:G17"/>
-    <mergeCell ref="A18:K18"/>
-    <mergeCell ref="D19:G19"/>
-    <mergeCell ref="A20:K20"/>
-    <mergeCell ref="D21:G21"/>
-    <mergeCell ref="A12:K12"/>
-    <mergeCell ref="D13:G13"/>
-    <mergeCell ref="A14:K14"/>
-    <mergeCell ref="D15:G15"/>
-    <mergeCell ref="A16:K16"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A11:K11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5828,54 +5825,54 @@
       <c r="A3" s="70" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="170" t="s">
+      <c r="B3" s="209" t="s">
         <v>532</v>
       </c>
-      <c r="C3" s="170"/>
-      <c r="D3" s="171"/>
+      <c r="C3" s="209"/>
+      <c r="D3" s="210"/>
       <c r="E3" s="71"/>
       <c r="F3" s="71"/>
       <c r="G3" s="71"/>
       <c r="H3" s="71"/>
-      <c r="I3" s="172"/>
-      <c r="J3" s="172"/>
-      <c r="K3" s="172"/>
+      <c r="I3" s="193"/>
+      <c r="J3" s="193"/>
+      <c r="K3" s="193"/>
       <c r="L3" s="73"/>
     </row>
     <row r="4" spans="1:12" s="61" customFormat="1" ht="12.75">
       <c r="A4" s="74" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="173" t="s">
+      <c r="B4" s="211" t="s">
         <v>533</v>
       </c>
-      <c r="C4" s="174"/>
-      <c r="D4" s="175"/>
+      <c r="C4" s="212"/>
+      <c r="D4" s="213"/>
       <c r="E4" s="71"/>
       <c r="F4" s="71"/>
       <c r="G4" s="71"/>
       <c r="H4" s="71"/>
-      <c r="I4" s="172"/>
-      <c r="J4" s="172"/>
-      <c r="K4" s="172"/>
+      <c r="I4" s="193"/>
+      <c r="J4" s="193"/>
+      <c r="K4" s="193"/>
       <c r="L4" s="73"/>
     </row>
     <row r="5" spans="1:12" s="62" customFormat="1" ht="25.5">
       <c r="A5" s="74" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="176" t="s">
+      <c r="B5" s="214" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="177"/>
-      <c r="D5" s="178"/>
+      <c r="C5" s="215"/>
+      <c r="D5" s="216"/>
       <c r="E5" s="75"/>
       <c r="F5" s="75"/>
       <c r="G5" s="75"/>
       <c r="H5" s="75"/>
-      <c r="I5" s="179"/>
-      <c r="J5" s="179"/>
-      <c r="K5" s="179"/>
+      <c r="I5" s="217"/>
+      <c r="J5" s="217"/>
+      <c r="K5" s="217"/>
       <c r="L5" s="76"/>
     </row>
     <row r="6" spans="1:12" s="61" customFormat="1" ht="15" customHeight="1">
@@ -5897,9 +5894,9 @@
       <c r="F6" s="72"/>
       <c r="G6" s="72"/>
       <c r="H6" s="72"/>
-      <c r="I6" s="172"/>
-      <c r="J6" s="172"/>
-      <c r="K6" s="172"/>
+      <c r="I6" s="193"/>
+      <c r="J6" s="193"/>
+      <c r="K6" s="193"/>
       <c r="L6" s="73"/>
     </row>
     <row r="7" spans="1:12" s="61" customFormat="1" ht="15" customHeight="1">
@@ -5921,16 +5918,16 @@
       <c r="F7" s="85"/>
       <c r="G7" s="85"/>
       <c r="H7" s="85"/>
-      <c r="I7" s="172"/>
-      <c r="J7" s="172"/>
-      <c r="K7" s="172"/>
+      <c r="I7" s="193"/>
+      <c r="J7" s="193"/>
+      <c r="K7" s="193"/>
       <c r="L7" s="73"/>
     </row>
     <row r="8" spans="1:12" s="61" customFormat="1" ht="15" customHeight="1">
-      <c r="A8" s="180"/>
-      <c r="B8" s="180"/>
-      <c r="C8" s="180"/>
-      <c r="D8" s="180"/>
+      <c r="A8" s="194"/>
+      <c r="B8" s="194"/>
+      <c r="C8" s="194"/>
+      <c r="D8" s="194"/>
       <c r="E8" s="72"/>
       <c r="F8" s="72"/>
       <c r="G8" s="72"/>
@@ -5941,76 +5938,76 @@
       <c r="L8" s="73"/>
     </row>
     <row r="9" spans="1:12" s="63" customFormat="1" ht="12" customHeight="1">
-      <c r="A9" s="205" t="s">
+      <c r="A9" s="197" t="s">
         <v>71</v>
       </c>
-      <c r="B9" s="207" t="s">
+      <c r="B9" s="199" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="205" t="s">
+      <c r="C9" s="197" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="211" t="s">
+      <c r="D9" s="203" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="212"/>
-      <c r="F9" s="212"/>
-      <c r="G9" s="213"/>
-      <c r="H9" s="209" t="s">
+      <c r="E9" s="204"/>
+      <c r="F9" s="204"/>
+      <c r="G9" s="205"/>
+      <c r="H9" s="201" t="s">
         <v>75</v>
       </c>
-      <c r="I9" s="210" t="s">
+      <c r="I9" s="202" t="s">
         <v>76</v>
       </c>
-      <c r="J9" s="210" t="s">
+      <c r="J9" s="202" t="s">
         <v>77</v>
       </c>
-      <c r="K9" s="210" t="s">
+      <c r="K9" s="202" t="s">
         <v>78</v>
       </c>
       <c r="L9" s="87"/>
     </row>
     <row r="10" spans="1:12" s="61" customFormat="1" ht="12" customHeight="1">
-      <c r="A10" s="206"/>
-      <c r="B10" s="208"/>
-      <c r="C10" s="206"/>
-      <c r="D10" s="214"/>
-      <c r="E10" s="215"/>
-      <c r="F10" s="215"/>
-      <c r="G10" s="216"/>
-      <c r="H10" s="205"/>
-      <c r="I10" s="205"/>
-      <c r="J10" s="205"/>
-      <c r="K10" s="205"/>
+      <c r="A10" s="198"/>
+      <c r="B10" s="200"/>
+      <c r="C10" s="198"/>
+      <c r="D10" s="206"/>
+      <c r="E10" s="207"/>
+      <c r="F10" s="207"/>
+      <c r="G10" s="208"/>
+      <c r="H10" s="197"/>
+      <c r="I10" s="197"/>
+      <c r="J10" s="197"/>
+      <c r="K10" s="197"/>
       <c r="L10" s="73"/>
     </row>
     <row r="11" spans="1:12" s="64" customFormat="1" ht="15">
-      <c r="A11" s="181"/>
-      <c r="B11" s="181"/>
-      <c r="C11" s="181"/>
-      <c r="D11" s="181"/>
-      <c r="E11" s="181"/>
-      <c r="F11" s="181"/>
-      <c r="G11" s="181"/>
-      <c r="H11" s="181"/>
-      <c r="I11" s="181"/>
-      <c r="J11" s="181"/>
-      <c r="K11" s="182"/>
+      <c r="A11" s="195"/>
+      <c r="B11" s="195"/>
+      <c r="C11" s="195"/>
+      <c r="D11" s="195"/>
+      <c r="E11" s="195"/>
+      <c r="F11" s="195"/>
+      <c r="G11" s="195"/>
+      <c r="H11" s="195"/>
+      <c r="I11" s="195"/>
+      <c r="J11" s="195"/>
+      <c r="K11" s="196"/>
     </row>
     <row r="12" spans="1:12" s="65" customFormat="1" ht="12.75">
-      <c r="A12" s="183" t="s">
+      <c r="A12" s="184" t="s">
         <v>534</v>
       </c>
-      <c r="B12" s="184"/>
-      <c r="C12" s="184"/>
-      <c r="D12" s="184"/>
-      <c r="E12" s="184"/>
-      <c r="F12" s="184"/>
-      <c r="G12" s="184"/>
-      <c r="H12" s="184"/>
-      <c r="I12" s="184"/>
-      <c r="J12" s="184"/>
-      <c r="K12" s="185"/>
+      <c r="B12" s="185"/>
+      <c r="C12" s="185"/>
+      <c r="D12" s="185"/>
+      <c r="E12" s="185"/>
+      <c r="F12" s="185"/>
+      <c r="G12" s="185"/>
+      <c r="H12" s="185"/>
+      <c r="I12" s="185"/>
+      <c r="J12" s="185"/>
+      <c r="K12" s="186"/>
     </row>
     <row r="13" spans="1:12" s="65" customFormat="1" ht="76.5" outlineLevel="1">
       <c r="A13" s="90" t="s">
@@ -6022,11 +6019,11 @@
       <c r="C13" s="92" t="s">
         <v>536</v>
       </c>
-      <c r="D13" s="194" t="s">
+      <c r="D13" s="175" t="s">
         <v>537</v>
       </c>
-      <c r="E13" s="187"/>
-      <c r="F13" s="187"/>
+      <c r="E13" s="176"/>
+      <c r="F13" s="176"/>
       <c r="G13" s="95"/>
       <c r="H13" s="94"/>
       <c r="I13" s="96"/>
@@ -6036,11 +6033,11 @@
       <c r="K13" s="92"/>
     </row>
     <row r="14" spans="1:12" s="65" customFormat="1" ht="12.75" outlineLevel="1">
-      <c r="A14" s="238" t="s">
+      <c r="A14" s="241" t="s">
         <v>538</v>
       </c>
-      <c r="B14" s="222"/>
-      <c r="C14" s="222"/>
+      <c r="B14" s="223"/>
+      <c r="C14" s="223"/>
       <c r="D14" s="88"/>
       <c r="E14" s="88"/>
       <c r="F14" s="88"/>
@@ -6060,11 +6057,11 @@
       <c r="C15" s="98" t="s">
         <v>540</v>
       </c>
-      <c r="D15" s="227" t="s">
+      <c r="D15" s="224" t="s">
         <v>541</v>
       </c>
-      <c r="E15" s="187"/>
-      <c r="F15" s="187"/>
+      <c r="E15" s="176"/>
+      <c r="F15" s="176"/>
       <c r="G15" s="95"/>
       <c r="H15" s="94"/>
       <c r="I15" s="93"/>
@@ -6074,11 +6071,11 @@
       <c r="K15" s="92"/>
     </row>
     <row r="16" spans="1:12" s="65" customFormat="1" ht="12.75" outlineLevel="1">
-      <c r="A16" s="238" t="s">
+      <c r="A16" s="241" t="s">
         <v>542</v>
       </c>
-      <c r="B16" s="222"/>
-      <c r="C16" s="222"/>
+      <c r="B16" s="223"/>
+      <c r="C16" s="223"/>
       <c r="D16" s="88"/>
       <c r="E16" s="88"/>
       <c r="F16" s="88"/>
@@ -6098,11 +6095,11 @@
       <c r="C17" s="92" t="s">
         <v>543</v>
       </c>
-      <c r="D17" s="227" t="s">
+      <c r="D17" s="224" t="s">
         <v>544</v>
       </c>
-      <c r="E17" s="228"/>
-      <c r="F17" s="228"/>
+      <c r="E17" s="225"/>
+      <c r="F17" s="225"/>
       <c r="G17" s="95"/>
       <c r="H17" s="94"/>
       <c r="I17" s="93"/>
@@ -6151,11 +6148,11 @@
     <row r="55" ht="12" customHeight="1"/>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="B1:D2"/>
-    <mergeCell ref="D9:G10"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="I5:K5"/>
     <mergeCell ref="A16:C16"/>
     <mergeCell ref="D17:F17"/>
     <mergeCell ref="I6:K6"/>
@@ -6170,12 +6167,12 @@
     <mergeCell ref="I9:I10"/>
     <mergeCell ref="J9:J10"/>
     <mergeCell ref="K9:K10"/>
+    <mergeCell ref="B1:D2"/>
+    <mergeCell ref="D9:G10"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="D15:F15"/>
     <mergeCell ref="B3:D3"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="I5:K5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -6269,10 +6266,10 @@
       <c r="F7" s="53" t="s">
         <v>68</v>
       </c>
-      <c r="G7" s="241" t="s">
+      <c r="G7" s="252" t="s">
         <v>550</v>
       </c>
-      <c r="H7" s="242"/>
+      <c r="H7" s="253"/>
     </row>
     <row r="8" spans="1:8" s="49" customFormat="1" ht="40.15" customHeight="1">
       <c r="A8" s="15"/>
@@ -6294,11 +6291,11 @@
         <f>COUNTIF(Auth!J10:J29, "Pending")</f>
         <v>0</v>
       </c>
-      <c r="G8" s="251">
+      <c r="G8" s="246">
         <f>Auth!D7</f>
         <v>26</v>
       </c>
-      <c r="H8" s="243"/>
+      <c r="H8" s="247"/>
     </row>
     <row r="9" spans="1:8" s="49" customFormat="1" ht="40.15" customHeight="1">
       <c r="A9" s="15"/>
@@ -6320,11 +6317,11 @@
         <f>COUNTIF(Home!J10:J29, "Pending")</f>
         <v>0</v>
       </c>
-      <c r="G9" s="252">
+      <c r="G9" s="248">
         <f>Home!D7</f>
         <v>17</v>
       </c>
-      <c r="H9" s="244"/>
+      <c r="H9" s="249"/>
     </row>
     <row r="10" spans="1:8" s="49" customFormat="1" ht="40.15" customHeight="1">
       <c r="A10" s="15"/>
@@ -6346,11 +6343,11 @@
         <f>COUNTIF(Favorite!J10:J29, "Pending")</f>
         <v>8</v>
       </c>
-      <c r="G10" s="253">
+      <c r="G10" s="254">
         <f>Favorite!D7</f>
         <v>8</v>
       </c>
-      <c r="H10" s="243"/>
+      <c r="H10" s="247"/>
     </row>
     <row r="11" spans="1:8" s="49" customFormat="1" ht="40.15" customHeight="1">
       <c r="A11" s="15"/>
@@ -6372,11 +6369,11 @@
         <f>COUNTIF(Booking!J10:J42, "Pending")</f>
         <v>23</v>
       </c>
-      <c r="G11" s="252">
+      <c r="G11" s="248">
         <f>Booking!D7</f>
         <v>23</v>
       </c>
-      <c r="H11" s="244"/>
+      <c r="H11" s="249"/>
     </row>
     <row r="12" spans="1:8" s="49" customFormat="1" ht="40.15" customHeight="1">
       <c r="A12" s="15"/>
@@ -6398,11 +6395,11 @@
         <f>COUNTIF('Cancel Booking'!J10:J29, "Pending")</f>
         <v>12</v>
       </c>
-      <c r="G12" s="251">
+      <c r="G12" s="246">
         <f>'Cancel Booking'!D7</f>
         <v>12</v>
       </c>
-      <c r="H12" s="243"/>
+      <c r="H12" s="247"/>
     </row>
     <row r="13" spans="1:8" s="49" customFormat="1" ht="40.15" customHeight="1">
       <c r="A13" s="15"/>
@@ -6424,11 +6421,11 @@
         <f>COUNTIF(Review!J10:J29, "Pending")</f>
         <v>10</v>
       </c>
-      <c r="G13" s="252">
+      <c r="G13" s="248">
         <f>Review!D7</f>
         <v>10</v>
       </c>
-      <c r="H13" s="244"/>
+      <c r="H13" s="249"/>
     </row>
     <row r="14" spans="1:8" s="49" customFormat="1" ht="40.15" customHeight="1">
       <c r="A14" s="15"/>
@@ -6450,11 +6447,11 @@
         <f>COUNTIF(Admin!J10:J29, "Pending")</f>
         <v>0</v>
       </c>
-      <c r="G14" s="251">
+      <c r="G14" s="246">
         <f>Admin!D7</f>
         <v>14</v>
       </c>
-      <c r="H14" s="243"/>
+      <c r="H14" s="247"/>
     </row>
     <row r="15" spans="1:8" ht="40.15" customHeight="1">
       <c r="A15" s="5"/>
@@ -6476,11 +6473,11 @@
         <f>COUNTIF(Venue!J10:J29, "Pending")</f>
         <v>6</v>
       </c>
-      <c r="G15" s="252">
+      <c r="G15" s="248">
         <f>Venue!D7</f>
         <v>6</v>
       </c>
-      <c r="H15" s="244"/>
+      <c r="H15" s="249"/>
     </row>
     <row r="16" spans="1:8" ht="40.15" customHeight="1">
       <c r="A16" s="5"/>
@@ -6500,11 +6497,11 @@
         <f>SUM(F8:F15)</f>
         <v>59</v>
       </c>
-      <c r="G16" s="254">
+      <c r="G16" s="250">
         <f>SUM(G8:H15)</f>
         <v>116</v>
       </c>
-      <c r="H16" s="245"/>
+      <c r="H16" s="251"/>
     </row>
     <row r="17" spans="1:9" ht="14.25">
       <c r="A17" s="5"/>
@@ -6654,11 +6651,11 @@
     </row>
     <row r="30" spans="1:9" ht="14.25">
       <c r="A30" s="15"/>
-      <c r="B30" s="246" t="s">
+      <c r="B30" s="242" t="s">
+        <v>44</v>
+      </c>
+      <c r="C30" s="16" t="s">
         <v>571</v>
-      </c>
-      <c r="C30" s="16" t="s">
-        <v>572</v>
       </c>
       <c r="D30" s="17">
         <v>12</v>
@@ -6670,18 +6667,18 @@
         <v>1</v>
       </c>
       <c r="G30" s="20" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H30" s="21" t="s">
-        <v>573</v>
-      </c>
-      <c r="I30" s="249"/>
+        <v>572</v>
+      </c>
+      <c r="I30" s="245"/>
     </row>
     <row r="31" spans="1:9" ht="13.5" customHeight="1">
       <c r="A31" s="15"/>
-      <c r="B31" s="247"/>
+      <c r="B31" s="243"/>
       <c r="C31" s="16" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="D31" s="22">
         <v>92</v>
@@ -6693,18 +6690,18 @@
         <v>0.96</v>
       </c>
       <c r="G31" s="25" t="s">
+        <v>574</v>
+      </c>
+      <c r="H31" s="26" t="s">
         <v>575</v>
       </c>
-      <c r="H31" s="26" t="s">
-        <v>576</v>
-      </c>
-      <c r="I31" s="249"/>
+      <c r="I31" s="245"/>
     </row>
     <row r="32" spans="1:9" ht="13.5" customHeight="1">
       <c r="A32" s="15"/>
-      <c r="B32" s="247"/>
+      <c r="B32" s="243"/>
       <c r="C32" s="16" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="D32" s="22">
         <v>137</v>
@@ -6716,18 +6713,18 @@
         <v>0.79</v>
       </c>
       <c r="G32" s="29" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H32" s="30" t="s">
-        <v>578</v>
-      </c>
-      <c r="I32" s="249"/>
+        <v>577</v>
+      </c>
+      <c r="I32" s="245"/>
     </row>
     <row r="33" spans="1:9" ht="12.75" customHeight="1">
       <c r="A33" s="15"/>
-      <c r="B33" s="247"/>
+      <c r="B33" s="243"/>
       <c r="C33" s="16" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="D33" s="22">
         <v>541</v>
@@ -6738,19 +6735,19 @@
       <c r="F33" s="32">
         <v>0.83</v>
       </c>
-      <c r="G33" s="250" t="s">
+      <c r="G33" s="170" t="s">
+        <v>583</v>
+      </c>
+      <c r="H33" s="33" t="s">
         <v>584</v>
       </c>
-      <c r="H33" s="33" t="s">
-        <v>585</v>
-      </c>
-      <c r="I33" s="249"/>
+      <c r="I33" s="245"/>
     </row>
     <row r="34" spans="1:9" ht="11.25" customHeight="1">
       <c r="A34" s="15"/>
-      <c r="B34" s="248"/>
+      <c r="B34" s="244"/>
       <c r="C34" s="16" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="D34" s="22">
         <v>167</v>
@@ -6762,12 +6759,12 @@
         <v>0.97</v>
       </c>
       <c r="G34" s="36" t="s">
+        <v>580</v>
+      </c>
+      <c r="H34" s="37" t="s">
         <v>581</v>
       </c>
-      <c r="H34" s="37" t="s">
-        <v>582</v>
-      </c>
-      <c r="I34" s="249"/>
+      <c r="I34" s="245"/>
     </row>
     <row r="35" spans="1:9" ht="14.25">
       <c r="A35" s="5"/>
@@ -6801,6 +6798,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="G11:H11"/>
     <mergeCell ref="B30:B34"/>
     <mergeCell ref="I30:I34"/>
     <mergeCell ref="G12:H12"/>
@@ -6808,11 +6810,6 @@
     <mergeCell ref="G14:H14"/>
     <mergeCell ref="G15:H15"/>
     <mergeCell ref="G16:H16"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="G11:H11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
@@ -6867,52 +6864,52 @@
       <c r="A3" s="70" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="170" t="s">
+      <c r="B3" s="209" t="s">
         <v>62</v>
       </c>
-      <c r="C3" s="170"/>
-      <c r="D3" s="171"/>
+      <c r="C3" s="209"/>
+      <c r="D3" s="210"/>
       <c r="E3" s="71"/>
       <c r="F3" s="71"/>
       <c r="G3" s="71"/>
       <c r="H3" s="71"/>
-      <c r="I3" s="172"/>
-      <c r="J3" s="172"/>
-      <c r="K3" s="172"/>
+      <c r="I3" s="193"/>
+      <c r="J3" s="193"/>
+      <c r="K3" s="193"/>
     </row>
     <row r="4" spans="1:11" ht="14.25">
       <c r="A4" s="74" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="173" t="s">
+      <c r="B4" s="211" t="s">
         <v>64</v>
       </c>
-      <c r="C4" s="174"/>
-      <c r="D4" s="175"/>
+      <c r="C4" s="212"/>
+      <c r="D4" s="213"/>
       <c r="E4" s="71"/>
       <c r="F4" s="71"/>
       <c r="G4" s="71"/>
       <c r="H4" s="71"/>
-      <c r="I4" s="172"/>
-      <c r="J4" s="172"/>
-      <c r="K4" s="172"/>
+      <c r="I4" s="193"/>
+      <c r="J4" s="193"/>
+      <c r="K4" s="193"/>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="74" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="176" t="s">
+      <c r="B5" s="214" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="177"/>
-      <c r="D5" s="178"/>
+      <c r="C5" s="215"/>
+      <c r="D5" s="216"/>
       <c r="E5" s="75"/>
       <c r="F5" s="75"/>
       <c r="G5" s="75"/>
       <c r="H5" s="75"/>
-      <c r="I5" s="179"/>
-      <c r="J5" s="179"/>
-      <c r="K5" s="179"/>
+      <c r="I5" s="217"/>
+      <c r="J5" s="217"/>
+      <c r="K5" s="217"/>
     </row>
     <row r="6" spans="1:11" ht="14.25">
       <c r="A6" s="77" t="s">
@@ -6931,9 +6928,9 @@
       <c r="F6" s="72"/>
       <c r="G6" s="72"/>
       <c r="H6" s="72"/>
-      <c r="I6" s="172"/>
-      <c r="J6" s="172"/>
-      <c r="K6" s="172"/>
+      <c r="I6" s="193"/>
+      <c r="J6" s="193"/>
+      <c r="K6" s="193"/>
     </row>
     <row r="7" spans="1:11" ht="14.25">
       <c r="A7" s="81" t="s">
@@ -6953,15 +6950,15 @@
       <c r="F7" s="85"/>
       <c r="G7" s="85"/>
       <c r="H7" s="85"/>
-      <c r="I7" s="172"/>
-      <c r="J7" s="172"/>
-      <c r="K7" s="172"/>
+      <c r="I7" s="193"/>
+      <c r="J7" s="193"/>
+      <c r="K7" s="193"/>
     </row>
     <row r="8" spans="1:11" ht="14.25">
-      <c r="A8" s="180"/>
-      <c r="B8" s="180"/>
-      <c r="C8" s="180"/>
-      <c r="D8" s="180"/>
+      <c r="A8" s="194"/>
+      <c r="B8" s="194"/>
+      <c r="C8" s="194"/>
+      <c r="D8" s="194"/>
       <c r="E8" s="72"/>
       <c r="F8" s="72"/>
       <c r="G8" s="72"/>
@@ -6971,74 +6968,74 @@
       <c r="K8" s="86"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="205" t="s">
+      <c r="A9" s="197" t="s">
         <v>71</v>
       </c>
-      <c r="B9" s="207" t="s">
+      <c r="B9" s="199" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="205" t="s">
+      <c r="C9" s="197" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="211" t="s">
+      <c r="D9" s="203" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="212"/>
-      <c r="F9" s="212"/>
-      <c r="G9" s="213"/>
-      <c r="H9" s="209" t="s">
+      <c r="E9" s="204"/>
+      <c r="F9" s="204"/>
+      <c r="G9" s="205"/>
+      <c r="H9" s="201" t="s">
         <v>75</v>
       </c>
-      <c r="I9" s="210" t="s">
+      <c r="I9" s="202" t="s">
         <v>76</v>
       </c>
-      <c r="J9" s="210" t="s">
+      <c r="J9" s="202" t="s">
         <v>77</v>
       </c>
-      <c r="K9" s="210" t="s">
+      <c r="K9" s="202" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="206"/>
-      <c r="B10" s="208"/>
-      <c r="C10" s="206"/>
-      <c r="D10" s="214"/>
-      <c r="E10" s="215"/>
-      <c r="F10" s="215"/>
-      <c r="G10" s="216"/>
-      <c r="H10" s="205"/>
-      <c r="I10" s="205"/>
-      <c r="J10" s="205"/>
-      <c r="K10" s="205"/>
+      <c r="A10" s="198"/>
+      <c r="B10" s="200"/>
+      <c r="C10" s="198"/>
+      <c r="D10" s="206"/>
+      <c r="E10" s="207"/>
+      <c r="F10" s="207"/>
+      <c r="G10" s="208"/>
+      <c r="H10" s="197"/>
+      <c r="I10" s="197"/>
+      <c r="J10" s="197"/>
+      <c r="K10" s="197"/>
     </row>
     <row r="11" spans="1:11" ht="15">
-      <c r="A11" s="181"/>
-      <c r="B11" s="181"/>
-      <c r="C11" s="181"/>
-      <c r="D11" s="181"/>
-      <c r="E11" s="181"/>
-      <c r="F11" s="181"/>
-      <c r="G11" s="181"/>
-      <c r="H11" s="181"/>
-      <c r="I11" s="181"/>
-      <c r="J11" s="181"/>
-      <c r="K11" s="182"/>
+      <c r="A11" s="195"/>
+      <c r="B11" s="195"/>
+      <c r="C11" s="195"/>
+      <c r="D11" s="195"/>
+      <c r="E11" s="195"/>
+      <c r="F11" s="195"/>
+      <c r="G11" s="195"/>
+      <c r="H11" s="195"/>
+      <c r="I11" s="195"/>
+      <c r="J11" s="195"/>
+      <c r="K11" s="196"/>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="183" t="s">
+      <c r="A12" s="184" t="s">
         <v>79</v>
       </c>
-      <c r="B12" s="184"/>
-      <c r="C12" s="184"/>
-      <c r="D12" s="184"/>
-      <c r="E12" s="184"/>
-      <c r="F12" s="184"/>
-      <c r="G12" s="184"/>
-      <c r="H12" s="184"/>
-      <c r="I12" s="184"/>
-      <c r="J12" s="184"/>
-      <c r="K12" s="185"/>
+      <c r="B12" s="185"/>
+      <c r="C12" s="185"/>
+      <c r="D12" s="185"/>
+      <c r="E12" s="185"/>
+      <c r="F12" s="185"/>
+      <c r="G12" s="185"/>
+      <c r="H12" s="185"/>
+      <c r="I12" s="185"/>
+      <c r="J12" s="185"/>
+      <c r="K12" s="186"/>
     </row>
     <row r="13" spans="1:11" ht="63.75">
       <c r="A13" s="90" t="s">
@@ -7050,12 +7047,12 @@
       <c r="C13" s="92" t="s">
         <v>82</v>
       </c>
-      <c r="D13" s="186" t="s">
+      <c r="D13" s="187" t="s">
         <v>83</v>
       </c>
-      <c r="E13" s="187"/>
-      <c r="F13" s="187"/>
-      <c r="G13" s="188"/>
+      <c r="E13" s="176"/>
+      <c r="F13" s="176"/>
+      <c r="G13" s="177"/>
       <c r="H13" s="94"/>
       <c r="I13" s="96"/>
       <c r="J13" s="92" t="s">
@@ -7064,19 +7061,19 @@
       <c r="K13" s="92"/>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="183" t="s">
+      <c r="A14" s="184" t="s">
         <v>84</v>
       </c>
-      <c r="B14" s="184"/>
-      <c r="C14" s="184"/>
-      <c r="D14" s="184"/>
-      <c r="E14" s="184"/>
-      <c r="F14" s="184"/>
-      <c r="G14" s="184"/>
-      <c r="H14" s="184"/>
-      <c r="I14" s="184"/>
-      <c r="J14" s="184"/>
-      <c r="K14" s="185"/>
+      <c r="B14" s="185"/>
+      <c r="C14" s="185"/>
+      <c r="D14" s="185"/>
+      <c r="E14" s="185"/>
+      <c r="F14" s="185"/>
+      <c r="G14" s="185"/>
+      <c r="H14" s="185"/>
+      <c r="I14" s="185"/>
+      <c r="J14" s="185"/>
+      <c r="K14" s="186"/>
     </row>
     <row r="15" spans="1:11" ht="63.75">
       <c r="A15" s="102" t="s">
@@ -7088,12 +7085,12 @@
       <c r="C15" s="102" t="s">
         <v>87</v>
       </c>
-      <c r="D15" s="189" t="s">
+      <c r="D15" s="188" t="s">
         <v>88</v>
       </c>
-      <c r="E15" s="190"/>
-      <c r="F15" s="190"/>
-      <c r="G15" s="191"/>
+      <c r="E15" s="189"/>
+      <c r="F15" s="189"/>
+      <c r="G15" s="190"/>
       <c r="H15" s="103"/>
       <c r="I15" s="103"/>
       <c r="J15" s="104" t="s">
@@ -7102,11 +7099,11 @@
       <c r="K15" s="103"/>
     </row>
     <row r="16" spans="1:11">
-      <c r="A16" s="183" t="s">
+      <c r="A16" s="184" t="s">
         <v>89</v>
       </c>
-      <c r="B16" s="184"/>
-      <c r="C16" s="184"/>
+      <c r="B16" s="185"/>
+      <c r="C16" s="185"/>
       <c r="D16" s="88"/>
       <c r="E16" s="88"/>
       <c r="F16" s="88"/>
@@ -7126,12 +7123,12 @@
       <c r="C17" s="98" t="s">
         <v>92</v>
       </c>
-      <c r="D17" s="186" t="s">
+      <c r="D17" s="187" t="s">
         <v>93</v>
       </c>
-      <c r="E17" s="192"/>
-      <c r="F17" s="192"/>
-      <c r="G17" s="193"/>
+      <c r="E17" s="191"/>
+      <c r="F17" s="191"/>
+      <c r="G17" s="192"/>
       <c r="H17" s="94"/>
       <c r="I17" s="93"/>
       <c r="J17" s="92" t="s">
@@ -7140,11 +7137,11 @@
       <c r="K17" s="92"/>
     </row>
     <row r="18" spans="1:11">
-      <c r="A18" s="183" t="s">
+      <c r="A18" s="184" t="s">
         <v>94</v>
       </c>
-      <c r="B18" s="184"/>
-      <c r="C18" s="184"/>
+      <c r="B18" s="185"/>
+      <c r="C18" s="185"/>
       <c r="D18" s="88"/>
       <c r="E18" s="88"/>
       <c r="F18" s="88"/>
@@ -7164,12 +7161,12 @@
       <c r="C19" s="92" t="s">
         <v>97</v>
       </c>
-      <c r="D19" s="194" t="s">
+      <c r="D19" s="175" t="s">
         <v>98</v>
       </c>
-      <c r="E19" s="187"/>
-      <c r="F19" s="187"/>
-      <c r="G19" s="188"/>
+      <c r="E19" s="176"/>
+      <c r="F19" s="176"/>
+      <c r="G19" s="177"/>
       <c r="H19" s="94"/>
       <c r="I19" s="93"/>
       <c r="J19" s="92" t="s">
@@ -7178,11 +7175,11 @@
       <c r="K19" s="92"/>
     </row>
     <row r="20" spans="1:11">
-      <c r="A20" s="183" t="s">
+      <c r="A20" s="184" t="s">
         <v>99</v>
       </c>
-      <c r="B20" s="184"/>
-      <c r="C20" s="184"/>
+      <c r="B20" s="185"/>
+      <c r="C20" s="185"/>
       <c r="D20" s="88"/>
       <c r="E20" s="88"/>
       <c r="F20" s="88"/>
@@ -7202,12 +7199,12 @@
       <c r="C21" s="92" t="s">
         <v>102</v>
       </c>
-      <c r="D21" s="194" t="s">
+      <c r="D21" s="175" t="s">
         <v>103</v>
       </c>
-      <c r="E21" s="187"/>
-      <c r="F21" s="187"/>
-      <c r="G21" s="188"/>
+      <c r="E21" s="176"/>
+      <c r="F21" s="176"/>
+      <c r="G21" s="177"/>
       <c r="H21" s="94"/>
       <c r="I21" s="93"/>
       <c r="J21" s="92" t="s">
@@ -7225,12 +7222,12 @@
       <c r="C22" s="92" t="s">
         <v>106</v>
       </c>
-      <c r="D22" s="194" t="s">
+      <c r="D22" s="175" t="s">
         <v>107</v>
       </c>
-      <c r="E22" s="187"/>
-      <c r="F22" s="187"/>
-      <c r="G22" s="188"/>
+      <c r="E22" s="176"/>
+      <c r="F22" s="176"/>
+      <c r="G22" s="177"/>
       <c r="H22" s="92"/>
       <c r="I22" s="92"/>
       <c r="J22" s="92" t="s">
@@ -7239,19 +7236,19 @@
       <c r="K22" s="92"/>
     </row>
     <row r="23" spans="1:11">
-      <c r="A23" s="183" t="s">
+      <c r="A23" s="184" t="s">
         <v>108</v>
       </c>
-      <c r="B23" s="184"/>
-      <c r="C23" s="184"/>
-      <c r="D23" s="184"/>
-      <c r="E23" s="184"/>
-      <c r="F23" s="184"/>
-      <c r="G23" s="184"/>
-      <c r="H23" s="184"/>
-      <c r="I23" s="184"/>
-      <c r="J23" s="184"/>
-      <c r="K23" s="185"/>
+      <c r="B23" s="185"/>
+      <c r="C23" s="185"/>
+      <c r="D23" s="185"/>
+      <c r="E23" s="185"/>
+      <c r="F23" s="185"/>
+      <c r="G23" s="185"/>
+      <c r="H23" s="185"/>
+      <c r="I23" s="185"/>
+      <c r="J23" s="185"/>
+      <c r="K23" s="186"/>
     </row>
     <row r="24" spans="1:11" ht="66.95" customHeight="1">
       <c r="A24" s="90" t="s">
@@ -7263,12 +7260,12 @@
       <c r="C24" s="92" t="s">
         <v>111</v>
       </c>
-      <c r="D24" s="194" t="s">
+      <c r="D24" s="175" t="s">
         <v>112</v>
       </c>
-      <c r="E24" s="187"/>
-      <c r="F24" s="187"/>
-      <c r="G24" s="188"/>
+      <c r="E24" s="176"/>
+      <c r="F24" s="176"/>
+      <c r="G24" s="177"/>
       <c r="H24" s="92"/>
       <c r="I24" s="92"/>
       <c r="J24" s="92" t="s">
@@ -7286,12 +7283,12 @@
       <c r="C25" s="92" t="s">
         <v>115</v>
       </c>
-      <c r="D25" s="194" t="s">
+      <c r="D25" s="175" t="s">
         <v>116</v>
       </c>
-      <c r="E25" s="187"/>
-      <c r="F25" s="187"/>
-      <c r="G25" s="188"/>
+      <c r="E25" s="176"/>
+      <c r="F25" s="176"/>
+      <c r="G25" s="177"/>
       <c r="H25" s="92"/>
       <c r="I25" s="92"/>
       <c r="J25" s="92" t="s">
@@ -7300,19 +7297,19 @@
       <c r="K25" s="92"/>
     </row>
     <row r="26" spans="1:11">
-      <c r="A26" s="183" t="s">
+      <c r="A26" s="184" t="s">
         <v>117</v>
       </c>
-      <c r="B26" s="184"/>
-      <c r="C26" s="184"/>
-      <c r="D26" s="184"/>
-      <c r="E26" s="184"/>
-      <c r="F26" s="184"/>
-      <c r="G26" s="184"/>
-      <c r="H26" s="184"/>
-      <c r="I26" s="184"/>
-      <c r="J26" s="184"/>
-      <c r="K26" s="185"/>
+      <c r="B26" s="185"/>
+      <c r="C26" s="185"/>
+      <c r="D26" s="185"/>
+      <c r="E26" s="185"/>
+      <c r="F26" s="185"/>
+      <c r="G26" s="185"/>
+      <c r="H26" s="185"/>
+      <c r="I26" s="185"/>
+      <c r="J26" s="185"/>
+      <c r="K26" s="186"/>
     </row>
     <row r="27" spans="1:11" s="137" customFormat="1" ht="63.75">
       <c r="A27" s="90" t="s">
@@ -7324,12 +7321,12 @@
       <c r="C27" s="92" t="s">
         <v>120</v>
       </c>
-      <c r="D27" s="194" t="s">
+      <c r="D27" s="175" t="s">
         <v>121</v>
       </c>
-      <c r="E27" s="187"/>
-      <c r="F27" s="187"/>
-      <c r="G27" s="188"/>
+      <c r="E27" s="176"/>
+      <c r="F27" s="176"/>
+      <c r="G27" s="177"/>
       <c r="H27" s="92"/>
       <c r="I27" s="92"/>
       <c r="J27" s="92" t="s">
@@ -7347,12 +7344,12 @@
       <c r="C28" s="92" t="s">
         <v>124</v>
       </c>
-      <c r="D28" s="194" t="s">
+      <c r="D28" s="175" t="s">
         <v>125</v>
       </c>
-      <c r="E28" s="187"/>
-      <c r="F28" s="187"/>
-      <c r="G28" s="188"/>
+      <c r="E28" s="176"/>
+      <c r="F28" s="176"/>
+      <c r="G28" s="177"/>
       <c r="H28" s="92"/>
       <c r="I28" s="92"/>
       <c r="J28" s="92" t="s">
@@ -7370,12 +7367,12 @@
       <c r="C29" s="92" t="s">
         <v>128</v>
       </c>
-      <c r="D29" s="194" t="s">
+      <c r="D29" s="175" t="s">
         <v>129</v>
       </c>
-      <c r="E29" s="187"/>
-      <c r="F29" s="187"/>
-      <c r="G29" s="188"/>
+      <c r="E29" s="176"/>
+      <c r="F29" s="176"/>
+      <c r="G29" s="177"/>
       <c r="H29" s="139"/>
       <c r="I29" s="139"/>
       <c r="J29" s="92" t="s">
@@ -7384,19 +7381,19 @@
       <c r="K29" s="139"/>
     </row>
     <row r="30" spans="1:11">
-      <c r="A30" s="195" t="s">
+      <c r="A30" s="178" t="s">
         <v>130</v>
       </c>
-      <c r="B30" s="196"/>
-      <c r="C30" s="196"/>
-      <c r="D30" s="196"/>
-      <c r="E30" s="196"/>
-      <c r="F30" s="196"/>
-      <c r="G30" s="196"/>
-      <c r="H30" s="196"/>
-      <c r="I30" s="196"/>
-      <c r="J30" s="196"/>
-      <c r="K30" s="197"/>
+      <c r="B30" s="179"/>
+      <c r="C30" s="179"/>
+      <c r="D30" s="179"/>
+      <c r="E30" s="179"/>
+      <c r="F30" s="179"/>
+      <c r="G30" s="179"/>
+      <c r="H30" s="179"/>
+      <c r="I30" s="179"/>
+      <c r="J30" s="179"/>
+      <c r="K30" s="180"/>
     </row>
     <row r="31" spans="1:11" ht="102">
       <c r="A31" s="90" t="s">
@@ -7408,12 +7405,12 @@
       <c r="C31" s="92" t="s">
         <v>132</v>
       </c>
-      <c r="D31" s="198" t="s">
+      <c r="D31" s="173" t="s">
         <v>133</v>
       </c>
-      <c r="E31" s="199"/>
-      <c r="F31" s="199"/>
-      <c r="G31" s="199"/>
+      <c r="E31" s="174"/>
+      <c r="F31" s="174"/>
+      <c r="G31" s="174"/>
       <c r="H31" s="92"/>
       <c r="I31" s="125"/>
       <c r="J31" s="92" t="s">
@@ -7431,12 +7428,12 @@
       <c r="C32" s="141" t="s">
         <v>135</v>
       </c>
-      <c r="D32" s="200" t="s">
+      <c r="D32" s="181" t="s">
         <v>136</v>
       </c>
-      <c r="E32" s="201"/>
-      <c r="F32" s="201"/>
-      <c r="G32" s="202"/>
+      <c r="E32" s="182"/>
+      <c r="F32" s="182"/>
+      <c r="G32" s="183"/>
       <c r="H32" s="141"/>
       <c r="I32" s="141"/>
       <c r="J32" s="140" t="s">
@@ -7454,12 +7451,12 @@
       <c r="C33" s="92" t="s">
         <v>138</v>
       </c>
-      <c r="D33" s="198" t="s">
+      <c r="D33" s="173" t="s">
         <v>139</v>
       </c>
-      <c r="E33" s="199"/>
-      <c r="F33" s="199"/>
-      <c r="G33" s="199"/>
+      <c r="E33" s="174"/>
+      <c r="F33" s="174"/>
+      <c r="G33" s="174"/>
       <c r="H33" s="92"/>
       <c r="I33" s="125"/>
       <c r="J33" s="92" t="s">
@@ -7477,12 +7474,12 @@
       <c r="C34" s="92" t="s">
         <v>141</v>
       </c>
-      <c r="D34" s="198" t="s">
+      <c r="D34" s="173" t="s">
         <v>142</v>
       </c>
-      <c r="E34" s="199"/>
-      <c r="F34" s="199"/>
-      <c r="G34" s="199"/>
+      <c r="E34" s="174"/>
+      <c r="F34" s="174"/>
+      <c r="G34" s="174"/>
       <c r="H34" s="92"/>
       <c r="I34" s="125"/>
       <c r="J34" s="92" t="s">
@@ -7500,12 +7497,12 @@
       <c r="C35" s="92" t="s">
         <v>144</v>
       </c>
-      <c r="D35" s="198" t="s">
+      <c r="D35" s="173" t="s">
         <v>145</v>
       </c>
-      <c r="E35" s="199"/>
-      <c r="F35" s="199"/>
-      <c r="G35" s="199"/>
+      <c r="E35" s="174"/>
+      <c r="F35" s="174"/>
+      <c r="G35" s="174"/>
       <c r="H35" s="92"/>
       <c r="I35" s="125"/>
       <c r="J35" s="92" t="s">
@@ -7523,12 +7520,12 @@
       <c r="C36" s="92" t="s">
         <v>147</v>
       </c>
-      <c r="D36" s="198" t="s">
+      <c r="D36" s="173" t="s">
         <v>148</v>
       </c>
-      <c r="E36" s="199"/>
-      <c r="F36" s="199"/>
-      <c r="G36" s="199"/>
+      <c r="E36" s="174"/>
+      <c r="F36" s="174"/>
+      <c r="G36" s="174"/>
       <c r="H36" s="92"/>
       <c r="I36" s="125"/>
       <c r="J36" s="92" t="s">
@@ -7546,12 +7543,12 @@
       <c r="C37" s="98" t="s">
         <v>150</v>
       </c>
-      <c r="D37" s="203" t="s">
+      <c r="D37" s="171" t="s">
         <v>151</v>
       </c>
-      <c r="E37" s="204"/>
-      <c r="F37" s="204"/>
-      <c r="G37" s="204"/>
+      <c r="E37" s="172"/>
+      <c r="F37" s="172"/>
+      <c r="G37" s="172"/>
       <c r="H37" s="98"/>
       <c r="I37" s="142"/>
       <c r="J37" s="98" t="s">
@@ -7569,12 +7566,12 @@
       <c r="C38" s="98" t="s">
         <v>153</v>
       </c>
-      <c r="D38" s="203" t="s">
+      <c r="D38" s="171" t="s">
         <v>154</v>
       </c>
-      <c r="E38" s="204"/>
-      <c r="F38" s="204"/>
-      <c r="G38" s="204"/>
+      <c r="E38" s="172"/>
+      <c r="F38" s="172"/>
+      <c r="G38" s="172"/>
       <c r="H38" s="98"/>
       <c r="I38" s="142"/>
       <c r="J38" s="98" t="s">
@@ -7592,12 +7589,12 @@
       <c r="C39" s="92" t="s">
         <v>156</v>
       </c>
-      <c r="D39" s="198" t="s">
+      <c r="D39" s="173" t="s">
         <v>157</v>
       </c>
-      <c r="E39" s="199"/>
-      <c r="F39" s="199"/>
-      <c r="G39" s="199"/>
+      <c r="E39" s="174"/>
+      <c r="F39" s="174"/>
+      <c r="G39" s="174"/>
       <c r="H39" s="92"/>
       <c r="I39" s="125"/>
       <c r="J39" s="92" t="s">
@@ -7615,12 +7612,12 @@
       <c r="C40" s="92" t="s">
         <v>159</v>
       </c>
-      <c r="D40" s="198" t="s">
+      <c r="D40" s="173" t="s">
         <v>160</v>
       </c>
-      <c r="E40" s="199"/>
-      <c r="F40" s="199"/>
-      <c r="G40" s="199"/>
+      <c r="E40" s="174"/>
+      <c r="F40" s="174"/>
+      <c r="G40" s="174"/>
       <c r="H40" s="92"/>
       <c r="I40" s="125"/>
       <c r="J40" s="92" t="s">
@@ -7638,12 +7635,12 @@
       <c r="C41" s="92" t="s">
         <v>159</v>
       </c>
-      <c r="D41" s="198" t="s">
+      <c r="D41" s="173" t="s">
         <v>160</v>
       </c>
-      <c r="E41" s="199"/>
-      <c r="F41" s="199"/>
-      <c r="G41" s="199"/>
+      <c r="E41" s="174"/>
+      <c r="F41" s="174"/>
+      <c r="G41" s="174"/>
       <c r="H41" s="92"/>
       <c r="I41" s="125"/>
       <c r="J41" s="92" t="s">
@@ -7661,12 +7658,12 @@
       <c r="C42" s="92" t="s">
         <v>163</v>
       </c>
-      <c r="D42" s="198" t="s">
+      <c r="D42" s="173" t="s">
         <v>164</v>
       </c>
-      <c r="E42" s="199"/>
-      <c r="F42" s="199"/>
-      <c r="G42" s="199"/>
+      <c r="E42" s="174"/>
+      <c r="F42" s="174"/>
+      <c r="G42" s="174"/>
       <c r="H42" s="92"/>
       <c r="I42" s="125"/>
       <c r="J42" s="92" t="s">
@@ -7676,36 +7673,12 @@
     </row>
   </sheetData>
   <mergeCells count="49">
-    <mergeCell ref="D38:G38"/>
-    <mergeCell ref="D39:G39"/>
-    <mergeCell ref="D40:G40"/>
-    <mergeCell ref="D41:G41"/>
-    <mergeCell ref="D42:G42"/>
-    <mergeCell ref="D33:G33"/>
-    <mergeCell ref="D34:G34"/>
-    <mergeCell ref="D35:G35"/>
-    <mergeCell ref="D36:G36"/>
-    <mergeCell ref="D37:G37"/>
-    <mergeCell ref="D28:G28"/>
-    <mergeCell ref="D29:G29"/>
-    <mergeCell ref="A30:K30"/>
-    <mergeCell ref="D31:G31"/>
-    <mergeCell ref="D32:G32"/>
-    <mergeCell ref="A23:K23"/>
-    <mergeCell ref="D24:G24"/>
-    <mergeCell ref="D25:G25"/>
-    <mergeCell ref="A26:K26"/>
-    <mergeCell ref="D27:G27"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="D19:G19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="D21:G21"/>
-    <mergeCell ref="D22:G22"/>
-    <mergeCell ref="D13:G13"/>
-    <mergeCell ref="A14:K14"/>
-    <mergeCell ref="D15:G15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="D17:G17"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="I5:K5"/>
     <mergeCell ref="I6:K6"/>
     <mergeCell ref="I7:K7"/>
     <mergeCell ref="A8:D8"/>
@@ -7719,12 +7692,36 @@
     <mergeCell ref="J9:J10"/>
     <mergeCell ref="K9:K10"/>
     <mergeCell ref="D9:G10"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="D13:G13"/>
+    <mergeCell ref="A14:K14"/>
+    <mergeCell ref="D15:G15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="D17:G17"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="D19:G19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="D21:G21"/>
+    <mergeCell ref="D22:G22"/>
+    <mergeCell ref="A23:K23"/>
+    <mergeCell ref="D24:G24"/>
+    <mergeCell ref="D25:G25"/>
+    <mergeCell ref="A26:K26"/>
+    <mergeCell ref="D27:G27"/>
+    <mergeCell ref="D28:G28"/>
+    <mergeCell ref="D29:G29"/>
+    <mergeCell ref="A30:K30"/>
+    <mergeCell ref="D31:G31"/>
+    <mergeCell ref="D32:G32"/>
+    <mergeCell ref="D33:G33"/>
+    <mergeCell ref="D34:G34"/>
+    <mergeCell ref="D35:G35"/>
+    <mergeCell ref="D36:G36"/>
+    <mergeCell ref="D37:G37"/>
+    <mergeCell ref="D38:G38"/>
+    <mergeCell ref="D39:G39"/>
+    <mergeCell ref="D40:G40"/>
+    <mergeCell ref="D41:G41"/>
+    <mergeCell ref="D42:G42"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7760,31 +7757,31 @@
       <c r="A3" s="70" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="170" t="s">
+      <c r="B3" s="209" t="s">
         <v>62</v>
       </c>
-      <c r="C3" s="170"/>
-      <c r="D3" s="171"/>
+      <c r="C3" s="209"/>
+      <c r="D3" s="210"/>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="74" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="173" t="s">
+      <c r="B4" s="211" t="s">
         <v>166</v>
       </c>
-      <c r="C4" s="174"/>
-      <c r="D4" s="175"/>
+      <c r="C4" s="212"/>
+      <c r="D4" s="213"/>
     </row>
     <row r="5" spans="1:11" ht="25.5">
       <c r="A5" s="74" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="176" t="s">
+      <c r="B5" s="214" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="177"/>
-      <c r="D5" s="178"/>
+      <c r="C5" s="215"/>
+      <c r="D5" s="216"/>
     </row>
     <row r="6" spans="1:11" ht="14.25">
       <c r="A6" s="77" t="s">
@@ -7815,74 +7812,74 @@
       </c>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="205" t="s">
+      <c r="A9" s="197" t="s">
         <v>71</v>
       </c>
-      <c r="B9" s="207" t="s">
+      <c r="B9" s="199" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="205" t="s">
+      <c r="C9" s="197" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="211" t="s">
+      <c r="D9" s="203" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="212"/>
-      <c r="F9" s="212"/>
-      <c r="G9" s="213"/>
-      <c r="H9" s="209" t="s">
+      <c r="E9" s="204"/>
+      <c r="F9" s="204"/>
+      <c r="G9" s="205"/>
+      <c r="H9" s="201" t="s">
         <v>75</v>
       </c>
-      <c r="I9" s="210" t="s">
+      <c r="I9" s="202" t="s">
         <v>76</v>
       </c>
-      <c r="J9" s="210" t="s">
+      <c r="J9" s="202" t="s">
         <v>77</v>
       </c>
-      <c r="K9" s="210" t="s">
+      <c r="K9" s="202" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="206"/>
-      <c r="B10" s="208"/>
-      <c r="C10" s="206"/>
-      <c r="D10" s="214"/>
-      <c r="E10" s="215"/>
-      <c r="F10" s="215"/>
-      <c r="G10" s="216"/>
-      <c r="H10" s="205"/>
-      <c r="I10" s="205"/>
-      <c r="J10" s="205"/>
-      <c r="K10" s="205"/>
+      <c r="A10" s="198"/>
+      <c r="B10" s="200"/>
+      <c r="C10" s="198"/>
+      <c r="D10" s="206"/>
+      <c r="E10" s="207"/>
+      <c r="F10" s="207"/>
+      <c r="G10" s="208"/>
+      <c r="H10" s="197"/>
+      <c r="I10" s="197"/>
+      <c r="J10" s="197"/>
+      <c r="K10" s="197"/>
     </row>
     <row r="11" spans="1:11" ht="15">
-      <c r="A11" s="181"/>
-      <c r="B11" s="181"/>
-      <c r="C11" s="181"/>
-      <c r="D11" s="181"/>
-      <c r="E11" s="181"/>
-      <c r="F11" s="181"/>
-      <c r="G11" s="181"/>
-      <c r="H11" s="181"/>
-      <c r="I11" s="181"/>
-      <c r="J11" s="181"/>
-      <c r="K11" s="182"/>
+      <c r="A11" s="195"/>
+      <c r="B11" s="195"/>
+      <c r="C11" s="195"/>
+      <c r="D11" s="195"/>
+      <c r="E11" s="195"/>
+      <c r="F11" s="195"/>
+      <c r="G11" s="195"/>
+      <c r="H11" s="195"/>
+      <c r="I11" s="195"/>
+      <c r="J11" s="195"/>
+      <c r="K11" s="196"/>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="183" t="s">
+      <c r="A12" s="184" t="s">
         <v>167</v>
       </c>
-      <c r="B12" s="184"/>
-      <c r="C12" s="184"/>
-      <c r="D12" s="184"/>
-      <c r="E12" s="184"/>
-      <c r="F12" s="184"/>
-      <c r="G12" s="184"/>
-      <c r="H12" s="184"/>
-      <c r="I12" s="184"/>
-      <c r="J12" s="184"/>
-      <c r="K12" s="185"/>
+      <c r="B12" s="185"/>
+      <c r="C12" s="185"/>
+      <c r="D12" s="185"/>
+      <c r="E12" s="185"/>
+      <c r="F12" s="185"/>
+      <c r="G12" s="185"/>
+      <c r="H12" s="185"/>
+      <c r="I12" s="185"/>
+      <c r="J12" s="185"/>
+      <c r="K12" s="186"/>
     </row>
     <row r="13" spans="1:11" ht="90" customHeight="1">
       <c r="A13" s="90" t="s">
@@ -7894,12 +7891,12 @@
       <c r="C13" s="92" t="s">
         <v>169</v>
       </c>
-      <c r="D13" s="186" t="s">
+      <c r="D13" s="187" t="s">
         <v>170</v>
       </c>
-      <c r="E13" s="187"/>
-      <c r="F13" s="187"/>
-      <c r="G13" s="188"/>
+      <c r="E13" s="176"/>
+      <c r="F13" s="176"/>
+      <c r="G13" s="177"/>
       <c r="H13" s="94"/>
       <c r="I13" s="96"/>
       <c r="J13" s="92" t="s">
@@ -7917,12 +7914,12 @@
       <c r="C14" s="92" t="s">
         <v>172</v>
       </c>
-      <c r="D14" s="186" t="s">
+      <c r="D14" s="187" t="s">
         <v>173</v>
       </c>
-      <c r="E14" s="187"/>
-      <c r="F14" s="187"/>
-      <c r="G14" s="188"/>
+      <c r="E14" s="176"/>
+      <c r="F14" s="176"/>
+      <c r="G14" s="177"/>
       <c r="H14" s="94"/>
       <c r="I14" s="96"/>
       <c r="J14" s="92" t="s">
@@ -7940,12 +7937,12 @@
       <c r="C15" s="92" t="s">
         <v>175</v>
       </c>
-      <c r="D15" s="186" t="s">
+      <c r="D15" s="187" t="s">
         <v>176</v>
       </c>
-      <c r="E15" s="187"/>
-      <c r="F15" s="187"/>
-      <c r="G15" s="188"/>
+      <c r="E15" s="176"/>
+      <c r="F15" s="176"/>
+      <c r="G15" s="177"/>
       <c r="H15" s="94"/>
       <c r="I15" s="96"/>
       <c r="J15" s="92" t="s">
@@ -7963,12 +7960,12 @@
       <c r="C16" s="92" t="s">
         <v>178</v>
       </c>
-      <c r="D16" s="186" t="s">
+      <c r="D16" s="187" t="s">
         <v>179</v>
       </c>
-      <c r="E16" s="187"/>
-      <c r="F16" s="187"/>
-      <c r="G16" s="188"/>
+      <c r="E16" s="176"/>
+      <c r="F16" s="176"/>
+      <c r="G16" s="177"/>
       <c r="H16" s="94"/>
       <c r="I16" s="96"/>
       <c r="J16" s="92" t="s">
@@ -7986,12 +7983,12 @@
       <c r="C17" s="92" t="s">
         <v>181</v>
       </c>
-      <c r="D17" s="186" t="s">
+      <c r="D17" s="187" t="s">
         <v>182</v>
       </c>
-      <c r="E17" s="187"/>
-      <c r="F17" s="187"/>
-      <c r="G17" s="188"/>
+      <c r="E17" s="176"/>
+      <c r="F17" s="176"/>
+      <c r="G17" s="177"/>
       <c r="H17" s="94"/>
       <c r="I17" s="96"/>
       <c r="J17" s="92" t="s">
@@ -8009,12 +8006,12 @@
       <c r="C18" s="92" t="s">
         <v>184</v>
       </c>
-      <c r="D18" s="186" t="s">
+      <c r="D18" s="187" t="s">
         <v>185</v>
       </c>
-      <c r="E18" s="187"/>
-      <c r="F18" s="187"/>
-      <c r="G18" s="188"/>
+      <c r="E18" s="176"/>
+      <c r="F18" s="176"/>
+      <c r="G18" s="177"/>
       <c r="H18" s="94"/>
       <c r="I18" s="96"/>
       <c r="J18" s="92" t="s">
@@ -8032,12 +8029,12 @@
       <c r="C19" s="92" t="s">
         <v>187</v>
       </c>
-      <c r="D19" s="186" t="s">
+      <c r="D19" s="187" t="s">
         <v>188</v>
       </c>
-      <c r="E19" s="187"/>
-      <c r="F19" s="187"/>
-      <c r="G19" s="188"/>
+      <c r="E19" s="176"/>
+      <c r="F19" s="176"/>
+      <c r="G19" s="177"/>
       <c r="H19" s="94"/>
       <c r="I19" s="96"/>
       <c r="J19" s="92" t="s">
@@ -8046,19 +8043,19 @@
       <c r="K19" s="92"/>
     </row>
     <row r="20" spans="1:11">
-      <c r="A20" s="183" t="s">
+      <c r="A20" s="184" t="s">
         <v>189</v>
       </c>
-      <c r="B20" s="184"/>
-      <c r="C20" s="184"/>
-      <c r="D20" s="184"/>
-      <c r="E20" s="184"/>
-      <c r="F20" s="184"/>
-      <c r="G20" s="184"/>
-      <c r="H20" s="184"/>
-      <c r="I20" s="184"/>
-      <c r="J20" s="184"/>
-      <c r="K20" s="185"/>
+      <c r="B20" s="185"/>
+      <c r="C20" s="185"/>
+      <c r="D20" s="185"/>
+      <c r="E20" s="185"/>
+      <c r="F20" s="185"/>
+      <c r="G20" s="185"/>
+      <c r="H20" s="185"/>
+      <c r="I20" s="185"/>
+      <c r="J20" s="185"/>
+      <c r="K20" s="186"/>
     </row>
     <row r="21" spans="1:11" ht="41.1" customHeight="1">
       <c r="A21" s="90" t="s">
@@ -8070,12 +8067,12 @@
       <c r="C21" s="92" t="s">
         <v>191</v>
       </c>
-      <c r="D21" s="186" t="s">
+      <c r="D21" s="187" t="s">
         <v>192</v>
       </c>
-      <c r="E21" s="187"/>
-      <c r="F21" s="187"/>
-      <c r="G21" s="188"/>
+      <c r="E21" s="176"/>
+      <c r="F21" s="176"/>
+      <c r="G21" s="177"/>
       <c r="H21" s="94"/>
       <c r="I21" s="96"/>
       <c r="J21" s="92" t="s">
@@ -8093,12 +8090,12 @@
       <c r="C22" s="92" t="s">
         <v>194</v>
       </c>
-      <c r="D22" s="186" t="s">
+      <c r="D22" s="187" t="s">
         <v>195</v>
       </c>
-      <c r="E22" s="187"/>
-      <c r="F22" s="187"/>
-      <c r="G22" s="188"/>
+      <c r="E22" s="176"/>
+      <c r="F22" s="176"/>
+      <c r="G22" s="177"/>
       <c r="H22" s="94"/>
       <c r="I22" s="96"/>
       <c r="J22" s="92" t="s">
@@ -8116,12 +8113,12 @@
       <c r="C23" s="92" t="s">
         <v>197</v>
       </c>
-      <c r="D23" s="186" t="s">
+      <c r="D23" s="187" t="s">
         <v>198</v>
       </c>
-      <c r="E23" s="187"/>
-      <c r="F23" s="187"/>
-      <c r="G23" s="188"/>
+      <c r="E23" s="176"/>
+      <c r="F23" s="176"/>
+      <c r="G23" s="177"/>
       <c r="H23" s="94"/>
       <c r="I23" s="96"/>
       <c r="J23" s="92" t="s">
@@ -8130,26 +8127,26 @@
       <c r="K23" s="92"/>
     </row>
     <row r="24" spans="1:11">
-      <c r="A24" s="217"/>
-      <c r="B24" s="217"/>
-      <c r="C24" s="217"/>
-      <c r="D24" s="217"/>
-      <c r="E24" s="217"/>
-      <c r="F24" s="217"/>
-      <c r="G24" s="217"/>
-      <c r="H24" s="217"/>
-      <c r="I24" s="217"/>
-      <c r="J24" s="217"/>
-      <c r="K24" s="217"/>
+      <c r="A24" s="218"/>
+      <c r="B24" s="218"/>
+      <c r="C24" s="218"/>
+      <c r="D24" s="218"/>
+      <c r="E24" s="218"/>
+      <c r="F24" s="218"/>
+      <c r="G24" s="218"/>
+      <c r="H24" s="218"/>
+      <c r="I24" s="218"/>
+      <c r="J24" s="218"/>
+      <c r="K24" s="218"/>
     </row>
     <row r="25" spans="1:11" ht="35.1" customHeight="1">
       <c r="A25" s="133"/>
       <c r="B25" s="134"/>
       <c r="C25" s="135"/>
-      <c r="D25" s="218"/>
-      <c r="E25" s="219"/>
-      <c r="F25" s="219"/>
-      <c r="G25" s="219"/>
+      <c r="D25" s="219"/>
+      <c r="E25" s="220"/>
+      <c r="F25" s="220"/>
+      <c r="G25" s="220"/>
       <c r="H25" s="135"/>
       <c r="I25" s="136"/>
       <c r="J25" s="135"/>
@@ -8159,10 +8156,10 @@
       <c r="A26" s="133"/>
       <c r="B26" s="134"/>
       <c r="C26" s="135"/>
-      <c r="D26" s="218"/>
-      <c r="E26" s="219"/>
-      <c r="F26" s="219"/>
-      <c r="G26" s="219"/>
+      <c r="D26" s="219"/>
+      <c r="E26" s="220"/>
+      <c r="F26" s="220"/>
+      <c r="G26" s="220"/>
       <c r="H26" s="135"/>
       <c r="I26" s="136"/>
       <c r="J26" s="135"/>
@@ -8172,10 +8169,10 @@
       <c r="A27" s="133"/>
       <c r="B27" s="134"/>
       <c r="C27" s="135"/>
-      <c r="D27" s="218"/>
-      <c r="E27" s="219"/>
-      <c r="F27" s="219"/>
-      <c r="G27" s="219"/>
+      <c r="D27" s="219"/>
+      <c r="E27" s="220"/>
+      <c r="F27" s="220"/>
+      <c r="G27" s="220"/>
       <c r="H27" s="135"/>
       <c r="I27" s="136"/>
       <c r="J27" s="135"/>
@@ -8183,21 +8180,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="D23:G23"/>
-    <mergeCell ref="A24:K24"/>
-    <mergeCell ref="D25:G25"/>
-    <mergeCell ref="D26:G26"/>
-    <mergeCell ref="D27:G27"/>
-    <mergeCell ref="D18:G18"/>
-    <mergeCell ref="D19:G19"/>
-    <mergeCell ref="A20:K20"/>
-    <mergeCell ref="D21:G21"/>
-    <mergeCell ref="D22:G22"/>
-    <mergeCell ref="D13:G13"/>
-    <mergeCell ref="D14:G14"/>
-    <mergeCell ref="D15:G15"/>
-    <mergeCell ref="D16:G16"/>
-    <mergeCell ref="D17:G17"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B5:D5"/>
@@ -8211,6 +8193,21 @@
     <mergeCell ref="J9:J10"/>
     <mergeCell ref="K9:K10"/>
     <mergeCell ref="D9:G10"/>
+    <mergeCell ref="D13:G13"/>
+    <mergeCell ref="D14:G14"/>
+    <mergeCell ref="D15:G15"/>
+    <mergeCell ref="D16:G16"/>
+    <mergeCell ref="D17:G17"/>
+    <mergeCell ref="D18:G18"/>
+    <mergeCell ref="D19:G19"/>
+    <mergeCell ref="A20:K20"/>
+    <mergeCell ref="D21:G21"/>
+    <mergeCell ref="D22:G22"/>
+    <mergeCell ref="D23:G23"/>
+    <mergeCell ref="A24:K24"/>
+    <mergeCell ref="D25:G25"/>
+    <mergeCell ref="D26:G26"/>
+    <mergeCell ref="D27:G27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8247,31 +8244,31 @@
       <c r="A3" s="70" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="170" t="s">
+      <c r="B3" s="209" t="s">
         <v>62</v>
       </c>
-      <c r="C3" s="170"/>
-      <c r="D3" s="171"/>
+      <c r="C3" s="209"/>
+      <c r="D3" s="210"/>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="74" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="173" t="s">
+      <c r="B4" s="211" t="s">
         <v>200</v>
       </c>
-      <c r="C4" s="174"/>
-      <c r="D4" s="175"/>
+      <c r="C4" s="212"/>
+      <c r="D4" s="213"/>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="74" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="176" t="s">
+      <c r="B5" s="214" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="177"/>
-      <c r="D5" s="178"/>
+      <c r="C5" s="215"/>
+      <c r="D5" s="216"/>
     </row>
     <row r="6" spans="1:11" ht="14.25">
       <c r="A6" s="77" t="s">
@@ -8302,74 +8299,74 @@
       </c>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="205" t="s">
+      <c r="A9" s="197" t="s">
         <v>71</v>
       </c>
-      <c r="B9" s="207" t="s">
+      <c r="B9" s="199" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="205" t="s">
+      <c r="C9" s="197" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="211" t="s">
+      <c r="D9" s="203" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="212"/>
-      <c r="F9" s="212"/>
-      <c r="G9" s="213"/>
-      <c r="H9" s="209" t="s">
+      <c r="E9" s="204"/>
+      <c r="F9" s="204"/>
+      <c r="G9" s="205"/>
+      <c r="H9" s="201" t="s">
         <v>75</v>
       </c>
-      <c r="I9" s="210" t="s">
+      <c r="I9" s="202" t="s">
         <v>76</v>
       </c>
-      <c r="J9" s="210" t="s">
+      <c r="J9" s="202" t="s">
         <v>77</v>
       </c>
-      <c r="K9" s="210" t="s">
+      <c r="K9" s="202" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="206"/>
-      <c r="B10" s="208"/>
-      <c r="C10" s="206"/>
-      <c r="D10" s="214"/>
-      <c r="E10" s="215"/>
-      <c r="F10" s="215"/>
-      <c r="G10" s="216"/>
-      <c r="H10" s="205"/>
-      <c r="I10" s="205"/>
-      <c r="J10" s="205"/>
-      <c r="K10" s="205"/>
+      <c r="A10" s="198"/>
+      <c r="B10" s="200"/>
+      <c r="C10" s="198"/>
+      <c r="D10" s="206"/>
+      <c r="E10" s="207"/>
+      <c r="F10" s="207"/>
+      <c r="G10" s="208"/>
+      <c r="H10" s="197"/>
+      <c r="I10" s="197"/>
+      <c r="J10" s="197"/>
+      <c r="K10" s="197"/>
     </row>
     <row r="11" spans="1:11" ht="15">
-      <c r="A11" s="181"/>
-      <c r="B11" s="181"/>
-      <c r="C11" s="181"/>
-      <c r="D11" s="181"/>
-      <c r="E11" s="181"/>
-      <c r="F11" s="181"/>
-      <c r="G11" s="181"/>
-      <c r="H11" s="181"/>
-      <c r="I11" s="181"/>
-      <c r="J11" s="181"/>
-      <c r="K11" s="182"/>
+      <c r="A11" s="195"/>
+      <c r="B11" s="195"/>
+      <c r="C11" s="195"/>
+      <c r="D11" s="195"/>
+      <c r="E11" s="195"/>
+      <c r="F11" s="195"/>
+      <c r="G11" s="195"/>
+      <c r="H11" s="195"/>
+      <c r="I11" s="195"/>
+      <c r="J11" s="195"/>
+      <c r="K11" s="196"/>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="183" t="s">
+      <c r="A12" s="184" t="s">
         <v>201</v>
       </c>
-      <c r="B12" s="184"/>
-      <c r="C12" s="184"/>
-      <c r="D12" s="184"/>
-      <c r="E12" s="184"/>
-      <c r="F12" s="184"/>
-      <c r="G12" s="184"/>
-      <c r="H12" s="184"/>
-      <c r="I12" s="184"/>
-      <c r="J12" s="184"/>
-      <c r="K12" s="185"/>
+      <c r="B12" s="185"/>
+      <c r="C12" s="185"/>
+      <c r="D12" s="185"/>
+      <c r="E12" s="185"/>
+      <c r="F12" s="185"/>
+      <c r="G12" s="185"/>
+      <c r="H12" s="185"/>
+      <c r="I12" s="185"/>
+      <c r="J12" s="185"/>
+      <c r="K12" s="186"/>
     </row>
     <row r="13" spans="1:11" ht="93" customHeight="1">
       <c r="A13" s="90" t="s">
@@ -8381,12 +8378,12 @@
       <c r="C13" s="92" t="s">
         <v>203</v>
       </c>
-      <c r="D13" s="186" t="s">
+      <c r="D13" s="187" t="s">
         <v>204</v>
       </c>
-      <c r="E13" s="187"/>
-      <c r="F13" s="187"/>
-      <c r="G13" s="188"/>
+      <c r="E13" s="176"/>
+      <c r="F13" s="176"/>
+      <c r="G13" s="177"/>
       <c r="H13" s="94"/>
       <c r="I13" s="96"/>
       <c r="J13" s="92" t="s">
@@ -8404,12 +8401,12 @@
       <c r="C14" s="92" t="s">
         <v>206</v>
       </c>
-      <c r="D14" s="186" t="s">
+      <c r="D14" s="187" t="s">
         <v>207</v>
       </c>
-      <c r="E14" s="187"/>
-      <c r="F14" s="187"/>
-      <c r="G14" s="188"/>
+      <c r="E14" s="176"/>
+      <c r="F14" s="176"/>
+      <c r="G14" s="177"/>
       <c r="H14" s="94"/>
       <c r="I14" s="96"/>
       <c r="J14" s="92" t="s">
@@ -8427,12 +8424,12 @@
       <c r="C15" s="92" t="s">
         <v>209</v>
       </c>
-      <c r="D15" s="186" t="s">
+      <c r="D15" s="187" t="s">
         <v>210</v>
       </c>
-      <c r="E15" s="187"/>
-      <c r="F15" s="187"/>
-      <c r="G15" s="188"/>
+      <c r="E15" s="176"/>
+      <c r="F15" s="176"/>
+      <c r="G15" s="177"/>
       <c r="H15" s="94"/>
       <c r="I15" s="96"/>
       <c r="J15" s="92" t="s">
@@ -8450,12 +8447,12 @@
       <c r="C16" s="92" t="s">
         <v>212</v>
       </c>
-      <c r="D16" s="186" t="s">
+      <c r="D16" s="187" t="s">
         <v>213</v>
       </c>
-      <c r="E16" s="187"/>
-      <c r="F16" s="187"/>
-      <c r="G16" s="188"/>
+      <c r="E16" s="176"/>
+      <c r="F16" s="176"/>
+      <c r="G16" s="177"/>
       <c r="H16" s="94"/>
       <c r="I16" s="96"/>
       <c r="J16" s="92" t="s">
@@ -8473,12 +8470,12 @@
       <c r="C17" s="92" t="s">
         <v>215</v>
       </c>
-      <c r="D17" s="186" t="s">
+      <c r="D17" s="187" t="s">
         <v>216</v>
       </c>
-      <c r="E17" s="187"/>
-      <c r="F17" s="187"/>
-      <c r="G17" s="188"/>
+      <c r="E17" s="176"/>
+      <c r="F17" s="176"/>
+      <c r="G17" s="177"/>
       <c r="H17" s="94"/>
       <c r="I17" s="96"/>
       <c r="J17" s="92" t="s">
@@ -8496,12 +8493,12 @@
       <c r="C18" s="92" t="s">
         <v>218</v>
       </c>
-      <c r="D18" s="186" t="s">
+      <c r="D18" s="187" t="s">
         <v>219</v>
       </c>
-      <c r="E18" s="187"/>
-      <c r="F18" s="187"/>
-      <c r="G18" s="188"/>
+      <c r="E18" s="176"/>
+      <c r="F18" s="176"/>
+      <c r="G18" s="177"/>
       <c r="H18" s="94"/>
       <c r="I18" s="96"/>
       <c r="J18" s="92" t="s">
@@ -8511,6 +8508,14 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="A11:K11"/>
+    <mergeCell ref="A12:K12"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="K9:K10"/>
     <mergeCell ref="D18:G18"/>
     <mergeCell ref="A9:A10"/>
     <mergeCell ref="B9:B10"/>
@@ -8522,14 +8527,6 @@
     <mergeCell ref="D15:G15"/>
     <mergeCell ref="D16:G16"/>
     <mergeCell ref="D17:G17"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="A11:K11"/>
-    <mergeCell ref="A12:K12"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="K9:K10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8581,52 +8578,52 @@
       <c r="A3" s="106" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="170" t="s">
+      <c r="B3" s="209" t="s">
         <v>62</v>
       </c>
-      <c r="C3" s="170"/>
-      <c r="D3" s="171"/>
+      <c r="C3" s="209"/>
+      <c r="D3" s="210"/>
       <c r="E3" s="71"/>
       <c r="F3" s="71"/>
       <c r="G3" s="71"/>
       <c r="H3" s="71"/>
-      <c r="I3" s="172"/>
-      <c r="J3" s="172"/>
-      <c r="K3" s="172"/>
+      <c r="I3" s="193"/>
+      <c r="J3" s="193"/>
+      <c r="K3" s="193"/>
     </row>
     <row r="4" spans="1:11" ht="14.25">
       <c r="A4" s="74" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="173" t="s">
+      <c r="B4" s="211" t="s">
         <v>221</v>
       </c>
-      <c r="C4" s="174"/>
-      <c r="D4" s="175"/>
+      <c r="C4" s="212"/>
+      <c r="D4" s="213"/>
       <c r="E4" s="71"/>
       <c r="F4" s="71"/>
       <c r="G4" s="71"/>
       <c r="H4" s="71"/>
-      <c r="I4" s="172"/>
-      <c r="J4" s="172"/>
-      <c r="K4" s="172"/>
+      <c r="I4" s="193"/>
+      <c r="J4" s="193"/>
+      <c r="K4" s="193"/>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="107" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="176" t="s">
+      <c r="B5" s="214" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="177"/>
-      <c r="D5" s="178"/>
+      <c r="C5" s="215"/>
+      <c r="D5" s="216"/>
       <c r="E5" s="75"/>
       <c r="F5" s="75"/>
       <c r="G5" s="75"/>
       <c r="H5" s="75"/>
-      <c r="I5" s="179"/>
-      <c r="J5" s="179"/>
-      <c r="K5" s="179"/>
+      <c r="I5" s="217"/>
+      <c r="J5" s="217"/>
+      <c r="K5" s="217"/>
     </row>
     <row r="6" spans="1:11" ht="14.25">
       <c r="A6" s="77" t="s">
@@ -8647,9 +8644,9 @@
       <c r="F6" s="72"/>
       <c r="G6" s="72"/>
       <c r="H6" s="72"/>
-      <c r="I6" s="172"/>
-      <c r="J6" s="172"/>
-      <c r="K6" s="172"/>
+      <c r="I6" s="193"/>
+      <c r="J6" s="193"/>
+      <c r="K6" s="193"/>
     </row>
     <row r="7" spans="1:11" ht="14.25">
       <c r="A7" s="81" t="s">
@@ -8670,15 +8667,15 @@
       <c r="F7" s="85"/>
       <c r="G7" s="85"/>
       <c r="H7" s="85"/>
-      <c r="I7" s="172"/>
-      <c r="J7" s="172"/>
-      <c r="K7" s="172"/>
+      <c r="I7" s="193"/>
+      <c r="J7" s="193"/>
+      <c r="K7" s="193"/>
     </row>
     <row r="8" spans="1:11" ht="14.25">
-      <c r="A8" s="180"/>
-      <c r="B8" s="180"/>
-      <c r="C8" s="180"/>
-      <c r="D8" s="180"/>
+      <c r="A8" s="194"/>
+      <c r="B8" s="194"/>
+      <c r="C8" s="194"/>
+      <c r="D8" s="194"/>
       <c r="E8" s="72"/>
       <c r="F8" s="72"/>
       <c r="G8" s="72"/>
@@ -8688,74 +8685,74 @@
       <c r="K8" s="86"/>
     </row>
     <row r="9" spans="1:11" ht="13.5" customHeight="1">
-      <c r="A9" s="205" t="s">
+      <c r="A9" s="197" t="s">
         <v>71</v>
       </c>
-      <c r="B9" s="207" t="s">
+      <c r="B9" s="199" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="205" t="s">
+      <c r="C9" s="197" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="211" t="s">
+      <c r="D9" s="203" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="212"/>
-      <c r="F9" s="212"/>
-      <c r="G9" s="213"/>
-      <c r="H9" s="209" t="s">
+      <c r="E9" s="204"/>
+      <c r="F9" s="204"/>
+      <c r="G9" s="205"/>
+      <c r="H9" s="201" t="s">
         <v>75</v>
       </c>
-      <c r="I9" s="210" t="s">
+      <c r="I9" s="202" t="s">
         <v>76</v>
       </c>
-      <c r="J9" s="210" t="s">
+      <c r="J9" s="202" t="s">
         <v>77</v>
       </c>
-      <c r="K9" s="210" t="s">
+      <c r="K9" s="202" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="206"/>
-      <c r="B10" s="208"/>
-      <c r="C10" s="206"/>
-      <c r="D10" s="214"/>
-      <c r="E10" s="215"/>
-      <c r="F10" s="215"/>
-      <c r="G10" s="216"/>
-      <c r="H10" s="205"/>
-      <c r="I10" s="205"/>
-      <c r="J10" s="205"/>
-      <c r="K10" s="205"/>
+      <c r="A10" s="198"/>
+      <c r="B10" s="200"/>
+      <c r="C10" s="198"/>
+      <c r="D10" s="206"/>
+      <c r="E10" s="207"/>
+      <c r="F10" s="207"/>
+      <c r="G10" s="208"/>
+      <c r="H10" s="197"/>
+      <c r="I10" s="197"/>
+      <c r="J10" s="197"/>
+      <c r="K10" s="197"/>
     </row>
     <row r="11" spans="1:11" ht="15">
-      <c r="A11" s="181"/>
-      <c r="B11" s="181"/>
-      <c r="C11" s="181"/>
-      <c r="D11" s="181"/>
-      <c r="E11" s="181"/>
-      <c r="F11" s="181"/>
-      <c r="G11" s="181"/>
-      <c r="H11" s="181"/>
-      <c r="I11" s="181"/>
-      <c r="J11" s="181"/>
-      <c r="K11" s="182"/>
+      <c r="A11" s="195"/>
+      <c r="B11" s="195"/>
+      <c r="C11" s="195"/>
+      <c r="D11" s="195"/>
+      <c r="E11" s="195"/>
+      <c r="F11" s="195"/>
+      <c r="G11" s="195"/>
+      <c r="H11" s="195"/>
+      <c r="I11" s="195"/>
+      <c r="J11" s="195"/>
+      <c r="K11" s="196"/>
     </row>
     <row r="12" spans="1:11" ht="16.5" customHeight="1">
-      <c r="A12" s="183" t="s">
+      <c r="A12" s="184" t="s">
         <v>222</v>
       </c>
-      <c r="B12" s="184"/>
-      <c r="C12" s="184"/>
-      <c r="D12" s="184"/>
-      <c r="E12" s="184"/>
-      <c r="F12" s="184"/>
-      <c r="G12" s="184"/>
-      <c r="H12" s="184"/>
-      <c r="I12" s="184"/>
-      <c r="J12" s="184"/>
-      <c r="K12" s="185"/>
+      <c r="B12" s="185"/>
+      <c r="C12" s="185"/>
+      <c r="D12" s="185"/>
+      <c r="E12" s="185"/>
+      <c r="F12" s="185"/>
+      <c r="G12" s="185"/>
+      <c r="H12" s="185"/>
+      <c r="I12" s="185"/>
+      <c r="J12" s="185"/>
+      <c r="K12" s="186"/>
     </row>
     <row r="13" spans="1:11" ht="54" customHeight="1">
       <c r="A13" s="90" t="s">
@@ -8767,11 +8764,11 @@
       <c r="C13" s="92" t="s">
         <v>224</v>
       </c>
-      <c r="D13" s="220" t="s">
+      <c r="D13" s="221" t="s">
         <v>225</v>
       </c>
-      <c r="E13" s="221"/>
-      <c r="F13" s="221"/>
+      <c r="E13" s="222"/>
+      <c r="F13" s="222"/>
       <c r="G13" s="124"/>
       <c r="H13" s="94"/>
       <c r="I13" s="96"/>
@@ -8790,11 +8787,11 @@
       <c r="C14" s="92" t="s">
         <v>227</v>
       </c>
-      <c r="D14" s="194" t="s">
+      <c r="D14" s="175" t="s">
         <v>228</v>
       </c>
-      <c r="E14" s="187"/>
-      <c r="F14" s="187"/>
+      <c r="E14" s="176"/>
+      <c r="F14" s="176"/>
       <c r="G14" s="124"/>
       <c r="H14" s="94"/>
       <c r="I14" s="96"/>
@@ -8813,11 +8810,11 @@
       <c r="C15" s="93" t="s">
         <v>230</v>
       </c>
-      <c r="D15" s="194" t="s">
+      <c r="D15" s="175" t="s">
         <v>231</v>
       </c>
-      <c r="E15" s="187"/>
-      <c r="F15" s="187"/>
+      <c r="E15" s="176"/>
+      <c r="F15" s="176"/>
       <c r="G15" s="95"/>
       <c r="H15" s="95"/>
       <c r="I15" s="125"/>
@@ -8827,11 +8824,11 @@
       <c r="K15" s="92"/>
     </row>
     <row r="16" spans="1:11" ht="18" customHeight="1">
-      <c r="A16" s="183" t="s">
+      <c r="A16" s="184" t="s">
         <v>232</v>
       </c>
-      <c r="B16" s="184"/>
-      <c r="C16" s="184"/>
+      <c r="B16" s="185"/>
+      <c r="C16" s="185"/>
       <c r="D16" s="126"/>
       <c r="E16" s="126"/>
       <c r="F16" s="126"/>
@@ -8851,11 +8848,11 @@
       <c r="C17" s="98" t="s">
         <v>234</v>
       </c>
-      <c r="D17" s="220" t="s">
+      <c r="D17" s="221" t="s">
         <v>235</v>
       </c>
-      <c r="E17" s="221"/>
-      <c r="F17" s="221"/>
+      <c r="E17" s="222"/>
+      <c r="F17" s="222"/>
       <c r="G17" s="124"/>
       <c r="H17" s="94"/>
       <c r="I17" s="93"/>
@@ -8874,11 +8871,11 @@
       <c r="C18" s="93" t="s">
         <v>237</v>
       </c>
-      <c r="D18" s="194" t="s">
+      <c r="D18" s="175" t="s">
         <v>238</v>
       </c>
-      <c r="E18" s="187"/>
-      <c r="F18" s="187"/>
+      <c r="E18" s="176"/>
+      <c r="F18" s="176"/>
       <c r="G18" s="95"/>
       <c r="H18" s="95"/>
       <c r="I18" s="92"/>
@@ -8897,11 +8894,11 @@
       <c r="C19" s="93" t="s">
         <v>240</v>
       </c>
-      <c r="D19" s="194" t="s">
+      <c r="D19" s="175" t="s">
         <v>238</v>
       </c>
-      <c r="E19" s="187"/>
-      <c r="F19" s="187"/>
+      <c r="E19" s="176"/>
+      <c r="F19" s="176"/>
       <c r="G19" s="95"/>
       <c r="H19" s="95"/>
       <c r="I19" s="92"/>
@@ -8911,11 +8908,11 @@
       <c r="K19" s="92"/>
     </row>
     <row r="20" spans="1:11" ht="19.5" customHeight="1">
-      <c r="A20" s="183" t="s">
+      <c r="A20" s="184" t="s">
         <v>241</v>
       </c>
-      <c r="B20" s="184"/>
-      <c r="C20" s="184"/>
+      <c r="B20" s="185"/>
+      <c r="C20" s="185"/>
       <c r="D20" s="126"/>
       <c r="E20" s="126"/>
       <c r="F20" s="126"/>
@@ -8935,11 +8932,11 @@
       <c r="C21" s="98" t="s">
         <v>243</v>
       </c>
-      <c r="D21" s="194" t="s">
+      <c r="D21" s="175" t="s">
         <v>244</v>
       </c>
-      <c r="E21" s="187"/>
-      <c r="F21" s="187"/>
+      <c r="E21" s="176"/>
+      <c r="F21" s="176"/>
       <c r="G21" s="95"/>
       <c r="H21" s="94"/>
       <c r="I21" s="93"/>
@@ -8958,11 +8955,11 @@
       <c r="C22" s="92" t="s">
         <v>246</v>
       </c>
-      <c r="D22" s="194" t="s">
+      <c r="D22" s="175" t="s">
         <v>247</v>
       </c>
-      <c r="E22" s="187"/>
-      <c r="F22" s="187"/>
+      <c r="E22" s="176"/>
+      <c r="F22" s="176"/>
       <c r="G22" s="95"/>
       <c r="H22" s="92"/>
       <c r="I22" s="92"/>
@@ -8981,11 +8978,11 @@
       <c r="C23" s="92" t="s">
         <v>249</v>
       </c>
-      <c r="D23" s="220" t="s">
+      <c r="D23" s="221" t="s">
         <v>247</v>
       </c>
-      <c r="E23" s="221"/>
-      <c r="F23" s="221"/>
+      <c r="E23" s="222"/>
+      <c r="F23" s="222"/>
       <c r="G23" s="124"/>
       <c r="H23" s="98"/>
       <c r="I23" s="98"/>
@@ -8995,14 +8992,14 @@
       <c r="K23" s="98"/>
     </row>
     <row r="24" spans="1:11" ht="18" customHeight="1">
-      <c r="A24" s="183" t="s">
+      <c r="A24" s="184" t="s">
         <v>250</v>
       </c>
-      <c r="B24" s="184"/>
-      <c r="C24" s="184"/>
-      <c r="D24" s="222"/>
-      <c r="E24" s="222"/>
-      <c r="F24" s="222"/>
+      <c r="B24" s="185"/>
+      <c r="C24" s="185"/>
+      <c r="D24" s="223"/>
+      <c r="E24" s="223"/>
+      <c r="F24" s="223"/>
       <c r="G24" s="88"/>
       <c r="H24" s="88"/>
       <c r="I24" s="88"/>
@@ -9019,11 +9016,11 @@
       <c r="C25" s="92" t="s">
         <v>252</v>
       </c>
-      <c r="D25" s="220" t="s">
+      <c r="D25" s="221" t="s">
         <v>253</v>
       </c>
-      <c r="E25" s="221"/>
-      <c r="F25" s="221"/>
+      <c r="E25" s="222"/>
+      <c r="F25" s="222"/>
       <c r="G25" s="124"/>
       <c r="H25" s="98"/>
       <c r="I25" s="98"/>
@@ -9042,11 +9039,11 @@
       <c r="C26" s="92" t="s">
         <v>255</v>
       </c>
-      <c r="D26" s="199" t="s">
+      <c r="D26" s="174" t="s">
         <v>256</v>
       </c>
-      <c r="E26" s="199"/>
-      <c r="F26" s="194"/>
+      <c r="E26" s="174"/>
+      <c r="F26" s="175"/>
       <c r="G26" s="95"/>
       <c r="H26" s="95"/>
       <c r="I26" s="92"/>
@@ -9065,11 +9062,11 @@
       <c r="C27" s="92" t="s">
         <v>258</v>
       </c>
-      <c r="D27" s="199" t="s">
+      <c r="D27" s="174" t="s">
         <v>259</v>
       </c>
-      <c r="E27" s="199"/>
-      <c r="F27" s="194"/>
+      <c r="E27" s="174"/>
+      <c r="F27" s="175"/>
       <c r="G27" s="95"/>
       <c r="H27" s="92"/>
       <c r="I27" s="92"/>
@@ -9105,6 +9102,25 @@
     </row>
   </sheetData>
   <mergeCells count="35">
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A11:K11"/>
+    <mergeCell ref="A12:K12"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="K9:K10"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="D17:F17"/>
     <mergeCell ref="D27:F27"/>
     <mergeCell ref="A9:A10"/>
     <mergeCell ref="B9:B10"/>
@@ -9121,25 +9137,6 @@
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="D21:F21"/>
     <mergeCell ref="D22:F22"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A11:K11"/>
-    <mergeCell ref="A12:K12"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="K9:K10"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="I5:K5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -9198,54 +9195,54 @@
       <c r="A3" s="106" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="170" t="s">
+      <c r="B3" s="209" t="s">
         <v>62</v>
       </c>
-      <c r="C3" s="170"/>
-      <c r="D3" s="171"/>
+      <c r="C3" s="209"/>
+      <c r="D3" s="210"/>
       <c r="E3" s="71"/>
       <c r="F3" s="71"/>
       <c r="G3" s="71"/>
       <c r="H3" s="71"/>
-      <c r="I3" s="172"/>
-      <c r="J3" s="172"/>
-      <c r="K3" s="172"/>
+      <c r="I3" s="193"/>
+      <c r="J3" s="193"/>
+      <c r="K3" s="193"/>
       <c r="L3" s="73"/>
     </row>
     <row r="4" spans="1:12" s="61" customFormat="1" ht="13.15" customHeight="1">
       <c r="A4" s="74" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="173" t="s">
+      <c r="B4" s="211" t="s">
         <v>260</v>
       </c>
-      <c r="C4" s="174"/>
-      <c r="D4" s="175"/>
+      <c r="C4" s="212"/>
+      <c r="D4" s="213"/>
       <c r="E4" s="71"/>
       <c r="F4" s="71"/>
       <c r="G4" s="71"/>
       <c r="H4" s="71"/>
-      <c r="I4" s="172"/>
-      <c r="J4" s="172"/>
-      <c r="K4" s="172"/>
+      <c r="I4" s="193"/>
+      <c r="J4" s="193"/>
+      <c r="K4" s="193"/>
       <c r="L4" s="73"/>
     </row>
     <row r="5" spans="1:12" s="62" customFormat="1" ht="12.75">
       <c r="A5" s="107" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="176" t="s">
+      <c r="B5" s="214" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="177"/>
-      <c r="D5" s="178"/>
+      <c r="C5" s="215"/>
+      <c r="D5" s="216"/>
       <c r="E5" s="75"/>
       <c r="F5" s="75"/>
       <c r="G5" s="75"/>
       <c r="H5" s="75"/>
-      <c r="I5" s="179"/>
-      <c r="J5" s="179"/>
-      <c r="K5" s="179"/>
+      <c r="I5" s="217"/>
+      <c r="J5" s="217"/>
+      <c r="K5" s="217"/>
       <c r="L5" s="76"/>
     </row>
     <row r="6" spans="1:12" s="61" customFormat="1" ht="15" customHeight="1">
@@ -9267,9 +9264,9 @@
       <c r="F6" s="72"/>
       <c r="G6" s="72"/>
       <c r="H6" s="72"/>
-      <c r="I6" s="172"/>
-      <c r="J6" s="172"/>
-      <c r="K6" s="172"/>
+      <c r="I6" s="193"/>
+      <c r="J6" s="193"/>
+      <c r="K6" s="193"/>
       <c r="L6" s="73"/>
     </row>
     <row r="7" spans="1:12" s="61" customFormat="1" ht="15" customHeight="1">
@@ -9291,16 +9288,16 @@
       <c r="F7" s="85"/>
       <c r="G7" s="85"/>
       <c r="H7" s="85"/>
-      <c r="I7" s="172"/>
-      <c r="J7" s="172"/>
-      <c r="K7" s="172"/>
+      <c r="I7" s="193"/>
+      <c r="J7" s="193"/>
+      <c r="K7" s="193"/>
       <c r="L7" s="73"/>
     </row>
     <row r="8" spans="1:12" s="61" customFormat="1" ht="15" customHeight="1">
-      <c r="A8" s="180"/>
-      <c r="B8" s="180"/>
-      <c r="C8" s="180"/>
-      <c r="D8" s="180"/>
+      <c r="A8" s="194"/>
+      <c r="B8" s="194"/>
+      <c r="C8" s="194"/>
+      <c r="D8" s="194"/>
       <c r="E8" s="72"/>
       <c r="F8" s="72"/>
       <c r="G8" s="72"/>
@@ -9311,76 +9308,76 @@
       <c r="L8" s="73"/>
     </row>
     <row r="9" spans="1:12" s="63" customFormat="1" ht="12" customHeight="1">
-      <c r="A9" s="205" t="s">
+      <c r="A9" s="197" t="s">
         <v>71</v>
       </c>
-      <c r="B9" s="207" t="s">
+      <c r="B9" s="199" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="205" t="s">
+      <c r="C9" s="197" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="211" t="s">
+      <c r="D9" s="203" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="212"/>
-      <c r="F9" s="212"/>
-      <c r="G9" s="213"/>
-      <c r="H9" s="209" t="s">
+      <c r="E9" s="204"/>
+      <c r="F9" s="204"/>
+      <c r="G9" s="205"/>
+      <c r="H9" s="201" t="s">
         <v>75</v>
       </c>
-      <c r="I9" s="210" t="s">
+      <c r="I9" s="202" t="s">
         <v>76</v>
       </c>
-      <c r="J9" s="210" t="s">
+      <c r="J9" s="202" t="s">
         <v>77</v>
       </c>
-      <c r="K9" s="210" t="s">
+      <c r="K9" s="202" t="s">
         <v>78</v>
       </c>
       <c r="L9" s="87"/>
     </row>
     <row r="10" spans="1:12" s="61" customFormat="1" ht="12" customHeight="1">
-      <c r="A10" s="206"/>
-      <c r="B10" s="208"/>
-      <c r="C10" s="206"/>
-      <c r="D10" s="214"/>
-      <c r="E10" s="215"/>
-      <c r="F10" s="215"/>
-      <c r="G10" s="216"/>
-      <c r="H10" s="205"/>
-      <c r="I10" s="205"/>
-      <c r="J10" s="205"/>
-      <c r="K10" s="205"/>
+      <c r="A10" s="198"/>
+      <c r="B10" s="200"/>
+      <c r="C10" s="198"/>
+      <c r="D10" s="206"/>
+      <c r="E10" s="207"/>
+      <c r="F10" s="207"/>
+      <c r="G10" s="208"/>
+      <c r="H10" s="197"/>
+      <c r="I10" s="197"/>
+      <c r="J10" s="197"/>
+      <c r="K10" s="197"/>
       <c r="L10" s="73"/>
     </row>
     <row r="11" spans="1:12" s="64" customFormat="1" ht="15">
-      <c r="A11" s="181"/>
-      <c r="B11" s="181"/>
-      <c r="C11" s="181"/>
-      <c r="D11" s="181"/>
-      <c r="E11" s="181"/>
-      <c r="F11" s="181"/>
-      <c r="G11" s="181"/>
-      <c r="H11" s="181"/>
-      <c r="I11" s="181"/>
-      <c r="J11" s="181"/>
-      <c r="K11" s="182"/>
+      <c r="A11" s="195"/>
+      <c r="B11" s="195"/>
+      <c r="C11" s="195"/>
+      <c r="D11" s="195"/>
+      <c r="E11" s="195"/>
+      <c r="F11" s="195"/>
+      <c r="G11" s="195"/>
+      <c r="H11" s="195"/>
+      <c r="I11" s="195"/>
+      <c r="J11" s="195"/>
+      <c r="K11" s="196"/>
     </row>
     <row r="12" spans="1:12" s="65" customFormat="1" ht="24.6" customHeight="1">
-      <c r="A12" s="223" t="s">
+      <c r="A12" s="227" t="s">
         <v>261</v>
       </c>
-      <c r="B12" s="224"/>
-      <c r="C12" s="224"/>
-      <c r="D12" s="224"/>
-      <c r="E12" s="224"/>
-      <c r="F12" s="224"/>
-      <c r="G12" s="224"/>
-      <c r="H12" s="224"/>
-      <c r="I12" s="224"/>
-      <c r="J12" s="224"/>
-      <c r="K12" s="225"/>
+      <c r="B12" s="228"/>
+      <c r="C12" s="228"/>
+      <c r="D12" s="228"/>
+      <c r="E12" s="228"/>
+      <c r="F12" s="228"/>
+      <c r="G12" s="228"/>
+      <c r="H12" s="228"/>
+      <c r="I12" s="228"/>
+      <c r="J12" s="228"/>
+      <c r="K12" s="229"/>
     </row>
     <row r="13" spans="1:12" s="65" customFormat="1" ht="81.599999999999994" customHeight="1" outlineLevel="1">
       <c r="A13" s="108" t="s">
@@ -9392,11 +9389,11 @@
       <c r="C13" s="109" t="s">
         <v>263</v>
       </c>
-      <c r="D13" s="194" t="s">
+      <c r="D13" s="175" t="s">
         <v>264</v>
       </c>
-      <c r="E13" s="187"/>
-      <c r="F13" s="187"/>
+      <c r="E13" s="176"/>
+      <c r="F13" s="176"/>
       <c r="G13" s="95"/>
       <c r="H13" s="94"/>
       <c r="I13" s="96"/>
@@ -9413,11 +9410,11 @@
       <c r="C14" s="111" t="s">
         <v>266</v>
       </c>
-      <c r="D14" s="194" t="s">
+      <c r="D14" s="175" t="s">
         <v>267</v>
       </c>
-      <c r="E14" s="187"/>
-      <c r="F14" s="187"/>
+      <c r="E14" s="176"/>
+      <c r="F14" s="176"/>
       <c r="G14" s="95"/>
       <c r="H14" s="94"/>
       <c r="I14" s="93"/>
@@ -9434,11 +9431,11 @@
       <c r="C15" s="109" t="s">
         <v>269</v>
       </c>
-      <c r="D15" s="194" t="s">
+      <c r="D15" s="175" t="s">
         <v>270</v>
       </c>
-      <c r="E15" s="187"/>
-      <c r="F15" s="187"/>
+      <c r="E15" s="176"/>
+      <c r="F15" s="176"/>
       <c r="G15" s="95"/>
       <c r="H15" s="94"/>
       <c r="I15" s="93"/>
@@ -9455,11 +9452,11 @@
       <c r="C16" s="111" t="s">
         <v>272</v>
       </c>
-      <c r="D16" s="194" t="s">
+      <c r="D16" s="175" t="s">
         <v>273</v>
       </c>
-      <c r="E16" s="187"/>
-      <c r="F16" s="187"/>
+      <c r="E16" s="176"/>
+      <c r="F16" s="176"/>
       <c r="G16" s="95"/>
       <c r="H16" s="94"/>
       <c r="I16" s="93"/>
@@ -9476,11 +9473,11 @@
       <c r="C17" s="109" t="s">
         <v>275</v>
       </c>
-      <c r="D17" s="194" t="s">
+      <c r="D17" s="175" t="s">
         <v>276</v>
       </c>
-      <c r="E17" s="187"/>
-      <c r="F17" s="187"/>
+      <c r="E17" s="176"/>
+      <c r="F17" s="176"/>
       <c r="G17" s="95"/>
       <c r="H17" s="94"/>
       <c r="I17" s="93"/>
@@ -9497,11 +9494,11 @@
       <c r="C18" s="111" t="s">
         <v>278</v>
       </c>
-      <c r="D18" s="194" t="s">
+      <c r="D18" s="175" t="s">
         <v>279</v>
       </c>
-      <c r="E18" s="187"/>
-      <c r="F18" s="187"/>
+      <c r="E18" s="176"/>
+      <c r="F18" s="176"/>
       <c r="G18" s="95"/>
       <c r="H18" s="94"/>
       <c r="I18" s="96"/>
@@ -9518,11 +9515,11 @@
       <c r="C19" s="109" t="s">
         <v>281</v>
       </c>
-      <c r="D19" s="194" t="s">
+      <c r="D19" s="175" t="s">
         <v>282</v>
       </c>
-      <c r="E19" s="187"/>
-      <c r="F19" s="187"/>
+      <c r="E19" s="176"/>
+      <c r="F19" s="176"/>
       <c r="G19" s="95"/>
       <c r="H19" s="94"/>
       <c r="I19" s="93"/>
@@ -9539,11 +9536,11 @@
       <c r="C20" s="111" t="s">
         <v>284</v>
       </c>
-      <c r="D20" s="194" t="s">
+      <c r="D20" s="175" t="s">
         <v>285</v>
       </c>
-      <c r="E20" s="187"/>
-      <c r="F20" s="187"/>
+      <c r="E20" s="176"/>
+      <c r="F20" s="176"/>
       <c r="G20" s="95"/>
       <c r="H20" s="94"/>
       <c r="I20" s="93"/>
@@ -9560,11 +9557,11 @@
       <c r="C21" s="109" t="s">
         <v>287</v>
       </c>
-      <c r="D21" s="194" t="s">
+      <c r="D21" s="175" t="s">
         <v>288</v>
       </c>
-      <c r="E21" s="187"/>
-      <c r="F21" s="187"/>
+      <c r="E21" s="176"/>
+      <c r="F21" s="176"/>
       <c r="G21" s="95"/>
       <c r="H21" s="94"/>
       <c r="I21" s="93"/>
@@ -9581,11 +9578,11 @@
       <c r="C22" s="111" t="s">
         <v>290</v>
       </c>
-      <c r="D22" s="194" t="s">
+      <c r="D22" s="175" t="s">
         <v>291</v>
       </c>
-      <c r="E22" s="187"/>
-      <c r="F22" s="187"/>
+      <c r="E22" s="176"/>
+      <c r="F22" s="176"/>
       <c r="G22" s="95"/>
       <c r="H22" s="94"/>
       <c r="I22" s="93"/>
@@ -9602,11 +9599,11 @@
       <c r="C23" s="109" t="s">
         <v>293</v>
       </c>
-      <c r="D23" s="194" t="s">
+      <c r="D23" s="175" t="s">
         <v>294</v>
       </c>
-      <c r="E23" s="187"/>
-      <c r="F23" s="187"/>
+      <c r="E23" s="176"/>
+      <c r="F23" s="176"/>
       <c r="G23" s="95"/>
       <c r="H23" s="94"/>
       <c r="I23" s="96"/>
@@ -9623,11 +9620,11 @@
       <c r="C24" s="111" t="s">
         <v>296</v>
       </c>
-      <c r="D24" s="194" t="s">
+      <c r="D24" s="175" t="s">
         <v>297</v>
       </c>
-      <c r="E24" s="187"/>
-      <c r="F24" s="187"/>
+      <c r="E24" s="176"/>
+      <c r="F24" s="176"/>
       <c r="G24" s="95"/>
       <c r="H24" s="94"/>
       <c r="I24" s="93"/>
@@ -9644,11 +9641,11 @@
       <c r="C25" s="109" t="s">
         <v>300</v>
       </c>
-      <c r="D25" s="194" t="s">
+      <c r="D25" s="175" t="s">
         <v>301</v>
       </c>
-      <c r="E25" s="187"/>
-      <c r="F25" s="187"/>
+      <c r="E25" s="176"/>
+      <c r="F25" s="176"/>
       <c r="G25" s="95"/>
       <c r="H25" s="94"/>
       <c r="I25" s="93"/>
@@ -9665,11 +9662,11 @@
       <c r="C26" s="111" t="s">
         <v>304</v>
       </c>
-      <c r="D26" s="194" t="s">
+      <c r="D26" s="175" t="s">
         <v>305</v>
       </c>
-      <c r="E26" s="187"/>
-      <c r="F26" s="187"/>
+      <c r="E26" s="176"/>
+      <c r="F26" s="176"/>
       <c r="G26" s="95"/>
       <c r="H26" s="94"/>
       <c r="I26" s="93"/>
@@ -9680,16 +9677,16 @@
       <c r="A27" s="226" t="s">
         <v>306</v>
       </c>
-      <c r="B27" s="184"/>
-      <c r="C27" s="184"/>
-      <c r="D27" s="184"/>
-      <c r="E27" s="184"/>
-      <c r="F27" s="184"/>
-      <c r="G27" s="184"/>
-      <c r="H27" s="184"/>
-      <c r="I27" s="184"/>
-      <c r="J27" s="184"/>
-      <c r="K27" s="185"/>
+      <c r="B27" s="185"/>
+      <c r="C27" s="185"/>
+      <c r="D27" s="185"/>
+      <c r="E27" s="185"/>
+      <c r="F27" s="185"/>
+      <c r="G27" s="185"/>
+      <c r="H27" s="185"/>
+      <c r="I27" s="185"/>
+      <c r="J27" s="185"/>
+      <c r="K27" s="186"/>
     </row>
     <row r="28" spans="1:11" ht="70.150000000000006" customHeight="1">
       <c r="A28" s="108" t="s">
@@ -9701,11 +9698,11 @@
       <c r="C28" s="109" t="s">
         <v>309</v>
       </c>
-      <c r="D28" s="194" t="s">
+      <c r="D28" s="175" t="s">
         <v>310</v>
       </c>
-      <c r="E28" s="187"/>
-      <c r="F28" s="187"/>
+      <c r="E28" s="176"/>
+      <c r="F28" s="176"/>
       <c r="G28" s="95"/>
       <c r="H28" s="94"/>
       <c r="I28" s="96"/>
@@ -9722,11 +9719,11 @@
       <c r="C29" s="111" t="s">
         <v>313</v>
       </c>
-      <c r="D29" s="194" t="s">
+      <c r="D29" s="175" t="s">
         <v>314</v>
       </c>
-      <c r="E29" s="187"/>
-      <c r="F29" s="187"/>
+      <c r="E29" s="176"/>
+      <c r="F29" s="176"/>
       <c r="G29" s="95"/>
       <c r="H29" s="94"/>
       <c r="I29" s="93"/>
@@ -9743,11 +9740,11 @@
       <c r="C30" s="109" t="s">
         <v>317</v>
       </c>
-      <c r="D30" s="194" t="s">
+      <c r="D30" s="175" t="s">
         <v>318</v>
       </c>
-      <c r="E30" s="187"/>
-      <c r="F30" s="187"/>
+      <c r="E30" s="176"/>
+      <c r="F30" s="176"/>
       <c r="G30" s="95"/>
       <c r="H30" s="94"/>
       <c r="I30" s="93"/>
@@ -9764,11 +9761,11 @@
       <c r="C31" s="111" t="s">
         <v>321</v>
       </c>
-      <c r="D31" s="194" t="s">
+      <c r="D31" s="175" t="s">
         <v>322</v>
       </c>
-      <c r="E31" s="187"/>
-      <c r="F31" s="187"/>
+      <c r="E31" s="176"/>
+      <c r="F31" s="176"/>
       <c r="G31" s="95"/>
       <c r="H31" s="94"/>
       <c r="I31" s="93"/>
@@ -9785,11 +9782,11 @@
       <c r="C32" s="109" t="s">
         <v>325</v>
       </c>
-      <c r="D32" s="194" t="s">
+      <c r="D32" s="175" t="s">
         <v>326</v>
       </c>
-      <c r="E32" s="187"/>
-      <c r="F32" s="187"/>
+      <c r="E32" s="176"/>
+      <c r="F32" s="176"/>
       <c r="G32" s="95"/>
       <c r="H32" s="94"/>
       <c r="I32" s="93"/>
@@ -9806,11 +9803,11 @@
       <c r="C33" s="111" t="s">
         <v>329</v>
       </c>
-      <c r="D33" s="194" t="s">
+      <c r="D33" s="175" t="s">
         <v>322</v>
       </c>
-      <c r="E33" s="187"/>
-      <c r="F33" s="187"/>
+      <c r="E33" s="176"/>
+      <c r="F33" s="176"/>
       <c r="G33" s="95"/>
       <c r="H33" s="94"/>
       <c r="I33" s="93"/>
@@ -9827,11 +9824,11 @@
       <c r="C34" s="109" t="s">
         <v>332</v>
       </c>
-      <c r="D34" s="194" t="s">
+      <c r="D34" s="175" t="s">
         <v>333</v>
       </c>
-      <c r="E34" s="187"/>
-      <c r="F34" s="187"/>
+      <c r="E34" s="176"/>
+      <c r="F34" s="176"/>
       <c r="G34" s="95"/>
       <c r="H34" s="94"/>
       <c r="I34" s="93"/>
@@ -9848,11 +9845,11 @@
       <c r="C35" s="111" t="s">
         <v>336</v>
       </c>
-      <c r="D35" s="194" t="s">
+      <c r="D35" s="175" t="s">
         <v>337</v>
       </c>
-      <c r="E35" s="187"/>
-      <c r="F35" s="187"/>
+      <c r="E35" s="176"/>
+      <c r="F35" s="176"/>
       <c r="G35" s="95"/>
       <c r="H35" s="94"/>
       <c r="I35" s="93"/>
@@ -9863,16 +9860,16 @@
       <c r="A36" s="226" t="s">
         <v>338</v>
       </c>
-      <c r="B36" s="184"/>
-      <c r="C36" s="184"/>
-      <c r="D36" s="184"/>
-      <c r="E36" s="184"/>
-      <c r="F36" s="184"/>
-      <c r="G36" s="184"/>
-      <c r="H36" s="184"/>
-      <c r="I36" s="184"/>
-      <c r="J36" s="184"/>
-      <c r="K36" s="185"/>
+      <c r="B36" s="185"/>
+      <c r="C36" s="185"/>
+      <c r="D36" s="185"/>
+      <c r="E36" s="185"/>
+      <c r="F36" s="185"/>
+      <c r="G36" s="185"/>
+      <c r="H36" s="185"/>
+      <c r="I36" s="185"/>
+      <c r="J36" s="185"/>
+      <c r="K36" s="186"/>
     </row>
     <row r="37" spans="1:11" ht="70.150000000000006" customHeight="1">
       <c r="A37" s="108" t="s">
@@ -9884,11 +9881,11 @@
       <c r="C37" s="109" t="s">
         <v>341</v>
       </c>
-      <c r="D37" s="194" t="s">
+      <c r="D37" s="175" t="s">
         <v>342</v>
       </c>
-      <c r="E37" s="187"/>
-      <c r="F37" s="187"/>
+      <c r="E37" s="176"/>
+      <c r="F37" s="176"/>
       <c r="G37" s="95"/>
       <c r="H37" s="94"/>
       <c r="I37" s="93"/>
@@ -9905,11 +9902,11 @@
       <c r="C38" s="111" t="s">
         <v>345</v>
       </c>
-      <c r="D38" s="194" t="s">
+      <c r="D38" s="175" t="s">
         <v>346</v>
       </c>
-      <c r="E38" s="187"/>
-      <c r="F38" s="187"/>
+      <c r="E38" s="176"/>
+      <c r="F38" s="176"/>
       <c r="G38" s="95"/>
       <c r="H38" s="94"/>
       <c r="I38" s="93"/>
@@ -9920,16 +9917,16 @@
       <c r="A39" s="226" t="s">
         <v>347</v>
       </c>
-      <c r="B39" s="184"/>
-      <c r="C39" s="184"/>
-      <c r="D39" s="184"/>
-      <c r="E39" s="184"/>
-      <c r="F39" s="184"/>
-      <c r="G39" s="184"/>
-      <c r="H39" s="184"/>
-      <c r="I39" s="184"/>
-      <c r="J39" s="184"/>
-      <c r="K39" s="185"/>
+      <c r="B39" s="185"/>
+      <c r="C39" s="185"/>
+      <c r="D39" s="185"/>
+      <c r="E39" s="185"/>
+      <c r="F39" s="185"/>
+      <c r="G39" s="185"/>
+      <c r="H39" s="185"/>
+      <c r="I39" s="185"/>
+      <c r="J39" s="185"/>
+      <c r="K39" s="186"/>
     </row>
     <row r="40" spans="1:11" ht="70.150000000000006" customHeight="1">
       <c r="A40" s="108" t="s">
@@ -9941,11 +9938,11 @@
       <c r="C40" s="109" t="s">
         <v>350</v>
       </c>
-      <c r="D40" s="194" t="s">
+      <c r="D40" s="175" t="s">
         <v>351</v>
       </c>
-      <c r="E40" s="187"/>
-      <c r="F40" s="187"/>
+      <c r="E40" s="176"/>
+      <c r="F40" s="176"/>
       <c r="G40" s="95"/>
       <c r="H40" s="94"/>
       <c r="I40" s="93"/>
@@ -9962,11 +9959,11 @@
       <c r="C41" s="111" t="s">
         <v>354</v>
       </c>
-      <c r="D41" s="194" t="s">
+      <c r="D41" s="175" t="s">
         <v>355</v>
       </c>
-      <c r="E41" s="187"/>
-      <c r="F41" s="187"/>
+      <c r="E41" s="176"/>
+      <c r="F41" s="176"/>
       <c r="G41" s="95"/>
       <c r="H41" s="94"/>
       <c r="I41" s="93"/>
@@ -9977,9 +9974,9 @@
       <c r="A42" s="90"/>
       <c r="B42" s="99"/>
       <c r="C42" s="92"/>
-      <c r="D42" s="227"/>
-      <c r="E42" s="228"/>
-      <c r="F42" s="228"/>
+      <c r="D42" s="224"/>
+      <c r="E42" s="225"/>
+      <c r="F42" s="225"/>
       <c r="G42" s="95"/>
       <c r="H42" s="94"/>
       <c r="I42" s="93"/>
@@ -9990,9 +9987,9 @@
       <c r="A43" s="90"/>
       <c r="B43" s="97"/>
       <c r="C43" s="98"/>
-      <c r="D43" s="227"/>
-      <c r="E43" s="187"/>
-      <c r="F43" s="187"/>
+      <c r="D43" s="224"/>
+      <c r="E43" s="176"/>
+      <c r="F43" s="176"/>
       <c r="G43" s="95"/>
       <c r="H43" s="94"/>
       <c r="I43" s="93"/>
@@ -10003,9 +10000,9 @@
       <c r="A44" s="90"/>
       <c r="B44" s="99"/>
       <c r="C44" s="92"/>
-      <c r="D44" s="227"/>
-      <c r="E44" s="228"/>
-      <c r="F44" s="228"/>
+      <c r="D44" s="224"/>
+      <c r="E44" s="225"/>
+      <c r="F44" s="225"/>
       <c r="G44" s="95"/>
       <c r="H44" s="94"/>
       <c r="I44" s="93"/>
@@ -10016,9 +10013,9 @@
       <c r="A45" s="90"/>
       <c r="B45" s="97"/>
       <c r="C45" s="98"/>
-      <c r="D45" s="227"/>
-      <c r="E45" s="187"/>
-      <c r="F45" s="187"/>
+      <c r="D45" s="224"/>
+      <c r="E45" s="176"/>
+      <c r="F45" s="176"/>
       <c r="G45" s="95"/>
       <c r="H45" s="94"/>
       <c r="I45" s="93"/>
@@ -10029,9 +10026,9 @@
       <c r="A46" s="90"/>
       <c r="B46" s="99"/>
       <c r="C46" s="92"/>
-      <c r="D46" s="227"/>
-      <c r="E46" s="228"/>
-      <c r="F46" s="228"/>
+      <c r="D46" s="224"/>
+      <c r="E46" s="225"/>
+      <c r="F46" s="225"/>
       <c r="G46" s="95"/>
       <c r="H46" s="94"/>
       <c r="I46" s="93"/>
@@ -10042,9 +10039,9 @@
       <c r="A47" s="90"/>
       <c r="B47" s="97"/>
       <c r="C47" s="98"/>
-      <c r="D47" s="227"/>
-      <c r="E47" s="187"/>
-      <c r="F47" s="187"/>
+      <c r="D47" s="224"/>
+      <c r="E47" s="176"/>
+      <c r="F47" s="176"/>
       <c r="G47" s="95"/>
       <c r="H47" s="94"/>
       <c r="I47" s="93"/>
@@ -10055,9 +10052,9 @@
       <c r="A48" s="90"/>
       <c r="B48" s="99"/>
       <c r="C48" s="92"/>
-      <c r="D48" s="227"/>
-      <c r="E48" s="228"/>
-      <c r="F48" s="228"/>
+      <c r="D48" s="224"/>
+      <c r="E48" s="225"/>
+      <c r="F48" s="225"/>
       <c r="G48" s="95"/>
       <c r="H48" s="94"/>
       <c r="I48" s="93"/>
@@ -10068,9 +10065,9 @@
       <c r="A49" s="90"/>
       <c r="B49" s="97"/>
       <c r="C49" s="98"/>
-      <c r="D49" s="227"/>
-      <c r="E49" s="187"/>
-      <c r="F49" s="187"/>
+      <c r="D49" s="224"/>
+      <c r="E49" s="176"/>
+      <c r="F49" s="176"/>
       <c r="G49" s="95"/>
       <c r="H49" s="94"/>
       <c r="I49" s="93"/>
@@ -10081,9 +10078,9 @@
       <c r="A50" s="90"/>
       <c r="B50" s="99"/>
       <c r="C50" s="92"/>
-      <c r="D50" s="227"/>
-      <c r="E50" s="228"/>
-      <c r="F50" s="228"/>
+      <c r="D50" s="224"/>
+      <c r="E50" s="225"/>
+      <c r="F50" s="225"/>
       <c r="G50" s="95"/>
       <c r="H50" s="94"/>
       <c r="I50" s="93"/>
@@ -10095,6 +10092,47 @@
     <row r="53" spans="1:11" ht="12" customHeight="1"/>
   </sheetData>
   <mergeCells count="57">
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A11:K11"/>
+    <mergeCell ref="A12:K12"/>
+    <mergeCell ref="H9:H10"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="K9:K10"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="A27:K27"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="A36:K36"/>
+    <mergeCell ref="D37:F37"/>
     <mergeCell ref="D48:F48"/>
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="D50:F50"/>
@@ -10111,47 +10149,6 @@
     <mergeCell ref="A39:K39"/>
     <mergeCell ref="D40:F40"/>
     <mergeCell ref="D41:F41"/>
-    <mergeCell ref="D42:F42"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="A36:K36"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="A27:K27"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A11:K11"/>
-    <mergeCell ref="A12:K12"/>
-    <mergeCell ref="H9:H10"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="K9:K10"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="I5:K5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10209,54 +10206,54 @@
       <c r="A3" s="106" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="170" t="s">
+      <c r="B3" s="209" t="s">
         <v>62</v>
       </c>
-      <c r="C3" s="170"/>
-      <c r="D3" s="171"/>
+      <c r="C3" s="209"/>
+      <c r="D3" s="210"/>
       <c r="E3" s="71"/>
       <c r="F3" s="71"/>
       <c r="G3" s="71"/>
       <c r="H3" s="71"/>
-      <c r="I3" s="172"/>
-      <c r="J3" s="172"/>
-      <c r="K3" s="172"/>
+      <c r="I3" s="193"/>
+      <c r="J3" s="193"/>
+      <c r="K3" s="193"/>
       <c r="L3" s="73"/>
     </row>
     <row r="4" spans="1:12" s="61" customFormat="1" ht="13.15" customHeight="1">
       <c r="A4" s="74" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="173" t="s">
+      <c r="B4" s="211" t="s">
         <v>356</v>
       </c>
-      <c r="C4" s="174"/>
-      <c r="D4" s="175"/>
+      <c r="C4" s="212"/>
+      <c r="D4" s="213"/>
       <c r="E4" s="71"/>
       <c r="F4" s="71"/>
       <c r="G4" s="71"/>
       <c r="H4" s="71"/>
-      <c r="I4" s="172"/>
-      <c r="J4" s="172"/>
-      <c r="K4" s="172"/>
+      <c r="I4" s="193"/>
+      <c r="J4" s="193"/>
+      <c r="K4" s="193"/>
       <c r="L4" s="73"/>
     </row>
     <row r="5" spans="1:12" s="62" customFormat="1" ht="25.5">
       <c r="A5" s="107" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="176" t="s">
+      <c r="B5" s="214" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="177"/>
-      <c r="D5" s="178"/>
+      <c r="C5" s="215"/>
+      <c r="D5" s="216"/>
       <c r="E5" s="75"/>
       <c r="F5" s="75"/>
       <c r="G5" s="75"/>
       <c r="H5" s="75"/>
-      <c r="I5" s="179"/>
-      <c r="J5" s="179"/>
-      <c r="K5" s="179"/>
+      <c r="I5" s="217"/>
+      <c r="J5" s="217"/>
+      <c r="K5" s="217"/>
       <c r="L5" s="76"/>
     </row>
     <row r="6" spans="1:12" s="61" customFormat="1" ht="15" customHeight="1">
@@ -10278,9 +10275,9 @@
       <c r="F6" s="72"/>
       <c r="G6" s="72"/>
       <c r="H6" s="72"/>
-      <c r="I6" s="172"/>
-      <c r="J6" s="172"/>
-      <c r="K6" s="172"/>
+      <c r="I6" s="193"/>
+      <c r="J6" s="193"/>
+      <c r="K6" s="193"/>
       <c r="L6" s="73"/>
     </row>
     <row r="7" spans="1:12" s="61" customFormat="1" ht="15" customHeight="1">
@@ -10302,16 +10299,16 @@
       <c r="F7" s="85"/>
       <c r="G7" s="85"/>
       <c r="H7" s="85"/>
-      <c r="I7" s="172"/>
-      <c r="J7" s="172"/>
-      <c r="K7" s="172"/>
+      <c r="I7" s="193"/>
+      <c r="J7" s="193"/>
+      <c r="K7" s="193"/>
       <c r="L7" s="73"/>
     </row>
     <row r="8" spans="1:12" s="61" customFormat="1" ht="15" customHeight="1">
-      <c r="A8" s="180"/>
-      <c r="B8" s="180"/>
-      <c r="C8" s="180"/>
-      <c r="D8" s="180"/>
+      <c r="A8" s="194"/>
+      <c r="B8" s="194"/>
+      <c r="C8" s="194"/>
+      <c r="D8" s="194"/>
       <c r="E8" s="72"/>
       <c r="F8" s="72"/>
       <c r="G8" s="72"/>
@@ -10322,76 +10319,76 @@
       <c r="L8" s="73"/>
     </row>
     <row r="9" spans="1:12" s="63" customFormat="1" ht="12" customHeight="1">
-      <c r="A9" s="205" t="s">
+      <c r="A9" s="197" t="s">
         <v>71</v>
       </c>
-      <c r="B9" s="207" t="s">
+      <c r="B9" s="199" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="205" t="s">
+      <c r="C9" s="197" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="211" t="s">
+      <c r="D9" s="203" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="212"/>
-      <c r="F9" s="212"/>
-      <c r="G9" s="213"/>
-      <c r="H9" s="209" t="s">
+      <c r="E9" s="204"/>
+      <c r="F9" s="204"/>
+      <c r="G9" s="205"/>
+      <c r="H9" s="201" t="s">
         <v>75</v>
       </c>
-      <c r="I9" s="210" t="s">
+      <c r="I9" s="202" t="s">
         <v>76</v>
       </c>
-      <c r="J9" s="210" t="s">
+      <c r="J9" s="202" t="s">
         <v>77</v>
       </c>
-      <c r="K9" s="210" t="s">
+      <c r="K9" s="202" t="s">
         <v>78</v>
       </c>
       <c r="L9" s="87"/>
     </row>
     <row r="10" spans="1:12" s="61" customFormat="1" ht="12" customHeight="1">
-      <c r="A10" s="206"/>
-      <c r="B10" s="208"/>
-      <c r="C10" s="206"/>
-      <c r="D10" s="214"/>
-      <c r="E10" s="215"/>
-      <c r="F10" s="215"/>
-      <c r="G10" s="216"/>
-      <c r="H10" s="205"/>
-      <c r="I10" s="205"/>
-      <c r="J10" s="205"/>
-      <c r="K10" s="205"/>
+      <c r="A10" s="198"/>
+      <c r="B10" s="200"/>
+      <c r="C10" s="198"/>
+      <c r="D10" s="206"/>
+      <c r="E10" s="207"/>
+      <c r="F10" s="207"/>
+      <c r="G10" s="208"/>
+      <c r="H10" s="197"/>
+      <c r="I10" s="197"/>
+      <c r="J10" s="197"/>
+      <c r="K10" s="197"/>
       <c r="L10" s="73"/>
     </row>
     <row r="11" spans="1:12" s="64" customFormat="1" ht="15">
-      <c r="A11" s="181"/>
-      <c r="B11" s="181"/>
-      <c r="C11" s="181"/>
-      <c r="D11" s="181"/>
-      <c r="E11" s="181"/>
-      <c r="F11" s="181"/>
-      <c r="G11" s="181"/>
-      <c r="H11" s="181"/>
-      <c r="I11" s="181"/>
-      <c r="J11" s="181"/>
-      <c r="K11" s="182"/>
+      <c r="A11" s="195"/>
+      <c r="B11" s="195"/>
+      <c r="C11" s="195"/>
+      <c r="D11" s="195"/>
+      <c r="E11" s="195"/>
+      <c r="F11" s="195"/>
+      <c r="G11" s="195"/>
+      <c r="H11" s="195"/>
+      <c r="I11" s="195"/>
+      <c r="J11" s="195"/>
+      <c r="K11" s="196"/>
     </row>
     <row r="12" spans="1:12" s="65" customFormat="1" ht="22.9" customHeight="1">
       <c r="A12" s="226" t="s">
         <v>357</v>
       </c>
-      <c r="B12" s="229"/>
-      <c r="C12" s="229"/>
-      <c r="D12" s="229"/>
-      <c r="E12" s="229"/>
-      <c r="F12" s="229"/>
-      <c r="G12" s="229"/>
-      <c r="H12" s="229"/>
-      <c r="I12" s="229"/>
-      <c r="J12" s="229"/>
-      <c r="K12" s="230"/>
+      <c r="B12" s="230"/>
+      <c r="C12" s="230"/>
+      <c r="D12" s="230"/>
+      <c r="E12" s="230"/>
+      <c r="F12" s="230"/>
+      <c r="G12" s="230"/>
+      <c r="H12" s="230"/>
+      <c r="I12" s="230"/>
+      <c r="J12" s="230"/>
+      <c r="K12" s="231"/>
     </row>
     <row r="13" spans="1:12" s="65" customFormat="1" ht="66.599999999999994" customHeight="1" outlineLevel="1">
       <c r="A13" s="108" t="s">
@@ -10403,11 +10400,11 @@
       <c r="C13" s="109" t="s">
         <v>359</v>
       </c>
-      <c r="D13" s="194" t="s">
+      <c r="D13" s="175" t="s">
         <v>360</v>
       </c>
-      <c r="E13" s="187"/>
-      <c r="F13" s="187"/>
+      <c r="E13" s="176"/>
+      <c r="F13" s="176"/>
       <c r="G13" s="95"/>
       <c r="H13" s="94"/>
       <c r="I13" s="96"/>
@@ -10424,11 +10421,11 @@
       <c r="C14" s="111" t="s">
         <v>362</v>
       </c>
-      <c r="D14" s="194" t="s">
+      <c r="D14" s="175" t="s">
         <v>363</v>
       </c>
-      <c r="E14" s="187"/>
-      <c r="F14" s="187"/>
+      <c r="E14" s="176"/>
+      <c r="F14" s="176"/>
       <c r="G14" s="95"/>
       <c r="H14" s="94"/>
       <c r="I14" s="93"/>
@@ -10445,11 +10442,11 @@
       <c r="C15" s="109" t="s">
         <v>365</v>
       </c>
-      <c r="D15" s="194" t="s">
+      <c r="D15" s="175" t="s">
         <v>366</v>
       </c>
-      <c r="E15" s="187"/>
-      <c r="F15" s="187"/>
+      <c r="E15" s="176"/>
+      <c r="F15" s="176"/>
       <c r="G15" s="95"/>
       <c r="H15" s="94"/>
       <c r="I15" s="93"/>
@@ -10460,16 +10457,16 @@
       <c r="A16" s="226" t="s">
         <v>367</v>
       </c>
-      <c r="B16" s="184"/>
-      <c r="C16" s="184"/>
-      <c r="D16" s="184"/>
-      <c r="E16" s="184"/>
-      <c r="F16" s="184"/>
-      <c r="G16" s="184"/>
-      <c r="H16" s="184"/>
-      <c r="I16" s="184"/>
-      <c r="J16" s="184"/>
-      <c r="K16" s="185"/>
+      <c r="B16" s="185"/>
+      <c r="C16" s="185"/>
+      <c r="D16" s="185"/>
+      <c r="E16" s="185"/>
+      <c r="F16" s="185"/>
+      <c r="G16" s="185"/>
+      <c r="H16" s="185"/>
+      <c r="I16" s="185"/>
+      <c r="J16" s="185"/>
+      <c r="K16" s="186"/>
     </row>
     <row r="17" spans="1:11" ht="70.150000000000006" customHeight="1">
       <c r="A17" s="110" t="s">
@@ -10481,11 +10478,11 @@
       <c r="C17" s="111" t="s">
         <v>369</v>
       </c>
-      <c r="D17" s="194" t="s">
+      <c r="D17" s="175" t="s">
         <v>370</v>
       </c>
-      <c r="E17" s="187"/>
-      <c r="F17" s="187"/>
+      <c r="E17" s="176"/>
+      <c r="F17" s="176"/>
       <c r="G17" s="95"/>
       <c r="H17" s="94"/>
       <c r="I17" s="93"/>
@@ -10502,11 +10499,11 @@
       <c r="C18" s="109" t="s">
         <v>372</v>
       </c>
-      <c r="D18" s="194" t="s">
+      <c r="D18" s="175" t="s">
         <v>373</v>
       </c>
-      <c r="E18" s="187"/>
-      <c r="F18" s="187"/>
+      <c r="E18" s="176"/>
+      <c r="F18" s="176"/>
       <c r="G18" s="95"/>
       <c r="H18" s="94"/>
       <c r="I18" s="93"/>
@@ -10523,11 +10520,11 @@
       <c r="C19" s="111" t="s">
         <v>375</v>
       </c>
-      <c r="D19" s="194" t="s">
+      <c r="D19" s="175" t="s">
         <v>376</v>
       </c>
-      <c r="E19" s="187"/>
-      <c r="F19" s="187"/>
+      <c r="E19" s="176"/>
+      <c r="F19" s="176"/>
       <c r="G19" s="95"/>
       <c r="H19" s="94"/>
       <c r="I19" s="93"/>
@@ -10535,19 +10532,19 @@
       <c r="K19" s="92"/>
     </row>
     <row r="20" spans="1:11" ht="28.15" customHeight="1">
-      <c r="A20" s="223" t="s">
+      <c r="A20" s="227" t="s">
         <v>377</v>
       </c>
-      <c r="B20" s="224"/>
-      <c r="C20" s="224"/>
-      <c r="D20" s="224"/>
-      <c r="E20" s="224"/>
-      <c r="F20" s="224"/>
-      <c r="G20" s="224"/>
-      <c r="H20" s="224"/>
-      <c r="I20" s="224"/>
-      <c r="J20" s="224"/>
-      <c r="K20" s="225"/>
+      <c r="B20" s="228"/>
+      <c r="C20" s="228"/>
+      <c r="D20" s="228"/>
+      <c r="E20" s="228"/>
+      <c r="F20" s="228"/>
+      <c r="G20" s="228"/>
+      <c r="H20" s="228"/>
+      <c r="I20" s="228"/>
+      <c r="J20" s="228"/>
+      <c r="K20" s="229"/>
     </row>
     <row r="21" spans="1:11" ht="70.150000000000006" customHeight="1">
       <c r="A21" s="108" t="s">
@@ -10559,11 +10556,11 @@
       <c r="C21" s="109" t="s">
         <v>379</v>
       </c>
-      <c r="D21" s="194" t="s">
+      <c r="D21" s="175" t="s">
         <v>380</v>
       </c>
-      <c r="E21" s="187"/>
-      <c r="F21" s="187"/>
+      <c r="E21" s="176"/>
+      <c r="F21" s="176"/>
       <c r="G21" s="95"/>
       <c r="H21" s="94"/>
       <c r="I21" s="93"/>
@@ -10580,11 +10577,11 @@
       <c r="C22" s="111" t="s">
         <v>382</v>
       </c>
-      <c r="D22" s="194" t="s">
+      <c r="D22" s="175" t="s">
         <v>383</v>
       </c>
-      <c r="E22" s="187"/>
-      <c r="F22" s="187"/>
+      <c r="E22" s="176"/>
+      <c r="F22" s="176"/>
       <c r="G22" s="95"/>
       <c r="H22" s="94"/>
       <c r="I22" s="93"/>
@@ -10601,11 +10598,11 @@
       <c r="C23" s="109" t="s">
         <v>385</v>
       </c>
-      <c r="D23" s="194" t="s">
+      <c r="D23" s="175" t="s">
         <v>386</v>
       </c>
-      <c r="E23" s="187"/>
-      <c r="F23" s="187"/>
+      <c r="E23" s="176"/>
+      <c r="F23" s="176"/>
       <c r="G23" s="95"/>
       <c r="H23" s="94"/>
       <c r="I23" s="93"/>
@@ -10622,11 +10619,11 @@
       <c r="C24" s="111" t="s">
         <v>388</v>
       </c>
-      <c r="D24" s="194" t="s">
+      <c r="D24" s="175" t="s">
         <v>389</v>
       </c>
-      <c r="E24" s="187"/>
-      <c r="F24" s="187"/>
+      <c r="E24" s="176"/>
+      <c r="F24" s="176"/>
       <c r="G24" s="95"/>
       <c r="H24" s="94"/>
       <c r="I24" s="93"/>
@@ -10634,19 +10631,19 @@
       <c r="K24" s="92"/>
     </row>
     <row r="25" spans="1:11" ht="31.15" customHeight="1">
-      <c r="A25" s="223" t="s">
+      <c r="A25" s="227" t="s">
         <v>390</v>
       </c>
-      <c r="B25" s="224"/>
-      <c r="C25" s="224"/>
-      <c r="D25" s="224"/>
-      <c r="E25" s="224"/>
-      <c r="F25" s="224"/>
-      <c r="G25" s="224"/>
-      <c r="H25" s="224"/>
-      <c r="I25" s="224"/>
-      <c r="J25" s="224"/>
-      <c r="K25" s="225"/>
+      <c r="B25" s="228"/>
+      <c r="C25" s="228"/>
+      <c r="D25" s="228"/>
+      <c r="E25" s="228"/>
+      <c r="F25" s="228"/>
+      <c r="G25" s="228"/>
+      <c r="H25" s="228"/>
+      <c r="I25" s="228"/>
+      <c r="J25" s="228"/>
+      <c r="K25" s="229"/>
     </row>
     <row r="26" spans="1:11" ht="70.150000000000006" customHeight="1">
       <c r="A26" s="108" t="s">
@@ -10658,11 +10655,11 @@
       <c r="C26" s="109" t="s">
         <v>392</v>
       </c>
-      <c r="D26" s="194" t="s">
+      <c r="D26" s="175" t="s">
         <v>393</v>
       </c>
-      <c r="E26" s="187"/>
-      <c r="F26" s="187"/>
+      <c r="E26" s="176"/>
+      <c r="F26" s="176"/>
       <c r="G26" s="95"/>
       <c r="H26" s="94"/>
       <c r="I26" s="93"/>
@@ -10679,11 +10676,11 @@
       <c r="C27" s="111" t="s">
         <v>395</v>
       </c>
-      <c r="D27" s="194" t="s">
+      <c r="D27" s="175" t="s">
         <v>396</v>
       </c>
-      <c r="E27" s="187"/>
-      <c r="F27" s="187"/>
+      <c r="E27" s="176"/>
+      <c r="F27" s="176"/>
       <c r="G27" s="95"/>
       <c r="H27" s="94"/>
       <c r="I27" s="93"/>
@@ -10700,11 +10697,11 @@
       <c r="C28" s="109" t="s">
         <v>398</v>
       </c>
-      <c r="D28" s="194" t="s">
+      <c r="D28" s="175" t="s">
         <v>399</v>
       </c>
-      <c r="E28" s="187"/>
-      <c r="F28" s="187"/>
+      <c r="E28" s="176"/>
+      <c r="F28" s="176"/>
       <c r="G28" s="95"/>
       <c r="H28" s="94"/>
       <c r="I28" s="93"/>
@@ -10721,11 +10718,11 @@
       <c r="C29" s="111" t="s">
         <v>401</v>
       </c>
-      <c r="D29" s="194" t="s">
+      <c r="D29" s="175" t="s">
         <v>402</v>
       </c>
-      <c r="E29" s="187"/>
-      <c r="F29" s="187"/>
+      <c r="E29" s="176"/>
+      <c r="F29" s="176"/>
       <c r="G29" s="95"/>
       <c r="H29" s="94"/>
       <c r="I29" s="93"/>
@@ -10736,9 +10733,9 @@
       <c r="A30" s="108"/>
       <c r="B30" s="109"/>
       <c r="C30" s="109"/>
-      <c r="D30" s="194"/>
-      <c r="E30" s="187"/>
-      <c r="F30" s="187"/>
+      <c r="D30" s="175"/>
+      <c r="E30" s="176"/>
+      <c r="F30" s="176"/>
       <c r="G30" s="95"/>
       <c r="H30" s="94"/>
       <c r="I30" s="93"/>
@@ -10749,9 +10746,9 @@
       <c r="A31" s="110"/>
       <c r="B31" s="120"/>
       <c r="C31" s="111"/>
-      <c r="D31" s="194"/>
-      <c r="E31" s="187"/>
-      <c r="F31" s="187"/>
+      <c r="D31" s="175"/>
+      <c r="E31" s="176"/>
+      <c r="F31" s="176"/>
       <c r="G31" s="95"/>
       <c r="H31" s="94"/>
       <c r="I31" s="93"/>
@@ -10762,9 +10759,9 @@
       <c r="A32" s="121"/>
       <c r="B32" s="122"/>
       <c r="C32" s="123"/>
-      <c r="D32" s="227"/>
-      <c r="E32" s="228"/>
-      <c r="F32" s="228"/>
+      <c r="D32" s="224"/>
+      <c r="E32" s="225"/>
+      <c r="F32" s="225"/>
       <c r="G32" s="95"/>
       <c r="H32" s="94"/>
       <c r="I32" s="93"/>
@@ -10775,9 +10772,9 @@
       <c r="A33" s="90"/>
       <c r="B33" s="99"/>
       <c r="C33" s="92"/>
-      <c r="D33" s="227"/>
-      <c r="E33" s="228"/>
-      <c r="F33" s="228"/>
+      <c r="D33" s="224"/>
+      <c r="E33" s="225"/>
+      <c r="F33" s="225"/>
       <c r="G33" s="95"/>
       <c r="H33" s="94"/>
       <c r="I33" s="93"/>
@@ -10788,9 +10785,9 @@
       <c r="A34" s="90"/>
       <c r="B34" s="99"/>
       <c r="C34" s="92"/>
-      <c r="D34" s="227"/>
-      <c r="E34" s="228"/>
-      <c r="F34" s="228"/>
+      <c r="D34" s="224"/>
+      <c r="E34" s="225"/>
+      <c r="F34" s="225"/>
       <c r="G34" s="95"/>
       <c r="H34" s="94"/>
       <c r="I34" s="93"/>
@@ -10801,9 +10798,9 @@
       <c r="A35" s="90"/>
       <c r="B35" s="99"/>
       <c r="C35" s="92"/>
-      <c r="D35" s="227"/>
-      <c r="E35" s="228"/>
-      <c r="F35" s="228"/>
+      <c r="D35" s="224"/>
+      <c r="E35" s="225"/>
+      <c r="F35" s="225"/>
       <c r="G35" s="95"/>
       <c r="H35" s="94"/>
       <c r="I35" s="93"/>
@@ -10814,9 +10811,9 @@
       <c r="A36" s="90"/>
       <c r="B36" s="99"/>
       <c r="C36" s="92"/>
-      <c r="D36" s="227"/>
-      <c r="E36" s="228"/>
-      <c r="F36" s="228"/>
+      <c r="D36" s="224"/>
+      <c r="E36" s="225"/>
+      <c r="F36" s="225"/>
       <c r="G36" s="95"/>
       <c r="H36" s="94"/>
       <c r="I36" s="93"/>
@@ -10827,9 +10824,9 @@
       <c r="A37" s="90"/>
       <c r="B37" s="99"/>
       <c r="C37" s="92"/>
-      <c r="D37" s="227"/>
-      <c r="E37" s="228"/>
-      <c r="F37" s="228"/>
+      <c r="D37" s="224"/>
+      <c r="E37" s="225"/>
+      <c r="F37" s="225"/>
       <c r="G37" s="95"/>
       <c r="H37" s="94"/>
       <c r="I37" s="93"/>
@@ -10840,9 +10837,9 @@
       <c r="A38" s="90"/>
       <c r="B38" s="99"/>
       <c r="C38" s="92"/>
-      <c r="D38" s="227"/>
-      <c r="E38" s="228"/>
-      <c r="F38" s="228"/>
+      <c r="D38" s="224"/>
+      <c r="E38" s="225"/>
+      <c r="F38" s="225"/>
       <c r="G38" s="95"/>
       <c r="H38" s="94"/>
       <c r="I38" s="93"/>
@@ -10853,9 +10850,9 @@
       <c r="A39" s="90"/>
       <c r="B39" s="99"/>
       <c r="C39" s="92"/>
-      <c r="D39" s="227"/>
-      <c r="E39" s="228"/>
-      <c r="F39" s="228"/>
+      <c r="D39" s="224"/>
+      <c r="E39" s="225"/>
+      <c r="F39" s="225"/>
       <c r="G39" s="95"/>
       <c r="H39" s="94"/>
       <c r="I39" s="93"/>
@@ -10866,9 +10863,9 @@
       <c r="A40" s="90"/>
       <c r="B40" s="99"/>
       <c r="C40" s="92"/>
-      <c r="D40" s="227"/>
-      <c r="E40" s="228"/>
-      <c r="F40" s="228"/>
+      <c r="D40" s="224"/>
+      <c r="E40" s="225"/>
+      <c r="F40" s="225"/>
       <c r="G40" s="95"/>
       <c r="H40" s="94"/>
       <c r="I40" s="93"/>
@@ -10879,9 +10876,9 @@
       <c r="A41" s="90"/>
       <c r="B41" s="99"/>
       <c r="C41" s="92"/>
-      <c r="D41" s="227"/>
-      <c r="E41" s="228"/>
-      <c r="F41" s="228"/>
+      <c r="D41" s="224"/>
+      <c r="E41" s="225"/>
+      <c r="F41" s="225"/>
       <c r="G41" s="95"/>
       <c r="H41" s="94"/>
       <c r="I41" s="93"/>
@@ -10892,9 +10889,9 @@
       <c r="A42" s="90"/>
       <c r="B42" s="99"/>
       <c r="C42" s="92"/>
-      <c r="D42" s="227"/>
-      <c r="E42" s="228"/>
-      <c r="F42" s="228"/>
+      <c r="D42" s="224"/>
+      <c r="E42" s="225"/>
+      <c r="F42" s="225"/>
       <c r="G42" s="95"/>
       <c r="H42" s="94"/>
       <c r="I42" s="93"/>
@@ -10905,9 +10902,9 @@
       <c r="A43" s="90"/>
       <c r="B43" s="99"/>
       <c r="C43" s="92"/>
-      <c r="D43" s="227"/>
-      <c r="E43" s="228"/>
-      <c r="F43" s="228"/>
+      <c r="D43" s="224"/>
+      <c r="E43" s="225"/>
+      <c r="F43" s="225"/>
       <c r="G43" s="95"/>
       <c r="H43" s="94"/>
       <c r="I43" s="93"/>
@@ -10918,9 +10915,9 @@
       <c r="A44" s="90"/>
       <c r="B44" s="99"/>
       <c r="C44" s="92"/>
-      <c r="D44" s="227"/>
-      <c r="E44" s="228"/>
-      <c r="F44" s="228"/>
+      <c r="D44" s="224"/>
+      <c r="E44" s="225"/>
+      <c r="F44" s="225"/>
       <c r="G44" s="95"/>
       <c r="H44" s="94"/>
       <c r="I44" s="93"/>
@@ -10931,9 +10928,9 @@
       <c r="A45" s="90"/>
       <c r="B45" s="99"/>
       <c r="C45" s="92"/>
-      <c r="D45" s="227"/>
-      <c r="E45" s="228"/>
-      <c r="F45" s="228"/>
+      <c r="D45" s="224"/>
+      <c r="E45" s="225"/>
+      <c r="F45" s="225"/>
       <c r="G45" s="95"/>
       <c r="H45" s="94"/>
       <c r="I45" s="93"/>
@@ -10944,9 +10941,9 @@
       <c r="A46" s="90"/>
       <c r="B46" s="99"/>
       <c r="C46" s="92"/>
-      <c r="D46" s="227"/>
-      <c r="E46" s="228"/>
-      <c r="F46" s="228"/>
+      <c r="D46" s="224"/>
+      <c r="E46" s="225"/>
+      <c r="F46" s="225"/>
       <c r="G46" s="95"/>
       <c r="H46" s="94"/>
       <c r="I46" s="93"/>
@@ -10957,9 +10954,9 @@
       <c r="A47" s="90"/>
       <c r="B47" s="99"/>
       <c r="C47" s="92"/>
-      <c r="D47" s="227"/>
-      <c r="E47" s="228"/>
-      <c r="F47" s="228"/>
+      <c r="D47" s="224"/>
+      <c r="E47" s="225"/>
+      <c r="F47" s="225"/>
       <c r="G47" s="95"/>
       <c r="H47" s="94"/>
       <c r="I47" s="93"/>
@@ -10970,9 +10967,9 @@
       <c r="A48" s="90"/>
       <c r="B48" s="99"/>
       <c r="C48" s="92"/>
-      <c r="D48" s="227"/>
-      <c r="E48" s="228"/>
-      <c r="F48" s="228"/>
+      <c r="D48" s="224"/>
+      <c r="E48" s="225"/>
+      <c r="F48" s="225"/>
       <c r="G48" s="95"/>
       <c r="H48" s="94"/>
       <c r="I48" s="93"/>
@@ -10985,6 +10982,45 @@
     <row r="52" ht="12" customHeight="1"/>
   </sheetData>
   <mergeCells count="55">
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A11:K11"/>
+    <mergeCell ref="A12:K12"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="K9:K10"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="A16:K16"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="A20:K20"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="A25:K25"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="D37:F37"/>
     <mergeCell ref="D48:F48"/>
     <mergeCell ref="A9:A10"/>
     <mergeCell ref="B9:B10"/>
@@ -11001,45 +11037,6 @@
     <mergeCell ref="D40:F40"/>
     <mergeCell ref="D41:F41"/>
     <mergeCell ref="D42:F42"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="D36:F36"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="A25:K25"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="A20:K20"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="A16:K16"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A11:K11"/>
-    <mergeCell ref="A12:K12"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="K9:K10"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="I5:K5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -11092,52 +11089,52 @@
       <c r="A3" s="70" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="170" t="s">
+      <c r="B3" s="209" t="s">
         <v>62</v>
       </c>
-      <c r="C3" s="170"/>
-      <c r="D3" s="171"/>
+      <c r="C3" s="209"/>
+      <c r="D3" s="210"/>
       <c r="E3" s="71"/>
       <c r="F3" s="71"/>
       <c r="G3" s="71"/>
       <c r="H3" s="71"/>
-      <c r="I3" s="172"/>
-      <c r="J3" s="172"/>
-      <c r="K3" s="172"/>
+      <c r="I3" s="193"/>
+      <c r="J3" s="193"/>
+      <c r="K3" s="193"/>
     </row>
     <row r="4" spans="1:11" ht="13.5" customHeight="1">
       <c r="A4" s="74" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="173" t="s">
+      <c r="B4" s="211" t="s">
         <v>404</v>
       </c>
-      <c r="C4" s="174"/>
-      <c r="D4" s="175"/>
+      <c r="C4" s="212"/>
+      <c r="D4" s="213"/>
       <c r="E4" s="71"/>
       <c r="F4" s="71"/>
       <c r="G4" s="71"/>
       <c r="H4" s="71"/>
-      <c r="I4" s="172"/>
-      <c r="J4" s="172"/>
-      <c r="K4" s="172"/>
+      <c r="I4" s="193"/>
+      <c r="J4" s="193"/>
+      <c r="K4" s="193"/>
     </row>
     <row r="5" spans="1:11" ht="12.75" customHeight="1">
       <c r="A5" s="74" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="176" t="s">
+      <c r="B5" s="214" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="177"/>
-      <c r="D5" s="178"/>
+      <c r="C5" s="215"/>
+      <c r="D5" s="216"/>
       <c r="E5" s="75"/>
       <c r="F5" s="75"/>
       <c r="G5" s="75"/>
       <c r="H5" s="75"/>
-      <c r="I5" s="179"/>
-      <c r="J5" s="179"/>
-      <c r="K5" s="179"/>
+      <c r="I5" s="217"/>
+      <c r="J5" s="217"/>
+      <c r="K5" s="217"/>
     </row>
     <row r="6" spans="1:11" ht="14.25">
       <c r="A6" s="77" t="s">
@@ -11158,9 +11155,9 @@
       <c r="F6" s="72"/>
       <c r="G6" s="72"/>
       <c r="H6" s="72"/>
-      <c r="I6" s="172"/>
-      <c r="J6" s="172"/>
-      <c r="K6" s="172"/>
+      <c r="I6" s="193"/>
+      <c r="J6" s="193"/>
+      <c r="K6" s="193"/>
     </row>
     <row r="7" spans="1:11" ht="14.25">
       <c r="A7" s="81" t="s">
@@ -11181,15 +11178,15 @@
       <c r="F7" s="85"/>
       <c r="G7" s="85"/>
       <c r="H7" s="85"/>
-      <c r="I7" s="172"/>
-      <c r="J7" s="172"/>
-      <c r="K7" s="172"/>
+      <c r="I7" s="193"/>
+      <c r="J7" s="193"/>
+      <c r="K7" s="193"/>
     </row>
     <row r="8" spans="1:11" ht="14.25">
-      <c r="A8" s="180"/>
-      <c r="B8" s="180"/>
-      <c r="C8" s="180"/>
-      <c r="D8" s="180"/>
+      <c r="A8" s="194"/>
+      <c r="B8" s="194"/>
+      <c r="C8" s="194"/>
+      <c r="D8" s="194"/>
       <c r="E8" s="72"/>
       <c r="F8" s="72"/>
       <c r="G8" s="72"/>
@@ -11199,74 +11196,74 @@
       <c r="K8" s="86"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="205" t="s">
+      <c r="A9" s="197" t="s">
         <v>71</v>
       </c>
-      <c r="B9" s="207" t="s">
+      <c r="B9" s="199" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="205" t="s">
+      <c r="C9" s="197" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="211" t="s">
+      <c r="D9" s="203" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="212"/>
-      <c r="F9" s="212"/>
-      <c r="G9" s="213"/>
-      <c r="H9" s="209" t="s">
+      <c r="E9" s="204"/>
+      <c r="F9" s="204"/>
+      <c r="G9" s="205"/>
+      <c r="H9" s="201" t="s">
         <v>75</v>
       </c>
-      <c r="I9" s="210" t="s">
+      <c r="I9" s="202" t="s">
         <v>76</v>
       </c>
-      <c r="J9" s="210" t="s">
+      <c r="J9" s="202" t="s">
         <v>77</v>
       </c>
-      <c r="K9" s="210" t="s">
+      <c r="K9" s="202" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="206"/>
-      <c r="B10" s="208"/>
-      <c r="C10" s="206"/>
-      <c r="D10" s="214"/>
-      <c r="E10" s="215"/>
-      <c r="F10" s="215"/>
-      <c r="G10" s="216"/>
-      <c r="H10" s="205"/>
-      <c r="I10" s="205"/>
-      <c r="J10" s="205"/>
-      <c r="K10" s="205"/>
+      <c r="A10" s="198"/>
+      <c r="B10" s="200"/>
+      <c r="C10" s="198"/>
+      <c r="D10" s="206"/>
+      <c r="E10" s="207"/>
+      <c r="F10" s="207"/>
+      <c r="G10" s="208"/>
+      <c r="H10" s="197"/>
+      <c r="I10" s="197"/>
+      <c r="J10" s="197"/>
+      <c r="K10" s="197"/>
     </row>
     <row r="11" spans="1:11" ht="15">
-      <c r="A11" s="181"/>
-      <c r="B11" s="181"/>
-      <c r="C11" s="181"/>
-      <c r="D11" s="181"/>
-      <c r="E11" s="181"/>
-      <c r="F11" s="181"/>
-      <c r="G11" s="181"/>
-      <c r="H11" s="181"/>
-      <c r="I11" s="181"/>
-      <c r="J11" s="181"/>
-      <c r="K11" s="182"/>
+      <c r="A11" s="195"/>
+      <c r="B11" s="195"/>
+      <c r="C11" s="195"/>
+      <c r="D11" s="195"/>
+      <c r="E11" s="195"/>
+      <c r="F11" s="195"/>
+      <c r="G11" s="195"/>
+      <c r="H11" s="195"/>
+      <c r="I11" s="195"/>
+      <c r="J11" s="195"/>
+      <c r="K11" s="196"/>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="183" t="s">
+      <c r="A12" s="184" t="s">
         <v>405</v>
       </c>
-      <c r="B12" s="184"/>
-      <c r="C12" s="184"/>
-      <c r="D12" s="184"/>
-      <c r="E12" s="184"/>
-      <c r="F12" s="184"/>
-      <c r="G12" s="184"/>
-      <c r="H12" s="184"/>
-      <c r="I12" s="184"/>
-      <c r="J12" s="184"/>
-      <c r="K12" s="185"/>
+      <c r="B12" s="185"/>
+      <c r="C12" s="185"/>
+      <c r="D12" s="185"/>
+      <c r="E12" s="185"/>
+      <c r="F12" s="185"/>
+      <c r="G12" s="185"/>
+      <c r="H12" s="185"/>
+      <c r="I12" s="185"/>
+      <c r="J12" s="185"/>
+      <c r="K12" s="186"/>
     </row>
     <row r="13" spans="1:11" ht="52.5" customHeight="1">
       <c r="A13" s="112" t="s">
@@ -11278,11 +11275,11 @@
       <c r="C13" s="91" t="s">
         <v>407</v>
       </c>
-      <c r="D13" s="231" t="s">
+      <c r="D13" s="232" t="s">
         <v>408</v>
       </c>
-      <c r="E13" s="232"/>
-      <c r="F13" s="232"/>
+      <c r="E13" s="233"/>
+      <c r="F13" s="233"/>
       <c r="G13" s="115"/>
       <c r="H13" s="114"/>
       <c r="I13" s="116"/>
@@ -11301,11 +11298,11 @@
       <c r="C14" s="91" t="s">
         <v>407</v>
       </c>
-      <c r="D14" s="231" t="s">
+      <c r="D14" s="232" t="s">
         <v>410</v>
       </c>
-      <c r="E14" s="232"/>
-      <c r="F14" s="232"/>
+      <c r="E14" s="233"/>
+      <c r="F14" s="233"/>
       <c r="G14" s="115"/>
       <c r="H14" s="114"/>
       <c r="I14" s="116"/>
@@ -11315,11 +11312,11 @@
       <c r="K14" s="91"/>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="233" t="s">
+      <c r="A15" s="234" t="s">
         <v>411</v>
       </c>
-      <c r="B15" s="234"/>
-      <c r="C15" s="234"/>
+      <c r="B15" s="235"/>
+      <c r="C15" s="235"/>
       <c r="D15" s="117"/>
       <c r="E15" s="117"/>
       <c r="F15" s="117"/>
@@ -11339,11 +11336,11 @@
       <c r="C16" s="119" t="s">
         <v>413</v>
       </c>
-      <c r="D16" s="231" t="s">
+      <c r="D16" s="232" t="s">
         <v>414</v>
       </c>
-      <c r="E16" s="232"/>
-      <c r="F16" s="232"/>
+      <c r="E16" s="233"/>
+      <c r="F16" s="233"/>
       <c r="G16" s="115"/>
       <c r="H16" s="114"/>
       <c r="I16" s="113"/>
@@ -11362,11 +11359,11 @@
       <c r="C17" s="119" t="s">
         <v>416</v>
       </c>
-      <c r="D17" s="231" t="s">
+      <c r="D17" s="232" t="s">
         <v>417</v>
       </c>
-      <c r="E17" s="232"/>
-      <c r="F17" s="232"/>
+      <c r="E17" s="233"/>
+      <c r="F17" s="233"/>
       <c r="G17" s="115"/>
       <c r="H17" s="114"/>
       <c r="I17" s="113"/>
@@ -11385,11 +11382,11 @@
       <c r="C18" s="119" t="s">
         <v>419</v>
       </c>
-      <c r="D18" s="231" t="s">
+      <c r="D18" s="232" t="s">
         <v>420</v>
       </c>
-      <c r="E18" s="232"/>
-      <c r="F18" s="232"/>
+      <c r="E18" s="233"/>
+      <c r="F18" s="233"/>
       <c r="G18" s="115"/>
       <c r="H18" s="114"/>
       <c r="I18" s="113"/>
@@ -11408,11 +11405,11 @@
       <c r="C19" s="119" t="s">
         <v>422</v>
       </c>
-      <c r="D19" s="231" t="s">
+      <c r="D19" s="232" t="s">
         <v>423</v>
       </c>
-      <c r="E19" s="232"/>
-      <c r="F19" s="232"/>
+      <c r="E19" s="233"/>
+      <c r="F19" s="233"/>
       <c r="G19" s="115"/>
       <c r="H19" s="114"/>
       <c r="I19" s="113"/>
@@ -11422,11 +11419,11 @@
       <c r="K19" s="91"/>
     </row>
     <row r="20" spans="1:11">
-      <c r="A20" s="233" t="s">
+      <c r="A20" s="234" t="s">
         <v>424</v>
       </c>
-      <c r="B20" s="234"/>
-      <c r="C20" s="234"/>
+      <c r="B20" s="235"/>
+      <c r="C20" s="235"/>
       <c r="D20" s="117"/>
       <c r="E20" s="117"/>
       <c r="F20" s="117"/>
@@ -11446,11 +11443,11 @@
       <c r="C21" s="91" t="s">
         <v>426</v>
       </c>
-      <c r="D21" s="231" t="s">
+      <c r="D21" s="232" t="s">
         <v>427</v>
       </c>
-      <c r="E21" s="235"/>
-      <c r="F21" s="235"/>
+      <c r="E21" s="236"/>
+      <c r="F21" s="236"/>
       <c r="G21" s="115"/>
       <c r="H21" s="114"/>
       <c r="I21" s="113"/>
@@ -11469,11 +11466,11 @@
       <c r="C22" s="91" t="s">
         <v>429</v>
       </c>
-      <c r="D22" s="231" t="s">
+      <c r="D22" s="232" t="s">
         <v>430</v>
       </c>
-      <c r="E22" s="235"/>
-      <c r="F22" s="235"/>
+      <c r="E22" s="236"/>
+      <c r="F22" s="236"/>
       <c r="G22" s="115"/>
       <c r="H22" s="114"/>
       <c r="I22" s="113"/>
@@ -11484,16 +11481,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="I5:K5"/>
     <mergeCell ref="I6:K6"/>
     <mergeCell ref="I7:K7"/>
     <mergeCell ref="A8:D8"/>
@@ -11507,12 +11500,16 @@
     <mergeCell ref="J9:J10"/>
     <mergeCell ref="K9:K10"/>
     <mergeCell ref="D9:G10"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="D22:F22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -11570,54 +11567,54 @@
       <c r="A3" s="106" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="170" t="s">
+      <c r="B3" s="209" t="s">
         <v>62</v>
       </c>
-      <c r="C3" s="170"/>
-      <c r="D3" s="171"/>
+      <c r="C3" s="209"/>
+      <c r="D3" s="210"/>
       <c r="E3" s="71"/>
       <c r="F3" s="71"/>
       <c r="G3" s="71"/>
       <c r="H3" s="71"/>
-      <c r="I3" s="172"/>
-      <c r="J3" s="172"/>
-      <c r="K3" s="172"/>
+      <c r="I3" s="193"/>
+      <c r="J3" s="193"/>
+      <c r="K3" s="193"/>
       <c r="L3" s="73"/>
     </row>
     <row r="4" spans="1:12" s="61" customFormat="1" ht="13.15" customHeight="1">
       <c r="A4" s="74" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="173" t="s">
+      <c r="B4" s="211" t="s">
         <v>431</v>
       </c>
-      <c r="C4" s="174"/>
-      <c r="D4" s="175"/>
+      <c r="C4" s="212"/>
+      <c r="D4" s="213"/>
       <c r="E4" s="71"/>
       <c r="F4" s="71"/>
       <c r="G4" s="71"/>
       <c r="H4" s="71"/>
-      <c r="I4" s="172"/>
-      <c r="J4" s="172"/>
-      <c r="K4" s="172"/>
+      <c r="I4" s="193"/>
+      <c r="J4" s="193"/>
+      <c r="K4" s="193"/>
       <c r="L4" s="73"/>
     </row>
     <row r="5" spans="1:12" s="62" customFormat="1" ht="25.5">
       <c r="A5" s="107" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="176" t="s">
+      <c r="B5" s="214" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="177"/>
-      <c r="D5" s="178"/>
+      <c r="C5" s="215"/>
+      <c r="D5" s="216"/>
       <c r="E5" s="75"/>
       <c r="F5" s="75"/>
       <c r="G5" s="75"/>
       <c r="H5" s="75"/>
-      <c r="I5" s="179"/>
-      <c r="J5" s="179"/>
-      <c r="K5" s="179"/>
+      <c r="I5" s="217"/>
+      <c r="J5" s="217"/>
+      <c r="K5" s="217"/>
       <c r="L5" s="76"/>
     </row>
     <row r="6" spans="1:12" s="61" customFormat="1" ht="15" customHeight="1">
@@ -11639,9 +11636,9 @@
       <c r="F6" s="72"/>
       <c r="G6" s="72"/>
       <c r="H6" s="72"/>
-      <c r="I6" s="172"/>
-      <c r="J6" s="172"/>
-      <c r="K6" s="172"/>
+      <c r="I6" s="193"/>
+      <c r="J6" s="193"/>
+      <c r="K6" s="193"/>
       <c r="L6" s="73"/>
     </row>
     <row r="7" spans="1:12" s="61" customFormat="1" ht="15" customHeight="1">
@@ -11663,16 +11660,16 @@
       <c r="F7" s="85"/>
       <c r="G7" s="85"/>
       <c r="H7" s="85"/>
-      <c r="I7" s="172"/>
-      <c r="J7" s="172"/>
-      <c r="K7" s="172"/>
+      <c r="I7" s="193"/>
+      <c r="J7" s="193"/>
+      <c r="K7" s="193"/>
       <c r="L7" s="73"/>
     </row>
     <row r="8" spans="1:12" s="61" customFormat="1" ht="15" customHeight="1">
-      <c r="A8" s="180"/>
-      <c r="B8" s="180"/>
-      <c r="C8" s="180"/>
-      <c r="D8" s="180"/>
+      <c r="A8" s="194"/>
+      <c r="B8" s="194"/>
+      <c r="C8" s="194"/>
+      <c r="D8" s="194"/>
       <c r="F8" s="72"/>
       <c r="G8" s="72"/>
       <c r="H8" s="72"/>
@@ -11682,76 +11679,76 @@
       <c r="L8" s="73"/>
     </row>
     <row r="9" spans="1:12" s="63" customFormat="1" ht="12" customHeight="1">
-      <c r="A9" s="205" t="s">
+      <c r="A9" s="197" t="s">
         <v>71</v>
       </c>
-      <c r="B9" s="207" t="s">
+      <c r="B9" s="199" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="205" t="s">
+      <c r="C9" s="197" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="211" t="s">
+      <c r="D9" s="203" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="212"/>
-      <c r="F9" s="212"/>
-      <c r="G9" s="213"/>
-      <c r="H9" s="209" t="s">
+      <c r="E9" s="204"/>
+      <c r="F9" s="204"/>
+      <c r="G9" s="205"/>
+      <c r="H9" s="201" t="s">
         <v>75</v>
       </c>
-      <c r="I9" s="210" t="s">
+      <c r="I9" s="202" t="s">
         <v>76</v>
       </c>
-      <c r="J9" s="210" t="s">
+      <c r="J9" s="202" t="s">
         <v>77</v>
       </c>
-      <c r="K9" s="210" t="s">
+      <c r="K9" s="202" t="s">
         <v>78</v>
       </c>
       <c r="L9" s="87"/>
     </row>
     <row r="10" spans="1:12" s="61" customFormat="1" ht="12" customHeight="1">
-      <c r="A10" s="206"/>
-      <c r="B10" s="208"/>
-      <c r="C10" s="206"/>
-      <c r="D10" s="214"/>
-      <c r="E10" s="215"/>
-      <c r="F10" s="215"/>
-      <c r="G10" s="216"/>
-      <c r="H10" s="205"/>
-      <c r="I10" s="205"/>
-      <c r="J10" s="205"/>
-      <c r="K10" s="205"/>
+      <c r="A10" s="198"/>
+      <c r="B10" s="200"/>
+      <c r="C10" s="198"/>
+      <c r="D10" s="206"/>
+      <c r="E10" s="207"/>
+      <c r="F10" s="207"/>
+      <c r="G10" s="208"/>
+      <c r="H10" s="197"/>
+      <c r="I10" s="197"/>
+      <c r="J10" s="197"/>
+      <c r="K10" s="197"/>
       <c r="L10" s="73"/>
     </row>
     <row r="11" spans="1:12" s="64" customFormat="1" ht="15">
-      <c r="A11" s="181"/>
-      <c r="B11" s="181"/>
-      <c r="C11" s="181"/>
-      <c r="D11" s="181"/>
-      <c r="E11" s="181"/>
-      <c r="F11" s="181"/>
-      <c r="G11" s="181"/>
-      <c r="H11" s="181"/>
-      <c r="I11" s="181"/>
-      <c r="J11" s="181"/>
-      <c r="K11" s="182"/>
+      <c r="A11" s="195"/>
+      <c r="B11" s="195"/>
+      <c r="C11" s="195"/>
+      <c r="D11" s="195"/>
+      <c r="E11" s="195"/>
+      <c r="F11" s="195"/>
+      <c r="G11" s="195"/>
+      <c r="H11" s="195"/>
+      <c r="I11" s="195"/>
+      <c r="J11" s="195"/>
+      <c r="K11" s="196"/>
     </row>
     <row r="12" spans="1:12" s="65" customFormat="1" ht="29.45" customHeight="1">
-      <c r="A12" s="236" t="s">
+      <c r="A12" s="237" t="s">
         <v>432</v>
       </c>
-      <c r="B12" s="184"/>
-      <c r="C12" s="184"/>
-      <c r="D12" s="184"/>
-      <c r="E12" s="184"/>
-      <c r="F12" s="184"/>
-      <c r="G12" s="184"/>
-      <c r="H12" s="184"/>
-      <c r="I12" s="184"/>
-      <c r="J12" s="184"/>
-      <c r="K12" s="185"/>
+      <c r="B12" s="185"/>
+      <c r="C12" s="185"/>
+      <c r="D12" s="185"/>
+      <c r="E12" s="185"/>
+      <c r="F12" s="185"/>
+      <c r="G12" s="185"/>
+      <c r="H12" s="185"/>
+      <c r="I12" s="185"/>
+      <c r="J12" s="185"/>
+      <c r="K12" s="186"/>
     </row>
     <row r="13" spans="1:12" s="65" customFormat="1" ht="69" customHeight="1" outlineLevel="1">
       <c r="A13" s="108" t="s">
@@ -11763,11 +11760,11 @@
       <c r="C13" s="109" t="s">
         <v>434</v>
       </c>
-      <c r="D13" s="194" t="s">
+      <c r="D13" s="175" t="s">
         <v>435</v>
       </c>
-      <c r="E13" s="187"/>
-      <c r="F13" s="187"/>
+      <c r="E13" s="176"/>
+      <c r="F13" s="176"/>
       <c r="G13" s="95"/>
       <c r="H13" s="94"/>
       <c r="I13" s="96"/>
@@ -11784,11 +11781,11 @@
       <c r="C14" s="111" t="s">
         <v>437</v>
       </c>
-      <c r="D14" s="194" t="s">
+      <c r="D14" s="175" t="s">
         <v>438</v>
       </c>
-      <c r="E14" s="187"/>
-      <c r="F14" s="187"/>
+      <c r="E14" s="176"/>
+      <c r="F14" s="176"/>
       <c r="G14" s="95"/>
       <c r="H14" s="94"/>
       <c r="I14" s="93"/>
@@ -11805,11 +11802,11 @@
       <c r="C15" s="109" t="s">
         <v>440</v>
       </c>
-      <c r="D15" s="194" t="s">
+      <c r="D15" s="175" t="s">
         <v>441</v>
       </c>
-      <c r="E15" s="187"/>
-      <c r="F15" s="187"/>
+      <c r="E15" s="176"/>
+      <c r="F15" s="176"/>
       <c r="G15" s="95"/>
       <c r="H15" s="94"/>
       <c r="I15" s="93"/>
@@ -11817,19 +11814,19 @@
       <c r="K15" s="92"/>
     </row>
     <row r="16" spans="1:12" ht="32.450000000000003" customHeight="1">
-      <c r="A16" s="236" t="s">
+      <c r="A16" s="237" t="s">
         <v>442</v>
       </c>
-      <c r="B16" s="184"/>
-      <c r="C16" s="184"/>
-      <c r="D16" s="184"/>
-      <c r="E16" s="184"/>
-      <c r="F16" s="184"/>
-      <c r="G16" s="184"/>
-      <c r="H16" s="184"/>
-      <c r="I16" s="184"/>
-      <c r="J16" s="184"/>
-      <c r="K16" s="185"/>
+      <c r="B16" s="185"/>
+      <c r="C16" s="185"/>
+      <c r="D16" s="185"/>
+      <c r="E16" s="185"/>
+      <c r="F16" s="185"/>
+      <c r="G16" s="185"/>
+      <c r="H16" s="185"/>
+      <c r="I16" s="185"/>
+      <c r="J16" s="185"/>
+      <c r="K16" s="186"/>
     </row>
     <row r="17" spans="1:11" ht="70.150000000000006" customHeight="1">
       <c r="A17" s="110" t="s">
@@ -11841,11 +11838,11 @@
       <c r="C17" s="111" t="s">
         <v>444</v>
       </c>
-      <c r="D17" s="194" t="s">
+      <c r="D17" s="175" t="s">
         <v>445</v>
       </c>
-      <c r="E17" s="187"/>
-      <c r="F17" s="187"/>
+      <c r="E17" s="176"/>
+      <c r="F17" s="176"/>
       <c r="G17" s="95"/>
       <c r="H17" s="94"/>
       <c r="I17" s="93"/>
@@ -11862,11 +11859,11 @@
       <c r="C18" s="109" t="s">
         <v>447</v>
       </c>
-      <c r="D18" s="194" t="s">
+      <c r="D18" s="175" t="s">
         <v>448</v>
       </c>
-      <c r="E18" s="187"/>
-      <c r="F18" s="187"/>
+      <c r="E18" s="176"/>
+      <c r="F18" s="176"/>
       <c r="G18" s="95"/>
       <c r="H18" s="94"/>
       <c r="I18" s="93"/>
@@ -11883,11 +11880,11 @@
       <c r="C19" s="111" t="s">
         <v>450</v>
       </c>
-      <c r="D19" s="194" t="s">
+      <c r="D19" s="175" t="s">
         <v>451</v>
       </c>
-      <c r="E19" s="187"/>
-      <c r="F19" s="187"/>
+      <c r="E19" s="176"/>
+      <c r="F19" s="176"/>
       <c r="G19" s="95"/>
       <c r="H19" s="94"/>
       <c r="I19" s="93"/>
@@ -11904,11 +11901,11 @@
       <c r="C20" s="109" t="s">
         <v>453</v>
       </c>
-      <c r="D20" s="194" t="s">
+      <c r="D20" s="175" t="s">
         <v>454</v>
       </c>
-      <c r="E20" s="187"/>
-      <c r="F20" s="187"/>
+      <c r="E20" s="176"/>
+      <c r="F20" s="176"/>
       <c r="G20" s="95"/>
       <c r="H20" s="94"/>
       <c r="I20" s="93"/>
@@ -11925,11 +11922,11 @@
       <c r="C21" s="111" t="s">
         <v>456</v>
       </c>
-      <c r="D21" s="194" t="s">
+      <c r="D21" s="175" t="s">
         <v>457</v>
       </c>
-      <c r="E21" s="187"/>
-      <c r="F21" s="187"/>
+      <c r="E21" s="176"/>
+      <c r="F21" s="176"/>
       <c r="G21" s="95"/>
       <c r="H21" s="94"/>
       <c r="I21" s="93"/>
@@ -11937,19 +11934,19 @@
       <c r="K21" s="92"/>
     </row>
     <row r="22" spans="1:11" ht="31.9" customHeight="1">
-      <c r="A22" s="236" t="s">
+      <c r="A22" s="237" t="s">
         <v>458</v>
       </c>
-      <c r="B22" s="184"/>
-      <c r="C22" s="184"/>
-      <c r="D22" s="184"/>
-      <c r="E22" s="184"/>
-      <c r="F22" s="184"/>
-      <c r="G22" s="184"/>
-      <c r="H22" s="184"/>
-      <c r="I22" s="184"/>
-      <c r="J22" s="184"/>
-      <c r="K22" s="185"/>
+      <c r="B22" s="185"/>
+      <c r="C22" s="185"/>
+      <c r="D22" s="185"/>
+      <c r="E22" s="185"/>
+      <c r="F22" s="185"/>
+      <c r="G22" s="185"/>
+      <c r="H22" s="185"/>
+      <c r="I22" s="185"/>
+      <c r="J22" s="185"/>
+      <c r="K22" s="186"/>
     </row>
     <row r="23" spans="1:11" ht="70.150000000000006" customHeight="1">
       <c r="A23" s="108" t="s">
@@ -11961,11 +11958,11 @@
       <c r="C23" s="109" t="s">
         <v>460</v>
       </c>
-      <c r="D23" s="194" t="s">
+      <c r="D23" s="175" t="s">
         <v>461</v>
       </c>
-      <c r="E23" s="187"/>
-      <c r="F23" s="187"/>
+      <c r="E23" s="176"/>
+      <c r="F23" s="176"/>
       <c r="G23" s="95"/>
       <c r="H23" s="94"/>
       <c r="I23" s="93"/>
@@ -11982,11 +11979,11 @@
       <c r="C24" s="111" t="s">
         <v>463</v>
       </c>
-      <c r="D24" s="194" t="s">
+      <c r="D24" s="175" t="s">
         <v>464</v>
       </c>
-      <c r="E24" s="187"/>
-      <c r="F24" s="187"/>
+      <c r="E24" s="176"/>
+      <c r="F24" s="176"/>
       <c r="G24" s="95"/>
       <c r="H24" s="94"/>
       <c r="I24" s="93"/>
@@ -12003,11 +12000,11 @@
       <c r="C25" s="109" t="s">
         <v>466</v>
       </c>
-      <c r="D25" s="194" t="s">
+      <c r="D25" s="175" t="s">
         <v>467</v>
       </c>
-      <c r="E25" s="187"/>
-      <c r="F25" s="187"/>
+      <c r="E25" s="176"/>
+      <c r="F25" s="176"/>
       <c r="G25" s="95"/>
       <c r="H25" s="94"/>
       <c r="I25" s="93"/>
@@ -12024,11 +12021,11 @@
       <c r="C26" s="111" t="s">
         <v>469</v>
       </c>
-      <c r="D26" s="194" t="s">
+      <c r="D26" s="175" t="s">
         <v>470</v>
       </c>
-      <c r="E26" s="187"/>
-      <c r="F26" s="187"/>
+      <c r="E26" s="176"/>
+      <c r="F26" s="176"/>
       <c r="G26" s="95"/>
       <c r="H26" s="94"/>
       <c r="I26" s="93"/>
@@ -12045,11 +12042,11 @@
       <c r="C27" s="109" t="s">
         <v>472</v>
       </c>
-      <c r="D27" s="194" t="s">
+      <c r="D27" s="175" t="s">
         <v>473</v>
       </c>
-      <c r="E27" s="187"/>
-      <c r="F27" s="187"/>
+      <c r="E27" s="176"/>
+      <c r="F27" s="176"/>
       <c r="G27" s="95"/>
       <c r="H27" s="94"/>
       <c r="I27" s="93"/>
@@ -12066,11 +12063,11 @@
       <c r="C28" s="111" t="s">
         <v>475</v>
       </c>
-      <c r="D28" s="194" t="s">
+      <c r="D28" s="175" t="s">
         <v>476</v>
       </c>
-      <c r="E28" s="187"/>
-      <c r="F28" s="187"/>
+      <c r="E28" s="176"/>
+      <c r="F28" s="176"/>
       <c r="G28" s="95"/>
       <c r="H28" s="94"/>
       <c r="I28" s="93"/>
@@ -12087,11 +12084,11 @@
       <c r="C29" s="109" t="s">
         <v>478</v>
       </c>
-      <c r="D29" s="194" t="s">
+      <c r="D29" s="175" t="s">
         <v>479</v>
       </c>
-      <c r="E29" s="187"/>
-      <c r="F29" s="187"/>
+      <c r="E29" s="176"/>
+      <c r="F29" s="176"/>
       <c r="G29" s="95"/>
       <c r="H29" s="94"/>
       <c r="I29" s="93"/>
@@ -12099,19 +12096,19 @@
       <c r="K29" s="92"/>
     </row>
     <row r="30" spans="1:11" ht="31.9" customHeight="1">
-      <c r="A30" s="236" t="s">
+      <c r="A30" s="237" t="s">
         <v>480</v>
       </c>
-      <c r="B30" s="184"/>
-      <c r="C30" s="184"/>
-      <c r="D30" s="184"/>
-      <c r="E30" s="184"/>
-      <c r="F30" s="184"/>
-      <c r="G30" s="184"/>
-      <c r="H30" s="184"/>
-      <c r="I30" s="184"/>
-      <c r="J30" s="184"/>
-      <c r="K30" s="185"/>
+      <c r="B30" s="185"/>
+      <c r="C30" s="185"/>
+      <c r="D30" s="185"/>
+      <c r="E30" s="185"/>
+      <c r="F30" s="185"/>
+      <c r="G30" s="185"/>
+      <c r="H30" s="185"/>
+      <c r="I30" s="185"/>
+      <c r="J30" s="185"/>
+      <c r="K30" s="186"/>
     </row>
     <row r="31" spans="1:11" ht="70.150000000000006" customHeight="1">
       <c r="A31" s="110" t="s">
@@ -12123,11 +12120,11 @@
       <c r="C31" s="111" t="s">
         <v>482</v>
       </c>
-      <c r="D31" s="194" t="s">
+      <c r="D31" s="175" t="s">
         <v>483</v>
       </c>
-      <c r="E31" s="187"/>
-      <c r="F31" s="187"/>
+      <c r="E31" s="176"/>
+      <c r="F31" s="176"/>
       <c r="G31" s="95"/>
       <c r="H31" s="94"/>
       <c r="I31" s="93"/>
@@ -12144,11 +12141,11 @@
       <c r="C32" s="109" t="s">
         <v>485</v>
       </c>
-      <c r="D32" s="194" t="s">
+      <c r="D32" s="175" t="s">
         <v>486</v>
       </c>
-      <c r="E32" s="187"/>
-      <c r="F32" s="187"/>
+      <c r="E32" s="176"/>
+      <c r="F32" s="176"/>
       <c r="G32" s="95"/>
       <c r="H32" s="94"/>
       <c r="I32" s="93"/>
@@ -12159,9 +12156,9 @@
       <c r="A33" s="90"/>
       <c r="B33" s="99"/>
       <c r="C33" s="92"/>
-      <c r="D33" s="227"/>
-      <c r="E33" s="228"/>
-      <c r="F33" s="228"/>
+      <c r="D33" s="224"/>
+      <c r="E33" s="225"/>
+      <c r="F33" s="225"/>
       <c r="G33" s="95"/>
       <c r="H33" s="94"/>
       <c r="I33" s="93"/>
@@ -12172,9 +12169,9 @@
       <c r="A34" s="90"/>
       <c r="B34" s="99"/>
       <c r="C34" s="92"/>
-      <c r="D34" s="227"/>
-      <c r="E34" s="228"/>
-      <c r="F34" s="228"/>
+      <c r="D34" s="224"/>
+      <c r="E34" s="225"/>
+      <c r="F34" s="225"/>
       <c r="G34" s="95"/>
       <c r="H34" s="94"/>
       <c r="I34" s="93"/>
@@ -12185,9 +12182,9 @@
       <c r="A35" s="90"/>
       <c r="B35" s="99"/>
       <c r="C35" s="92"/>
-      <c r="D35" s="227"/>
-      <c r="E35" s="228"/>
-      <c r="F35" s="228"/>
+      <c r="D35" s="224"/>
+      <c r="E35" s="225"/>
+      <c r="F35" s="225"/>
       <c r="G35" s="95"/>
       <c r="H35" s="94"/>
       <c r="I35" s="93"/>
@@ -12198,9 +12195,9 @@
       <c r="A36" s="90"/>
       <c r="B36" s="99"/>
       <c r="C36" s="92"/>
-      <c r="D36" s="227"/>
-      <c r="E36" s="228"/>
-      <c r="F36" s="228"/>
+      <c r="D36" s="224"/>
+      <c r="E36" s="225"/>
+      <c r="F36" s="225"/>
       <c r="G36" s="95"/>
       <c r="H36" s="94"/>
       <c r="I36" s="93"/>
@@ -12211,9 +12208,9 @@
       <c r="A37" s="90"/>
       <c r="B37" s="99"/>
       <c r="C37" s="92"/>
-      <c r="D37" s="227"/>
-      <c r="E37" s="228"/>
-      <c r="F37" s="228"/>
+      <c r="D37" s="224"/>
+      <c r="E37" s="225"/>
+      <c r="F37" s="225"/>
       <c r="G37" s="95"/>
       <c r="H37" s="94"/>
       <c r="I37" s="93"/>
@@ -12224,9 +12221,9 @@
       <c r="A38" s="90"/>
       <c r="B38" s="99"/>
       <c r="C38" s="92"/>
-      <c r="D38" s="227"/>
-      <c r="E38" s="228"/>
-      <c r="F38" s="228"/>
+      <c r="D38" s="224"/>
+      <c r="E38" s="225"/>
+      <c r="F38" s="225"/>
       <c r="G38" s="95"/>
       <c r="H38" s="94"/>
       <c r="I38" s="93"/>
@@ -12237,9 +12234,9 @@
       <c r="A39" s="90"/>
       <c r="B39" s="99"/>
       <c r="C39" s="92"/>
-      <c r="D39" s="227"/>
-      <c r="E39" s="228"/>
-      <c r="F39" s="228"/>
+      <c r="D39" s="224"/>
+      <c r="E39" s="225"/>
+      <c r="F39" s="225"/>
       <c r="G39" s="95"/>
       <c r="H39" s="94"/>
       <c r="I39" s="93"/>
@@ -12250,9 +12247,9 @@
       <c r="A40" s="90"/>
       <c r="B40" s="99"/>
       <c r="C40" s="92"/>
-      <c r="D40" s="227"/>
-      <c r="E40" s="228"/>
-      <c r="F40" s="228"/>
+      <c r="D40" s="224"/>
+      <c r="E40" s="225"/>
+      <c r="F40" s="225"/>
       <c r="G40" s="95"/>
       <c r="H40" s="94"/>
       <c r="I40" s="93"/>
@@ -12263,9 +12260,9 @@
       <c r="A41" s="90"/>
       <c r="B41" s="99"/>
       <c r="C41" s="92"/>
-      <c r="D41" s="227"/>
-      <c r="E41" s="228"/>
-      <c r="F41" s="228"/>
+      <c r="D41" s="224"/>
+      <c r="E41" s="225"/>
+      <c r="F41" s="225"/>
       <c r="G41" s="95"/>
       <c r="H41" s="94"/>
       <c r="I41" s="93"/>
@@ -12276,9 +12273,9 @@
       <c r="A42" s="90"/>
       <c r="B42" s="99"/>
       <c r="C42" s="92"/>
-      <c r="D42" s="227"/>
-      <c r="E42" s="228"/>
-      <c r="F42" s="228"/>
+      <c r="D42" s="224"/>
+      <c r="E42" s="225"/>
+      <c r="F42" s="225"/>
       <c r="G42" s="95"/>
       <c r="H42" s="94"/>
       <c r="I42" s="93"/>
@@ -12289,9 +12286,9 @@
       <c r="A43" s="90"/>
       <c r="B43" s="99"/>
       <c r="C43" s="92"/>
-      <c r="D43" s="227"/>
-      <c r="E43" s="228"/>
-      <c r="F43" s="228"/>
+      <c r="D43" s="224"/>
+      <c r="E43" s="225"/>
+      <c r="F43" s="225"/>
       <c r="G43" s="95"/>
       <c r="H43" s="94"/>
       <c r="I43" s="93"/>
@@ -12302,9 +12299,9 @@
       <c r="A44" s="90"/>
       <c r="B44" s="99"/>
       <c r="C44" s="92"/>
-      <c r="D44" s="227"/>
-      <c r="E44" s="228"/>
-      <c r="F44" s="228"/>
+      <c r="D44" s="224"/>
+      <c r="E44" s="225"/>
+      <c r="F44" s="225"/>
       <c r="G44" s="95"/>
       <c r="H44" s="94"/>
       <c r="I44" s="93"/>
@@ -12315,9 +12312,9 @@
       <c r="A45" s="90"/>
       <c r="B45" s="99"/>
       <c r="C45" s="92"/>
-      <c r="D45" s="227"/>
-      <c r="E45" s="228"/>
-      <c r="F45" s="228"/>
+      <c r="D45" s="224"/>
+      <c r="E45" s="225"/>
+      <c r="F45" s="225"/>
       <c r="G45" s="95"/>
       <c r="H45" s="94"/>
       <c r="I45" s="93"/>
@@ -12328,9 +12325,9 @@
       <c r="A46" s="90"/>
       <c r="B46" s="99"/>
       <c r="C46" s="92"/>
-      <c r="D46" s="227"/>
-      <c r="E46" s="228"/>
-      <c r="F46" s="228"/>
+      <c r="D46" s="224"/>
+      <c r="E46" s="225"/>
+      <c r="F46" s="225"/>
       <c r="G46" s="95"/>
       <c r="H46" s="94"/>
       <c r="I46" s="93"/>
@@ -12341,9 +12338,9 @@
       <c r="A47" s="90"/>
       <c r="B47" s="99"/>
       <c r="C47" s="92"/>
-      <c r="D47" s="227"/>
-      <c r="E47" s="228"/>
-      <c r="F47" s="228"/>
+      <c r="D47" s="224"/>
+      <c r="E47" s="225"/>
+      <c r="F47" s="225"/>
       <c r="G47" s="95"/>
       <c r="H47" s="94"/>
       <c r="I47" s="93"/>
@@ -12354,9 +12351,9 @@
       <c r="A48" s="90"/>
       <c r="B48" s="99"/>
       <c r="C48" s="92"/>
-      <c r="D48" s="227"/>
-      <c r="E48" s="228"/>
-      <c r="F48" s="228"/>
+      <c r="D48" s="224"/>
+      <c r="E48" s="225"/>
+      <c r="F48" s="225"/>
       <c r="G48" s="95"/>
       <c r="H48" s="94"/>
       <c r="I48" s="93"/>
@@ -12367,9 +12364,9 @@
       <c r="A49" s="90"/>
       <c r="B49" s="99"/>
       <c r="C49" s="92"/>
-      <c r="D49" s="227"/>
-      <c r="E49" s="228"/>
-      <c r="F49" s="228"/>
+      <c r="D49" s="224"/>
+      <c r="E49" s="225"/>
+      <c r="F49" s="225"/>
       <c r="G49" s="95"/>
       <c r="H49" s="94"/>
       <c r="I49" s="93"/>
@@ -12380,9 +12377,9 @@
       <c r="A50" s="90"/>
       <c r="B50" s="99"/>
       <c r="C50" s="92"/>
-      <c r="D50" s="227"/>
-      <c r="E50" s="228"/>
-      <c r="F50" s="228"/>
+      <c r="D50" s="224"/>
+      <c r="E50" s="225"/>
+      <c r="F50" s="225"/>
       <c r="G50" s="95"/>
       <c r="H50" s="94"/>
       <c r="I50" s="93"/>
@@ -12393,9 +12390,9 @@
       <c r="A51" s="90"/>
       <c r="B51" s="99"/>
       <c r="C51" s="92"/>
-      <c r="D51" s="227"/>
-      <c r="E51" s="228"/>
-      <c r="F51" s="228"/>
+      <c r="D51" s="224"/>
+      <c r="E51" s="225"/>
+      <c r="F51" s="225"/>
       <c r="G51" s="95"/>
       <c r="H51" s="94"/>
       <c r="I51" s="93"/>
@@ -12406,9 +12403,9 @@
       <c r="A52" s="90"/>
       <c r="B52" s="99"/>
       <c r="C52" s="92"/>
-      <c r="D52" s="227"/>
-      <c r="E52" s="228"/>
-      <c r="F52" s="228"/>
+      <c r="D52" s="224"/>
+      <c r="E52" s="225"/>
+      <c r="F52" s="225"/>
       <c r="G52" s="95"/>
       <c r="H52" s="94"/>
       <c r="I52" s="93"/>
@@ -12419,9 +12416,9 @@
       <c r="A53" s="90"/>
       <c r="B53" s="99"/>
       <c r="C53" s="92"/>
-      <c r="D53" s="227"/>
-      <c r="E53" s="228"/>
-      <c r="F53" s="228"/>
+      <c r="D53" s="224"/>
+      <c r="E53" s="225"/>
+      <c r="F53" s="225"/>
       <c r="G53" s="95"/>
       <c r="H53" s="94"/>
       <c r="I53" s="93"/>
@@ -12432,9 +12429,9 @@
       <c r="A54" s="90"/>
       <c r="B54" s="99"/>
       <c r="C54" s="92"/>
-      <c r="D54" s="227"/>
-      <c r="E54" s="228"/>
-      <c r="F54" s="228"/>
+      <c r="D54" s="224"/>
+      <c r="E54" s="225"/>
+      <c r="F54" s="225"/>
       <c r="G54" s="95"/>
       <c r="H54" s="94"/>
       <c r="I54" s="93"/>
@@ -12445,9 +12442,9 @@
       <c r="A55" s="90"/>
       <c r="B55" s="99"/>
       <c r="C55" s="92"/>
-      <c r="D55" s="227"/>
-      <c r="E55" s="228"/>
-      <c r="F55" s="228"/>
+      <c r="D55" s="224"/>
+      <c r="E55" s="225"/>
+      <c r="F55" s="225"/>
       <c r="G55" s="95"/>
       <c r="H55" s="94"/>
       <c r="I55" s="93"/>
@@ -12458,9 +12455,9 @@
       <c r="A56" s="90"/>
       <c r="B56" s="99"/>
       <c r="C56" s="92"/>
-      <c r="D56" s="227"/>
-      <c r="E56" s="228"/>
-      <c r="F56" s="228"/>
+      <c r="D56" s="224"/>
+      <c r="E56" s="225"/>
+      <c r="F56" s="225"/>
       <c r="G56" s="95"/>
       <c r="H56" s="94"/>
       <c r="I56" s="93"/>
@@ -12471,9 +12468,9 @@
       <c r="A57" s="90"/>
       <c r="B57" s="99"/>
       <c r="C57" s="92"/>
-      <c r="D57" s="227"/>
-      <c r="E57" s="228"/>
-      <c r="F57" s="228"/>
+      <c r="D57" s="224"/>
+      <c r="E57" s="225"/>
+      <c r="F57" s="225"/>
       <c r="G57" s="95"/>
       <c r="H57" s="94"/>
       <c r="I57" s="93"/>
@@ -12484,9 +12481,9 @@
       <c r="A58" s="90"/>
       <c r="B58" s="99"/>
       <c r="C58" s="92"/>
-      <c r="D58" s="227"/>
-      <c r="E58" s="228"/>
-      <c r="F58" s="228"/>
+      <c r="D58" s="224"/>
+      <c r="E58" s="225"/>
+      <c r="F58" s="225"/>
       <c r="G58" s="95"/>
       <c r="H58" s="94"/>
       <c r="I58" s="93"/>
@@ -12497,9 +12494,9 @@
       <c r="A59" s="90"/>
       <c r="B59" s="99"/>
       <c r="C59" s="92"/>
-      <c r="D59" s="227"/>
-      <c r="E59" s="228"/>
-      <c r="F59" s="228"/>
+      <c r="D59" s="224"/>
+      <c r="E59" s="225"/>
+      <c r="F59" s="225"/>
       <c r="G59" s="95"/>
       <c r="H59" s="94"/>
       <c r="I59" s="93"/>
@@ -12510,9 +12507,9 @@
       <c r="A60" s="90"/>
       <c r="B60" s="99"/>
       <c r="C60" s="92"/>
-      <c r="D60" s="227"/>
-      <c r="E60" s="228"/>
-      <c r="F60" s="228"/>
+      <c r="D60" s="224"/>
+      <c r="E60" s="225"/>
+      <c r="F60" s="225"/>
       <c r="G60" s="95"/>
       <c r="H60" s="94"/>
       <c r="I60" s="93"/>
@@ -12523,9 +12520,9 @@
       <c r="A61" s="90"/>
       <c r="B61" s="99"/>
       <c r="C61" s="92"/>
-      <c r="D61" s="227"/>
-      <c r="E61" s="228"/>
-      <c r="F61" s="228"/>
+      <c r="D61" s="224"/>
+      <c r="E61" s="225"/>
+      <c r="F61" s="225"/>
       <c r="G61" s="95"/>
       <c r="H61" s="94"/>
       <c r="I61" s="93"/>
@@ -12536,9 +12533,9 @@
       <c r="A62" s="90"/>
       <c r="B62" s="99"/>
       <c r="C62" s="92"/>
-      <c r="D62" s="227"/>
-      <c r="E62" s="228"/>
-      <c r="F62" s="228"/>
+      <c r="D62" s="224"/>
+      <c r="E62" s="225"/>
+      <c r="F62" s="225"/>
       <c r="G62" s="95"/>
       <c r="H62" s="94"/>
       <c r="I62" s="93"/>
@@ -12549,9 +12546,9 @@
       <c r="A63" s="90"/>
       <c r="B63" s="99"/>
       <c r="C63" s="92"/>
-      <c r="D63" s="227"/>
-      <c r="E63" s="228"/>
-      <c r="F63" s="228"/>
+      <c r="D63" s="224"/>
+      <c r="E63" s="225"/>
+      <c r="F63" s="225"/>
       <c r="G63" s="95"/>
       <c r="H63" s="94"/>
       <c r="I63" s="93"/>
@@ -12562,9 +12559,9 @@
       <c r="A64" s="90"/>
       <c r="B64" s="99"/>
       <c r="C64" s="92"/>
-      <c r="D64" s="227"/>
-      <c r="E64" s="228"/>
-      <c r="F64" s="228"/>
+      <c r="D64" s="224"/>
+      <c r="E64" s="225"/>
+      <c r="F64" s="225"/>
       <c r="G64" s="95"/>
       <c r="H64" s="94"/>
       <c r="I64" s="93"/>
@@ -12575,9 +12572,9 @@
       <c r="A65" s="90"/>
       <c r="B65" s="99"/>
       <c r="C65" s="92"/>
-      <c r="D65" s="227"/>
-      <c r="E65" s="228"/>
-      <c r="F65" s="228"/>
+      <c r="D65" s="224"/>
+      <c r="E65" s="225"/>
+      <c r="F65" s="225"/>
       <c r="G65" s="95"/>
       <c r="H65" s="94"/>
       <c r="I65" s="93"/>
@@ -12588,9 +12585,9 @@
       <c r="A66" s="90"/>
       <c r="B66" s="99"/>
       <c r="C66" s="92"/>
-      <c r="D66" s="227"/>
-      <c r="E66" s="228"/>
-      <c r="F66" s="228"/>
+      <c r="D66" s="224"/>
+      <c r="E66" s="225"/>
+      <c r="F66" s="225"/>
       <c r="G66" s="95"/>
       <c r="H66" s="94"/>
       <c r="I66" s="93"/>
@@ -12601,9 +12598,9 @@
       <c r="A67" s="90"/>
       <c r="B67" s="99"/>
       <c r="C67" s="92"/>
-      <c r="D67" s="227"/>
-      <c r="E67" s="228"/>
-      <c r="F67" s="228"/>
+      <c r="D67" s="224"/>
+      <c r="E67" s="225"/>
+      <c r="F67" s="225"/>
       <c r="G67" s="95"/>
       <c r="H67" s="94"/>
       <c r="I67" s="93"/>
@@ -12614,9 +12611,9 @@
       <c r="A68" s="90"/>
       <c r="B68" s="99"/>
       <c r="C68" s="92"/>
-      <c r="D68" s="227"/>
-      <c r="E68" s="228"/>
-      <c r="F68" s="228"/>
+      <c r="D68" s="224"/>
+      <c r="E68" s="225"/>
+      <c r="F68" s="225"/>
       <c r="G68" s="95"/>
       <c r="H68" s="94"/>
       <c r="I68" s="93"/>
@@ -12627,9 +12624,9 @@
       <c r="A69" s="90"/>
       <c r="B69" s="99"/>
       <c r="C69" s="92"/>
-      <c r="D69" s="227"/>
-      <c r="E69" s="228"/>
-      <c r="F69" s="228"/>
+      <c r="D69" s="224"/>
+      <c r="E69" s="225"/>
+      <c r="F69" s="225"/>
       <c r="G69" s="95"/>
       <c r="H69" s="94"/>
       <c r="I69" s="93"/>
@@ -12640,9 +12637,9 @@
       <c r="A70" s="90"/>
       <c r="B70" s="99"/>
       <c r="C70" s="92"/>
-      <c r="D70" s="227"/>
-      <c r="E70" s="228"/>
-      <c r="F70" s="228"/>
+      <c r="D70" s="224"/>
+      <c r="E70" s="225"/>
+      <c r="F70" s="225"/>
       <c r="G70" s="95"/>
       <c r="H70" s="94"/>
       <c r="I70" s="93"/>
@@ -12653,9 +12650,9 @@
       <c r="A71" s="90"/>
       <c r="B71" s="99"/>
       <c r="C71" s="92"/>
-      <c r="D71" s="227"/>
-      <c r="E71" s="228"/>
-      <c r="F71" s="228"/>
+      <c r="D71" s="224"/>
+      <c r="E71" s="225"/>
+      <c r="F71" s="225"/>
       <c r="G71" s="95"/>
       <c r="H71" s="94"/>
       <c r="I71" s="93"/>
@@ -12666,9 +12663,9 @@
       <c r="A72" s="90"/>
       <c r="B72" s="99"/>
       <c r="C72" s="92"/>
-      <c r="D72" s="227"/>
-      <c r="E72" s="228"/>
-      <c r="F72" s="228"/>
+      <c r="D72" s="224"/>
+      <c r="E72" s="225"/>
+      <c r="F72" s="225"/>
       <c r="G72" s="95"/>
       <c r="H72" s="94"/>
       <c r="I72" s="93"/>
@@ -12679,9 +12676,9 @@
       <c r="A73" s="90"/>
       <c r="B73" s="99"/>
       <c r="C73" s="92"/>
-      <c r="D73" s="227"/>
-      <c r="E73" s="228"/>
-      <c r="F73" s="228"/>
+      <c r="D73" s="224"/>
+      <c r="E73" s="225"/>
+      <c r="F73" s="225"/>
       <c r="G73" s="95"/>
       <c r="H73" s="94"/>
       <c r="I73" s="93"/>
@@ -12692,9 +12689,9 @@
       <c r="A74" s="90"/>
       <c r="B74" s="99"/>
       <c r="C74" s="92"/>
-      <c r="D74" s="227"/>
-      <c r="E74" s="228"/>
-      <c r="F74" s="228"/>
+      <c r="D74" s="224"/>
+      <c r="E74" s="225"/>
+      <c r="F74" s="225"/>
       <c r="G74" s="95"/>
       <c r="H74" s="94"/>
       <c r="I74" s="93"/>
@@ -12705,9 +12702,9 @@
       <c r="A75" s="90"/>
       <c r="B75" s="99"/>
       <c r="C75" s="92"/>
-      <c r="D75" s="227"/>
-      <c r="E75" s="228"/>
-      <c r="F75" s="228"/>
+      <c r="D75" s="224"/>
+      <c r="E75" s="225"/>
+      <c r="F75" s="225"/>
       <c r="G75" s="95"/>
       <c r="H75" s="94"/>
       <c r="I75" s="93"/>
@@ -12718,9 +12715,9 @@
       <c r="A76" s="90"/>
       <c r="B76" s="99"/>
       <c r="C76" s="92"/>
-      <c r="D76" s="227"/>
-      <c r="E76" s="228"/>
-      <c r="F76" s="228"/>
+      <c r="D76" s="224"/>
+      <c r="E76" s="225"/>
+      <c r="F76" s="225"/>
       <c r="G76" s="95"/>
       <c r="H76" s="94"/>
       <c r="I76" s="93"/>
@@ -12731,9 +12728,9 @@
       <c r="A77" s="90"/>
       <c r="B77" s="99"/>
       <c r="C77" s="92"/>
-      <c r="D77" s="227"/>
-      <c r="E77" s="228"/>
-      <c r="F77" s="228"/>
+      <c r="D77" s="224"/>
+      <c r="E77" s="225"/>
+      <c r="F77" s="225"/>
       <c r="G77" s="95"/>
       <c r="H77" s="94"/>
       <c r="I77" s="93"/>
@@ -12744,9 +12741,9 @@
       <c r="A78" s="90"/>
       <c r="B78" s="99"/>
       <c r="C78" s="92"/>
-      <c r="D78" s="227"/>
-      <c r="E78" s="228"/>
-      <c r="F78" s="228"/>
+      <c r="D78" s="224"/>
+      <c r="E78" s="225"/>
+      <c r="F78" s="225"/>
       <c r="G78" s="95"/>
       <c r="H78" s="94"/>
       <c r="I78" s="93"/>
@@ -12757,9 +12754,9 @@
       <c r="A79" s="90"/>
       <c r="B79" s="99"/>
       <c r="C79" s="92"/>
-      <c r="D79" s="227"/>
-      <c r="E79" s="228"/>
-      <c r="F79" s="228"/>
+      <c r="D79" s="224"/>
+      <c r="E79" s="225"/>
+      <c r="F79" s="225"/>
       <c r="G79" s="95"/>
       <c r="H79" s="94"/>
       <c r="I79" s="93"/>
@@ -12770,9 +12767,9 @@
       <c r="A80" s="90"/>
       <c r="B80" s="99"/>
       <c r="C80" s="92"/>
-      <c r="D80" s="227"/>
-      <c r="E80" s="228"/>
-      <c r="F80" s="228"/>
+      <c r="D80" s="224"/>
+      <c r="E80" s="225"/>
+      <c r="F80" s="225"/>
       <c r="G80" s="95"/>
       <c r="H80" s="94"/>
       <c r="I80" s="93"/>
@@ -12783,9 +12780,9 @@
       <c r="A81" s="90"/>
       <c r="B81" s="99"/>
       <c r="C81" s="92"/>
-      <c r="D81" s="227"/>
-      <c r="E81" s="228"/>
-      <c r="F81" s="228"/>
+      <c r="D81" s="224"/>
+      <c r="E81" s="225"/>
+      <c r="F81" s="225"/>
       <c r="G81" s="95"/>
       <c r="H81" s="94"/>
       <c r="I81" s="93"/>
@@ -12796,9 +12793,9 @@
       <c r="A82" s="90"/>
       <c r="B82" s="99"/>
       <c r="C82" s="92"/>
-      <c r="D82" s="227"/>
-      <c r="E82" s="228"/>
-      <c r="F82" s="228"/>
+      <c r="D82" s="224"/>
+      <c r="E82" s="225"/>
+      <c r="F82" s="225"/>
       <c r="G82" s="95"/>
       <c r="H82" s="94"/>
       <c r="I82" s="93"/>
@@ -12809,9 +12806,9 @@
       <c r="A83" s="90"/>
       <c r="B83" s="99"/>
       <c r="C83" s="92"/>
-      <c r="D83" s="227"/>
-      <c r="E83" s="228"/>
-      <c r="F83" s="228"/>
+      <c r="D83" s="224"/>
+      <c r="E83" s="225"/>
+      <c r="F83" s="225"/>
       <c r="G83" s="95"/>
       <c r="H83" s="94"/>
       <c r="I83" s="93"/>
@@ -12822,9 +12819,9 @@
       <c r="A84" s="90"/>
       <c r="B84" s="99"/>
       <c r="C84" s="92"/>
-      <c r="D84" s="227"/>
-      <c r="E84" s="228"/>
-      <c r="F84" s="228"/>
+      <c r="D84" s="224"/>
+      <c r="E84" s="225"/>
+      <c r="F84" s="225"/>
       <c r="G84" s="95"/>
       <c r="H84" s="94"/>
       <c r="I84" s="93"/>
@@ -12835,9 +12832,9 @@
       <c r="A85" s="90"/>
       <c r="B85" s="99"/>
       <c r="C85" s="92"/>
-      <c r="D85" s="227"/>
-      <c r="E85" s="228"/>
-      <c r="F85" s="228"/>
+      <c r="D85" s="224"/>
+      <c r="E85" s="225"/>
+      <c r="F85" s="225"/>
       <c r="G85" s="95"/>
       <c r="H85" s="94"/>
       <c r="I85" s="93"/>
@@ -12848,9 +12845,9 @@
       <c r="A86" s="90"/>
       <c r="B86" s="99"/>
       <c r="C86" s="92"/>
-      <c r="D86" s="227"/>
-      <c r="E86" s="228"/>
-      <c r="F86" s="228"/>
+      <c r="D86" s="224"/>
+      <c r="E86" s="225"/>
+      <c r="F86" s="225"/>
       <c r="G86" s="95"/>
       <c r="H86" s="94"/>
       <c r="I86" s="93"/>
@@ -12861,9 +12858,9 @@
       <c r="A87" s="90"/>
       <c r="B87" s="99"/>
       <c r="C87" s="92"/>
-      <c r="D87" s="227"/>
-      <c r="E87" s="228"/>
-      <c r="F87" s="228"/>
+      <c r="D87" s="224"/>
+      <c r="E87" s="225"/>
+      <c r="F87" s="225"/>
       <c r="G87" s="95"/>
       <c r="H87" s="94"/>
       <c r="I87" s="93"/>
@@ -12872,81 +12869,12 @@
     </row>
   </sheetData>
   <mergeCells count="94">
-    <mergeCell ref="D83:F83"/>
-    <mergeCell ref="D84:F84"/>
-    <mergeCell ref="D85:F85"/>
-    <mergeCell ref="D86:F86"/>
-    <mergeCell ref="D87:F87"/>
-    <mergeCell ref="D78:F78"/>
-    <mergeCell ref="D79:F79"/>
-    <mergeCell ref="D80:F80"/>
-    <mergeCell ref="D81:F81"/>
-    <mergeCell ref="D82:F82"/>
-    <mergeCell ref="D73:F73"/>
-    <mergeCell ref="D74:F74"/>
-    <mergeCell ref="D75:F75"/>
-    <mergeCell ref="D76:F76"/>
-    <mergeCell ref="D77:F77"/>
-    <mergeCell ref="D68:F68"/>
-    <mergeCell ref="D69:F69"/>
-    <mergeCell ref="D70:F70"/>
-    <mergeCell ref="D71:F71"/>
-    <mergeCell ref="D72:F72"/>
-    <mergeCell ref="D63:F63"/>
-    <mergeCell ref="D64:F64"/>
-    <mergeCell ref="D65:F65"/>
-    <mergeCell ref="D66:F66"/>
-    <mergeCell ref="D67:F67"/>
-    <mergeCell ref="D58:F58"/>
-    <mergeCell ref="D59:F59"/>
-    <mergeCell ref="D60:F60"/>
-    <mergeCell ref="D61:F61"/>
-    <mergeCell ref="D62:F62"/>
-    <mergeCell ref="D53:F53"/>
-    <mergeCell ref="D54:F54"/>
-    <mergeCell ref="D55:F55"/>
-    <mergeCell ref="D56:F56"/>
-    <mergeCell ref="D57:F57"/>
-    <mergeCell ref="D48:F48"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="D50:F50"/>
-    <mergeCell ref="D51:F51"/>
-    <mergeCell ref="D52:F52"/>
-    <mergeCell ref="D43:F43"/>
-    <mergeCell ref="D44:F44"/>
-    <mergeCell ref="D45:F45"/>
-    <mergeCell ref="D46:F46"/>
-    <mergeCell ref="D47:F47"/>
-    <mergeCell ref="D38:F38"/>
-    <mergeCell ref="D39:F39"/>
-    <mergeCell ref="D40:F40"/>
-    <mergeCell ref="D41:F41"/>
-    <mergeCell ref="D42:F42"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="D36:F36"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="A30:K30"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="A22:K22"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="A16:K16"/>
-    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="I5:K5"/>
     <mergeCell ref="I6:K6"/>
     <mergeCell ref="I7:K7"/>
     <mergeCell ref="A8:D8"/>
@@ -12960,12 +12888,81 @@
     <mergeCell ref="J9:J10"/>
     <mergeCell ref="K9:K10"/>
     <mergeCell ref="D9:G10"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="A16:K16"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="A22:K22"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="A30:K30"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="D38:F38"/>
+    <mergeCell ref="D39:F39"/>
+    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="D44:F44"/>
+    <mergeCell ref="D45:F45"/>
+    <mergeCell ref="D46:F46"/>
+    <mergeCell ref="D47:F47"/>
+    <mergeCell ref="D48:F48"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="D50:F50"/>
+    <mergeCell ref="D51:F51"/>
+    <mergeCell ref="D52:F52"/>
+    <mergeCell ref="D53:F53"/>
+    <mergeCell ref="D54:F54"/>
+    <mergeCell ref="D55:F55"/>
+    <mergeCell ref="D56:F56"/>
+    <mergeCell ref="D57:F57"/>
+    <mergeCell ref="D58:F58"/>
+    <mergeCell ref="D59:F59"/>
+    <mergeCell ref="D60:F60"/>
+    <mergeCell ref="D61:F61"/>
+    <mergeCell ref="D62:F62"/>
+    <mergeCell ref="D63:F63"/>
+    <mergeCell ref="D64:F64"/>
+    <mergeCell ref="D65:F65"/>
+    <mergeCell ref="D66:F66"/>
+    <mergeCell ref="D67:F67"/>
+    <mergeCell ref="D68:F68"/>
+    <mergeCell ref="D69:F69"/>
+    <mergeCell ref="D70:F70"/>
+    <mergeCell ref="D71:F71"/>
+    <mergeCell ref="D72:F72"/>
+    <mergeCell ref="D73:F73"/>
+    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="D75:F75"/>
+    <mergeCell ref="D76:F76"/>
+    <mergeCell ref="D77:F77"/>
+    <mergeCell ref="D78:F78"/>
+    <mergeCell ref="D79:F79"/>
+    <mergeCell ref="D80:F80"/>
+    <mergeCell ref="D81:F81"/>
+    <mergeCell ref="D82:F82"/>
+    <mergeCell ref="D83:F83"/>
+    <mergeCell ref="D84:F84"/>
+    <mergeCell ref="D85:F85"/>
+    <mergeCell ref="D86:F86"/>
+    <mergeCell ref="D87:F87"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/test-case-example.xlsx
+++ b/test-case-example.xlsx
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="977" uniqueCount="585">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="993" uniqueCount="588">
   <si>
     <t>TEST CASE</t>
   </si>
@@ -2352,6 +2352,15 @@
   </si>
   <si>
     <t>auth (116, 126, 139, 143, 149 - 174, 188-189, 193, 199-224, 230-239, 246, 258, 271-272, 277, 532, 586, 590-595); booking (380 - 382, 392); cancel (477 - 488); payment (649-657, 695); revenue_report (750)</t>
+  </si>
+  <si>
+    <t>28/4/2026</t>
+  </si>
+  <si>
+    <t>116, 126, 139, 143, 149-174, 188-189, 193, 199-224, 230-239, 244-284, 380-382, 392, 477-488, 532, 586, 590-595, 649-657, 687-695, 749, 821, 880-881</t>
+  </si>
+  <si>
+    <t>auth (116 - 124, 230 - 284); booking (380 - 392); cancel (477 - 488); payment (649-657, 687-695); revenue_report (749, 821)</t>
   </si>
 </sst>
 </file>
@@ -2725,7 +2734,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="64">
+  <borders count="74">
     <border>
       <left/>
       <right/>
@@ -3530,6 +3539,132 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFAAAAAA"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFAAAAAA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFAAAAAA"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFAAAAAA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFAAAAAA"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFAAAAAA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFAAAAAA"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFAAAAAA"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFAAAAAA"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFAAAAAA"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFAAAAAA"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFAAAAAA"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -3541,7 +3676,7 @@
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="255">
+  <cellXfs count="270">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3" applyFont="1"/>
@@ -3991,147 +4126,147 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="36" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="37" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="39" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="40" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="41" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="39" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="40" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="41" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="39" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="40" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="56" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="49" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="42" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="49" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="42" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="52" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="53" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="50" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="51" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="54" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="48" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="55" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="39" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="40" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="56" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="58" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="59" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="60" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="40" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="56" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="58" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="59" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="60" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="40" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="56" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="39" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="40" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="56" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="39" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="40" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="56" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="49" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="42" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="49" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="42" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="52" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="53" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="50" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="51" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="54" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="48" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="55" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="36" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="37" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="39" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="40" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="41" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="39" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="40" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="41" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -4150,24 +4285,24 @@
     <xf numFmtId="0" fontId="18" fillId="9" borderId="40" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="39" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="40" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="56" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="39" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="39" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="39" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="40" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="56" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="9" borderId="40" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -4195,13 +4330,34 @@
     <xf numFmtId="0" fontId="13" fillId="6" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="39" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="39" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4216,32 +4372,56 @@
     <xf numFmtId="9" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="9" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="1" fontId="10" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="66" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="3" borderId="67" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="3" borderId="72" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="3" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -4272,19 +4452,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>135547</xdr:colOff>
+      <xdr:colOff>114300</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>12023</xdr:rowOff>
+      <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3386677</xdr:colOff>
+      <xdr:colOff>3514725</xdr:colOff>
       <xdr:row>33</xdr:row>
-      <xdr:rowOff>123824</xdr:rowOff>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPr id="3" name="Picture 2"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -4297,8 +4477,46 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7955572" y="8813123"/>
-          <a:ext cx="3251130" cy="797601"/>
+          <a:off x="8315325" y="8848725"/>
+          <a:ext cx="3400425" cy="809625"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3514725</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8315325" y="9810750"/>
+          <a:ext cx="3400425" cy="809625"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5179,11 +5397,11 @@
       <c r="A3" s="70" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="209" t="s">
+      <c r="B3" s="171" t="s">
         <v>62</v>
       </c>
-      <c r="C3" s="209"/>
-      <c r="D3" s="210"/>
+      <c r="C3" s="171"/>
+      <c r="D3" s="172"/>
       <c r="E3" s="71"/>
       <c r="F3" s="71"/>
       <c r="G3" s="71"/>
@@ -5192,11 +5410,11 @@
       <c r="A4" s="74" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="211" t="s">
+      <c r="B4" s="174" t="s">
         <v>488</v>
       </c>
-      <c r="C4" s="212"/>
-      <c r="D4" s="213"/>
+      <c r="C4" s="175"/>
+      <c r="D4" s="176"/>
       <c r="E4" s="71"/>
       <c r="F4" s="71"/>
       <c r="G4" s="71"/>
@@ -5205,11 +5423,11 @@
       <c r="A5" s="74" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="214" t="s">
+      <c r="B5" s="177" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="215"/>
-      <c r="D5" s="216"/>
+      <c r="C5" s="178"/>
+      <c r="D5" s="179"/>
       <c r="E5" s="75"/>
       <c r="F5" s="75"/>
       <c r="G5" s="75"/>
@@ -5258,59 +5476,59 @@
       <c r="G8" s="72"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="197" t="s">
+      <c r="A9" s="187" t="s">
         <v>71</v>
       </c>
-      <c r="B9" s="199" t="s">
+      <c r="B9" s="189" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="197" t="s">
+      <c r="C9" s="187" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="203" t="s">
+      <c r="D9" s="193" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="204"/>
-      <c r="F9" s="204"/>
-      <c r="G9" s="205"/>
-      <c r="H9" s="201" t="s">
+      <c r="E9" s="194"/>
+      <c r="F9" s="194"/>
+      <c r="G9" s="195"/>
+      <c r="H9" s="191" t="s">
         <v>75</v>
       </c>
-      <c r="I9" s="202" t="s">
+      <c r="I9" s="192" t="s">
         <v>76</v>
       </c>
-      <c r="J9" s="202" t="s">
+      <c r="J9" s="192" t="s">
         <v>77</v>
       </c>
-      <c r="K9" s="202" t="s">
+      <c r="K9" s="192" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="198"/>
-      <c r="B10" s="200"/>
-      <c r="C10" s="198"/>
-      <c r="D10" s="206"/>
-      <c r="E10" s="207"/>
-      <c r="F10" s="207"/>
-      <c r="G10" s="208"/>
-      <c r="H10" s="197"/>
-      <c r="I10" s="197"/>
-      <c r="J10" s="197"/>
-      <c r="K10" s="197"/>
+      <c r="A10" s="188"/>
+      <c r="B10" s="190"/>
+      <c r="C10" s="188"/>
+      <c r="D10" s="196"/>
+      <c r="E10" s="197"/>
+      <c r="F10" s="197"/>
+      <c r="G10" s="198"/>
+      <c r="H10" s="187"/>
+      <c r="I10" s="187"/>
+      <c r="J10" s="187"/>
+      <c r="K10" s="187"/>
     </row>
     <row r="11" spans="1:11" ht="15">
-      <c r="A11" s="195"/>
-      <c r="B11" s="195"/>
-      <c r="C11" s="195"/>
-      <c r="D11" s="195"/>
-      <c r="E11" s="195"/>
-      <c r="F11" s="195"/>
-      <c r="G11" s="195"/>
-      <c r="H11" s="195"/>
-      <c r="I11" s="195"/>
-      <c r="J11" s="195"/>
-      <c r="K11" s="196"/>
+      <c r="A11" s="182"/>
+      <c r="B11" s="182"/>
+      <c r="C11" s="182"/>
+      <c r="D11" s="182"/>
+      <c r="E11" s="182"/>
+      <c r="F11" s="182"/>
+      <c r="G11" s="182"/>
+      <c r="H11" s="182"/>
+      <c r="I11" s="182"/>
+      <c r="J11" s="182"/>
+      <c r="K11" s="183"/>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="184" t="s">
@@ -5337,12 +5555,12 @@
       <c r="C13" s="92" t="s">
         <v>491</v>
       </c>
-      <c r="D13" s="187" t="s">
+      <c r="D13" s="199" t="s">
         <v>492</v>
       </c>
-      <c r="E13" s="176"/>
-      <c r="F13" s="176"/>
-      <c r="G13" s="177"/>
+      <c r="E13" s="200"/>
+      <c r="F13" s="200"/>
+      <c r="G13" s="201"/>
       <c r="H13" s="94"/>
       <c r="I13" s="96"/>
       <c r="J13" s="92" t="s">
@@ -5375,12 +5593,12 @@
       <c r="C15" s="102" t="s">
         <v>495</v>
       </c>
-      <c r="D15" s="188" t="s">
+      <c r="D15" s="202" t="s">
         <v>496</v>
       </c>
-      <c r="E15" s="189"/>
-      <c r="F15" s="189"/>
-      <c r="G15" s="190"/>
+      <c r="E15" s="203"/>
+      <c r="F15" s="203"/>
+      <c r="G15" s="204"/>
       <c r="H15" s="103"/>
       <c r="I15" s="103"/>
       <c r="J15" s="104" t="s">
@@ -5413,12 +5631,12 @@
       <c r="C17" s="102" t="s">
         <v>499</v>
       </c>
-      <c r="D17" s="188" t="s">
+      <c r="D17" s="202" t="s">
         <v>500</v>
       </c>
-      <c r="E17" s="189"/>
-      <c r="F17" s="189"/>
-      <c r="G17" s="190"/>
+      <c r="E17" s="203"/>
+      <c r="F17" s="203"/>
+      <c r="G17" s="204"/>
       <c r="H17" s="103"/>
       <c r="I17" s="103"/>
       <c r="J17" s="104" t="s">
@@ -5451,12 +5669,12 @@
       <c r="C19" s="102" t="s">
         <v>503</v>
       </c>
-      <c r="D19" s="188" t="s">
+      <c r="D19" s="202" t="s">
         <v>504</v>
       </c>
-      <c r="E19" s="189"/>
-      <c r="F19" s="189"/>
-      <c r="G19" s="190"/>
+      <c r="E19" s="203"/>
+      <c r="F19" s="203"/>
+      <c r="G19" s="204"/>
       <c r="H19" s="103"/>
       <c r="I19" s="103"/>
       <c r="J19" s="104" t="s">
@@ -5489,12 +5707,12 @@
       <c r="C21" s="102" t="s">
         <v>507</v>
       </c>
-      <c r="D21" s="188" t="s">
+      <c r="D21" s="202" t="s">
         <v>508</v>
       </c>
-      <c r="E21" s="189"/>
-      <c r="F21" s="189"/>
-      <c r="G21" s="190"/>
+      <c r="E21" s="203"/>
+      <c r="F21" s="203"/>
+      <c r="G21" s="204"/>
       <c r="H21" s="103"/>
       <c r="I21" s="103"/>
       <c r="J21" s="104" t="s">
@@ -5527,12 +5745,12 @@
       <c r="C23" s="102" t="s">
         <v>511</v>
       </c>
-      <c r="D23" s="188" t="s">
+      <c r="D23" s="202" t="s">
         <v>512</v>
       </c>
-      <c r="E23" s="189"/>
-      <c r="F23" s="189"/>
-      <c r="G23" s="190"/>
+      <c r="E23" s="203"/>
+      <c r="F23" s="203"/>
+      <c r="G23" s="204"/>
       <c r="H23" s="103"/>
       <c r="I23" s="103"/>
       <c r="J23" s="104" t="s">
@@ -5565,12 +5783,12 @@
       <c r="C25" s="102" t="s">
         <v>515</v>
       </c>
-      <c r="D25" s="188" t="s">
+      <c r="D25" s="202" t="s">
         <v>516</v>
       </c>
-      <c r="E25" s="189"/>
-      <c r="F25" s="189"/>
-      <c r="G25" s="190"/>
+      <c r="E25" s="203"/>
+      <c r="F25" s="203"/>
+      <c r="G25" s="204"/>
       <c r="H25" s="103"/>
       <c r="I25" s="103"/>
       <c r="J25" s="104" t="s">
@@ -5603,12 +5821,12 @@
       <c r="C27" s="102" t="s">
         <v>519</v>
       </c>
-      <c r="D27" s="188" t="s">
+      <c r="D27" s="202" t="s">
         <v>520</v>
       </c>
-      <c r="E27" s="189"/>
-      <c r="F27" s="189"/>
-      <c r="G27" s="190"/>
+      <c r="E27" s="203"/>
+      <c r="F27" s="203"/>
+      <c r="G27" s="204"/>
       <c r="H27" s="103"/>
       <c r="I27" s="103"/>
       <c r="J27" s="104" t="s">
@@ -5641,12 +5859,12 @@
       <c r="C29" s="102" t="s">
         <v>523</v>
       </c>
-      <c r="D29" s="188" t="s">
+      <c r="D29" s="202" t="s">
         <v>524</v>
       </c>
-      <c r="E29" s="189"/>
-      <c r="F29" s="189"/>
-      <c r="G29" s="190"/>
+      <c r="E29" s="203"/>
+      <c r="F29" s="203"/>
+      <c r="G29" s="204"/>
       <c r="H29" s="103"/>
       <c r="I29" s="103"/>
       <c r="J29" s="104" t="s">
@@ -5679,12 +5897,12 @@
       <c r="C31" s="102" t="s">
         <v>527</v>
       </c>
-      <c r="D31" s="188" t="s">
+      <c r="D31" s="202" t="s">
         <v>528</v>
       </c>
-      <c r="E31" s="189"/>
-      <c r="F31" s="189"/>
-      <c r="G31" s="190"/>
+      <c r="E31" s="203"/>
+      <c r="F31" s="203"/>
+      <c r="G31" s="204"/>
       <c r="H31" s="103"/>
       <c r="I31" s="103"/>
       <c r="J31" s="104" t="s">
@@ -5717,12 +5935,12 @@
       <c r="C33" s="102" t="s">
         <v>531</v>
       </c>
-      <c r="D33" s="188" t="s">
+      <c r="D33" s="202" t="s">
         <v>524</v>
       </c>
-      <c r="E33" s="189"/>
-      <c r="F33" s="189"/>
-      <c r="G33" s="190"/>
+      <c r="E33" s="203"/>
+      <c r="F33" s="203"/>
+      <c r="G33" s="204"/>
       <c r="H33" s="103"/>
       <c r="I33" s="103"/>
       <c r="J33" s="104" t="s">
@@ -5732,25 +5950,6 @@
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A11:K11"/>
-    <mergeCell ref="A12:K12"/>
-    <mergeCell ref="D13:G13"/>
-    <mergeCell ref="A14:K14"/>
-    <mergeCell ref="D15:G15"/>
-    <mergeCell ref="A16:K16"/>
-    <mergeCell ref="D23:G23"/>
-    <mergeCell ref="A24:K24"/>
-    <mergeCell ref="D25:G25"/>
-    <mergeCell ref="A26:K26"/>
-    <mergeCell ref="D17:G17"/>
-    <mergeCell ref="A18:K18"/>
-    <mergeCell ref="D19:G19"/>
-    <mergeCell ref="A20:K20"/>
-    <mergeCell ref="D21:G21"/>
     <mergeCell ref="A32:K32"/>
     <mergeCell ref="D33:G33"/>
     <mergeCell ref="A9:A10"/>
@@ -5767,6 +5966,25 @@
     <mergeCell ref="A30:K30"/>
     <mergeCell ref="D31:G31"/>
     <mergeCell ref="A22:K22"/>
+    <mergeCell ref="D23:G23"/>
+    <mergeCell ref="A24:K24"/>
+    <mergeCell ref="D25:G25"/>
+    <mergeCell ref="A26:K26"/>
+    <mergeCell ref="D17:G17"/>
+    <mergeCell ref="A18:K18"/>
+    <mergeCell ref="D19:G19"/>
+    <mergeCell ref="A20:K20"/>
+    <mergeCell ref="D21:G21"/>
+    <mergeCell ref="A12:K12"/>
+    <mergeCell ref="D13:G13"/>
+    <mergeCell ref="A14:K14"/>
+    <mergeCell ref="D15:G15"/>
+    <mergeCell ref="A16:K16"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A11:K11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5795,9 +6013,9 @@
       <c r="A1" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="239"/>
-      <c r="C1" s="239"/>
-      <c r="D1" s="239"/>
+      <c r="B1" s="240"/>
+      <c r="C1" s="240"/>
+      <c r="D1" s="240"/>
       <c r="E1" s="67"/>
       <c r="F1" s="67"/>
       <c r="G1" s="67"/>
@@ -5809,9 +6027,9 @@
     </row>
     <row r="2" spans="1:12" s="60" customFormat="1" ht="11.25" customHeight="1">
       <c r="A2" s="69"/>
-      <c r="B2" s="240"/>
-      <c r="C2" s="240"/>
-      <c r="D2" s="240"/>
+      <c r="B2" s="241"/>
+      <c r="C2" s="241"/>
+      <c r="D2" s="241"/>
       <c r="E2" s="67"/>
       <c r="F2" s="67"/>
       <c r="G2" s="67"/>
@@ -5825,54 +6043,54 @@
       <c r="A3" s="70" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="209" t="s">
+      <c r="B3" s="171" t="s">
         <v>532</v>
       </c>
-      <c r="C3" s="209"/>
-      <c r="D3" s="210"/>
+      <c r="C3" s="171"/>
+      <c r="D3" s="172"/>
       <c r="E3" s="71"/>
       <c r="F3" s="71"/>
       <c r="G3" s="71"/>
       <c r="H3" s="71"/>
-      <c r="I3" s="193"/>
-      <c r="J3" s="193"/>
-      <c r="K3" s="193"/>
+      <c r="I3" s="173"/>
+      <c r="J3" s="173"/>
+      <c r="K3" s="173"/>
       <c r="L3" s="73"/>
     </row>
     <row r="4" spans="1:12" s="61" customFormat="1" ht="12.75">
       <c r="A4" s="74" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="211" t="s">
+      <c r="B4" s="174" t="s">
         <v>533</v>
       </c>
-      <c r="C4" s="212"/>
-      <c r="D4" s="213"/>
+      <c r="C4" s="175"/>
+      <c r="D4" s="176"/>
       <c r="E4" s="71"/>
       <c r="F4" s="71"/>
       <c r="G4" s="71"/>
       <c r="H4" s="71"/>
-      <c r="I4" s="193"/>
-      <c r="J4" s="193"/>
-      <c r="K4" s="193"/>
+      <c r="I4" s="173"/>
+      <c r="J4" s="173"/>
+      <c r="K4" s="173"/>
       <c r="L4" s="73"/>
     </row>
     <row r="5" spans="1:12" s="62" customFormat="1" ht="25.5">
       <c r="A5" s="74" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="214" t="s">
+      <c r="B5" s="177" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="215"/>
-      <c r="D5" s="216"/>
+      <c r="C5" s="178"/>
+      <c r="D5" s="179"/>
       <c r="E5" s="75"/>
       <c r="F5" s="75"/>
       <c r="G5" s="75"/>
       <c r="H5" s="75"/>
-      <c r="I5" s="217"/>
-      <c r="J5" s="217"/>
-      <c r="K5" s="217"/>
+      <c r="I5" s="180"/>
+      <c r="J5" s="180"/>
+      <c r="K5" s="180"/>
       <c r="L5" s="76"/>
     </row>
     <row r="6" spans="1:12" s="61" customFormat="1" ht="15" customHeight="1">
@@ -5894,9 +6112,9 @@
       <c r="F6" s="72"/>
       <c r="G6" s="72"/>
       <c r="H6" s="72"/>
-      <c r="I6" s="193"/>
-      <c r="J6" s="193"/>
-      <c r="K6" s="193"/>
+      <c r="I6" s="173"/>
+      <c r="J6" s="173"/>
+      <c r="K6" s="173"/>
       <c r="L6" s="73"/>
     </row>
     <row r="7" spans="1:12" s="61" customFormat="1" ht="15" customHeight="1">
@@ -5918,16 +6136,16 @@
       <c r="F7" s="85"/>
       <c r="G7" s="85"/>
       <c r="H7" s="85"/>
-      <c r="I7" s="193"/>
-      <c r="J7" s="193"/>
-      <c r="K7" s="193"/>
+      <c r="I7" s="173"/>
+      <c r="J7" s="173"/>
+      <c r="K7" s="173"/>
       <c r="L7" s="73"/>
     </row>
     <row r="8" spans="1:12" s="61" customFormat="1" ht="15" customHeight="1">
-      <c r="A8" s="194"/>
-      <c r="B8" s="194"/>
-      <c r="C8" s="194"/>
-      <c r="D8" s="194"/>
+      <c r="A8" s="181"/>
+      <c r="B8" s="181"/>
+      <c r="C8" s="181"/>
+      <c r="D8" s="181"/>
       <c r="E8" s="72"/>
       <c r="F8" s="72"/>
       <c r="G8" s="72"/>
@@ -5938,61 +6156,61 @@
       <c r="L8" s="73"/>
     </row>
     <row r="9" spans="1:12" s="63" customFormat="1" ht="12" customHeight="1">
-      <c r="A9" s="197" t="s">
+      <c r="A9" s="187" t="s">
         <v>71</v>
       </c>
-      <c r="B9" s="199" t="s">
+      <c r="B9" s="189" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="197" t="s">
+      <c r="C9" s="187" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="203" t="s">
+      <c r="D9" s="193" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="204"/>
-      <c r="F9" s="204"/>
-      <c r="G9" s="205"/>
-      <c r="H9" s="201" t="s">
+      <c r="E9" s="194"/>
+      <c r="F9" s="194"/>
+      <c r="G9" s="195"/>
+      <c r="H9" s="191" t="s">
         <v>75</v>
       </c>
-      <c r="I9" s="202" t="s">
+      <c r="I9" s="192" t="s">
         <v>76</v>
       </c>
-      <c r="J9" s="202" t="s">
+      <c r="J9" s="192" t="s">
         <v>77</v>
       </c>
-      <c r="K9" s="202" t="s">
+      <c r="K9" s="192" t="s">
         <v>78</v>
       </c>
       <c r="L9" s="87"/>
     </row>
     <row r="10" spans="1:12" s="61" customFormat="1" ht="12" customHeight="1">
-      <c r="A10" s="198"/>
-      <c r="B10" s="200"/>
-      <c r="C10" s="198"/>
-      <c r="D10" s="206"/>
-      <c r="E10" s="207"/>
-      <c r="F10" s="207"/>
-      <c r="G10" s="208"/>
-      <c r="H10" s="197"/>
-      <c r="I10" s="197"/>
-      <c r="J10" s="197"/>
-      <c r="K10" s="197"/>
+      <c r="A10" s="188"/>
+      <c r="B10" s="190"/>
+      <c r="C10" s="188"/>
+      <c r="D10" s="196"/>
+      <c r="E10" s="197"/>
+      <c r="F10" s="197"/>
+      <c r="G10" s="198"/>
+      <c r="H10" s="187"/>
+      <c r="I10" s="187"/>
+      <c r="J10" s="187"/>
+      <c r="K10" s="187"/>
       <c r="L10" s="73"/>
     </row>
     <row r="11" spans="1:12" s="64" customFormat="1" ht="15">
-      <c r="A11" s="195"/>
-      <c r="B11" s="195"/>
-      <c r="C11" s="195"/>
-      <c r="D11" s="195"/>
-      <c r="E11" s="195"/>
-      <c r="F11" s="195"/>
-      <c r="G11" s="195"/>
-      <c r="H11" s="195"/>
-      <c r="I11" s="195"/>
-      <c r="J11" s="195"/>
-      <c r="K11" s="196"/>
+      <c r="A11" s="182"/>
+      <c r="B11" s="182"/>
+      <c r="C11" s="182"/>
+      <c r="D11" s="182"/>
+      <c r="E11" s="182"/>
+      <c r="F11" s="182"/>
+      <c r="G11" s="182"/>
+      <c r="H11" s="182"/>
+      <c r="I11" s="182"/>
+      <c r="J11" s="182"/>
+      <c r="K11" s="183"/>
     </row>
     <row r="12" spans="1:12" s="65" customFormat="1" ht="12.75">
       <c r="A12" s="184" t="s">
@@ -6019,11 +6237,11 @@
       <c r="C13" s="92" t="s">
         <v>536</v>
       </c>
-      <c r="D13" s="175" t="s">
+      <c r="D13" s="207" t="s">
         <v>537</v>
       </c>
-      <c r="E13" s="176"/>
-      <c r="F13" s="176"/>
+      <c r="E13" s="200"/>
+      <c r="F13" s="200"/>
       <c r="G13" s="95"/>
       <c r="H13" s="94"/>
       <c r="I13" s="96"/>
@@ -6033,7 +6251,7 @@
       <c r="K13" s="92"/>
     </row>
     <row r="14" spans="1:12" s="65" customFormat="1" ht="12.75" outlineLevel="1">
-      <c r="A14" s="241" t="s">
+      <c r="A14" s="239" t="s">
         <v>538</v>
       </c>
       <c r="B14" s="223"/>
@@ -6057,11 +6275,11 @@
       <c r="C15" s="98" t="s">
         <v>540</v>
       </c>
-      <c r="D15" s="224" t="s">
+      <c r="D15" s="228" t="s">
         <v>541</v>
       </c>
-      <c r="E15" s="176"/>
-      <c r="F15" s="176"/>
+      <c r="E15" s="200"/>
+      <c r="F15" s="200"/>
       <c r="G15" s="95"/>
       <c r="H15" s="94"/>
       <c r="I15" s="93"/>
@@ -6071,7 +6289,7 @@
       <c r="K15" s="92"/>
     </row>
     <row r="16" spans="1:12" s="65" customFormat="1" ht="12.75" outlineLevel="1">
-      <c r="A16" s="241" t="s">
+      <c r="A16" s="239" t="s">
         <v>542</v>
       </c>
       <c r="B16" s="223"/>
@@ -6095,11 +6313,11 @@
       <c r="C17" s="92" t="s">
         <v>543</v>
       </c>
-      <c r="D17" s="224" t="s">
+      <c r="D17" s="228" t="s">
         <v>544</v>
       </c>
-      <c r="E17" s="225"/>
-      <c r="F17" s="225"/>
+      <c r="E17" s="229"/>
+      <c r="F17" s="229"/>
       <c r="G17" s="95"/>
       <c r="H17" s="94"/>
       <c r="I17" s="93"/>
@@ -6148,11 +6366,12 @@
     <row r="55" ht="12" customHeight="1"/>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="B1:D2"/>
+    <mergeCell ref="D9:G10"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="B3:D3"/>
     <mergeCell ref="A16:C16"/>
     <mergeCell ref="D17:F17"/>
     <mergeCell ref="I6:K6"/>
@@ -6167,12 +6386,11 @@
     <mergeCell ref="I9:I10"/>
     <mergeCell ref="J9:J10"/>
     <mergeCell ref="K9:K10"/>
-    <mergeCell ref="B1:D2"/>
-    <mergeCell ref="D9:G10"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="I5:K5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -6182,7 +6400,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="13.5"/>
   <cols>
     <col min="3" max="3" width="22.75" customWidth="1"/>
@@ -6266,10 +6484,10 @@
       <c r="F7" s="53" t="s">
         <v>68</v>
       </c>
-      <c r="G7" s="252" t="s">
+      <c r="G7" s="242" t="s">
         <v>550</v>
       </c>
-      <c r="H7" s="253"/>
+      <c r="H7" s="243"/>
     </row>
     <row r="8" spans="1:8" s="49" customFormat="1" ht="40.15" customHeight="1">
       <c r="A8" s="15"/>
@@ -6291,11 +6509,11 @@
         <f>COUNTIF(Auth!J10:J29, "Pending")</f>
         <v>0</v>
       </c>
-      <c r="G8" s="246">
+      <c r="G8" s="244">
         <f>Auth!D7</f>
         <v>26</v>
       </c>
-      <c r="H8" s="247"/>
+      <c r="H8" s="245"/>
     </row>
     <row r="9" spans="1:8" s="49" customFormat="1" ht="40.15" customHeight="1">
       <c r="A9" s="15"/>
@@ -6317,11 +6535,11 @@
         <f>COUNTIF(Home!J10:J29, "Pending")</f>
         <v>0</v>
       </c>
-      <c r="G9" s="248">
+      <c r="G9" s="246">
         <f>Home!D7</f>
         <v>17</v>
       </c>
-      <c r="H9" s="249"/>
+      <c r="H9" s="247"/>
     </row>
     <row r="10" spans="1:8" s="49" customFormat="1" ht="40.15" customHeight="1">
       <c r="A10" s="15"/>
@@ -6343,11 +6561,11 @@
         <f>COUNTIF(Favorite!J10:J29, "Pending")</f>
         <v>8</v>
       </c>
-      <c r="G10" s="254">
+      <c r="G10" s="248">
         <f>Favorite!D7</f>
         <v>8</v>
       </c>
-      <c r="H10" s="247"/>
+      <c r="H10" s="245"/>
     </row>
     <row r="11" spans="1:8" s="49" customFormat="1" ht="40.15" customHeight="1">
       <c r="A11" s="15"/>
@@ -6369,11 +6587,11 @@
         <f>COUNTIF(Booking!J10:J42, "Pending")</f>
         <v>23</v>
       </c>
-      <c r="G11" s="248">
+      <c r="G11" s="246">
         <f>Booking!D7</f>
         <v>23</v>
       </c>
-      <c r="H11" s="249"/>
+      <c r="H11" s="247"/>
     </row>
     <row r="12" spans="1:8" s="49" customFormat="1" ht="40.15" customHeight="1">
       <c r="A12" s="15"/>
@@ -6395,11 +6613,11 @@
         <f>COUNTIF('Cancel Booking'!J10:J29, "Pending")</f>
         <v>12</v>
       </c>
-      <c r="G12" s="246">
+      <c r="G12" s="244">
         <f>'Cancel Booking'!D7</f>
         <v>12</v>
       </c>
-      <c r="H12" s="247"/>
+      <c r="H12" s="245"/>
     </row>
     <row r="13" spans="1:8" s="49" customFormat="1" ht="40.15" customHeight="1">
       <c r="A13" s="15"/>
@@ -6421,11 +6639,11 @@
         <f>COUNTIF(Review!J10:J29, "Pending")</f>
         <v>10</v>
       </c>
-      <c r="G13" s="248">
+      <c r="G13" s="246">
         <f>Review!D7</f>
         <v>10</v>
       </c>
-      <c r="H13" s="249"/>
+      <c r="H13" s="247"/>
     </row>
     <row r="14" spans="1:8" s="49" customFormat="1" ht="40.15" customHeight="1">
       <c r="A14" s="15"/>
@@ -6447,11 +6665,11 @@
         <f>COUNTIF(Admin!J10:J29, "Pending")</f>
         <v>0</v>
       </c>
-      <c r="G14" s="246">
+      <c r="G14" s="244">
         <f>Admin!D7</f>
         <v>14</v>
       </c>
-      <c r="H14" s="247"/>
+      <c r="H14" s="245"/>
     </row>
     <row r="15" spans="1:8" ht="40.15" customHeight="1">
       <c r="A15" s="5"/>
@@ -6473,11 +6691,11 @@
         <f>COUNTIF(Venue!J10:J29, "Pending")</f>
         <v>6</v>
       </c>
-      <c r="G15" s="248">
+      <c r="G15" s="246">
         <f>Venue!D7</f>
         <v>6</v>
       </c>
-      <c r="H15" s="249"/>
+      <c r="H15" s="247"/>
     </row>
     <row r="16" spans="1:8" ht="40.15" customHeight="1">
       <c r="A16" s="5"/>
@@ -6497,11 +6715,11 @@
         <f>SUM(F8:F15)</f>
         <v>59</v>
       </c>
-      <c r="G16" s="250">
+      <c r="G16" s="253">
         <f>SUM(G8:H15)</f>
         <v>116</v>
       </c>
-      <c r="H16" s="251"/>
+      <c r="H16" s="254"/>
     </row>
     <row r="17" spans="1:9" ht="14.25">
       <c r="A17" s="5"/>
@@ -6650,8 +6868,8 @@
       <c r="I29" s="14"/>
     </row>
     <row r="30" spans="1:9" ht="14.25">
-      <c r="A30" s="15"/>
-      <c r="B30" s="242" t="s">
+      <c r="A30" s="5"/>
+      <c r="B30" s="249" t="s">
         <v>44</v>
       </c>
       <c r="C30" s="16" t="s">
@@ -6672,11 +6890,11 @@
       <c r="H30" s="21" t="s">
         <v>572</v>
       </c>
-      <c r="I30" s="245"/>
-    </row>
-    <row r="31" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A31" s="15"/>
-      <c r="B31" s="243"/>
+      <c r="I30" s="252"/>
+    </row>
+    <row r="31" spans="1:9" ht="14.25">
+      <c r="A31" s="5"/>
+      <c r="B31" s="250"/>
       <c r="C31" s="16" t="s">
         <v>573</v>
       </c>
@@ -6695,11 +6913,11 @@
       <c r="H31" s="26" t="s">
         <v>575</v>
       </c>
-      <c r="I31" s="245"/>
-    </row>
-    <row r="32" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A32" s="15"/>
-      <c r="B32" s="243"/>
+      <c r="I31" s="252"/>
+    </row>
+    <row r="32" spans="1:9" ht="16.5" customHeight="1">
+      <c r="A32" s="5"/>
+      <c r="B32" s="250"/>
       <c r="C32" s="16" t="s">
         <v>576</v>
       </c>
@@ -6718,11 +6936,11 @@
       <c r="H32" s="30" t="s">
         <v>577</v>
       </c>
-      <c r="I32" s="245"/>
-    </row>
-    <row r="33" spans="1:9" ht="12.75" customHeight="1">
-      <c r="A33" s="15"/>
-      <c r="B33" s="243"/>
+      <c r="I32" s="252"/>
+    </row>
+    <row r="33" spans="1:9" ht="15" customHeight="1">
+      <c r="A33" s="5"/>
+      <c r="B33" s="250"/>
       <c r="C33" s="16" t="s">
         <v>578</v>
       </c>
@@ -6733,83 +6951,202 @@
         <v>123</v>
       </c>
       <c r="F33" s="32">
+        <v>0.77</v>
+      </c>
+      <c r="G33" s="170" t="s">
+        <v>586</v>
+      </c>
+      <c r="H33" s="33" t="s">
+        <v>587</v>
+      </c>
+      <c r="I33" s="252"/>
+    </row>
+    <row r="34" spans="1:9" ht="14.25">
+      <c r="A34" s="5"/>
+      <c r="B34" s="262"/>
+      <c r="C34" s="263" t="s">
+        <v>579</v>
+      </c>
+      <c r="D34" s="264">
+        <v>167</v>
+      </c>
+      <c r="E34" s="265">
+        <v>5</v>
+      </c>
+      <c r="F34" s="266">
+        <v>0.97</v>
+      </c>
+      <c r="G34" s="267" t="s">
+        <v>580</v>
+      </c>
+      <c r="H34" s="268" t="s">
+        <v>581</v>
+      </c>
+      <c r="I34" s="269"/>
+    </row>
+    <row r="35" spans="1:9" ht="14.25">
+      <c r="A35" s="15"/>
+      <c r="B35" s="255" t="s">
+        <v>585</v>
+      </c>
+      <c r="C35" s="256" t="s">
+        <v>571</v>
+      </c>
+      <c r="D35" s="257">
+        <v>12</v>
+      </c>
+      <c r="E35" s="258">
+        <v>0</v>
+      </c>
+      <c r="F35" s="259">
+        <v>1</v>
+      </c>
+      <c r="G35" s="260" t="s">
+        <v>572</v>
+      </c>
+      <c r="H35" s="261" t="s">
+        <v>572</v>
+      </c>
+      <c r="I35" s="252"/>
+    </row>
+    <row r="36" spans="1:9" ht="17.25" customHeight="1">
+      <c r="A36" s="15"/>
+      <c r="B36" s="250"/>
+      <c r="C36" s="16" t="s">
+        <v>573</v>
+      </c>
+      <c r="D36" s="22">
+        <v>92</v>
+      </c>
+      <c r="E36" s="23">
+        <v>4</v>
+      </c>
+      <c r="F36" s="24">
+        <v>0.96</v>
+      </c>
+      <c r="G36" s="25" t="s">
+        <v>574</v>
+      </c>
+      <c r="H36" s="26" t="s">
+        <v>575</v>
+      </c>
+      <c r="I36" s="252"/>
+    </row>
+    <row r="37" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A37" s="15"/>
+      <c r="B37" s="250"/>
+      <c r="C37" s="16" t="s">
+        <v>576</v>
+      </c>
+      <c r="D37" s="22">
+        <v>137</v>
+      </c>
+      <c r="E37" s="27">
+        <v>29</v>
+      </c>
+      <c r="F37" s="28">
+        <v>0.79</v>
+      </c>
+      <c r="G37" s="29" t="s">
+        <v>582</v>
+      </c>
+      <c r="H37" s="30" t="s">
+        <v>577</v>
+      </c>
+      <c r="I37" s="252"/>
+    </row>
+    <row r="38" spans="1:9" ht="12.75" customHeight="1">
+      <c r="A38" s="15"/>
+      <c r="B38" s="250"/>
+      <c r="C38" s="16" t="s">
+        <v>578</v>
+      </c>
+      <c r="D38" s="22">
+        <v>541</v>
+      </c>
+      <c r="E38" s="31">
+        <v>123</v>
+      </c>
+      <c r="F38" s="32">
         <v>0.83</v>
       </c>
-      <c r="G33" s="170" t="s">
+      <c r="G38" s="170" t="s">
         <v>583</v>
       </c>
-      <c r="H33" s="33" t="s">
+      <c r="H38" s="33" t="s">
         <v>584</v>
       </c>
-      <c r="I33" s="245"/>
-    </row>
-    <row r="34" spans="1:9" ht="11.25" customHeight="1">
-      <c r="A34" s="15"/>
-      <c r="B34" s="244"/>
-      <c r="C34" s="16" t="s">
+      <c r="I38" s="252"/>
+    </row>
+    <row r="39" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A39" s="15"/>
+      <c r="B39" s="251"/>
+      <c r="C39" s="16" t="s">
         <v>579</v>
       </c>
-      <c r="D34" s="22">
+      <c r="D39" s="22">
         <v>167</v>
       </c>
-      <c r="E34" s="34">
+      <c r="E39" s="34">
         <v>5</v>
       </c>
-      <c r="F34" s="35">
+      <c r="F39" s="35">
         <v>0.97</v>
       </c>
-      <c r="G34" s="36" t="s">
+      <c r="G39" s="36" t="s">
         <v>580</v>
       </c>
-      <c r="H34" s="37" t="s">
+      <c r="H39" s="37" t="s">
         <v>581</v>
       </c>
-      <c r="I34" s="245"/>
-    </row>
-    <row r="35" spans="1:9" ht="14.25">
-      <c r="A35" s="5"/>
-      <c r="B35" s="38"/>
-      <c r="C35" s="39" t="s">
+      <c r="I39" s="252"/>
+    </row>
+    <row r="40" spans="1:9" ht="14.25">
+      <c r="A40" s="5"/>
+      <c r="B40" s="38"/>
+      <c r="C40" s="39" t="s">
         <v>559</v>
       </c>
-      <c r="D35" s="40">
-        <f>SUM(D28:D34)</f>
-        <v>949</v>
-      </c>
-      <c r="E35" s="41">
-        <f>SUM(E28:E34)</f>
-        <v>161</v>
-      </c>
-      <c r="F35" s="40"/>
-      <c r="G35" s="42"/>
-      <c r="H35" s="43"/>
-      <c r="I35" s="44"/>
-    </row>
-    <row r="36" spans="1:9" ht="14.25">
-      <c r="A36" s="5"/>
-      <c r="B36" s="45"/>
-      <c r="C36" s="5"/>
-      <c r="D36" s="46"/>
-      <c r="E36" s="47"/>
-      <c r="F36" s="47"/>
-      <c r="G36" s="47"/>
-      <c r="H36" s="47"/>
-      <c r="I36" s="47"/>
+      <c r="D40" s="40">
+        <f>SUM(D28:D39)</f>
+        <v>1898</v>
+      </c>
+      <c r="E40" s="41">
+        <f>SUM(E28:E39)</f>
+        <v>322</v>
+      </c>
+      <c r="F40" s="40"/>
+      <c r="G40" s="42"/>
+      <c r="H40" s="43"/>
+      <c r="I40" s="44"/>
+    </row>
+    <row r="41" spans="1:9" ht="14.25">
+      <c r="A41" s="5"/>
+      <c r="B41" s="45"/>
+      <c r="C41" s="5"/>
+      <c r="D41" s="46"/>
+      <c r="E41" s="47"/>
+      <c r="F41" s="47"/>
+      <c r="G41" s="47"/>
+      <c r="H41" s="47"/>
+      <c r="I41" s="47"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="14">
+    <mergeCell ref="B35:B39"/>
+    <mergeCell ref="I35:I39"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="B30:B34"/>
+    <mergeCell ref="I30:I34"/>
     <mergeCell ref="G7:H7"/>
     <mergeCell ref="G8:H8"/>
     <mergeCell ref="G9:H9"/>
     <mergeCell ref="G10:H10"/>
     <mergeCell ref="G11:H11"/>
-    <mergeCell ref="B30:B34"/>
-    <mergeCell ref="I30:I34"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="G16:H16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
@@ -6864,52 +7201,52 @@
       <c r="A3" s="70" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="209" t="s">
+      <c r="B3" s="171" t="s">
         <v>62</v>
       </c>
-      <c r="C3" s="209"/>
-      <c r="D3" s="210"/>
+      <c r="C3" s="171"/>
+      <c r="D3" s="172"/>
       <c r="E3" s="71"/>
       <c r="F3" s="71"/>
       <c r="G3" s="71"/>
       <c r="H3" s="71"/>
-      <c r="I3" s="193"/>
-      <c r="J3" s="193"/>
-      <c r="K3" s="193"/>
+      <c r="I3" s="173"/>
+      <c r="J3" s="173"/>
+      <c r="K3" s="173"/>
     </row>
     <row r="4" spans="1:11" ht="14.25">
       <c r="A4" s="74" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="211" t="s">
+      <c r="B4" s="174" t="s">
         <v>64</v>
       </c>
-      <c r="C4" s="212"/>
-      <c r="D4" s="213"/>
+      <c r="C4" s="175"/>
+      <c r="D4" s="176"/>
       <c r="E4" s="71"/>
       <c r="F4" s="71"/>
       <c r="G4" s="71"/>
       <c r="H4" s="71"/>
-      <c r="I4" s="193"/>
-      <c r="J4" s="193"/>
-      <c r="K4" s="193"/>
+      <c r="I4" s="173"/>
+      <c r="J4" s="173"/>
+      <c r="K4" s="173"/>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="74" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="214" t="s">
+      <c r="B5" s="177" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="215"/>
-      <c r="D5" s="216"/>
+      <c r="C5" s="178"/>
+      <c r="D5" s="179"/>
       <c r="E5" s="75"/>
       <c r="F5" s="75"/>
       <c r="G5" s="75"/>
       <c r="H5" s="75"/>
-      <c r="I5" s="217"/>
-      <c r="J5" s="217"/>
-      <c r="K5" s="217"/>
+      <c r="I5" s="180"/>
+      <c r="J5" s="180"/>
+      <c r="K5" s="180"/>
     </row>
     <row r="6" spans="1:11" ht="14.25">
       <c r="A6" s="77" t="s">
@@ -6928,9 +7265,9 @@
       <c r="F6" s="72"/>
       <c r="G6" s="72"/>
       <c r="H6" s="72"/>
-      <c r="I6" s="193"/>
-      <c r="J6" s="193"/>
-      <c r="K6" s="193"/>
+      <c r="I6" s="173"/>
+      <c r="J6" s="173"/>
+      <c r="K6" s="173"/>
     </row>
     <row r="7" spans="1:11" ht="14.25">
       <c r="A7" s="81" t="s">
@@ -6950,15 +7287,15 @@
       <c r="F7" s="85"/>
       <c r="G7" s="85"/>
       <c r="H7" s="85"/>
-      <c r="I7" s="193"/>
-      <c r="J7" s="193"/>
-      <c r="K7" s="193"/>
+      <c r="I7" s="173"/>
+      <c r="J7" s="173"/>
+      <c r="K7" s="173"/>
     </row>
     <row r="8" spans="1:11" ht="14.25">
-      <c r="A8" s="194"/>
-      <c r="B8" s="194"/>
-      <c r="C8" s="194"/>
-      <c r="D8" s="194"/>
+      <c r="A8" s="181"/>
+      <c r="B8" s="181"/>
+      <c r="C8" s="181"/>
+      <c r="D8" s="181"/>
       <c r="E8" s="72"/>
       <c r="F8" s="72"/>
       <c r="G8" s="72"/>
@@ -6968,59 +7305,59 @@
       <c r="K8" s="86"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="197" t="s">
+      <c r="A9" s="187" t="s">
         <v>71</v>
       </c>
-      <c r="B9" s="199" t="s">
+      <c r="B9" s="189" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="197" t="s">
+      <c r="C9" s="187" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="203" t="s">
+      <c r="D9" s="193" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="204"/>
-      <c r="F9" s="204"/>
-      <c r="G9" s="205"/>
-      <c r="H9" s="201" t="s">
+      <c r="E9" s="194"/>
+      <c r="F9" s="194"/>
+      <c r="G9" s="195"/>
+      <c r="H9" s="191" t="s">
         <v>75</v>
       </c>
-      <c r="I9" s="202" t="s">
+      <c r="I9" s="192" t="s">
         <v>76</v>
       </c>
-      <c r="J9" s="202" t="s">
+      <c r="J9" s="192" t="s">
         <v>77</v>
       </c>
-      <c r="K9" s="202" t="s">
+      <c r="K9" s="192" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="198"/>
-      <c r="B10" s="200"/>
-      <c r="C10" s="198"/>
-      <c r="D10" s="206"/>
-      <c r="E10" s="207"/>
-      <c r="F10" s="207"/>
-      <c r="G10" s="208"/>
-      <c r="H10" s="197"/>
-      <c r="I10" s="197"/>
-      <c r="J10" s="197"/>
-      <c r="K10" s="197"/>
+      <c r="A10" s="188"/>
+      <c r="B10" s="190"/>
+      <c r="C10" s="188"/>
+      <c r="D10" s="196"/>
+      <c r="E10" s="197"/>
+      <c r="F10" s="197"/>
+      <c r="G10" s="198"/>
+      <c r="H10" s="187"/>
+      <c r="I10" s="187"/>
+      <c r="J10" s="187"/>
+      <c r="K10" s="187"/>
     </row>
     <row r="11" spans="1:11" ht="15">
-      <c r="A11" s="195"/>
-      <c r="B11" s="195"/>
-      <c r="C11" s="195"/>
-      <c r="D11" s="195"/>
-      <c r="E11" s="195"/>
-      <c r="F11" s="195"/>
-      <c r="G11" s="195"/>
-      <c r="H11" s="195"/>
-      <c r="I11" s="195"/>
-      <c r="J11" s="195"/>
-      <c r="K11" s="196"/>
+      <c r="A11" s="182"/>
+      <c r="B11" s="182"/>
+      <c r="C11" s="182"/>
+      <c r="D11" s="182"/>
+      <c r="E11" s="182"/>
+      <c r="F11" s="182"/>
+      <c r="G11" s="182"/>
+      <c r="H11" s="182"/>
+      <c r="I11" s="182"/>
+      <c r="J11" s="182"/>
+      <c r="K11" s="183"/>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="184" t="s">
@@ -7047,12 +7384,12 @@
       <c r="C13" s="92" t="s">
         <v>82</v>
       </c>
-      <c r="D13" s="187" t="s">
+      <c r="D13" s="199" t="s">
         <v>83</v>
       </c>
-      <c r="E13" s="176"/>
-      <c r="F13" s="176"/>
-      <c r="G13" s="177"/>
+      <c r="E13" s="200"/>
+      <c r="F13" s="200"/>
+      <c r="G13" s="201"/>
       <c r="H13" s="94"/>
       <c r="I13" s="96"/>
       <c r="J13" s="92" t="s">
@@ -7085,12 +7422,12 @@
       <c r="C15" s="102" t="s">
         <v>87</v>
       </c>
-      <c r="D15" s="188" t="s">
+      <c r="D15" s="202" t="s">
         <v>88</v>
       </c>
-      <c r="E15" s="189"/>
-      <c r="F15" s="189"/>
-      <c r="G15" s="190"/>
+      <c r="E15" s="203"/>
+      <c r="F15" s="203"/>
+      <c r="G15" s="204"/>
       <c r="H15" s="103"/>
       <c r="I15" s="103"/>
       <c r="J15" s="104" t="s">
@@ -7123,12 +7460,12 @@
       <c r="C17" s="98" t="s">
         <v>92</v>
       </c>
-      <c r="D17" s="187" t="s">
+      <c r="D17" s="199" t="s">
         <v>93</v>
       </c>
-      <c r="E17" s="191"/>
-      <c r="F17" s="191"/>
-      <c r="G17" s="192"/>
+      <c r="E17" s="205"/>
+      <c r="F17" s="205"/>
+      <c r="G17" s="206"/>
       <c r="H17" s="94"/>
       <c r="I17" s="93"/>
       <c r="J17" s="92" t="s">
@@ -7161,12 +7498,12 @@
       <c r="C19" s="92" t="s">
         <v>97</v>
       </c>
-      <c r="D19" s="175" t="s">
+      <c r="D19" s="207" t="s">
         <v>98</v>
       </c>
-      <c r="E19" s="176"/>
-      <c r="F19" s="176"/>
-      <c r="G19" s="177"/>
+      <c r="E19" s="200"/>
+      <c r="F19" s="200"/>
+      <c r="G19" s="201"/>
       <c r="H19" s="94"/>
       <c r="I19" s="93"/>
       <c r="J19" s="92" t="s">
@@ -7199,12 +7536,12 @@
       <c r="C21" s="92" t="s">
         <v>102</v>
       </c>
-      <c r="D21" s="175" t="s">
+      <c r="D21" s="207" t="s">
         <v>103</v>
       </c>
-      <c r="E21" s="176"/>
-      <c r="F21" s="176"/>
-      <c r="G21" s="177"/>
+      <c r="E21" s="200"/>
+      <c r="F21" s="200"/>
+      <c r="G21" s="201"/>
       <c r="H21" s="94"/>
       <c r="I21" s="93"/>
       <c r="J21" s="92" t="s">
@@ -7222,12 +7559,12 @@
       <c r="C22" s="92" t="s">
         <v>106</v>
       </c>
-      <c r="D22" s="175" t="s">
+      <c r="D22" s="207" t="s">
         <v>107</v>
       </c>
-      <c r="E22" s="176"/>
-      <c r="F22" s="176"/>
-      <c r="G22" s="177"/>
+      <c r="E22" s="200"/>
+      <c r="F22" s="200"/>
+      <c r="G22" s="201"/>
       <c r="H22" s="92"/>
       <c r="I22" s="92"/>
       <c r="J22" s="92" t="s">
@@ -7260,12 +7597,12 @@
       <c r="C24" s="92" t="s">
         <v>111</v>
       </c>
-      <c r="D24" s="175" t="s">
+      <c r="D24" s="207" t="s">
         <v>112</v>
       </c>
-      <c r="E24" s="176"/>
-      <c r="F24" s="176"/>
-      <c r="G24" s="177"/>
+      <c r="E24" s="200"/>
+      <c r="F24" s="200"/>
+      <c r="G24" s="201"/>
       <c r="H24" s="92"/>
       <c r="I24" s="92"/>
       <c r="J24" s="92" t="s">
@@ -7283,12 +7620,12 @@
       <c r="C25" s="92" t="s">
         <v>115</v>
       </c>
-      <c r="D25" s="175" t="s">
+      <c r="D25" s="207" t="s">
         <v>116</v>
       </c>
-      <c r="E25" s="176"/>
-      <c r="F25" s="176"/>
-      <c r="G25" s="177"/>
+      <c r="E25" s="200"/>
+      <c r="F25" s="200"/>
+      <c r="G25" s="201"/>
       <c r="H25" s="92"/>
       <c r="I25" s="92"/>
       <c r="J25" s="92" t="s">
@@ -7321,12 +7658,12 @@
       <c r="C27" s="92" t="s">
         <v>120</v>
       </c>
-      <c r="D27" s="175" t="s">
+      <c r="D27" s="207" t="s">
         <v>121</v>
       </c>
-      <c r="E27" s="176"/>
-      <c r="F27" s="176"/>
-      <c r="G27" s="177"/>
+      <c r="E27" s="200"/>
+      <c r="F27" s="200"/>
+      <c r="G27" s="201"/>
       <c r="H27" s="92"/>
       <c r="I27" s="92"/>
       <c r="J27" s="92" t="s">
@@ -7344,12 +7681,12 @@
       <c r="C28" s="92" t="s">
         <v>124</v>
       </c>
-      <c r="D28" s="175" t="s">
+      <c r="D28" s="207" t="s">
         <v>125</v>
       </c>
-      <c r="E28" s="176"/>
-      <c r="F28" s="176"/>
-      <c r="G28" s="177"/>
+      <c r="E28" s="200"/>
+      <c r="F28" s="200"/>
+      <c r="G28" s="201"/>
       <c r="H28" s="92"/>
       <c r="I28" s="92"/>
       <c r="J28" s="92" t="s">
@@ -7367,12 +7704,12 @@
       <c r="C29" s="92" t="s">
         <v>128</v>
       </c>
-      <c r="D29" s="175" t="s">
+      <c r="D29" s="207" t="s">
         <v>129</v>
       </c>
-      <c r="E29" s="176"/>
-      <c r="F29" s="176"/>
-      <c r="G29" s="177"/>
+      <c r="E29" s="200"/>
+      <c r="F29" s="200"/>
+      <c r="G29" s="201"/>
       <c r="H29" s="139"/>
       <c r="I29" s="139"/>
       <c r="J29" s="92" t="s">
@@ -7381,19 +7718,19 @@
       <c r="K29" s="139"/>
     </row>
     <row r="30" spans="1:11">
-      <c r="A30" s="178" t="s">
+      <c r="A30" s="208" t="s">
         <v>130</v>
       </c>
-      <c r="B30" s="179"/>
-      <c r="C30" s="179"/>
-      <c r="D30" s="179"/>
-      <c r="E30" s="179"/>
-      <c r="F30" s="179"/>
-      <c r="G30" s="179"/>
-      <c r="H30" s="179"/>
-      <c r="I30" s="179"/>
-      <c r="J30" s="179"/>
-      <c r="K30" s="180"/>
+      <c r="B30" s="209"/>
+      <c r="C30" s="209"/>
+      <c r="D30" s="209"/>
+      <c r="E30" s="209"/>
+      <c r="F30" s="209"/>
+      <c r="G30" s="209"/>
+      <c r="H30" s="209"/>
+      <c r="I30" s="209"/>
+      <c r="J30" s="209"/>
+      <c r="K30" s="210"/>
     </row>
     <row r="31" spans="1:11" ht="102">
       <c r="A31" s="90" t="s">
@@ -7405,12 +7742,12 @@
       <c r="C31" s="92" t="s">
         <v>132</v>
       </c>
-      <c r="D31" s="173" t="s">
+      <c r="D31" s="211" t="s">
         <v>133</v>
       </c>
-      <c r="E31" s="174"/>
-      <c r="F31" s="174"/>
-      <c r="G31" s="174"/>
+      <c r="E31" s="212"/>
+      <c r="F31" s="212"/>
+      <c r="G31" s="212"/>
       <c r="H31" s="92"/>
       <c r="I31" s="125"/>
       <c r="J31" s="92" t="s">
@@ -7428,12 +7765,12 @@
       <c r="C32" s="141" t="s">
         <v>135</v>
       </c>
-      <c r="D32" s="181" t="s">
+      <c r="D32" s="213" t="s">
         <v>136</v>
       </c>
-      <c r="E32" s="182"/>
-      <c r="F32" s="182"/>
-      <c r="G32" s="183"/>
+      <c r="E32" s="214"/>
+      <c r="F32" s="214"/>
+      <c r="G32" s="215"/>
       <c r="H32" s="141"/>
       <c r="I32" s="141"/>
       <c r="J32" s="140" t="s">
@@ -7451,12 +7788,12 @@
       <c r="C33" s="92" t="s">
         <v>138</v>
       </c>
-      <c r="D33" s="173" t="s">
+      <c r="D33" s="211" t="s">
         <v>139</v>
       </c>
-      <c r="E33" s="174"/>
-      <c r="F33" s="174"/>
-      <c r="G33" s="174"/>
+      <c r="E33" s="212"/>
+      <c r="F33" s="212"/>
+      <c r="G33" s="212"/>
       <c r="H33" s="92"/>
       <c r="I33" s="125"/>
       <c r="J33" s="92" t="s">
@@ -7474,12 +7811,12 @@
       <c r="C34" s="92" t="s">
         <v>141</v>
       </c>
-      <c r="D34" s="173" t="s">
+      <c r="D34" s="211" t="s">
         <v>142</v>
       </c>
-      <c r="E34" s="174"/>
-      <c r="F34" s="174"/>
-      <c r="G34" s="174"/>
+      <c r="E34" s="212"/>
+      <c r="F34" s="212"/>
+      <c r="G34" s="212"/>
       <c r="H34" s="92"/>
       <c r="I34" s="125"/>
       <c r="J34" s="92" t="s">
@@ -7497,12 +7834,12 @@
       <c r="C35" s="92" t="s">
         <v>144</v>
       </c>
-      <c r="D35" s="173" t="s">
+      <c r="D35" s="211" t="s">
         <v>145</v>
       </c>
-      <c r="E35" s="174"/>
-      <c r="F35" s="174"/>
-      <c r="G35" s="174"/>
+      <c r="E35" s="212"/>
+      <c r="F35" s="212"/>
+      <c r="G35" s="212"/>
       <c r="H35" s="92"/>
       <c r="I35" s="125"/>
       <c r="J35" s="92" t="s">
@@ -7520,12 +7857,12 @@
       <c r="C36" s="92" t="s">
         <v>147</v>
       </c>
-      <c r="D36" s="173" t="s">
+      <c r="D36" s="211" t="s">
         <v>148</v>
       </c>
-      <c r="E36" s="174"/>
-      <c r="F36" s="174"/>
-      <c r="G36" s="174"/>
+      <c r="E36" s="212"/>
+      <c r="F36" s="212"/>
+      <c r="G36" s="212"/>
       <c r="H36" s="92"/>
       <c r="I36" s="125"/>
       <c r="J36" s="92" t="s">
@@ -7543,12 +7880,12 @@
       <c r="C37" s="98" t="s">
         <v>150</v>
       </c>
-      <c r="D37" s="171" t="s">
+      <c r="D37" s="216" t="s">
         <v>151</v>
       </c>
-      <c r="E37" s="172"/>
-      <c r="F37" s="172"/>
-      <c r="G37" s="172"/>
+      <c r="E37" s="217"/>
+      <c r="F37" s="217"/>
+      <c r="G37" s="217"/>
       <c r="H37" s="98"/>
       <c r="I37" s="142"/>
       <c r="J37" s="98" t="s">
@@ -7566,12 +7903,12 @@
       <c r="C38" s="98" t="s">
         <v>153</v>
       </c>
-      <c r="D38" s="171" t="s">
+      <c r="D38" s="216" t="s">
         <v>154</v>
       </c>
-      <c r="E38" s="172"/>
-      <c r="F38" s="172"/>
-      <c r="G38" s="172"/>
+      <c r="E38" s="217"/>
+      <c r="F38" s="217"/>
+      <c r="G38" s="217"/>
       <c r="H38" s="98"/>
       <c r="I38" s="142"/>
       <c r="J38" s="98" t="s">
@@ -7589,12 +7926,12 @@
       <c r="C39" s="92" t="s">
         <v>156</v>
       </c>
-      <c r="D39" s="173" t="s">
+      <c r="D39" s="211" t="s">
         <v>157</v>
       </c>
-      <c r="E39" s="174"/>
-      <c r="F39" s="174"/>
-      <c r="G39" s="174"/>
+      <c r="E39" s="212"/>
+      <c r="F39" s="212"/>
+      <c r="G39" s="212"/>
       <c r="H39" s="92"/>
       <c r="I39" s="125"/>
       <c r="J39" s="92" t="s">
@@ -7612,12 +7949,12 @@
       <c r="C40" s="92" t="s">
         <v>159</v>
       </c>
-      <c r="D40" s="173" t="s">
+      <c r="D40" s="211" t="s">
         <v>160</v>
       </c>
-      <c r="E40" s="174"/>
-      <c r="F40" s="174"/>
-      <c r="G40" s="174"/>
+      <c r="E40" s="212"/>
+      <c r="F40" s="212"/>
+      <c r="G40" s="212"/>
       <c r="H40" s="92"/>
       <c r="I40" s="125"/>
       <c r="J40" s="92" t="s">
@@ -7635,12 +7972,12 @@
       <c r="C41" s="92" t="s">
         <v>159</v>
       </c>
-      <c r="D41" s="173" t="s">
+      <c r="D41" s="211" t="s">
         <v>160</v>
       </c>
-      <c r="E41" s="174"/>
-      <c r="F41" s="174"/>
-      <c r="G41" s="174"/>
+      <c r="E41" s="212"/>
+      <c r="F41" s="212"/>
+      <c r="G41" s="212"/>
       <c r="H41" s="92"/>
       <c r="I41" s="125"/>
       <c r="J41" s="92" t="s">
@@ -7658,12 +7995,12 @@
       <c r="C42" s="92" t="s">
         <v>163</v>
       </c>
-      <c r="D42" s="173" t="s">
+      <c r="D42" s="211" t="s">
         <v>164</v>
       </c>
-      <c r="E42" s="174"/>
-      <c r="F42" s="174"/>
-      <c r="G42" s="174"/>
+      <c r="E42" s="212"/>
+      <c r="F42" s="212"/>
+      <c r="G42" s="212"/>
       <c r="H42" s="92"/>
       <c r="I42" s="125"/>
       <c r="J42" s="92" t="s">
@@ -7673,12 +8010,36 @@
     </row>
   </sheetData>
   <mergeCells count="49">
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="D38:G38"/>
+    <mergeCell ref="D39:G39"/>
+    <mergeCell ref="D40:G40"/>
+    <mergeCell ref="D41:G41"/>
+    <mergeCell ref="D42:G42"/>
+    <mergeCell ref="D33:G33"/>
+    <mergeCell ref="D34:G34"/>
+    <mergeCell ref="D35:G35"/>
+    <mergeCell ref="D36:G36"/>
+    <mergeCell ref="D37:G37"/>
+    <mergeCell ref="D28:G28"/>
+    <mergeCell ref="D29:G29"/>
+    <mergeCell ref="A30:K30"/>
+    <mergeCell ref="D31:G31"/>
+    <mergeCell ref="D32:G32"/>
+    <mergeCell ref="A23:K23"/>
+    <mergeCell ref="D24:G24"/>
+    <mergeCell ref="D25:G25"/>
+    <mergeCell ref="A26:K26"/>
+    <mergeCell ref="D27:G27"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="D19:G19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="D21:G21"/>
+    <mergeCell ref="D22:G22"/>
+    <mergeCell ref="D13:G13"/>
+    <mergeCell ref="A14:K14"/>
+    <mergeCell ref="D15:G15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="D17:G17"/>
     <mergeCell ref="I6:K6"/>
     <mergeCell ref="I7:K7"/>
     <mergeCell ref="A8:D8"/>
@@ -7692,36 +8053,12 @@
     <mergeCell ref="J9:J10"/>
     <mergeCell ref="K9:K10"/>
     <mergeCell ref="D9:G10"/>
-    <mergeCell ref="D13:G13"/>
-    <mergeCell ref="A14:K14"/>
-    <mergeCell ref="D15:G15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="D17:G17"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="D19:G19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="D21:G21"/>
-    <mergeCell ref="D22:G22"/>
-    <mergeCell ref="A23:K23"/>
-    <mergeCell ref="D24:G24"/>
-    <mergeCell ref="D25:G25"/>
-    <mergeCell ref="A26:K26"/>
-    <mergeCell ref="D27:G27"/>
-    <mergeCell ref="D28:G28"/>
-    <mergeCell ref="D29:G29"/>
-    <mergeCell ref="A30:K30"/>
-    <mergeCell ref="D31:G31"/>
-    <mergeCell ref="D32:G32"/>
-    <mergeCell ref="D33:G33"/>
-    <mergeCell ref="D34:G34"/>
-    <mergeCell ref="D35:G35"/>
-    <mergeCell ref="D36:G36"/>
-    <mergeCell ref="D37:G37"/>
-    <mergeCell ref="D38:G38"/>
-    <mergeCell ref="D39:G39"/>
-    <mergeCell ref="D40:G40"/>
-    <mergeCell ref="D41:G41"/>
-    <mergeCell ref="D42:G42"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="I5:K5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7757,31 +8094,31 @@
       <c r="A3" s="70" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="209" t="s">
+      <c r="B3" s="171" t="s">
         <v>62</v>
       </c>
-      <c r="C3" s="209"/>
-      <c r="D3" s="210"/>
+      <c r="C3" s="171"/>
+      <c r="D3" s="172"/>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="74" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="211" t="s">
+      <c r="B4" s="174" t="s">
         <v>166</v>
       </c>
-      <c r="C4" s="212"/>
-      <c r="D4" s="213"/>
+      <c r="C4" s="175"/>
+      <c r="D4" s="176"/>
     </row>
     <row r="5" spans="1:11" ht="25.5">
       <c r="A5" s="74" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="214" t="s">
+      <c r="B5" s="177" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="215"/>
-      <c r="D5" s="216"/>
+      <c r="C5" s="178"/>
+      <c r="D5" s="179"/>
     </row>
     <row r="6" spans="1:11" ht="14.25">
       <c r="A6" s="77" t="s">
@@ -7812,59 +8149,59 @@
       </c>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="197" t="s">
+      <c r="A9" s="187" t="s">
         <v>71</v>
       </c>
-      <c r="B9" s="199" t="s">
+      <c r="B9" s="189" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="197" t="s">
+      <c r="C9" s="187" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="203" t="s">
+      <c r="D9" s="193" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="204"/>
-      <c r="F9" s="204"/>
-      <c r="G9" s="205"/>
-      <c r="H9" s="201" t="s">
+      <c r="E9" s="194"/>
+      <c r="F9" s="194"/>
+      <c r="G9" s="195"/>
+      <c r="H9" s="191" t="s">
         <v>75</v>
       </c>
-      <c r="I9" s="202" t="s">
+      <c r="I9" s="192" t="s">
         <v>76</v>
       </c>
-      <c r="J9" s="202" t="s">
+      <c r="J9" s="192" t="s">
         <v>77</v>
       </c>
-      <c r="K9" s="202" t="s">
+      <c r="K9" s="192" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="198"/>
-      <c r="B10" s="200"/>
-      <c r="C10" s="198"/>
-      <c r="D10" s="206"/>
-      <c r="E10" s="207"/>
-      <c r="F10" s="207"/>
-      <c r="G10" s="208"/>
-      <c r="H10" s="197"/>
-      <c r="I10" s="197"/>
-      <c r="J10" s="197"/>
-      <c r="K10" s="197"/>
+      <c r="A10" s="188"/>
+      <c r="B10" s="190"/>
+      <c r="C10" s="188"/>
+      <c r="D10" s="196"/>
+      <c r="E10" s="197"/>
+      <c r="F10" s="197"/>
+      <c r="G10" s="198"/>
+      <c r="H10" s="187"/>
+      <c r="I10" s="187"/>
+      <c r="J10" s="187"/>
+      <c r="K10" s="187"/>
     </row>
     <row r="11" spans="1:11" ht="15">
-      <c r="A11" s="195"/>
-      <c r="B11" s="195"/>
-      <c r="C11" s="195"/>
-      <c r="D11" s="195"/>
-      <c r="E11" s="195"/>
-      <c r="F11" s="195"/>
-      <c r="G11" s="195"/>
-      <c r="H11" s="195"/>
-      <c r="I11" s="195"/>
-      <c r="J11" s="195"/>
-      <c r="K11" s="196"/>
+      <c r="A11" s="182"/>
+      <c r="B11" s="182"/>
+      <c r="C11" s="182"/>
+      <c r="D11" s="182"/>
+      <c r="E11" s="182"/>
+      <c r="F11" s="182"/>
+      <c r="G11" s="182"/>
+      <c r="H11" s="182"/>
+      <c r="I11" s="182"/>
+      <c r="J11" s="182"/>
+      <c r="K11" s="183"/>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="184" t="s">
@@ -7891,12 +8228,12 @@
       <c r="C13" s="92" t="s">
         <v>169</v>
       </c>
-      <c r="D13" s="187" t="s">
+      <c r="D13" s="199" t="s">
         <v>170</v>
       </c>
-      <c r="E13" s="176"/>
-      <c r="F13" s="176"/>
-      <c r="G13" s="177"/>
+      <c r="E13" s="200"/>
+      <c r="F13" s="200"/>
+      <c r="G13" s="201"/>
       <c r="H13" s="94"/>
       <c r="I13" s="96"/>
       <c r="J13" s="92" t="s">
@@ -7914,12 +8251,12 @@
       <c r="C14" s="92" t="s">
         <v>172</v>
       </c>
-      <c r="D14" s="187" t="s">
+      <c r="D14" s="199" t="s">
         <v>173</v>
       </c>
-      <c r="E14" s="176"/>
-      <c r="F14" s="176"/>
-      <c r="G14" s="177"/>
+      <c r="E14" s="200"/>
+      <c r="F14" s="200"/>
+      <c r="G14" s="201"/>
       <c r="H14" s="94"/>
       <c r="I14" s="96"/>
       <c r="J14" s="92" t="s">
@@ -7937,12 +8274,12 @@
       <c r="C15" s="92" t="s">
         <v>175</v>
       </c>
-      <c r="D15" s="187" t="s">
+      <c r="D15" s="199" t="s">
         <v>176</v>
       </c>
-      <c r="E15" s="176"/>
-      <c r="F15" s="176"/>
-      <c r="G15" s="177"/>
+      <c r="E15" s="200"/>
+      <c r="F15" s="200"/>
+      <c r="G15" s="201"/>
       <c r="H15" s="94"/>
       <c r="I15" s="96"/>
       <c r="J15" s="92" t="s">
@@ -7960,12 +8297,12 @@
       <c r="C16" s="92" t="s">
         <v>178</v>
       </c>
-      <c r="D16" s="187" t="s">
+      <c r="D16" s="199" t="s">
         <v>179</v>
       </c>
-      <c r="E16" s="176"/>
-      <c r="F16" s="176"/>
-      <c r="G16" s="177"/>
+      <c r="E16" s="200"/>
+      <c r="F16" s="200"/>
+      <c r="G16" s="201"/>
       <c r="H16" s="94"/>
       <c r="I16" s="96"/>
       <c r="J16" s="92" t="s">
@@ -7983,12 +8320,12 @@
       <c r="C17" s="92" t="s">
         <v>181</v>
       </c>
-      <c r="D17" s="187" t="s">
+      <c r="D17" s="199" t="s">
         <v>182</v>
       </c>
-      <c r="E17" s="176"/>
-      <c r="F17" s="176"/>
-      <c r="G17" s="177"/>
+      <c r="E17" s="200"/>
+      <c r="F17" s="200"/>
+      <c r="G17" s="201"/>
       <c r="H17" s="94"/>
       <c r="I17" s="96"/>
       <c r="J17" s="92" t="s">
@@ -8006,12 +8343,12 @@
       <c r="C18" s="92" t="s">
         <v>184</v>
       </c>
-      <c r="D18" s="187" t="s">
+      <c r="D18" s="199" t="s">
         <v>185</v>
       </c>
-      <c r="E18" s="176"/>
-      <c r="F18" s="176"/>
-      <c r="G18" s="177"/>
+      <c r="E18" s="200"/>
+      <c r="F18" s="200"/>
+      <c r="G18" s="201"/>
       <c r="H18" s="94"/>
       <c r="I18" s="96"/>
       <c r="J18" s="92" t="s">
@@ -8029,12 +8366,12 @@
       <c r="C19" s="92" t="s">
         <v>187</v>
       </c>
-      <c r="D19" s="187" t="s">
+      <c r="D19" s="199" t="s">
         <v>188</v>
       </c>
-      <c r="E19" s="176"/>
-      <c r="F19" s="176"/>
-      <c r="G19" s="177"/>
+      <c r="E19" s="200"/>
+      <c r="F19" s="200"/>
+      <c r="G19" s="201"/>
       <c r="H19" s="94"/>
       <c r="I19" s="96"/>
       <c r="J19" s="92" t="s">
@@ -8067,12 +8404,12 @@
       <c r="C21" s="92" t="s">
         <v>191</v>
       </c>
-      <c r="D21" s="187" t="s">
+      <c r="D21" s="199" t="s">
         <v>192</v>
       </c>
-      <c r="E21" s="176"/>
-      <c r="F21" s="176"/>
-      <c r="G21" s="177"/>
+      <c r="E21" s="200"/>
+      <c r="F21" s="200"/>
+      <c r="G21" s="201"/>
       <c r="H21" s="94"/>
       <c r="I21" s="96"/>
       <c r="J21" s="92" t="s">
@@ -8090,12 +8427,12 @@
       <c r="C22" s="92" t="s">
         <v>194</v>
       </c>
-      <c r="D22" s="187" t="s">
+      <c r="D22" s="199" t="s">
         <v>195</v>
       </c>
-      <c r="E22" s="176"/>
-      <c r="F22" s="176"/>
-      <c r="G22" s="177"/>
+      <c r="E22" s="200"/>
+      <c r="F22" s="200"/>
+      <c r="G22" s="201"/>
       <c r="H22" s="94"/>
       <c r="I22" s="96"/>
       <c r="J22" s="92" t="s">
@@ -8113,12 +8450,12 @@
       <c r="C23" s="92" t="s">
         <v>197</v>
       </c>
-      <c r="D23" s="187" t="s">
+      <c r="D23" s="199" t="s">
         <v>198</v>
       </c>
-      <c r="E23" s="176"/>
-      <c r="F23" s="176"/>
-      <c r="G23" s="177"/>
+      <c r="E23" s="200"/>
+      <c r="F23" s="200"/>
+      <c r="G23" s="201"/>
       <c r="H23" s="94"/>
       <c r="I23" s="96"/>
       <c r="J23" s="92" t="s">
@@ -8180,6 +8517,21 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="D23:G23"/>
+    <mergeCell ref="A24:K24"/>
+    <mergeCell ref="D25:G25"/>
+    <mergeCell ref="D26:G26"/>
+    <mergeCell ref="D27:G27"/>
+    <mergeCell ref="D18:G18"/>
+    <mergeCell ref="D19:G19"/>
+    <mergeCell ref="A20:K20"/>
+    <mergeCell ref="D21:G21"/>
+    <mergeCell ref="D22:G22"/>
+    <mergeCell ref="D13:G13"/>
+    <mergeCell ref="D14:G14"/>
+    <mergeCell ref="D15:G15"/>
+    <mergeCell ref="D16:G16"/>
+    <mergeCell ref="D17:G17"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B5:D5"/>
@@ -8193,21 +8545,6 @@
     <mergeCell ref="J9:J10"/>
     <mergeCell ref="K9:K10"/>
     <mergeCell ref="D9:G10"/>
-    <mergeCell ref="D13:G13"/>
-    <mergeCell ref="D14:G14"/>
-    <mergeCell ref="D15:G15"/>
-    <mergeCell ref="D16:G16"/>
-    <mergeCell ref="D17:G17"/>
-    <mergeCell ref="D18:G18"/>
-    <mergeCell ref="D19:G19"/>
-    <mergeCell ref="A20:K20"/>
-    <mergeCell ref="D21:G21"/>
-    <mergeCell ref="D22:G22"/>
-    <mergeCell ref="D23:G23"/>
-    <mergeCell ref="A24:K24"/>
-    <mergeCell ref="D25:G25"/>
-    <mergeCell ref="D26:G26"/>
-    <mergeCell ref="D27:G27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8244,31 +8581,31 @@
       <c r="A3" s="70" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="209" t="s">
+      <c r="B3" s="171" t="s">
         <v>62</v>
       </c>
-      <c r="C3" s="209"/>
-      <c r="D3" s="210"/>
+      <c r="C3" s="171"/>
+      <c r="D3" s="172"/>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="74" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="211" t="s">
+      <c r="B4" s="174" t="s">
         <v>200</v>
       </c>
-      <c r="C4" s="212"/>
-      <c r="D4" s="213"/>
+      <c r="C4" s="175"/>
+      <c r="D4" s="176"/>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="74" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="214" t="s">
+      <c r="B5" s="177" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="215"/>
-      <c r="D5" s="216"/>
+      <c r="C5" s="178"/>
+      <c r="D5" s="179"/>
     </row>
     <row r="6" spans="1:11" ht="14.25">
       <c r="A6" s="77" t="s">
@@ -8299,59 +8636,59 @@
       </c>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="197" t="s">
+      <c r="A9" s="187" t="s">
         <v>71</v>
       </c>
-      <c r="B9" s="199" t="s">
+      <c r="B9" s="189" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="197" t="s">
+      <c r="C9" s="187" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="203" t="s">
+      <c r="D9" s="193" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="204"/>
-      <c r="F9" s="204"/>
-      <c r="G9" s="205"/>
-      <c r="H9" s="201" t="s">
+      <c r="E9" s="194"/>
+      <c r="F9" s="194"/>
+      <c r="G9" s="195"/>
+      <c r="H9" s="191" t="s">
         <v>75</v>
       </c>
-      <c r="I9" s="202" t="s">
+      <c r="I9" s="192" t="s">
         <v>76</v>
       </c>
-      <c r="J9" s="202" t="s">
+      <c r="J9" s="192" t="s">
         <v>77</v>
       </c>
-      <c r="K9" s="202" t="s">
+      <c r="K9" s="192" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="198"/>
-      <c r="B10" s="200"/>
-      <c r="C10" s="198"/>
-      <c r="D10" s="206"/>
-      <c r="E10" s="207"/>
-      <c r="F10" s="207"/>
-      <c r="G10" s="208"/>
-      <c r="H10" s="197"/>
-      <c r="I10" s="197"/>
-      <c r="J10" s="197"/>
-      <c r="K10" s="197"/>
+      <c r="A10" s="188"/>
+      <c r="B10" s="190"/>
+      <c r="C10" s="188"/>
+      <c r="D10" s="196"/>
+      <c r="E10" s="197"/>
+      <c r="F10" s="197"/>
+      <c r="G10" s="198"/>
+      <c r="H10" s="187"/>
+      <c r="I10" s="187"/>
+      <c r="J10" s="187"/>
+      <c r="K10" s="187"/>
     </row>
     <row r="11" spans="1:11" ht="15">
-      <c r="A11" s="195"/>
-      <c r="B11" s="195"/>
-      <c r="C11" s="195"/>
-      <c r="D11" s="195"/>
-      <c r="E11" s="195"/>
-      <c r="F11" s="195"/>
-      <c r="G11" s="195"/>
-      <c r="H11" s="195"/>
-      <c r="I11" s="195"/>
-      <c r="J11" s="195"/>
-      <c r="K11" s="196"/>
+      <c r="A11" s="182"/>
+      <c r="B11" s="182"/>
+      <c r="C11" s="182"/>
+      <c r="D11" s="182"/>
+      <c r="E11" s="182"/>
+      <c r="F11" s="182"/>
+      <c r="G11" s="182"/>
+      <c r="H11" s="182"/>
+      <c r="I11" s="182"/>
+      <c r="J11" s="182"/>
+      <c r="K11" s="183"/>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="184" t="s">
@@ -8378,12 +8715,12 @@
       <c r="C13" s="92" t="s">
         <v>203</v>
       </c>
-      <c r="D13" s="187" t="s">
+      <c r="D13" s="199" t="s">
         <v>204</v>
       </c>
-      <c r="E13" s="176"/>
-      <c r="F13" s="176"/>
-      <c r="G13" s="177"/>
+      <c r="E13" s="200"/>
+      <c r="F13" s="200"/>
+      <c r="G13" s="201"/>
       <c r="H13" s="94"/>
       <c r="I13" s="96"/>
       <c r="J13" s="92" t="s">
@@ -8401,12 +8738,12 @@
       <c r="C14" s="92" t="s">
         <v>206</v>
       </c>
-      <c r="D14" s="187" t="s">
+      <c r="D14" s="199" t="s">
         <v>207</v>
       </c>
-      <c r="E14" s="176"/>
-      <c r="F14" s="176"/>
-      <c r="G14" s="177"/>
+      <c r="E14" s="200"/>
+      <c r="F14" s="200"/>
+      <c r="G14" s="201"/>
       <c r="H14" s="94"/>
       <c r="I14" s="96"/>
       <c r="J14" s="92" t="s">
@@ -8424,12 +8761,12 @@
       <c r="C15" s="92" t="s">
         <v>209</v>
       </c>
-      <c r="D15" s="187" t="s">
+      <c r="D15" s="199" t="s">
         <v>210</v>
       </c>
-      <c r="E15" s="176"/>
-      <c r="F15" s="176"/>
-      <c r="G15" s="177"/>
+      <c r="E15" s="200"/>
+      <c r="F15" s="200"/>
+      <c r="G15" s="201"/>
       <c r="H15" s="94"/>
       <c r="I15" s="96"/>
       <c r="J15" s="92" t="s">
@@ -8447,12 +8784,12 @@
       <c r="C16" s="92" t="s">
         <v>212</v>
       </c>
-      <c r="D16" s="187" t="s">
+      <c r="D16" s="199" t="s">
         <v>213</v>
       </c>
-      <c r="E16" s="176"/>
-      <c r="F16" s="176"/>
-      <c r="G16" s="177"/>
+      <c r="E16" s="200"/>
+      <c r="F16" s="200"/>
+      <c r="G16" s="201"/>
       <c r="H16" s="94"/>
       <c r="I16" s="96"/>
       <c r="J16" s="92" t="s">
@@ -8470,12 +8807,12 @@
       <c r="C17" s="92" t="s">
         <v>215</v>
       </c>
-      <c r="D17" s="187" t="s">
+      <c r="D17" s="199" t="s">
         <v>216</v>
       </c>
-      <c r="E17" s="176"/>
-      <c r="F17" s="176"/>
-      <c r="G17" s="177"/>
+      <c r="E17" s="200"/>
+      <c r="F17" s="200"/>
+      <c r="G17" s="201"/>
       <c r="H17" s="94"/>
       <c r="I17" s="96"/>
       <c r="J17" s="92" t="s">
@@ -8493,12 +8830,12 @@
       <c r="C18" s="92" t="s">
         <v>218</v>
       </c>
-      <c r="D18" s="187" t="s">
+      <c r="D18" s="199" t="s">
         <v>219</v>
       </c>
-      <c r="E18" s="176"/>
-      <c r="F18" s="176"/>
-      <c r="G18" s="177"/>
+      <c r="E18" s="200"/>
+      <c r="F18" s="200"/>
+      <c r="G18" s="201"/>
       <c r="H18" s="94"/>
       <c r="I18" s="96"/>
       <c r="J18" s="92" t="s">
@@ -8508,14 +8845,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="A11:K11"/>
-    <mergeCell ref="A12:K12"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="K9:K10"/>
     <mergeCell ref="D18:G18"/>
     <mergeCell ref="A9:A10"/>
     <mergeCell ref="B9:B10"/>
@@ -8527,6 +8856,14 @@
     <mergeCell ref="D15:G15"/>
     <mergeCell ref="D16:G16"/>
     <mergeCell ref="D17:G17"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="A11:K11"/>
+    <mergeCell ref="A12:K12"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="K9:K10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8578,52 +8915,52 @@
       <c r="A3" s="106" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="209" t="s">
+      <c r="B3" s="171" t="s">
         <v>62</v>
       </c>
-      <c r="C3" s="209"/>
-      <c r="D3" s="210"/>
+      <c r="C3" s="171"/>
+      <c r="D3" s="172"/>
       <c r="E3" s="71"/>
       <c r="F3" s="71"/>
       <c r="G3" s="71"/>
       <c r="H3" s="71"/>
-      <c r="I3" s="193"/>
-      <c r="J3" s="193"/>
-      <c r="K3" s="193"/>
+      <c r="I3" s="173"/>
+      <c r="J3" s="173"/>
+      <c r="K3" s="173"/>
     </row>
     <row r="4" spans="1:11" ht="14.25">
       <c r="A4" s="74" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="211" t="s">
+      <c r="B4" s="174" t="s">
         <v>221</v>
       </c>
-      <c r="C4" s="212"/>
-      <c r="D4" s="213"/>
+      <c r="C4" s="175"/>
+      <c r="D4" s="176"/>
       <c r="E4" s="71"/>
       <c r="F4" s="71"/>
       <c r="G4" s="71"/>
       <c r="H4" s="71"/>
-      <c r="I4" s="193"/>
-      <c r="J4" s="193"/>
-      <c r="K4" s="193"/>
+      <c r="I4" s="173"/>
+      <c r="J4" s="173"/>
+      <c r="K4" s="173"/>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="107" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="214" t="s">
+      <c r="B5" s="177" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="215"/>
-      <c r="D5" s="216"/>
+      <c r="C5" s="178"/>
+      <c r="D5" s="179"/>
       <c r="E5" s="75"/>
       <c r="F5" s="75"/>
       <c r="G5" s="75"/>
       <c r="H5" s="75"/>
-      <c r="I5" s="217"/>
-      <c r="J5" s="217"/>
-      <c r="K5" s="217"/>
+      <c r="I5" s="180"/>
+      <c r="J5" s="180"/>
+      <c r="K5" s="180"/>
     </row>
     <row r="6" spans="1:11" ht="14.25">
       <c r="A6" s="77" t="s">
@@ -8644,9 +8981,9 @@
       <c r="F6" s="72"/>
       <c r="G6" s="72"/>
       <c r="H6" s="72"/>
-      <c r="I6" s="193"/>
-      <c r="J6" s="193"/>
-      <c r="K6" s="193"/>
+      <c r="I6" s="173"/>
+      <c r="J6" s="173"/>
+      <c r="K6" s="173"/>
     </row>
     <row r="7" spans="1:11" ht="14.25">
       <c r="A7" s="81" t="s">
@@ -8667,15 +9004,15 @@
       <c r="F7" s="85"/>
       <c r="G7" s="85"/>
       <c r="H7" s="85"/>
-      <c r="I7" s="193"/>
-      <c r="J7" s="193"/>
-      <c r="K7" s="193"/>
+      <c r="I7" s="173"/>
+      <c r="J7" s="173"/>
+      <c r="K7" s="173"/>
     </row>
     <row r="8" spans="1:11" ht="14.25">
-      <c r="A8" s="194"/>
-      <c r="B8" s="194"/>
-      <c r="C8" s="194"/>
-      <c r="D8" s="194"/>
+      <c r="A8" s="181"/>
+      <c r="B8" s="181"/>
+      <c r="C8" s="181"/>
+      <c r="D8" s="181"/>
       <c r="E8" s="72"/>
       <c r="F8" s="72"/>
       <c r="G8" s="72"/>
@@ -8685,59 +9022,59 @@
       <c r="K8" s="86"/>
     </row>
     <row r="9" spans="1:11" ht="13.5" customHeight="1">
-      <c r="A9" s="197" t="s">
+      <c r="A9" s="187" t="s">
         <v>71</v>
       </c>
-      <c r="B9" s="199" t="s">
+      <c r="B9" s="189" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="197" t="s">
+      <c r="C9" s="187" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="203" t="s">
+      <c r="D9" s="193" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="204"/>
-      <c r="F9" s="204"/>
-      <c r="G9" s="205"/>
-      <c r="H9" s="201" t="s">
+      <c r="E9" s="194"/>
+      <c r="F9" s="194"/>
+      <c r="G9" s="195"/>
+      <c r="H9" s="191" t="s">
         <v>75</v>
       </c>
-      <c r="I9" s="202" t="s">
+      <c r="I9" s="192" t="s">
         <v>76</v>
       </c>
-      <c r="J9" s="202" t="s">
+      <c r="J9" s="192" t="s">
         <v>77</v>
       </c>
-      <c r="K9" s="202" t="s">
+      <c r="K9" s="192" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="198"/>
-      <c r="B10" s="200"/>
-      <c r="C10" s="198"/>
-      <c r="D10" s="206"/>
-      <c r="E10" s="207"/>
-      <c r="F10" s="207"/>
-      <c r="G10" s="208"/>
-      <c r="H10" s="197"/>
-      <c r="I10" s="197"/>
-      <c r="J10" s="197"/>
-      <c r="K10" s="197"/>
+      <c r="A10" s="188"/>
+      <c r="B10" s="190"/>
+      <c r="C10" s="188"/>
+      <c r="D10" s="196"/>
+      <c r="E10" s="197"/>
+      <c r="F10" s="197"/>
+      <c r="G10" s="198"/>
+      <c r="H10" s="187"/>
+      <c r="I10" s="187"/>
+      <c r="J10" s="187"/>
+      <c r="K10" s="187"/>
     </row>
     <row r="11" spans="1:11" ht="15">
-      <c r="A11" s="195"/>
-      <c r="B11" s="195"/>
-      <c r="C11" s="195"/>
-      <c r="D11" s="195"/>
-      <c r="E11" s="195"/>
-      <c r="F11" s="195"/>
-      <c r="G11" s="195"/>
-      <c r="H11" s="195"/>
-      <c r="I11" s="195"/>
-      <c r="J11" s="195"/>
-      <c r="K11" s="196"/>
+      <c r="A11" s="182"/>
+      <c r="B11" s="182"/>
+      <c r="C11" s="182"/>
+      <c r="D11" s="182"/>
+      <c r="E11" s="182"/>
+      <c r="F11" s="182"/>
+      <c r="G11" s="182"/>
+      <c r="H11" s="182"/>
+      <c r="I11" s="182"/>
+      <c r="J11" s="182"/>
+      <c r="K11" s="183"/>
     </row>
     <row r="12" spans="1:11" ht="16.5" customHeight="1">
       <c r="A12" s="184" t="s">
@@ -8787,11 +9124,11 @@
       <c r="C14" s="92" t="s">
         <v>227</v>
       </c>
-      <c r="D14" s="175" t="s">
+      <c r="D14" s="207" t="s">
         <v>228</v>
       </c>
-      <c r="E14" s="176"/>
-      <c r="F14" s="176"/>
+      <c r="E14" s="200"/>
+      <c r="F14" s="200"/>
       <c r="G14" s="124"/>
       <c r="H14" s="94"/>
       <c r="I14" s="96"/>
@@ -8810,11 +9147,11 @@
       <c r="C15" s="93" t="s">
         <v>230</v>
       </c>
-      <c r="D15" s="175" t="s">
+      <c r="D15" s="207" t="s">
         <v>231</v>
       </c>
-      <c r="E15" s="176"/>
-      <c r="F15" s="176"/>
+      <c r="E15" s="200"/>
+      <c r="F15" s="200"/>
       <c r="G15" s="95"/>
       <c r="H15" s="95"/>
       <c r="I15" s="125"/>
@@ -8871,11 +9208,11 @@
       <c r="C18" s="93" t="s">
         <v>237</v>
       </c>
-      <c r="D18" s="175" t="s">
+      <c r="D18" s="207" t="s">
         <v>238</v>
       </c>
-      <c r="E18" s="176"/>
-      <c r="F18" s="176"/>
+      <c r="E18" s="200"/>
+      <c r="F18" s="200"/>
       <c r="G18" s="95"/>
       <c r="H18" s="95"/>
       <c r="I18" s="92"/>
@@ -8894,11 +9231,11 @@
       <c r="C19" s="93" t="s">
         <v>240</v>
       </c>
-      <c r="D19" s="175" t="s">
+      <c r="D19" s="207" t="s">
         <v>238</v>
       </c>
-      <c r="E19" s="176"/>
-      <c r="F19" s="176"/>
+      <c r="E19" s="200"/>
+      <c r="F19" s="200"/>
       <c r="G19" s="95"/>
       <c r="H19" s="95"/>
       <c r="I19" s="92"/>
@@ -8932,11 +9269,11 @@
       <c r="C21" s="98" t="s">
         <v>243</v>
       </c>
-      <c r="D21" s="175" t="s">
+      <c r="D21" s="207" t="s">
         <v>244</v>
       </c>
-      <c r="E21" s="176"/>
-      <c r="F21" s="176"/>
+      <c r="E21" s="200"/>
+      <c r="F21" s="200"/>
       <c r="G21" s="95"/>
       <c r="H21" s="94"/>
       <c r="I21" s="93"/>
@@ -8955,11 +9292,11 @@
       <c r="C22" s="92" t="s">
         <v>246</v>
       </c>
-      <c r="D22" s="175" t="s">
+      <c r="D22" s="207" t="s">
         <v>247</v>
       </c>
-      <c r="E22" s="176"/>
-      <c r="F22" s="176"/>
+      <c r="E22" s="200"/>
+      <c r="F22" s="200"/>
       <c r="G22" s="95"/>
       <c r="H22" s="92"/>
       <c r="I22" s="92"/>
@@ -9039,11 +9376,11 @@
       <c r="C26" s="92" t="s">
         <v>255</v>
       </c>
-      <c r="D26" s="174" t="s">
+      <c r="D26" s="212" t="s">
         <v>256</v>
       </c>
-      <c r="E26" s="174"/>
-      <c r="F26" s="175"/>
+      <c r="E26" s="212"/>
+      <c r="F26" s="207"/>
       <c r="G26" s="95"/>
       <c r="H26" s="95"/>
       <c r="I26" s="92"/>
@@ -9062,11 +9399,11 @@
       <c r="C27" s="92" t="s">
         <v>258</v>
       </c>
-      <c r="D27" s="174" t="s">
+      <c r="D27" s="212" t="s">
         <v>259</v>
       </c>
-      <c r="E27" s="174"/>
-      <c r="F27" s="175"/>
+      <c r="E27" s="212"/>
+      <c r="F27" s="207"/>
       <c r="G27" s="95"/>
       <c r="H27" s="92"/>
       <c r="I27" s="92"/>
@@ -9102,25 +9439,6 @@
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A11:K11"/>
-    <mergeCell ref="A12:K12"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="K9:K10"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="D17:F17"/>
     <mergeCell ref="D27:F27"/>
     <mergeCell ref="A9:A10"/>
     <mergeCell ref="B9:B10"/>
@@ -9137,6 +9455,25 @@
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="D21:F21"/>
     <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A11:K11"/>
+    <mergeCell ref="A12:K12"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="K9:K10"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="I5:K5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -9195,54 +9532,54 @@
       <c r="A3" s="106" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="209" t="s">
+      <c r="B3" s="171" t="s">
         <v>62</v>
       </c>
-      <c r="C3" s="209"/>
-      <c r="D3" s="210"/>
+      <c r="C3" s="171"/>
+      <c r="D3" s="172"/>
       <c r="E3" s="71"/>
       <c r="F3" s="71"/>
       <c r="G3" s="71"/>
       <c r="H3" s="71"/>
-      <c r="I3" s="193"/>
-      <c r="J3" s="193"/>
-      <c r="K3" s="193"/>
+      <c r="I3" s="173"/>
+      <c r="J3" s="173"/>
+      <c r="K3" s="173"/>
       <c r="L3" s="73"/>
     </row>
     <row r="4" spans="1:12" s="61" customFormat="1" ht="13.15" customHeight="1">
       <c r="A4" s="74" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="211" t="s">
+      <c r="B4" s="174" t="s">
         <v>260</v>
       </c>
-      <c r="C4" s="212"/>
-      <c r="D4" s="213"/>
+      <c r="C4" s="175"/>
+      <c r="D4" s="176"/>
       <c r="E4" s="71"/>
       <c r="F4" s="71"/>
       <c r="G4" s="71"/>
       <c r="H4" s="71"/>
-      <c r="I4" s="193"/>
-      <c r="J4" s="193"/>
-      <c r="K4" s="193"/>
+      <c r="I4" s="173"/>
+      <c r="J4" s="173"/>
+      <c r="K4" s="173"/>
       <c r="L4" s="73"/>
     </row>
     <row r="5" spans="1:12" s="62" customFormat="1" ht="12.75">
       <c r="A5" s="107" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="214" t="s">
+      <c r="B5" s="177" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="215"/>
-      <c r="D5" s="216"/>
+      <c r="C5" s="178"/>
+      <c r="D5" s="179"/>
       <c r="E5" s="75"/>
       <c r="F5" s="75"/>
       <c r="G5" s="75"/>
       <c r="H5" s="75"/>
-      <c r="I5" s="217"/>
-      <c r="J5" s="217"/>
-      <c r="K5" s="217"/>
+      <c r="I5" s="180"/>
+      <c r="J5" s="180"/>
+      <c r="K5" s="180"/>
       <c r="L5" s="76"/>
     </row>
     <row r="6" spans="1:12" s="61" customFormat="1" ht="15" customHeight="1">
@@ -9264,9 +9601,9 @@
       <c r="F6" s="72"/>
       <c r="G6" s="72"/>
       <c r="H6" s="72"/>
-      <c r="I6" s="193"/>
-      <c r="J6" s="193"/>
-      <c r="K6" s="193"/>
+      <c r="I6" s="173"/>
+      <c r="J6" s="173"/>
+      <c r="K6" s="173"/>
       <c r="L6" s="73"/>
     </row>
     <row r="7" spans="1:12" s="61" customFormat="1" ht="15" customHeight="1">
@@ -9288,16 +9625,16 @@
       <c r="F7" s="85"/>
       <c r="G7" s="85"/>
       <c r="H7" s="85"/>
-      <c r="I7" s="193"/>
-      <c r="J7" s="193"/>
-      <c r="K7" s="193"/>
+      <c r="I7" s="173"/>
+      <c r="J7" s="173"/>
+      <c r="K7" s="173"/>
       <c r="L7" s="73"/>
     </row>
     <row r="8" spans="1:12" s="61" customFormat="1" ht="15" customHeight="1">
-      <c r="A8" s="194"/>
-      <c r="B8" s="194"/>
-      <c r="C8" s="194"/>
-      <c r="D8" s="194"/>
+      <c r="A8" s="181"/>
+      <c r="B8" s="181"/>
+      <c r="C8" s="181"/>
+      <c r="D8" s="181"/>
       <c r="E8" s="72"/>
       <c r="F8" s="72"/>
       <c r="G8" s="72"/>
@@ -9308,76 +9645,76 @@
       <c r="L8" s="73"/>
     </row>
     <row r="9" spans="1:12" s="63" customFormat="1" ht="12" customHeight="1">
-      <c r="A9" s="197" t="s">
+      <c r="A9" s="187" t="s">
         <v>71</v>
       </c>
-      <c r="B9" s="199" t="s">
+      <c r="B9" s="189" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="197" t="s">
+      <c r="C9" s="187" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="203" t="s">
+      <c r="D9" s="193" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="204"/>
-      <c r="F9" s="204"/>
-      <c r="G9" s="205"/>
-      <c r="H9" s="201" t="s">
+      <c r="E9" s="194"/>
+      <c r="F9" s="194"/>
+      <c r="G9" s="195"/>
+      <c r="H9" s="191" t="s">
         <v>75</v>
       </c>
-      <c r="I9" s="202" t="s">
+      <c r="I9" s="192" t="s">
         <v>76</v>
       </c>
-      <c r="J9" s="202" t="s">
+      <c r="J9" s="192" t="s">
         <v>77</v>
       </c>
-      <c r="K9" s="202" t="s">
+      <c r="K9" s="192" t="s">
         <v>78</v>
       </c>
       <c r="L9" s="87"/>
     </row>
     <row r="10" spans="1:12" s="61" customFormat="1" ht="12" customHeight="1">
-      <c r="A10" s="198"/>
-      <c r="B10" s="200"/>
-      <c r="C10" s="198"/>
-      <c r="D10" s="206"/>
-      <c r="E10" s="207"/>
-      <c r="F10" s="207"/>
-      <c r="G10" s="208"/>
-      <c r="H10" s="197"/>
-      <c r="I10" s="197"/>
-      <c r="J10" s="197"/>
-      <c r="K10" s="197"/>
+      <c r="A10" s="188"/>
+      <c r="B10" s="190"/>
+      <c r="C10" s="188"/>
+      <c r="D10" s="196"/>
+      <c r="E10" s="197"/>
+      <c r="F10" s="197"/>
+      <c r="G10" s="198"/>
+      <c r="H10" s="187"/>
+      <c r="I10" s="187"/>
+      <c r="J10" s="187"/>
+      <c r="K10" s="187"/>
       <c r="L10" s="73"/>
     </row>
     <row r="11" spans="1:12" s="64" customFormat="1" ht="15">
-      <c r="A11" s="195"/>
-      <c r="B11" s="195"/>
-      <c r="C11" s="195"/>
-      <c r="D11" s="195"/>
-      <c r="E11" s="195"/>
-      <c r="F11" s="195"/>
-      <c r="G11" s="195"/>
-      <c r="H11" s="195"/>
-      <c r="I11" s="195"/>
-      <c r="J11" s="195"/>
-      <c r="K11" s="196"/>
+      <c r="A11" s="182"/>
+      <c r="B11" s="182"/>
+      <c r="C11" s="182"/>
+      <c r="D11" s="182"/>
+      <c r="E11" s="182"/>
+      <c r="F11" s="182"/>
+      <c r="G11" s="182"/>
+      <c r="H11" s="182"/>
+      <c r="I11" s="182"/>
+      <c r="J11" s="182"/>
+      <c r="K11" s="183"/>
     </row>
     <row r="12" spans="1:12" s="65" customFormat="1" ht="24.6" customHeight="1">
-      <c r="A12" s="227" t="s">
+      <c r="A12" s="224" t="s">
         <v>261</v>
       </c>
-      <c r="B12" s="228"/>
-      <c r="C12" s="228"/>
-      <c r="D12" s="228"/>
-      <c r="E12" s="228"/>
-      <c r="F12" s="228"/>
-      <c r="G12" s="228"/>
-      <c r="H12" s="228"/>
-      <c r="I12" s="228"/>
-      <c r="J12" s="228"/>
-      <c r="K12" s="229"/>
+      <c r="B12" s="225"/>
+      <c r="C12" s="225"/>
+      <c r="D12" s="225"/>
+      <c r="E12" s="225"/>
+      <c r="F12" s="225"/>
+      <c r="G12" s="225"/>
+      <c r="H12" s="225"/>
+      <c r="I12" s="225"/>
+      <c r="J12" s="225"/>
+      <c r="K12" s="226"/>
     </row>
     <row r="13" spans="1:12" s="65" customFormat="1" ht="81.599999999999994" customHeight="1" outlineLevel="1">
       <c r="A13" s="108" t="s">
@@ -9389,11 +9726,11 @@
       <c r="C13" s="109" t="s">
         <v>263</v>
       </c>
-      <c r="D13" s="175" t="s">
+      <c r="D13" s="207" t="s">
         <v>264</v>
       </c>
-      <c r="E13" s="176"/>
-      <c r="F13" s="176"/>
+      <c r="E13" s="200"/>
+      <c r="F13" s="200"/>
       <c r="G13" s="95"/>
       <c r="H13" s="94"/>
       <c r="I13" s="96"/>
@@ -9410,11 +9747,11 @@
       <c r="C14" s="111" t="s">
         <v>266</v>
       </c>
-      <c r="D14" s="175" t="s">
+      <c r="D14" s="207" t="s">
         <v>267</v>
       </c>
-      <c r="E14" s="176"/>
-      <c r="F14" s="176"/>
+      <c r="E14" s="200"/>
+      <c r="F14" s="200"/>
       <c r="G14" s="95"/>
       <c r="H14" s="94"/>
       <c r="I14" s="93"/>
@@ -9431,11 +9768,11 @@
       <c r="C15" s="109" t="s">
         <v>269</v>
       </c>
-      <c r="D15" s="175" t="s">
+      <c r="D15" s="207" t="s">
         <v>270</v>
       </c>
-      <c r="E15" s="176"/>
-      <c r="F15" s="176"/>
+      <c r="E15" s="200"/>
+      <c r="F15" s="200"/>
       <c r="G15" s="95"/>
       <c r="H15" s="94"/>
       <c r="I15" s="93"/>
@@ -9452,11 +9789,11 @@
       <c r="C16" s="111" t="s">
         <v>272</v>
       </c>
-      <c r="D16" s="175" t="s">
+      <c r="D16" s="207" t="s">
         <v>273</v>
       </c>
-      <c r="E16" s="176"/>
-      <c r="F16" s="176"/>
+      <c r="E16" s="200"/>
+      <c r="F16" s="200"/>
       <c r="G16" s="95"/>
       <c r="H16" s="94"/>
       <c r="I16" s="93"/>
@@ -9473,11 +9810,11 @@
       <c r="C17" s="109" t="s">
         <v>275</v>
       </c>
-      <c r="D17" s="175" t="s">
+      <c r="D17" s="207" t="s">
         <v>276</v>
       </c>
-      <c r="E17" s="176"/>
-      <c r="F17" s="176"/>
+      <c r="E17" s="200"/>
+      <c r="F17" s="200"/>
       <c r="G17" s="95"/>
       <c r="H17" s="94"/>
       <c r="I17" s="93"/>
@@ -9494,11 +9831,11 @@
       <c r="C18" s="111" t="s">
         <v>278</v>
       </c>
-      <c r="D18" s="175" t="s">
+      <c r="D18" s="207" t="s">
         <v>279</v>
       </c>
-      <c r="E18" s="176"/>
-      <c r="F18" s="176"/>
+      <c r="E18" s="200"/>
+      <c r="F18" s="200"/>
       <c r="G18" s="95"/>
       <c r="H18" s="94"/>
       <c r="I18" s="96"/>
@@ -9515,11 +9852,11 @@
       <c r="C19" s="109" t="s">
         <v>281</v>
       </c>
-      <c r="D19" s="175" t="s">
+      <c r="D19" s="207" t="s">
         <v>282</v>
       </c>
-      <c r="E19" s="176"/>
-      <c r="F19" s="176"/>
+      <c r="E19" s="200"/>
+      <c r="F19" s="200"/>
       <c r="G19" s="95"/>
       <c r="H19" s="94"/>
       <c r="I19" s="93"/>
@@ -9536,11 +9873,11 @@
       <c r="C20" s="111" t="s">
         <v>284</v>
       </c>
-      <c r="D20" s="175" t="s">
+      <c r="D20" s="207" t="s">
         <v>285</v>
       </c>
-      <c r="E20" s="176"/>
-      <c r="F20" s="176"/>
+      <c r="E20" s="200"/>
+      <c r="F20" s="200"/>
       <c r="G20" s="95"/>
       <c r="H20" s="94"/>
       <c r="I20" s="93"/>
@@ -9557,11 +9894,11 @@
       <c r="C21" s="109" t="s">
         <v>287</v>
       </c>
-      <c r="D21" s="175" t="s">
+      <c r="D21" s="207" t="s">
         <v>288</v>
       </c>
-      <c r="E21" s="176"/>
-      <c r="F21" s="176"/>
+      <c r="E21" s="200"/>
+      <c r="F21" s="200"/>
       <c r="G21" s="95"/>
       <c r="H21" s="94"/>
       <c r="I21" s="93"/>
@@ -9578,11 +9915,11 @@
       <c r="C22" s="111" t="s">
         <v>290</v>
       </c>
-      <c r="D22" s="175" t="s">
+      <c r="D22" s="207" t="s">
         <v>291</v>
       </c>
-      <c r="E22" s="176"/>
-      <c r="F22" s="176"/>
+      <c r="E22" s="200"/>
+      <c r="F22" s="200"/>
       <c r="G22" s="95"/>
       <c r="H22" s="94"/>
       <c r="I22" s="93"/>
@@ -9599,11 +9936,11 @@
       <c r="C23" s="109" t="s">
         <v>293</v>
       </c>
-      <c r="D23" s="175" t="s">
+      <c r="D23" s="207" t="s">
         <v>294</v>
       </c>
-      <c r="E23" s="176"/>
-      <c r="F23" s="176"/>
+      <c r="E23" s="200"/>
+      <c r="F23" s="200"/>
       <c r="G23" s="95"/>
       <c r="H23" s="94"/>
       <c r="I23" s="96"/>
@@ -9620,11 +9957,11 @@
       <c r="C24" s="111" t="s">
         <v>296</v>
       </c>
-      <c r="D24" s="175" t="s">
+      <c r="D24" s="207" t="s">
         <v>297</v>
       </c>
-      <c r="E24" s="176"/>
-      <c r="F24" s="176"/>
+      <c r="E24" s="200"/>
+      <c r="F24" s="200"/>
       <c r="G24" s="95"/>
       <c r="H24" s="94"/>
       <c r="I24" s="93"/>
@@ -9641,11 +9978,11 @@
       <c r="C25" s="109" t="s">
         <v>300</v>
       </c>
-      <c r="D25" s="175" t="s">
+      <c r="D25" s="207" t="s">
         <v>301</v>
       </c>
-      <c r="E25" s="176"/>
-      <c r="F25" s="176"/>
+      <c r="E25" s="200"/>
+      <c r="F25" s="200"/>
       <c r="G25" s="95"/>
       <c r="H25" s="94"/>
       <c r="I25" s="93"/>
@@ -9662,11 +9999,11 @@
       <c r="C26" s="111" t="s">
         <v>304</v>
       </c>
-      <c r="D26" s="175" t="s">
+      <c r="D26" s="207" t="s">
         <v>305</v>
       </c>
-      <c r="E26" s="176"/>
-      <c r="F26" s="176"/>
+      <c r="E26" s="200"/>
+      <c r="F26" s="200"/>
       <c r="G26" s="95"/>
       <c r="H26" s="94"/>
       <c r="I26" s="93"/>
@@ -9674,7 +10011,7 @@
       <c r="K26" s="92"/>
     </row>
     <row r="27" spans="1:11" ht="25.15" customHeight="1">
-      <c r="A27" s="226" t="s">
+      <c r="A27" s="227" t="s">
         <v>306</v>
       </c>
       <c r="B27" s="185"/>
@@ -9698,11 +10035,11 @@
       <c r="C28" s="109" t="s">
         <v>309</v>
       </c>
-      <c r="D28" s="175" t="s">
+      <c r="D28" s="207" t="s">
         <v>310</v>
       </c>
-      <c r="E28" s="176"/>
-      <c r="F28" s="176"/>
+      <c r="E28" s="200"/>
+      <c r="F28" s="200"/>
       <c r="G28" s="95"/>
       <c r="H28" s="94"/>
       <c r="I28" s="96"/>
@@ -9719,11 +10056,11 @@
       <c r="C29" s="111" t="s">
         <v>313</v>
       </c>
-      <c r="D29" s="175" t="s">
+      <c r="D29" s="207" t="s">
         <v>314</v>
       </c>
-      <c r="E29" s="176"/>
-      <c r="F29" s="176"/>
+      <c r="E29" s="200"/>
+      <c r="F29" s="200"/>
       <c r="G29" s="95"/>
       <c r="H29" s="94"/>
       <c r="I29" s="93"/>
@@ -9740,11 +10077,11 @@
       <c r="C30" s="109" t="s">
         <v>317</v>
       </c>
-      <c r="D30" s="175" t="s">
+      <c r="D30" s="207" t="s">
         <v>318</v>
       </c>
-      <c r="E30" s="176"/>
-      <c r="F30" s="176"/>
+      <c r="E30" s="200"/>
+      <c r="F30" s="200"/>
       <c r="G30" s="95"/>
       <c r="H30" s="94"/>
       <c r="I30" s="93"/>
@@ -9761,11 +10098,11 @@
       <c r="C31" s="111" t="s">
         <v>321</v>
       </c>
-      <c r="D31" s="175" t="s">
+      <c r="D31" s="207" t="s">
         <v>322</v>
       </c>
-      <c r="E31" s="176"/>
-      <c r="F31" s="176"/>
+      <c r="E31" s="200"/>
+      <c r="F31" s="200"/>
       <c r="G31" s="95"/>
       <c r="H31" s="94"/>
       <c r="I31" s="93"/>
@@ -9782,11 +10119,11 @@
       <c r="C32" s="109" t="s">
         <v>325</v>
       </c>
-      <c r="D32" s="175" t="s">
+      <c r="D32" s="207" t="s">
         <v>326</v>
       </c>
-      <c r="E32" s="176"/>
-      <c r="F32" s="176"/>
+      <c r="E32" s="200"/>
+      <c r="F32" s="200"/>
       <c r="G32" s="95"/>
       <c r="H32" s="94"/>
       <c r="I32" s="93"/>
@@ -9803,11 +10140,11 @@
       <c r="C33" s="111" t="s">
         <v>329</v>
       </c>
-      <c r="D33" s="175" t="s">
+      <c r="D33" s="207" t="s">
         <v>322</v>
       </c>
-      <c r="E33" s="176"/>
-      <c r="F33" s="176"/>
+      <c r="E33" s="200"/>
+      <c r="F33" s="200"/>
       <c r="G33" s="95"/>
       <c r="H33" s="94"/>
       <c r="I33" s="93"/>
@@ -9824,11 +10161,11 @@
       <c r="C34" s="109" t="s">
         <v>332</v>
       </c>
-      <c r="D34" s="175" t="s">
+      <c r="D34" s="207" t="s">
         <v>333</v>
       </c>
-      <c r="E34" s="176"/>
-      <c r="F34" s="176"/>
+      <c r="E34" s="200"/>
+      <c r="F34" s="200"/>
       <c r="G34" s="95"/>
       <c r="H34" s="94"/>
       <c r="I34" s="93"/>
@@ -9845,11 +10182,11 @@
       <c r="C35" s="111" t="s">
         <v>336</v>
       </c>
-      <c r="D35" s="175" t="s">
+      <c r="D35" s="207" t="s">
         <v>337</v>
       </c>
-      <c r="E35" s="176"/>
-      <c r="F35" s="176"/>
+      <c r="E35" s="200"/>
+      <c r="F35" s="200"/>
       <c r="G35" s="95"/>
       <c r="H35" s="94"/>
       <c r="I35" s="93"/>
@@ -9857,7 +10194,7 @@
       <c r="K35" s="92"/>
     </row>
     <row r="36" spans="1:11" ht="28.15" customHeight="1">
-      <c r="A36" s="226" t="s">
+      <c r="A36" s="227" t="s">
         <v>338</v>
       </c>
       <c r="B36" s="185"/>
@@ -9881,11 +10218,11 @@
       <c r="C37" s="109" t="s">
         <v>341</v>
       </c>
-      <c r="D37" s="175" t="s">
+      <c r="D37" s="207" t="s">
         <v>342</v>
       </c>
-      <c r="E37" s="176"/>
-      <c r="F37" s="176"/>
+      <c r="E37" s="200"/>
+      <c r="F37" s="200"/>
       <c r="G37" s="95"/>
       <c r="H37" s="94"/>
       <c r="I37" s="93"/>
@@ -9902,11 +10239,11 @@
       <c r="C38" s="111" t="s">
         <v>345</v>
       </c>
-      <c r="D38" s="175" t="s">
+      <c r="D38" s="207" t="s">
         <v>346</v>
       </c>
-      <c r="E38" s="176"/>
-      <c r="F38" s="176"/>
+      <c r="E38" s="200"/>
+      <c r="F38" s="200"/>
       <c r="G38" s="95"/>
       <c r="H38" s="94"/>
       <c r="I38" s="93"/>
@@ -9914,7 +10251,7 @@
       <c r="K38" s="92"/>
     </row>
     <row r="39" spans="1:11" ht="28.9" customHeight="1">
-      <c r="A39" s="226" t="s">
+      <c r="A39" s="227" t="s">
         <v>347</v>
       </c>
       <c r="B39" s="185"/>
@@ -9938,11 +10275,11 @@
       <c r="C40" s="109" t="s">
         <v>350</v>
       </c>
-      <c r="D40" s="175" t="s">
+      <c r="D40" s="207" t="s">
         <v>351</v>
       </c>
-      <c r="E40" s="176"/>
-      <c r="F40" s="176"/>
+      <c r="E40" s="200"/>
+      <c r="F40" s="200"/>
       <c r="G40" s="95"/>
       <c r="H40" s="94"/>
       <c r="I40" s="93"/>
@@ -9959,11 +10296,11 @@
       <c r="C41" s="111" t="s">
         <v>354</v>
       </c>
-      <c r="D41" s="175" t="s">
+      <c r="D41" s="207" t="s">
         <v>355</v>
       </c>
-      <c r="E41" s="176"/>
-      <c r="F41" s="176"/>
+      <c r="E41" s="200"/>
+      <c r="F41" s="200"/>
       <c r="G41" s="95"/>
       <c r="H41" s="94"/>
       <c r="I41" s="93"/>
@@ -9974,9 +10311,9 @@
       <c r="A42" s="90"/>
       <c r="B42" s="99"/>
       <c r="C42" s="92"/>
-      <c r="D42" s="224"/>
-      <c r="E42" s="225"/>
-      <c r="F42" s="225"/>
+      <c r="D42" s="228"/>
+      <c r="E42" s="229"/>
+      <c r="F42" s="229"/>
       <c r="G42" s="95"/>
       <c r="H42" s="94"/>
       <c r="I42" s="93"/>
@@ -9987,9 +10324,9 @@
       <c r="A43" s="90"/>
       <c r="B43" s="97"/>
       <c r="C43" s="98"/>
-      <c r="D43" s="224"/>
-      <c r="E43" s="176"/>
-      <c r="F43" s="176"/>
+      <c r="D43" s="228"/>
+      <c r="E43" s="200"/>
+      <c r="F43" s="200"/>
       <c r="G43" s="95"/>
       <c r="H43" s="94"/>
       <c r="I43" s="93"/>
@@ -10000,9 +10337,9 @@
       <c r="A44" s="90"/>
       <c r="B44" s="99"/>
       <c r="C44" s="92"/>
-      <c r="D44" s="224"/>
-      <c r="E44" s="225"/>
-      <c r="F44" s="225"/>
+      <c r="D44" s="228"/>
+      <c r="E44" s="229"/>
+      <c r="F44" s="229"/>
       <c r="G44" s="95"/>
       <c r="H44" s="94"/>
       <c r="I44" s="93"/>
@@ -10013,9 +10350,9 @@
       <c r="A45" s="90"/>
       <c r="B45" s="97"/>
       <c r="C45" s="98"/>
-      <c r="D45" s="224"/>
-      <c r="E45" s="176"/>
-      <c r="F45" s="176"/>
+      <c r="D45" s="228"/>
+      <c r="E45" s="200"/>
+      <c r="F45" s="200"/>
       <c r="G45" s="95"/>
       <c r="H45" s="94"/>
       <c r="I45" s="93"/>
@@ -10026,9 +10363,9 @@
       <c r="A46" s="90"/>
       <c r="B46" s="99"/>
       <c r="C46" s="92"/>
-      <c r="D46" s="224"/>
-      <c r="E46" s="225"/>
-      <c r="F46" s="225"/>
+      <c r="D46" s="228"/>
+      <c r="E46" s="229"/>
+      <c r="F46" s="229"/>
       <c r="G46" s="95"/>
       <c r="H46" s="94"/>
       <c r="I46" s="93"/>
@@ -10039,9 +10376,9 @@
       <c r="A47" s="90"/>
       <c r="B47" s="97"/>
       <c r="C47" s="98"/>
-      <c r="D47" s="224"/>
-      <c r="E47" s="176"/>
-      <c r="F47" s="176"/>
+      <c r="D47" s="228"/>
+      <c r="E47" s="200"/>
+      <c r="F47" s="200"/>
       <c r="G47" s="95"/>
       <c r="H47" s="94"/>
       <c r="I47" s="93"/>
@@ -10052,9 +10389,9 @@
       <c r="A48" s="90"/>
       <c r="B48" s="99"/>
       <c r="C48" s="92"/>
-      <c r="D48" s="224"/>
-      <c r="E48" s="225"/>
-      <c r="F48" s="225"/>
+      <c r="D48" s="228"/>
+      <c r="E48" s="229"/>
+      <c r="F48" s="229"/>
       <c r="G48" s="95"/>
       <c r="H48" s="94"/>
       <c r="I48" s="93"/>
@@ -10065,9 +10402,9 @@
       <c r="A49" s="90"/>
       <c r="B49" s="97"/>
       <c r="C49" s="98"/>
-      <c r="D49" s="224"/>
-      <c r="E49" s="176"/>
-      <c r="F49" s="176"/>
+      <c r="D49" s="228"/>
+      <c r="E49" s="200"/>
+      <c r="F49" s="200"/>
       <c r="G49" s="95"/>
       <c r="H49" s="94"/>
       <c r="I49" s="93"/>
@@ -10078,9 +10415,9 @@
       <c r="A50" s="90"/>
       <c r="B50" s="99"/>
       <c r="C50" s="92"/>
-      <c r="D50" s="224"/>
-      <c r="E50" s="225"/>
-      <c r="F50" s="225"/>
+      <c r="D50" s="228"/>
+      <c r="E50" s="229"/>
+      <c r="F50" s="229"/>
       <c r="G50" s="95"/>
       <c r="H50" s="94"/>
       <c r="I50" s="93"/>
@@ -10092,47 +10429,6 @@
     <row r="53" spans="1:11" ht="12" customHeight="1"/>
   </sheetData>
   <mergeCells count="57">
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A11:K11"/>
-    <mergeCell ref="A12:K12"/>
-    <mergeCell ref="H9:H10"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="K9:K10"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="A27:K27"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="D42:F42"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="A36:K36"/>
-    <mergeCell ref="D37:F37"/>
     <mergeCell ref="D48:F48"/>
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="D50:F50"/>
@@ -10149,6 +10445,47 @@
     <mergeCell ref="A39:K39"/>
     <mergeCell ref="D40:F40"/>
     <mergeCell ref="D41:F41"/>
+    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="A36:K36"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="A27:K27"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A11:K11"/>
+    <mergeCell ref="A12:K12"/>
+    <mergeCell ref="H9:H10"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="K9:K10"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="I5:K5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10206,54 +10543,54 @@
       <c r="A3" s="106" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="209" t="s">
+      <c r="B3" s="171" t="s">
         <v>62</v>
       </c>
-      <c r="C3" s="209"/>
-      <c r="D3" s="210"/>
+      <c r="C3" s="171"/>
+      <c r="D3" s="172"/>
       <c r="E3" s="71"/>
       <c r="F3" s="71"/>
       <c r="G3" s="71"/>
       <c r="H3" s="71"/>
-      <c r="I3" s="193"/>
-      <c r="J3" s="193"/>
-      <c r="K3" s="193"/>
+      <c r="I3" s="173"/>
+      <c r="J3" s="173"/>
+      <c r="K3" s="173"/>
       <c r="L3" s="73"/>
     </row>
     <row r="4" spans="1:12" s="61" customFormat="1" ht="13.15" customHeight="1">
       <c r="A4" s="74" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="211" t="s">
+      <c r="B4" s="174" t="s">
         <v>356</v>
       </c>
-      <c r="C4" s="212"/>
-      <c r="D4" s="213"/>
+      <c r="C4" s="175"/>
+      <c r="D4" s="176"/>
       <c r="E4" s="71"/>
       <c r="F4" s="71"/>
       <c r="G4" s="71"/>
       <c r="H4" s="71"/>
-      <c r="I4" s="193"/>
-      <c r="J4" s="193"/>
-      <c r="K4" s="193"/>
+      <c r="I4" s="173"/>
+      <c r="J4" s="173"/>
+      <c r="K4" s="173"/>
       <c r="L4" s="73"/>
     </row>
     <row r="5" spans="1:12" s="62" customFormat="1" ht="25.5">
       <c r="A5" s="107" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="214" t="s">
+      <c r="B5" s="177" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="215"/>
-      <c r="D5" s="216"/>
+      <c r="C5" s="178"/>
+      <c r="D5" s="179"/>
       <c r="E5" s="75"/>
       <c r="F5" s="75"/>
       <c r="G5" s="75"/>
       <c r="H5" s="75"/>
-      <c r="I5" s="217"/>
-      <c r="J5" s="217"/>
-      <c r="K5" s="217"/>
+      <c r="I5" s="180"/>
+      <c r="J5" s="180"/>
+      <c r="K5" s="180"/>
       <c r="L5" s="76"/>
     </row>
     <row r="6" spans="1:12" s="61" customFormat="1" ht="15" customHeight="1">
@@ -10275,9 +10612,9 @@
       <c r="F6" s="72"/>
       <c r="G6" s="72"/>
       <c r="H6" s="72"/>
-      <c r="I6" s="193"/>
-      <c r="J6" s="193"/>
-      <c r="K6" s="193"/>
+      <c r="I6" s="173"/>
+      <c r="J6" s="173"/>
+      <c r="K6" s="173"/>
       <c r="L6" s="73"/>
     </row>
     <row r="7" spans="1:12" s="61" customFormat="1" ht="15" customHeight="1">
@@ -10299,16 +10636,16 @@
       <c r="F7" s="85"/>
       <c r="G7" s="85"/>
       <c r="H7" s="85"/>
-      <c r="I7" s="193"/>
-      <c r="J7" s="193"/>
-      <c r="K7" s="193"/>
+      <c r="I7" s="173"/>
+      <c r="J7" s="173"/>
+      <c r="K7" s="173"/>
       <c r="L7" s="73"/>
     </row>
     <row r="8" spans="1:12" s="61" customFormat="1" ht="15" customHeight="1">
-      <c r="A8" s="194"/>
-      <c r="B8" s="194"/>
-      <c r="C8" s="194"/>
-      <c r="D8" s="194"/>
+      <c r="A8" s="181"/>
+      <c r="B8" s="181"/>
+      <c r="C8" s="181"/>
+      <c r="D8" s="181"/>
       <c r="E8" s="72"/>
       <c r="F8" s="72"/>
       <c r="G8" s="72"/>
@@ -10319,64 +10656,64 @@
       <c r="L8" s="73"/>
     </row>
     <row r="9" spans="1:12" s="63" customFormat="1" ht="12" customHeight="1">
-      <c r="A9" s="197" t="s">
+      <c r="A9" s="187" t="s">
         <v>71</v>
       </c>
-      <c r="B9" s="199" t="s">
+      <c r="B9" s="189" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="197" t="s">
+      <c r="C9" s="187" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="203" t="s">
+      <c r="D9" s="193" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="204"/>
-      <c r="F9" s="204"/>
-      <c r="G9" s="205"/>
-      <c r="H9" s="201" t="s">
+      <c r="E9" s="194"/>
+      <c r="F9" s="194"/>
+      <c r="G9" s="195"/>
+      <c r="H9" s="191" t="s">
         <v>75</v>
       </c>
-      <c r="I9" s="202" t="s">
+      <c r="I9" s="192" t="s">
         <v>76</v>
       </c>
-      <c r="J9" s="202" t="s">
+      <c r="J9" s="192" t="s">
         <v>77</v>
       </c>
-      <c r="K9" s="202" t="s">
+      <c r="K9" s="192" t="s">
         <v>78</v>
       </c>
       <c r="L9" s="87"/>
     </row>
     <row r="10" spans="1:12" s="61" customFormat="1" ht="12" customHeight="1">
-      <c r="A10" s="198"/>
-      <c r="B10" s="200"/>
-      <c r="C10" s="198"/>
-      <c r="D10" s="206"/>
-      <c r="E10" s="207"/>
-      <c r="F10" s="207"/>
-      <c r="G10" s="208"/>
-      <c r="H10" s="197"/>
-      <c r="I10" s="197"/>
-      <c r="J10" s="197"/>
-      <c r="K10" s="197"/>
+      <c r="A10" s="188"/>
+      <c r="B10" s="190"/>
+      <c r="C10" s="188"/>
+      <c r="D10" s="196"/>
+      <c r="E10" s="197"/>
+      <c r="F10" s="197"/>
+      <c r="G10" s="198"/>
+      <c r="H10" s="187"/>
+      <c r="I10" s="187"/>
+      <c r="J10" s="187"/>
+      <c r="K10" s="187"/>
       <c r="L10" s="73"/>
     </row>
     <row r="11" spans="1:12" s="64" customFormat="1" ht="15">
-      <c r="A11" s="195"/>
-      <c r="B11" s="195"/>
-      <c r="C11" s="195"/>
-      <c r="D11" s="195"/>
-      <c r="E11" s="195"/>
-      <c r="F11" s="195"/>
-      <c r="G11" s="195"/>
-      <c r="H11" s="195"/>
-      <c r="I11" s="195"/>
-      <c r="J11" s="195"/>
-      <c r="K11" s="196"/>
+      <c r="A11" s="182"/>
+      <c r="B11" s="182"/>
+      <c r="C11" s="182"/>
+      <c r="D11" s="182"/>
+      <c r="E11" s="182"/>
+      <c r="F11" s="182"/>
+      <c r="G11" s="182"/>
+      <c r="H11" s="182"/>
+      <c r="I11" s="182"/>
+      <c r="J11" s="182"/>
+      <c r="K11" s="183"/>
     </row>
     <row r="12" spans="1:12" s="65" customFormat="1" ht="22.9" customHeight="1">
-      <c r="A12" s="226" t="s">
+      <c r="A12" s="227" t="s">
         <v>357</v>
       </c>
       <c r="B12" s="230"/>
@@ -10400,11 +10737,11 @@
       <c r="C13" s="109" t="s">
         <v>359</v>
       </c>
-      <c r="D13" s="175" t="s">
+      <c r="D13" s="207" t="s">
         <v>360</v>
       </c>
-      <c r="E13" s="176"/>
-      <c r="F13" s="176"/>
+      <c r="E13" s="200"/>
+      <c r="F13" s="200"/>
       <c r="G13" s="95"/>
       <c r="H13" s="94"/>
       <c r="I13" s="96"/>
@@ -10421,11 +10758,11 @@
       <c r="C14" s="111" t="s">
         <v>362</v>
       </c>
-      <c r="D14" s="175" t="s">
+      <c r="D14" s="207" t="s">
         <v>363</v>
       </c>
-      <c r="E14" s="176"/>
-      <c r="F14" s="176"/>
+      <c r="E14" s="200"/>
+      <c r="F14" s="200"/>
       <c r="G14" s="95"/>
       <c r="H14" s="94"/>
       <c r="I14" s="93"/>
@@ -10442,11 +10779,11 @@
       <c r="C15" s="109" t="s">
         <v>365</v>
       </c>
-      <c r="D15" s="175" t="s">
+      <c r="D15" s="207" t="s">
         <v>366</v>
       </c>
-      <c r="E15" s="176"/>
-      <c r="F15" s="176"/>
+      <c r="E15" s="200"/>
+      <c r="F15" s="200"/>
       <c r="G15" s="95"/>
       <c r="H15" s="94"/>
       <c r="I15" s="93"/>
@@ -10454,7 +10791,7 @@
       <c r="K15" s="92"/>
     </row>
     <row r="16" spans="1:12" ht="27" customHeight="1">
-      <c r="A16" s="226" t="s">
+      <c r="A16" s="227" t="s">
         <v>367</v>
       </c>
       <c r="B16" s="185"/>
@@ -10478,11 +10815,11 @@
       <c r="C17" s="111" t="s">
         <v>369</v>
       </c>
-      <c r="D17" s="175" t="s">
+      <c r="D17" s="207" t="s">
         <v>370</v>
       </c>
-      <c r="E17" s="176"/>
-      <c r="F17" s="176"/>
+      <c r="E17" s="200"/>
+      <c r="F17" s="200"/>
       <c r="G17" s="95"/>
       <c r="H17" s="94"/>
       <c r="I17" s="93"/>
@@ -10499,11 +10836,11 @@
       <c r="C18" s="109" t="s">
         <v>372</v>
       </c>
-      <c r="D18" s="175" t="s">
+      <c r="D18" s="207" t="s">
         <v>373</v>
       </c>
-      <c r="E18" s="176"/>
-      <c r="F18" s="176"/>
+      <c r="E18" s="200"/>
+      <c r="F18" s="200"/>
       <c r="G18" s="95"/>
       <c r="H18" s="94"/>
       <c r="I18" s="93"/>
@@ -10520,11 +10857,11 @@
       <c r="C19" s="111" t="s">
         <v>375</v>
       </c>
-      <c r="D19" s="175" t="s">
+      <c r="D19" s="207" t="s">
         <v>376</v>
       </c>
-      <c r="E19" s="176"/>
-      <c r="F19" s="176"/>
+      <c r="E19" s="200"/>
+      <c r="F19" s="200"/>
       <c r="G19" s="95"/>
       <c r="H19" s="94"/>
       <c r="I19" s="93"/>
@@ -10532,19 +10869,19 @@
       <c r="K19" s="92"/>
     </row>
     <row r="20" spans="1:11" ht="28.15" customHeight="1">
-      <c r="A20" s="227" t="s">
+      <c r="A20" s="224" t="s">
         <v>377</v>
       </c>
-      <c r="B20" s="228"/>
-      <c r="C20" s="228"/>
-      <c r="D20" s="228"/>
-      <c r="E20" s="228"/>
-      <c r="F20" s="228"/>
-      <c r="G20" s="228"/>
-      <c r="H20" s="228"/>
-      <c r="I20" s="228"/>
-      <c r="J20" s="228"/>
-      <c r="K20" s="229"/>
+      <c r="B20" s="225"/>
+      <c r="C20" s="225"/>
+      <c r="D20" s="225"/>
+      <c r="E20" s="225"/>
+      <c r="F20" s="225"/>
+      <c r="G20" s="225"/>
+      <c r="H20" s="225"/>
+      <c r="I20" s="225"/>
+      <c r="J20" s="225"/>
+      <c r="K20" s="226"/>
     </row>
     <row r="21" spans="1:11" ht="70.150000000000006" customHeight="1">
       <c r="A21" s="108" t="s">
@@ -10556,11 +10893,11 @@
       <c r="C21" s="109" t="s">
         <v>379</v>
       </c>
-      <c r="D21" s="175" t="s">
+      <c r="D21" s="207" t="s">
         <v>380</v>
       </c>
-      <c r="E21" s="176"/>
-      <c r="F21" s="176"/>
+      <c r="E21" s="200"/>
+      <c r="F21" s="200"/>
       <c r="G21" s="95"/>
       <c r="H21" s="94"/>
       <c r="I21" s="93"/>
@@ -10577,11 +10914,11 @@
       <c r="C22" s="111" t="s">
         <v>382</v>
       </c>
-      <c r="D22" s="175" t="s">
+      <c r="D22" s="207" t="s">
         <v>383</v>
       </c>
-      <c r="E22" s="176"/>
-      <c r="F22" s="176"/>
+      <c r="E22" s="200"/>
+      <c r="F22" s="200"/>
       <c r="G22" s="95"/>
       <c r="H22" s="94"/>
       <c r="I22" s="93"/>
@@ -10598,11 +10935,11 @@
       <c r="C23" s="109" t="s">
         <v>385</v>
       </c>
-      <c r="D23" s="175" t="s">
+      <c r="D23" s="207" t="s">
         <v>386</v>
       </c>
-      <c r="E23" s="176"/>
-      <c r="F23" s="176"/>
+      <c r="E23" s="200"/>
+      <c r="F23" s="200"/>
       <c r="G23" s="95"/>
       <c r="H23" s="94"/>
       <c r="I23" s="93"/>
@@ -10619,11 +10956,11 @@
       <c r="C24" s="111" t="s">
         <v>388</v>
       </c>
-      <c r="D24" s="175" t="s">
+      <c r="D24" s="207" t="s">
         <v>389</v>
       </c>
-      <c r="E24" s="176"/>
-      <c r="F24" s="176"/>
+      <c r="E24" s="200"/>
+      <c r="F24" s="200"/>
       <c r="G24" s="95"/>
       <c r="H24" s="94"/>
       <c r="I24" s="93"/>
@@ -10631,19 +10968,19 @@
       <c r="K24" s="92"/>
     </row>
     <row r="25" spans="1:11" ht="31.15" customHeight="1">
-      <c r="A25" s="227" t="s">
+      <c r="A25" s="224" t="s">
         <v>390</v>
       </c>
-      <c r="B25" s="228"/>
-      <c r="C25" s="228"/>
-      <c r="D25" s="228"/>
-      <c r="E25" s="228"/>
-      <c r="F25" s="228"/>
-      <c r="G25" s="228"/>
-      <c r="H25" s="228"/>
-      <c r="I25" s="228"/>
-      <c r="J25" s="228"/>
-      <c r="K25" s="229"/>
+      <c r="B25" s="225"/>
+      <c r="C25" s="225"/>
+      <c r="D25" s="225"/>
+      <c r="E25" s="225"/>
+      <c r="F25" s="225"/>
+      <c r="G25" s="225"/>
+      <c r="H25" s="225"/>
+      <c r="I25" s="225"/>
+      <c r="J25" s="225"/>
+      <c r="K25" s="226"/>
     </row>
     <row r="26" spans="1:11" ht="70.150000000000006" customHeight="1">
       <c r="A26" s="108" t="s">
@@ -10655,11 +10992,11 @@
       <c r="C26" s="109" t="s">
         <v>392</v>
       </c>
-      <c r="D26" s="175" t="s">
+      <c r="D26" s="207" t="s">
         <v>393</v>
       </c>
-      <c r="E26" s="176"/>
-      <c r="F26" s="176"/>
+      <c r="E26" s="200"/>
+      <c r="F26" s="200"/>
       <c r="G26" s="95"/>
       <c r="H26" s="94"/>
       <c r="I26" s="93"/>
@@ -10676,11 +11013,11 @@
       <c r="C27" s="111" t="s">
         <v>395</v>
       </c>
-      <c r="D27" s="175" t="s">
+      <c r="D27" s="207" t="s">
         <v>396</v>
       </c>
-      <c r="E27" s="176"/>
-      <c r="F27" s="176"/>
+      <c r="E27" s="200"/>
+      <c r="F27" s="200"/>
       <c r="G27" s="95"/>
       <c r="H27" s="94"/>
       <c r="I27" s="93"/>
@@ -10697,11 +11034,11 @@
       <c r="C28" s="109" t="s">
         <v>398</v>
       </c>
-      <c r="D28" s="175" t="s">
+      <c r="D28" s="207" t="s">
         <v>399</v>
       </c>
-      <c r="E28" s="176"/>
-      <c r="F28" s="176"/>
+      <c r="E28" s="200"/>
+      <c r="F28" s="200"/>
       <c r="G28" s="95"/>
       <c r="H28" s="94"/>
       <c r="I28" s="93"/>
@@ -10718,11 +11055,11 @@
       <c r="C29" s="111" t="s">
         <v>401</v>
       </c>
-      <c r="D29" s="175" t="s">
+      <c r="D29" s="207" t="s">
         <v>402</v>
       </c>
-      <c r="E29" s="176"/>
-      <c r="F29" s="176"/>
+      <c r="E29" s="200"/>
+      <c r="F29" s="200"/>
       <c r="G29" s="95"/>
       <c r="H29" s="94"/>
       <c r="I29" s="93"/>
@@ -10733,9 +11070,9 @@
       <c r="A30" s="108"/>
       <c r="B30" s="109"/>
       <c r="C30" s="109"/>
-      <c r="D30" s="175"/>
-      <c r="E30" s="176"/>
-      <c r="F30" s="176"/>
+      <c r="D30" s="207"/>
+      <c r="E30" s="200"/>
+      <c r="F30" s="200"/>
       <c r="G30" s="95"/>
       <c r="H30" s="94"/>
       <c r="I30" s="93"/>
@@ -10746,9 +11083,9 @@
       <c r="A31" s="110"/>
       <c r="B31" s="120"/>
       <c r="C31" s="111"/>
-      <c r="D31" s="175"/>
-      <c r="E31" s="176"/>
-      <c r="F31" s="176"/>
+      <c r="D31" s="207"/>
+      <c r="E31" s="200"/>
+      <c r="F31" s="200"/>
       <c r="G31" s="95"/>
       <c r="H31" s="94"/>
       <c r="I31" s="93"/>
@@ -10759,9 +11096,9 @@
       <c r="A32" s="121"/>
       <c r="B32" s="122"/>
       <c r="C32" s="123"/>
-      <c r="D32" s="224"/>
-      <c r="E32" s="225"/>
-      <c r="F32" s="225"/>
+      <c r="D32" s="228"/>
+      <c r="E32" s="229"/>
+      <c r="F32" s="229"/>
       <c r="G32" s="95"/>
       <c r="H32" s="94"/>
       <c r="I32" s="93"/>
@@ -10772,9 +11109,9 @@
       <c r="A33" s="90"/>
       <c r="B33" s="99"/>
       <c r="C33" s="92"/>
-      <c r="D33" s="224"/>
-      <c r="E33" s="225"/>
-      <c r="F33" s="225"/>
+      <c r="D33" s="228"/>
+      <c r="E33" s="229"/>
+      <c r="F33" s="229"/>
       <c r="G33" s="95"/>
       <c r="H33" s="94"/>
       <c r="I33" s="93"/>
@@ -10785,9 +11122,9 @@
       <c r="A34" s="90"/>
       <c r="B34" s="99"/>
       <c r="C34" s="92"/>
-      <c r="D34" s="224"/>
-      <c r="E34" s="225"/>
-      <c r="F34" s="225"/>
+      <c r="D34" s="228"/>
+      <c r="E34" s="229"/>
+      <c r="F34" s="229"/>
       <c r="G34" s="95"/>
       <c r="H34" s="94"/>
       <c r="I34" s="93"/>
@@ -10798,9 +11135,9 @@
       <c r="A35" s="90"/>
       <c r="B35" s="99"/>
       <c r="C35" s="92"/>
-      <c r="D35" s="224"/>
-      <c r="E35" s="225"/>
-      <c r="F35" s="225"/>
+      <c r="D35" s="228"/>
+      <c r="E35" s="229"/>
+      <c r="F35" s="229"/>
       <c r="G35" s="95"/>
       <c r="H35" s="94"/>
       <c r="I35" s="93"/>
@@ -10811,9 +11148,9 @@
       <c r="A36" s="90"/>
       <c r="B36" s="99"/>
       <c r="C36" s="92"/>
-      <c r="D36" s="224"/>
-      <c r="E36" s="225"/>
-      <c r="F36" s="225"/>
+      <c r="D36" s="228"/>
+      <c r="E36" s="229"/>
+      <c r="F36" s="229"/>
       <c r="G36" s="95"/>
       <c r="H36" s="94"/>
       <c r="I36" s="93"/>
@@ -10824,9 +11161,9 @@
       <c r="A37" s="90"/>
       <c r="B37" s="99"/>
       <c r="C37" s="92"/>
-      <c r="D37" s="224"/>
-      <c r="E37" s="225"/>
-      <c r="F37" s="225"/>
+      <c r="D37" s="228"/>
+      <c r="E37" s="229"/>
+      <c r="F37" s="229"/>
       <c r="G37" s="95"/>
       <c r="H37" s="94"/>
       <c r="I37" s="93"/>
@@ -10837,9 +11174,9 @@
       <c r="A38" s="90"/>
       <c r="B38" s="99"/>
       <c r="C38" s="92"/>
-      <c r="D38" s="224"/>
-      <c r="E38" s="225"/>
-      <c r="F38" s="225"/>
+      <c r="D38" s="228"/>
+      <c r="E38" s="229"/>
+      <c r="F38" s="229"/>
       <c r="G38" s="95"/>
       <c r="H38" s="94"/>
       <c r="I38" s="93"/>
@@ -10850,9 +11187,9 @@
       <c r="A39" s="90"/>
       <c r="B39" s="99"/>
       <c r="C39" s="92"/>
-      <c r="D39" s="224"/>
-      <c r="E39" s="225"/>
-      <c r="F39" s="225"/>
+      <c r="D39" s="228"/>
+      <c r="E39" s="229"/>
+      <c r="F39" s="229"/>
       <c r="G39" s="95"/>
       <c r="H39" s="94"/>
       <c r="I39" s="93"/>
@@ -10863,9 +11200,9 @@
       <c r="A40" s="90"/>
       <c r="B40" s="99"/>
       <c r="C40" s="92"/>
-      <c r="D40" s="224"/>
-      <c r="E40" s="225"/>
-      <c r="F40" s="225"/>
+      <c r="D40" s="228"/>
+      <c r="E40" s="229"/>
+      <c r="F40" s="229"/>
       <c r="G40" s="95"/>
       <c r="H40" s="94"/>
       <c r="I40" s="93"/>
@@ -10876,9 +11213,9 @@
       <c r="A41" s="90"/>
       <c r="B41" s="99"/>
       <c r="C41" s="92"/>
-      <c r="D41" s="224"/>
-      <c r="E41" s="225"/>
-      <c r="F41" s="225"/>
+      <c r="D41" s="228"/>
+      <c r="E41" s="229"/>
+      <c r="F41" s="229"/>
       <c r="G41" s="95"/>
       <c r="H41" s="94"/>
       <c r="I41" s="93"/>
@@ -10889,9 +11226,9 @@
       <c r="A42" s="90"/>
       <c r="B42" s="99"/>
       <c r="C42" s="92"/>
-      <c r="D42" s="224"/>
-      <c r="E42" s="225"/>
-      <c r="F42" s="225"/>
+      <c r="D42" s="228"/>
+      <c r="E42" s="229"/>
+      <c r="F42" s="229"/>
       <c r="G42" s="95"/>
       <c r="H42" s="94"/>
       <c r="I42" s="93"/>
@@ -10902,9 +11239,9 @@
       <c r="A43" s="90"/>
       <c r="B43" s="99"/>
       <c r="C43" s="92"/>
-      <c r="D43" s="224"/>
-      <c r="E43" s="225"/>
-      <c r="F43" s="225"/>
+      <c r="D43" s="228"/>
+      <c r="E43" s="229"/>
+      <c r="F43" s="229"/>
       <c r="G43" s="95"/>
       <c r="H43" s="94"/>
       <c r="I43" s="93"/>
@@ -10915,9 +11252,9 @@
       <c r="A44" s="90"/>
       <c r="B44" s="99"/>
       <c r="C44" s="92"/>
-      <c r="D44" s="224"/>
-      <c r="E44" s="225"/>
-      <c r="F44" s="225"/>
+      <c r="D44" s="228"/>
+      <c r="E44" s="229"/>
+      <c r="F44" s="229"/>
       <c r="G44" s="95"/>
       <c r="H44" s="94"/>
       <c r="I44" s="93"/>
@@ -10928,9 +11265,9 @@
       <c r="A45" s="90"/>
       <c r="B45" s="99"/>
       <c r="C45" s="92"/>
-      <c r="D45" s="224"/>
-      <c r="E45" s="225"/>
-      <c r="F45" s="225"/>
+      <c r="D45" s="228"/>
+      <c r="E45" s="229"/>
+      <c r="F45" s="229"/>
       <c r="G45" s="95"/>
       <c r="H45" s="94"/>
       <c r="I45" s="93"/>
@@ -10941,9 +11278,9 @@
       <c r="A46" s="90"/>
       <c r="B46" s="99"/>
       <c r="C46" s="92"/>
-      <c r="D46" s="224"/>
-      <c r="E46" s="225"/>
-      <c r="F46" s="225"/>
+      <c r="D46" s="228"/>
+      <c r="E46" s="229"/>
+      <c r="F46" s="229"/>
       <c r="G46" s="95"/>
       <c r="H46" s="94"/>
       <c r="I46" s="93"/>
@@ -10954,9 +11291,9 @@
       <c r="A47" s="90"/>
       <c r="B47" s="99"/>
       <c r="C47" s="92"/>
-      <c r="D47" s="224"/>
-      <c r="E47" s="225"/>
-      <c r="F47" s="225"/>
+      <c r="D47" s="228"/>
+      <c r="E47" s="229"/>
+      <c r="F47" s="229"/>
       <c r="G47" s="95"/>
       <c r="H47" s="94"/>
       <c r="I47" s="93"/>
@@ -10967,9 +11304,9 @@
       <c r="A48" s="90"/>
       <c r="B48" s="99"/>
       <c r="C48" s="92"/>
-      <c r="D48" s="224"/>
-      <c r="E48" s="225"/>
-      <c r="F48" s="225"/>
+      <c r="D48" s="228"/>
+      <c r="E48" s="229"/>
+      <c r="F48" s="229"/>
       <c r="G48" s="95"/>
       <c r="H48" s="94"/>
       <c r="I48" s="93"/>
@@ -10982,45 +11319,6 @@
     <row r="52" ht="12" customHeight="1"/>
   </sheetData>
   <mergeCells count="55">
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A11:K11"/>
-    <mergeCell ref="A12:K12"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="K9:K10"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="A16:K16"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="A20:K20"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="A25:K25"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="D36:F36"/>
-    <mergeCell ref="D37:F37"/>
     <mergeCell ref="D48:F48"/>
     <mergeCell ref="A9:A10"/>
     <mergeCell ref="B9:B10"/>
@@ -11037,6 +11335,45 @@
     <mergeCell ref="D40:F40"/>
     <mergeCell ref="D41:F41"/>
     <mergeCell ref="D42:F42"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="A25:K25"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="A20:K20"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="A16:K16"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A11:K11"/>
+    <mergeCell ref="A12:K12"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="K9:K10"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="I5:K5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -11089,52 +11426,52 @@
       <c r="A3" s="70" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="209" t="s">
+      <c r="B3" s="171" t="s">
         <v>62</v>
       </c>
-      <c r="C3" s="209"/>
-      <c r="D3" s="210"/>
+      <c r="C3" s="171"/>
+      <c r="D3" s="172"/>
       <c r="E3" s="71"/>
       <c r="F3" s="71"/>
       <c r="G3" s="71"/>
       <c r="H3" s="71"/>
-      <c r="I3" s="193"/>
-      <c r="J3" s="193"/>
-      <c r="K3" s="193"/>
+      <c r="I3" s="173"/>
+      <c r="J3" s="173"/>
+      <c r="K3" s="173"/>
     </row>
     <row r="4" spans="1:11" ht="13.5" customHeight="1">
       <c r="A4" s="74" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="211" t="s">
+      <c r="B4" s="174" t="s">
         <v>404</v>
       </c>
-      <c r="C4" s="212"/>
-      <c r="D4" s="213"/>
+      <c r="C4" s="175"/>
+      <c r="D4" s="176"/>
       <c r="E4" s="71"/>
       <c r="F4" s="71"/>
       <c r="G4" s="71"/>
       <c r="H4" s="71"/>
-      <c r="I4" s="193"/>
-      <c r="J4" s="193"/>
-      <c r="K4" s="193"/>
+      <c r="I4" s="173"/>
+      <c r="J4" s="173"/>
+      <c r="K4" s="173"/>
     </row>
     <row r="5" spans="1:11" ht="12.75" customHeight="1">
       <c r="A5" s="74" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="214" t="s">
+      <c r="B5" s="177" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="215"/>
-      <c r="D5" s="216"/>
+      <c r="C5" s="178"/>
+      <c r="D5" s="179"/>
       <c r="E5" s="75"/>
       <c r="F5" s="75"/>
       <c r="G5" s="75"/>
       <c r="H5" s="75"/>
-      <c r="I5" s="217"/>
-      <c r="J5" s="217"/>
-      <c r="K5" s="217"/>
+      <c r="I5" s="180"/>
+      <c r="J5" s="180"/>
+      <c r="K5" s="180"/>
     </row>
     <row r="6" spans="1:11" ht="14.25">
       <c r="A6" s="77" t="s">
@@ -11155,9 +11492,9 @@
       <c r="F6" s="72"/>
       <c r="G6" s="72"/>
       <c r="H6" s="72"/>
-      <c r="I6" s="193"/>
-      <c r="J6" s="193"/>
-      <c r="K6" s="193"/>
+      <c r="I6" s="173"/>
+      <c r="J6" s="173"/>
+      <c r="K6" s="173"/>
     </row>
     <row r="7" spans="1:11" ht="14.25">
       <c r="A7" s="81" t="s">
@@ -11178,15 +11515,15 @@
       <c r="F7" s="85"/>
       <c r="G7" s="85"/>
       <c r="H7" s="85"/>
-      <c r="I7" s="193"/>
-      <c r="J7" s="193"/>
-      <c r="K7" s="193"/>
+      <c r="I7" s="173"/>
+      <c r="J7" s="173"/>
+      <c r="K7" s="173"/>
     </row>
     <row r="8" spans="1:11" ht="14.25">
-      <c r="A8" s="194"/>
-      <c r="B8" s="194"/>
-      <c r="C8" s="194"/>
-      <c r="D8" s="194"/>
+      <c r="A8" s="181"/>
+      <c r="B8" s="181"/>
+      <c r="C8" s="181"/>
+      <c r="D8" s="181"/>
       <c r="E8" s="72"/>
       <c r="F8" s="72"/>
       <c r="G8" s="72"/>
@@ -11196,59 +11533,59 @@
       <c r="K8" s="86"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="197" t="s">
+      <c r="A9" s="187" t="s">
         <v>71</v>
       </c>
-      <c r="B9" s="199" t="s">
+      <c r="B9" s="189" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="197" t="s">
+      <c r="C9" s="187" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="203" t="s">
+      <c r="D9" s="193" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="204"/>
-      <c r="F9" s="204"/>
-      <c r="G9" s="205"/>
-      <c r="H9" s="201" t="s">
+      <c r="E9" s="194"/>
+      <c r="F9" s="194"/>
+      <c r="G9" s="195"/>
+      <c r="H9" s="191" t="s">
         <v>75</v>
       </c>
-      <c r="I9" s="202" t="s">
+      <c r="I9" s="192" t="s">
         <v>76</v>
       </c>
-      <c r="J9" s="202" t="s">
+      <c r="J9" s="192" t="s">
         <v>77</v>
       </c>
-      <c r="K9" s="202" t="s">
+      <c r="K9" s="192" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="198"/>
-      <c r="B10" s="200"/>
-      <c r="C10" s="198"/>
-      <c r="D10" s="206"/>
-      <c r="E10" s="207"/>
-      <c r="F10" s="207"/>
-      <c r="G10" s="208"/>
-      <c r="H10" s="197"/>
-      <c r="I10" s="197"/>
-      <c r="J10" s="197"/>
-      <c r="K10" s="197"/>
+      <c r="A10" s="188"/>
+      <c r="B10" s="190"/>
+      <c r="C10" s="188"/>
+      <c r="D10" s="196"/>
+      <c r="E10" s="197"/>
+      <c r="F10" s="197"/>
+      <c r="G10" s="198"/>
+      <c r="H10" s="187"/>
+      <c r="I10" s="187"/>
+      <c r="J10" s="187"/>
+      <c r="K10" s="187"/>
     </row>
     <row r="11" spans="1:11" ht="15">
-      <c r="A11" s="195"/>
-      <c r="B11" s="195"/>
-      <c r="C11" s="195"/>
-      <c r="D11" s="195"/>
-      <c r="E11" s="195"/>
-      <c r="F11" s="195"/>
-      <c r="G11" s="195"/>
-      <c r="H11" s="195"/>
-      <c r="I11" s="195"/>
-      <c r="J11" s="195"/>
-      <c r="K11" s="196"/>
+      <c r="A11" s="182"/>
+      <c r="B11" s="182"/>
+      <c r="C11" s="182"/>
+      <c r="D11" s="182"/>
+      <c r="E11" s="182"/>
+      <c r="F11" s="182"/>
+      <c r="G11" s="182"/>
+      <c r="H11" s="182"/>
+      <c r="I11" s="182"/>
+      <c r="J11" s="182"/>
+      <c r="K11" s="183"/>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="184" t="s">
@@ -11481,12 +11818,16 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="D17:F17"/>
     <mergeCell ref="I6:K6"/>
     <mergeCell ref="I7:K7"/>
     <mergeCell ref="A8:D8"/>
@@ -11500,16 +11841,12 @@
     <mergeCell ref="J9:J10"/>
     <mergeCell ref="K9:K10"/>
     <mergeCell ref="D9:G10"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="I5:K5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -11567,54 +11904,54 @@
       <c r="A3" s="106" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="209" t="s">
+      <c r="B3" s="171" t="s">
         <v>62</v>
       </c>
-      <c r="C3" s="209"/>
-      <c r="D3" s="210"/>
+      <c r="C3" s="171"/>
+      <c r="D3" s="172"/>
       <c r="E3" s="71"/>
       <c r="F3" s="71"/>
       <c r="G3" s="71"/>
       <c r="H3" s="71"/>
-      <c r="I3" s="193"/>
-      <c r="J3" s="193"/>
-      <c r="K3" s="193"/>
+      <c r="I3" s="173"/>
+      <c r="J3" s="173"/>
+      <c r="K3" s="173"/>
       <c r="L3" s="73"/>
     </row>
     <row r="4" spans="1:12" s="61" customFormat="1" ht="13.15" customHeight="1">
       <c r="A4" s="74" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="211" t="s">
+      <c r="B4" s="174" t="s">
         <v>431</v>
       </c>
-      <c r="C4" s="212"/>
-      <c r="D4" s="213"/>
+      <c r="C4" s="175"/>
+      <c r="D4" s="176"/>
       <c r="E4" s="71"/>
       <c r="F4" s="71"/>
       <c r="G4" s="71"/>
       <c r="H4" s="71"/>
-      <c r="I4" s="193"/>
-      <c r="J4" s="193"/>
-      <c r="K4" s="193"/>
+      <c r="I4" s="173"/>
+      <c r="J4" s="173"/>
+      <c r="K4" s="173"/>
       <c r="L4" s="73"/>
     </row>
     <row r="5" spans="1:12" s="62" customFormat="1" ht="25.5">
       <c r="A5" s="107" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="214" t="s">
+      <c r="B5" s="177" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="215"/>
-      <c r="D5" s="216"/>
+      <c r="C5" s="178"/>
+      <c r="D5" s="179"/>
       <c r="E5" s="75"/>
       <c r="F5" s="75"/>
       <c r="G5" s="75"/>
       <c r="H5" s="75"/>
-      <c r="I5" s="217"/>
-      <c r="J5" s="217"/>
-      <c r="K5" s="217"/>
+      <c r="I5" s="180"/>
+      <c r="J5" s="180"/>
+      <c r="K5" s="180"/>
       <c r="L5" s="76"/>
     </row>
     <row r="6" spans="1:12" s="61" customFormat="1" ht="15" customHeight="1">
@@ -11636,9 +11973,9 @@
       <c r="F6" s="72"/>
       <c r="G6" s="72"/>
       <c r="H6" s="72"/>
-      <c r="I6" s="193"/>
-      <c r="J6" s="193"/>
-      <c r="K6" s="193"/>
+      <c r="I6" s="173"/>
+      <c r="J6" s="173"/>
+      <c r="K6" s="173"/>
       <c r="L6" s="73"/>
     </row>
     <row r="7" spans="1:12" s="61" customFormat="1" ht="15" customHeight="1">
@@ -11660,16 +11997,16 @@
       <c r="F7" s="85"/>
       <c r="G7" s="85"/>
       <c r="H7" s="85"/>
-      <c r="I7" s="193"/>
-      <c r="J7" s="193"/>
-      <c r="K7" s="193"/>
+      <c r="I7" s="173"/>
+      <c r="J7" s="173"/>
+      <c r="K7" s="173"/>
       <c r="L7" s="73"/>
     </row>
     <row r="8" spans="1:12" s="61" customFormat="1" ht="15" customHeight="1">
-      <c r="A8" s="194"/>
-      <c r="B8" s="194"/>
-      <c r="C8" s="194"/>
-      <c r="D8" s="194"/>
+      <c r="A8" s="181"/>
+      <c r="B8" s="181"/>
+      <c r="C8" s="181"/>
+      <c r="D8" s="181"/>
       <c r="F8" s="72"/>
       <c r="G8" s="72"/>
       <c r="H8" s="72"/>
@@ -11679,61 +12016,61 @@
       <c r="L8" s="73"/>
     </row>
     <row r="9" spans="1:12" s="63" customFormat="1" ht="12" customHeight="1">
-      <c r="A9" s="197" t="s">
+      <c r="A9" s="187" t="s">
         <v>71</v>
       </c>
-      <c r="B9" s="199" t="s">
+      <c r="B9" s="189" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="197" t="s">
+      <c r="C9" s="187" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="203" t="s">
+      <c r="D9" s="193" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="204"/>
-      <c r="F9" s="204"/>
-      <c r="G9" s="205"/>
-      <c r="H9" s="201" t="s">
+      <c r="E9" s="194"/>
+      <c r="F9" s="194"/>
+      <c r="G9" s="195"/>
+      <c r="H9" s="191" t="s">
         <v>75</v>
       </c>
-      <c r="I9" s="202" t="s">
+      <c r="I9" s="192" t="s">
         <v>76</v>
       </c>
-      <c r="J9" s="202" t="s">
+      <c r="J9" s="192" t="s">
         <v>77</v>
       </c>
-      <c r="K9" s="202" t="s">
+      <c r="K9" s="192" t="s">
         <v>78</v>
       </c>
       <c r="L9" s="87"/>
     </row>
     <row r="10" spans="1:12" s="61" customFormat="1" ht="12" customHeight="1">
-      <c r="A10" s="198"/>
-      <c r="B10" s="200"/>
-      <c r="C10" s="198"/>
-      <c r="D10" s="206"/>
-      <c r="E10" s="207"/>
-      <c r="F10" s="207"/>
-      <c r="G10" s="208"/>
-      <c r="H10" s="197"/>
-      <c r="I10" s="197"/>
-      <c r="J10" s="197"/>
-      <c r="K10" s="197"/>
+      <c r="A10" s="188"/>
+      <c r="B10" s="190"/>
+      <c r="C10" s="188"/>
+      <c r="D10" s="196"/>
+      <c r="E10" s="197"/>
+      <c r="F10" s="197"/>
+      <c r="G10" s="198"/>
+      <c r="H10" s="187"/>
+      <c r="I10" s="187"/>
+      <c r="J10" s="187"/>
+      <c r="K10" s="187"/>
       <c r="L10" s="73"/>
     </row>
     <row r="11" spans="1:12" s="64" customFormat="1" ht="15">
-      <c r="A11" s="195"/>
-      <c r="B11" s="195"/>
-      <c r="C11" s="195"/>
-      <c r="D11" s="195"/>
-      <c r="E11" s="195"/>
-      <c r="F11" s="195"/>
-      <c r="G11" s="195"/>
-      <c r="H11" s="195"/>
-      <c r="I11" s="195"/>
-      <c r="J11" s="195"/>
-      <c r="K11" s="196"/>
+      <c r="A11" s="182"/>
+      <c r="B11" s="182"/>
+      <c r="C11" s="182"/>
+      <c r="D11" s="182"/>
+      <c r="E11" s="182"/>
+      <c r="F11" s="182"/>
+      <c r="G11" s="182"/>
+      <c r="H11" s="182"/>
+      <c r="I11" s="182"/>
+      <c r="J11" s="182"/>
+      <c r="K11" s="183"/>
     </row>
     <row r="12" spans="1:12" s="65" customFormat="1" ht="29.45" customHeight="1">
       <c r="A12" s="237" t="s">
@@ -11760,11 +12097,11 @@
       <c r="C13" s="109" t="s">
         <v>434</v>
       </c>
-      <c r="D13" s="175" t="s">
+      <c r="D13" s="207" t="s">
         <v>435</v>
       </c>
-      <c r="E13" s="176"/>
-      <c r="F13" s="176"/>
+      <c r="E13" s="200"/>
+      <c r="F13" s="200"/>
       <c r="G13" s="95"/>
       <c r="H13" s="94"/>
       <c r="I13" s="96"/>
@@ -11781,11 +12118,11 @@
       <c r="C14" s="111" t="s">
         <v>437</v>
       </c>
-      <c r="D14" s="175" t="s">
+      <c r="D14" s="207" t="s">
         <v>438</v>
       </c>
-      <c r="E14" s="176"/>
-      <c r="F14" s="176"/>
+      <c r="E14" s="200"/>
+      <c r="F14" s="200"/>
       <c r="G14" s="95"/>
       <c r="H14" s="94"/>
       <c r="I14" s="93"/>
@@ -11802,11 +12139,11 @@
       <c r="C15" s="109" t="s">
         <v>440</v>
       </c>
-      <c r="D15" s="175" t="s">
+      <c r="D15" s="207" t="s">
         <v>441</v>
       </c>
-      <c r="E15" s="176"/>
-      <c r="F15" s="176"/>
+      <c r="E15" s="200"/>
+      <c r="F15" s="200"/>
       <c r="G15" s="95"/>
       <c r="H15" s="94"/>
       <c r="I15" s="93"/>
@@ -11838,11 +12175,11 @@
       <c r="C17" s="111" t="s">
         <v>444</v>
       </c>
-      <c r="D17" s="175" t="s">
+      <c r="D17" s="207" t="s">
         <v>445</v>
       </c>
-      <c r="E17" s="176"/>
-      <c r="F17" s="176"/>
+      <c r="E17" s="200"/>
+      <c r="F17" s="200"/>
       <c r="G17" s="95"/>
       <c r="H17" s="94"/>
       <c r="I17" s="93"/>
@@ -11859,11 +12196,11 @@
       <c r="C18" s="109" t="s">
         <v>447</v>
       </c>
-      <c r="D18" s="175" t="s">
+      <c r="D18" s="207" t="s">
         <v>448</v>
       </c>
-      <c r="E18" s="176"/>
-      <c r="F18" s="176"/>
+      <c r="E18" s="200"/>
+      <c r="F18" s="200"/>
       <c r="G18" s="95"/>
       <c r="H18" s="94"/>
       <c r="I18" s="93"/>
@@ -11880,11 +12217,11 @@
       <c r="C19" s="111" t="s">
         <v>450</v>
       </c>
-      <c r="D19" s="175" t="s">
+      <c r="D19" s="207" t="s">
         <v>451</v>
       </c>
-      <c r="E19" s="176"/>
-      <c r="F19" s="176"/>
+      <c r="E19" s="200"/>
+      <c r="F19" s="200"/>
       <c r="G19" s="95"/>
       <c r="H19" s="94"/>
       <c r="I19" s="93"/>
@@ -11901,11 +12238,11 @@
       <c r="C20" s="109" t="s">
         <v>453</v>
       </c>
-      <c r="D20" s="175" t="s">
+      <c r="D20" s="207" t="s">
         <v>454</v>
       </c>
-      <c r="E20" s="176"/>
-      <c r="F20" s="176"/>
+      <c r="E20" s="200"/>
+      <c r="F20" s="200"/>
       <c r="G20" s="95"/>
       <c r="H20" s="94"/>
       <c r="I20" s="93"/>
@@ -11922,11 +12259,11 @@
       <c r="C21" s="111" t="s">
         <v>456</v>
       </c>
-      <c r="D21" s="175" t="s">
+      <c r="D21" s="207" t="s">
         <v>457</v>
       </c>
-      <c r="E21" s="176"/>
-      <c r="F21" s="176"/>
+      <c r="E21" s="200"/>
+      <c r="F21" s="200"/>
       <c r="G21" s="95"/>
       <c r="H21" s="94"/>
       <c r="I21" s="93"/>
@@ -11958,11 +12295,11 @@
       <c r="C23" s="109" t="s">
         <v>460</v>
       </c>
-      <c r="D23" s="175" t="s">
+      <c r="D23" s="207" t="s">
         <v>461</v>
       </c>
-      <c r="E23" s="176"/>
-      <c r="F23" s="176"/>
+      <c r="E23" s="200"/>
+      <c r="F23" s="200"/>
       <c r="G23" s="95"/>
       <c r="H23" s="94"/>
       <c r="I23" s="93"/>
@@ -11979,11 +12316,11 @@
       <c r="C24" s="111" t="s">
         <v>463</v>
       </c>
-      <c r="D24" s="175" t="s">
+      <c r="D24" s="207" t="s">
         <v>464</v>
       </c>
-      <c r="E24" s="176"/>
-      <c r="F24" s="176"/>
+      <c r="E24" s="200"/>
+      <c r="F24" s="200"/>
       <c r="G24" s="95"/>
       <c r="H24" s="94"/>
       <c r="I24" s="93"/>
@@ -12000,11 +12337,11 @@
       <c r="C25" s="109" t="s">
         <v>466</v>
       </c>
-      <c r="D25" s="175" t="s">
+      <c r="D25" s="207" t="s">
         <v>467</v>
       </c>
-      <c r="E25" s="176"/>
-      <c r="F25" s="176"/>
+      <c r="E25" s="200"/>
+      <c r="F25" s="200"/>
       <c r="G25" s="95"/>
       <c r="H25" s="94"/>
       <c r="I25" s="93"/>
@@ -12021,11 +12358,11 @@
       <c r="C26" s="111" t="s">
         <v>469</v>
       </c>
-      <c r="D26" s="175" t="s">
+      <c r="D26" s="207" t="s">
         <v>470</v>
       </c>
-      <c r="E26" s="176"/>
-      <c r="F26" s="176"/>
+      <c r="E26" s="200"/>
+      <c r="F26" s="200"/>
       <c r="G26" s="95"/>
       <c r="H26" s="94"/>
       <c r="I26" s="93"/>
@@ -12042,11 +12379,11 @@
       <c r="C27" s="109" t="s">
         <v>472</v>
       </c>
-      <c r="D27" s="175" t="s">
+      <c r="D27" s="207" t="s">
         <v>473</v>
       </c>
-      <c r="E27" s="176"/>
-      <c r="F27" s="176"/>
+      <c r="E27" s="200"/>
+      <c r="F27" s="200"/>
       <c r="G27" s="95"/>
       <c r="H27" s="94"/>
       <c r="I27" s="93"/>
@@ -12063,11 +12400,11 @@
       <c r="C28" s="111" t="s">
         <v>475</v>
       </c>
-      <c r="D28" s="175" t="s">
+      <c r="D28" s="207" t="s">
         <v>476</v>
       </c>
-      <c r="E28" s="176"/>
-      <c r="F28" s="176"/>
+      <c r="E28" s="200"/>
+      <c r="F28" s="200"/>
       <c r="G28" s="95"/>
       <c r="H28" s="94"/>
       <c r="I28" s="93"/>
@@ -12084,11 +12421,11 @@
       <c r="C29" s="109" t="s">
         <v>478</v>
       </c>
-      <c r="D29" s="175" t="s">
+      <c r="D29" s="207" t="s">
         <v>479</v>
       </c>
-      <c r="E29" s="176"/>
-      <c r="F29" s="176"/>
+      <c r="E29" s="200"/>
+      <c r="F29" s="200"/>
       <c r="G29" s="95"/>
       <c r="H29" s="94"/>
       <c r="I29" s="93"/>
@@ -12120,11 +12457,11 @@
       <c r="C31" s="111" t="s">
         <v>482</v>
       </c>
-      <c r="D31" s="175" t="s">
+      <c r="D31" s="207" t="s">
         <v>483</v>
       </c>
-      <c r="E31" s="176"/>
-      <c r="F31" s="176"/>
+      <c r="E31" s="200"/>
+      <c r="F31" s="200"/>
       <c r="G31" s="95"/>
       <c r="H31" s="94"/>
       <c r="I31" s="93"/>
@@ -12141,11 +12478,11 @@
       <c r="C32" s="109" t="s">
         <v>485</v>
       </c>
-      <c r="D32" s="175" t="s">
+      <c r="D32" s="207" t="s">
         <v>486</v>
       </c>
-      <c r="E32" s="176"/>
-      <c r="F32" s="176"/>
+      <c r="E32" s="200"/>
+      <c r="F32" s="200"/>
       <c r="G32" s="95"/>
       <c r="H32" s="94"/>
       <c r="I32" s="93"/>
@@ -12156,9 +12493,9 @@
       <c r="A33" s="90"/>
       <c r="B33" s="99"/>
       <c r="C33" s="92"/>
-      <c r="D33" s="224"/>
-      <c r="E33" s="225"/>
-      <c r="F33" s="225"/>
+      <c r="D33" s="228"/>
+      <c r="E33" s="229"/>
+      <c r="F33" s="229"/>
       <c r="G33" s="95"/>
       <c r="H33" s="94"/>
       <c r="I33" s="93"/>
@@ -12169,9 +12506,9 @@
       <c r="A34" s="90"/>
       <c r="B34" s="99"/>
       <c r="C34" s="92"/>
-      <c r="D34" s="224"/>
-      <c r="E34" s="225"/>
-      <c r="F34" s="225"/>
+      <c r="D34" s="228"/>
+      <c r="E34" s="229"/>
+      <c r="F34" s="229"/>
       <c r="G34" s="95"/>
       <c r="H34" s="94"/>
       <c r="I34" s="93"/>
@@ -12182,9 +12519,9 @@
       <c r="A35" s="90"/>
       <c r="B35" s="99"/>
       <c r="C35" s="92"/>
-      <c r="D35" s="224"/>
-      <c r="E35" s="225"/>
-      <c r="F35" s="225"/>
+      <c r="D35" s="228"/>
+      <c r="E35" s="229"/>
+      <c r="F35" s="229"/>
       <c r="G35" s="95"/>
       <c r="H35" s="94"/>
       <c r="I35" s="93"/>
@@ -12195,9 +12532,9 @@
       <c r="A36" s="90"/>
       <c r="B36" s="99"/>
       <c r="C36" s="92"/>
-      <c r="D36" s="224"/>
-      <c r="E36" s="225"/>
-      <c r="F36" s="225"/>
+      <c r="D36" s="228"/>
+      <c r="E36" s="229"/>
+      <c r="F36" s="229"/>
       <c r="G36" s="95"/>
       <c r="H36" s="94"/>
       <c r="I36" s="93"/>
@@ -12208,9 +12545,9 @@
       <c r="A37" s="90"/>
       <c r="B37" s="99"/>
       <c r="C37" s="92"/>
-      <c r="D37" s="224"/>
-      <c r="E37" s="225"/>
-      <c r="F37" s="225"/>
+      <c r="D37" s="228"/>
+      <c r="E37" s="229"/>
+      <c r="F37" s="229"/>
       <c r="G37" s="95"/>
       <c r="H37" s="94"/>
       <c r="I37" s="93"/>
@@ -12221,9 +12558,9 @@
       <c r="A38" s="90"/>
       <c r="B38" s="99"/>
       <c r="C38" s="92"/>
-      <c r="D38" s="224"/>
-      <c r="E38" s="225"/>
-      <c r="F38" s="225"/>
+      <c r="D38" s="228"/>
+      <c r="E38" s="229"/>
+      <c r="F38" s="229"/>
       <c r="G38" s="95"/>
       <c r="H38" s="94"/>
       <c r="I38" s="93"/>
@@ -12234,9 +12571,9 @@
       <c r="A39" s="90"/>
       <c r="B39" s="99"/>
       <c r="C39" s="92"/>
-      <c r="D39" s="224"/>
-      <c r="E39" s="225"/>
-      <c r="F39" s="225"/>
+      <c r="D39" s="228"/>
+      <c r="E39" s="229"/>
+      <c r="F39" s="229"/>
       <c r="G39" s="95"/>
       <c r="H39" s="94"/>
       <c r="I39" s="93"/>
@@ -12247,9 +12584,9 @@
       <c r="A40" s="90"/>
       <c r="B40" s="99"/>
       <c r="C40" s="92"/>
-      <c r="D40" s="224"/>
-      <c r="E40" s="225"/>
-      <c r="F40" s="225"/>
+      <c r="D40" s="228"/>
+      <c r="E40" s="229"/>
+      <c r="F40" s="229"/>
       <c r="G40" s="95"/>
       <c r="H40" s="94"/>
       <c r="I40" s="93"/>
@@ -12260,9 +12597,9 @@
       <c r="A41" s="90"/>
       <c r="B41" s="99"/>
       <c r="C41" s="92"/>
-      <c r="D41" s="224"/>
-      <c r="E41" s="225"/>
-      <c r="F41" s="225"/>
+      <c r="D41" s="228"/>
+      <c r="E41" s="229"/>
+      <c r="F41" s="229"/>
       <c r="G41" s="95"/>
       <c r="H41" s="94"/>
       <c r="I41" s="93"/>
@@ -12273,9 +12610,9 @@
       <c r="A42" s="90"/>
       <c r="B42" s="99"/>
       <c r="C42" s="92"/>
-      <c r="D42" s="224"/>
-      <c r="E42" s="225"/>
-      <c r="F42" s="225"/>
+      <c r="D42" s="228"/>
+      <c r="E42" s="229"/>
+      <c r="F42" s="229"/>
       <c r="G42" s="95"/>
       <c r="H42" s="94"/>
       <c r="I42" s="93"/>
@@ -12286,9 +12623,9 @@
       <c r="A43" s="90"/>
       <c r="B43" s="99"/>
       <c r="C43" s="92"/>
-      <c r="D43" s="224"/>
-      <c r="E43" s="225"/>
-      <c r="F43" s="225"/>
+      <c r="D43" s="228"/>
+      <c r="E43" s="229"/>
+      <c r="F43" s="229"/>
       <c r="G43" s="95"/>
       <c r="H43" s="94"/>
       <c r="I43" s="93"/>
@@ -12299,9 +12636,9 @@
       <c r="A44" s="90"/>
       <c r="B44" s="99"/>
       <c r="C44" s="92"/>
-      <c r="D44" s="224"/>
-      <c r="E44" s="225"/>
-      <c r="F44" s="225"/>
+      <c r="D44" s="228"/>
+      <c r="E44" s="229"/>
+      <c r="F44" s="229"/>
       <c r="G44" s="95"/>
       <c r="H44" s="94"/>
       <c r="I44" s="93"/>
@@ -12312,9 +12649,9 @@
       <c r="A45" s="90"/>
       <c r="B45" s="99"/>
       <c r="C45" s="92"/>
-      <c r="D45" s="224"/>
-      <c r="E45" s="225"/>
-      <c r="F45" s="225"/>
+      <c r="D45" s="228"/>
+      <c r="E45" s="229"/>
+      <c r="F45" s="229"/>
       <c r="G45" s="95"/>
       <c r="H45" s="94"/>
       <c r="I45" s="93"/>
@@ -12325,9 +12662,9 @@
       <c r="A46" s="90"/>
       <c r="B46" s="99"/>
       <c r="C46" s="92"/>
-      <c r="D46" s="224"/>
-      <c r="E46" s="225"/>
-      <c r="F46" s="225"/>
+      <c r="D46" s="228"/>
+      <c r="E46" s="229"/>
+      <c r="F46" s="229"/>
       <c r="G46" s="95"/>
       <c r="H46" s="94"/>
       <c r="I46" s="93"/>
@@ -12338,9 +12675,9 @@
       <c r="A47" s="90"/>
       <c r="B47" s="99"/>
       <c r="C47" s="92"/>
-      <c r="D47" s="224"/>
-      <c r="E47" s="225"/>
-      <c r="F47" s="225"/>
+      <c r="D47" s="228"/>
+      <c r="E47" s="229"/>
+      <c r="F47" s="229"/>
       <c r="G47" s="95"/>
       <c r="H47" s="94"/>
       <c r="I47" s="93"/>
@@ -12351,9 +12688,9 @@
       <c r="A48" s="90"/>
       <c r="B48" s="99"/>
       <c r="C48" s="92"/>
-      <c r="D48" s="224"/>
-      <c r="E48" s="225"/>
-      <c r="F48" s="225"/>
+      <c r="D48" s="228"/>
+      <c r="E48" s="229"/>
+      <c r="F48" s="229"/>
       <c r="G48" s="95"/>
       <c r="H48" s="94"/>
       <c r="I48" s="93"/>
@@ -12364,9 +12701,9 @@
       <c r="A49" s="90"/>
       <c r="B49" s="99"/>
       <c r="C49" s="92"/>
-      <c r="D49" s="224"/>
-      <c r="E49" s="225"/>
-      <c r="F49" s="225"/>
+      <c r="D49" s="228"/>
+      <c r="E49" s="229"/>
+      <c r="F49" s="229"/>
       <c r="G49" s="95"/>
       <c r="H49" s="94"/>
       <c r="I49" s="93"/>
@@ -12377,9 +12714,9 @@
       <c r="A50" s="90"/>
       <c r="B50" s="99"/>
       <c r="C50" s="92"/>
-      <c r="D50" s="224"/>
-      <c r="E50" s="225"/>
-      <c r="F50" s="225"/>
+      <c r="D50" s="228"/>
+      <c r="E50" s="229"/>
+      <c r="F50" s="229"/>
       <c r="G50" s="95"/>
       <c r="H50" s="94"/>
       <c r="I50" s="93"/>
@@ -12390,9 +12727,9 @@
       <c r="A51" s="90"/>
       <c r="B51" s="99"/>
       <c r="C51" s="92"/>
-      <c r="D51" s="224"/>
-      <c r="E51" s="225"/>
-      <c r="F51" s="225"/>
+      <c r="D51" s="228"/>
+      <c r="E51" s="229"/>
+      <c r="F51" s="229"/>
       <c r="G51" s="95"/>
       <c r="H51" s="94"/>
       <c r="I51" s="93"/>
@@ -12403,9 +12740,9 @@
       <c r="A52" s="90"/>
       <c r="B52" s="99"/>
       <c r="C52" s="92"/>
-      <c r="D52" s="224"/>
-      <c r="E52" s="225"/>
-      <c r="F52" s="225"/>
+      <c r="D52" s="228"/>
+      <c r="E52" s="229"/>
+      <c r="F52" s="229"/>
       <c r="G52" s="95"/>
       <c r="H52" s="94"/>
       <c r="I52" s="93"/>
@@ -12416,9 +12753,9 @@
       <c r="A53" s="90"/>
       <c r="B53" s="99"/>
       <c r="C53" s="92"/>
-      <c r="D53" s="224"/>
-      <c r="E53" s="225"/>
-      <c r="F53" s="225"/>
+      <c r="D53" s="228"/>
+      <c r="E53" s="229"/>
+      <c r="F53" s="229"/>
       <c r="G53" s="95"/>
       <c r="H53" s="94"/>
       <c r="I53" s="93"/>
@@ -12429,9 +12766,9 @@
       <c r="A54" s="90"/>
       <c r="B54" s="99"/>
       <c r="C54" s="92"/>
-      <c r="D54" s="224"/>
-      <c r="E54" s="225"/>
-      <c r="F54" s="225"/>
+      <c r="D54" s="228"/>
+      <c r="E54" s="229"/>
+      <c r="F54" s="229"/>
       <c r="G54" s="95"/>
       <c r="H54" s="94"/>
       <c r="I54" s="93"/>
@@ -12442,9 +12779,9 @@
       <c r="A55" s="90"/>
       <c r="B55" s="99"/>
       <c r="C55" s="92"/>
-      <c r="D55" s="224"/>
-      <c r="E55" s="225"/>
-      <c r="F55" s="225"/>
+      <c r="D55" s="228"/>
+      <c r="E55" s="229"/>
+      <c r="F55" s="229"/>
       <c r="G55" s="95"/>
       <c r="H55" s="94"/>
       <c r="I55" s="93"/>
@@ -12455,9 +12792,9 @@
       <c r="A56" s="90"/>
       <c r="B56" s="99"/>
       <c r="C56" s="92"/>
-      <c r="D56" s="224"/>
-      <c r="E56" s="225"/>
-      <c r="F56" s="225"/>
+      <c r="D56" s="228"/>
+      <c r="E56" s="229"/>
+      <c r="F56" s="229"/>
       <c r="G56" s="95"/>
       <c r="H56" s="94"/>
       <c r="I56" s="93"/>
@@ -12468,9 +12805,9 @@
       <c r="A57" s="90"/>
       <c r="B57" s="99"/>
       <c r="C57" s="92"/>
-      <c r="D57" s="224"/>
-      <c r="E57" s="225"/>
-      <c r="F57" s="225"/>
+      <c r="D57" s="228"/>
+      <c r="E57" s="229"/>
+      <c r="F57" s="229"/>
       <c r="G57" s="95"/>
       <c r="H57" s="94"/>
       <c r="I57" s="93"/>
@@ -12481,9 +12818,9 @@
       <c r="A58" s="90"/>
       <c r="B58" s="99"/>
       <c r="C58" s="92"/>
-      <c r="D58" s="224"/>
-      <c r="E58" s="225"/>
-      <c r="F58" s="225"/>
+      <c r="D58" s="228"/>
+      <c r="E58" s="229"/>
+      <c r="F58" s="229"/>
       <c r="G58" s="95"/>
       <c r="H58" s="94"/>
       <c r="I58" s="93"/>
@@ -12494,9 +12831,9 @@
       <c r="A59" s="90"/>
       <c r="B59" s="99"/>
       <c r="C59" s="92"/>
-      <c r="D59" s="224"/>
-      <c r="E59" s="225"/>
-      <c r="F59" s="225"/>
+      <c r="D59" s="228"/>
+      <c r="E59" s="229"/>
+      <c r="F59" s="229"/>
       <c r="G59" s="95"/>
       <c r="H59" s="94"/>
       <c r="I59" s="93"/>
@@ -12507,9 +12844,9 @@
       <c r="A60" s="90"/>
       <c r="B60" s="99"/>
       <c r="C60" s="92"/>
-      <c r="D60" s="224"/>
-      <c r="E60" s="225"/>
-      <c r="F60" s="225"/>
+      <c r="D60" s="228"/>
+      <c r="E60" s="229"/>
+      <c r="F60" s="229"/>
       <c r="G60" s="95"/>
       <c r="H60" s="94"/>
       <c r="I60" s="93"/>
@@ -12520,9 +12857,9 @@
       <c r="A61" s="90"/>
       <c r="B61" s="99"/>
       <c r="C61" s="92"/>
-      <c r="D61" s="224"/>
-      <c r="E61" s="225"/>
-      <c r="F61" s="225"/>
+      <c r="D61" s="228"/>
+      <c r="E61" s="229"/>
+      <c r="F61" s="229"/>
       <c r="G61" s="95"/>
       <c r="H61" s="94"/>
       <c r="I61" s="93"/>
@@ -12533,9 +12870,9 @@
       <c r="A62" s="90"/>
       <c r="B62" s="99"/>
       <c r="C62" s="92"/>
-      <c r="D62" s="224"/>
-      <c r="E62" s="225"/>
-      <c r="F62" s="225"/>
+      <c r="D62" s="228"/>
+      <c r="E62" s="229"/>
+      <c r="F62" s="229"/>
       <c r="G62" s="95"/>
       <c r="H62" s="94"/>
       <c r="I62" s="93"/>
@@ -12546,9 +12883,9 @@
       <c r="A63" s="90"/>
       <c r="B63" s="99"/>
       <c r="C63" s="92"/>
-      <c r="D63" s="224"/>
-      <c r="E63" s="225"/>
-      <c r="F63" s="225"/>
+      <c r="D63" s="228"/>
+      <c r="E63" s="229"/>
+      <c r="F63" s="229"/>
       <c r="G63" s="95"/>
       <c r="H63" s="94"/>
       <c r="I63" s="93"/>
@@ -12559,9 +12896,9 @@
       <c r="A64" s="90"/>
       <c r="B64" s="99"/>
       <c r="C64" s="92"/>
-      <c r="D64" s="224"/>
-      <c r="E64" s="225"/>
-      <c r="F64" s="225"/>
+      <c r="D64" s="228"/>
+      <c r="E64" s="229"/>
+      <c r="F64" s="229"/>
       <c r="G64" s="95"/>
       <c r="H64" s="94"/>
       <c r="I64" s="93"/>
@@ -12572,9 +12909,9 @@
       <c r="A65" s="90"/>
       <c r="B65" s="99"/>
       <c r="C65" s="92"/>
-      <c r="D65" s="224"/>
-      <c r="E65" s="225"/>
-      <c r="F65" s="225"/>
+      <c r="D65" s="228"/>
+      <c r="E65" s="229"/>
+      <c r="F65" s="229"/>
       <c r="G65" s="95"/>
       <c r="H65" s="94"/>
       <c r="I65" s="93"/>
@@ -12585,9 +12922,9 @@
       <c r="A66" s="90"/>
       <c r="B66" s="99"/>
       <c r="C66" s="92"/>
-      <c r="D66" s="224"/>
-      <c r="E66" s="225"/>
-      <c r="F66" s="225"/>
+      <c r="D66" s="228"/>
+      <c r="E66" s="229"/>
+      <c r="F66" s="229"/>
       <c r="G66" s="95"/>
       <c r="H66" s="94"/>
       <c r="I66" s="93"/>
@@ -12598,9 +12935,9 @@
       <c r="A67" s="90"/>
       <c r="B67" s="99"/>
       <c r="C67" s="92"/>
-      <c r="D67" s="224"/>
-      <c r="E67" s="225"/>
-      <c r="F67" s="225"/>
+      <c r="D67" s="228"/>
+      <c r="E67" s="229"/>
+      <c r="F67" s="229"/>
       <c r="G67" s="95"/>
       <c r="H67" s="94"/>
       <c r="I67" s="93"/>
@@ -12611,9 +12948,9 @@
       <c r="A68" s="90"/>
       <c r="B68" s="99"/>
       <c r="C68" s="92"/>
-      <c r="D68" s="224"/>
-      <c r="E68" s="225"/>
-      <c r="F68" s="225"/>
+      <c r="D68" s="228"/>
+      <c r="E68" s="229"/>
+      <c r="F68" s="229"/>
       <c r="G68" s="95"/>
       <c r="H68" s="94"/>
       <c r="I68" s="93"/>
@@ -12624,9 +12961,9 @@
       <c r="A69" s="90"/>
       <c r="B69" s="99"/>
       <c r="C69" s="92"/>
-      <c r="D69" s="224"/>
-      <c r="E69" s="225"/>
-      <c r="F69" s="225"/>
+      <c r="D69" s="228"/>
+      <c r="E69" s="229"/>
+      <c r="F69" s="229"/>
       <c r="G69" s="95"/>
       <c r="H69" s="94"/>
       <c r="I69" s="93"/>
@@ -12637,9 +12974,9 @@
       <c r="A70" s="90"/>
       <c r="B70" s="99"/>
       <c r="C70" s="92"/>
-      <c r="D70" s="224"/>
-      <c r="E70" s="225"/>
-      <c r="F70" s="225"/>
+      <c r="D70" s="228"/>
+      <c r="E70" s="229"/>
+      <c r="F70" s="229"/>
       <c r="G70" s="95"/>
       <c r="H70" s="94"/>
       <c r="I70" s="93"/>
@@ -12650,9 +12987,9 @@
       <c r="A71" s="90"/>
       <c r="B71" s="99"/>
       <c r="C71" s="92"/>
-      <c r="D71" s="224"/>
-      <c r="E71" s="225"/>
-      <c r="F71" s="225"/>
+      <c r="D71" s="228"/>
+      <c r="E71" s="229"/>
+      <c r="F71" s="229"/>
       <c r="G71" s="95"/>
       <c r="H71" s="94"/>
       <c r="I71" s="93"/>
@@ -12663,9 +13000,9 @@
       <c r="A72" s="90"/>
       <c r="B72" s="99"/>
       <c r="C72" s="92"/>
-      <c r="D72" s="224"/>
-      <c r="E72" s="225"/>
-      <c r="F72" s="225"/>
+      <c r="D72" s="228"/>
+      <c r="E72" s="229"/>
+      <c r="F72" s="229"/>
       <c r="G72" s="95"/>
       <c r="H72" s="94"/>
       <c r="I72" s="93"/>
@@ -12676,9 +13013,9 @@
       <c r="A73" s="90"/>
       <c r="B73" s="99"/>
       <c r="C73" s="92"/>
-      <c r="D73" s="224"/>
-      <c r="E73" s="225"/>
-      <c r="F73" s="225"/>
+      <c r="D73" s="228"/>
+      <c r="E73" s="229"/>
+      <c r="F73" s="229"/>
       <c r="G73" s="95"/>
       <c r="H73" s="94"/>
       <c r="I73" s="93"/>
@@ -12689,9 +13026,9 @@
       <c r="A74" s="90"/>
       <c r="B74" s="99"/>
       <c r="C74" s="92"/>
-      <c r="D74" s="224"/>
-      <c r="E74" s="225"/>
-      <c r="F74" s="225"/>
+      <c r="D74" s="228"/>
+      <c r="E74" s="229"/>
+      <c r="F74" s="229"/>
       <c r="G74" s="95"/>
       <c r="H74" s="94"/>
       <c r="I74" s="93"/>
@@ -12702,9 +13039,9 @@
       <c r="A75" s="90"/>
       <c r="B75" s="99"/>
       <c r="C75" s="92"/>
-      <c r="D75" s="224"/>
-      <c r="E75" s="225"/>
-      <c r="F75" s="225"/>
+      <c r="D75" s="228"/>
+      <c r="E75" s="229"/>
+      <c r="F75" s="229"/>
       <c r="G75" s="95"/>
       <c r="H75" s="94"/>
       <c r="I75" s="93"/>
@@ -12715,9 +13052,9 @@
       <c r="A76" s="90"/>
       <c r="B76" s="99"/>
       <c r="C76" s="92"/>
-      <c r="D76" s="224"/>
-      <c r="E76" s="225"/>
-      <c r="F76" s="225"/>
+      <c r="D76" s="228"/>
+      <c r="E76" s="229"/>
+      <c r="F76" s="229"/>
       <c r="G76" s="95"/>
       <c r="H76" s="94"/>
       <c r="I76" s="93"/>
@@ -12728,9 +13065,9 @@
       <c r="A77" s="90"/>
       <c r="B77" s="99"/>
       <c r="C77" s="92"/>
-      <c r="D77" s="224"/>
-      <c r="E77" s="225"/>
-      <c r="F77" s="225"/>
+      <c r="D77" s="228"/>
+      <c r="E77" s="229"/>
+      <c r="F77" s="229"/>
       <c r="G77" s="95"/>
       <c r="H77" s="94"/>
       <c r="I77" s="93"/>
@@ -12741,9 +13078,9 @@
       <c r="A78" s="90"/>
       <c r="B78" s="99"/>
       <c r="C78" s="92"/>
-      <c r="D78" s="224"/>
-      <c r="E78" s="225"/>
-      <c r="F78" s="225"/>
+      <c r="D78" s="228"/>
+      <c r="E78" s="229"/>
+      <c r="F78" s="229"/>
       <c r="G78" s="95"/>
       <c r="H78" s="94"/>
       <c r="I78" s="93"/>
@@ -12754,9 +13091,9 @@
       <c r="A79" s="90"/>
       <c r="B79" s="99"/>
       <c r="C79" s="92"/>
-      <c r="D79" s="224"/>
-      <c r="E79" s="225"/>
-      <c r="F79" s="225"/>
+      <c r="D79" s="228"/>
+      <c r="E79" s="229"/>
+      <c r="F79" s="229"/>
       <c r="G79" s="95"/>
       <c r="H79" s="94"/>
       <c r="I79" s="93"/>
@@ -12767,9 +13104,9 @@
       <c r="A80" s="90"/>
       <c r="B80" s="99"/>
       <c r="C80" s="92"/>
-      <c r="D80" s="224"/>
-      <c r="E80" s="225"/>
-      <c r="F80" s="225"/>
+      <c r="D80" s="228"/>
+      <c r="E80" s="229"/>
+      <c r="F80" s="229"/>
       <c r="G80" s="95"/>
       <c r="H80" s="94"/>
       <c r="I80" s="93"/>
@@ -12780,9 +13117,9 @@
       <c r="A81" s="90"/>
       <c r="B81" s="99"/>
       <c r="C81" s="92"/>
-      <c r="D81" s="224"/>
-      <c r="E81" s="225"/>
-      <c r="F81" s="225"/>
+      <c r="D81" s="228"/>
+      <c r="E81" s="229"/>
+      <c r="F81" s="229"/>
       <c r="G81" s="95"/>
       <c r="H81" s="94"/>
       <c r="I81" s="93"/>
@@ -12793,9 +13130,9 @@
       <c r="A82" s="90"/>
       <c r="B82" s="99"/>
       <c r="C82" s="92"/>
-      <c r="D82" s="224"/>
-      <c r="E82" s="225"/>
-      <c r="F82" s="225"/>
+      <c r="D82" s="228"/>
+      <c r="E82" s="229"/>
+      <c r="F82" s="229"/>
       <c r="G82" s="95"/>
       <c r="H82" s="94"/>
       <c r="I82" s="93"/>
@@ -12806,9 +13143,9 @@
       <c r="A83" s="90"/>
       <c r="B83" s="99"/>
       <c r="C83" s="92"/>
-      <c r="D83" s="224"/>
-      <c r="E83" s="225"/>
-      <c r="F83" s="225"/>
+      <c r="D83" s="228"/>
+      <c r="E83" s="229"/>
+      <c r="F83" s="229"/>
       <c r="G83" s="95"/>
       <c r="H83" s="94"/>
       <c r="I83" s="93"/>
@@ -12819,9 +13156,9 @@
       <c r="A84" s="90"/>
       <c r="B84" s="99"/>
       <c r="C84" s="92"/>
-      <c r="D84" s="224"/>
-      <c r="E84" s="225"/>
-      <c r="F84" s="225"/>
+      <c r="D84" s="228"/>
+      <c r="E84" s="229"/>
+      <c r="F84" s="229"/>
       <c r="G84" s="95"/>
       <c r="H84" s="94"/>
       <c r="I84" s="93"/>
@@ -12832,9 +13169,9 @@
       <c r="A85" s="90"/>
       <c r="B85" s="99"/>
       <c r="C85" s="92"/>
-      <c r="D85" s="224"/>
-      <c r="E85" s="225"/>
-      <c r="F85" s="225"/>
+      <c r="D85" s="228"/>
+      <c r="E85" s="229"/>
+      <c r="F85" s="229"/>
       <c r="G85" s="95"/>
       <c r="H85" s="94"/>
       <c r="I85" s="93"/>
@@ -12845,9 +13182,9 @@
       <c r="A86" s="90"/>
       <c r="B86" s="99"/>
       <c r="C86" s="92"/>
-      <c r="D86" s="224"/>
-      <c r="E86" s="225"/>
-      <c r="F86" s="225"/>
+      <c r="D86" s="228"/>
+      <c r="E86" s="229"/>
+      <c r="F86" s="229"/>
       <c r="G86" s="95"/>
       <c r="H86" s="94"/>
       <c r="I86" s="93"/>
@@ -12858,9 +13195,9 @@
       <c r="A87" s="90"/>
       <c r="B87" s="99"/>
       <c r="C87" s="92"/>
-      <c r="D87" s="224"/>
-      <c r="E87" s="225"/>
-      <c r="F87" s="225"/>
+      <c r="D87" s="228"/>
+      <c r="E87" s="229"/>
+      <c r="F87" s="229"/>
       <c r="G87" s="95"/>
       <c r="H87" s="94"/>
       <c r="I87" s="93"/>
@@ -12869,12 +13206,81 @@
     </row>
   </sheetData>
   <mergeCells count="94">
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="D83:F83"/>
+    <mergeCell ref="D84:F84"/>
+    <mergeCell ref="D85:F85"/>
+    <mergeCell ref="D86:F86"/>
+    <mergeCell ref="D87:F87"/>
+    <mergeCell ref="D78:F78"/>
+    <mergeCell ref="D79:F79"/>
+    <mergeCell ref="D80:F80"/>
+    <mergeCell ref="D81:F81"/>
+    <mergeCell ref="D82:F82"/>
+    <mergeCell ref="D73:F73"/>
+    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="D75:F75"/>
+    <mergeCell ref="D76:F76"/>
+    <mergeCell ref="D77:F77"/>
+    <mergeCell ref="D68:F68"/>
+    <mergeCell ref="D69:F69"/>
+    <mergeCell ref="D70:F70"/>
+    <mergeCell ref="D71:F71"/>
+    <mergeCell ref="D72:F72"/>
+    <mergeCell ref="D63:F63"/>
+    <mergeCell ref="D64:F64"/>
+    <mergeCell ref="D65:F65"/>
+    <mergeCell ref="D66:F66"/>
+    <mergeCell ref="D67:F67"/>
+    <mergeCell ref="D58:F58"/>
+    <mergeCell ref="D59:F59"/>
+    <mergeCell ref="D60:F60"/>
+    <mergeCell ref="D61:F61"/>
+    <mergeCell ref="D62:F62"/>
+    <mergeCell ref="D53:F53"/>
+    <mergeCell ref="D54:F54"/>
+    <mergeCell ref="D55:F55"/>
+    <mergeCell ref="D56:F56"/>
+    <mergeCell ref="D57:F57"/>
+    <mergeCell ref="D48:F48"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="D50:F50"/>
+    <mergeCell ref="D51:F51"/>
+    <mergeCell ref="D52:F52"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="D44:F44"/>
+    <mergeCell ref="D45:F45"/>
+    <mergeCell ref="D46:F46"/>
+    <mergeCell ref="D47:F47"/>
+    <mergeCell ref="D38:F38"/>
+    <mergeCell ref="D39:F39"/>
+    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="A30:K30"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="A22:K22"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="A16:K16"/>
+    <mergeCell ref="D17:F17"/>
     <mergeCell ref="I6:K6"/>
     <mergeCell ref="I7:K7"/>
     <mergeCell ref="A8:D8"/>
@@ -12888,81 +13294,12 @@
     <mergeCell ref="J9:J10"/>
     <mergeCell ref="K9:K10"/>
     <mergeCell ref="D9:G10"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="A16:K16"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="A22:K22"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="A30:K30"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="D36:F36"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="D38:F38"/>
-    <mergeCell ref="D39:F39"/>
-    <mergeCell ref="D40:F40"/>
-    <mergeCell ref="D41:F41"/>
-    <mergeCell ref="D42:F42"/>
-    <mergeCell ref="D43:F43"/>
-    <mergeCell ref="D44:F44"/>
-    <mergeCell ref="D45:F45"/>
-    <mergeCell ref="D46:F46"/>
-    <mergeCell ref="D47:F47"/>
-    <mergeCell ref="D48:F48"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="D50:F50"/>
-    <mergeCell ref="D51:F51"/>
-    <mergeCell ref="D52:F52"/>
-    <mergeCell ref="D53:F53"/>
-    <mergeCell ref="D54:F54"/>
-    <mergeCell ref="D55:F55"/>
-    <mergeCell ref="D56:F56"/>
-    <mergeCell ref="D57:F57"/>
-    <mergeCell ref="D58:F58"/>
-    <mergeCell ref="D59:F59"/>
-    <mergeCell ref="D60:F60"/>
-    <mergeCell ref="D61:F61"/>
-    <mergeCell ref="D62:F62"/>
-    <mergeCell ref="D63:F63"/>
-    <mergeCell ref="D64:F64"/>
-    <mergeCell ref="D65:F65"/>
-    <mergeCell ref="D66:F66"/>
-    <mergeCell ref="D67:F67"/>
-    <mergeCell ref="D68:F68"/>
-    <mergeCell ref="D69:F69"/>
-    <mergeCell ref="D70:F70"/>
-    <mergeCell ref="D71:F71"/>
-    <mergeCell ref="D72:F72"/>
-    <mergeCell ref="D73:F73"/>
-    <mergeCell ref="D74:F74"/>
-    <mergeCell ref="D75:F75"/>
-    <mergeCell ref="D76:F76"/>
-    <mergeCell ref="D77:F77"/>
-    <mergeCell ref="D78:F78"/>
-    <mergeCell ref="D79:F79"/>
-    <mergeCell ref="D80:F80"/>
-    <mergeCell ref="D81:F81"/>
-    <mergeCell ref="D82:F82"/>
-    <mergeCell ref="D83:F83"/>
-    <mergeCell ref="D84:F84"/>
-    <mergeCell ref="D85:F85"/>
-    <mergeCell ref="D86:F86"/>
-    <mergeCell ref="D87:F87"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="I5:K5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/test-case-example.xlsx
+++ b/test-case-example.xlsx
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="977" uniqueCount="585">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="993" uniqueCount="589">
   <si>
     <t>TEST CASE</t>
   </si>
@@ -2352,6 +2352,18 @@
   </si>
   <si>
     <t>auth (116, 126, 139, 143, 149 - 174, 188-189, 193, 199-224, 230-239, 246, 258, 271-272, 277, 532, 586, 590-595); booking (380 - 382, 392); cancel (477 - 488); payment (649-657, 695); revenue_report (750)</t>
+  </si>
+  <si>
+    <t>116, 126, 139, 143, 149-174, 188-189, 193, 199-224, 230-239, 244-284, 380-382, 392, 477-488, 532, 586, 590-595, 649-657, 687-695, 749, 821, 880-881</t>
+  </si>
+  <si>
+    <t>auth (116 - 124, 230 - 284); booking (380 - 392); cancel (477 - 488); payment (649-657, 687-695); revenue_report (749, 821)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11, 16, 196, 295 - 335  </t>
+  </si>
+  <si>
+    <t>28/4/2026</t>
   </si>
 </sst>
 </file>
@@ -2725,7 +2737,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="64">
+  <borders count="74">
     <border>
       <left/>
       <right/>
@@ -3530,6 +3542,132 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFAAAAAA"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFAAAAAA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFAAAAAA"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFAAAAAA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFAAAAAA"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFAAAAAA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFAAAAAA"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFAAAAAA"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFAAAAAA"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFAAAAAA"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFAAAAAA"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFAAAAAA"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -3541,7 +3679,7 @@
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="255">
+  <cellXfs count="270">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3" applyFont="1"/>
@@ -3991,147 +4129,147 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="36" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="37" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="39" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="40" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="41" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="39" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="40" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="41" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="39" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="40" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="56" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="49" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="42" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="49" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="42" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="52" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="53" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="50" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="51" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="54" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="48" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="55" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="39" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="40" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="56" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="58" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="59" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="60" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="40" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="56" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="58" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="59" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="60" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="40" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="56" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="39" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="40" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="56" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="39" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="40" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="56" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="49" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="42" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="49" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="42" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="52" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="53" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="50" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="51" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="54" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="48" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="55" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="36" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="37" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="39" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="40" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="41" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="39" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="40" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="41" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -4150,24 +4288,24 @@
     <xf numFmtId="0" fontId="18" fillId="9" borderId="40" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="39" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="40" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="56" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="39" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="39" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="39" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="40" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="56" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="9" borderId="40" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -4195,13 +4333,34 @@
     <xf numFmtId="0" fontId="13" fillId="6" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="39" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="39" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4216,32 +4375,56 @@
     <xf numFmtId="9" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="9" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="1" fontId="10" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="66" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="3" borderId="67" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="3" borderId="72" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="3" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -4269,22 +4452,17 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>135547</xdr:colOff>
+      <xdr:colOff>97446</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>12023</xdr:rowOff>
+      <xdr:rowOff>116798</xdr:rowOff>
     </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>3386677</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>123824</xdr:rowOff>
-    </xdr:to>
+    <xdr:ext cx="3406435" cy="835702"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPr id="5" name="Picture 4"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -4297,8 +4475,46 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7955572" y="8813123"/>
-          <a:ext cx="3251130" cy="797601"/>
+          <a:off x="8298471" y="8917898"/>
+          <a:ext cx="3406435" cy="835702"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3505199</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>136203</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 5"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8296275" y="9877425"/>
+          <a:ext cx="3409949" cy="841053"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5179,11 +5395,11 @@
       <c r="A3" s="70" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="209" t="s">
+      <c r="B3" s="171" t="s">
         <v>62</v>
       </c>
-      <c r="C3" s="209"/>
-      <c r="D3" s="210"/>
+      <c r="C3" s="171"/>
+      <c r="D3" s="172"/>
       <c r="E3" s="71"/>
       <c r="F3" s="71"/>
       <c r="G3" s="71"/>
@@ -5192,11 +5408,11 @@
       <c r="A4" s="74" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="211" t="s">
+      <c r="B4" s="174" t="s">
         <v>488</v>
       </c>
-      <c r="C4" s="212"/>
-      <c r="D4" s="213"/>
+      <c r="C4" s="175"/>
+      <c r="D4" s="176"/>
       <c r="E4" s="71"/>
       <c r="F4" s="71"/>
       <c r="G4" s="71"/>
@@ -5205,11 +5421,11 @@
       <c r="A5" s="74" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="214" t="s">
+      <c r="B5" s="177" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="215"/>
-      <c r="D5" s="216"/>
+      <c r="C5" s="178"/>
+      <c r="D5" s="179"/>
       <c r="E5" s="75"/>
       <c r="F5" s="75"/>
       <c r="G5" s="75"/>
@@ -5258,59 +5474,59 @@
       <c r="G8" s="72"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="197" t="s">
+      <c r="A9" s="187" t="s">
         <v>71</v>
       </c>
-      <c r="B9" s="199" t="s">
+      <c r="B9" s="189" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="197" t="s">
+      <c r="C9" s="187" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="203" t="s">
+      <c r="D9" s="193" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="204"/>
-      <c r="F9" s="204"/>
-      <c r="G9" s="205"/>
-      <c r="H9" s="201" t="s">
+      <c r="E9" s="194"/>
+      <c r="F9" s="194"/>
+      <c r="G9" s="195"/>
+      <c r="H9" s="191" t="s">
         <v>75</v>
       </c>
-      <c r="I9" s="202" t="s">
+      <c r="I9" s="192" t="s">
         <v>76</v>
       </c>
-      <c r="J9" s="202" t="s">
+      <c r="J9" s="192" t="s">
         <v>77</v>
       </c>
-      <c r="K9" s="202" t="s">
+      <c r="K9" s="192" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="198"/>
-      <c r="B10" s="200"/>
-      <c r="C10" s="198"/>
-      <c r="D10" s="206"/>
-      <c r="E10" s="207"/>
-      <c r="F10" s="207"/>
-      <c r="G10" s="208"/>
-      <c r="H10" s="197"/>
-      <c r="I10" s="197"/>
-      <c r="J10" s="197"/>
-      <c r="K10" s="197"/>
+      <c r="A10" s="188"/>
+      <c r="B10" s="190"/>
+      <c r="C10" s="188"/>
+      <c r="D10" s="196"/>
+      <c r="E10" s="197"/>
+      <c r="F10" s="197"/>
+      <c r="G10" s="198"/>
+      <c r="H10" s="187"/>
+      <c r="I10" s="187"/>
+      <c r="J10" s="187"/>
+      <c r="K10" s="187"/>
     </row>
     <row r="11" spans="1:11" ht="15">
-      <c r="A11" s="195"/>
-      <c r="B11" s="195"/>
-      <c r="C11" s="195"/>
-      <c r="D11" s="195"/>
-      <c r="E11" s="195"/>
-      <c r="F11" s="195"/>
-      <c r="G11" s="195"/>
-      <c r="H11" s="195"/>
-      <c r="I11" s="195"/>
-      <c r="J11" s="195"/>
-      <c r="K11" s="196"/>
+      <c r="A11" s="182"/>
+      <c r="B11" s="182"/>
+      <c r="C11" s="182"/>
+      <c r="D11" s="182"/>
+      <c r="E11" s="182"/>
+      <c r="F11" s="182"/>
+      <c r="G11" s="182"/>
+      <c r="H11" s="182"/>
+      <c r="I11" s="182"/>
+      <c r="J11" s="182"/>
+      <c r="K11" s="183"/>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="184" t="s">
@@ -5337,12 +5553,12 @@
       <c r="C13" s="92" t="s">
         <v>491</v>
       </c>
-      <c r="D13" s="187" t="s">
+      <c r="D13" s="199" t="s">
         <v>492</v>
       </c>
-      <c r="E13" s="176"/>
-      <c r="F13" s="176"/>
-      <c r="G13" s="177"/>
+      <c r="E13" s="200"/>
+      <c r="F13" s="200"/>
+      <c r="G13" s="201"/>
       <c r="H13" s="94"/>
       <c r="I13" s="96"/>
       <c r="J13" s="92" t="s">
@@ -5375,12 +5591,12 @@
       <c r="C15" s="102" t="s">
         <v>495</v>
       </c>
-      <c r="D15" s="188" t="s">
+      <c r="D15" s="202" t="s">
         <v>496</v>
       </c>
-      <c r="E15" s="189"/>
-      <c r="F15" s="189"/>
-      <c r="G15" s="190"/>
+      <c r="E15" s="203"/>
+      <c r="F15" s="203"/>
+      <c r="G15" s="204"/>
       <c r="H15" s="103"/>
       <c r="I15" s="103"/>
       <c r="J15" s="104" t="s">
@@ -5413,12 +5629,12 @@
       <c r="C17" s="102" t="s">
         <v>499</v>
       </c>
-      <c r="D17" s="188" t="s">
+      <c r="D17" s="202" t="s">
         <v>500</v>
       </c>
-      <c r="E17" s="189"/>
-      <c r="F17" s="189"/>
-      <c r="G17" s="190"/>
+      <c r="E17" s="203"/>
+      <c r="F17" s="203"/>
+      <c r="G17" s="204"/>
       <c r="H17" s="103"/>
       <c r="I17" s="103"/>
       <c r="J17" s="104" t="s">
@@ -5451,12 +5667,12 @@
       <c r="C19" s="102" t="s">
         <v>503</v>
       </c>
-      <c r="D19" s="188" t="s">
+      <c r="D19" s="202" t="s">
         <v>504</v>
       </c>
-      <c r="E19" s="189"/>
-      <c r="F19" s="189"/>
-      <c r="G19" s="190"/>
+      <c r="E19" s="203"/>
+      <c r="F19" s="203"/>
+      <c r="G19" s="204"/>
       <c r="H19" s="103"/>
       <c r="I19" s="103"/>
       <c r="J19" s="104" t="s">
@@ -5489,12 +5705,12 @@
       <c r="C21" s="102" t="s">
         <v>507</v>
       </c>
-      <c r="D21" s="188" t="s">
+      <c r="D21" s="202" t="s">
         <v>508</v>
       </c>
-      <c r="E21" s="189"/>
-      <c r="F21" s="189"/>
-      <c r="G21" s="190"/>
+      <c r="E21" s="203"/>
+      <c r="F21" s="203"/>
+      <c r="G21" s="204"/>
       <c r="H21" s="103"/>
       <c r="I21" s="103"/>
       <c r="J21" s="104" t="s">
@@ -5527,12 +5743,12 @@
       <c r="C23" s="102" t="s">
         <v>511</v>
       </c>
-      <c r="D23" s="188" t="s">
+      <c r="D23" s="202" t="s">
         <v>512</v>
       </c>
-      <c r="E23" s="189"/>
-      <c r="F23" s="189"/>
-      <c r="G23" s="190"/>
+      <c r="E23" s="203"/>
+      <c r="F23" s="203"/>
+      <c r="G23" s="204"/>
       <c r="H23" s="103"/>
       <c r="I23" s="103"/>
       <c r="J23" s="104" t="s">
@@ -5565,12 +5781,12 @@
       <c r="C25" s="102" t="s">
         <v>515</v>
       </c>
-      <c r="D25" s="188" t="s">
+      <c r="D25" s="202" t="s">
         <v>516</v>
       </c>
-      <c r="E25" s="189"/>
-      <c r="F25" s="189"/>
-      <c r="G25" s="190"/>
+      <c r="E25" s="203"/>
+      <c r="F25" s="203"/>
+      <c r="G25" s="204"/>
       <c r="H25" s="103"/>
       <c r="I25" s="103"/>
       <c r="J25" s="104" t="s">
@@ -5603,12 +5819,12 @@
       <c r="C27" s="102" t="s">
         <v>519</v>
       </c>
-      <c r="D27" s="188" t="s">
+      <c r="D27" s="202" t="s">
         <v>520</v>
       </c>
-      <c r="E27" s="189"/>
-      <c r="F27" s="189"/>
-      <c r="G27" s="190"/>
+      <c r="E27" s="203"/>
+      <c r="F27" s="203"/>
+      <c r="G27" s="204"/>
       <c r="H27" s="103"/>
       <c r="I27" s="103"/>
       <c r="J27" s="104" t="s">
@@ -5641,12 +5857,12 @@
       <c r="C29" s="102" t="s">
         <v>523</v>
       </c>
-      <c r="D29" s="188" t="s">
+      <c r="D29" s="202" t="s">
         <v>524</v>
       </c>
-      <c r="E29" s="189"/>
-      <c r="F29" s="189"/>
-      <c r="G29" s="190"/>
+      <c r="E29" s="203"/>
+      <c r="F29" s="203"/>
+      <c r="G29" s="204"/>
       <c r="H29" s="103"/>
       <c r="I29" s="103"/>
       <c r="J29" s="104" t="s">
@@ -5679,12 +5895,12 @@
       <c r="C31" s="102" t="s">
         <v>527</v>
       </c>
-      <c r="D31" s="188" t="s">
+      <c r="D31" s="202" t="s">
         <v>528</v>
       </c>
-      <c r="E31" s="189"/>
-      <c r="F31" s="189"/>
-      <c r="G31" s="190"/>
+      <c r="E31" s="203"/>
+      <c r="F31" s="203"/>
+      <c r="G31" s="204"/>
       <c r="H31" s="103"/>
       <c r="I31" s="103"/>
       <c r="J31" s="104" t="s">
@@ -5717,12 +5933,12 @@
       <c r="C33" s="102" t="s">
         <v>531</v>
       </c>
-      <c r="D33" s="188" t="s">
+      <c r="D33" s="202" t="s">
         <v>524</v>
       </c>
-      <c r="E33" s="189"/>
-      <c r="F33" s="189"/>
-      <c r="G33" s="190"/>
+      <c r="E33" s="203"/>
+      <c r="F33" s="203"/>
+      <c r="G33" s="204"/>
       <c r="H33" s="103"/>
       <c r="I33" s="103"/>
       <c r="J33" s="104" t="s">
@@ -5732,25 +5948,6 @@
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A11:K11"/>
-    <mergeCell ref="A12:K12"/>
-    <mergeCell ref="D13:G13"/>
-    <mergeCell ref="A14:K14"/>
-    <mergeCell ref="D15:G15"/>
-    <mergeCell ref="A16:K16"/>
-    <mergeCell ref="D23:G23"/>
-    <mergeCell ref="A24:K24"/>
-    <mergeCell ref="D25:G25"/>
-    <mergeCell ref="A26:K26"/>
-    <mergeCell ref="D17:G17"/>
-    <mergeCell ref="A18:K18"/>
-    <mergeCell ref="D19:G19"/>
-    <mergeCell ref="A20:K20"/>
-    <mergeCell ref="D21:G21"/>
     <mergeCell ref="A32:K32"/>
     <mergeCell ref="D33:G33"/>
     <mergeCell ref="A9:A10"/>
@@ -5767,6 +5964,25 @@
     <mergeCell ref="A30:K30"/>
     <mergeCell ref="D31:G31"/>
     <mergeCell ref="A22:K22"/>
+    <mergeCell ref="D23:G23"/>
+    <mergeCell ref="A24:K24"/>
+    <mergeCell ref="D25:G25"/>
+    <mergeCell ref="A26:K26"/>
+    <mergeCell ref="D17:G17"/>
+    <mergeCell ref="A18:K18"/>
+    <mergeCell ref="D19:G19"/>
+    <mergeCell ref="A20:K20"/>
+    <mergeCell ref="D21:G21"/>
+    <mergeCell ref="A12:K12"/>
+    <mergeCell ref="D13:G13"/>
+    <mergeCell ref="A14:K14"/>
+    <mergeCell ref="D15:G15"/>
+    <mergeCell ref="A16:K16"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A11:K11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5795,9 +6011,9 @@
       <c r="A1" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="239"/>
-      <c r="C1" s="239"/>
-      <c r="D1" s="239"/>
+      <c r="B1" s="240"/>
+      <c r="C1" s="240"/>
+      <c r="D1" s="240"/>
       <c r="E1" s="67"/>
       <c r="F1" s="67"/>
       <c r="G1" s="67"/>
@@ -5809,9 +6025,9 @@
     </row>
     <row r="2" spans="1:12" s="60" customFormat="1" ht="11.25" customHeight="1">
       <c r="A2" s="69"/>
-      <c r="B2" s="240"/>
-      <c r="C2" s="240"/>
-      <c r="D2" s="240"/>
+      <c r="B2" s="241"/>
+      <c r="C2" s="241"/>
+      <c r="D2" s="241"/>
       <c r="E2" s="67"/>
       <c r="F2" s="67"/>
       <c r="G2" s="67"/>
@@ -5825,54 +6041,54 @@
       <c r="A3" s="70" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="209" t="s">
+      <c r="B3" s="171" t="s">
         <v>532</v>
       </c>
-      <c r="C3" s="209"/>
-      <c r="D3" s="210"/>
+      <c r="C3" s="171"/>
+      <c r="D3" s="172"/>
       <c r="E3" s="71"/>
       <c r="F3" s="71"/>
       <c r="G3" s="71"/>
       <c r="H3" s="71"/>
-      <c r="I3" s="193"/>
-      <c r="J3" s="193"/>
-      <c r="K3" s="193"/>
+      <c r="I3" s="173"/>
+      <c r="J3" s="173"/>
+      <c r="K3" s="173"/>
       <c r="L3" s="73"/>
     </row>
     <row r="4" spans="1:12" s="61" customFormat="1" ht="12.75">
       <c r="A4" s="74" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="211" t="s">
+      <c r="B4" s="174" t="s">
         <v>533</v>
       </c>
-      <c r="C4" s="212"/>
-      <c r="D4" s="213"/>
+      <c r="C4" s="175"/>
+      <c r="D4" s="176"/>
       <c r="E4" s="71"/>
       <c r="F4" s="71"/>
       <c r="G4" s="71"/>
       <c r="H4" s="71"/>
-      <c r="I4" s="193"/>
-      <c r="J4" s="193"/>
-      <c r="K4" s="193"/>
+      <c r="I4" s="173"/>
+      <c r="J4" s="173"/>
+      <c r="K4" s="173"/>
       <c r="L4" s="73"/>
     </row>
     <row r="5" spans="1:12" s="62" customFormat="1" ht="25.5">
       <c r="A5" s="74" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="214" t="s">
+      <c r="B5" s="177" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="215"/>
-      <c r="D5" s="216"/>
+      <c r="C5" s="178"/>
+      <c r="D5" s="179"/>
       <c r="E5" s="75"/>
       <c r="F5" s="75"/>
       <c r="G5" s="75"/>
       <c r="H5" s="75"/>
-      <c r="I5" s="217"/>
-      <c r="J5" s="217"/>
-      <c r="K5" s="217"/>
+      <c r="I5" s="180"/>
+      <c r="J5" s="180"/>
+      <c r="K5" s="180"/>
       <c r="L5" s="76"/>
     </row>
     <row r="6" spans="1:12" s="61" customFormat="1" ht="15" customHeight="1">
@@ -5894,9 +6110,9 @@
       <c r="F6" s="72"/>
       <c r="G6" s="72"/>
       <c r="H6" s="72"/>
-      <c r="I6" s="193"/>
-      <c r="J6" s="193"/>
-      <c r="K6" s="193"/>
+      <c r="I6" s="173"/>
+      <c r="J6" s="173"/>
+      <c r="K6" s="173"/>
       <c r="L6" s="73"/>
     </row>
     <row r="7" spans="1:12" s="61" customFormat="1" ht="15" customHeight="1">
@@ -5918,16 +6134,16 @@
       <c r="F7" s="85"/>
       <c r="G7" s="85"/>
       <c r="H7" s="85"/>
-      <c r="I7" s="193"/>
-      <c r="J7" s="193"/>
-      <c r="K7" s="193"/>
+      <c r="I7" s="173"/>
+      <c r="J7" s="173"/>
+      <c r="K7" s="173"/>
       <c r="L7" s="73"/>
     </row>
     <row r="8" spans="1:12" s="61" customFormat="1" ht="15" customHeight="1">
-      <c r="A8" s="194"/>
-      <c r="B8" s="194"/>
-      <c r="C8" s="194"/>
-      <c r="D8" s="194"/>
+      <c r="A8" s="181"/>
+      <c r="B8" s="181"/>
+      <c r="C8" s="181"/>
+      <c r="D8" s="181"/>
       <c r="E8" s="72"/>
       <c r="F8" s="72"/>
       <c r="G8" s="72"/>
@@ -5938,61 +6154,61 @@
       <c r="L8" s="73"/>
     </row>
     <row r="9" spans="1:12" s="63" customFormat="1" ht="12" customHeight="1">
-      <c r="A9" s="197" t="s">
+      <c r="A9" s="187" t="s">
         <v>71</v>
       </c>
-      <c r="B9" s="199" t="s">
+      <c r="B9" s="189" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="197" t="s">
+      <c r="C9" s="187" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="203" t="s">
+      <c r="D9" s="193" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="204"/>
-      <c r="F9" s="204"/>
-      <c r="G9" s="205"/>
-      <c r="H9" s="201" t="s">
+      <c r="E9" s="194"/>
+      <c r="F9" s="194"/>
+      <c r="G9" s="195"/>
+      <c r="H9" s="191" t="s">
         <v>75</v>
       </c>
-      <c r="I9" s="202" t="s">
+      <c r="I9" s="192" t="s">
         <v>76</v>
       </c>
-      <c r="J9" s="202" t="s">
+      <c r="J9" s="192" t="s">
         <v>77</v>
       </c>
-      <c r="K9" s="202" t="s">
+      <c r="K9" s="192" t="s">
         <v>78</v>
       </c>
       <c r="L9" s="87"/>
     </row>
     <row r="10" spans="1:12" s="61" customFormat="1" ht="12" customHeight="1">
-      <c r="A10" s="198"/>
-      <c r="B10" s="200"/>
-      <c r="C10" s="198"/>
-      <c r="D10" s="206"/>
-      <c r="E10" s="207"/>
-      <c r="F10" s="207"/>
-      <c r="G10" s="208"/>
-      <c r="H10" s="197"/>
-      <c r="I10" s="197"/>
-      <c r="J10" s="197"/>
-      <c r="K10" s="197"/>
+      <c r="A10" s="188"/>
+      <c r="B10" s="190"/>
+      <c r="C10" s="188"/>
+      <c r="D10" s="196"/>
+      <c r="E10" s="197"/>
+      <c r="F10" s="197"/>
+      <c r="G10" s="198"/>
+      <c r="H10" s="187"/>
+      <c r="I10" s="187"/>
+      <c r="J10" s="187"/>
+      <c r="K10" s="187"/>
       <c r="L10" s="73"/>
     </row>
     <row r="11" spans="1:12" s="64" customFormat="1" ht="15">
-      <c r="A11" s="195"/>
-      <c r="B11" s="195"/>
-      <c r="C11" s="195"/>
-      <c r="D11" s="195"/>
-      <c r="E11" s="195"/>
-      <c r="F11" s="195"/>
-      <c r="G11" s="195"/>
-      <c r="H11" s="195"/>
-      <c r="I11" s="195"/>
-      <c r="J11" s="195"/>
-      <c r="K11" s="196"/>
+      <c r="A11" s="182"/>
+      <c r="B11" s="182"/>
+      <c r="C11" s="182"/>
+      <c r="D11" s="182"/>
+      <c r="E11" s="182"/>
+      <c r="F11" s="182"/>
+      <c r="G11" s="182"/>
+      <c r="H11" s="182"/>
+      <c r="I11" s="182"/>
+      <c r="J11" s="182"/>
+      <c r="K11" s="183"/>
     </row>
     <row r="12" spans="1:12" s="65" customFormat="1" ht="12.75">
       <c r="A12" s="184" t="s">
@@ -6019,11 +6235,11 @@
       <c r="C13" s="92" t="s">
         <v>536</v>
       </c>
-      <c r="D13" s="175" t="s">
+      <c r="D13" s="207" t="s">
         <v>537</v>
       </c>
-      <c r="E13" s="176"/>
-      <c r="F13" s="176"/>
+      <c r="E13" s="200"/>
+      <c r="F13" s="200"/>
       <c r="G13" s="95"/>
       <c r="H13" s="94"/>
       <c r="I13" s="96"/>
@@ -6033,7 +6249,7 @@
       <c r="K13" s="92"/>
     </row>
     <row r="14" spans="1:12" s="65" customFormat="1" ht="12.75" outlineLevel="1">
-      <c r="A14" s="241" t="s">
+      <c r="A14" s="239" t="s">
         <v>538</v>
       </c>
       <c r="B14" s="223"/>
@@ -6057,11 +6273,11 @@
       <c r="C15" s="98" t="s">
         <v>540</v>
       </c>
-      <c r="D15" s="224" t="s">
+      <c r="D15" s="228" t="s">
         <v>541</v>
       </c>
-      <c r="E15" s="176"/>
-      <c r="F15" s="176"/>
+      <c r="E15" s="200"/>
+      <c r="F15" s="200"/>
       <c r="G15" s="95"/>
       <c r="H15" s="94"/>
       <c r="I15" s="93"/>
@@ -6071,7 +6287,7 @@
       <c r="K15" s="92"/>
     </row>
     <row r="16" spans="1:12" s="65" customFormat="1" ht="12.75" outlineLevel="1">
-      <c r="A16" s="241" t="s">
+      <c r="A16" s="239" t="s">
         <v>542</v>
       </c>
       <c r="B16" s="223"/>
@@ -6095,11 +6311,11 @@
       <c r="C17" s="92" t="s">
         <v>543</v>
       </c>
-      <c r="D17" s="224" t="s">
+      <c r="D17" s="228" t="s">
         <v>544</v>
       </c>
-      <c r="E17" s="225"/>
-      <c r="F17" s="225"/>
+      <c r="E17" s="229"/>
+      <c r="F17" s="229"/>
       <c r="G17" s="95"/>
       <c r="H17" s="94"/>
       <c r="I17" s="93"/>
@@ -6148,11 +6364,12 @@
     <row r="55" ht="12" customHeight="1"/>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="B1:D2"/>
+    <mergeCell ref="D9:G10"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="B3:D3"/>
     <mergeCell ref="A16:C16"/>
     <mergeCell ref="D17:F17"/>
     <mergeCell ref="I6:K6"/>
@@ -6167,12 +6384,11 @@
     <mergeCell ref="I9:I10"/>
     <mergeCell ref="J9:J10"/>
     <mergeCell ref="K9:K10"/>
-    <mergeCell ref="B1:D2"/>
-    <mergeCell ref="D9:G10"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="I5:K5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -6182,7 +6398,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="13.5"/>
   <cols>
     <col min="3" max="3" width="22.75" customWidth="1"/>
@@ -6266,10 +6482,10 @@
       <c r="F7" s="53" t="s">
         <v>68</v>
       </c>
-      <c r="G7" s="252" t="s">
+      <c r="G7" s="242" t="s">
         <v>550</v>
       </c>
-      <c r="H7" s="253"/>
+      <c r="H7" s="243"/>
     </row>
     <row r="8" spans="1:8" s="49" customFormat="1" ht="40.15" customHeight="1">
       <c r="A8" s="15"/>
@@ -6291,11 +6507,11 @@
         <f>COUNTIF(Auth!J10:J29, "Pending")</f>
         <v>0</v>
       </c>
-      <c r="G8" s="246">
+      <c r="G8" s="244">
         <f>Auth!D7</f>
         <v>26</v>
       </c>
-      <c r="H8" s="247"/>
+      <c r="H8" s="245"/>
     </row>
     <row r="9" spans="1:8" s="49" customFormat="1" ht="40.15" customHeight="1">
       <c r="A9" s="15"/>
@@ -6317,11 +6533,11 @@
         <f>COUNTIF(Home!J10:J29, "Pending")</f>
         <v>0</v>
       </c>
-      <c r="G9" s="248">
+      <c r="G9" s="246">
         <f>Home!D7</f>
         <v>17</v>
       </c>
-      <c r="H9" s="249"/>
+      <c r="H9" s="247"/>
     </row>
     <row r="10" spans="1:8" s="49" customFormat="1" ht="40.15" customHeight="1">
       <c r="A10" s="15"/>
@@ -6343,11 +6559,11 @@
         <f>COUNTIF(Favorite!J10:J29, "Pending")</f>
         <v>8</v>
       </c>
-      <c r="G10" s="254">
+      <c r="G10" s="248">
         <f>Favorite!D7</f>
         <v>8</v>
       </c>
-      <c r="H10" s="247"/>
+      <c r="H10" s="245"/>
     </row>
     <row r="11" spans="1:8" s="49" customFormat="1" ht="40.15" customHeight="1">
       <c r="A11" s="15"/>
@@ -6369,11 +6585,11 @@
         <f>COUNTIF(Booking!J10:J42, "Pending")</f>
         <v>23</v>
       </c>
-      <c r="G11" s="248">
+      <c r="G11" s="246">
         <f>Booking!D7</f>
         <v>23</v>
       </c>
-      <c r="H11" s="249"/>
+      <c r="H11" s="247"/>
     </row>
     <row r="12" spans="1:8" s="49" customFormat="1" ht="40.15" customHeight="1">
       <c r="A12" s="15"/>
@@ -6395,11 +6611,11 @@
         <f>COUNTIF('Cancel Booking'!J10:J29, "Pending")</f>
         <v>12</v>
       </c>
-      <c r="G12" s="246">
+      <c r="G12" s="244">
         <f>'Cancel Booking'!D7</f>
         <v>12</v>
       </c>
-      <c r="H12" s="247"/>
+      <c r="H12" s="245"/>
     </row>
     <row r="13" spans="1:8" s="49" customFormat="1" ht="40.15" customHeight="1">
       <c r="A13" s="15"/>
@@ -6421,11 +6637,11 @@
         <f>COUNTIF(Review!J10:J29, "Pending")</f>
         <v>10</v>
       </c>
-      <c r="G13" s="248">
+      <c r="G13" s="246">
         <f>Review!D7</f>
         <v>10</v>
       </c>
-      <c r="H13" s="249"/>
+      <c r="H13" s="247"/>
     </row>
     <row r="14" spans="1:8" s="49" customFormat="1" ht="40.15" customHeight="1">
       <c r="A14" s="15"/>
@@ -6447,11 +6663,11 @@
         <f>COUNTIF(Admin!J10:J29, "Pending")</f>
         <v>0</v>
       </c>
-      <c r="G14" s="246">
+      <c r="G14" s="244">
         <f>Admin!D7</f>
         <v>14</v>
       </c>
-      <c r="H14" s="247"/>
+      <c r="H14" s="245"/>
     </row>
     <row r="15" spans="1:8" ht="40.15" customHeight="1">
       <c r="A15" s="5"/>
@@ -6473,11 +6689,11 @@
         <f>COUNTIF(Venue!J10:J29, "Pending")</f>
         <v>6</v>
       </c>
-      <c r="G15" s="248">
+      <c r="G15" s="246">
         <f>Venue!D7</f>
         <v>6</v>
       </c>
-      <c r="H15" s="249"/>
+      <c r="H15" s="247"/>
     </row>
     <row r="16" spans="1:8" ht="40.15" customHeight="1">
       <c r="A16" s="5"/>
@@ -6497,11 +6713,11 @@
         <f>SUM(F8:F15)</f>
         <v>59</v>
       </c>
-      <c r="G16" s="250">
+      <c r="G16" s="253">
         <f>SUM(G8:H15)</f>
         <v>116</v>
       </c>
-      <c r="H16" s="251"/>
+      <c r="H16" s="254"/>
     </row>
     <row r="17" spans="1:9" ht="14.25">
       <c r="A17" s="5"/>
@@ -6650,8 +6866,8 @@
       <c r="I29" s="14"/>
     </row>
     <row r="30" spans="1:9" ht="14.25">
-      <c r="A30" s="15"/>
-      <c r="B30" s="242" t="s">
+      <c r="A30" s="5"/>
+      <c r="B30" s="249" t="s">
         <v>44</v>
       </c>
       <c r="C30" s="16" t="s">
@@ -6672,11 +6888,11 @@
       <c r="H30" s="21" t="s">
         <v>572</v>
       </c>
-      <c r="I30" s="245"/>
-    </row>
-    <row r="31" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A31" s="15"/>
-      <c r="B31" s="243"/>
+      <c r="I30" s="252"/>
+    </row>
+    <row r="31" spans="1:9" ht="14.25">
+      <c r="A31" s="5"/>
+      <c r="B31" s="250"/>
       <c r="C31" s="16" t="s">
         <v>573</v>
       </c>
@@ -6695,11 +6911,11 @@
       <c r="H31" s="26" t="s">
         <v>575</v>
       </c>
-      <c r="I31" s="245"/>
-    </row>
-    <row r="32" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A32" s="15"/>
-      <c r="B32" s="243"/>
+      <c r="I31" s="252"/>
+    </row>
+    <row r="32" spans="1:9" ht="17.25" customHeight="1">
+      <c r="A32" s="5"/>
+      <c r="B32" s="250"/>
       <c r="C32" s="16" t="s">
         <v>576</v>
       </c>
@@ -6713,16 +6929,16 @@
         <v>0.79</v>
       </c>
       <c r="G32" s="29" t="s">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="H32" s="30" t="s">
         <v>577</v>
       </c>
-      <c r="I32" s="245"/>
-    </row>
-    <row r="33" spans="1:9" ht="12.75" customHeight="1">
-      <c r="A33" s="15"/>
-      <c r="B33" s="243"/>
+      <c r="I32" s="252"/>
+    </row>
+    <row r="33" spans="1:9" ht="17.25" customHeight="1">
+      <c r="A33" s="5"/>
+      <c r="B33" s="250"/>
       <c r="C33" s="16" t="s">
         <v>578</v>
       </c>
@@ -6733,83 +6949,202 @@
         <v>123</v>
       </c>
       <c r="F33" s="32">
+        <v>0.77</v>
+      </c>
+      <c r="G33" s="170" t="s">
+        <v>585</v>
+      </c>
+      <c r="H33" s="33" t="s">
+        <v>586</v>
+      </c>
+      <c r="I33" s="252"/>
+    </row>
+    <row r="34" spans="1:9" ht="16.5" customHeight="1">
+      <c r="A34" s="5"/>
+      <c r="B34" s="262"/>
+      <c r="C34" s="263" t="s">
+        <v>579</v>
+      </c>
+      <c r="D34" s="264">
+        <v>167</v>
+      </c>
+      <c r="E34" s="265">
+        <v>5</v>
+      </c>
+      <c r="F34" s="266">
+        <v>0.97</v>
+      </c>
+      <c r="G34" s="267" t="s">
+        <v>580</v>
+      </c>
+      <c r="H34" s="268" t="s">
+        <v>581</v>
+      </c>
+      <c r="I34" s="269"/>
+    </row>
+    <row r="35" spans="1:9" ht="16.5" customHeight="1">
+      <c r="A35" s="15"/>
+      <c r="B35" s="255" t="s">
+        <v>588</v>
+      </c>
+      <c r="C35" s="256" t="s">
+        <v>571</v>
+      </c>
+      <c r="D35" s="257">
+        <v>12</v>
+      </c>
+      <c r="E35" s="258">
+        <v>0</v>
+      </c>
+      <c r="F35" s="259">
+        <v>1</v>
+      </c>
+      <c r="G35" s="260" t="s">
+        <v>572</v>
+      </c>
+      <c r="H35" s="261" t="s">
+        <v>572</v>
+      </c>
+      <c r="I35" s="252"/>
+    </row>
+    <row r="36" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A36" s="15"/>
+      <c r="B36" s="250"/>
+      <c r="C36" s="16" t="s">
+        <v>573</v>
+      </c>
+      <c r="D36" s="22">
+        <v>92</v>
+      </c>
+      <c r="E36" s="23">
+        <v>4</v>
+      </c>
+      <c r="F36" s="24">
+        <v>0.96</v>
+      </c>
+      <c r="G36" s="25" t="s">
+        <v>574</v>
+      </c>
+      <c r="H36" s="26" t="s">
+        <v>575</v>
+      </c>
+      <c r="I36" s="252"/>
+    </row>
+    <row r="37" spans="1:9" ht="17.25" customHeight="1">
+      <c r="A37" s="15"/>
+      <c r="B37" s="250"/>
+      <c r="C37" s="16" t="s">
+        <v>576</v>
+      </c>
+      <c r="D37" s="22">
+        <v>137</v>
+      </c>
+      <c r="E37" s="27">
+        <v>29</v>
+      </c>
+      <c r="F37" s="28">
+        <v>0.79</v>
+      </c>
+      <c r="G37" s="29" t="s">
+        <v>582</v>
+      </c>
+      <c r="H37" s="30" t="s">
+        <v>577</v>
+      </c>
+      <c r="I37" s="252"/>
+    </row>
+    <row r="38" spans="1:9" ht="12.75" customHeight="1">
+      <c r="A38" s="15"/>
+      <c r="B38" s="250"/>
+      <c r="C38" s="16" t="s">
+        <v>578</v>
+      </c>
+      <c r="D38" s="22">
+        <v>541</v>
+      </c>
+      <c r="E38" s="31">
+        <v>123</v>
+      </c>
+      <c r="F38" s="32">
         <v>0.83</v>
       </c>
-      <c r="G33" s="170" t="s">
+      <c r="G38" s="170" t="s">
         <v>583</v>
       </c>
-      <c r="H33" s="33" t="s">
+      <c r="H38" s="33" t="s">
         <v>584</v>
       </c>
-      <c r="I33" s="245"/>
-    </row>
-    <row r="34" spans="1:9" ht="11.25" customHeight="1">
-      <c r="A34" s="15"/>
-      <c r="B34" s="244"/>
-      <c r="C34" s="16" t="s">
+      <c r="I38" s="252"/>
+    </row>
+    <row r="39" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A39" s="15"/>
+      <c r="B39" s="251"/>
+      <c r="C39" s="16" t="s">
         <v>579</v>
       </c>
-      <c r="D34" s="22">
+      <c r="D39" s="22">
         <v>167</v>
       </c>
-      <c r="E34" s="34">
+      <c r="E39" s="34">
         <v>5</v>
       </c>
-      <c r="F34" s="35">
+      <c r="F39" s="35">
         <v>0.97</v>
       </c>
-      <c r="G34" s="36" t="s">
+      <c r="G39" s="36" t="s">
         <v>580</v>
       </c>
-      <c r="H34" s="37" t="s">
+      <c r="H39" s="37" t="s">
         <v>581</v>
       </c>
-      <c r="I34" s="245"/>
-    </row>
-    <row r="35" spans="1:9" ht="14.25">
-      <c r="A35" s="5"/>
-      <c r="B35" s="38"/>
-      <c r="C35" s="39" t="s">
+      <c r="I39" s="252"/>
+    </row>
+    <row r="40" spans="1:9" ht="14.25">
+      <c r="A40" s="5"/>
+      <c r="B40" s="38"/>
+      <c r="C40" s="39" t="s">
         <v>559</v>
       </c>
-      <c r="D35" s="40">
-        <f>SUM(D28:D34)</f>
-        <v>949</v>
-      </c>
-      <c r="E35" s="41">
-        <f>SUM(E28:E34)</f>
-        <v>161</v>
-      </c>
-      <c r="F35" s="40"/>
-      <c r="G35" s="42"/>
-      <c r="H35" s="43"/>
-      <c r="I35" s="44"/>
-    </row>
-    <row r="36" spans="1:9" ht="14.25">
-      <c r="A36" s="5"/>
-      <c r="B36" s="45"/>
-      <c r="C36" s="5"/>
-      <c r="D36" s="46"/>
-      <c r="E36" s="47"/>
-      <c r="F36" s="47"/>
-      <c r="G36" s="47"/>
-      <c r="H36" s="47"/>
-      <c r="I36" s="47"/>
+      <c r="D40" s="40">
+        <f>SUM(D28:D39)</f>
+        <v>1898</v>
+      </c>
+      <c r="E40" s="41">
+        <f>SUM(E28:E39)</f>
+        <v>322</v>
+      </c>
+      <c r="F40" s="40"/>
+      <c r="G40" s="42"/>
+      <c r="H40" s="43"/>
+      <c r="I40" s="44"/>
+    </row>
+    <row r="41" spans="1:9" ht="14.25">
+      <c r="A41" s="5"/>
+      <c r="B41" s="45"/>
+      <c r="C41" s="5"/>
+      <c r="D41" s="46"/>
+      <c r="E41" s="47"/>
+      <c r="F41" s="47"/>
+      <c r="G41" s="47"/>
+      <c r="H41" s="47"/>
+      <c r="I41" s="47"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="14">
+    <mergeCell ref="B35:B39"/>
+    <mergeCell ref="I35:I39"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="B30:B34"/>
+    <mergeCell ref="I30:I34"/>
     <mergeCell ref="G7:H7"/>
     <mergeCell ref="G8:H8"/>
     <mergeCell ref="G9:H9"/>
     <mergeCell ref="G10:H10"/>
     <mergeCell ref="G11:H11"/>
-    <mergeCell ref="B30:B34"/>
-    <mergeCell ref="I30:I34"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="G16:H16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
@@ -6864,52 +7199,52 @@
       <c r="A3" s="70" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="209" t="s">
+      <c r="B3" s="171" t="s">
         <v>62</v>
       </c>
-      <c r="C3" s="209"/>
-      <c r="D3" s="210"/>
+      <c r="C3" s="171"/>
+      <c r="D3" s="172"/>
       <c r="E3" s="71"/>
       <c r="F3" s="71"/>
       <c r="G3" s="71"/>
       <c r="H3" s="71"/>
-      <c r="I3" s="193"/>
-      <c r="J3" s="193"/>
-      <c r="K3" s="193"/>
+      <c r="I3" s="173"/>
+      <c r="J3" s="173"/>
+      <c r="K3" s="173"/>
     </row>
     <row r="4" spans="1:11" ht="14.25">
       <c r="A4" s="74" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="211" t="s">
+      <c r="B4" s="174" t="s">
         <v>64</v>
       </c>
-      <c r="C4" s="212"/>
-      <c r="D4" s="213"/>
+      <c r="C4" s="175"/>
+      <c r="D4" s="176"/>
       <c r="E4" s="71"/>
       <c r="F4" s="71"/>
       <c r="G4" s="71"/>
       <c r="H4" s="71"/>
-      <c r="I4" s="193"/>
-      <c r="J4" s="193"/>
-      <c r="K4" s="193"/>
+      <c r="I4" s="173"/>
+      <c r="J4" s="173"/>
+      <c r="K4" s="173"/>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="74" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="214" t="s">
+      <c r="B5" s="177" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="215"/>
-      <c r="D5" s="216"/>
+      <c r="C5" s="178"/>
+      <c r="D5" s="179"/>
       <c r="E5" s="75"/>
       <c r="F5" s="75"/>
       <c r="G5" s="75"/>
       <c r="H5" s="75"/>
-      <c r="I5" s="217"/>
-      <c r="J5" s="217"/>
-      <c r="K5" s="217"/>
+      <c r="I5" s="180"/>
+      <c r="J5" s="180"/>
+      <c r="K5" s="180"/>
     </row>
     <row r="6" spans="1:11" ht="14.25">
       <c r="A6" s="77" t="s">
@@ -6928,9 +7263,9 @@
       <c r="F6" s="72"/>
       <c r="G6" s="72"/>
       <c r="H6" s="72"/>
-      <c r="I6" s="193"/>
-      <c r="J6" s="193"/>
-      <c r="K6" s="193"/>
+      <c r="I6" s="173"/>
+      <c r="J6" s="173"/>
+      <c r="K6" s="173"/>
     </row>
     <row r="7" spans="1:11" ht="14.25">
       <c r="A7" s="81" t="s">
@@ -6950,15 +7285,15 @@
       <c r="F7" s="85"/>
       <c r="G7" s="85"/>
       <c r="H7" s="85"/>
-      <c r="I7" s="193"/>
-      <c r="J7" s="193"/>
-      <c r="K7" s="193"/>
+      <c r="I7" s="173"/>
+      <c r="J7" s="173"/>
+      <c r="K7" s="173"/>
     </row>
     <row r="8" spans="1:11" ht="14.25">
-      <c r="A8" s="194"/>
-      <c r="B8" s="194"/>
-      <c r="C8" s="194"/>
-      <c r="D8" s="194"/>
+      <c r="A8" s="181"/>
+      <c r="B8" s="181"/>
+      <c r="C8" s="181"/>
+      <c r="D8" s="181"/>
       <c r="E8" s="72"/>
       <c r="F8" s="72"/>
       <c r="G8" s="72"/>
@@ -6968,59 +7303,59 @@
       <c r="K8" s="86"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="197" t="s">
+      <c r="A9" s="187" t="s">
         <v>71</v>
       </c>
-      <c r="B9" s="199" t="s">
+      <c r="B9" s="189" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="197" t="s">
+      <c r="C9" s="187" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="203" t="s">
+      <c r="D9" s="193" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="204"/>
-      <c r="F9" s="204"/>
-      <c r="G9" s="205"/>
-      <c r="H9" s="201" t="s">
+      <c r="E9" s="194"/>
+      <c r="F9" s="194"/>
+      <c r="G9" s="195"/>
+      <c r="H9" s="191" t="s">
         <v>75</v>
       </c>
-      <c r="I9" s="202" t="s">
+      <c r="I9" s="192" t="s">
         <v>76</v>
       </c>
-      <c r="J9" s="202" t="s">
+      <c r="J9" s="192" t="s">
         <v>77</v>
       </c>
-      <c r="K9" s="202" t="s">
+      <c r="K9" s="192" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="198"/>
-      <c r="B10" s="200"/>
-      <c r="C10" s="198"/>
-      <c r="D10" s="206"/>
-      <c r="E10" s="207"/>
-      <c r="F10" s="207"/>
-      <c r="G10" s="208"/>
-      <c r="H10" s="197"/>
-      <c r="I10" s="197"/>
-      <c r="J10" s="197"/>
-      <c r="K10" s="197"/>
+      <c r="A10" s="188"/>
+      <c r="B10" s="190"/>
+      <c r="C10" s="188"/>
+      <c r="D10" s="196"/>
+      <c r="E10" s="197"/>
+      <c r="F10" s="197"/>
+      <c r="G10" s="198"/>
+      <c r="H10" s="187"/>
+      <c r="I10" s="187"/>
+      <c r="J10" s="187"/>
+      <c r="K10" s="187"/>
     </row>
     <row r="11" spans="1:11" ht="15">
-      <c r="A11" s="195"/>
-      <c r="B11" s="195"/>
-      <c r="C11" s="195"/>
-      <c r="D11" s="195"/>
-      <c r="E11" s="195"/>
-      <c r="F11" s="195"/>
-      <c r="G11" s="195"/>
-      <c r="H11" s="195"/>
-      <c r="I11" s="195"/>
-      <c r="J11" s="195"/>
-      <c r="K11" s="196"/>
+      <c r="A11" s="182"/>
+      <c r="B11" s="182"/>
+      <c r="C11" s="182"/>
+      <c r="D11" s="182"/>
+      <c r="E11" s="182"/>
+      <c r="F11" s="182"/>
+      <c r="G11" s="182"/>
+      <c r="H11" s="182"/>
+      <c r="I11" s="182"/>
+      <c r="J11" s="182"/>
+      <c r="K11" s="183"/>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="184" t="s">
@@ -7047,12 +7382,12 @@
       <c r="C13" s="92" t="s">
         <v>82</v>
       </c>
-      <c r="D13" s="187" t="s">
+      <c r="D13" s="199" t="s">
         <v>83</v>
       </c>
-      <c r="E13" s="176"/>
-      <c r="F13" s="176"/>
-      <c r="G13" s="177"/>
+      <c r="E13" s="200"/>
+      <c r="F13" s="200"/>
+      <c r="G13" s="201"/>
       <c r="H13" s="94"/>
       <c r="I13" s="96"/>
       <c r="J13" s="92" t="s">
@@ -7085,12 +7420,12 @@
       <c r="C15" s="102" t="s">
         <v>87</v>
       </c>
-      <c r="D15" s="188" t="s">
+      <c r="D15" s="202" t="s">
         <v>88</v>
       </c>
-      <c r="E15" s="189"/>
-      <c r="F15" s="189"/>
-      <c r="G15" s="190"/>
+      <c r="E15" s="203"/>
+      <c r="F15" s="203"/>
+      <c r="G15" s="204"/>
       <c r="H15" s="103"/>
       <c r="I15" s="103"/>
       <c r="J15" s="104" t="s">
@@ -7123,12 +7458,12 @@
       <c r="C17" s="98" t="s">
         <v>92</v>
       </c>
-      <c r="D17" s="187" t="s">
+      <c r="D17" s="199" t="s">
         <v>93</v>
       </c>
-      <c r="E17" s="191"/>
-      <c r="F17" s="191"/>
-      <c r="G17" s="192"/>
+      <c r="E17" s="205"/>
+      <c r="F17" s="205"/>
+      <c r="G17" s="206"/>
       <c r="H17" s="94"/>
       <c r="I17" s="93"/>
       <c r="J17" s="92" t="s">
@@ -7161,12 +7496,12 @@
       <c r="C19" s="92" t="s">
         <v>97</v>
       </c>
-      <c r="D19" s="175" t="s">
+      <c r="D19" s="207" t="s">
         <v>98</v>
       </c>
-      <c r="E19" s="176"/>
-      <c r="F19" s="176"/>
-      <c r="G19" s="177"/>
+      <c r="E19" s="200"/>
+      <c r="F19" s="200"/>
+      <c r="G19" s="201"/>
       <c r="H19" s="94"/>
       <c r="I19" s="93"/>
       <c r="J19" s="92" t="s">
@@ -7199,12 +7534,12 @@
       <c r="C21" s="92" t="s">
         <v>102</v>
       </c>
-      <c r="D21" s="175" t="s">
+      <c r="D21" s="207" t="s">
         <v>103</v>
       </c>
-      <c r="E21" s="176"/>
-      <c r="F21" s="176"/>
-      <c r="G21" s="177"/>
+      <c r="E21" s="200"/>
+      <c r="F21" s="200"/>
+      <c r="G21" s="201"/>
       <c r="H21" s="94"/>
       <c r="I21" s="93"/>
       <c r="J21" s="92" t="s">
@@ -7222,12 +7557,12 @@
       <c r="C22" s="92" t="s">
         <v>106</v>
       </c>
-      <c r="D22" s="175" t="s">
+      <c r="D22" s="207" t="s">
         <v>107</v>
       </c>
-      <c r="E22" s="176"/>
-      <c r="F22" s="176"/>
-      <c r="G22" s="177"/>
+      <c r="E22" s="200"/>
+      <c r="F22" s="200"/>
+      <c r="G22" s="201"/>
       <c r="H22" s="92"/>
       <c r="I22" s="92"/>
       <c r="J22" s="92" t="s">
@@ -7260,12 +7595,12 @@
       <c r="C24" s="92" t="s">
         <v>111</v>
       </c>
-      <c r="D24" s="175" t="s">
+      <c r="D24" s="207" t="s">
         <v>112</v>
       </c>
-      <c r="E24" s="176"/>
-      <c r="F24" s="176"/>
-      <c r="G24" s="177"/>
+      <c r="E24" s="200"/>
+      <c r="F24" s="200"/>
+      <c r="G24" s="201"/>
       <c r="H24" s="92"/>
       <c r="I24" s="92"/>
       <c r="J24" s="92" t="s">
@@ -7283,12 +7618,12 @@
       <c r="C25" s="92" t="s">
         <v>115</v>
       </c>
-      <c r="D25" s="175" t="s">
+      <c r="D25" s="207" t="s">
         <v>116</v>
       </c>
-      <c r="E25" s="176"/>
-      <c r="F25" s="176"/>
-      <c r="G25" s="177"/>
+      <c r="E25" s="200"/>
+      <c r="F25" s="200"/>
+      <c r="G25" s="201"/>
       <c r="H25" s="92"/>
       <c r="I25" s="92"/>
       <c r="J25" s="92" t="s">
@@ -7321,12 +7656,12 @@
       <c r="C27" s="92" t="s">
         <v>120</v>
       </c>
-      <c r="D27" s="175" t="s">
+      <c r="D27" s="207" t="s">
         <v>121</v>
       </c>
-      <c r="E27" s="176"/>
-      <c r="F27" s="176"/>
-      <c r="G27" s="177"/>
+      <c r="E27" s="200"/>
+      <c r="F27" s="200"/>
+      <c r="G27" s="201"/>
       <c r="H27" s="92"/>
       <c r="I27" s="92"/>
       <c r="J27" s="92" t="s">
@@ -7344,12 +7679,12 @@
       <c r="C28" s="92" t="s">
         <v>124</v>
       </c>
-      <c r="D28" s="175" t="s">
+      <c r="D28" s="207" t="s">
         <v>125</v>
       </c>
-      <c r="E28" s="176"/>
-      <c r="F28" s="176"/>
-      <c r="G28" s="177"/>
+      <c r="E28" s="200"/>
+      <c r="F28" s="200"/>
+      <c r="G28" s="201"/>
       <c r="H28" s="92"/>
       <c r="I28" s="92"/>
       <c r="J28" s="92" t="s">
@@ -7367,12 +7702,12 @@
       <c r="C29" s="92" t="s">
         <v>128</v>
       </c>
-      <c r="D29" s="175" t="s">
+      <c r="D29" s="207" t="s">
         <v>129</v>
       </c>
-      <c r="E29" s="176"/>
-      <c r="F29" s="176"/>
-      <c r="G29" s="177"/>
+      <c r="E29" s="200"/>
+      <c r="F29" s="200"/>
+      <c r="G29" s="201"/>
       <c r="H29" s="139"/>
       <c r="I29" s="139"/>
       <c r="J29" s="92" t="s">
@@ -7381,19 +7716,19 @@
       <c r="K29" s="139"/>
     </row>
     <row r="30" spans="1:11">
-      <c r="A30" s="178" t="s">
+      <c r="A30" s="208" t="s">
         <v>130</v>
       </c>
-      <c r="B30" s="179"/>
-      <c r="C30" s="179"/>
-      <c r="D30" s="179"/>
-      <c r="E30" s="179"/>
-      <c r="F30" s="179"/>
-      <c r="G30" s="179"/>
-      <c r="H30" s="179"/>
-      <c r="I30" s="179"/>
-      <c r="J30" s="179"/>
-      <c r="K30" s="180"/>
+      <c r="B30" s="209"/>
+      <c r="C30" s="209"/>
+      <c r="D30" s="209"/>
+      <c r="E30" s="209"/>
+      <c r="F30" s="209"/>
+      <c r="G30" s="209"/>
+      <c r="H30" s="209"/>
+      <c r="I30" s="209"/>
+      <c r="J30" s="209"/>
+      <c r="K30" s="210"/>
     </row>
     <row r="31" spans="1:11" ht="102">
       <c r="A31" s="90" t="s">
@@ -7405,12 +7740,12 @@
       <c r="C31" s="92" t="s">
         <v>132</v>
       </c>
-      <c r="D31" s="173" t="s">
+      <c r="D31" s="211" t="s">
         <v>133</v>
       </c>
-      <c r="E31" s="174"/>
-      <c r="F31" s="174"/>
-      <c r="G31" s="174"/>
+      <c r="E31" s="212"/>
+      <c r="F31" s="212"/>
+      <c r="G31" s="212"/>
       <c r="H31" s="92"/>
       <c r="I31" s="125"/>
       <c r="J31" s="92" t="s">
@@ -7428,12 +7763,12 @@
       <c r="C32" s="141" t="s">
         <v>135</v>
       </c>
-      <c r="D32" s="181" t="s">
+      <c r="D32" s="213" t="s">
         <v>136</v>
       </c>
-      <c r="E32" s="182"/>
-      <c r="F32" s="182"/>
-      <c r="G32" s="183"/>
+      <c r="E32" s="214"/>
+      <c r="F32" s="214"/>
+      <c r="G32" s="215"/>
       <c r="H32" s="141"/>
       <c r="I32" s="141"/>
       <c r="J32" s="140" t="s">
@@ -7451,12 +7786,12 @@
       <c r="C33" s="92" t="s">
         <v>138</v>
       </c>
-      <c r="D33" s="173" t="s">
+      <c r="D33" s="211" t="s">
         <v>139</v>
       </c>
-      <c r="E33" s="174"/>
-      <c r="F33" s="174"/>
-      <c r="G33" s="174"/>
+      <c r="E33" s="212"/>
+      <c r="F33" s="212"/>
+      <c r="G33" s="212"/>
       <c r="H33" s="92"/>
       <c r="I33" s="125"/>
       <c r="J33" s="92" t="s">
@@ -7474,12 +7809,12 @@
       <c r="C34" s="92" t="s">
         <v>141</v>
       </c>
-      <c r="D34" s="173" t="s">
+      <c r="D34" s="211" t="s">
         <v>142</v>
       </c>
-      <c r="E34" s="174"/>
-      <c r="F34" s="174"/>
-      <c r="G34" s="174"/>
+      <c r="E34" s="212"/>
+      <c r="F34" s="212"/>
+      <c r="G34" s="212"/>
       <c r="H34" s="92"/>
       <c r="I34" s="125"/>
       <c r="J34" s="92" t="s">
@@ -7497,12 +7832,12 @@
       <c r="C35" s="92" t="s">
         <v>144</v>
       </c>
-      <c r="D35" s="173" t="s">
+      <c r="D35" s="211" t="s">
         <v>145</v>
       </c>
-      <c r="E35" s="174"/>
-      <c r="F35" s="174"/>
-      <c r="G35" s="174"/>
+      <c r="E35" s="212"/>
+      <c r="F35" s="212"/>
+      <c r="G35" s="212"/>
       <c r="H35" s="92"/>
       <c r="I35" s="125"/>
       <c r="J35" s="92" t="s">
@@ -7520,12 +7855,12 @@
       <c r="C36" s="92" t="s">
         <v>147</v>
       </c>
-      <c r="D36" s="173" t="s">
+      <c r="D36" s="211" t="s">
         <v>148</v>
       </c>
-      <c r="E36" s="174"/>
-      <c r="F36" s="174"/>
-      <c r="G36" s="174"/>
+      <c r="E36" s="212"/>
+      <c r="F36" s="212"/>
+      <c r="G36" s="212"/>
       <c r="H36" s="92"/>
       <c r="I36" s="125"/>
       <c r="J36" s="92" t="s">
@@ -7543,12 +7878,12 @@
       <c r="C37" s="98" t="s">
         <v>150</v>
       </c>
-      <c r="D37" s="171" t="s">
+      <c r="D37" s="216" t="s">
         <v>151</v>
       </c>
-      <c r="E37" s="172"/>
-      <c r="F37" s="172"/>
-      <c r="G37" s="172"/>
+      <c r="E37" s="217"/>
+      <c r="F37" s="217"/>
+      <c r="G37" s="217"/>
       <c r="H37" s="98"/>
       <c r="I37" s="142"/>
       <c r="J37" s="98" t="s">
@@ -7566,12 +7901,12 @@
       <c r="C38" s="98" t="s">
         <v>153</v>
       </c>
-      <c r="D38" s="171" t="s">
+      <c r="D38" s="216" t="s">
         <v>154</v>
       </c>
-      <c r="E38" s="172"/>
-      <c r="F38" s="172"/>
-      <c r="G38" s="172"/>
+      <c r="E38" s="217"/>
+      <c r="F38" s="217"/>
+      <c r="G38" s="217"/>
       <c r="H38" s="98"/>
       <c r="I38" s="142"/>
       <c r="J38" s="98" t="s">
@@ -7589,12 +7924,12 @@
       <c r="C39" s="92" t="s">
         <v>156</v>
       </c>
-      <c r="D39" s="173" t="s">
+      <c r="D39" s="211" t="s">
         <v>157</v>
       </c>
-      <c r="E39" s="174"/>
-      <c r="F39" s="174"/>
-      <c r="G39" s="174"/>
+      <c r="E39" s="212"/>
+      <c r="F39" s="212"/>
+      <c r="G39" s="212"/>
       <c r="H39" s="92"/>
       <c r="I39" s="125"/>
       <c r="J39" s="92" t="s">
@@ -7612,12 +7947,12 @@
       <c r="C40" s="92" t="s">
         <v>159</v>
       </c>
-      <c r="D40" s="173" t="s">
+      <c r="D40" s="211" t="s">
         <v>160</v>
       </c>
-      <c r="E40" s="174"/>
-      <c r="F40" s="174"/>
-      <c r="G40" s="174"/>
+      <c r="E40" s="212"/>
+      <c r="F40" s="212"/>
+      <c r="G40" s="212"/>
       <c r="H40" s="92"/>
       <c r="I40" s="125"/>
       <c r="J40" s="92" t="s">
@@ -7635,12 +7970,12 @@
       <c r="C41" s="92" t="s">
         <v>159</v>
       </c>
-      <c r="D41" s="173" t="s">
+      <c r="D41" s="211" t="s">
         <v>160</v>
       </c>
-      <c r="E41" s="174"/>
-      <c r="F41" s="174"/>
-      <c r="G41" s="174"/>
+      <c r="E41" s="212"/>
+      <c r="F41" s="212"/>
+      <c r="G41" s="212"/>
       <c r="H41" s="92"/>
       <c r="I41" s="125"/>
       <c r="J41" s="92" t="s">
@@ -7658,12 +7993,12 @@
       <c r="C42" s="92" t="s">
         <v>163</v>
       </c>
-      <c r="D42" s="173" t="s">
+      <c r="D42" s="211" t="s">
         <v>164</v>
       </c>
-      <c r="E42" s="174"/>
-      <c r="F42" s="174"/>
-      <c r="G42" s="174"/>
+      <c r="E42" s="212"/>
+      <c r="F42" s="212"/>
+      <c r="G42" s="212"/>
       <c r="H42" s="92"/>
       <c r="I42" s="125"/>
       <c r="J42" s="92" t="s">
@@ -7673,12 +8008,36 @@
     </row>
   </sheetData>
   <mergeCells count="49">
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="D38:G38"/>
+    <mergeCell ref="D39:G39"/>
+    <mergeCell ref="D40:G40"/>
+    <mergeCell ref="D41:G41"/>
+    <mergeCell ref="D42:G42"/>
+    <mergeCell ref="D33:G33"/>
+    <mergeCell ref="D34:G34"/>
+    <mergeCell ref="D35:G35"/>
+    <mergeCell ref="D36:G36"/>
+    <mergeCell ref="D37:G37"/>
+    <mergeCell ref="D28:G28"/>
+    <mergeCell ref="D29:G29"/>
+    <mergeCell ref="A30:K30"/>
+    <mergeCell ref="D31:G31"/>
+    <mergeCell ref="D32:G32"/>
+    <mergeCell ref="A23:K23"/>
+    <mergeCell ref="D24:G24"/>
+    <mergeCell ref="D25:G25"/>
+    <mergeCell ref="A26:K26"/>
+    <mergeCell ref="D27:G27"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="D19:G19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="D21:G21"/>
+    <mergeCell ref="D22:G22"/>
+    <mergeCell ref="D13:G13"/>
+    <mergeCell ref="A14:K14"/>
+    <mergeCell ref="D15:G15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="D17:G17"/>
     <mergeCell ref="I6:K6"/>
     <mergeCell ref="I7:K7"/>
     <mergeCell ref="A8:D8"/>
@@ -7692,36 +8051,12 @@
     <mergeCell ref="J9:J10"/>
     <mergeCell ref="K9:K10"/>
     <mergeCell ref="D9:G10"/>
-    <mergeCell ref="D13:G13"/>
-    <mergeCell ref="A14:K14"/>
-    <mergeCell ref="D15:G15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="D17:G17"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="D19:G19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="D21:G21"/>
-    <mergeCell ref="D22:G22"/>
-    <mergeCell ref="A23:K23"/>
-    <mergeCell ref="D24:G24"/>
-    <mergeCell ref="D25:G25"/>
-    <mergeCell ref="A26:K26"/>
-    <mergeCell ref="D27:G27"/>
-    <mergeCell ref="D28:G28"/>
-    <mergeCell ref="D29:G29"/>
-    <mergeCell ref="A30:K30"/>
-    <mergeCell ref="D31:G31"/>
-    <mergeCell ref="D32:G32"/>
-    <mergeCell ref="D33:G33"/>
-    <mergeCell ref="D34:G34"/>
-    <mergeCell ref="D35:G35"/>
-    <mergeCell ref="D36:G36"/>
-    <mergeCell ref="D37:G37"/>
-    <mergeCell ref="D38:G38"/>
-    <mergeCell ref="D39:G39"/>
-    <mergeCell ref="D40:G40"/>
-    <mergeCell ref="D41:G41"/>
-    <mergeCell ref="D42:G42"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="I5:K5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7757,31 +8092,31 @@
       <c r="A3" s="70" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="209" t="s">
+      <c r="B3" s="171" t="s">
         <v>62</v>
       </c>
-      <c r="C3" s="209"/>
-      <c r="D3" s="210"/>
+      <c r="C3" s="171"/>
+      <c r="D3" s="172"/>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="74" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="211" t="s">
+      <c r="B4" s="174" t="s">
         <v>166</v>
       </c>
-      <c r="C4" s="212"/>
-      <c r="D4" s="213"/>
+      <c r="C4" s="175"/>
+      <c r="D4" s="176"/>
     </row>
     <row r="5" spans="1:11" ht="25.5">
       <c r="A5" s="74" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="214" t="s">
+      <c r="B5" s="177" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="215"/>
-      <c r="D5" s="216"/>
+      <c r="C5" s="178"/>
+      <c r="D5" s="179"/>
     </row>
     <row r="6" spans="1:11" ht="14.25">
       <c r="A6" s="77" t="s">
@@ -7812,59 +8147,59 @@
       </c>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="197" t="s">
+      <c r="A9" s="187" t="s">
         <v>71</v>
       </c>
-      <c r="B9" s="199" t="s">
+      <c r="B9" s="189" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="197" t="s">
+      <c r="C9" s="187" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="203" t="s">
+      <c r="D9" s="193" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="204"/>
-      <c r="F9" s="204"/>
-      <c r="G9" s="205"/>
-      <c r="H9" s="201" t="s">
+      <c r="E9" s="194"/>
+      <c r="F9" s="194"/>
+      <c r="G9" s="195"/>
+      <c r="H9" s="191" t="s">
         <v>75</v>
       </c>
-      <c r="I9" s="202" t="s">
+      <c r="I9" s="192" t="s">
         <v>76</v>
       </c>
-      <c r="J9" s="202" t="s">
+      <c r="J9" s="192" t="s">
         <v>77</v>
       </c>
-      <c r="K9" s="202" t="s">
+      <c r="K9" s="192" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="198"/>
-      <c r="B10" s="200"/>
-      <c r="C10" s="198"/>
-      <c r="D10" s="206"/>
-      <c r="E10" s="207"/>
-      <c r="F10" s="207"/>
-      <c r="G10" s="208"/>
-      <c r="H10" s="197"/>
-      <c r="I10" s="197"/>
-      <c r="J10" s="197"/>
-      <c r="K10" s="197"/>
+      <c r="A10" s="188"/>
+      <c r="B10" s="190"/>
+      <c r="C10" s="188"/>
+      <c r="D10" s="196"/>
+      <c r="E10" s="197"/>
+      <c r="F10" s="197"/>
+      <c r="G10" s="198"/>
+      <c r="H10" s="187"/>
+      <c r="I10" s="187"/>
+      <c r="J10" s="187"/>
+      <c r="K10" s="187"/>
     </row>
     <row r="11" spans="1:11" ht="15">
-      <c r="A11" s="195"/>
-      <c r="B11" s="195"/>
-      <c r="C11" s="195"/>
-      <c r="D11" s="195"/>
-      <c r="E11" s="195"/>
-      <c r="F11" s="195"/>
-      <c r="G11" s="195"/>
-      <c r="H11" s="195"/>
-      <c r="I11" s="195"/>
-      <c r="J11" s="195"/>
-      <c r="K11" s="196"/>
+      <c r="A11" s="182"/>
+      <c r="B11" s="182"/>
+      <c r="C11" s="182"/>
+      <c r="D11" s="182"/>
+      <c r="E11" s="182"/>
+      <c r="F11" s="182"/>
+      <c r="G11" s="182"/>
+      <c r="H11" s="182"/>
+      <c r="I11" s="182"/>
+      <c r="J11" s="182"/>
+      <c r="K11" s="183"/>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="184" t="s">
@@ -7891,12 +8226,12 @@
       <c r="C13" s="92" t="s">
         <v>169</v>
       </c>
-      <c r="D13" s="187" t="s">
+      <c r="D13" s="199" t="s">
         <v>170</v>
       </c>
-      <c r="E13" s="176"/>
-      <c r="F13" s="176"/>
-      <c r="G13" s="177"/>
+      <c r="E13" s="200"/>
+      <c r="F13" s="200"/>
+      <c r="G13" s="201"/>
       <c r="H13" s="94"/>
       <c r="I13" s="96"/>
       <c r="J13" s="92" t="s">
@@ -7914,12 +8249,12 @@
       <c r="C14" s="92" t="s">
         <v>172</v>
       </c>
-      <c r="D14" s="187" t="s">
+      <c r="D14" s="199" t="s">
         <v>173</v>
       </c>
-      <c r="E14" s="176"/>
-      <c r="F14" s="176"/>
-      <c r="G14" s="177"/>
+      <c r="E14" s="200"/>
+      <c r="F14" s="200"/>
+      <c r="G14" s="201"/>
       <c r="H14" s="94"/>
       <c r="I14" s="96"/>
       <c r="J14" s="92" t="s">
@@ -7937,12 +8272,12 @@
       <c r="C15" s="92" t="s">
         <v>175</v>
       </c>
-      <c r="D15" s="187" t="s">
+      <c r="D15" s="199" t="s">
         <v>176</v>
       </c>
-      <c r="E15" s="176"/>
-      <c r="F15" s="176"/>
-      <c r="G15" s="177"/>
+      <c r="E15" s="200"/>
+      <c r="F15" s="200"/>
+      <c r="G15" s="201"/>
       <c r="H15" s="94"/>
       <c r="I15" s="96"/>
       <c r="J15" s="92" t="s">
@@ -7960,12 +8295,12 @@
       <c r="C16" s="92" t="s">
         <v>178</v>
       </c>
-      <c r="D16" s="187" t="s">
+      <c r="D16" s="199" t="s">
         <v>179</v>
       </c>
-      <c r="E16" s="176"/>
-      <c r="F16" s="176"/>
-      <c r="G16" s="177"/>
+      <c r="E16" s="200"/>
+      <c r="F16" s="200"/>
+      <c r="G16" s="201"/>
       <c r="H16" s="94"/>
       <c r="I16" s="96"/>
       <c r="J16" s="92" t="s">
@@ -7983,12 +8318,12 @@
       <c r="C17" s="92" t="s">
         <v>181</v>
       </c>
-      <c r="D17" s="187" t="s">
+      <c r="D17" s="199" t="s">
         <v>182</v>
       </c>
-      <c r="E17" s="176"/>
-      <c r="F17" s="176"/>
-      <c r="G17" s="177"/>
+      <c r="E17" s="200"/>
+      <c r="F17" s="200"/>
+      <c r="G17" s="201"/>
       <c r="H17" s="94"/>
       <c r="I17" s="96"/>
       <c r="J17" s="92" t="s">
@@ -8006,12 +8341,12 @@
       <c r="C18" s="92" t="s">
         <v>184</v>
       </c>
-      <c r="D18" s="187" t="s">
+      <c r="D18" s="199" t="s">
         <v>185</v>
       </c>
-      <c r="E18" s="176"/>
-      <c r="F18" s="176"/>
-      <c r="G18" s="177"/>
+      <c r="E18" s="200"/>
+      <c r="F18" s="200"/>
+      <c r="G18" s="201"/>
       <c r="H18" s="94"/>
       <c r="I18" s="96"/>
       <c r="J18" s="92" t="s">
@@ -8029,12 +8364,12 @@
       <c r="C19" s="92" t="s">
         <v>187</v>
       </c>
-      <c r="D19" s="187" t="s">
+      <c r="D19" s="199" t="s">
         <v>188</v>
       </c>
-      <c r="E19" s="176"/>
-      <c r="F19" s="176"/>
-      <c r="G19" s="177"/>
+      <c r="E19" s="200"/>
+      <c r="F19" s="200"/>
+      <c r="G19" s="201"/>
       <c r="H19" s="94"/>
       <c r="I19" s="96"/>
       <c r="J19" s="92" t="s">
@@ -8067,12 +8402,12 @@
       <c r="C21" s="92" t="s">
         <v>191</v>
       </c>
-      <c r="D21" s="187" t="s">
+      <c r="D21" s="199" t="s">
         <v>192</v>
       </c>
-      <c r="E21" s="176"/>
-      <c r="F21" s="176"/>
-      <c r="G21" s="177"/>
+      <c r="E21" s="200"/>
+      <c r="F21" s="200"/>
+      <c r="G21" s="201"/>
       <c r="H21" s="94"/>
       <c r="I21" s="96"/>
       <c r="J21" s="92" t="s">
@@ -8090,12 +8425,12 @@
       <c r="C22" s="92" t="s">
         <v>194</v>
       </c>
-      <c r="D22" s="187" t="s">
+      <c r="D22" s="199" t="s">
         <v>195</v>
       </c>
-      <c r="E22" s="176"/>
-      <c r="F22" s="176"/>
-      <c r="G22" s="177"/>
+      <c r="E22" s="200"/>
+      <c r="F22" s="200"/>
+      <c r="G22" s="201"/>
       <c r="H22" s="94"/>
       <c r="I22" s="96"/>
       <c r="J22" s="92" t="s">
@@ -8113,12 +8448,12 @@
       <c r="C23" s="92" t="s">
         <v>197</v>
       </c>
-      <c r="D23" s="187" t="s">
+      <c r="D23" s="199" t="s">
         <v>198</v>
       </c>
-      <c r="E23" s="176"/>
-      <c r="F23" s="176"/>
-      <c r="G23" s="177"/>
+      <c r="E23" s="200"/>
+      <c r="F23" s="200"/>
+      <c r="G23" s="201"/>
       <c r="H23" s="94"/>
       <c r="I23" s="96"/>
       <c r="J23" s="92" t="s">
@@ -8180,6 +8515,21 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="D23:G23"/>
+    <mergeCell ref="A24:K24"/>
+    <mergeCell ref="D25:G25"/>
+    <mergeCell ref="D26:G26"/>
+    <mergeCell ref="D27:G27"/>
+    <mergeCell ref="D18:G18"/>
+    <mergeCell ref="D19:G19"/>
+    <mergeCell ref="A20:K20"/>
+    <mergeCell ref="D21:G21"/>
+    <mergeCell ref="D22:G22"/>
+    <mergeCell ref="D13:G13"/>
+    <mergeCell ref="D14:G14"/>
+    <mergeCell ref="D15:G15"/>
+    <mergeCell ref="D16:G16"/>
+    <mergeCell ref="D17:G17"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B5:D5"/>
@@ -8193,21 +8543,6 @@
     <mergeCell ref="J9:J10"/>
     <mergeCell ref="K9:K10"/>
     <mergeCell ref="D9:G10"/>
-    <mergeCell ref="D13:G13"/>
-    <mergeCell ref="D14:G14"/>
-    <mergeCell ref="D15:G15"/>
-    <mergeCell ref="D16:G16"/>
-    <mergeCell ref="D17:G17"/>
-    <mergeCell ref="D18:G18"/>
-    <mergeCell ref="D19:G19"/>
-    <mergeCell ref="A20:K20"/>
-    <mergeCell ref="D21:G21"/>
-    <mergeCell ref="D22:G22"/>
-    <mergeCell ref="D23:G23"/>
-    <mergeCell ref="A24:K24"/>
-    <mergeCell ref="D25:G25"/>
-    <mergeCell ref="D26:G26"/>
-    <mergeCell ref="D27:G27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8244,31 +8579,31 @@
       <c r="A3" s="70" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="209" t="s">
+      <c r="B3" s="171" t="s">
         <v>62</v>
       </c>
-      <c r="C3" s="209"/>
-      <c r="D3" s="210"/>
+      <c r="C3" s="171"/>
+      <c r="D3" s="172"/>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="74" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="211" t="s">
+      <c r="B4" s="174" t="s">
         <v>200</v>
       </c>
-      <c r="C4" s="212"/>
-      <c r="D4" s="213"/>
+      <c r="C4" s="175"/>
+      <c r="D4" s="176"/>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="74" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="214" t="s">
+      <c r="B5" s="177" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="215"/>
-      <c r="D5" s="216"/>
+      <c r="C5" s="178"/>
+      <c r="D5" s="179"/>
     </row>
     <row r="6" spans="1:11" ht="14.25">
       <c r="A6" s="77" t="s">
@@ -8299,59 +8634,59 @@
       </c>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="197" t="s">
+      <c r="A9" s="187" t="s">
         <v>71</v>
       </c>
-      <c r="B9" s="199" t="s">
+      <c r="B9" s="189" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="197" t="s">
+      <c r="C9" s="187" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="203" t="s">
+      <c r="D9" s="193" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="204"/>
-      <c r="F9" s="204"/>
-      <c r="G9" s="205"/>
-      <c r="H9" s="201" t="s">
+      <c r="E9" s="194"/>
+      <c r="F9" s="194"/>
+      <c r="G9" s="195"/>
+      <c r="H9" s="191" t="s">
         <v>75</v>
       </c>
-      <c r="I9" s="202" t="s">
+      <c r="I9" s="192" t="s">
         <v>76</v>
       </c>
-      <c r="J9" s="202" t="s">
+      <c r="J9" s="192" t="s">
         <v>77</v>
       </c>
-      <c r="K9" s="202" t="s">
+      <c r="K9" s="192" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="198"/>
-      <c r="B10" s="200"/>
-      <c r="C10" s="198"/>
-      <c r="D10" s="206"/>
-      <c r="E10" s="207"/>
-      <c r="F10" s="207"/>
-      <c r="G10" s="208"/>
-      <c r="H10" s="197"/>
-      <c r="I10" s="197"/>
-      <c r="J10" s="197"/>
-      <c r="K10" s="197"/>
+      <c r="A10" s="188"/>
+      <c r="B10" s="190"/>
+      <c r="C10" s="188"/>
+      <c r="D10" s="196"/>
+      <c r="E10" s="197"/>
+      <c r="F10" s="197"/>
+      <c r="G10" s="198"/>
+      <c r="H10" s="187"/>
+      <c r="I10" s="187"/>
+      <c r="J10" s="187"/>
+      <c r="K10" s="187"/>
     </row>
     <row r="11" spans="1:11" ht="15">
-      <c r="A11" s="195"/>
-      <c r="B11" s="195"/>
-      <c r="C11" s="195"/>
-      <c r="D11" s="195"/>
-      <c r="E11" s="195"/>
-      <c r="F11" s="195"/>
-      <c r="G11" s="195"/>
-      <c r="H11" s="195"/>
-      <c r="I11" s="195"/>
-      <c r="J11" s="195"/>
-      <c r="K11" s="196"/>
+      <c r="A11" s="182"/>
+      <c r="B11" s="182"/>
+      <c r="C11" s="182"/>
+      <c r="D11" s="182"/>
+      <c r="E11" s="182"/>
+      <c r="F11" s="182"/>
+      <c r="G11" s="182"/>
+      <c r="H11" s="182"/>
+      <c r="I11" s="182"/>
+      <c r="J11" s="182"/>
+      <c r="K11" s="183"/>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="184" t="s">
@@ -8378,12 +8713,12 @@
       <c r="C13" s="92" t="s">
         <v>203</v>
       </c>
-      <c r="D13" s="187" t="s">
+      <c r="D13" s="199" t="s">
         <v>204</v>
       </c>
-      <c r="E13" s="176"/>
-      <c r="F13" s="176"/>
-      <c r="G13" s="177"/>
+      <c r="E13" s="200"/>
+      <c r="F13" s="200"/>
+      <c r="G13" s="201"/>
       <c r="H13" s="94"/>
       <c r="I13" s="96"/>
       <c r="J13" s="92" t="s">
@@ -8401,12 +8736,12 @@
       <c r="C14" s="92" t="s">
         <v>206</v>
       </c>
-      <c r="D14" s="187" t="s">
+      <c r="D14" s="199" t="s">
         <v>207</v>
       </c>
-      <c r="E14" s="176"/>
-      <c r="F14" s="176"/>
-      <c r="G14" s="177"/>
+      <c r="E14" s="200"/>
+      <c r="F14" s="200"/>
+      <c r="G14" s="201"/>
       <c r="H14" s="94"/>
       <c r="I14" s="96"/>
       <c r="J14" s="92" t="s">
@@ -8424,12 +8759,12 @@
       <c r="C15" s="92" t="s">
         <v>209</v>
       </c>
-      <c r="D15" s="187" t="s">
+      <c r="D15" s="199" t="s">
         <v>210</v>
       </c>
-      <c r="E15" s="176"/>
-      <c r="F15" s="176"/>
-      <c r="G15" s="177"/>
+      <c r="E15" s="200"/>
+      <c r="F15" s="200"/>
+      <c r="G15" s="201"/>
       <c r="H15" s="94"/>
       <c r="I15" s="96"/>
       <c r="J15" s="92" t="s">
@@ -8447,12 +8782,12 @@
       <c r="C16" s="92" t="s">
         <v>212</v>
       </c>
-      <c r="D16" s="187" t="s">
+      <c r="D16" s="199" t="s">
         <v>213</v>
       </c>
-      <c r="E16" s="176"/>
-      <c r="F16" s="176"/>
-      <c r="G16" s="177"/>
+      <c r="E16" s="200"/>
+      <c r="F16" s="200"/>
+      <c r="G16" s="201"/>
       <c r="H16" s="94"/>
       <c r="I16" s="96"/>
       <c r="J16" s="92" t="s">
@@ -8470,12 +8805,12 @@
       <c r="C17" s="92" t="s">
         <v>215</v>
       </c>
-      <c r="D17" s="187" t="s">
+      <c r="D17" s="199" t="s">
         <v>216</v>
       </c>
-      <c r="E17" s="176"/>
-      <c r="F17" s="176"/>
-      <c r="G17" s="177"/>
+      <c r="E17" s="200"/>
+      <c r="F17" s="200"/>
+      <c r="G17" s="201"/>
       <c r="H17" s="94"/>
       <c r="I17" s="96"/>
       <c r="J17" s="92" t="s">
@@ -8493,12 +8828,12 @@
       <c r="C18" s="92" t="s">
         <v>218</v>
       </c>
-      <c r="D18" s="187" t="s">
+      <c r="D18" s="199" t="s">
         <v>219</v>
       </c>
-      <c r="E18" s="176"/>
-      <c r="F18" s="176"/>
-      <c r="G18" s="177"/>
+      <c r="E18" s="200"/>
+      <c r="F18" s="200"/>
+      <c r="G18" s="201"/>
       <c r="H18" s="94"/>
       <c r="I18" s="96"/>
       <c r="J18" s="92" t="s">
@@ -8508,14 +8843,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="A11:K11"/>
-    <mergeCell ref="A12:K12"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="K9:K10"/>
     <mergeCell ref="D18:G18"/>
     <mergeCell ref="A9:A10"/>
     <mergeCell ref="B9:B10"/>
@@ -8527,6 +8854,14 @@
     <mergeCell ref="D15:G15"/>
     <mergeCell ref="D16:G16"/>
     <mergeCell ref="D17:G17"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="A11:K11"/>
+    <mergeCell ref="A12:K12"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="K9:K10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8578,52 +8913,52 @@
       <c r="A3" s="106" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="209" t="s">
+      <c r="B3" s="171" t="s">
         <v>62</v>
       </c>
-      <c r="C3" s="209"/>
-      <c r="D3" s="210"/>
+      <c r="C3" s="171"/>
+      <c r="D3" s="172"/>
       <c r="E3" s="71"/>
       <c r="F3" s="71"/>
       <c r="G3" s="71"/>
       <c r="H3" s="71"/>
-      <c r="I3" s="193"/>
-      <c r="J3" s="193"/>
-      <c r="K3" s="193"/>
+      <c r="I3" s="173"/>
+      <c r="J3" s="173"/>
+      <c r="K3" s="173"/>
     </row>
     <row r="4" spans="1:11" ht="14.25">
       <c r="A4" s="74" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="211" t="s">
+      <c r="B4" s="174" t="s">
         <v>221</v>
       </c>
-      <c r="C4" s="212"/>
-      <c r="D4" s="213"/>
+      <c r="C4" s="175"/>
+      <c r="D4" s="176"/>
       <c r="E4" s="71"/>
       <c r="F4" s="71"/>
       <c r="G4" s="71"/>
       <c r="H4" s="71"/>
-      <c r="I4" s="193"/>
-      <c r="J4" s="193"/>
-      <c r="K4" s="193"/>
+      <c r="I4" s="173"/>
+      <c r="J4" s="173"/>
+      <c r="K4" s="173"/>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="107" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="214" t="s">
+      <c r="B5" s="177" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="215"/>
-      <c r="D5" s="216"/>
+      <c r="C5" s="178"/>
+      <c r="D5" s="179"/>
       <c r="E5" s="75"/>
       <c r="F5" s="75"/>
       <c r="G5" s="75"/>
       <c r="H5" s="75"/>
-      <c r="I5" s="217"/>
-      <c r="J5" s="217"/>
-      <c r="K5" s="217"/>
+      <c r="I5" s="180"/>
+      <c r="J5" s="180"/>
+      <c r="K5" s="180"/>
     </row>
     <row r="6" spans="1:11" ht="14.25">
       <c r="A6" s="77" t="s">
@@ -8644,9 +8979,9 @@
       <c r="F6" s="72"/>
       <c r="G6" s="72"/>
       <c r="H6" s="72"/>
-      <c r="I6" s="193"/>
-      <c r="J6" s="193"/>
-      <c r="K6" s="193"/>
+      <c r="I6" s="173"/>
+      <c r="J6" s="173"/>
+      <c r="K6" s="173"/>
     </row>
     <row r="7" spans="1:11" ht="14.25">
       <c r="A7" s="81" t="s">
@@ -8667,15 +9002,15 @@
       <c r="F7" s="85"/>
       <c r="G7" s="85"/>
       <c r="H7" s="85"/>
-      <c r="I7" s="193"/>
-      <c r="J7" s="193"/>
-      <c r="K7" s="193"/>
+      <c r="I7" s="173"/>
+      <c r="J7" s="173"/>
+      <c r="K7" s="173"/>
     </row>
     <row r="8" spans="1:11" ht="14.25">
-      <c r="A8" s="194"/>
-      <c r="B8" s="194"/>
-      <c r="C8" s="194"/>
-      <c r="D8" s="194"/>
+      <c r="A8" s="181"/>
+      <c r="B8" s="181"/>
+      <c r="C8" s="181"/>
+      <c r="D8" s="181"/>
       <c r="E8" s="72"/>
       <c r="F8" s="72"/>
       <c r="G8" s="72"/>
@@ -8685,59 +9020,59 @@
       <c r="K8" s="86"/>
     </row>
     <row r="9" spans="1:11" ht="13.5" customHeight="1">
-      <c r="A9" s="197" t="s">
+      <c r="A9" s="187" t="s">
         <v>71</v>
       </c>
-      <c r="B9" s="199" t="s">
+      <c r="B9" s="189" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="197" t="s">
+      <c r="C9" s="187" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="203" t="s">
+      <c r="D9" s="193" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="204"/>
-      <c r="F9" s="204"/>
-      <c r="G9" s="205"/>
-      <c r="H9" s="201" t="s">
+      <c r="E9" s="194"/>
+      <c r="F9" s="194"/>
+      <c r="G9" s="195"/>
+      <c r="H9" s="191" t="s">
         <v>75</v>
       </c>
-      <c r="I9" s="202" t="s">
+      <c r="I9" s="192" t="s">
         <v>76</v>
       </c>
-      <c r="J9" s="202" t="s">
+      <c r="J9" s="192" t="s">
         <v>77</v>
       </c>
-      <c r="K9" s="202" t="s">
+      <c r="K9" s="192" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="198"/>
-      <c r="B10" s="200"/>
-      <c r="C10" s="198"/>
-      <c r="D10" s="206"/>
-      <c r="E10" s="207"/>
-      <c r="F10" s="207"/>
-      <c r="G10" s="208"/>
-      <c r="H10" s="197"/>
-      <c r="I10" s="197"/>
-      <c r="J10" s="197"/>
-      <c r="K10" s="197"/>
+      <c r="A10" s="188"/>
+      <c r="B10" s="190"/>
+      <c r="C10" s="188"/>
+      <c r="D10" s="196"/>
+      <c r="E10" s="197"/>
+      <c r="F10" s="197"/>
+      <c r="G10" s="198"/>
+      <c r="H10" s="187"/>
+      <c r="I10" s="187"/>
+      <c r="J10" s="187"/>
+      <c r="K10" s="187"/>
     </row>
     <row r="11" spans="1:11" ht="15">
-      <c r="A11" s="195"/>
-      <c r="B11" s="195"/>
-      <c r="C11" s="195"/>
-      <c r="D11" s="195"/>
-      <c r="E11" s="195"/>
-      <c r="F11" s="195"/>
-      <c r="G11" s="195"/>
-      <c r="H11" s="195"/>
-      <c r="I11" s="195"/>
-      <c r="J11" s="195"/>
-      <c r="K11" s="196"/>
+      <c r="A11" s="182"/>
+      <c r="B11" s="182"/>
+      <c r="C11" s="182"/>
+      <c r="D11" s="182"/>
+      <c r="E11" s="182"/>
+      <c r="F11" s="182"/>
+      <c r="G11" s="182"/>
+      <c r="H11" s="182"/>
+      <c r="I11" s="182"/>
+      <c r="J11" s="182"/>
+      <c r="K11" s="183"/>
     </row>
     <row r="12" spans="1:11" ht="16.5" customHeight="1">
       <c r="A12" s="184" t="s">
@@ -8787,11 +9122,11 @@
       <c r="C14" s="92" t="s">
         <v>227</v>
       </c>
-      <c r="D14" s="175" t="s">
+      <c r="D14" s="207" t="s">
         <v>228</v>
       </c>
-      <c r="E14" s="176"/>
-      <c r="F14" s="176"/>
+      <c r="E14" s="200"/>
+      <c r="F14" s="200"/>
       <c r="G14" s="124"/>
       <c r="H14" s="94"/>
       <c r="I14" s="96"/>
@@ -8810,11 +9145,11 @@
       <c r="C15" s="93" t="s">
         <v>230</v>
       </c>
-      <c r="D15" s="175" t="s">
+      <c r="D15" s="207" t="s">
         <v>231</v>
       </c>
-      <c r="E15" s="176"/>
-      <c r="F15" s="176"/>
+      <c r="E15" s="200"/>
+      <c r="F15" s="200"/>
       <c r="G15" s="95"/>
       <c r="H15" s="95"/>
       <c r="I15" s="125"/>
@@ -8871,11 +9206,11 @@
       <c r="C18" s="93" t="s">
         <v>237</v>
       </c>
-      <c r="D18" s="175" t="s">
+      <c r="D18" s="207" t="s">
         <v>238</v>
       </c>
-      <c r="E18" s="176"/>
-      <c r="F18" s="176"/>
+      <c r="E18" s="200"/>
+      <c r="F18" s="200"/>
       <c r="G18" s="95"/>
       <c r="H18" s="95"/>
       <c r="I18" s="92"/>
@@ -8894,11 +9229,11 @@
       <c r="C19" s="93" t="s">
         <v>240</v>
       </c>
-      <c r="D19" s="175" t="s">
+      <c r="D19" s="207" t="s">
         <v>238</v>
       </c>
-      <c r="E19" s="176"/>
-      <c r="F19" s="176"/>
+      <c r="E19" s="200"/>
+      <c r="F19" s="200"/>
       <c r="G19" s="95"/>
       <c r="H19" s="95"/>
       <c r="I19" s="92"/>
@@ -8932,11 +9267,11 @@
       <c r="C21" s="98" t="s">
         <v>243</v>
       </c>
-      <c r="D21" s="175" t="s">
+      <c r="D21" s="207" t="s">
         <v>244</v>
       </c>
-      <c r="E21" s="176"/>
-      <c r="F21" s="176"/>
+      <c r="E21" s="200"/>
+      <c r="F21" s="200"/>
       <c r="G21" s="95"/>
       <c r="H21" s="94"/>
       <c r="I21" s="93"/>
@@ -8955,11 +9290,11 @@
       <c r="C22" s="92" t="s">
         <v>246</v>
       </c>
-      <c r="D22" s="175" t="s">
+      <c r="D22" s="207" t="s">
         <v>247</v>
       </c>
-      <c r="E22" s="176"/>
-      <c r="F22" s="176"/>
+      <c r="E22" s="200"/>
+      <c r="F22" s="200"/>
       <c r="G22" s="95"/>
       <c r="H22" s="92"/>
       <c r="I22" s="92"/>
@@ -9039,11 +9374,11 @@
       <c r="C26" s="92" t="s">
         <v>255</v>
       </c>
-      <c r="D26" s="174" t="s">
+      <c r="D26" s="212" t="s">
         <v>256</v>
       </c>
-      <c r="E26" s="174"/>
-      <c r="F26" s="175"/>
+      <c r="E26" s="212"/>
+      <c r="F26" s="207"/>
       <c r="G26" s="95"/>
       <c r="H26" s="95"/>
       <c r="I26" s="92"/>
@@ -9062,11 +9397,11 @@
       <c r="C27" s="92" t="s">
         <v>258</v>
       </c>
-      <c r="D27" s="174" t="s">
+      <c r="D27" s="212" t="s">
         <v>259</v>
       </c>
-      <c r="E27" s="174"/>
-      <c r="F27" s="175"/>
+      <c r="E27" s="212"/>
+      <c r="F27" s="207"/>
       <c r="G27" s="95"/>
       <c r="H27" s="92"/>
       <c r="I27" s="92"/>
@@ -9102,25 +9437,6 @@
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A11:K11"/>
-    <mergeCell ref="A12:K12"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="K9:K10"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="D17:F17"/>
     <mergeCell ref="D27:F27"/>
     <mergeCell ref="A9:A10"/>
     <mergeCell ref="B9:B10"/>
@@ -9137,6 +9453,25 @@
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="D21:F21"/>
     <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A11:K11"/>
+    <mergeCell ref="A12:K12"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="K9:K10"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="I5:K5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -9195,54 +9530,54 @@
       <c r="A3" s="106" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="209" t="s">
+      <c r="B3" s="171" t="s">
         <v>62</v>
       </c>
-      <c r="C3" s="209"/>
-      <c r="D3" s="210"/>
+      <c r="C3" s="171"/>
+      <c r="D3" s="172"/>
       <c r="E3" s="71"/>
       <c r="F3" s="71"/>
       <c r="G3" s="71"/>
       <c r="H3" s="71"/>
-      <c r="I3" s="193"/>
-      <c r="J3" s="193"/>
-      <c r="K3" s="193"/>
+      <c r="I3" s="173"/>
+      <c r="J3" s="173"/>
+      <c r="K3" s="173"/>
       <c r="L3" s="73"/>
     </row>
     <row r="4" spans="1:12" s="61" customFormat="1" ht="13.15" customHeight="1">
       <c r="A4" s="74" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="211" t="s">
+      <c r="B4" s="174" t="s">
         <v>260</v>
       </c>
-      <c r="C4" s="212"/>
-      <c r="D4" s="213"/>
+      <c r="C4" s="175"/>
+      <c r="D4" s="176"/>
       <c r="E4" s="71"/>
       <c r="F4" s="71"/>
       <c r="G4" s="71"/>
       <c r="H4" s="71"/>
-      <c r="I4" s="193"/>
-      <c r="J4" s="193"/>
-      <c r="K4" s="193"/>
+      <c r="I4" s="173"/>
+      <c r="J4" s="173"/>
+      <c r="K4" s="173"/>
       <c r="L4" s="73"/>
     </row>
     <row r="5" spans="1:12" s="62" customFormat="1" ht="12.75">
       <c r="A5" s="107" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="214" t="s">
+      <c r="B5" s="177" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="215"/>
-      <c r="D5" s="216"/>
+      <c r="C5" s="178"/>
+      <c r="D5" s="179"/>
       <c r="E5" s="75"/>
       <c r="F5" s="75"/>
       <c r="G5" s="75"/>
       <c r="H5" s="75"/>
-      <c r="I5" s="217"/>
-      <c r="J5" s="217"/>
-      <c r="K5" s="217"/>
+      <c r="I5" s="180"/>
+      <c r="J5" s="180"/>
+      <c r="K5" s="180"/>
       <c r="L5" s="76"/>
     </row>
     <row r="6" spans="1:12" s="61" customFormat="1" ht="15" customHeight="1">
@@ -9264,9 +9599,9 @@
       <c r="F6" s="72"/>
       <c r="G6" s="72"/>
       <c r="H6" s="72"/>
-      <c r="I6" s="193"/>
-      <c r="J6" s="193"/>
-      <c r="K6" s="193"/>
+      <c r="I6" s="173"/>
+      <c r="J6" s="173"/>
+      <c r="K6" s="173"/>
       <c r="L6" s="73"/>
     </row>
     <row r="7" spans="1:12" s="61" customFormat="1" ht="15" customHeight="1">
@@ -9288,16 +9623,16 @@
       <c r="F7" s="85"/>
       <c r="G7" s="85"/>
       <c r="H7" s="85"/>
-      <c r="I7" s="193"/>
-      <c r="J7" s="193"/>
-      <c r="K7" s="193"/>
+      <c r="I7" s="173"/>
+      <c r="J7" s="173"/>
+      <c r="K7" s="173"/>
       <c r="L7" s="73"/>
     </row>
     <row r="8" spans="1:12" s="61" customFormat="1" ht="15" customHeight="1">
-      <c r="A8" s="194"/>
-      <c r="B8" s="194"/>
-      <c r="C8" s="194"/>
-      <c r="D8" s="194"/>
+      <c r="A8" s="181"/>
+      <c r="B8" s="181"/>
+      <c r="C8" s="181"/>
+      <c r="D8" s="181"/>
       <c r="E8" s="72"/>
       <c r="F8" s="72"/>
       <c r="G8" s="72"/>
@@ -9308,76 +9643,76 @@
       <c r="L8" s="73"/>
     </row>
     <row r="9" spans="1:12" s="63" customFormat="1" ht="12" customHeight="1">
-      <c r="A9" s="197" t="s">
+      <c r="A9" s="187" t="s">
         <v>71</v>
       </c>
-      <c r="B9" s="199" t="s">
+      <c r="B9" s="189" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="197" t="s">
+      <c r="C9" s="187" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="203" t="s">
+      <c r="D9" s="193" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="204"/>
-      <c r="F9" s="204"/>
-      <c r="G9" s="205"/>
-      <c r="H9" s="201" t="s">
+      <c r="E9" s="194"/>
+      <c r="F9" s="194"/>
+      <c r="G9" s="195"/>
+      <c r="H9" s="191" t="s">
         <v>75</v>
       </c>
-      <c r="I9" s="202" t="s">
+      <c r="I9" s="192" t="s">
         <v>76</v>
       </c>
-      <c r="J9" s="202" t="s">
+      <c r="J9" s="192" t="s">
         <v>77</v>
       </c>
-      <c r="K9" s="202" t="s">
+      <c r="K9" s="192" t="s">
         <v>78</v>
       </c>
       <c r="L9" s="87"/>
     </row>
     <row r="10" spans="1:12" s="61" customFormat="1" ht="12" customHeight="1">
-      <c r="A10" s="198"/>
-      <c r="B10" s="200"/>
-      <c r="C10" s="198"/>
-      <c r="D10" s="206"/>
-      <c r="E10" s="207"/>
-      <c r="F10" s="207"/>
-      <c r="G10" s="208"/>
-      <c r="H10" s="197"/>
-      <c r="I10" s="197"/>
-      <c r="J10" s="197"/>
-      <c r="K10" s="197"/>
+      <c r="A10" s="188"/>
+      <c r="B10" s="190"/>
+      <c r="C10" s="188"/>
+      <c r="D10" s="196"/>
+      <c r="E10" s="197"/>
+      <c r="F10" s="197"/>
+      <c r="G10" s="198"/>
+      <c r="H10" s="187"/>
+      <c r="I10" s="187"/>
+      <c r="J10" s="187"/>
+      <c r="K10" s="187"/>
       <c r="L10" s="73"/>
     </row>
     <row r="11" spans="1:12" s="64" customFormat="1" ht="15">
-      <c r="A11" s="195"/>
-      <c r="B11" s="195"/>
-      <c r="C11" s="195"/>
-      <c r="D11" s="195"/>
-      <c r="E11" s="195"/>
-      <c r="F11" s="195"/>
-      <c r="G11" s="195"/>
-      <c r="H11" s="195"/>
-      <c r="I11" s="195"/>
-      <c r="J11" s="195"/>
-      <c r="K11" s="196"/>
+      <c r="A11" s="182"/>
+      <c r="B11" s="182"/>
+      <c r="C11" s="182"/>
+      <c r="D11" s="182"/>
+      <c r="E11" s="182"/>
+      <c r="F11" s="182"/>
+      <c r="G11" s="182"/>
+      <c r="H11" s="182"/>
+      <c r="I11" s="182"/>
+      <c r="J11" s="182"/>
+      <c r="K11" s="183"/>
     </row>
     <row r="12" spans="1:12" s="65" customFormat="1" ht="24.6" customHeight="1">
-      <c r="A12" s="227" t="s">
+      <c r="A12" s="224" t="s">
         <v>261</v>
       </c>
-      <c r="B12" s="228"/>
-      <c r="C12" s="228"/>
-      <c r="D12" s="228"/>
-      <c r="E12" s="228"/>
-      <c r="F12" s="228"/>
-      <c r="G12" s="228"/>
-      <c r="H12" s="228"/>
-      <c r="I12" s="228"/>
-      <c r="J12" s="228"/>
-      <c r="K12" s="229"/>
+      <c r="B12" s="225"/>
+      <c r="C12" s="225"/>
+      <c r="D12" s="225"/>
+      <c r="E12" s="225"/>
+      <c r="F12" s="225"/>
+      <c r="G12" s="225"/>
+      <c r="H12" s="225"/>
+      <c r="I12" s="225"/>
+      <c r="J12" s="225"/>
+      <c r="K12" s="226"/>
     </row>
     <row r="13" spans="1:12" s="65" customFormat="1" ht="81.599999999999994" customHeight="1" outlineLevel="1">
       <c r="A13" s="108" t="s">
@@ -9389,11 +9724,11 @@
       <c r="C13" s="109" t="s">
         <v>263</v>
       </c>
-      <c r="D13" s="175" t="s">
+      <c r="D13" s="207" t="s">
         <v>264</v>
       </c>
-      <c r="E13" s="176"/>
-      <c r="F13" s="176"/>
+      <c r="E13" s="200"/>
+      <c r="F13" s="200"/>
       <c r="G13" s="95"/>
       <c r="H13" s="94"/>
       <c r="I13" s="96"/>
@@ -9410,11 +9745,11 @@
       <c r="C14" s="111" t="s">
         <v>266</v>
       </c>
-      <c r="D14" s="175" t="s">
+      <c r="D14" s="207" t="s">
         <v>267</v>
       </c>
-      <c r="E14" s="176"/>
-      <c r="F14" s="176"/>
+      <c r="E14" s="200"/>
+      <c r="F14" s="200"/>
       <c r="G14" s="95"/>
       <c r="H14" s="94"/>
       <c r="I14" s="93"/>
@@ -9431,11 +9766,11 @@
       <c r="C15" s="109" t="s">
         <v>269</v>
       </c>
-      <c r="D15" s="175" t="s">
+      <c r="D15" s="207" t="s">
         <v>270</v>
       </c>
-      <c r="E15" s="176"/>
-      <c r="F15" s="176"/>
+      <c r="E15" s="200"/>
+      <c r="F15" s="200"/>
       <c r="G15" s="95"/>
       <c r="H15" s="94"/>
       <c r="I15" s="93"/>
@@ -9452,11 +9787,11 @@
       <c r="C16" s="111" t="s">
         <v>272</v>
       </c>
-      <c r="D16" s="175" t="s">
+      <c r="D16" s="207" t="s">
         <v>273</v>
       </c>
-      <c r="E16" s="176"/>
-      <c r="F16" s="176"/>
+      <c r="E16" s="200"/>
+      <c r="F16" s="200"/>
       <c r="G16" s="95"/>
       <c r="H16" s="94"/>
       <c r="I16" s="93"/>
@@ -9473,11 +9808,11 @@
       <c r="C17" s="109" t="s">
         <v>275</v>
       </c>
-      <c r="D17" s="175" t="s">
+      <c r="D17" s="207" t="s">
         <v>276</v>
       </c>
-      <c r="E17" s="176"/>
-      <c r="F17" s="176"/>
+      <c r="E17" s="200"/>
+      <c r="F17" s="200"/>
       <c r="G17" s="95"/>
       <c r="H17" s="94"/>
       <c r="I17" s="93"/>
@@ -9494,11 +9829,11 @@
       <c r="C18" s="111" t="s">
         <v>278</v>
       </c>
-      <c r="D18" s="175" t="s">
+      <c r="D18" s="207" t="s">
         <v>279</v>
       </c>
-      <c r="E18" s="176"/>
-      <c r="F18" s="176"/>
+      <c r="E18" s="200"/>
+      <c r="F18" s="200"/>
       <c r="G18" s="95"/>
       <c r="H18" s="94"/>
       <c r="I18" s="96"/>
@@ -9515,11 +9850,11 @@
       <c r="C19" s="109" t="s">
         <v>281</v>
       </c>
-      <c r="D19" s="175" t="s">
+      <c r="D19" s="207" t="s">
         <v>282</v>
       </c>
-      <c r="E19" s="176"/>
-      <c r="F19" s="176"/>
+      <c r="E19" s="200"/>
+      <c r="F19" s="200"/>
       <c r="G19" s="95"/>
       <c r="H19" s="94"/>
       <c r="I19" s="93"/>
@@ -9536,11 +9871,11 @@
       <c r="C20" s="111" t="s">
         <v>284</v>
       </c>
-      <c r="D20" s="175" t="s">
+      <c r="D20" s="207" t="s">
         <v>285</v>
       </c>
-      <c r="E20" s="176"/>
-      <c r="F20" s="176"/>
+      <c r="E20" s="200"/>
+      <c r="F20" s="200"/>
       <c r="G20" s="95"/>
       <c r="H20" s="94"/>
       <c r="I20" s="93"/>
@@ -9557,11 +9892,11 @@
       <c r="C21" s="109" t="s">
         <v>287</v>
       </c>
-      <c r="D21" s="175" t="s">
+      <c r="D21" s="207" t="s">
         <v>288</v>
       </c>
-      <c r="E21" s="176"/>
-      <c r="F21" s="176"/>
+      <c r="E21" s="200"/>
+      <c r="F21" s="200"/>
       <c r="G21" s="95"/>
       <c r="H21" s="94"/>
       <c r="I21" s="93"/>
@@ -9578,11 +9913,11 @@
       <c r="C22" s="111" t="s">
         <v>290</v>
       </c>
-      <c r="D22" s="175" t="s">
+      <c r="D22" s="207" t="s">
         <v>291</v>
       </c>
-      <c r="E22" s="176"/>
-      <c r="F22" s="176"/>
+      <c r="E22" s="200"/>
+      <c r="F22" s="200"/>
       <c r="G22" s="95"/>
       <c r="H22" s="94"/>
       <c r="I22" s="93"/>
@@ -9599,11 +9934,11 @@
       <c r="C23" s="109" t="s">
         <v>293</v>
       </c>
-      <c r="D23" s="175" t="s">
+      <c r="D23" s="207" t="s">
         <v>294</v>
       </c>
-      <c r="E23" s="176"/>
-      <c r="F23" s="176"/>
+      <c r="E23" s="200"/>
+      <c r="F23" s="200"/>
       <c r="G23" s="95"/>
       <c r="H23" s="94"/>
       <c r="I23" s="96"/>
@@ -9620,11 +9955,11 @@
       <c r="C24" s="111" t="s">
         <v>296</v>
       </c>
-      <c r="D24" s="175" t="s">
+      <c r="D24" s="207" t="s">
         <v>297</v>
       </c>
-      <c r="E24" s="176"/>
-      <c r="F24" s="176"/>
+      <c r="E24" s="200"/>
+      <c r="F24" s="200"/>
       <c r="G24" s="95"/>
       <c r="H24" s="94"/>
       <c r="I24" s="93"/>
@@ -9641,11 +9976,11 @@
       <c r="C25" s="109" t="s">
         <v>300</v>
       </c>
-      <c r="D25" s="175" t="s">
+      <c r="D25" s="207" t="s">
         <v>301</v>
       </c>
-      <c r="E25" s="176"/>
-      <c r="F25" s="176"/>
+      <c r="E25" s="200"/>
+      <c r="F25" s="200"/>
       <c r="G25" s="95"/>
       <c r="H25" s="94"/>
       <c r="I25" s="93"/>
@@ -9662,11 +9997,11 @@
       <c r="C26" s="111" t="s">
         <v>304</v>
       </c>
-      <c r="D26" s="175" t="s">
+      <c r="D26" s="207" t="s">
         <v>305</v>
       </c>
-      <c r="E26" s="176"/>
-      <c r="F26" s="176"/>
+      <c r="E26" s="200"/>
+      <c r="F26" s="200"/>
       <c r="G26" s="95"/>
       <c r="H26" s="94"/>
       <c r="I26" s="93"/>
@@ -9674,7 +10009,7 @@
       <c r="K26" s="92"/>
     </row>
     <row r="27" spans="1:11" ht="25.15" customHeight="1">
-      <c r="A27" s="226" t="s">
+      <c r="A27" s="227" t="s">
         <v>306</v>
       </c>
       <c r="B27" s="185"/>
@@ -9698,11 +10033,11 @@
       <c r="C28" s="109" t="s">
         <v>309</v>
       </c>
-      <c r="D28" s="175" t="s">
+      <c r="D28" s="207" t="s">
         <v>310</v>
       </c>
-      <c r="E28" s="176"/>
-      <c r="F28" s="176"/>
+      <c r="E28" s="200"/>
+      <c r="F28" s="200"/>
       <c r="G28" s="95"/>
       <c r="H28" s="94"/>
       <c r="I28" s="96"/>
@@ -9719,11 +10054,11 @@
       <c r="C29" s="111" t="s">
         <v>313</v>
       </c>
-      <c r="D29" s="175" t="s">
+      <c r="D29" s="207" t="s">
         <v>314</v>
       </c>
-      <c r="E29" s="176"/>
-      <c r="F29" s="176"/>
+      <c r="E29" s="200"/>
+      <c r="F29" s="200"/>
       <c r="G29" s="95"/>
       <c r="H29" s="94"/>
       <c r="I29" s="93"/>
@@ -9740,11 +10075,11 @@
       <c r="C30" s="109" t="s">
         <v>317</v>
       </c>
-      <c r="D30" s="175" t="s">
+      <c r="D30" s="207" t="s">
         <v>318</v>
       </c>
-      <c r="E30" s="176"/>
-      <c r="F30" s="176"/>
+      <c r="E30" s="200"/>
+      <c r="F30" s="200"/>
       <c r="G30" s="95"/>
       <c r="H30" s="94"/>
       <c r="I30" s="93"/>
@@ -9761,11 +10096,11 @@
       <c r="C31" s="111" t="s">
         <v>321</v>
       </c>
-      <c r="D31" s="175" t="s">
+      <c r="D31" s="207" t="s">
         <v>322</v>
       </c>
-      <c r="E31" s="176"/>
-      <c r="F31" s="176"/>
+      <c r="E31" s="200"/>
+      <c r="F31" s="200"/>
       <c r="G31" s="95"/>
       <c r="H31" s="94"/>
       <c r="I31" s="93"/>
@@ -9782,11 +10117,11 @@
       <c r="C32" s="109" t="s">
         <v>325</v>
       </c>
-      <c r="D32" s="175" t="s">
+      <c r="D32" s="207" t="s">
         <v>326</v>
       </c>
-      <c r="E32" s="176"/>
-      <c r="F32" s="176"/>
+      <c r="E32" s="200"/>
+      <c r="F32" s="200"/>
       <c r="G32" s="95"/>
       <c r="H32" s="94"/>
       <c r="I32" s="93"/>
@@ -9803,11 +10138,11 @@
       <c r="C33" s="111" t="s">
         <v>329</v>
       </c>
-      <c r="D33" s="175" t="s">
+      <c r="D33" s="207" t="s">
         <v>322</v>
       </c>
-      <c r="E33" s="176"/>
-      <c r="F33" s="176"/>
+      <c r="E33" s="200"/>
+      <c r="F33" s="200"/>
       <c r="G33" s="95"/>
       <c r="H33" s="94"/>
       <c r="I33" s="93"/>
@@ -9824,11 +10159,11 @@
       <c r="C34" s="109" t="s">
         <v>332</v>
       </c>
-      <c r="D34" s="175" t="s">
+      <c r="D34" s="207" t="s">
         <v>333</v>
       </c>
-      <c r="E34" s="176"/>
-      <c r="F34" s="176"/>
+      <c r="E34" s="200"/>
+      <c r="F34" s="200"/>
       <c r="G34" s="95"/>
       <c r="H34" s="94"/>
       <c r="I34" s="93"/>
@@ -9845,11 +10180,11 @@
       <c r="C35" s="111" t="s">
         <v>336</v>
       </c>
-      <c r="D35" s="175" t="s">
+      <c r="D35" s="207" t="s">
         <v>337</v>
       </c>
-      <c r="E35" s="176"/>
-      <c r="F35" s="176"/>
+      <c r="E35" s="200"/>
+      <c r="F35" s="200"/>
       <c r="G35" s="95"/>
       <c r="H35" s="94"/>
       <c r="I35" s="93"/>
@@ -9857,7 +10192,7 @@
       <c r="K35" s="92"/>
     </row>
     <row r="36" spans="1:11" ht="28.15" customHeight="1">
-      <c r="A36" s="226" t="s">
+      <c r="A36" s="227" t="s">
         <v>338</v>
       </c>
       <c r="B36" s="185"/>
@@ -9881,11 +10216,11 @@
       <c r="C37" s="109" t="s">
         <v>341</v>
       </c>
-      <c r="D37" s="175" t="s">
+      <c r="D37" s="207" t="s">
         <v>342</v>
       </c>
-      <c r="E37" s="176"/>
-      <c r="F37" s="176"/>
+      <c r="E37" s="200"/>
+      <c r="F37" s="200"/>
       <c r="G37" s="95"/>
       <c r="H37" s="94"/>
       <c r="I37" s="93"/>
@@ -9902,11 +10237,11 @@
       <c r="C38" s="111" t="s">
         <v>345</v>
       </c>
-      <c r="D38" s="175" t="s">
+      <c r="D38" s="207" t="s">
         <v>346</v>
       </c>
-      <c r="E38" s="176"/>
-      <c r="F38" s="176"/>
+      <c r="E38" s="200"/>
+      <c r="F38" s="200"/>
       <c r="G38" s="95"/>
       <c r="H38" s="94"/>
       <c r="I38" s="93"/>
@@ -9914,7 +10249,7 @@
       <c r="K38" s="92"/>
     </row>
     <row r="39" spans="1:11" ht="28.9" customHeight="1">
-      <c r="A39" s="226" t="s">
+      <c r="A39" s="227" t="s">
         <v>347</v>
       </c>
       <c r="B39" s="185"/>
@@ -9938,11 +10273,11 @@
       <c r="C40" s="109" t="s">
         <v>350</v>
       </c>
-      <c r="D40" s="175" t="s">
+      <c r="D40" s="207" t="s">
         <v>351</v>
       </c>
-      <c r="E40" s="176"/>
-      <c r="F40" s="176"/>
+      <c r="E40" s="200"/>
+      <c r="F40" s="200"/>
       <c r="G40" s="95"/>
       <c r="H40" s="94"/>
       <c r="I40" s="93"/>
@@ -9959,11 +10294,11 @@
       <c r="C41" s="111" t="s">
         <v>354</v>
       </c>
-      <c r="D41" s="175" t="s">
+      <c r="D41" s="207" t="s">
         <v>355</v>
       </c>
-      <c r="E41" s="176"/>
-      <c r="F41" s="176"/>
+      <c r="E41" s="200"/>
+      <c r="F41" s="200"/>
       <c r="G41" s="95"/>
       <c r="H41" s="94"/>
       <c r="I41" s="93"/>
@@ -9974,9 +10309,9 @@
       <c r="A42" s="90"/>
       <c r="B42" s="99"/>
       <c r="C42" s="92"/>
-      <c r="D42" s="224"/>
-      <c r="E42" s="225"/>
-      <c r="F42" s="225"/>
+      <c r="D42" s="228"/>
+      <c r="E42" s="229"/>
+      <c r="F42" s="229"/>
       <c r="G42" s="95"/>
       <c r="H42" s="94"/>
       <c r="I42" s="93"/>
@@ -9987,9 +10322,9 @@
       <c r="A43" s="90"/>
       <c r="B43" s="97"/>
       <c r="C43" s="98"/>
-      <c r="D43" s="224"/>
-      <c r="E43" s="176"/>
-      <c r="F43" s="176"/>
+      <c r="D43" s="228"/>
+      <c r="E43" s="200"/>
+      <c r="F43" s="200"/>
       <c r="G43" s="95"/>
       <c r="H43" s="94"/>
       <c r="I43" s="93"/>
@@ -10000,9 +10335,9 @@
       <c r="A44" s="90"/>
       <c r="B44" s="99"/>
       <c r="C44" s="92"/>
-      <c r="D44" s="224"/>
-      <c r="E44" s="225"/>
-      <c r="F44" s="225"/>
+      <c r="D44" s="228"/>
+      <c r="E44" s="229"/>
+      <c r="F44" s="229"/>
       <c r="G44" s="95"/>
       <c r="H44" s="94"/>
       <c r="I44" s="93"/>
@@ -10013,9 +10348,9 @@
       <c r="A45" s="90"/>
       <c r="B45" s="97"/>
       <c r="C45" s="98"/>
-      <c r="D45" s="224"/>
-      <c r="E45" s="176"/>
-      <c r="F45" s="176"/>
+      <c r="D45" s="228"/>
+      <c r="E45" s="200"/>
+      <c r="F45" s="200"/>
       <c r="G45" s="95"/>
       <c r="H45" s="94"/>
       <c r="I45" s="93"/>
@@ -10026,9 +10361,9 @@
       <c r="A46" s="90"/>
       <c r="B46" s="99"/>
       <c r="C46" s="92"/>
-      <c r="D46" s="224"/>
-      <c r="E46" s="225"/>
-      <c r="F46" s="225"/>
+      <c r="D46" s="228"/>
+      <c r="E46" s="229"/>
+      <c r="F46" s="229"/>
       <c r="G46" s="95"/>
       <c r="H46" s="94"/>
       <c r="I46" s="93"/>
@@ -10039,9 +10374,9 @@
       <c r="A47" s="90"/>
       <c r="B47" s="97"/>
       <c r="C47" s="98"/>
-      <c r="D47" s="224"/>
-      <c r="E47" s="176"/>
-      <c r="F47" s="176"/>
+      <c r="D47" s="228"/>
+      <c r="E47" s="200"/>
+      <c r="F47" s="200"/>
       <c r="G47" s="95"/>
       <c r="H47" s="94"/>
       <c r="I47" s="93"/>
@@ -10052,9 +10387,9 @@
       <c r="A48" s="90"/>
       <c r="B48" s="99"/>
       <c r="C48" s="92"/>
-      <c r="D48" s="224"/>
-      <c r="E48" s="225"/>
-      <c r="F48" s="225"/>
+      <c r="D48" s="228"/>
+      <c r="E48" s="229"/>
+      <c r="F48" s="229"/>
       <c r="G48" s="95"/>
       <c r="H48" s="94"/>
       <c r="I48" s="93"/>
@@ -10065,9 +10400,9 @@
       <c r="A49" s="90"/>
       <c r="B49" s="97"/>
       <c r="C49" s="98"/>
-      <c r="D49" s="224"/>
-      <c r="E49" s="176"/>
-      <c r="F49" s="176"/>
+      <c r="D49" s="228"/>
+      <c r="E49" s="200"/>
+      <c r="F49" s="200"/>
       <c r="G49" s="95"/>
       <c r="H49" s="94"/>
       <c r="I49" s="93"/>
@@ -10078,9 +10413,9 @@
       <c r="A50" s="90"/>
       <c r="B50" s="99"/>
       <c r="C50" s="92"/>
-      <c r="D50" s="224"/>
-      <c r="E50" s="225"/>
-      <c r="F50" s="225"/>
+      <c r="D50" s="228"/>
+      <c r="E50" s="229"/>
+      <c r="F50" s="229"/>
       <c r="G50" s="95"/>
       <c r="H50" s="94"/>
       <c r="I50" s="93"/>
@@ -10092,47 +10427,6 @@
     <row r="53" spans="1:11" ht="12" customHeight="1"/>
   </sheetData>
   <mergeCells count="57">
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A11:K11"/>
-    <mergeCell ref="A12:K12"/>
-    <mergeCell ref="H9:H10"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="K9:K10"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="A27:K27"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="D42:F42"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="A36:K36"/>
-    <mergeCell ref="D37:F37"/>
     <mergeCell ref="D48:F48"/>
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="D50:F50"/>
@@ -10149,6 +10443,47 @@
     <mergeCell ref="A39:K39"/>
     <mergeCell ref="D40:F40"/>
     <mergeCell ref="D41:F41"/>
+    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="A36:K36"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="A27:K27"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A11:K11"/>
+    <mergeCell ref="A12:K12"/>
+    <mergeCell ref="H9:H10"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="K9:K10"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="I5:K5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10206,54 +10541,54 @@
       <c r="A3" s="106" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="209" t="s">
+      <c r="B3" s="171" t="s">
         <v>62</v>
       </c>
-      <c r="C3" s="209"/>
-      <c r="D3" s="210"/>
+      <c r="C3" s="171"/>
+      <c r="D3" s="172"/>
       <c r="E3" s="71"/>
       <c r="F3" s="71"/>
       <c r="G3" s="71"/>
       <c r="H3" s="71"/>
-      <c r="I3" s="193"/>
-      <c r="J3" s="193"/>
-      <c r="K3" s="193"/>
+      <c r="I3" s="173"/>
+      <c r="J3" s="173"/>
+      <c r="K3" s="173"/>
       <c r="L3" s="73"/>
     </row>
     <row r="4" spans="1:12" s="61" customFormat="1" ht="13.15" customHeight="1">
       <c r="A4" s="74" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="211" t="s">
+      <c r="B4" s="174" t="s">
         <v>356</v>
       </c>
-      <c r="C4" s="212"/>
-      <c r="D4" s="213"/>
+      <c r="C4" s="175"/>
+      <c r="D4" s="176"/>
       <c r="E4" s="71"/>
       <c r="F4" s="71"/>
       <c r="G4" s="71"/>
       <c r="H4" s="71"/>
-      <c r="I4" s="193"/>
-      <c r="J4" s="193"/>
-      <c r="K4" s="193"/>
+      <c r="I4" s="173"/>
+      <c r="J4" s="173"/>
+      <c r="K4" s="173"/>
       <c r="L4" s="73"/>
     </row>
     <row r="5" spans="1:12" s="62" customFormat="1" ht="25.5">
       <c r="A5" s="107" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="214" t="s">
+      <c r="B5" s="177" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="215"/>
-      <c r="D5" s="216"/>
+      <c r="C5" s="178"/>
+      <c r="D5" s="179"/>
       <c r="E5" s="75"/>
       <c r="F5" s="75"/>
       <c r="G5" s="75"/>
       <c r="H5" s="75"/>
-      <c r="I5" s="217"/>
-      <c r="J5" s="217"/>
-      <c r="K5" s="217"/>
+      <c r="I5" s="180"/>
+      <c r="J5" s="180"/>
+      <c r="K5" s="180"/>
       <c r="L5" s="76"/>
     </row>
     <row r="6" spans="1:12" s="61" customFormat="1" ht="15" customHeight="1">
@@ -10275,9 +10610,9 @@
       <c r="F6" s="72"/>
       <c r="G6" s="72"/>
       <c r="H6" s="72"/>
-      <c r="I6" s="193"/>
-      <c r="J6" s="193"/>
-      <c r="K6" s="193"/>
+      <c r="I6" s="173"/>
+      <c r="J6" s="173"/>
+      <c r="K6" s="173"/>
       <c r="L6" s="73"/>
     </row>
     <row r="7" spans="1:12" s="61" customFormat="1" ht="15" customHeight="1">
@@ -10299,16 +10634,16 @@
       <c r="F7" s="85"/>
       <c r="G7" s="85"/>
       <c r="H7" s="85"/>
-      <c r="I7" s="193"/>
-      <c r="J7" s="193"/>
-      <c r="K7" s="193"/>
+      <c r="I7" s="173"/>
+      <c r="J7" s="173"/>
+      <c r="K7" s="173"/>
       <c r="L7" s="73"/>
     </row>
     <row r="8" spans="1:12" s="61" customFormat="1" ht="15" customHeight="1">
-      <c r="A8" s="194"/>
-      <c r="B8" s="194"/>
-      <c r="C8" s="194"/>
-      <c r="D8" s="194"/>
+      <c r="A8" s="181"/>
+      <c r="B8" s="181"/>
+      <c r="C8" s="181"/>
+      <c r="D8" s="181"/>
       <c r="E8" s="72"/>
       <c r="F8" s="72"/>
       <c r="G8" s="72"/>
@@ -10319,64 +10654,64 @@
       <c r="L8" s="73"/>
     </row>
     <row r="9" spans="1:12" s="63" customFormat="1" ht="12" customHeight="1">
-      <c r="A9" s="197" t="s">
+      <c r="A9" s="187" t="s">
         <v>71</v>
       </c>
-      <c r="B9" s="199" t="s">
+      <c r="B9" s="189" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="197" t="s">
+      <c r="C9" s="187" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="203" t="s">
+      <c r="D9" s="193" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="204"/>
-      <c r="F9" s="204"/>
-      <c r="G9" s="205"/>
-      <c r="H9" s="201" t="s">
+      <c r="E9" s="194"/>
+      <c r="F9" s="194"/>
+      <c r="G9" s="195"/>
+      <c r="H9" s="191" t="s">
         <v>75</v>
       </c>
-      <c r="I9" s="202" t="s">
+      <c r="I9" s="192" t="s">
         <v>76</v>
       </c>
-      <c r="J9" s="202" t="s">
+      <c r="J9" s="192" t="s">
         <v>77</v>
       </c>
-      <c r="K9" s="202" t="s">
+      <c r="K9" s="192" t="s">
         <v>78</v>
       </c>
       <c r="L9" s="87"/>
     </row>
     <row r="10" spans="1:12" s="61" customFormat="1" ht="12" customHeight="1">
-      <c r="A10" s="198"/>
-      <c r="B10" s="200"/>
-      <c r="C10" s="198"/>
-      <c r="D10" s="206"/>
-      <c r="E10" s="207"/>
-      <c r="F10" s="207"/>
-      <c r="G10" s="208"/>
-      <c r="H10" s="197"/>
-      <c r="I10" s="197"/>
-      <c r="J10" s="197"/>
-      <c r="K10" s="197"/>
+      <c r="A10" s="188"/>
+      <c r="B10" s="190"/>
+      <c r="C10" s="188"/>
+      <c r="D10" s="196"/>
+      <c r="E10" s="197"/>
+      <c r="F10" s="197"/>
+      <c r="G10" s="198"/>
+      <c r="H10" s="187"/>
+      <c r="I10" s="187"/>
+      <c r="J10" s="187"/>
+      <c r="K10" s="187"/>
       <c r="L10" s="73"/>
     </row>
     <row r="11" spans="1:12" s="64" customFormat="1" ht="15">
-      <c r="A11" s="195"/>
-      <c r="B11" s="195"/>
-      <c r="C11" s="195"/>
-      <c r="D11" s="195"/>
-      <c r="E11" s="195"/>
-      <c r="F11" s="195"/>
-      <c r="G11" s="195"/>
-      <c r="H11" s="195"/>
-      <c r="I11" s="195"/>
-      <c r="J11" s="195"/>
-      <c r="K11" s="196"/>
+      <c r="A11" s="182"/>
+      <c r="B11" s="182"/>
+      <c r="C11" s="182"/>
+      <c r="D11" s="182"/>
+      <c r="E11" s="182"/>
+      <c r="F11" s="182"/>
+      <c r="G11" s="182"/>
+      <c r="H11" s="182"/>
+      <c r="I11" s="182"/>
+      <c r="J11" s="182"/>
+      <c r="K11" s="183"/>
     </row>
     <row r="12" spans="1:12" s="65" customFormat="1" ht="22.9" customHeight="1">
-      <c r="A12" s="226" t="s">
+      <c r="A12" s="227" t="s">
         <v>357</v>
       </c>
       <c r="B12" s="230"/>
@@ -10400,11 +10735,11 @@
       <c r="C13" s="109" t="s">
         <v>359</v>
       </c>
-      <c r="D13" s="175" t="s">
+      <c r="D13" s="207" t="s">
         <v>360</v>
       </c>
-      <c r="E13" s="176"/>
-      <c r="F13" s="176"/>
+      <c r="E13" s="200"/>
+      <c r="F13" s="200"/>
       <c r="G13" s="95"/>
       <c r="H13" s="94"/>
       <c r="I13" s="96"/>
@@ -10421,11 +10756,11 @@
       <c r="C14" s="111" t="s">
         <v>362</v>
       </c>
-      <c r="D14" s="175" t="s">
+      <c r="D14" s="207" t="s">
         <v>363</v>
       </c>
-      <c r="E14" s="176"/>
-      <c r="F14" s="176"/>
+      <c r="E14" s="200"/>
+      <c r="F14" s="200"/>
       <c r="G14" s="95"/>
       <c r="H14" s="94"/>
       <c r="I14" s="93"/>
@@ -10442,11 +10777,11 @@
       <c r="C15" s="109" t="s">
         <v>365</v>
       </c>
-      <c r="D15" s="175" t="s">
+      <c r="D15" s="207" t="s">
         <v>366</v>
       </c>
-      <c r="E15" s="176"/>
-      <c r="F15" s="176"/>
+      <c r="E15" s="200"/>
+      <c r="F15" s="200"/>
       <c r="G15" s="95"/>
       <c r="H15" s="94"/>
       <c r="I15" s="93"/>
@@ -10454,7 +10789,7 @@
       <c r="K15" s="92"/>
     </row>
     <row r="16" spans="1:12" ht="27" customHeight="1">
-      <c r="A16" s="226" t="s">
+      <c r="A16" s="227" t="s">
         <v>367</v>
       </c>
       <c r="B16" s="185"/>
@@ -10478,11 +10813,11 @@
       <c r="C17" s="111" t="s">
         <v>369</v>
       </c>
-      <c r="D17" s="175" t="s">
+      <c r="D17" s="207" t="s">
         <v>370</v>
       </c>
-      <c r="E17" s="176"/>
-      <c r="F17" s="176"/>
+      <c r="E17" s="200"/>
+      <c r="F17" s="200"/>
       <c r="G17" s="95"/>
       <c r="H17" s="94"/>
       <c r="I17" s="93"/>
@@ -10499,11 +10834,11 @@
       <c r="C18" s="109" t="s">
         <v>372</v>
       </c>
-      <c r="D18" s="175" t="s">
+      <c r="D18" s="207" t="s">
         <v>373</v>
       </c>
-      <c r="E18" s="176"/>
-      <c r="F18" s="176"/>
+      <c r="E18" s="200"/>
+      <c r="F18" s="200"/>
       <c r="G18" s="95"/>
       <c r="H18" s="94"/>
       <c r="I18" s="93"/>
@@ -10520,11 +10855,11 @@
       <c r="C19" s="111" t="s">
         <v>375</v>
       </c>
-      <c r="D19" s="175" t="s">
+      <c r="D19" s="207" t="s">
         <v>376</v>
       </c>
-      <c r="E19" s="176"/>
-      <c r="F19" s="176"/>
+      <c r="E19" s="200"/>
+      <c r="F19" s="200"/>
       <c r="G19" s="95"/>
       <c r="H19" s="94"/>
       <c r="I19" s="93"/>
@@ -10532,19 +10867,19 @@
       <c r="K19" s="92"/>
     </row>
     <row r="20" spans="1:11" ht="28.15" customHeight="1">
-      <c r="A20" s="227" t="s">
+      <c r="A20" s="224" t="s">
         <v>377</v>
       </c>
-      <c r="B20" s="228"/>
-      <c r="C20" s="228"/>
-      <c r="D20" s="228"/>
-      <c r="E20" s="228"/>
-      <c r="F20" s="228"/>
-      <c r="G20" s="228"/>
-      <c r="H20" s="228"/>
-      <c r="I20" s="228"/>
-      <c r="J20" s="228"/>
-      <c r="K20" s="229"/>
+      <c r="B20" s="225"/>
+      <c r="C20" s="225"/>
+      <c r="D20" s="225"/>
+      <c r="E20" s="225"/>
+      <c r="F20" s="225"/>
+      <c r="G20" s="225"/>
+      <c r="H20" s="225"/>
+      <c r="I20" s="225"/>
+      <c r="J20" s="225"/>
+      <c r="K20" s="226"/>
     </row>
     <row r="21" spans="1:11" ht="70.150000000000006" customHeight="1">
       <c r="A21" s="108" t="s">
@@ -10556,11 +10891,11 @@
       <c r="C21" s="109" t="s">
         <v>379</v>
       </c>
-      <c r="D21" s="175" t="s">
+      <c r="D21" s="207" t="s">
         <v>380</v>
       </c>
-      <c r="E21" s="176"/>
-      <c r="F21" s="176"/>
+      <c r="E21" s="200"/>
+      <c r="F21" s="200"/>
       <c r="G21" s="95"/>
       <c r="H21" s="94"/>
       <c r="I21" s="93"/>
@@ -10577,11 +10912,11 @@
       <c r="C22" s="111" t="s">
         <v>382</v>
       </c>
-      <c r="D22" s="175" t="s">
+      <c r="D22" s="207" t="s">
         <v>383</v>
       </c>
-      <c r="E22" s="176"/>
-      <c r="F22" s="176"/>
+      <c r="E22" s="200"/>
+      <c r="F22" s="200"/>
       <c r="G22" s="95"/>
       <c r="H22" s="94"/>
       <c r="I22" s="93"/>
@@ -10598,11 +10933,11 @@
       <c r="C23" s="109" t="s">
         <v>385</v>
       </c>
-      <c r="D23" s="175" t="s">
+      <c r="D23" s="207" t="s">
         <v>386</v>
       </c>
-      <c r="E23" s="176"/>
-      <c r="F23" s="176"/>
+      <c r="E23" s="200"/>
+      <c r="F23" s="200"/>
       <c r="G23" s="95"/>
       <c r="H23" s="94"/>
       <c r="I23" s="93"/>
@@ -10619,11 +10954,11 @@
       <c r="C24" s="111" t="s">
         <v>388</v>
       </c>
-      <c r="D24" s="175" t="s">
+      <c r="D24" s="207" t="s">
         <v>389</v>
       </c>
-      <c r="E24" s="176"/>
-      <c r="F24" s="176"/>
+      <c r="E24" s="200"/>
+      <c r="F24" s="200"/>
       <c r="G24" s="95"/>
       <c r="H24" s="94"/>
       <c r="I24" s="93"/>
@@ -10631,19 +10966,19 @@
       <c r="K24" s="92"/>
     </row>
     <row r="25" spans="1:11" ht="31.15" customHeight="1">
-      <c r="A25" s="227" t="s">
+      <c r="A25" s="224" t="s">
         <v>390</v>
       </c>
-      <c r="B25" s="228"/>
-      <c r="C25" s="228"/>
-      <c r="D25" s="228"/>
-      <c r="E25" s="228"/>
-      <c r="F25" s="228"/>
-      <c r="G25" s="228"/>
-      <c r="H25" s="228"/>
-      <c r="I25" s="228"/>
-      <c r="J25" s="228"/>
-      <c r="K25" s="229"/>
+      <c r="B25" s="225"/>
+      <c r="C25" s="225"/>
+      <c r="D25" s="225"/>
+      <c r="E25" s="225"/>
+      <c r="F25" s="225"/>
+      <c r="G25" s="225"/>
+      <c r="H25" s="225"/>
+      <c r="I25" s="225"/>
+      <c r="J25" s="225"/>
+      <c r="K25" s="226"/>
     </row>
     <row r="26" spans="1:11" ht="70.150000000000006" customHeight="1">
       <c r="A26" s="108" t="s">
@@ -10655,11 +10990,11 @@
       <c r="C26" s="109" t="s">
         <v>392</v>
       </c>
-      <c r="D26" s="175" t="s">
+      <c r="D26" s="207" t="s">
         <v>393</v>
       </c>
-      <c r="E26" s="176"/>
-      <c r="F26" s="176"/>
+      <c r="E26" s="200"/>
+      <c r="F26" s="200"/>
       <c r="G26" s="95"/>
       <c r="H26" s="94"/>
       <c r="I26" s="93"/>
@@ -10676,11 +11011,11 @@
       <c r="C27" s="111" t="s">
         <v>395</v>
       </c>
-      <c r="D27" s="175" t="s">
+      <c r="D27" s="207" t="s">
         <v>396</v>
       </c>
-      <c r="E27" s="176"/>
-      <c r="F27" s="176"/>
+      <c r="E27" s="200"/>
+      <c r="F27" s="200"/>
       <c r="G27" s="95"/>
       <c r="H27" s="94"/>
       <c r="I27" s="93"/>
@@ -10697,11 +11032,11 @@
       <c r="C28" s="109" t="s">
         <v>398</v>
       </c>
-      <c r="D28" s="175" t="s">
+      <c r="D28" s="207" t="s">
         <v>399</v>
       </c>
-      <c r="E28" s="176"/>
-      <c r="F28" s="176"/>
+      <c r="E28" s="200"/>
+      <c r="F28" s="200"/>
       <c r="G28" s="95"/>
       <c r="H28" s="94"/>
       <c r="I28" s="93"/>
@@ -10718,11 +11053,11 @@
       <c r="C29" s="111" t="s">
         <v>401</v>
       </c>
-      <c r="D29" s="175" t="s">
+      <c r="D29" s="207" t="s">
         <v>402</v>
       </c>
-      <c r="E29" s="176"/>
-      <c r="F29" s="176"/>
+      <c r="E29" s="200"/>
+      <c r="F29" s="200"/>
       <c r="G29" s="95"/>
       <c r="H29" s="94"/>
       <c r="I29" s="93"/>
@@ -10733,9 +11068,9 @@
       <c r="A30" s="108"/>
       <c r="B30" s="109"/>
       <c r="C30" s="109"/>
-      <c r="D30" s="175"/>
-      <c r="E30" s="176"/>
-      <c r="F30" s="176"/>
+      <c r="D30" s="207"/>
+      <c r="E30" s="200"/>
+      <c r="F30" s="200"/>
       <c r="G30" s="95"/>
       <c r="H30" s="94"/>
       <c r="I30" s="93"/>
@@ -10746,9 +11081,9 @@
       <c r="A31" s="110"/>
       <c r="B31" s="120"/>
       <c r="C31" s="111"/>
-      <c r="D31" s="175"/>
-      <c r="E31" s="176"/>
-      <c r="F31" s="176"/>
+      <c r="D31" s="207"/>
+      <c r="E31" s="200"/>
+      <c r="F31" s="200"/>
       <c r="G31" s="95"/>
       <c r="H31" s="94"/>
       <c r="I31" s="93"/>
@@ -10759,9 +11094,9 @@
       <c r="A32" s="121"/>
       <c r="B32" s="122"/>
       <c r="C32" s="123"/>
-      <c r="D32" s="224"/>
-      <c r="E32" s="225"/>
-      <c r="F32" s="225"/>
+      <c r="D32" s="228"/>
+      <c r="E32" s="229"/>
+      <c r="F32" s="229"/>
       <c r="G32" s="95"/>
       <c r="H32" s="94"/>
       <c r="I32" s="93"/>
@@ -10772,9 +11107,9 @@
       <c r="A33" s="90"/>
       <c r="B33" s="99"/>
       <c r="C33" s="92"/>
-      <c r="D33" s="224"/>
-      <c r="E33" s="225"/>
-      <c r="F33" s="225"/>
+      <c r="D33" s="228"/>
+      <c r="E33" s="229"/>
+      <c r="F33" s="229"/>
       <c r="G33" s="95"/>
       <c r="H33" s="94"/>
       <c r="I33" s="93"/>
@@ -10785,9 +11120,9 @@
       <c r="A34" s="90"/>
       <c r="B34" s="99"/>
       <c r="C34" s="92"/>
-      <c r="D34" s="224"/>
-      <c r="E34" s="225"/>
-      <c r="F34" s="225"/>
+      <c r="D34" s="228"/>
+      <c r="E34" s="229"/>
+      <c r="F34" s="229"/>
       <c r="G34" s="95"/>
       <c r="H34" s="94"/>
       <c r="I34" s="93"/>
@@ -10798,9 +11133,9 @@
       <c r="A35" s="90"/>
       <c r="B35" s="99"/>
       <c r="C35" s="92"/>
-      <c r="D35" s="224"/>
-      <c r="E35" s="225"/>
-      <c r="F35" s="225"/>
+      <c r="D35" s="228"/>
+      <c r="E35" s="229"/>
+      <c r="F35" s="229"/>
       <c r="G35" s="95"/>
       <c r="H35" s="94"/>
       <c r="I35" s="93"/>
@@ -10811,9 +11146,9 @@
       <c r="A36" s="90"/>
       <c r="B36" s="99"/>
       <c r="C36" s="92"/>
-      <c r="D36" s="224"/>
-      <c r="E36" s="225"/>
-      <c r="F36" s="225"/>
+      <c r="D36" s="228"/>
+      <c r="E36" s="229"/>
+      <c r="F36" s="229"/>
       <c r="G36" s="95"/>
       <c r="H36" s="94"/>
       <c r="I36" s="93"/>
@@ -10824,9 +11159,9 @@
       <c r="A37" s="90"/>
       <c r="B37" s="99"/>
       <c r="C37" s="92"/>
-      <c r="D37" s="224"/>
-      <c r="E37" s="225"/>
-      <c r="F37" s="225"/>
+      <c r="D37" s="228"/>
+      <c r="E37" s="229"/>
+      <c r="F37" s="229"/>
       <c r="G37" s="95"/>
       <c r="H37" s="94"/>
       <c r="I37" s="93"/>
@@ -10837,9 +11172,9 @@
       <c r="A38" s="90"/>
       <c r="B38" s="99"/>
       <c r="C38" s="92"/>
-      <c r="D38" s="224"/>
-      <c r="E38" s="225"/>
-      <c r="F38" s="225"/>
+      <c r="D38" s="228"/>
+      <c r="E38" s="229"/>
+      <c r="F38" s="229"/>
       <c r="G38" s="95"/>
       <c r="H38" s="94"/>
       <c r="I38" s="93"/>
@@ -10850,9 +11185,9 @@
       <c r="A39" s="90"/>
       <c r="B39" s="99"/>
       <c r="C39" s="92"/>
-      <c r="D39" s="224"/>
-      <c r="E39" s="225"/>
-      <c r="F39" s="225"/>
+      <c r="D39" s="228"/>
+      <c r="E39" s="229"/>
+      <c r="F39" s="229"/>
       <c r="G39" s="95"/>
       <c r="H39" s="94"/>
       <c r="I39" s="93"/>
@@ -10863,9 +11198,9 @@
       <c r="A40" s="90"/>
       <c r="B40" s="99"/>
       <c r="C40" s="92"/>
-      <c r="D40" s="224"/>
-      <c r="E40" s="225"/>
-      <c r="F40" s="225"/>
+      <c r="D40" s="228"/>
+      <c r="E40" s="229"/>
+      <c r="F40" s="229"/>
       <c r="G40" s="95"/>
       <c r="H40" s="94"/>
       <c r="I40" s="93"/>
@@ -10876,9 +11211,9 @@
       <c r="A41" s="90"/>
       <c r="B41" s="99"/>
       <c r="C41" s="92"/>
-      <c r="D41" s="224"/>
-      <c r="E41" s="225"/>
-      <c r="F41" s="225"/>
+      <c r="D41" s="228"/>
+      <c r="E41" s="229"/>
+      <c r="F41" s="229"/>
       <c r="G41" s="95"/>
       <c r="H41" s="94"/>
       <c r="I41" s="93"/>
@@ -10889,9 +11224,9 @@
       <c r="A42" s="90"/>
       <c r="B42" s="99"/>
       <c r="C42" s="92"/>
-      <c r="D42" s="224"/>
-      <c r="E42" s="225"/>
-      <c r="F42" s="225"/>
+      <c r="D42" s="228"/>
+      <c r="E42" s="229"/>
+      <c r="F42" s="229"/>
       <c r="G42" s="95"/>
       <c r="H42" s="94"/>
       <c r="I42" s="93"/>
@@ -10902,9 +11237,9 @@
       <c r="A43" s="90"/>
       <c r="B43" s="99"/>
       <c r="C43" s="92"/>
-      <c r="D43" s="224"/>
-      <c r="E43" s="225"/>
-      <c r="F43" s="225"/>
+      <c r="D43" s="228"/>
+      <c r="E43" s="229"/>
+      <c r="F43" s="229"/>
       <c r="G43" s="95"/>
       <c r="H43" s="94"/>
       <c r="I43" s="93"/>
@@ -10915,9 +11250,9 @@
       <c r="A44" s="90"/>
       <c r="B44" s="99"/>
       <c r="C44" s="92"/>
-      <c r="D44" s="224"/>
-      <c r="E44" s="225"/>
-      <c r="F44" s="225"/>
+      <c r="D44" s="228"/>
+      <c r="E44" s="229"/>
+      <c r="F44" s="229"/>
       <c r="G44" s="95"/>
       <c r="H44" s="94"/>
       <c r="I44" s="93"/>
@@ -10928,9 +11263,9 @@
       <c r="A45" s="90"/>
       <c r="B45" s="99"/>
       <c r="C45" s="92"/>
-      <c r="D45" s="224"/>
-      <c r="E45" s="225"/>
-      <c r="F45" s="225"/>
+      <c r="D45" s="228"/>
+      <c r="E45" s="229"/>
+      <c r="F45" s="229"/>
       <c r="G45" s="95"/>
       <c r="H45" s="94"/>
       <c r="I45" s="93"/>
@@ -10941,9 +11276,9 @@
       <c r="A46" s="90"/>
       <c r="B46" s="99"/>
       <c r="C46" s="92"/>
-      <c r="D46" s="224"/>
-      <c r="E46" s="225"/>
-      <c r="F46" s="225"/>
+      <c r="D46" s="228"/>
+      <c r="E46" s="229"/>
+      <c r="F46" s="229"/>
       <c r="G46" s="95"/>
       <c r="H46" s="94"/>
       <c r="I46" s="93"/>
@@ -10954,9 +11289,9 @@
       <c r="A47" s="90"/>
       <c r="B47" s="99"/>
       <c r="C47" s="92"/>
-      <c r="D47" s="224"/>
-      <c r="E47" s="225"/>
-      <c r="F47" s="225"/>
+      <c r="D47" s="228"/>
+      <c r="E47" s="229"/>
+      <c r="F47" s="229"/>
       <c r="G47" s="95"/>
       <c r="H47" s="94"/>
       <c r="I47" s="93"/>
@@ -10967,9 +11302,9 @@
       <c r="A48" s="90"/>
       <c r="B48" s="99"/>
       <c r="C48" s="92"/>
-      <c r="D48" s="224"/>
-      <c r="E48" s="225"/>
-      <c r="F48" s="225"/>
+      <c r="D48" s="228"/>
+      <c r="E48" s="229"/>
+      <c r="F48" s="229"/>
       <c r="G48" s="95"/>
       <c r="H48" s="94"/>
       <c r="I48" s="93"/>
@@ -10982,45 +11317,6 @@
     <row r="52" ht="12" customHeight="1"/>
   </sheetData>
   <mergeCells count="55">
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A11:K11"/>
-    <mergeCell ref="A12:K12"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="K9:K10"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="A16:K16"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="A20:K20"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="A25:K25"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="D36:F36"/>
-    <mergeCell ref="D37:F37"/>
     <mergeCell ref="D48:F48"/>
     <mergeCell ref="A9:A10"/>
     <mergeCell ref="B9:B10"/>
@@ -11037,6 +11333,45 @@
     <mergeCell ref="D40:F40"/>
     <mergeCell ref="D41:F41"/>
     <mergeCell ref="D42:F42"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="A25:K25"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="A20:K20"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="A16:K16"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A11:K11"/>
+    <mergeCell ref="A12:K12"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="K9:K10"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="I5:K5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -11089,52 +11424,52 @@
       <c r="A3" s="70" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="209" t="s">
+      <c r="B3" s="171" t="s">
         <v>62</v>
       </c>
-      <c r="C3" s="209"/>
-      <c r="D3" s="210"/>
+      <c r="C3" s="171"/>
+      <c r="D3" s="172"/>
       <c r="E3" s="71"/>
       <c r="F3" s="71"/>
       <c r="G3" s="71"/>
       <c r="H3" s="71"/>
-      <c r="I3" s="193"/>
-      <c r="J3" s="193"/>
-      <c r="K3" s="193"/>
+      <c r="I3" s="173"/>
+      <c r="J3" s="173"/>
+      <c r="K3" s="173"/>
     </row>
     <row r="4" spans="1:11" ht="13.5" customHeight="1">
       <c r="A4" s="74" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="211" t="s">
+      <c r="B4" s="174" t="s">
         <v>404</v>
       </c>
-      <c r="C4" s="212"/>
-      <c r="D4" s="213"/>
+      <c r="C4" s="175"/>
+      <c r="D4" s="176"/>
       <c r="E4" s="71"/>
       <c r="F4" s="71"/>
       <c r="G4" s="71"/>
       <c r="H4" s="71"/>
-      <c r="I4" s="193"/>
-      <c r="J4" s="193"/>
-      <c r="K4" s="193"/>
+      <c r="I4" s="173"/>
+      <c r="J4" s="173"/>
+      <c r="K4" s="173"/>
     </row>
     <row r="5" spans="1:11" ht="12.75" customHeight="1">
       <c r="A5" s="74" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="214" t="s">
+      <c r="B5" s="177" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="215"/>
-      <c r="D5" s="216"/>
+      <c r="C5" s="178"/>
+      <c r="D5" s="179"/>
       <c r="E5" s="75"/>
       <c r="F5" s="75"/>
       <c r="G5" s="75"/>
       <c r="H5" s="75"/>
-      <c r="I5" s="217"/>
-      <c r="J5" s="217"/>
-      <c r="K5" s="217"/>
+      <c r="I5" s="180"/>
+      <c r="J5" s="180"/>
+      <c r="K5" s="180"/>
     </row>
     <row r="6" spans="1:11" ht="14.25">
       <c r="A6" s="77" t="s">
@@ -11155,9 +11490,9 @@
       <c r="F6" s="72"/>
       <c r="G6" s="72"/>
       <c r="H6" s="72"/>
-      <c r="I6" s="193"/>
-      <c r="J6" s="193"/>
-      <c r="K6" s="193"/>
+      <c r="I6" s="173"/>
+      <c r="J6" s="173"/>
+      <c r="K6" s="173"/>
     </row>
     <row r="7" spans="1:11" ht="14.25">
       <c r="A7" s="81" t="s">
@@ -11178,15 +11513,15 @@
       <c r="F7" s="85"/>
       <c r="G7" s="85"/>
       <c r="H7" s="85"/>
-      <c r="I7" s="193"/>
-      <c r="J7" s="193"/>
-      <c r="K7" s="193"/>
+      <c r="I7" s="173"/>
+      <c r="J7" s="173"/>
+      <c r="K7" s="173"/>
     </row>
     <row r="8" spans="1:11" ht="14.25">
-      <c r="A8" s="194"/>
-      <c r="B8" s="194"/>
-      <c r="C8" s="194"/>
-      <c r="D8" s="194"/>
+      <c r="A8" s="181"/>
+      <c r="B8" s="181"/>
+      <c r="C8" s="181"/>
+      <c r="D8" s="181"/>
       <c r="E8" s="72"/>
       <c r="F8" s="72"/>
       <c r="G8" s="72"/>
@@ -11196,59 +11531,59 @@
       <c r="K8" s="86"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="197" t="s">
+      <c r="A9" s="187" t="s">
         <v>71</v>
       </c>
-      <c r="B9" s="199" t="s">
+      <c r="B9" s="189" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="197" t="s">
+      <c r="C9" s="187" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="203" t="s">
+      <c r="D9" s="193" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="204"/>
-      <c r="F9" s="204"/>
-      <c r="G9" s="205"/>
-      <c r="H9" s="201" t="s">
+      <c r="E9" s="194"/>
+      <c r="F9" s="194"/>
+      <c r="G9" s="195"/>
+      <c r="H9" s="191" t="s">
         <v>75</v>
       </c>
-      <c r="I9" s="202" t="s">
+      <c r="I9" s="192" t="s">
         <v>76</v>
       </c>
-      <c r="J9" s="202" t="s">
+      <c r="J9" s="192" t="s">
         <v>77</v>
       </c>
-      <c r="K9" s="202" t="s">
+      <c r="K9" s="192" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="198"/>
-      <c r="B10" s="200"/>
-      <c r="C10" s="198"/>
-      <c r="D10" s="206"/>
-      <c r="E10" s="207"/>
-      <c r="F10" s="207"/>
-      <c r="G10" s="208"/>
-      <c r="H10" s="197"/>
-      <c r="I10" s="197"/>
-      <c r="J10" s="197"/>
-      <c r="K10" s="197"/>
+      <c r="A10" s="188"/>
+      <c r="B10" s="190"/>
+      <c r="C10" s="188"/>
+      <c r="D10" s="196"/>
+      <c r="E10" s="197"/>
+      <c r="F10" s="197"/>
+      <c r="G10" s="198"/>
+      <c r="H10" s="187"/>
+      <c r="I10" s="187"/>
+      <c r="J10" s="187"/>
+      <c r="K10" s="187"/>
     </row>
     <row r="11" spans="1:11" ht="15">
-      <c r="A11" s="195"/>
-      <c r="B11" s="195"/>
-      <c r="C11" s="195"/>
-      <c r="D11" s="195"/>
-      <c r="E11" s="195"/>
-      <c r="F11" s="195"/>
-      <c r="G11" s="195"/>
-      <c r="H11" s="195"/>
-      <c r="I11" s="195"/>
-      <c r="J11" s="195"/>
-      <c r="K11" s="196"/>
+      <c r="A11" s="182"/>
+      <c r="B11" s="182"/>
+      <c r="C11" s="182"/>
+      <c r="D11" s="182"/>
+      <c r="E11" s="182"/>
+      <c r="F11" s="182"/>
+      <c r="G11" s="182"/>
+      <c r="H11" s="182"/>
+      <c r="I11" s="182"/>
+      <c r="J11" s="182"/>
+      <c r="K11" s="183"/>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="184" t="s">
@@ -11481,12 +11816,16 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="D17:F17"/>
     <mergeCell ref="I6:K6"/>
     <mergeCell ref="I7:K7"/>
     <mergeCell ref="A8:D8"/>
@@ -11500,16 +11839,12 @@
     <mergeCell ref="J9:J10"/>
     <mergeCell ref="K9:K10"/>
     <mergeCell ref="D9:G10"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="I5:K5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -11567,54 +11902,54 @@
       <c r="A3" s="106" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="209" t="s">
+      <c r="B3" s="171" t="s">
         <v>62</v>
       </c>
-      <c r="C3" s="209"/>
-      <c r="D3" s="210"/>
+      <c r="C3" s="171"/>
+      <c r="D3" s="172"/>
       <c r="E3" s="71"/>
       <c r="F3" s="71"/>
       <c r="G3" s="71"/>
       <c r="H3" s="71"/>
-      <c r="I3" s="193"/>
-      <c r="J3" s="193"/>
-      <c r="K3" s="193"/>
+      <c r="I3" s="173"/>
+      <c r="J3" s="173"/>
+      <c r="K3" s="173"/>
       <c r="L3" s="73"/>
     </row>
     <row r="4" spans="1:12" s="61" customFormat="1" ht="13.15" customHeight="1">
       <c r="A4" s="74" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="211" t="s">
+      <c r="B4" s="174" t="s">
         <v>431</v>
       </c>
-      <c r="C4" s="212"/>
-      <c r="D4" s="213"/>
+      <c r="C4" s="175"/>
+      <c r="D4" s="176"/>
       <c r="E4" s="71"/>
       <c r="F4" s="71"/>
       <c r="G4" s="71"/>
       <c r="H4" s="71"/>
-      <c r="I4" s="193"/>
-      <c r="J4" s="193"/>
-      <c r="K4" s="193"/>
+      <c r="I4" s="173"/>
+      <c r="J4" s="173"/>
+      <c r="K4" s="173"/>
       <c r="L4" s="73"/>
     </row>
     <row r="5" spans="1:12" s="62" customFormat="1" ht="25.5">
       <c r="A5" s="107" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="214" t="s">
+      <c r="B5" s="177" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="215"/>
-      <c r="D5" s="216"/>
+      <c r="C5" s="178"/>
+      <c r="D5" s="179"/>
       <c r="E5" s="75"/>
       <c r="F5" s="75"/>
       <c r="G5" s="75"/>
       <c r="H5" s="75"/>
-      <c r="I5" s="217"/>
-      <c r="J5" s="217"/>
-      <c r="K5" s="217"/>
+      <c r="I5" s="180"/>
+      <c r="J5" s="180"/>
+      <c r="K5" s="180"/>
       <c r="L5" s="76"/>
     </row>
     <row r="6" spans="1:12" s="61" customFormat="1" ht="15" customHeight="1">
@@ -11636,9 +11971,9 @@
       <c r="F6" s="72"/>
       <c r="G6" s="72"/>
       <c r="H6" s="72"/>
-      <c r="I6" s="193"/>
-      <c r="J6" s="193"/>
-      <c r="K6" s="193"/>
+      <c r="I6" s="173"/>
+      <c r="J6" s="173"/>
+      <c r="K6" s="173"/>
       <c r="L6" s="73"/>
     </row>
     <row r="7" spans="1:12" s="61" customFormat="1" ht="15" customHeight="1">
@@ -11660,16 +11995,16 @@
       <c r="F7" s="85"/>
       <c r="G7" s="85"/>
       <c r="H7" s="85"/>
-      <c r="I7" s="193"/>
-      <c r="J7" s="193"/>
-      <c r="K7" s="193"/>
+      <c r="I7" s="173"/>
+      <c r="J7" s="173"/>
+      <c r="K7" s="173"/>
       <c r="L7" s="73"/>
     </row>
     <row r="8" spans="1:12" s="61" customFormat="1" ht="15" customHeight="1">
-      <c r="A8" s="194"/>
-      <c r="B8" s="194"/>
-      <c r="C8" s="194"/>
-      <c r="D8" s="194"/>
+      <c r="A8" s="181"/>
+      <c r="B8" s="181"/>
+      <c r="C8" s="181"/>
+      <c r="D8" s="181"/>
       <c r="F8" s="72"/>
       <c r="G8" s="72"/>
       <c r="H8" s="72"/>
@@ -11679,61 +12014,61 @@
       <c r="L8" s="73"/>
     </row>
     <row r="9" spans="1:12" s="63" customFormat="1" ht="12" customHeight="1">
-      <c r="A9" s="197" t="s">
+      <c r="A9" s="187" t="s">
         <v>71</v>
       </c>
-      <c r="B9" s="199" t="s">
+      <c r="B9" s="189" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="197" t="s">
+      <c r="C9" s="187" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="203" t="s">
+      <c r="D9" s="193" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="204"/>
-      <c r="F9" s="204"/>
-      <c r="G9" s="205"/>
-      <c r="H9" s="201" t="s">
+      <c r="E9" s="194"/>
+      <c r="F9" s="194"/>
+      <c r="G9" s="195"/>
+      <c r="H9" s="191" t="s">
         <v>75</v>
       </c>
-      <c r="I9" s="202" t="s">
+      <c r="I9" s="192" t="s">
         <v>76</v>
       </c>
-      <c r="J9" s="202" t="s">
+      <c r="J9" s="192" t="s">
         <v>77</v>
       </c>
-      <c r="K9" s="202" t="s">
+      <c r="K9" s="192" t="s">
         <v>78</v>
       </c>
       <c r="L9" s="87"/>
     </row>
     <row r="10" spans="1:12" s="61" customFormat="1" ht="12" customHeight="1">
-      <c r="A10" s="198"/>
-      <c r="B10" s="200"/>
-      <c r="C10" s="198"/>
-      <c r="D10" s="206"/>
-      <c r="E10" s="207"/>
-      <c r="F10" s="207"/>
-      <c r="G10" s="208"/>
-      <c r="H10" s="197"/>
-      <c r="I10" s="197"/>
-      <c r="J10" s="197"/>
-      <c r="K10" s="197"/>
+      <c r="A10" s="188"/>
+      <c r="B10" s="190"/>
+      <c r="C10" s="188"/>
+      <c r="D10" s="196"/>
+      <c r="E10" s="197"/>
+      <c r="F10" s="197"/>
+      <c r="G10" s="198"/>
+      <c r="H10" s="187"/>
+      <c r="I10" s="187"/>
+      <c r="J10" s="187"/>
+      <c r="K10" s="187"/>
       <c r="L10" s="73"/>
     </row>
     <row r="11" spans="1:12" s="64" customFormat="1" ht="15">
-      <c r="A11" s="195"/>
-      <c r="B11" s="195"/>
-      <c r="C11" s="195"/>
-      <c r="D11" s="195"/>
-      <c r="E11" s="195"/>
-      <c r="F11" s="195"/>
-      <c r="G11" s="195"/>
-      <c r="H11" s="195"/>
-      <c r="I11" s="195"/>
-      <c r="J11" s="195"/>
-      <c r="K11" s="196"/>
+      <c r="A11" s="182"/>
+      <c r="B11" s="182"/>
+      <c r="C11" s="182"/>
+      <c r="D11" s="182"/>
+      <c r="E11" s="182"/>
+      <c r="F11" s="182"/>
+      <c r="G11" s="182"/>
+      <c r="H11" s="182"/>
+      <c r="I11" s="182"/>
+      <c r="J11" s="182"/>
+      <c r="K11" s="183"/>
     </row>
     <row r="12" spans="1:12" s="65" customFormat="1" ht="29.45" customHeight="1">
       <c r="A12" s="237" t="s">
@@ -11760,11 +12095,11 @@
       <c r="C13" s="109" t="s">
         <v>434</v>
       </c>
-      <c r="D13" s="175" t="s">
+      <c r="D13" s="207" t="s">
         <v>435</v>
       </c>
-      <c r="E13" s="176"/>
-      <c r="F13" s="176"/>
+      <c r="E13" s="200"/>
+      <c r="F13" s="200"/>
       <c r="G13" s="95"/>
       <c r="H13" s="94"/>
       <c r="I13" s="96"/>
@@ -11781,11 +12116,11 @@
       <c r="C14" s="111" t="s">
         <v>437</v>
       </c>
-      <c r="D14" s="175" t="s">
+      <c r="D14" s="207" t="s">
         <v>438</v>
       </c>
-      <c r="E14" s="176"/>
-      <c r="F14" s="176"/>
+      <c r="E14" s="200"/>
+      <c r="F14" s="200"/>
       <c r="G14" s="95"/>
       <c r="H14" s="94"/>
       <c r="I14" s="93"/>
@@ -11802,11 +12137,11 @@
       <c r="C15" s="109" t="s">
         <v>440</v>
       </c>
-      <c r="D15" s="175" t="s">
+      <c r="D15" s="207" t="s">
         <v>441</v>
       </c>
-      <c r="E15" s="176"/>
-      <c r="F15" s="176"/>
+      <c r="E15" s="200"/>
+      <c r="F15" s="200"/>
       <c r="G15" s="95"/>
       <c r="H15" s="94"/>
       <c r="I15" s="93"/>
@@ -11838,11 +12173,11 @@
       <c r="C17" s="111" t="s">
         <v>444</v>
       </c>
-      <c r="D17" s="175" t="s">
+      <c r="D17" s="207" t="s">
         <v>445</v>
       </c>
-      <c r="E17" s="176"/>
-      <c r="F17" s="176"/>
+      <c r="E17" s="200"/>
+      <c r="F17" s="200"/>
       <c r="G17" s="95"/>
       <c r="H17" s="94"/>
       <c r="I17" s="93"/>
@@ -11859,11 +12194,11 @@
       <c r="C18" s="109" t="s">
         <v>447</v>
       </c>
-      <c r="D18" s="175" t="s">
+      <c r="D18" s="207" t="s">
         <v>448</v>
       </c>
-      <c r="E18" s="176"/>
-      <c r="F18" s="176"/>
+      <c r="E18" s="200"/>
+      <c r="F18" s="200"/>
       <c r="G18" s="95"/>
       <c r="H18" s="94"/>
       <c r="I18" s="93"/>
@@ -11880,11 +12215,11 @@
       <c r="C19" s="111" t="s">
         <v>450</v>
       </c>
-      <c r="D19" s="175" t="s">
+      <c r="D19" s="207" t="s">
         <v>451</v>
       </c>
-      <c r="E19" s="176"/>
-      <c r="F19" s="176"/>
+      <c r="E19" s="200"/>
+      <c r="F19" s="200"/>
       <c r="G19" s="95"/>
       <c r="H19" s="94"/>
       <c r="I19" s="93"/>
@@ -11901,11 +12236,11 @@
       <c r="C20" s="109" t="s">
         <v>453</v>
       </c>
-      <c r="D20" s="175" t="s">
+      <c r="D20" s="207" t="s">
         <v>454</v>
       </c>
-      <c r="E20" s="176"/>
-      <c r="F20" s="176"/>
+      <c r="E20" s="200"/>
+      <c r="F20" s="200"/>
       <c r="G20" s="95"/>
       <c r="H20" s="94"/>
       <c r="I20" s="93"/>
@@ -11922,11 +12257,11 @@
       <c r="C21" s="111" t="s">
         <v>456</v>
       </c>
-      <c r="D21" s="175" t="s">
+      <c r="D21" s="207" t="s">
         <v>457</v>
       </c>
-      <c r="E21" s="176"/>
-      <c r="F21" s="176"/>
+      <c r="E21" s="200"/>
+      <c r="F21" s="200"/>
       <c r="G21" s="95"/>
       <c r="H21" s="94"/>
       <c r="I21" s="93"/>
@@ -11958,11 +12293,11 @@
       <c r="C23" s="109" t="s">
         <v>460</v>
       </c>
-      <c r="D23" s="175" t="s">
+      <c r="D23" s="207" t="s">
         <v>461</v>
       </c>
-      <c r="E23" s="176"/>
-      <c r="F23" s="176"/>
+      <c r="E23" s="200"/>
+      <c r="F23" s="200"/>
       <c r="G23" s="95"/>
       <c r="H23" s="94"/>
       <c r="I23" s="93"/>
@@ -11979,11 +12314,11 @@
       <c r="C24" s="111" t="s">
         <v>463</v>
       </c>
-      <c r="D24" s="175" t="s">
+      <c r="D24" s="207" t="s">
         <v>464</v>
       </c>
-      <c r="E24" s="176"/>
-      <c r="F24" s="176"/>
+      <c r="E24" s="200"/>
+      <c r="F24" s="200"/>
       <c r="G24" s="95"/>
       <c r="H24" s="94"/>
       <c r="I24" s="93"/>
@@ -12000,11 +12335,11 @@
       <c r="C25" s="109" t="s">
         <v>466</v>
       </c>
-      <c r="D25" s="175" t="s">
+      <c r="D25" s="207" t="s">
         <v>467</v>
       </c>
-      <c r="E25" s="176"/>
-      <c r="F25" s="176"/>
+      <c r="E25" s="200"/>
+      <c r="F25" s="200"/>
       <c r="G25" s="95"/>
       <c r="H25" s="94"/>
       <c r="I25" s="93"/>
@@ -12021,11 +12356,11 @@
       <c r="C26" s="111" t="s">
         <v>469</v>
       </c>
-      <c r="D26" s="175" t="s">
+      <c r="D26" s="207" t="s">
         <v>470</v>
       </c>
-      <c r="E26" s="176"/>
-      <c r="F26" s="176"/>
+      <c r="E26" s="200"/>
+      <c r="F26" s="200"/>
       <c r="G26" s="95"/>
       <c r="H26" s="94"/>
       <c r="I26" s="93"/>
@@ -12042,11 +12377,11 @@
       <c r="C27" s="109" t="s">
         <v>472</v>
       </c>
-      <c r="D27" s="175" t="s">
+      <c r="D27" s="207" t="s">
         <v>473</v>
       </c>
-      <c r="E27" s="176"/>
-      <c r="F27" s="176"/>
+      <c r="E27" s="200"/>
+      <c r="F27" s="200"/>
       <c r="G27" s="95"/>
       <c r="H27" s="94"/>
       <c r="I27" s="93"/>
@@ -12063,11 +12398,11 @@
       <c r="C28" s="111" t="s">
         <v>475</v>
       </c>
-      <c r="D28" s="175" t="s">
+      <c r="D28" s="207" t="s">
         <v>476</v>
       </c>
-      <c r="E28" s="176"/>
-      <c r="F28" s="176"/>
+      <c r="E28" s="200"/>
+      <c r="F28" s="200"/>
       <c r="G28" s="95"/>
       <c r="H28" s="94"/>
       <c r="I28" s="93"/>
@@ -12084,11 +12419,11 @@
       <c r="C29" s="109" t="s">
         <v>478</v>
       </c>
-      <c r="D29" s="175" t="s">
+      <c r="D29" s="207" t="s">
         <v>479</v>
       </c>
-      <c r="E29" s="176"/>
-      <c r="F29" s="176"/>
+      <c r="E29" s="200"/>
+      <c r="F29" s="200"/>
       <c r="G29" s="95"/>
       <c r="H29" s="94"/>
       <c r="I29" s="93"/>
@@ -12120,11 +12455,11 @@
       <c r="C31" s="111" t="s">
         <v>482</v>
       </c>
-      <c r="D31" s="175" t="s">
+      <c r="D31" s="207" t="s">
         <v>483</v>
       </c>
-      <c r="E31" s="176"/>
-      <c r="F31" s="176"/>
+      <c r="E31" s="200"/>
+      <c r="F31" s="200"/>
       <c r="G31" s="95"/>
       <c r="H31" s="94"/>
       <c r="I31" s="93"/>
@@ -12141,11 +12476,11 @@
       <c r="C32" s="109" t="s">
         <v>485</v>
       </c>
-      <c r="D32" s="175" t="s">
+      <c r="D32" s="207" t="s">
         <v>486</v>
       </c>
-      <c r="E32" s="176"/>
-      <c r="F32" s="176"/>
+      <c r="E32" s="200"/>
+      <c r="F32" s="200"/>
       <c r="G32" s="95"/>
       <c r="H32" s="94"/>
       <c r="I32" s="93"/>
@@ -12156,9 +12491,9 @@
       <c r="A33" s="90"/>
       <c r="B33" s="99"/>
       <c r="C33" s="92"/>
-      <c r="D33" s="224"/>
-      <c r="E33" s="225"/>
-      <c r="F33" s="225"/>
+      <c r="D33" s="228"/>
+      <c r="E33" s="229"/>
+      <c r="F33" s="229"/>
       <c r="G33" s="95"/>
       <c r="H33" s="94"/>
       <c r="I33" s="93"/>
@@ -12169,9 +12504,9 @@
       <c r="A34" s="90"/>
       <c r="B34" s="99"/>
       <c r="C34" s="92"/>
-      <c r="D34" s="224"/>
-      <c r="E34" s="225"/>
-      <c r="F34" s="225"/>
+      <c r="D34" s="228"/>
+      <c r="E34" s="229"/>
+      <c r="F34" s="229"/>
       <c r="G34" s="95"/>
       <c r="H34" s="94"/>
       <c r="I34" s="93"/>
@@ -12182,9 +12517,9 @@
       <c r="A35" s="90"/>
       <c r="B35" s="99"/>
       <c r="C35" s="92"/>
-      <c r="D35" s="224"/>
-      <c r="E35" s="225"/>
-      <c r="F35" s="225"/>
+      <c r="D35" s="228"/>
+      <c r="E35" s="229"/>
+      <c r="F35" s="229"/>
       <c r="G35" s="95"/>
       <c r="H35" s="94"/>
       <c r="I35" s="93"/>
@@ -12195,9 +12530,9 @@
       <c r="A36" s="90"/>
       <c r="B36" s="99"/>
       <c r="C36" s="92"/>
-      <c r="D36" s="224"/>
-      <c r="E36" s="225"/>
-      <c r="F36" s="225"/>
+      <c r="D36" s="228"/>
+      <c r="E36" s="229"/>
+      <c r="F36" s="229"/>
       <c r="G36" s="95"/>
       <c r="H36" s="94"/>
       <c r="I36" s="93"/>
@@ -12208,9 +12543,9 @@
       <c r="A37" s="90"/>
       <c r="B37" s="99"/>
       <c r="C37" s="92"/>
-      <c r="D37" s="224"/>
-      <c r="E37" s="225"/>
-      <c r="F37" s="225"/>
+      <c r="D37" s="228"/>
+      <c r="E37" s="229"/>
+      <c r="F37" s="229"/>
       <c r="G37" s="95"/>
       <c r="H37" s="94"/>
       <c r="I37" s="93"/>
@@ -12221,9 +12556,9 @@
       <c r="A38" s="90"/>
       <c r="B38" s="99"/>
       <c r="C38" s="92"/>
-      <c r="D38" s="224"/>
-      <c r="E38" s="225"/>
-      <c r="F38" s="225"/>
+      <c r="D38" s="228"/>
+      <c r="E38" s="229"/>
+      <c r="F38" s="229"/>
       <c r="G38" s="95"/>
       <c r="H38" s="94"/>
       <c r="I38" s="93"/>
@@ -12234,9 +12569,9 @@
       <c r="A39" s="90"/>
       <c r="B39" s="99"/>
       <c r="C39" s="92"/>
-      <c r="D39" s="224"/>
-      <c r="E39" s="225"/>
-      <c r="F39" s="225"/>
+      <c r="D39" s="228"/>
+      <c r="E39" s="229"/>
+      <c r="F39" s="229"/>
       <c r="G39" s="95"/>
       <c r="H39" s="94"/>
       <c r="I39" s="93"/>
@@ -12247,9 +12582,9 @@
       <c r="A40" s="90"/>
       <c r="B40" s="99"/>
       <c r="C40" s="92"/>
-      <c r="D40" s="224"/>
-      <c r="E40" s="225"/>
-      <c r="F40" s="225"/>
+      <c r="D40" s="228"/>
+      <c r="E40" s="229"/>
+      <c r="F40" s="229"/>
       <c r="G40" s="95"/>
       <c r="H40" s="94"/>
       <c r="I40" s="93"/>
@@ -12260,9 +12595,9 @@
       <c r="A41" s="90"/>
       <c r="B41" s="99"/>
       <c r="C41" s="92"/>
-      <c r="D41" s="224"/>
-      <c r="E41" s="225"/>
-      <c r="F41" s="225"/>
+      <c r="D41" s="228"/>
+      <c r="E41" s="229"/>
+      <c r="F41" s="229"/>
       <c r="G41" s="95"/>
       <c r="H41" s="94"/>
       <c r="I41" s="93"/>
@@ -12273,9 +12608,9 @@
       <c r="A42" s="90"/>
       <c r="B42" s="99"/>
       <c r="C42" s="92"/>
-      <c r="D42" s="224"/>
-      <c r="E42" s="225"/>
-      <c r="F42" s="225"/>
+      <c r="D42" s="228"/>
+      <c r="E42" s="229"/>
+      <c r="F42" s="229"/>
       <c r="G42" s="95"/>
       <c r="H42" s="94"/>
       <c r="I42" s="93"/>
@@ -12286,9 +12621,9 @@
       <c r="A43" s="90"/>
       <c r="B43" s="99"/>
       <c r="C43" s="92"/>
-      <c r="D43" s="224"/>
-      <c r="E43" s="225"/>
-      <c r="F43" s="225"/>
+      <c r="D43" s="228"/>
+      <c r="E43" s="229"/>
+      <c r="F43" s="229"/>
       <c r="G43" s="95"/>
       <c r="H43" s="94"/>
       <c r="I43" s="93"/>
@@ -12299,9 +12634,9 @@
       <c r="A44" s="90"/>
       <c r="B44" s="99"/>
       <c r="C44" s="92"/>
-      <c r="D44" s="224"/>
-      <c r="E44" s="225"/>
-      <c r="F44" s="225"/>
+      <c r="D44" s="228"/>
+      <c r="E44" s="229"/>
+      <c r="F44" s="229"/>
       <c r="G44" s="95"/>
       <c r="H44" s="94"/>
       <c r="I44" s="93"/>
@@ -12312,9 +12647,9 @@
       <c r="A45" s="90"/>
       <c r="B45" s="99"/>
       <c r="C45" s="92"/>
-      <c r="D45" s="224"/>
-      <c r="E45" s="225"/>
-      <c r="F45" s="225"/>
+      <c r="D45" s="228"/>
+      <c r="E45" s="229"/>
+      <c r="F45" s="229"/>
       <c r="G45" s="95"/>
       <c r="H45" s="94"/>
       <c r="I45" s="93"/>
@@ -12325,9 +12660,9 @@
       <c r="A46" s="90"/>
       <c r="B46" s="99"/>
       <c r="C46" s="92"/>
-      <c r="D46" s="224"/>
-      <c r="E46" s="225"/>
-      <c r="F46" s="225"/>
+      <c r="D46" s="228"/>
+      <c r="E46" s="229"/>
+      <c r="F46" s="229"/>
       <c r="G46" s="95"/>
       <c r="H46" s="94"/>
       <c r="I46" s="93"/>
@@ -12338,9 +12673,9 @@
       <c r="A47" s="90"/>
       <c r="B47" s="99"/>
       <c r="C47" s="92"/>
-      <c r="D47" s="224"/>
-      <c r="E47" s="225"/>
-      <c r="F47" s="225"/>
+      <c r="D47" s="228"/>
+      <c r="E47" s="229"/>
+      <c r="F47" s="229"/>
       <c r="G47" s="95"/>
       <c r="H47" s="94"/>
       <c r="I47" s="93"/>
@@ -12351,9 +12686,9 @@
       <c r="A48" s="90"/>
       <c r="B48" s="99"/>
       <c r="C48" s="92"/>
-      <c r="D48" s="224"/>
-      <c r="E48" s="225"/>
-      <c r="F48" s="225"/>
+      <c r="D48" s="228"/>
+      <c r="E48" s="229"/>
+      <c r="F48" s="229"/>
       <c r="G48" s="95"/>
       <c r="H48" s="94"/>
       <c r="I48" s="93"/>
@@ -12364,9 +12699,9 @@
       <c r="A49" s="90"/>
       <c r="B49" s="99"/>
       <c r="C49" s="92"/>
-      <c r="D49" s="224"/>
-      <c r="E49" s="225"/>
-      <c r="F49" s="225"/>
+      <c r="D49" s="228"/>
+      <c r="E49" s="229"/>
+      <c r="F49" s="229"/>
       <c r="G49" s="95"/>
       <c r="H49" s="94"/>
       <c r="I49" s="93"/>
@@ -12377,9 +12712,9 @@
       <c r="A50" s="90"/>
       <c r="B50" s="99"/>
       <c r="C50" s="92"/>
-      <c r="D50" s="224"/>
-      <c r="E50" s="225"/>
-      <c r="F50" s="225"/>
+      <c r="D50" s="228"/>
+      <c r="E50" s="229"/>
+      <c r="F50" s="229"/>
       <c r="G50" s="95"/>
       <c r="H50" s="94"/>
       <c r="I50" s="93"/>
@@ -12390,9 +12725,9 @@
       <c r="A51" s="90"/>
       <c r="B51" s="99"/>
       <c r="C51" s="92"/>
-      <c r="D51" s="224"/>
-      <c r="E51" s="225"/>
-      <c r="F51" s="225"/>
+      <c r="D51" s="228"/>
+      <c r="E51" s="229"/>
+      <c r="F51" s="229"/>
       <c r="G51" s="95"/>
       <c r="H51" s="94"/>
       <c r="I51" s="93"/>
@@ -12403,9 +12738,9 @@
       <c r="A52" s="90"/>
       <c r="B52" s="99"/>
       <c r="C52" s="92"/>
-      <c r="D52" s="224"/>
-      <c r="E52" s="225"/>
-      <c r="F52" s="225"/>
+      <c r="D52" s="228"/>
+      <c r="E52" s="229"/>
+      <c r="F52" s="229"/>
       <c r="G52" s="95"/>
       <c r="H52" s="94"/>
       <c r="I52" s="93"/>
@@ -12416,9 +12751,9 @@
       <c r="A53" s="90"/>
       <c r="B53" s="99"/>
       <c r="C53" s="92"/>
-      <c r="D53" s="224"/>
-      <c r="E53" s="225"/>
-      <c r="F53" s="225"/>
+      <c r="D53" s="228"/>
+      <c r="E53" s="229"/>
+      <c r="F53" s="229"/>
       <c r="G53" s="95"/>
       <c r="H53" s="94"/>
       <c r="I53" s="93"/>
@@ -12429,9 +12764,9 @@
       <c r="A54" s="90"/>
       <c r="B54" s="99"/>
       <c r="C54" s="92"/>
-      <c r="D54" s="224"/>
-      <c r="E54" s="225"/>
-      <c r="F54" s="225"/>
+      <c r="D54" s="228"/>
+      <c r="E54" s="229"/>
+      <c r="F54" s="229"/>
       <c r="G54" s="95"/>
       <c r="H54" s="94"/>
       <c r="I54" s="93"/>
@@ -12442,9 +12777,9 @@
       <c r="A55" s="90"/>
       <c r="B55" s="99"/>
       <c r="C55" s="92"/>
-      <c r="D55" s="224"/>
-      <c r="E55" s="225"/>
-      <c r="F55" s="225"/>
+      <c r="D55" s="228"/>
+      <c r="E55" s="229"/>
+      <c r="F55" s="229"/>
       <c r="G55" s="95"/>
       <c r="H55" s="94"/>
       <c r="I55" s="93"/>
@@ -12455,9 +12790,9 @@
       <c r="A56" s="90"/>
       <c r="B56" s="99"/>
       <c r="C56" s="92"/>
-      <c r="D56" s="224"/>
-      <c r="E56" s="225"/>
-      <c r="F56" s="225"/>
+      <c r="D56" s="228"/>
+      <c r="E56" s="229"/>
+      <c r="F56" s="229"/>
       <c r="G56" s="95"/>
       <c r="H56" s="94"/>
       <c r="I56" s="93"/>
@@ -12468,9 +12803,9 @@
       <c r="A57" s="90"/>
       <c r="B57" s="99"/>
       <c r="C57" s="92"/>
-      <c r="D57" s="224"/>
-      <c r="E57" s="225"/>
-      <c r="F57" s="225"/>
+      <c r="D57" s="228"/>
+      <c r="E57" s="229"/>
+      <c r="F57" s="229"/>
       <c r="G57" s="95"/>
       <c r="H57" s="94"/>
       <c r="I57" s="93"/>
@@ -12481,9 +12816,9 @@
       <c r="A58" s="90"/>
       <c r="B58" s="99"/>
       <c r="C58" s="92"/>
-      <c r="D58" s="224"/>
-      <c r="E58" s="225"/>
-      <c r="F58" s="225"/>
+      <c r="D58" s="228"/>
+      <c r="E58" s="229"/>
+      <c r="F58" s="229"/>
       <c r="G58" s="95"/>
       <c r="H58" s="94"/>
       <c r="I58" s="93"/>
@@ -12494,9 +12829,9 @@
       <c r="A59" s="90"/>
       <c r="B59" s="99"/>
       <c r="C59" s="92"/>
-      <c r="D59" s="224"/>
-      <c r="E59" s="225"/>
-      <c r="F59" s="225"/>
+      <c r="D59" s="228"/>
+      <c r="E59" s="229"/>
+      <c r="F59" s="229"/>
       <c r="G59" s="95"/>
       <c r="H59" s="94"/>
       <c r="I59" s="93"/>
@@ -12507,9 +12842,9 @@
       <c r="A60" s="90"/>
       <c r="B60" s="99"/>
       <c r="C60" s="92"/>
-      <c r="D60" s="224"/>
-      <c r="E60" s="225"/>
-      <c r="F60" s="225"/>
+      <c r="D60" s="228"/>
+      <c r="E60" s="229"/>
+      <c r="F60" s="229"/>
       <c r="G60" s="95"/>
       <c r="H60" s="94"/>
       <c r="I60" s="93"/>
@@ -12520,9 +12855,9 @@
       <c r="A61" s="90"/>
       <c r="B61" s="99"/>
       <c r="C61" s="92"/>
-      <c r="D61" s="224"/>
-      <c r="E61" s="225"/>
-      <c r="F61" s="225"/>
+      <c r="D61" s="228"/>
+      <c r="E61" s="229"/>
+      <c r="F61" s="229"/>
       <c r="G61" s="95"/>
       <c r="H61" s="94"/>
       <c r="I61" s="93"/>
@@ -12533,9 +12868,9 @@
       <c r="A62" s="90"/>
       <c r="B62" s="99"/>
       <c r="C62" s="92"/>
-      <c r="D62" s="224"/>
-      <c r="E62" s="225"/>
-      <c r="F62" s="225"/>
+      <c r="D62" s="228"/>
+      <c r="E62" s="229"/>
+      <c r="F62" s="229"/>
       <c r="G62" s="95"/>
       <c r="H62" s="94"/>
       <c r="I62" s="93"/>
@@ -12546,9 +12881,9 @@
       <c r="A63" s="90"/>
       <c r="B63" s="99"/>
       <c r="C63" s="92"/>
-      <c r="D63" s="224"/>
-      <c r="E63" s="225"/>
-      <c r="F63" s="225"/>
+      <c r="D63" s="228"/>
+      <c r="E63" s="229"/>
+      <c r="F63" s="229"/>
       <c r="G63" s="95"/>
       <c r="H63" s="94"/>
       <c r="I63" s="93"/>
@@ -12559,9 +12894,9 @@
       <c r="A64" s="90"/>
       <c r="B64" s="99"/>
       <c r="C64" s="92"/>
-      <c r="D64" s="224"/>
-      <c r="E64" s="225"/>
-      <c r="F64" s="225"/>
+      <c r="D64" s="228"/>
+      <c r="E64" s="229"/>
+      <c r="F64" s="229"/>
       <c r="G64" s="95"/>
       <c r="H64" s="94"/>
       <c r="I64" s="93"/>
@@ -12572,9 +12907,9 @@
       <c r="A65" s="90"/>
       <c r="B65" s="99"/>
       <c r="C65" s="92"/>
-      <c r="D65" s="224"/>
-      <c r="E65" s="225"/>
-      <c r="F65" s="225"/>
+      <c r="D65" s="228"/>
+      <c r="E65" s="229"/>
+      <c r="F65" s="229"/>
       <c r="G65" s="95"/>
       <c r="H65" s="94"/>
       <c r="I65" s="93"/>
@@ -12585,9 +12920,9 @@
       <c r="A66" s="90"/>
       <c r="B66" s="99"/>
       <c r="C66" s="92"/>
-      <c r="D66" s="224"/>
-      <c r="E66" s="225"/>
-      <c r="F66" s="225"/>
+      <c r="D66" s="228"/>
+      <c r="E66" s="229"/>
+      <c r="F66" s="229"/>
       <c r="G66" s="95"/>
       <c r="H66" s="94"/>
       <c r="I66" s="93"/>
@@ -12598,9 +12933,9 @@
       <c r="A67" s="90"/>
       <c r="B67" s="99"/>
       <c r="C67" s="92"/>
-      <c r="D67" s="224"/>
-      <c r="E67" s="225"/>
-      <c r="F67" s="225"/>
+      <c r="D67" s="228"/>
+      <c r="E67" s="229"/>
+      <c r="F67" s="229"/>
       <c r="G67" s="95"/>
       <c r="H67" s="94"/>
       <c r="I67" s="93"/>
@@ -12611,9 +12946,9 @@
       <c r="A68" s="90"/>
       <c r="B68" s="99"/>
       <c r="C68" s="92"/>
-      <c r="D68" s="224"/>
-      <c r="E68" s="225"/>
-      <c r="F68" s="225"/>
+      <c r="D68" s="228"/>
+      <c r="E68" s="229"/>
+      <c r="F68" s="229"/>
       <c r="G68" s="95"/>
       <c r="H68" s="94"/>
       <c r="I68" s="93"/>
@@ -12624,9 +12959,9 @@
       <c r="A69" s="90"/>
       <c r="B69" s="99"/>
       <c r="C69" s="92"/>
-      <c r="D69" s="224"/>
-      <c r="E69" s="225"/>
-      <c r="F69" s="225"/>
+      <c r="D69" s="228"/>
+      <c r="E69" s="229"/>
+      <c r="F69" s="229"/>
       <c r="G69" s="95"/>
       <c r="H69" s="94"/>
       <c r="I69" s="93"/>
@@ -12637,9 +12972,9 @@
       <c r="A70" s="90"/>
       <c r="B70" s="99"/>
       <c r="C70" s="92"/>
-      <c r="D70" s="224"/>
-      <c r="E70" s="225"/>
-      <c r="F70" s="225"/>
+      <c r="D70" s="228"/>
+      <c r="E70" s="229"/>
+      <c r="F70" s="229"/>
       <c r="G70" s="95"/>
       <c r="H70" s="94"/>
       <c r="I70" s="93"/>
@@ -12650,9 +12985,9 @@
       <c r="A71" s="90"/>
       <c r="B71" s="99"/>
       <c r="C71" s="92"/>
-      <c r="D71" s="224"/>
-      <c r="E71" s="225"/>
-      <c r="F71" s="225"/>
+      <c r="D71" s="228"/>
+      <c r="E71" s="229"/>
+      <c r="F71" s="229"/>
       <c r="G71" s="95"/>
       <c r="H71" s="94"/>
       <c r="I71" s="93"/>
@@ -12663,9 +12998,9 @@
       <c r="A72" s="90"/>
       <c r="B72" s="99"/>
       <c r="C72" s="92"/>
-      <c r="D72" s="224"/>
-      <c r="E72" s="225"/>
-      <c r="F72" s="225"/>
+      <c r="D72" s="228"/>
+      <c r="E72" s="229"/>
+      <c r="F72" s="229"/>
       <c r="G72" s="95"/>
       <c r="H72" s="94"/>
       <c r="I72" s="93"/>
@@ -12676,9 +13011,9 @@
       <c r="A73" s="90"/>
       <c r="B73" s="99"/>
       <c r="C73" s="92"/>
-      <c r="D73" s="224"/>
-      <c r="E73" s="225"/>
-      <c r="F73" s="225"/>
+      <c r="D73" s="228"/>
+      <c r="E73" s="229"/>
+      <c r="F73" s="229"/>
       <c r="G73" s="95"/>
       <c r="H73" s="94"/>
       <c r="I73" s="93"/>
@@ -12689,9 +13024,9 @@
       <c r="A74" s="90"/>
       <c r="B74" s="99"/>
       <c r="C74" s="92"/>
-      <c r="D74" s="224"/>
-      <c r="E74" s="225"/>
-      <c r="F74" s="225"/>
+      <c r="D74" s="228"/>
+      <c r="E74" s="229"/>
+      <c r="F74" s="229"/>
       <c r="G74" s="95"/>
       <c r="H74" s="94"/>
       <c r="I74" s="93"/>
@@ -12702,9 +13037,9 @@
       <c r="A75" s="90"/>
       <c r="B75" s="99"/>
       <c r="C75" s="92"/>
-      <c r="D75" s="224"/>
-      <c r="E75" s="225"/>
-      <c r="F75" s="225"/>
+      <c r="D75" s="228"/>
+      <c r="E75" s="229"/>
+      <c r="F75" s="229"/>
       <c r="G75" s="95"/>
       <c r="H75" s="94"/>
       <c r="I75" s="93"/>
@@ -12715,9 +13050,9 @@
       <c r="A76" s="90"/>
       <c r="B76" s="99"/>
       <c r="C76" s="92"/>
-      <c r="D76" s="224"/>
-      <c r="E76" s="225"/>
-      <c r="F76" s="225"/>
+      <c r="D76" s="228"/>
+      <c r="E76" s="229"/>
+      <c r="F76" s="229"/>
       <c r="G76" s="95"/>
       <c r="H76" s="94"/>
       <c r="I76" s="93"/>
@@ -12728,9 +13063,9 @@
       <c r="A77" s="90"/>
       <c r="B77" s="99"/>
       <c r="C77" s="92"/>
-      <c r="D77" s="224"/>
-      <c r="E77" s="225"/>
-      <c r="F77" s="225"/>
+      <c r="D77" s="228"/>
+      <c r="E77" s="229"/>
+      <c r="F77" s="229"/>
       <c r="G77" s="95"/>
       <c r="H77" s="94"/>
       <c r="I77" s="93"/>
@@ -12741,9 +13076,9 @@
       <c r="A78" s="90"/>
       <c r="B78" s="99"/>
       <c r="C78" s="92"/>
-      <c r="D78" s="224"/>
-      <c r="E78" s="225"/>
-      <c r="F78" s="225"/>
+      <c r="D78" s="228"/>
+      <c r="E78" s="229"/>
+      <c r="F78" s="229"/>
       <c r="G78" s="95"/>
       <c r="H78" s="94"/>
       <c r="I78" s="93"/>
@@ -12754,9 +13089,9 @@
       <c r="A79" s="90"/>
       <c r="B79" s="99"/>
       <c r="C79" s="92"/>
-      <c r="D79" s="224"/>
-      <c r="E79" s="225"/>
-      <c r="F79" s="225"/>
+      <c r="D79" s="228"/>
+      <c r="E79" s="229"/>
+      <c r="F79" s="229"/>
       <c r="G79" s="95"/>
       <c r="H79" s="94"/>
       <c r="I79" s="93"/>
@@ -12767,9 +13102,9 @@
       <c r="A80" s="90"/>
       <c r="B80" s="99"/>
       <c r="C80" s="92"/>
-      <c r="D80" s="224"/>
-      <c r="E80" s="225"/>
-      <c r="F80" s="225"/>
+      <c r="D80" s="228"/>
+      <c r="E80" s="229"/>
+      <c r="F80" s="229"/>
       <c r="G80" s="95"/>
       <c r="H80" s="94"/>
       <c r="I80" s="93"/>
@@ -12780,9 +13115,9 @@
       <c r="A81" s="90"/>
       <c r="B81" s="99"/>
       <c r="C81" s="92"/>
-      <c r="D81" s="224"/>
-      <c r="E81" s="225"/>
-      <c r="F81" s="225"/>
+      <c r="D81" s="228"/>
+      <c r="E81" s="229"/>
+      <c r="F81" s="229"/>
       <c r="G81" s="95"/>
       <c r="H81" s="94"/>
       <c r="I81" s="93"/>
@@ -12793,9 +13128,9 @@
       <c r="A82" s="90"/>
       <c r="B82" s="99"/>
       <c r="C82" s="92"/>
-      <c r="D82" s="224"/>
-      <c r="E82" s="225"/>
-      <c r="F82" s="225"/>
+      <c r="D82" s="228"/>
+      <c r="E82" s="229"/>
+      <c r="F82" s="229"/>
       <c r="G82" s="95"/>
       <c r="H82" s="94"/>
       <c r="I82" s="93"/>
@@ -12806,9 +13141,9 @@
       <c r="A83" s="90"/>
       <c r="B83" s="99"/>
       <c r="C83" s="92"/>
-      <c r="D83" s="224"/>
-      <c r="E83" s="225"/>
-      <c r="F83" s="225"/>
+      <c r="D83" s="228"/>
+      <c r="E83" s="229"/>
+      <c r="F83" s="229"/>
       <c r="G83" s="95"/>
       <c r="H83" s="94"/>
       <c r="I83" s="93"/>
@@ -12819,9 +13154,9 @@
       <c r="A84" s="90"/>
       <c r="B84" s="99"/>
       <c r="C84" s="92"/>
-      <c r="D84" s="224"/>
-      <c r="E84" s="225"/>
-      <c r="F84" s="225"/>
+      <c r="D84" s="228"/>
+      <c r="E84" s="229"/>
+      <c r="F84" s="229"/>
       <c r="G84" s="95"/>
       <c r="H84" s="94"/>
       <c r="I84" s="93"/>
@@ -12832,9 +13167,9 @@
       <c r="A85" s="90"/>
       <c r="B85" s="99"/>
       <c r="C85" s="92"/>
-      <c r="D85" s="224"/>
-      <c r="E85" s="225"/>
-      <c r="F85" s="225"/>
+      <c r="D85" s="228"/>
+      <c r="E85" s="229"/>
+      <c r="F85" s="229"/>
       <c r="G85" s="95"/>
       <c r="H85" s="94"/>
       <c r="I85" s="93"/>
@@ -12845,9 +13180,9 @@
       <c r="A86" s="90"/>
       <c r="B86" s="99"/>
       <c r="C86" s="92"/>
-      <c r="D86" s="224"/>
-      <c r="E86" s="225"/>
-      <c r="F86" s="225"/>
+      <c r="D86" s="228"/>
+      <c r="E86" s="229"/>
+      <c r="F86" s="229"/>
       <c r="G86" s="95"/>
       <c r="H86" s="94"/>
       <c r="I86" s="93"/>
@@ -12858,9 +13193,9 @@
       <c r="A87" s="90"/>
       <c r="B87" s="99"/>
       <c r="C87" s="92"/>
-      <c r="D87" s="224"/>
-      <c r="E87" s="225"/>
-      <c r="F87" s="225"/>
+      <c r="D87" s="228"/>
+      <c r="E87" s="229"/>
+      <c r="F87" s="229"/>
       <c r="G87" s="95"/>
       <c r="H87" s="94"/>
       <c r="I87" s="93"/>
@@ -12869,12 +13204,81 @@
     </row>
   </sheetData>
   <mergeCells count="94">
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="D83:F83"/>
+    <mergeCell ref="D84:F84"/>
+    <mergeCell ref="D85:F85"/>
+    <mergeCell ref="D86:F86"/>
+    <mergeCell ref="D87:F87"/>
+    <mergeCell ref="D78:F78"/>
+    <mergeCell ref="D79:F79"/>
+    <mergeCell ref="D80:F80"/>
+    <mergeCell ref="D81:F81"/>
+    <mergeCell ref="D82:F82"/>
+    <mergeCell ref="D73:F73"/>
+    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="D75:F75"/>
+    <mergeCell ref="D76:F76"/>
+    <mergeCell ref="D77:F77"/>
+    <mergeCell ref="D68:F68"/>
+    <mergeCell ref="D69:F69"/>
+    <mergeCell ref="D70:F70"/>
+    <mergeCell ref="D71:F71"/>
+    <mergeCell ref="D72:F72"/>
+    <mergeCell ref="D63:F63"/>
+    <mergeCell ref="D64:F64"/>
+    <mergeCell ref="D65:F65"/>
+    <mergeCell ref="D66:F66"/>
+    <mergeCell ref="D67:F67"/>
+    <mergeCell ref="D58:F58"/>
+    <mergeCell ref="D59:F59"/>
+    <mergeCell ref="D60:F60"/>
+    <mergeCell ref="D61:F61"/>
+    <mergeCell ref="D62:F62"/>
+    <mergeCell ref="D53:F53"/>
+    <mergeCell ref="D54:F54"/>
+    <mergeCell ref="D55:F55"/>
+    <mergeCell ref="D56:F56"/>
+    <mergeCell ref="D57:F57"/>
+    <mergeCell ref="D48:F48"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="D50:F50"/>
+    <mergeCell ref="D51:F51"/>
+    <mergeCell ref="D52:F52"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="D44:F44"/>
+    <mergeCell ref="D45:F45"/>
+    <mergeCell ref="D46:F46"/>
+    <mergeCell ref="D47:F47"/>
+    <mergeCell ref="D38:F38"/>
+    <mergeCell ref="D39:F39"/>
+    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="A30:K30"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="A22:K22"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="A16:K16"/>
+    <mergeCell ref="D17:F17"/>
     <mergeCell ref="I6:K6"/>
     <mergeCell ref="I7:K7"/>
     <mergeCell ref="A8:D8"/>
@@ -12888,81 +13292,12 @@
     <mergeCell ref="J9:J10"/>
     <mergeCell ref="K9:K10"/>
     <mergeCell ref="D9:G10"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="A16:K16"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="A22:K22"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="A30:K30"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="D36:F36"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="D38:F38"/>
-    <mergeCell ref="D39:F39"/>
-    <mergeCell ref="D40:F40"/>
-    <mergeCell ref="D41:F41"/>
-    <mergeCell ref="D42:F42"/>
-    <mergeCell ref="D43:F43"/>
-    <mergeCell ref="D44:F44"/>
-    <mergeCell ref="D45:F45"/>
-    <mergeCell ref="D46:F46"/>
-    <mergeCell ref="D47:F47"/>
-    <mergeCell ref="D48:F48"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="D50:F50"/>
-    <mergeCell ref="D51:F51"/>
-    <mergeCell ref="D52:F52"/>
-    <mergeCell ref="D53:F53"/>
-    <mergeCell ref="D54:F54"/>
-    <mergeCell ref="D55:F55"/>
-    <mergeCell ref="D56:F56"/>
-    <mergeCell ref="D57:F57"/>
-    <mergeCell ref="D58:F58"/>
-    <mergeCell ref="D59:F59"/>
-    <mergeCell ref="D60:F60"/>
-    <mergeCell ref="D61:F61"/>
-    <mergeCell ref="D62:F62"/>
-    <mergeCell ref="D63:F63"/>
-    <mergeCell ref="D64:F64"/>
-    <mergeCell ref="D65:F65"/>
-    <mergeCell ref="D66:F66"/>
-    <mergeCell ref="D67:F67"/>
-    <mergeCell ref="D68:F68"/>
-    <mergeCell ref="D69:F69"/>
-    <mergeCell ref="D70:F70"/>
-    <mergeCell ref="D71:F71"/>
-    <mergeCell ref="D72:F72"/>
-    <mergeCell ref="D73:F73"/>
-    <mergeCell ref="D74:F74"/>
-    <mergeCell ref="D75:F75"/>
-    <mergeCell ref="D76:F76"/>
-    <mergeCell ref="D77:F77"/>
-    <mergeCell ref="D78:F78"/>
-    <mergeCell ref="D79:F79"/>
-    <mergeCell ref="D80:F80"/>
-    <mergeCell ref="D81:F81"/>
-    <mergeCell ref="D82:F82"/>
-    <mergeCell ref="D83:F83"/>
-    <mergeCell ref="D84:F84"/>
-    <mergeCell ref="D85:F85"/>
-    <mergeCell ref="D86:F86"/>
-    <mergeCell ref="D87:F87"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="I5:K5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/test-case-example.xlsx
+++ b/test-case-example.xlsx
@@ -4126,15 +4126,162 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="66" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="3" borderId="67" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="3" borderId="72" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="58" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="59" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="60" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="40" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="56" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="39" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="40" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="56" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="39" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="40" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="56" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="49" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="42" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="49" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="42" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="52" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="53" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="50" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="51" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="54" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="48" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="55" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="36" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="37" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="39" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -4156,117 +4303,6 @@
     <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="39" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="40" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="56" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="49" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="42" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="49" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="42" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="52" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="53" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="50" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="51" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="54" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="48" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="55" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="39" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="40" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="56" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="58" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="59" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="60" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="40" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="56" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -4285,6 +4321,15 @@
     <xf numFmtId="0" fontId="18" fillId="9" borderId="40" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="39" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="25" fillId="9" borderId="39" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -4294,15 +4339,6 @@
     <xf numFmtId="0" fontId="25" fillId="9" borderId="56" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="39" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="9" borderId="40" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -4330,14 +4366,53 @@
     <xf numFmtId="0" fontId="13" fillId="6" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="9" borderId="39" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="10" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="3" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -4345,83 +4420,8 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="9" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="1" fontId="8" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="10" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="66" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="3" borderId="67" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="3" borderId="72" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="3" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -5397,11 +5397,11 @@
       <c r="A3" s="70" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="171" t="s">
+      <c r="B3" s="221" t="s">
         <v>62</v>
       </c>
-      <c r="C3" s="171"/>
-      <c r="D3" s="172"/>
+      <c r="C3" s="221"/>
+      <c r="D3" s="222"/>
       <c r="E3" s="71"/>
       <c r="F3" s="71"/>
       <c r="G3" s="71"/>
@@ -5410,11 +5410,11 @@
       <c r="A4" s="74" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="174" t="s">
+      <c r="B4" s="223" t="s">
         <v>488</v>
       </c>
-      <c r="C4" s="175"/>
-      <c r="D4" s="176"/>
+      <c r="C4" s="224"/>
+      <c r="D4" s="225"/>
       <c r="E4" s="71"/>
       <c r="F4" s="71"/>
       <c r="G4" s="71"/>
@@ -5423,11 +5423,11 @@
       <c r="A5" s="74" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="177" t="s">
+      <c r="B5" s="226" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="178"/>
-      <c r="D5" s="179"/>
+      <c r="C5" s="227"/>
+      <c r="D5" s="228"/>
       <c r="E5" s="75"/>
       <c r="F5" s="75"/>
       <c r="G5" s="75"/>
@@ -5467,83 +5467,83 @@
       <c r="G7" s="85"/>
     </row>
     <row r="8" spans="1:11" ht="14.25">
-      <c r="A8" s="238"/>
-      <c r="B8" s="238"/>
-      <c r="C8" s="238"/>
-      <c r="D8" s="238"/>
+      <c r="A8" s="250"/>
+      <c r="B8" s="250"/>
+      <c r="C8" s="250"/>
+      <c r="D8" s="250"/>
       <c r="E8" s="72"/>
       <c r="F8" s="72"/>
       <c r="G8" s="72"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="187" t="s">
+      <c r="A9" s="209" t="s">
         <v>71</v>
       </c>
-      <c r="B9" s="189" t="s">
+      <c r="B9" s="211" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="187" t="s">
+      <c r="C9" s="209" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="193" t="s">
+      <c r="D9" s="215" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="194"/>
-      <c r="F9" s="194"/>
-      <c r="G9" s="195"/>
-      <c r="H9" s="191" t="s">
+      <c r="E9" s="216"/>
+      <c r="F9" s="216"/>
+      <c r="G9" s="217"/>
+      <c r="H9" s="213" t="s">
         <v>75</v>
       </c>
-      <c r="I9" s="192" t="s">
+      <c r="I9" s="214" t="s">
         <v>76</v>
       </c>
-      <c r="J9" s="192" t="s">
+      <c r="J9" s="214" t="s">
         <v>77</v>
       </c>
-      <c r="K9" s="192" t="s">
+      <c r="K9" s="214" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="188"/>
-      <c r="B10" s="190"/>
-      <c r="C10" s="188"/>
-      <c r="D10" s="196"/>
-      <c r="E10" s="197"/>
-      <c r="F10" s="197"/>
-      <c r="G10" s="198"/>
-      <c r="H10" s="187"/>
-      <c r="I10" s="187"/>
-      <c r="J10" s="187"/>
-      <c r="K10" s="187"/>
+      <c r="A10" s="210"/>
+      <c r="B10" s="212"/>
+      <c r="C10" s="210"/>
+      <c r="D10" s="218"/>
+      <c r="E10" s="219"/>
+      <c r="F10" s="219"/>
+      <c r="G10" s="220"/>
+      <c r="H10" s="209"/>
+      <c r="I10" s="209"/>
+      <c r="J10" s="209"/>
+      <c r="K10" s="209"/>
     </row>
     <row r="11" spans="1:11" ht="15">
-      <c r="A11" s="182"/>
-      <c r="B11" s="182"/>
-      <c r="C11" s="182"/>
-      <c r="D11" s="182"/>
-      <c r="E11" s="182"/>
-      <c r="F11" s="182"/>
-      <c r="G11" s="182"/>
-      <c r="H11" s="182"/>
-      <c r="I11" s="182"/>
-      <c r="J11" s="182"/>
-      <c r="K11" s="183"/>
+      <c r="A11" s="207"/>
+      <c r="B11" s="207"/>
+      <c r="C11" s="207"/>
+      <c r="D11" s="207"/>
+      <c r="E11" s="207"/>
+      <c r="F11" s="207"/>
+      <c r="G11" s="207"/>
+      <c r="H11" s="207"/>
+      <c r="I11" s="207"/>
+      <c r="J11" s="207"/>
+      <c r="K11" s="208"/>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="184" t="s">
+      <c r="A12" s="196" t="s">
         <v>489</v>
       </c>
-      <c r="B12" s="185"/>
-      <c r="C12" s="185"/>
-      <c r="D12" s="185"/>
-      <c r="E12" s="185"/>
-      <c r="F12" s="185"/>
-      <c r="G12" s="185"/>
-      <c r="H12" s="185"/>
-      <c r="I12" s="185"/>
-      <c r="J12" s="185"/>
-      <c r="K12" s="186"/>
+      <c r="B12" s="197"/>
+      <c r="C12" s="197"/>
+      <c r="D12" s="197"/>
+      <c r="E12" s="197"/>
+      <c r="F12" s="197"/>
+      <c r="G12" s="197"/>
+      <c r="H12" s="197"/>
+      <c r="I12" s="197"/>
+      <c r="J12" s="197"/>
+      <c r="K12" s="198"/>
     </row>
     <row r="13" spans="1:11" ht="38.25">
       <c r="A13" s="90" t="s">
@@ -5558,9 +5558,9 @@
       <c r="D13" s="199" t="s">
         <v>492</v>
       </c>
-      <c r="E13" s="200"/>
-      <c r="F13" s="200"/>
-      <c r="G13" s="201"/>
+      <c r="E13" s="188"/>
+      <c r="F13" s="188"/>
+      <c r="G13" s="189"/>
       <c r="H13" s="94"/>
       <c r="I13" s="96"/>
       <c r="J13" s="92" t="s">
@@ -5569,19 +5569,19 @@
       <c r="K13" s="92"/>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="184" t="s">
+      <c r="A14" s="196" t="s">
         <v>493</v>
       </c>
-      <c r="B14" s="185"/>
-      <c r="C14" s="185"/>
-      <c r="D14" s="185"/>
-      <c r="E14" s="185"/>
-      <c r="F14" s="185"/>
-      <c r="G14" s="185"/>
-      <c r="H14" s="185"/>
-      <c r="I14" s="185"/>
-      <c r="J14" s="185"/>
-      <c r="K14" s="186"/>
+      <c r="B14" s="197"/>
+      <c r="C14" s="197"/>
+      <c r="D14" s="197"/>
+      <c r="E14" s="197"/>
+      <c r="F14" s="197"/>
+      <c r="G14" s="197"/>
+      <c r="H14" s="197"/>
+      <c r="I14" s="197"/>
+      <c r="J14" s="197"/>
+      <c r="K14" s="198"/>
     </row>
     <row r="15" spans="1:11" ht="25.5">
       <c r="A15" s="102" t="s">
@@ -5593,12 +5593,12 @@
       <c r="C15" s="102" t="s">
         <v>495</v>
       </c>
-      <c r="D15" s="202" t="s">
+      <c r="D15" s="200" t="s">
         <v>496</v>
       </c>
-      <c r="E15" s="203"/>
-      <c r="F15" s="203"/>
-      <c r="G15" s="204"/>
+      <c r="E15" s="201"/>
+      <c r="F15" s="201"/>
+      <c r="G15" s="202"/>
       <c r="H15" s="103"/>
       <c r="I15" s="103"/>
       <c r="J15" s="104" t="s">
@@ -5607,19 +5607,19 @@
       <c r="K15" s="103"/>
     </row>
     <row r="16" spans="1:11">
-      <c r="A16" s="184" t="s">
+      <c r="A16" s="196" t="s">
         <v>497</v>
       </c>
-      <c r="B16" s="185"/>
-      <c r="C16" s="185"/>
-      <c r="D16" s="185"/>
-      <c r="E16" s="185"/>
-      <c r="F16" s="185"/>
-      <c r="G16" s="185"/>
-      <c r="H16" s="185"/>
-      <c r="I16" s="185"/>
-      <c r="J16" s="185"/>
-      <c r="K16" s="186"/>
+      <c r="B16" s="197"/>
+      <c r="C16" s="197"/>
+      <c r="D16" s="197"/>
+      <c r="E16" s="197"/>
+      <c r="F16" s="197"/>
+      <c r="G16" s="197"/>
+      <c r="H16" s="197"/>
+      <c r="I16" s="197"/>
+      <c r="J16" s="197"/>
+      <c r="K16" s="198"/>
     </row>
     <row r="17" spans="1:11" ht="38.25">
       <c r="A17" s="102" t="s">
@@ -5631,12 +5631,12 @@
       <c r="C17" s="102" t="s">
         <v>499</v>
       </c>
-      <c r="D17" s="202" t="s">
+      <c r="D17" s="200" t="s">
         <v>500</v>
       </c>
-      <c r="E17" s="203"/>
-      <c r="F17" s="203"/>
-      <c r="G17" s="204"/>
+      <c r="E17" s="201"/>
+      <c r="F17" s="201"/>
+      <c r="G17" s="202"/>
       <c r="H17" s="103"/>
       <c r="I17" s="103"/>
       <c r="J17" s="104" t="s">
@@ -5645,19 +5645,19 @@
       <c r="K17" s="103"/>
     </row>
     <row r="18" spans="1:11">
-      <c r="A18" s="184" t="s">
+      <c r="A18" s="196" t="s">
         <v>501</v>
       </c>
-      <c r="B18" s="185"/>
-      <c r="C18" s="185"/>
-      <c r="D18" s="185"/>
-      <c r="E18" s="185"/>
-      <c r="F18" s="185"/>
-      <c r="G18" s="185"/>
-      <c r="H18" s="185"/>
-      <c r="I18" s="185"/>
-      <c r="J18" s="185"/>
-      <c r="K18" s="186"/>
+      <c r="B18" s="197"/>
+      <c r="C18" s="197"/>
+      <c r="D18" s="197"/>
+      <c r="E18" s="197"/>
+      <c r="F18" s="197"/>
+      <c r="G18" s="197"/>
+      <c r="H18" s="197"/>
+      <c r="I18" s="197"/>
+      <c r="J18" s="197"/>
+      <c r="K18" s="198"/>
     </row>
     <row r="19" spans="1:11" ht="38.25">
       <c r="A19" s="102" t="s">
@@ -5669,12 +5669,12 @@
       <c r="C19" s="102" t="s">
         <v>503</v>
       </c>
-      <c r="D19" s="202" t="s">
+      <c r="D19" s="200" t="s">
         <v>504</v>
       </c>
-      <c r="E19" s="203"/>
-      <c r="F19" s="203"/>
-      <c r="G19" s="204"/>
+      <c r="E19" s="201"/>
+      <c r="F19" s="201"/>
+      <c r="G19" s="202"/>
       <c r="H19" s="103"/>
       <c r="I19" s="103"/>
       <c r="J19" s="104" t="s">
@@ -5683,19 +5683,19 @@
       <c r="K19" s="103"/>
     </row>
     <row r="20" spans="1:11">
-      <c r="A20" s="184" t="s">
+      <c r="A20" s="196" t="s">
         <v>505</v>
       </c>
-      <c r="B20" s="185"/>
-      <c r="C20" s="185"/>
-      <c r="D20" s="185"/>
-      <c r="E20" s="185"/>
-      <c r="F20" s="185"/>
-      <c r="G20" s="185"/>
-      <c r="H20" s="185"/>
-      <c r="I20" s="185"/>
-      <c r="J20" s="185"/>
-      <c r="K20" s="186"/>
+      <c r="B20" s="197"/>
+      <c r="C20" s="197"/>
+      <c r="D20" s="197"/>
+      <c r="E20" s="197"/>
+      <c r="F20" s="197"/>
+      <c r="G20" s="197"/>
+      <c r="H20" s="197"/>
+      <c r="I20" s="197"/>
+      <c r="J20" s="197"/>
+      <c r="K20" s="198"/>
     </row>
     <row r="21" spans="1:11" ht="38.25">
       <c r="A21" s="102" t="s">
@@ -5707,12 +5707,12 @@
       <c r="C21" s="102" t="s">
         <v>507</v>
       </c>
-      <c r="D21" s="202" t="s">
+      <c r="D21" s="200" t="s">
         <v>508</v>
       </c>
-      <c r="E21" s="203"/>
-      <c r="F21" s="203"/>
-      <c r="G21" s="204"/>
+      <c r="E21" s="201"/>
+      <c r="F21" s="201"/>
+      <c r="G21" s="202"/>
       <c r="H21" s="103"/>
       <c r="I21" s="103"/>
       <c r="J21" s="104" t="s">
@@ -5721,19 +5721,19 @@
       <c r="K21" s="103"/>
     </row>
     <row r="22" spans="1:11">
-      <c r="A22" s="184" t="s">
+      <c r="A22" s="196" t="s">
         <v>509</v>
       </c>
-      <c r="B22" s="185"/>
-      <c r="C22" s="185"/>
-      <c r="D22" s="185"/>
-      <c r="E22" s="185"/>
-      <c r="F22" s="185"/>
-      <c r="G22" s="185"/>
-      <c r="H22" s="185"/>
-      <c r="I22" s="185"/>
-      <c r="J22" s="185"/>
-      <c r="K22" s="186"/>
+      <c r="B22" s="197"/>
+      <c r="C22" s="197"/>
+      <c r="D22" s="197"/>
+      <c r="E22" s="197"/>
+      <c r="F22" s="197"/>
+      <c r="G22" s="197"/>
+      <c r="H22" s="197"/>
+      <c r="I22" s="197"/>
+      <c r="J22" s="197"/>
+      <c r="K22" s="198"/>
     </row>
     <row r="23" spans="1:11" ht="38.25">
       <c r="A23" s="102" t="s">
@@ -5745,12 +5745,12 @@
       <c r="C23" s="102" t="s">
         <v>511</v>
       </c>
-      <c r="D23" s="202" t="s">
+      <c r="D23" s="200" t="s">
         <v>512</v>
       </c>
-      <c r="E23" s="203"/>
-      <c r="F23" s="203"/>
-      <c r="G23" s="204"/>
+      <c r="E23" s="201"/>
+      <c r="F23" s="201"/>
+      <c r="G23" s="202"/>
       <c r="H23" s="103"/>
       <c r="I23" s="103"/>
       <c r="J23" s="104" t="s">
@@ -5759,19 +5759,19 @@
       <c r="K23" s="103"/>
     </row>
     <row r="24" spans="1:11">
-      <c r="A24" s="184" t="s">
+      <c r="A24" s="196" t="s">
         <v>513</v>
       </c>
-      <c r="B24" s="185"/>
-      <c r="C24" s="185"/>
-      <c r="D24" s="185"/>
-      <c r="E24" s="185"/>
-      <c r="F24" s="185"/>
-      <c r="G24" s="185"/>
-      <c r="H24" s="185"/>
-      <c r="I24" s="185"/>
-      <c r="J24" s="185"/>
-      <c r="K24" s="186"/>
+      <c r="B24" s="197"/>
+      <c r="C24" s="197"/>
+      <c r="D24" s="197"/>
+      <c r="E24" s="197"/>
+      <c r="F24" s="197"/>
+      <c r="G24" s="197"/>
+      <c r="H24" s="197"/>
+      <c r="I24" s="197"/>
+      <c r="J24" s="197"/>
+      <c r="K24" s="198"/>
     </row>
     <row r="25" spans="1:11" ht="38.25">
       <c r="A25" s="102" t="s">
@@ -5783,12 +5783,12 @@
       <c r="C25" s="102" t="s">
         <v>515</v>
       </c>
-      <c r="D25" s="202" t="s">
+      <c r="D25" s="200" t="s">
         <v>516</v>
       </c>
-      <c r="E25" s="203"/>
-      <c r="F25" s="203"/>
-      <c r="G25" s="204"/>
+      <c r="E25" s="201"/>
+      <c r="F25" s="201"/>
+      <c r="G25" s="202"/>
       <c r="H25" s="103"/>
       <c r="I25" s="103"/>
       <c r="J25" s="104" t="s">
@@ -5797,19 +5797,19 @@
       <c r="K25" s="103"/>
     </row>
     <row r="26" spans="1:11">
-      <c r="A26" s="184" t="s">
+      <c r="A26" s="196" t="s">
         <v>517</v>
       </c>
-      <c r="B26" s="185"/>
-      <c r="C26" s="185"/>
-      <c r="D26" s="185"/>
-      <c r="E26" s="185"/>
-      <c r="F26" s="185"/>
-      <c r="G26" s="185"/>
-      <c r="H26" s="185"/>
-      <c r="I26" s="185"/>
-      <c r="J26" s="185"/>
-      <c r="K26" s="186"/>
+      <c r="B26" s="197"/>
+      <c r="C26" s="197"/>
+      <c r="D26" s="197"/>
+      <c r="E26" s="197"/>
+      <c r="F26" s="197"/>
+      <c r="G26" s="197"/>
+      <c r="H26" s="197"/>
+      <c r="I26" s="197"/>
+      <c r="J26" s="197"/>
+      <c r="K26" s="198"/>
     </row>
     <row r="27" spans="1:11" ht="38.25">
       <c r="A27" s="102" t="s">
@@ -5821,12 +5821,12 @@
       <c r="C27" s="102" t="s">
         <v>519</v>
       </c>
-      <c r="D27" s="202" t="s">
+      <c r="D27" s="200" t="s">
         <v>520</v>
       </c>
-      <c r="E27" s="203"/>
-      <c r="F27" s="203"/>
-      <c r="G27" s="204"/>
+      <c r="E27" s="201"/>
+      <c r="F27" s="201"/>
+      <c r="G27" s="202"/>
       <c r="H27" s="103"/>
       <c r="I27" s="103"/>
       <c r="J27" s="104" t="s">
@@ -5835,19 +5835,19 @@
       <c r="K27" s="103"/>
     </row>
     <row r="28" spans="1:11">
-      <c r="A28" s="184" t="s">
+      <c r="A28" s="196" t="s">
         <v>521</v>
       </c>
-      <c r="B28" s="185"/>
-      <c r="C28" s="185"/>
-      <c r="D28" s="185"/>
-      <c r="E28" s="185"/>
-      <c r="F28" s="185"/>
-      <c r="G28" s="185"/>
-      <c r="H28" s="185"/>
-      <c r="I28" s="185"/>
-      <c r="J28" s="185"/>
-      <c r="K28" s="186"/>
+      <c r="B28" s="197"/>
+      <c r="C28" s="197"/>
+      <c r="D28" s="197"/>
+      <c r="E28" s="197"/>
+      <c r="F28" s="197"/>
+      <c r="G28" s="197"/>
+      <c r="H28" s="197"/>
+      <c r="I28" s="197"/>
+      <c r="J28" s="197"/>
+      <c r="K28" s="198"/>
     </row>
     <row r="29" spans="1:11" ht="38.25">
       <c r="A29" s="102" t="s">
@@ -5859,12 +5859,12 @@
       <c r="C29" s="102" t="s">
         <v>523</v>
       </c>
-      <c r="D29" s="202" t="s">
+      <c r="D29" s="200" t="s">
         <v>524</v>
       </c>
-      <c r="E29" s="203"/>
-      <c r="F29" s="203"/>
-      <c r="G29" s="204"/>
+      <c r="E29" s="201"/>
+      <c r="F29" s="201"/>
+      <c r="G29" s="202"/>
       <c r="H29" s="103"/>
       <c r="I29" s="103"/>
       <c r="J29" s="104" t="s">
@@ -5873,19 +5873,19 @@
       <c r="K29" s="103"/>
     </row>
     <row r="30" spans="1:11">
-      <c r="A30" s="184" t="s">
+      <c r="A30" s="196" t="s">
         <v>525</v>
       </c>
-      <c r="B30" s="185"/>
-      <c r="C30" s="185"/>
-      <c r="D30" s="185"/>
-      <c r="E30" s="185"/>
-      <c r="F30" s="185"/>
-      <c r="G30" s="185"/>
-      <c r="H30" s="185"/>
-      <c r="I30" s="185"/>
-      <c r="J30" s="185"/>
-      <c r="K30" s="186"/>
+      <c r="B30" s="197"/>
+      <c r="C30" s="197"/>
+      <c r="D30" s="197"/>
+      <c r="E30" s="197"/>
+      <c r="F30" s="197"/>
+      <c r="G30" s="197"/>
+      <c r="H30" s="197"/>
+      <c r="I30" s="197"/>
+      <c r="J30" s="197"/>
+      <c r="K30" s="198"/>
     </row>
     <row r="31" spans="1:11" ht="38.25">
       <c r="A31" s="102" t="s">
@@ -5897,12 +5897,12 @@
       <c r="C31" s="102" t="s">
         <v>527</v>
       </c>
-      <c r="D31" s="202" t="s">
+      <c r="D31" s="200" t="s">
         <v>528</v>
       </c>
-      <c r="E31" s="203"/>
-      <c r="F31" s="203"/>
-      <c r="G31" s="204"/>
+      <c r="E31" s="201"/>
+      <c r="F31" s="201"/>
+      <c r="G31" s="202"/>
       <c r="H31" s="103"/>
       <c r="I31" s="103"/>
       <c r="J31" s="104" t="s">
@@ -5911,19 +5911,19 @@
       <c r="K31" s="103"/>
     </row>
     <row r="32" spans="1:11">
-      <c r="A32" s="184" t="s">
+      <c r="A32" s="196" t="s">
         <v>529</v>
       </c>
-      <c r="B32" s="185"/>
-      <c r="C32" s="185"/>
-      <c r="D32" s="185"/>
-      <c r="E32" s="185"/>
-      <c r="F32" s="185"/>
-      <c r="G32" s="185"/>
-      <c r="H32" s="185"/>
-      <c r="I32" s="185"/>
-      <c r="J32" s="185"/>
-      <c r="K32" s="186"/>
+      <c r="B32" s="197"/>
+      <c r="C32" s="197"/>
+      <c r="D32" s="197"/>
+      <c r="E32" s="197"/>
+      <c r="F32" s="197"/>
+      <c r="G32" s="197"/>
+      <c r="H32" s="197"/>
+      <c r="I32" s="197"/>
+      <c r="J32" s="197"/>
+      <c r="K32" s="198"/>
     </row>
     <row r="33" spans="1:11" ht="38.25">
       <c r="A33" s="102" t="s">
@@ -5935,12 +5935,12 @@
       <c r="C33" s="102" t="s">
         <v>531</v>
       </c>
-      <c r="D33" s="202" t="s">
+      <c r="D33" s="200" t="s">
         <v>524</v>
       </c>
-      <c r="E33" s="203"/>
-      <c r="F33" s="203"/>
-      <c r="G33" s="204"/>
+      <c r="E33" s="201"/>
+      <c r="F33" s="201"/>
+      <c r="G33" s="202"/>
       <c r="H33" s="103"/>
       <c r="I33" s="103"/>
       <c r="J33" s="104" t="s">
@@ -5950,6 +5950,25 @@
     </row>
   </sheetData>
   <mergeCells count="35">
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A11:K11"/>
+    <mergeCell ref="A12:K12"/>
+    <mergeCell ref="D13:G13"/>
+    <mergeCell ref="A14:K14"/>
+    <mergeCell ref="D15:G15"/>
+    <mergeCell ref="A16:K16"/>
+    <mergeCell ref="D23:G23"/>
+    <mergeCell ref="A24:K24"/>
+    <mergeCell ref="D25:G25"/>
+    <mergeCell ref="A26:K26"/>
+    <mergeCell ref="D17:G17"/>
+    <mergeCell ref="A18:K18"/>
+    <mergeCell ref="D19:G19"/>
+    <mergeCell ref="A20:K20"/>
+    <mergeCell ref="D21:G21"/>
     <mergeCell ref="A32:K32"/>
     <mergeCell ref="D33:G33"/>
     <mergeCell ref="A9:A10"/>
@@ -5966,25 +5985,6 @@
     <mergeCell ref="A30:K30"/>
     <mergeCell ref="D31:G31"/>
     <mergeCell ref="A22:K22"/>
-    <mergeCell ref="D23:G23"/>
-    <mergeCell ref="A24:K24"/>
-    <mergeCell ref="D25:G25"/>
-    <mergeCell ref="A26:K26"/>
-    <mergeCell ref="D17:G17"/>
-    <mergeCell ref="A18:K18"/>
-    <mergeCell ref="D19:G19"/>
-    <mergeCell ref="A20:K20"/>
-    <mergeCell ref="D21:G21"/>
-    <mergeCell ref="A12:K12"/>
-    <mergeCell ref="D13:G13"/>
-    <mergeCell ref="A14:K14"/>
-    <mergeCell ref="D15:G15"/>
-    <mergeCell ref="A16:K16"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A11:K11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6013,9 +6013,9 @@
       <c r="A1" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="240"/>
-      <c r="C1" s="240"/>
-      <c r="D1" s="240"/>
+      <c r="B1" s="251"/>
+      <c r="C1" s="251"/>
+      <c r="D1" s="251"/>
       <c r="E1" s="67"/>
       <c r="F1" s="67"/>
       <c r="G1" s="67"/>
@@ -6027,9 +6027,9 @@
     </row>
     <row r="2" spans="1:12" s="60" customFormat="1" ht="11.25" customHeight="1">
       <c r="A2" s="69"/>
-      <c r="B2" s="241"/>
-      <c r="C2" s="241"/>
-      <c r="D2" s="241"/>
+      <c r="B2" s="252"/>
+      <c r="C2" s="252"/>
+      <c r="D2" s="252"/>
       <c r="E2" s="67"/>
       <c r="F2" s="67"/>
       <c r="G2" s="67"/>
@@ -6043,54 +6043,54 @@
       <c r="A3" s="70" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="171" t="s">
+      <c r="B3" s="221" t="s">
         <v>532</v>
       </c>
-      <c r="C3" s="171"/>
-      <c r="D3" s="172"/>
+      <c r="C3" s="221"/>
+      <c r="D3" s="222"/>
       <c r="E3" s="71"/>
       <c r="F3" s="71"/>
       <c r="G3" s="71"/>
       <c r="H3" s="71"/>
-      <c r="I3" s="173"/>
-      <c r="J3" s="173"/>
-      <c r="K3" s="173"/>
+      <c r="I3" s="205"/>
+      <c r="J3" s="205"/>
+      <c r="K3" s="205"/>
       <c r="L3" s="73"/>
     </row>
     <row r="4" spans="1:12" s="61" customFormat="1" ht="12.75">
       <c r="A4" s="74" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="174" t="s">
+      <c r="B4" s="223" t="s">
         <v>533</v>
       </c>
-      <c r="C4" s="175"/>
-      <c r="D4" s="176"/>
+      <c r="C4" s="224"/>
+      <c r="D4" s="225"/>
       <c r="E4" s="71"/>
       <c r="F4" s="71"/>
       <c r="G4" s="71"/>
       <c r="H4" s="71"/>
-      <c r="I4" s="173"/>
-      <c r="J4" s="173"/>
-      <c r="K4" s="173"/>
+      <c r="I4" s="205"/>
+      <c r="J4" s="205"/>
+      <c r="K4" s="205"/>
       <c r="L4" s="73"/>
     </row>
     <row r="5" spans="1:12" s="62" customFormat="1" ht="25.5">
       <c r="A5" s="74" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="177" t="s">
+      <c r="B5" s="226" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="178"/>
-      <c r="D5" s="179"/>
+      <c r="C5" s="227"/>
+      <c r="D5" s="228"/>
       <c r="E5" s="75"/>
       <c r="F5" s="75"/>
       <c r="G5" s="75"/>
       <c r="H5" s="75"/>
-      <c r="I5" s="180"/>
-      <c r="J5" s="180"/>
-      <c r="K5" s="180"/>
+      <c r="I5" s="229"/>
+      <c r="J5" s="229"/>
+      <c r="K5" s="229"/>
       <c r="L5" s="76"/>
     </row>
     <row r="6" spans="1:12" s="61" customFormat="1" ht="15" customHeight="1">
@@ -6112,9 +6112,9 @@
       <c r="F6" s="72"/>
       <c r="G6" s="72"/>
       <c r="H6" s="72"/>
-      <c r="I6" s="173"/>
-      <c r="J6" s="173"/>
-      <c r="K6" s="173"/>
+      <c r="I6" s="205"/>
+      <c r="J6" s="205"/>
+      <c r="K6" s="205"/>
       <c r="L6" s="73"/>
     </row>
     <row r="7" spans="1:12" s="61" customFormat="1" ht="15" customHeight="1">
@@ -6136,16 +6136,16 @@
       <c r="F7" s="85"/>
       <c r="G7" s="85"/>
       <c r="H7" s="85"/>
-      <c r="I7" s="173"/>
-      <c r="J7" s="173"/>
-      <c r="K7" s="173"/>
+      <c r="I7" s="205"/>
+      <c r="J7" s="205"/>
+      <c r="K7" s="205"/>
       <c r="L7" s="73"/>
     </row>
     <row r="8" spans="1:12" s="61" customFormat="1" ht="15" customHeight="1">
-      <c r="A8" s="181"/>
-      <c r="B8" s="181"/>
-      <c r="C8" s="181"/>
-      <c r="D8" s="181"/>
+      <c r="A8" s="206"/>
+      <c r="B8" s="206"/>
+      <c r="C8" s="206"/>
+      <c r="D8" s="206"/>
       <c r="E8" s="72"/>
       <c r="F8" s="72"/>
       <c r="G8" s="72"/>
@@ -6156,76 +6156,76 @@
       <c r="L8" s="73"/>
     </row>
     <row r="9" spans="1:12" s="63" customFormat="1" ht="12" customHeight="1">
-      <c r="A9" s="187" t="s">
+      <c r="A9" s="209" t="s">
         <v>71</v>
       </c>
-      <c r="B9" s="189" t="s">
+      <c r="B9" s="211" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="187" t="s">
+      <c r="C9" s="209" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="193" t="s">
+      <c r="D9" s="215" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="194"/>
-      <c r="F9" s="194"/>
-      <c r="G9" s="195"/>
-      <c r="H9" s="191" t="s">
+      <c r="E9" s="216"/>
+      <c r="F9" s="216"/>
+      <c r="G9" s="217"/>
+      <c r="H9" s="213" t="s">
         <v>75</v>
       </c>
-      <c r="I9" s="192" t="s">
+      <c r="I9" s="214" t="s">
         <v>76</v>
       </c>
-      <c r="J9" s="192" t="s">
+      <c r="J9" s="214" t="s">
         <v>77</v>
       </c>
-      <c r="K9" s="192" t="s">
+      <c r="K9" s="214" t="s">
         <v>78</v>
       </c>
       <c r="L9" s="87"/>
     </row>
     <row r="10" spans="1:12" s="61" customFormat="1" ht="12" customHeight="1">
-      <c r="A10" s="188"/>
-      <c r="B10" s="190"/>
-      <c r="C10" s="188"/>
-      <c r="D10" s="196"/>
-      <c r="E10" s="197"/>
-      <c r="F10" s="197"/>
-      <c r="G10" s="198"/>
-      <c r="H10" s="187"/>
-      <c r="I10" s="187"/>
-      <c r="J10" s="187"/>
-      <c r="K10" s="187"/>
+      <c r="A10" s="210"/>
+      <c r="B10" s="212"/>
+      <c r="C10" s="210"/>
+      <c r="D10" s="218"/>
+      <c r="E10" s="219"/>
+      <c r="F10" s="219"/>
+      <c r="G10" s="220"/>
+      <c r="H10" s="209"/>
+      <c r="I10" s="209"/>
+      <c r="J10" s="209"/>
+      <c r="K10" s="209"/>
       <c r="L10" s="73"/>
     </row>
     <row r="11" spans="1:12" s="64" customFormat="1" ht="15">
-      <c r="A11" s="182"/>
-      <c r="B11" s="182"/>
-      <c r="C11" s="182"/>
-      <c r="D11" s="182"/>
-      <c r="E11" s="182"/>
-      <c r="F11" s="182"/>
-      <c r="G11" s="182"/>
-      <c r="H11" s="182"/>
-      <c r="I11" s="182"/>
-      <c r="J11" s="182"/>
-      <c r="K11" s="183"/>
+      <c r="A11" s="207"/>
+      <c r="B11" s="207"/>
+      <c r="C11" s="207"/>
+      <c r="D11" s="207"/>
+      <c r="E11" s="207"/>
+      <c r="F11" s="207"/>
+      <c r="G11" s="207"/>
+      <c r="H11" s="207"/>
+      <c r="I11" s="207"/>
+      <c r="J11" s="207"/>
+      <c r="K11" s="208"/>
     </row>
     <row r="12" spans="1:12" s="65" customFormat="1" ht="12.75">
-      <c r="A12" s="184" t="s">
+      <c r="A12" s="196" t="s">
         <v>534</v>
       </c>
-      <c r="B12" s="185"/>
-      <c r="C12" s="185"/>
-      <c r="D12" s="185"/>
-      <c r="E12" s="185"/>
-      <c r="F12" s="185"/>
-      <c r="G12" s="185"/>
-      <c r="H12" s="185"/>
-      <c r="I12" s="185"/>
-      <c r="J12" s="185"/>
-      <c r="K12" s="186"/>
+      <c r="B12" s="197"/>
+      <c r="C12" s="197"/>
+      <c r="D12" s="197"/>
+      <c r="E12" s="197"/>
+      <c r="F12" s="197"/>
+      <c r="G12" s="197"/>
+      <c r="H12" s="197"/>
+      <c r="I12" s="197"/>
+      <c r="J12" s="197"/>
+      <c r="K12" s="198"/>
     </row>
     <row r="13" spans="1:12" s="65" customFormat="1" ht="76.5" outlineLevel="1">
       <c r="A13" s="90" t="s">
@@ -6237,11 +6237,11 @@
       <c r="C13" s="92" t="s">
         <v>536</v>
       </c>
-      <c r="D13" s="207" t="s">
+      <c r="D13" s="187" t="s">
         <v>537</v>
       </c>
-      <c r="E13" s="200"/>
-      <c r="F13" s="200"/>
+      <c r="E13" s="188"/>
+      <c r="F13" s="188"/>
       <c r="G13" s="95"/>
       <c r="H13" s="94"/>
       <c r="I13" s="96"/>
@@ -6251,11 +6251,11 @@
       <c r="K13" s="92"/>
     </row>
     <row r="14" spans="1:12" s="65" customFormat="1" ht="12.75" outlineLevel="1">
-      <c r="A14" s="239" t="s">
+      <c r="A14" s="253" t="s">
         <v>538</v>
       </c>
-      <c r="B14" s="223"/>
-      <c r="C14" s="223"/>
+      <c r="B14" s="235"/>
+      <c r="C14" s="235"/>
       <c r="D14" s="88"/>
       <c r="E14" s="88"/>
       <c r="F14" s="88"/>
@@ -6275,11 +6275,11 @@
       <c r="C15" s="98" t="s">
         <v>540</v>
       </c>
-      <c r="D15" s="228" t="s">
+      <c r="D15" s="236" t="s">
         <v>541</v>
       </c>
-      <c r="E15" s="200"/>
-      <c r="F15" s="200"/>
+      <c r="E15" s="188"/>
+      <c r="F15" s="188"/>
       <c r="G15" s="95"/>
       <c r="H15" s="94"/>
       <c r="I15" s="93"/>
@@ -6289,11 +6289,11 @@
       <c r="K15" s="92"/>
     </row>
     <row r="16" spans="1:12" s="65" customFormat="1" ht="12.75" outlineLevel="1">
-      <c r="A16" s="239" t="s">
+      <c r="A16" s="253" t="s">
         <v>542</v>
       </c>
-      <c r="B16" s="223"/>
-      <c r="C16" s="223"/>
+      <c r="B16" s="235"/>
+      <c r="C16" s="235"/>
       <c r="D16" s="88"/>
       <c r="E16" s="88"/>
       <c r="F16" s="88"/>
@@ -6313,11 +6313,11 @@
       <c r="C17" s="92" t="s">
         <v>543</v>
       </c>
-      <c r="D17" s="228" t="s">
+      <c r="D17" s="236" t="s">
         <v>544</v>
       </c>
-      <c r="E17" s="229"/>
-      <c r="F17" s="229"/>
+      <c r="E17" s="237"/>
+      <c r="F17" s="237"/>
       <c r="G17" s="95"/>
       <c r="H17" s="94"/>
       <c r="I17" s="93"/>
@@ -6366,12 +6366,11 @@
     <row r="55" ht="12" customHeight="1"/>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="B1:D2"/>
-    <mergeCell ref="D9:G10"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="I5:K5"/>
     <mergeCell ref="A16:C16"/>
     <mergeCell ref="D17:F17"/>
     <mergeCell ref="I6:K6"/>
@@ -6386,11 +6385,12 @@
     <mergeCell ref="I9:I10"/>
     <mergeCell ref="J9:J10"/>
     <mergeCell ref="K9:K10"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="B1:D2"/>
+    <mergeCell ref="D9:G10"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="B3:D3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -6484,10 +6484,10 @@
       <c r="F7" s="53" t="s">
         <v>68</v>
       </c>
-      <c r="G7" s="242" t="s">
+      <c r="G7" s="267" t="s">
         <v>550</v>
       </c>
-      <c r="H7" s="243"/>
+      <c r="H7" s="268"/>
     </row>
     <row r="8" spans="1:8" s="49" customFormat="1" ht="40.15" customHeight="1">
       <c r="A8" s="15"/>
@@ -6509,11 +6509,11 @@
         <f>COUNTIF(Auth!J10:J29, "Pending")</f>
         <v>0</v>
       </c>
-      <c r="G8" s="244">
+      <c r="G8" s="258">
         <f>Auth!D7</f>
         <v>26</v>
       </c>
-      <c r="H8" s="245"/>
+      <c r="H8" s="259"/>
     </row>
     <row r="9" spans="1:8" s="49" customFormat="1" ht="40.15" customHeight="1">
       <c r="A9" s="15"/>
@@ -6535,11 +6535,11 @@
         <f>COUNTIF(Home!J10:J29, "Pending")</f>
         <v>0</v>
       </c>
-      <c r="G9" s="246">
+      <c r="G9" s="260">
         <f>Home!D7</f>
         <v>17</v>
       </c>
-      <c r="H9" s="247"/>
+      <c r="H9" s="261"/>
     </row>
     <row r="10" spans="1:8" s="49" customFormat="1" ht="40.15" customHeight="1">
       <c r="A10" s="15"/>
@@ -6561,11 +6561,11 @@
         <f>COUNTIF(Favorite!J10:J29, "Pending")</f>
         <v>8</v>
       </c>
-      <c r="G10" s="248">
+      <c r="G10" s="269">
         <f>Favorite!D7</f>
         <v>8</v>
       </c>
-      <c r="H10" s="245"/>
+      <c r="H10" s="259"/>
     </row>
     <row r="11" spans="1:8" s="49" customFormat="1" ht="40.15" customHeight="1">
       <c r="A11" s="15"/>
@@ -6587,11 +6587,11 @@
         <f>COUNTIF(Booking!J10:J42, "Pending")</f>
         <v>23</v>
       </c>
-      <c r="G11" s="246">
+      <c r="G11" s="260">
         <f>Booking!D7</f>
         <v>23</v>
       </c>
-      <c r="H11" s="247"/>
+      <c r="H11" s="261"/>
     </row>
     <row r="12" spans="1:8" s="49" customFormat="1" ht="40.15" customHeight="1">
       <c r="A12" s="15"/>
@@ -6613,11 +6613,11 @@
         <f>COUNTIF('Cancel Booking'!J10:J29, "Pending")</f>
         <v>12</v>
       </c>
-      <c r="G12" s="244">
+      <c r="G12" s="258">
         <f>'Cancel Booking'!D7</f>
         <v>12</v>
       </c>
-      <c r="H12" s="245"/>
+      <c r="H12" s="259"/>
     </row>
     <row r="13" spans="1:8" s="49" customFormat="1" ht="40.15" customHeight="1">
       <c r="A13" s="15"/>
@@ -6639,11 +6639,11 @@
         <f>COUNTIF(Review!J10:J29, "Pending")</f>
         <v>10</v>
       </c>
-      <c r="G13" s="246">
+      <c r="G13" s="260">
         <f>Review!D7</f>
         <v>10</v>
       </c>
-      <c r="H13" s="247"/>
+      <c r="H13" s="261"/>
     </row>
     <row r="14" spans="1:8" s="49" customFormat="1" ht="40.15" customHeight="1">
       <c r="A14" s="15"/>
@@ -6665,11 +6665,11 @@
         <f>COUNTIF(Admin!J10:J29, "Pending")</f>
         <v>0</v>
       </c>
-      <c r="G14" s="244">
+      <c r="G14" s="258">
         <f>Admin!D7</f>
         <v>14</v>
       </c>
-      <c r="H14" s="245"/>
+      <c r="H14" s="259"/>
     </row>
     <row r="15" spans="1:8" ht="40.15" customHeight="1">
       <c r="A15" s="5"/>
@@ -6691,11 +6691,11 @@
         <f>COUNTIF(Venue!J10:J29, "Pending")</f>
         <v>6</v>
       </c>
-      <c r="G15" s="246">
+      <c r="G15" s="260">
         <f>Venue!D7</f>
         <v>6</v>
       </c>
-      <c r="H15" s="247"/>
+      <c r="H15" s="261"/>
     </row>
     <row r="16" spans="1:8" ht="40.15" customHeight="1">
       <c r="A16" s="5"/>
@@ -6715,11 +6715,11 @@
         <f>SUM(F8:F15)</f>
         <v>59</v>
       </c>
-      <c r="G16" s="253">
+      <c r="G16" s="262">
         <f>SUM(G8:H15)</f>
         <v>116</v>
       </c>
-      <c r="H16" s="254"/>
+      <c r="H16" s="263"/>
     </row>
     <row r="17" spans="1:9" ht="14.25">
       <c r="A17" s="5"/>
@@ -6869,7 +6869,7 @@
     </row>
     <row r="30" spans="1:9" ht="14.25">
       <c r="A30" s="5"/>
-      <c r="B30" s="249" t="s">
+      <c r="B30" s="264" t="s">
         <v>44</v>
       </c>
       <c r="C30" s="16" t="s">
@@ -6890,11 +6890,11 @@
       <c r="H30" s="21" t="s">
         <v>572</v>
       </c>
-      <c r="I30" s="252"/>
+      <c r="I30" s="257"/>
     </row>
     <row r="31" spans="1:9" ht="14.25">
       <c r="A31" s="5"/>
-      <c r="B31" s="250"/>
+      <c r="B31" s="255"/>
       <c r="C31" s="16" t="s">
         <v>573</v>
       </c>
@@ -6913,11 +6913,11 @@
       <c r="H31" s="26" t="s">
         <v>575</v>
       </c>
-      <c r="I31" s="252"/>
+      <c r="I31" s="257"/>
     </row>
     <row r="32" spans="1:9" ht="16.5" customHeight="1">
       <c r="A32" s="5"/>
-      <c r="B32" s="250"/>
+      <c r="B32" s="255"/>
       <c r="C32" s="16" t="s">
         <v>576</v>
       </c>
@@ -6936,11 +6936,11 @@
       <c r="H32" s="30" t="s">
         <v>577</v>
       </c>
-      <c r="I32" s="252"/>
+      <c r="I32" s="257"/>
     </row>
     <row r="33" spans="1:9" ht="15" customHeight="1">
       <c r="A33" s="5"/>
-      <c r="B33" s="250"/>
+      <c r="B33" s="255"/>
       <c r="C33" s="16" t="s">
         <v>578</v>
       </c>
@@ -6959,59 +6959,59 @@
       <c r="H33" s="33" t="s">
         <v>587</v>
       </c>
-      <c r="I33" s="252"/>
+      <c r="I33" s="257"/>
     </row>
     <row r="34" spans="1:9" ht="14.25">
       <c r="A34" s="5"/>
-      <c r="B34" s="262"/>
-      <c r="C34" s="263" t="s">
+      <c r="B34" s="265"/>
+      <c r="C34" s="177" t="s">
         <v>579</v>
       </c>
-      <c r="D34" s="264">
+      <c r="D34" s="178">
         <v>167</v>
       </c>
-      <c r="E34" s="265">
+      <c r="E34" s="179">
         <v>5</v>
       </c>
-      <c r="F34" s="266">
+      <c r="F34" s="180">
         <v>0.97</v>
       </c>
-      <c r="G34" s="267" t="s">
+      <c r="G34" s="181" t="s">
         <v>580</v>
       </c>
-      <c r="H34" s="268" t="s">
+      <c r="H34" s="182" t="s">
         <v>581</v>
       </c>
-      <c r="I34" s="269"/>
+      <c r="I34" s="266"/>
     </row>
     <row r="35" spans="1:9" ht="14.25">
       <c r="A35" s="15"/>
-      <c r="B35" s="255" t="s">
+      <c r="B35" s="254" t="s">
         <v>585</v>
       </c>
-      <c r="C35" s="256" t="s">
+      <c r="C35" s="171" t="s">
         <v>571</v>
       </c>
-      <c r="D35" s="257">
+      <c r="D35" s="172">
         <v>12</v>
       </c>
-      <c r="E35" s="258">
+      <c r="E35" s="173">
         <v>0</v>
       </c>
-      <c r="F35" s="259">
+      <c r="F35" s="174">
         <v>1</v>
       </c>
-      <c r="G35" s="260" t="s">
+      <c r="G35" s="175" t="s">
         <v>572</v>
       </c>
-      <c r="H35" s="261" t="s">
+      <c r="H35" s="176" t="s">
         <v>572</v>
       </c>
-      <c r="I35" s="252"/>
+      <c r="I35" s="257"/>
     </row>
     <row r="36" spans="1:9" ht="17.25" customHeight="1">
       <c r="A36" s="15"/>
-      <c r="B36" s="250"/>
+      <c r="B36" s="255"/>
       <c r="C36" s="16" t="s">
         <v>573</v>
       </c>
@@ -7030,11 +7030,11 @@
       <c r="H36" s="26" t="s">
         <v>575</v>
       </c>
-      <c r="I36" s="252"/>
+      <c r="I36" s="257"/>
     </row>
     <row r="37" spans="1:9" ht="15.75" customHeight="1">
       <c r="A37" s="15"/>
-      <c r="B37" s="250"/>
+      <c r="B37" s="255"/>
       <c r="C37" s="16" t="s">
         <v>576</v>
       </c>
@@ -7053,11 +7053,11 @@
       <c r="H37" s="30" t="s">
         <v>577</v>
       </c>
-      <c r="I37" s="252"/>
+      <c r="I37" s="257"/>
     </row>
     <row r="38" spans="1:9" ht="12.75" customHeight="1">
       <c r="A38" s="15"/>
-      <c r="B38" s="250"/>
+      <c r="B38" s="255"/>
       <c r="C38" s="16" t="s">
         <v>578</v>
       </c>
@@ -7076,11 +7076,11 @@
       <c r="H38" s="33" t="s">
         <v>584</v>
       </c>
-      <c r="I38" s="252"/>
+      <c r="I38" s="257"/>
     </row>
     <row r="39" spans="1:9" ht="14.25" customHeight="1">
       <c r="A39" s="15"/>
-      <c r="B39" s="251"/>
+      <c r="B39" s="256"/>
       <c r="C39" s="16" t="s">
         <v>579</v>
       </c>
@@ -7099,7 +7099,7 @@
       <c r="H39" s="37" t="s">
         <v>581</v>
       </c>
-      <c r="I39" s="252"/>
+      <c r="I39" s="257"/>
     </row>
     <row r="40" spans="1:9" ht="14.25">
       <c r="A40" s="5"/>
@@ -7133,6 +7133,11 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="G11:H11"/>
     <mergeCell ref="B35:B39"/>
     <mergeCell ref="I35:I39"/>
     <mergeCell ref="G12:H12"/>
@@ -7142,11 +7147,6 @@
     <mergeCell ref="G16:H16"/>
     <mergeCell ref="B30:B34"/>
     <mergeCell ref="I30:I34"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="G11:H11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
@@ -7201,52 +7201,52 @@
       <c r="A3" s="70" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="171" t="s">
+      <c r="B3" s="221" t="s">
         <v>62</v>
       </c>
-      <c r="C3" s="171"/>
-      <c r="D3" s="172"/>
+      <c r="C3" s="221"/>
+      <c r="D3" s="222"/>
       <c r="E3" s="71"/>
       <c r="F3" s="71"/>
       <c r="G3" s="71"/>
       <c r="H3" s="71"/>
-      <c r="I3" s="173"/>
-      <c r="J3" s="173"/>
-      <c r="K3" s="173"/>
+      <c r="I3" s="205"/>
+      <c r="J3" s="205"/>
+      <c r="K3" s="205"/>
     </row>
     <row r="4" spans="1:11" ht="14.25">
       <c r="A4" s="74" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="174" t="s">
+      <c r="B4" s="223" t="s">
         <v>64</v>
       </c>
-      <c r="C4" s="175"/>
-      <c r="D4" s="176"/>
+      <c r="C4" s="224"/>
+      <c r="D4" s="225"/>
       <c r="E4" s="71"/>
       <c r="F4" s="71"/>
       <c r="G4" s="71"/>
       <c r="H4" s="71"/>
-      <c r="I4" s="173"/>
-      <c r="J4" s="173"/>
-      <c r="K4" s="173"/>
+      <c r="I4" s="205"/>
+      <c r="J4" s="205"/>
+      <c r="K4" s="205"/>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="74" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="177" t="s">
+      <c r="B5" s="226" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="178"/>
-      <c r="D5" s="179"/>
+      <c r="C5" s="227"/>
+      <c r="D5" s="228"/>
       <c r="E5" s="75"/>
       <c r="F5" s="75"/>
       <c r="G5" s="75"/>
       <c r="H5" s="75"/>
-      <c r="I5" s="180"/>
-      <c r="J5" s="180"/>
-      <c r="K5" s="180"/>
+      <c r="I5" s="229"/>
+      <c r="J5" s="229"/>
+      <c r="K5" s="229"/>
     </row>
     <row r="6" spans="1:11" ht="14.25">
       <c r="A6" s="77" t="s">
@@ -7265,9 +7265,9 @@
       <c r="F6" s="72"/>
       <c r="G6" s="72"/>
       <c r="H6" s="72"/>
-      <c r="I6" s="173"/>
-      <c r="J6" s="173"/>
-      <c r="K6" s="173"/>
+      <c r="I6" s="205"/>
+      <c r="J6" s="205"/>
+      <c r="K6" s="205"/>
     </row>
     <row r="7" spans="1:11" ht="14.25">
       <c r="A7" s="81" t="s">
@@ -7287,15 +7287,15 @@
       <c r="F7" s="85"/>
       <c r="G7" s="85"/>
       <c r="H7" s="85"/>
-      <c r="I7" s="173"/>
-      <c r="J7" s="173"/>
-      <c r="K7" s="173"/>
+      <c r="I7" s="205"/>
+      <c r="J7" s="205"/>
+      <c r="K7" s="205"/>
     </row>
     <row r="8" spans="1:11" ht="14.25">
-      <c r="A8" s="181"/>
-      <c r="B8" s="181"/>
-      <c r="C8" s="181"/>
-      <c r="D8" s="181"/>
+      <c r="A8" s="206"/>
+      <c r="B8" s="206"/>
+      <c r="C8" s="206"/>
+      <c r="D8" s="206"/>
       <c r="E8" s="72"/>
       <c r="F8" s="72"/>
       <c r="G8" s="72"/>
@@ -7305,74 +7305,74 @@
       <c r="K8" s="86"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="187" t="s">
+      <c r="A9" s="209" t="s">
         <v>71</v>
       </c>
-      <c r="B9" s="189" t="s">
+      <c r="B9" s="211" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="187" t="s">
+      <c r="C9" s="209" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="193" t="s">
+      <c r="D9" s="215" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="194"/>
-      <c r="F9" s="194"/>
-      <c r="G9" s="195"/>
-      <c r="H9" s="191" t="s">
+      <c r="E9" s="216"/>
+      <c r="F9" s="216"/>
+      <c r="G9" s="217"/>
+      <c r="H9" s="213" t="s">
         <v>75</v>
       </c>
-      <c r="I9" s="192" t="s">
+      <c r="I9" s="214" t="s">
         <v>76</v>
       </c>
-      <c r="J9" s="192" t="s">
+      <c r="J9" s="214" t="s">
         <v>77</v>
       </c>
-      <c r="K9" s="192" t="s">
+      <c r="K9" s="214" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="188"/>
-      <c r="B10" s="190"/>
-      <c r="C10" s="188"/>
-      <c r="D10" s="196"/>
-      <c r="E10" s="197"/>
-      <c r="F10" s="197"/>
-      <c r="G10" s="198"/>
-      <c r="H10" s="187"/>
-      <c r="I10" s="187"/>
-      <c r="J10" s="187"/>
-      <c r="K10" s="187"/>
+      <c r="A10" s="210"/>
+      <c r="B10" s="212"/>
+      <c r="C10" s="210"/>
+      <c r="D10" s="218"/>
+      <c r="E10" s="219"/>
+      <c r="F10" s="219"/>
+      <c r="G10" s="220"/>
+      <c r="H10" s="209"/>
+      <c r="I10" s="209"/>
+      <c r="J10" s="209"/>
+      <c r="K10" s="209"/>
     </row>
     <row r="11" spans="1:11" ht="15">
-      <c r="A11" s="182"/>
-      <c r="B11" s="182"/>
-      <c r="C11" s="182"/>
-      <c r="D11" s="182"/>
-      <c r="E11" s="182"/>
-      <c r="F11" s="182"/>
-      <c r="G11" s="182"/>
-      <c r="H11" s="182"/>
-      <c r="I11" s="182"/>
-      <c r="J11" s="182"/>
-      <c r="K11" s="183"/>
+      <c r="A11" s="207"/>
+      <c r="B11" s="207"/>
+      <c r="C11" s="207"/>
+      <c r="D11" s="207"/>
+      <c r="E11" s="207"/>
+      <c r="F11" s="207"/>
+      <c r="G11" s="207"/>
+      <c r="H11" s="207"/>
+      <c r="I11" s="207"/>
+      <c r="J11" s="207"/>
+      <c r="K11" s="208"/>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="184" t="s">
+      <c r="A12" s="196" t="s">
         <v>79</v>
       </c>
-      <c r="B12" s="185"/>
-      <c r="C12" s="185"/>
-      <c r="D12" s="185"/>
-      <c r="E12" s="185"/>
-      <c r="F12" s="185"/>
-      <c r="G12" s="185"/>
-      <c r="H12" s="185"/>
-      <c r="I12" s="185"/>
-      <c r="J12" s="185"/>
-      <c r="K12" s="186"/>
+      <c r="B12" s="197"/>
+      <c r="C12" s="197"/>
+      <c r="D12" s="197"/>
+      <c r="E12" s="197"/>
+      <c r="F12" s="197"/>
+      <c r="G12" s="197"/>
+      <c r="H12" s="197"/>
+      <c r="I12" s="197"/>
+      <c r="J12" s="197"/>
+      <c r="K12" s="198"/>
     </row>
     <row r="13" spans="1:11" ht="63.75">
       <c r="A13" s="90" t="s">
@@ -7387,9 +7387,9 @@
       <c r="D13" s="199" t="s">
         <v>83</v>
       </c>
-      <c r="E13" s="200"/>
-      <c r="F13" s="200"/>
-      <c r="G13" s="201"/>
+      <c r="E13" s="188"/>
+      <c r="F13" s="188"/>
+      <c r="G13" s="189"/>
       <c r="H13" s="94"/>
       <c r="I13" s="96"/>
       <c r="J13" s="92" t="s">
@@ -7398,19 +7398,19 @@
       <c r="K13" s="92"/>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="184" t="s">
+      <c r="A14" s="196" t="s">
         <v>84</v>
       </c>
-      <c r="B14" s="185"/>
-      <c r="C14" s="185"/>
-      <c r="D14" s="185"/>
-      <c r="E14" s="185"/>
-      <c r="F14" s="185"/>
-      <c r="G14" s="185"/>
-      <c r="H14" s="185"/>
-      <c r="I14" s="185"/>
-      <c r="J14" s="185"/>
-      <c r="K14" s="186"/>
+      <c r="B14" s="197"/>
+      <c r="C14" s="197"/>
+      <c r="D14" s="197"/>
+      <c r="E14" s="197"/>
+      <c r="F14" s="197"/>
+      <c r="G14" s="197"/>
+      <c r="H14" s="197"/>
+      <c r="I14" s="197"/>
+      <c r="J14" s="197"/>
+      <c r="K14" s="198"/>
     </row>
     <row r="15" spans="1:11" ht="63.75">
       <c r="A15" s="102" t="s">
@@ -7422,12 +7422,12 @@
       <c r="C15" s="102" t="s">
         <v>87</v>
       </c>
-      <c r="D15" s="202" t="s">
+      <c r="D15" s="200" t="s">
         <v>88</v>
       </c>
-      <c r="E15" s="203"/>
-      <c r="F15" s="203"/>
-      <c r="G15" s="204"/>
+      <c r="E15" s="201"/>
+      <c r="F15" s="201"/>
+      <c r="G15" s="202"/>
       <c r="H15" s="103"/>
       <c r="I15" s="103"/>
       <c r="J15" s="104" t="s">
@@ -7436,11 +7436,11 @@
       <c r="K15" s="103"/>
     </row>
     <row r="16" spans="1:11">
-      <c r="A16" s="184" t="s">
+      <c r="A16" s="196" t="s">
         <v>89</v>
       </c>
-      <c r="B16" s="185"/>
-      <c r="C16" s="185"/>
+      <c r="B16" s="197"/>
+      <c r="C16" s="197"/>
       <c r="D16" s="88"/>
       <c r="E16" s="88"/>
       <c r="F16" s="88"/>
@@ -7463,9 +7463,9 @@
       <c r="D17" s="199" t="s">
         <v>93</v>
       </c>
-      <c r="E17" s="205"/>
-      <c r="F17" s="205"/>
-      <c r="G17" s="206"/>
+      <c r="E17" s="203"/>
+      <c r="F17" s="203"/>
+      <c r="G17" s="204"/>
       <c r="H17" s="94"/>
       <c r="I17" s="93"/>
       <c r="J17" s="92" t="s">
@@ -7474,11 +7474,11 @@
       <c r="K17" s="92"/>
     </row>
     <row r="18" spans="1:11">
-      <c r="A18" s="184" t="s">
+      <c r="A18" s="196" t="s">
         <v>94</v>
       </c>
-      <c r="B18" s="185"/>
-      <c r="C18" s="185"/>
+      <c r="B18" s="197"/>
+      <c r="C18" s="197"/>
       <c r="D18" s="88"/>
       <c r="E18" s="88"/>
       <c r="F18" s="88"/>
@@ -7498,12 +7498,12 @@
       <c r="C19" s="92" t="s">
         <v>97</v>
       </c>
-      <c r="D19" s="207" t="s">
+      <c r="D19" s="187" t="s">
         <v>98</v>
       </c>
-      <c r="E19" s="200"/>
-      <c r="F19" s="200"/>
-      <c r="G19" s="201"/>
+      <c r="E19" s="188"/>
+      <c r="F19" s="188"/>
+      <c r="G19" s="189"/>
       <c r="H19" s="94"/>
       <c r="I19" s="93"/>
       <c r="J19" s="92" t="s">
@@ -7512,11 +7512,11 @@
       <c r="K19" s="92"/>
     </row>
     <row r="20" spans="1:11">
-      <c r="A20" s="184" t="s">
+      <c r="A20" s="196" t="s">
         <v>99</v>
       </c>
-      <c r="B20" s="185"/>
-      <c r="C20" s="185"/>
+      <c r="B20" s="197"/>
+      <c r="C20" s="197"/>
       <c r="D20" s="88"/>
       <c r="E20" s="88"/>
       <c r="F20" s="88"/>
@@ -7536,12 +7536,12 @@
       <c r="C21" s="92" t="s">
         <v>102</v>
       </c>
-      <c r="D21" s="207" t="s">
+      <c r="D21" s="187" t="s">
         <v>103</v>
       </c>
-      <c r="E21" s="200"/>
-      <c r="F21" s="200"/>
-      <c r="G21" s="201"/>
+      <c r="E21" s="188"/>
+      <c r="F21" s="188"/>
+      <c r="G21" s="189"/>
       <c r="H21" s="94"/>
       <c r="I21" s="93"/>
       <c r="J21" s="92" t="s">
@@ -7559,12 +7559,12 @@
       <c r="C22" s="92" t="s">
         <v>106</v>
       </c>
-      <c r="D22" s="207" t="s">
+      <c r="D22" s="187" t="s">
         <v>107</v>
       </c>
-      <c r="E22" s="200"/>
-      <c r="F22" s="200"/>
-      <c r="G22" s="201"/>
+      <c r="E22" s="188"/>
+      <c r="F22" s="188"/>
+      <c r="G22" s="189"/>
       <c r="H22" s="92"/>
       <c r="I22" s="92"/>
       <c r="J22" s="92" t="s">
@@ -7573,19 +7573,19 @@
       <c r="K22" s="92"/>
     </row>
     <row r="23" spans="1:11">
-      <c r="A23" s="184" t="s">
+      <c r="A23" s="196" t="s">
         <v>108</v>
       </c>
-      <c r="B23" s="185"/>
-      <c r="C23" s="185"/>
-      <c r="D23" s="185"/>
-      <c r="E23" s="185"/>
-      <c r="F23" s="185"/>
-      <c r="G23" s="185"/>
-      <c r="H23" s="185"/>
-      <c r="I23" s="185"/>
-      <c r="J23" s="185"/>
-      <c r="K23" s="186"/>
+      <c r="B23" s="197"/>
+      <c r="C23" s="197"/>
+      <c r="D23" s="197"/>
+      <c r="E23" s="197"/>
+      <c r="F23" s="197"/>
+      <c r="G23" s="197"/>
+      <c r="H23" s="197"/>
+      <c r="I23" s="197"/>
+      <c r="J23" s="197"/>
+      <c r="K23" s="198"/>
     </row>
     <row r="24" spans="1:11" ht="66.95" customHeight="1">
       <c r="A24" s="90" t="s">
@@ -7597,12 +7597,12 @@
       <c r="C24" s="92" t="s">
         <v>111</v>
       </c>
-      <c r="D24" s="207" t="s">
+      <c r="D24" s="187" t="s">
         <v>112</v>
       </c>
-      <c r="E24" s="200"/>
-      <c r="F24" s="200"/>
-      <c r="G24" s="201"/>
+      <c r="E24" s="188"/>
+      <c r="F24" s="188"/>
+      <c r="G24" s="189"/>
       <c r="H24" s="92"/>
       <c r="I24" s="92"/>
       <c r="J24" s="92" t="s">
@@ -7620,12 +7620,12 @@
       <c r="C25" s="92" t="s">
         <v>115</v>
       </c>
-      <c r="D25" s="207" t="s">
+      <c r="D25" s="187" t="s">
         <v>116</v>
       </c>
-      <c r="E25" s="200"/>
-      <c r="F25" s="200"/>
-      <c r="G25" s="201"/>
+      <c r="E25" s="188"/>
+      <c r="F25" s="188"/>
+      <c r="G25" s="189"/>
       <c r="H25" s="92"/>
       <c r="I25" s="92"/>
       <c r="J25" s="92" t="s">
@@ -7634,19 +7634,19 @@
       <c r="K25" s="92"/>
     </row>
     <row r="26" spans="1:11">
-      <c r="A26" s="184" t="s">
+      <c r="A26" s="196" t="s">
         <v>117</v>
       </c>
-      <c r="B26" s="185"/>
-      <c r="C26" s="185"/>
-      <c r="D26" s="185"/>
-      <c r="E26" s="185"/>
-      <c r="F26" s="185"/>
-      <c r="G26" s="185"/>
-      <c r="H26" s="185"/>
-      <c r="I26" s="185"/>
-      <c r="J26" s="185"/>
-      <c r="K26" s="186"/>
+      <c r="B26" s="197"/>
+      <c r="C26" s="197"/>
+      <c r="D26" s="197"/>
+      <c r="E26" s="197"/>
+      <c r="F26" s="197"/>
+      <c r="G26" s="197"/>
+      <c r="H26" s="197"/>
+      <c r="I26" s="197"/>
+      <c r="J26" s="197"/>
+      <c r="K26" s="198"/>
     </row>
     <row r="27" spans="1:11" s="137" customFormat="1" ht="63.75">
       <c r="A27" s="90" t="s">
@@ -7658,12 +7658,12 @@
       <c r="C27" s="92" t="s">
         <v>120</v>
       </c>
-      <c r="D27" s="207" t="s">
+      <c r="D27" s="187" t="s">
         <v>121</v>
       </c>
-      <c r="E27" s="200"/>
-      <c r="F27" s="200"/>
-      <c r="G27" s="201"/>
+      <c r="E27" s="188"/>
+      <c r="F27" s="188"/>
+      <c r="G27" s="189"/>
       <c r="H27" s="92"/>
       <c r="I27" s="92"/>
       <c r="J27" s="92" t="s">
@@ -7681,12 +7681,12 @@
       <c r="C28" s="92" t="s">
         <v>124</v>
       </c>
-      <c r="D28" s="207" t="s">
+      <c r="D28" s="187" t="s">
         <v>125</v>
       </c>
-      <c r="E28" s="200"/>
-      <c r="F28" s="200"/>
-      <c r="G28" s="201"/>
+      <c r="E28" s="188"/>
+      <c r="F28" s="188"/>
+      <c r="G28" s="189"/>
       <c r="H28" s="92"/>
       <c r="I28" s="92"/>
       <c r="J28" s="92" t="s">
@@ -7704,12 +7704,12 @@
       <c r="C29" s="92" t="s">
         <v>128</v>
       </c>
-      <c r="D29" s="207" t="s">
+      <c r="D29" s="187" t="s">
         <v>129</v>
       </c>
-      <c r="E29" s="200"/>
-      <c r="F29" s="200"/>
-      <c r="G29" s="201"/>
+      <c r="E29" s="188"/>
+      <c r="F29" s="188"/>
+      <c r="G29" s="189"/>
       <c r="H29" s="139"/>
       <c r="I29" s="139"/>
       <c r="J29" s="92" t="s">
@@ -7718,19 +7718,19 @@
       <c r="K29" s="139"/>
     </row>
     <row r="30" spans="1:11">
-      <c r="A30" s="208" t="s">
+      <c r="A30" s="190" t="s">
         <v>130</v>
       </c>
-      <c r="B30" s="209"/>
-      <c r="C30" s="209"/>
-      <c r="D30" s="209"/>
-      <c r="E30" s="209"/>
-      <c r="F30" s="209"/>
-      <c r="G30" s="209"/>
-      <c r="H30" s="209"/>
-      <c r="I30" s="209"/>
-      <c r="J30" s="209"/>
-      <c r="K30" s="210"/>
+      <c r="B30" s="191"/>
+      <c r="C30" s="191"/>
+      <c r="D30" s="191"/>
+      <c r="E30" s="191"/>
+      <c r="F30" s="191"/>
+      <c r="G30" s="191"/>
+      <c r="H30" s="191"/>
+      <c r="I30" s="191"/>
+      <c r="J30" s="191"/>
+      <c r="K30" s="192"/>
     </row>
     <row r="31" spans="1:11" ht="102">
       <c r="A31" s="90" t="s">
@@ -7742,12 +7742,12 @@
       <c r="C31" s="92" t="s">
         <v>132</v>
       </c>
-      <c r="D31" s="211" t="s">
+      <c r="D31" s="185" t="s">
         <v>133</v>
       </c>
-      <c r="E31" s="212"/>
-      <c r="F31" s="212"/>
-      <c r="G31" s="212"/>
+      <c r="E31" s="186"/>
+      <c r="F31" s="186"/>
+      <c r="G31" s="186"/>
       <c r="H31" s="92"/>
       <c r="I31" s="125"/>
       <c r="J31" s="92" t="s">
@@ -7765,12 +7765,12 @@
       <c r="C32" s="141" t="s">
         <v>135</v>
       </c>
-      <c r="D32" s="213" t="s">
+      <c r="D32" s="193" t="s">
         <v>136</v>
       </c>
-      <c r="E32" s="214"/>
-      <c r="F32" s="214"/>
-      <c r="G32" s="215"/>
+      <c r="E32" s="194"/>
+      <c r="F32" s="194"/>
+      <c r="G32" s="195"/>
       <c r="H32" s="141"/>
       <c r="I32" s="141"/>
       <c r="J32" s="140" t="s">
@@ -7788,12 +7788,12 @@
       <c r="C33" s="92" t="s">
         <v>138</v>
       </c>
-      <c r="D33" s="211" t="s">
+      <c r="D33" s="185" t="s">
         <v>139</v>
       </c>
-      <c r="E33" s="212"/>
-      <c r="F33" s="212"/>
-      <c r="G33" s="212"/>
+      <c r="E33" s="186"/>
+      <c r="F33" s="186"/>
+      <c r="G33" s="186"/>
       <c r="H33" s="92"/>
       <c r="I33" s="125"/>
       <c r="J33" s="92" t="s">
@@ -7811,12 +7811,12 @@
       <c r="C34" s="92" t="s">
         <v>141</v>
       </c>
-      <c r="D34" s="211" t="s">
+      <c r="D34" s="185" t="s">
         <v>142</v>
       </c>
-      <c r="E34" s="212"/>
-      <c r="F34" s="212"/>
-      <c r="G34" s="212"/>
+      <c r="E34" s="186"/>
+      <c r="F34" s="186"/>
+      <c r="G34" s="186"/>
       <c r="H34" s="92"/>
       <c r="I34" s="125"/>
       <c r="J34" s="92" t="s">
@@ -7834,12 +7834,12 @@
       <c r="C35" s="92" t="s">
         <v>144</v>
       </c>
-      <c r="D35" s="211" t="s">
+      <c r="D35" s="185" t="s">
         <v>145</v>
       </c>
-      <c r="E35" s="212"/>
-      <c r="F35" s="212"/>
-      <c r="G35" s="212"/>
+      <c r="E35" s="186"/>
+      <c r="F35" s="186"/>
+      <c r="G35" s="186"/>
       <c r="H35" s="92"/>
       <c r="I35" s="125"/>
       <c r="J35" s="92" t="s">
@@ -7857,12 +7857,12 @@
       <c r="C36" s="92" t="s">
         <v>147</v>
       </c>
-      <c r="D36" s="211" t="s">
+      <c r="D36" s="185" t="s">
         <v>148</v>
       </c>
-      <c r="E36" s="212"/>
-      <c r="F36" s="212"/>
-      <c r="G36" s="212"/>
+      <c r="E36" s="186"/>
+      <c r="F36" s="186"/>
+      <c r="G36" s="186"/>
       <c r="H36" s="92"/>
       <c r="I36" s="125"/>
       <c r="J36" s="92" t="s">
@@ -7880,12 +7880,12 @@
       <c r="C37" s="98" t="s">
         <v>150</v>
       </c>
-      <c r="D37" s="216" t="s">
+      <c r="D37" s="183" t="s">
         <v>151</v>
       </c>
-      <c r="E37" s="217"/>
-      <c r="F37" s="217"/>
-      <c r="G37" s="217"/>
+      <c r="E37" s="184"/>
+      <c r="F37" s="184"/>
+      <c r="G37" s="184"/>
       <c r="H37" s="98"/>
       <c r="I37" s="142"/>
       <c r="J37" s="98" t="s">
@@ -7903,12 +7903,12 @@
       <c r="C38" s="98" t="s">
         <v>153</v>
       </c>
-      <c r="D38" s="216" t="s">
+      <c r="D38" s="183" t="s">
         <v>154</v>
       </c>
-      <c r="E38" s="217"/>
-      <c r="F38" s="217"/>
-      <c r="G38" s="217"/>
+      <c r="E38" s="184"/>
+      <c r="F38" s="184"/>
+      <c r="G38" s="184"/>
       <c r="H38" s="98"/>
       <c r="I38" s="142"/>
       <c r="J38" s="98" t="s">
@@ -7926,12 +7926,12 @@
       <c r="C39" s="92" t="s">
         <v>156</v>
       </c>
-      <c r="D39" s="211" t="s">
+      <c r="D39" s="185" t="s">
         <v>157</v>
       </c>
-      <c r="E39" s="212"/>
-      <c r="F39" s="212"/>
-      <c r="G39" s="212"/>
+      <c r="E39" s="186"/>
+      <c r="F39" s="186"/>
+      <c r="G39" s="186"/>
       <c r="H39" s="92"/>
       <c r="I39" s="125"/>
       <c r="J39" s="92" t="s">
@@ -7949,12 +7949,12 @@
       <c r="C40" s="92" t="s">
         <v>159</v>
       </c>
-      <c r="D40" s="211" t="s">
+      <c r="D40" s="185" t="s">
         <v>160</v>
       </c>
-      <c r="E40" s="212"/>
-      <c r="F40" s="212"/>
-      <c r="G40" s="212"/>
+      <c r="E40" s="186"/>
+      <c r="F40" s="186"/>
+      <c r="G40" s="186"/>
       <c r="H40" s="92"/>
       <c r="I40" s="125"/>
       <c r="J40" s="92" t="s">
@@ -7972,12 +7972,12 @@
       <c r="C41" s="92" t="s">
         <v>159</v>
       </c>
-      <c r="D41" s="211" t="s">
+      <c r="D41" s="185" t="s">
         <v>160</v>
       </c>
-      <c r="E41" s="212"/>
-      <c r="F41" s="212"/>
-      <c r="G41" s="212"/>
+      <c r="E41" s="186"/>
+      <c r="F41" s="186"/>
+      <c r="G41" s="186"/>
       <c r="H41" s="92"/>
       <c r="I41" s="125"/>
       <c r="J41" s="92" t="s">
@@ -7995,12 +7995,12 @@
       <c r="C42" s="92" t="s">
         <v>163</v>
       </c>
-      <c r="D42" s="211" t="s">
+      <c r="D42" s="185" t="s">
         <v>164</v>
       </c>
-      <c r="E42" s="212"/>
-      <c r="F42" s="212"/>
-      <c r="G42" s="212"/>
+      <c r="E42" s="186"/>
+      <c r="F42" s="186"/>
+      <c r="G42" s="186"/>
       <c r="H42" s="92"/>
       <c r="I42" s="125"/>
       <c r="J42" s="92" t="s">
@@ -8010,36 +8010,12 @@
     </row>
   </sheetData>
   <mergeCells count="49">
-    <mergeCell ref="D38:G38"/>
-    <mergeCell ref="D39:G39"/>
-    <mergeCell ref="D40:G40"/>
-    <mergeCell ref="D41:G41"/>
-    <mergeCell ref="D42:G42"/>
-    <mergeCell ref="D33:G33"/>
-    <mergeCell ref="D34:G34"/>
-    <mergeCell ref="D35:G35"/>
-    <mergeCell ref="D36:G36"/>
-    <mergeCell ref="D37:G37"/>
-    <mergeCell ref="D28:G28"/>
-    <mergeCell ref="D29:G29"/>
-    <mergeCell ref="A30:K30"/>
-    <mergeCell ref="D31:G31"/>
-    <mergeCell ref="D32:G32"/>
-    <mergeCell ref="A23:K23"/>
-    <mergeCell ref="D24:G24"/>
-    <mergeCell ref="D25:G25"/>
-    <mergeCell ref="A26:K26"/>
-    <mergeCell ref="D27:G27"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="D19:G19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="D21:G21"/>
-    <mergeCell ref="D22:G22"/>
-    <mergeCell ref="D13:G13"/>
-    <mergeCell ref="A14:K14"/>
-    <mergeCell ref="D15:G15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="D17:G17"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="I5:K5"/>
     <mergeCell ref="I6:K6"/>
     <mergeCell ref="I7:K7"/>
     <mergeCell ref="A8:D8"/>
@@ -8053,12 +8029,36 @@
     <mergeCell ref="J9:J10"/>
     <mergeCell ref="K9:K10"/>
     <mergeCell ref="D9:G10"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="D13:G13"/>
+    <mergeCell ref="A14:K14"/>
+    <mergeCell ref="D15:G15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="D17:G17"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="D19:G19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="D21:G21"/>
+    <mergeCell ref="D22:G22"/>
+    <mergeCell ref="A23:K23"/>
+    <mergeCell ref="D24:G24"/>
+    <mergeCell ref="D25:G25"/>
+    <mergeCell ref="A26:K26"/>
+    <mergeCell ref="D27:G27"/>
+    <mergeCell ref="D28:G28"/>
+    <mergeCell ref="D29:G29"/>
+    <mergeCell ref="A30:K30"/>
+    <mergeCell ref="D31:G31"/>
+    <mergeCell ref="D32:G32"/>
+    <mergeCell ref="D33:G33"/>
+    <mergeCell ref="D34:G34"/>
+    <mergeCell ref="D35:G35"/>
+    <mergeCell ref="D36:G36"/>
+    <mergeCell ref="D37:G37"/>
+    <mergeCell ref="D38:G38"/>
+    <mergeCell ref="D39:G39"/>
+    <mergeCell ref="D40:G40"/>
+    <mergeCell ref="D41:G41"/>
+    <mergeCell ref="D42:G42"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8094,31 +8094,31 @@
       <c r="A3" s="70" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="171" t="s">
+      <c r="B3" s="221" t="s">
         <v>62</v>
       </c>
-      <c r="C3" s="171"/>
-      <c r="D3" s="172"/>
+      <c r="C3" s="221"/>
+      <c r="D3" s="222"/>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="74" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="174" t="s">
+      <c r="B4" s="223" t="s">
         <v>166</v>
       </c>
-      <c r="C4" s="175"/>
-      <c r="D4" s="176"/>
+      <c r="C4" s="224"/>
+      <c r="D4" s="225"/>
     </row>
     <row r="5" spans="1:11" ht="25.5">
       <c r="A5" s="74" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="177" t="s">
+      <c r="B5" s="226" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="178"/>
-      <c r="D5" s="179"/>
+      <c r="C5" s="227"/>
+      <c r="D5" s="228"/>
     </row>
     <row r="6" spans="1:11" ht="14.25">
       <c r="A6" s="77" t="s">
@@ -8149,74 +8149,74 @@
       </c>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="187" t="s">
+      <c r="A9" s="209" t="s">
         <v>71</v>
       </c>
-      <c r="B9" s="189" t="s">
+      <c r="B9" s="211" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="187" t="s">
+      <c r="C9" s="209" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="193" t="s">
+      <c r="D9" s="215" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="194"/>
-      <c r="F9" s="194"/>
-      <c r="G9" s="195"/>
-      <c r="H9" s="191" t="s">
+      <c r="E9" s="216"/>
+      <c r="F9" s="216"/>
+      <c r="G9" s="217"/>
+      <c r="H9" s="213" t="s">
         <v>75</v>
       </c>
-      <c r="I9" s="192" t="s">
+      <c r="I9" s="214" t="s">
         <v>76</v>
       </c>
-      <c r="J9" s="192" t="s">
+      <c r="J9" s="214" t="s">
         <v>77</v>
       </c>
-      <c r="K9" s="192" t="s">
+      <c r="K9" s="214" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="188"/>
-      <c r="B10" s="190"/>
-      <c r="C10" s="188"/>
-      <c r="D10" s="196"/>
-      <c r="E10" s="197"/>
-      <c r="F10" s="197"/>
-      <c r="G10" s="198"/>
-      <c r="H10" s="187"/>
-      <c r="I10" s="187"/>
-      <c r="J10" s="187"/>
-      <c r="K10" s="187"/>
+      <c r="A10" s="210"/>
+      <c r="B10" s="212"/>
+      <c r="C10" s="210"/>
+      <c r="D10" s="218"/>
+      <c r="E10" s="219"/>
+      <c r="F10" s="219"/>
+      <c r="G10" s="220"/>
+      <c r="H10" s="209"/>
+      <c r="I10" s="209"/>
+      <c r="J10" s="209"/>
+      <c r="K10" s="209"/>
     </row>
     <row r="11" spans="1:11" ht="15">
-      <c r="A11" s="182"/>
-      <c r="B11" s="182"/>
-      <c r="C11" s="182"/>
-      <c r="D11" s="182"/>
-      <c r="E11" s="182"/>
-      <c r="F11" s="182"/>
-      <c r="G11" s="182"/>
-      <c r="H11" s="182"/>
-      <c r="I11" s="182"/>
-      <c r="J11" s="182"/>
-      <c r="K11" s="183"/>
+      <c r="A11" s="207"/>
+      <c r="B11" s="207"/>
+      <c r="C11" s="207"/>
+      <c r="D11" s="207"/>
+      <c r="E11" s="207"/>
+      <c r="F11" s="207"/>
+      <c r="G11" s="207"/>
+      <c r="H11" s="207"/>
+      <c r="I11" s="207"/>
+      <c r="J11" s="207"/>
+      <c r="K11" s="208"/>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="184" t="s">
+      <c r="A12" s="196" t="s">
         <v>167</v>
       </c>
-      <c r="B12" s="185"/>
-      <c r="C12" s="185"/>
-      <c r="D12" s="185"/>
-      <c r="E12" s="185"/>
-      <c r="F12" s="185"/>
-      <c r="G12" s="185"/>
-      <c r="H12" s="185"/>
-      <c r="I12" s="185"/>
-      <c r="J12" s="185"/>
-      <c r="K12" s="186"/>
+      <c r="B12" s="197"/>
+      <c r="C12" s="197"/>
+      <c r="D12" s="197"/>
+      <c r="E12" s="197"/>
+      <c r="F12" s="197"/>
+      <c r="G12" s="197"/>
+      <c r="H12" s="197"/>
+      <c r="I12" s="197"/>
+      <c r="J12" s="197"/>
+      <c r="K12" s="198"/>
     </row>
     <row r="13" spans="1:11" ht="90" customHeight="1">
       <c r="A13" s="90" t="s">
@@ -8231,9 +8231,9 @@
       <c r="D13" s="199" t="s">
         <v>170</v>
       </c>
-      <c r="E13" s="200"/>
-      <c r="F13" s="200"/>
-      <c r="G13" s="201"/>
+      <c r="E13" s="188"/>
+      <c r="F13" s="188"/>
+      <c r="G13" s="189"/>
       <c r="H13" s="94"/>
       <c r="I13" s="96"/>
       <c r="J13" s="92" t="s">
@@ -8254,9 +8254,9 @@
       <c r="D14" s="199" t="s">
         <v>173</v>
       </c>
-      <c r="E14" s="200"/>
-      <c r="F14" s="200"/>
-      <c r="G14" s="201"/>
+      <c r="E14" s="188"/>
+      <c r="F14" s="188"/>
+      <c r="G14" s="189"/>
       <c r="H14" s="94"/>
       <c r="I14" s="96"/>
       <c r="J14" s="92" t="s">
@@ -8277,9 +8277,9 @@
       <c r="D15" s="199" t="s">
         <v>176</v>
       </c>
-      <c r="E15" s="200"/>
-      <c r="F15" s="200"/>
-      <c r="G15" s="201"/>
+      <c r="E15" s="188"/>
+      <c r="F15" s="188"/>
+      <c r="G15" s="189"/>
       <c r="H15" s="94"/>
       <c r="I15" s="96"/>
       <c r="J15" s="92" t="s">
@@ -8300,9 +8300,9 @@
       <c r="D16" s="199" t="s">
         <v>179</v>
       </c>
-      <c r="E16" s="200"/>
-      <c r="F16" s="200"/>
-      <c r="G16" s="201"/>
+      <c r="E16" s="188"/>
+      <c r="F16" s="188"/>
+      <c r="G16" s="189"/>
       <c r="H16" s="94"/>
       <c r="I16" s="96"/>
       <c r="J16" s="92" t="s">
@@ -8323,9 +8323,9 @@
       <c r="D17" s="199" t="s">
         <v>182</v>
       </c>
-      <c r="E17" s="200"/>
-      <c r="F17" s="200"/>
-      <c r="G17" s="201"/>
+      <c r="E17" s="188"/>
+      <c r="F17" s="188"/>
+      <c r="G17" s="189"/>
       <c r="H17" s="94"/>
       <c r="I17" s="96"/>
       <c r="J17" s="92" t="s">
@@ -8346,9 +8346,9 @@
       <c r="D18" s="199" t="s">
         <v>185</v>
       </c>
-      <c r="E18" s="200"/>
-      <c r="F18" s="200"/>
-      <c r="G18" s="201"/>
+      <c r="E18" s="188"/>
+      <c r="F18" s="188"/>
+      <c r="G18" s="189"/>
       <c r="H18" s="94"/>
       <c r="I18" s="96"/>
       <c r="J18" s="92" t="s">
@@ -8369,9 +8369,9 @@
       <c r="D19" s="199" t="s">
         <v>188</v>
       </c>
-      <c r="E19" s="200"/>
-      <c r="F19" s="200"/>
-      <c r="G19" s="201"/>
+      <c r="E19" s="188"/>
+      <c r="F19" s="188"/>
+      <c r="G19" s="189"/>
       <c r="H19" s="94"/>
       <c r="I19" s="96"/>
       <c r="J19" s="92" t="s">
@@ -8380,19 +8380,19 @@
       <c r="K19" s="92"/>
     </row>
     <row r="20" spans="1:11">
-      <c r="A20" s="184" t="s">
+      <c r="A20" s="196" t="s">
         <v>189</v>
       </c>
-      <c r="B20" s="185"/>
-      <c r="C20" s="185"/>
-      <c r="D20" s="185"/>
-      <c r="E20" s="185"/>
-      <c r="F20" s="185"/>
-      <c r="G20" s="185"/>
-      <c r="H20" s="185"/>
-      <c r="I20" s="185"/>
-      <c r="J20" s="185"/>
-      <c r="K20" s="186"/>
+      <c r="B20" s="197"/>
+      <c r="C20" s="197"/>
+      <c r="D20" s="197"/>
+      <c r="E20" s="197"/>
+      <c r="F20" s="197"/>
+      <c r="G20" s="197"/>
+      <c r="H20" s="197"/>
+      <c r="I20" s="197"/>
+      <c r="J20" s="197"/>
+      <c r="K20" s="198"/>
     </row>
     <row r="21" spans="1:11" ht="41.1" customHeight="1">
       <c r="A21" s="90" t="s">
@@ -8407,9 +8407,9 @@
       <c r="D21" s="199" t="s">
         <v>192</v>
       </c>
-      <c r="E21" s="200"/>
-      <c r="F21" s="200"/>
-      <c r="G21" s="201"/>
+      <c r="E21" s="188"/>
+      <c r="F21" s="188"/>
+      <c r="G21" s="189"/>
       <c r="H21" s="94"/>
       <c r="I21" s="96"/>
       <c r="J21" s="92" t="s">
@@ -8430,9 +8430,9 @@
       <c r="D22" s="199" t="s">
         <v>195</v>
       </c>
-      <c r="E22" s="200"/>
-      <c r="F22" s="200"/>
-      <c r="G22" s="201"/>
+      <c r="E22" s="188"/>
+      <c r="F22" s="188"/>
+      <c r="G22" s="189"/>
       <c r="H22" s="94"/>
       <c r="I22" s="96"/>
       <c r="J22" s="92" t="s">
@@ -8453,9 +8453,9 @@
       <c r="D23" s="199" t="s">
         <v>198</v>
       </c>
-      <c r="E23" s="200"/>
-      <c r="F23" s="200"/>
-      <c r="G23" s="201"/>
+      <c r="E23" s="188"/>
+      <c r="F23" s="188"/>
+      <c r="G23" s="189"/>
       <c r="H23" s="94"/>
       <c r="I23" s="96"/>
       <c r="J23" s="92" t="s">
@@ -8464,26 +8464,26 @@
       <c r="K23" s="92"/>
     </row>
     <row r="24" spans="1:11">
-      <c r="A24" s="218"/>
-      <c r="B24" s="218"/>
-      <c r="C24" s="218"/>
-      <c r="D24" s="218"/>
-      <c r="E24" s="218"/>
-      <c r="F24" s="218"/>
-      <c r="G24" s="218"/>
-      <c r="H24" s="218"/>
-      <c r="I24" s="218"/>
-      <c r="J24" s="218"/>
-      <c r="K24" s="218"/>
+      <c r="A24" s="230"/>
+      <c r="B24" s="230"/>
+      <c r="C24" s="230"/>
+      <c r="D24" s="230"/>
+      <c r="E24" s="230"/>
+      <c r="F24" s="230"/>
+      <c r="G24" s="230"/>
+      <c r="H24" s="230"/>
+      <c r="I24" s="230"/>
+      <c r="J24" s="230"/>
+      <c r="K24" s="230"/>
     </row>
     <row r="25" spans="1:11" ht="35.1" customHeight="1">
       <c r="A25" s="133"/>
       <c r="B25" s="134"/>
       <c r="C25" s="135"/>
-      <c r="D25" s="219"/>
-      <c r="E25" s="220"/>
-      <c r="F25" s="220"/>
-      <c r="G25" s="220"/>
+      <c r="D25" s="231"/>
+      <c r="E25" s="232"/>
+      <c r="F25" s="232"/>
+      <c r="G25" s="232"/>
       <c r="H25" s="135"/>
       <c r="I25" s="136"/>
       <c r="J25" s="135"/>
@@ -8493,10 +8493,10 @@
       <c r="A26" s="133"/>
       <c r="B26" s="134"/>
       <c r="C26" s="135"/>
-      <c r="D26" s="219"/>
-      <c r="E26" s="220"/>
-      <c r="F26" s="220"/>
-      <c r="G26" s="220"/>
+      <c r="D26" s="231"/>
+      <c r="E26" s="232"/>
+      <c r="F26" s="232"/>
+      <c r="G26" s="232"/>
       <c r="H26" s="135"/>
       <c r="I26" s="136"/>
       <c r="J26" s="135"/>
@@ -8506,10 +8506,10 @@
       <c r="A27" s="133"/>
       <c r="B27" s="134"/>
       <c r="C27" s="135"/>
-      <c r="D27" s="219"/>
-      <c r="E27" s="220"/>
-      <c r="F27" s="220"/>
-      <c r="G27" s="220"/>
+      <c r="D27" s="231"/>
+      <c r="E27" s="232"/>
+      <c r="F27" s="232"/>
+      <c r="G27" s="232"/>
       <c r="H27" s="135"/>
       <c r="I27" s="136"/>
       <c r="J27" s="135"/>
@@ -8517,21 +8517,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="D23:G23"/>
-    <mergeCell ref="A24:K24"/>
-    <mergeCell ref="D25:G25"/>
-    <mergeCell ref="D26:G26"/>
-    <mergeCell ref="D27:G27"/>
-    <mergeCell ref="D18:G18"/>
-    <mergeCell ref="D19:G19"/>
-    <mergeCell ref="A20:K20"/>
-    <mergeCell ref="D21:G21"/>
-    <mergeCell ref="D22:G22"/>
-    <mergeCell ref="D13:G13"/>
-    <mergeCell ref="D14:G14"/>
-    <mergeCell ref="D15:G15"/>
-    <mergeCell ref="D16:G16"/>
-    <mergeCell ref="D17:G17"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B5:D5"/>
@@ -8545,6 +8530,21 @@
     <mergeCell ref="J9:J10"/>
     <mergeCell ref="K9:K10"/>
     <mergeCell ref="D9:G10"/>
+    <mergeCell ref="D13:G13"/>
+    <mergeCell ref="D14:G14"/>
+    <mergeCell ref="D15:G15"/>
+    <mergeCell ref="D16:G16"/>
+    <mergeCell ref="D17:G17"/>
+    <mergeCell ref="D18:G18"/>
+    <mergeCell ref="D19:G19"/>
+    <mergeCell ref="A20:K20"/>
+    <mergeCell ref="D21:G21"/>
+    <mergeCell ref="D22:G22"/>
+    <mergeCell ref="D23:G23"/>
+    <mergeCell ref="A24:K24"/>
+    <mergeCell ref="D25:G25"/>
+    <mergeCell ref="D26:G26"/>
+    <mergeCell ref="D27:G27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8581,31 +8581,31 @@
       <c r="A3" s="70" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="171" t="s">
+      <c r="B3" s="221" t="s">
         <v>62</v>
       </c>
-      <c r="C3" s="171"/>
-      <c r="D3" s="172"/>
+      <c r="C3" s="221"/>
+      <c r="D3" s="222"/>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="74" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="174" t="s">
+      <c r="B4" s="223" t="s">
         <v>200</v>
       </c>
-      <c r="C4" s="175"/>
-      <c r="D4" s="176"/>
+      <c r="C4" s="224"/>
+      <c r="D4" s="225"/>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="74" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="177" t="s">
+      <c r="B5" s="226" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="178"/>
-      <c r="D5" s="179"/>
+      <c r="C5" s="227"/>
+      <c r="D5" s="228"/>
     </row>
     <row r="6" spans="1:11" ht="14.25">
       <c r="A6" s="77" t="s">
@@ -8636,74 +8636,74 @@
       </c>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="187" t="s">
+      <c r="A9" s="209" t="s">
         <v>71</v>
       </c>
-      <c r="B9" s="189" t="s">
+      <c r="B9" s="211" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="187" t="s">
+      <c r="C9" s="209" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="193" t="s">
+      <c r="D9" s="215" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="194"/>
-      <c r="F9" s="194"/>
-      <c r="G9" s="195"/>
-      <c r="H9" s="191" t="s">
+      <c r="E9" s="216"/>
+      <c r="F9" s="216"/>
+      <c r="G9" s="217"/>
+      <c r="H9" s="213" t="s">
         <v>75</v>
       </c>
-      <c r="I9" s="192" t="s">
+      <c r="I9" s="214" t="s">
         <v>76</v>
       </c>
-      <c r="J9" s="192" t="s">
+      <c r="J9" s="214" t="s">
         <v>77</v>
       </c>
-      <c r="K9" s="192" t="s">
+      <c r="K9" s="214" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="188"/>
-      <c r="B10" s="190"/>
-      <c r="C10" s="188"/>
-      <c r="D10" s="196"/>
-      <c r="E10" s="197"/>
-      <c r="F10" s="197"/>
-      <c r="G10" s="198"/>
-      <c r="H10" s="187"/>
-      <c r="I10" s="187"/>
-      <c r="J10" s="187"/>
-      <c r="K10" s="187"/>
+      <c r="A10" s="210"/>
+      <c r="B10" s="212"/>
+      <c r="C10" s="210"/>
+      <c r="D10" s="218"/>
+      <c r="E10" s="219"/>
+      <c r="F10" s="219"/>
+      <c r="G10" s="220"/>
+      <c r="H10" s="209"/>
+      <c r="I10" s="209"/>
+      <c r="J10" s="209"/>
+      <c r="K10" s="209"/>
     </row>
     <row r="11" spans="1:11" ht="15">
-      <c r="A11" s="182"/>
-      <c r="B11" s="182"/>
-      <c r="C11" s="182"/>
-      <c r="D11" s="182"/>
-      <c r="E11" s="182"/>
-      <c r="F11" s="182"/>
-      <c r="G11" s="182"/>
-      <c r="H11" s="182"/>
-      <c r="I11" s="182"/>
-      <c r="J11" s="182"/>
-      <c r="K11" s="183"/>
+      <c r="A11" s="207"/>
+      <c r="B11" s="207"/>
+      <c r="C11" s="207"/>
+      <c r="D11" s="207"/>
+      <c r="E11" s="207"/>
+      <c r="F11" s="207"/>
+      <c r="G11" s="207"/>
+      <c r="H11" s="207"/>
+      <c r="I11" s="207"/>
+      <c r="J11" s="207"/>
+      <c r="K11" s="208"/>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="184" t="s">
+      <c r="A12" s="196" t="s">
         <v>201</v>
       </c>
-      <c r="B12" s="185"/>
-      <c r="C12" s="185"/>
-      <c r="D12" s="185"/>
-      <c r="E12" s="185"/>
-      <c r="F12" s="185"/>
-      <c r="G12" s="185"/>
-      <c r="H12" s="185"/>
-      <c r="I12" s="185"/>
-      <c r="J12" s="185"/>
-      <c r="K12" s="186"/>
+      <c r="B12" s="197"/>
+      <c r="C12" s="197"/>
+      <c r="D12" s="197"/>
+      <c r="E12" s="197"/>
+      <c r="F12" s="197"/>
+      <c r="G12" s="197"/>
+      <c r="H12" s="197"/>
+      <c r="I12" s="197"/>
+      <c r="J12" s="197"/>
+      <c r="K12" s="198"/>
     </row>
     <row r="13" spans="1:11" ht="93" customHeight="1">
       <c r="A13" s="90" t="s">
@@ -8718,9 +8718,9 @@
       <c r="D13" s="199" t="s">
         <v>204</v>
       </c>
-      <c r="E13" s="200"/>
-      <c r="F13" s="200"/>
-      <c r="G13" s="201"/>
+      <c r="E13" s="188"/>
+      <c r="F13" s="188"/>
+      <c r="G13" s="189"/>
       <c r="H13" s="94"/>
       <c r="I13" s="96"/>
       <c r="J13" s="92" t="s">
@@ -8741,9 +8741,9 @@
       <c r="D14" s="199" t="s">
         <v>207</v>
       </c>
-      <c r="E14" s="200"/>
-      <c r="F14" s="200"/>
-      <c r="G14" s="201"/>
+      <c r="E14" s="188"/>
+      <c r="F14" s="188"/>
+      <c r="G14" s="189"/>
       <c r="H14" s="94"/>
       <c r="I14" s="96"/>
       <c r="J14" s="92" t="s">
@@ -8764,9 +8764,9 @@
       <c r="D15" s="199" t="s">
         <v>210</v>
       </c>
-      <c r="E15" s="200"/>
-      <c r="F15" s="200"/>
-      <c r="G15" s="201"/>
+      <c r="E15" s="188"/>
+      <c r="F15" s="188"/>
+      <c r="G15" s="189"/>
       <c r="H15" s="94"/>
       <c r="I15" s="96"/>
       <c r="J15" s="92" t="s">
@@ -8787,9 +8787,9 @@
       <c r="D16" s="199" t="s">
         <v>213</v>
       </c>
-      <c r="E16" s="200"/>
-      <c r="F16" s="200"/>
-      <c r="G16" s="201"/>
+      <c r="E16" s="188"/>
+      <c r="F16" s="188"/>
+      <c r="G16" s="189"/>
       <c r="H16" s="94"/>
       <c r="I16" s="96"/>
       <c r="J16" s="92" t="s">
@@ -8810,9 +8810,9 @@
       <c r="D17" s="199" t="s">
         <v>216</v>
       </c>
-      <c r="E17" s="200"/>
-      <c r="F17" s="200"/>
-      <c r="G17" s="201"/>
+      <c r="E17" s="188"/>
+      <c r="F17" s="188"/>
+      <c r="G17" s="189"/>
       <c r="H17" s="94"/>
       <c r="I17" s="96"/>
       <c r="J17" s="92" t="s">
@@ -8833,9 +8833,9 @@
       <c r="D18" s="199" t="s">
         <v>219</v>
       </c>
-      <c r="E18" s="200"/>
-      <c r="F18" s="200"/>
-      <c r="G18" s="201"/>
+      <c r="E18" s="188"/>
+      <c r="F18" s="188"/>
+      <c r="G18" s="189"/>
       <c r="H18" s="94"/>
       <c r="I18" s="96"/>
       <c r="J18" s="92" t="s">
@@ -8845,6 +8845,14 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="A11:K11"/>
+    <mergeCell ref="A12:K12"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="K9:K10"/>
     <mergeCell ref="D18:G18"/>
     <mergeCell ref="A9:A10"/>
     <mergeCell ref="B9:B10"/>
@@ -8856,14 +8864,6 @@
     <mergeCell ref="D15:G15"/>
     <mergeCell ref="D16:G16"/>
     <mergeCell ref="D17:G17"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="A11:K11"/>
-    <mergeCell ref="A12:K12"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="K9:K10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8915,52 +8915,52 @@
       <c r="A3" s="106" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="171" t="s">
+      <c r="B3" s="221" t="s">
         <v>62</v>
       </c>
-      <c r="C3" s="171"/>
-      <c r="D3" s="172"/>
+      <c r="C3" s="221"/>
+      <c r="D3" s="222"/>
       <c r="E3" s="71"/>
       <c r="F3" s="71"/>
       <c r="G3" s="71"/>
       <c r="H3" s="71"/>
-      <c r="I3" s="173"/>
-      <c r="J3" s="173"/>
-      <c r="K3" s="173"/>
+      <c r="I3" s="205"/>
+      <c r="J3" s="205"/>
+      <c r="K3" s="205"/>
     </row>
     <row r="4" spans="1:11" ht="14.25">
       <c r="A4" s="74" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="174" t="s">
+      <c r="B4" s="223" t="s">
         <v>221</v>
       </c>
-      <c r="C4" s="175"/>
-      <c r="D4" s="176"/>
+      <c r="C4" s="224"/>
+      <c r="D4" s="225"/>
       <c r="E4" s="71"/>
       <c r="F4" s="71"/>
       <c r="G4" s="71"/>
       <c r="H4" s="71"/>
-      <c r="I4" s="173"/>
-      <c r="J4" s="173"/>
-      <c r="K4" s="173"/>
+      <c r="I4" s="205"/>
+      <c r="J4" s="205"/>
+      <c r="K4" s="205"/>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="107" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="177" t="s">
+      <c r="B5" s="226" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="178"/>
-      <c r="D5" s="179"/>
+      <c r="C5" s="227"/>
+      <c r="D5" s="228"/>
       <c r="E5" s="75"/>
       <c r="F5" s="75"/>
       <c r="G5" s="75"/>
       <c r="H5" s="75"/>
-      <c r="I5" s="180"/>
-      <c r="J5" s="180"/>
-      <c r="K5" s="180"/>
+      <c r="I5" s="229"/>
+      <c r="J5" s="229"/>
+      <c r="K5" s="229"/>
     </row>
     <row r="6" spans="1:11" ht="14.25">
       <c r="A6" s="77" t="s">
@@ -8981,9 +8981,9 @@
       <c r="F6" s="72"/>
       <c r="G6" s="72"/>
       <c r="H6" s="72"/>
-      <c r="I6" s="173"/>
-      <c r="J6" s="173"/>
-      <c r="K6" s="173"/>
+      <c r="I6" s="205"/>
+      <c r="J6" s="205"/>
+      <c r="K6" s="205"/>
     </row>
     <row r="7" spans="1:11" ht="14.25">
       <c r="A7" s="81" t="s">
@@ -9004,15 +9004,15 @@
       <c r="F7" s="85"/>
       <c r="G7" s="85"/>
       <c r="H7" s="85"/>
-      <c r="I7" s="173"/>
-      <c r="J7" s="173"/>
-      <c r="K7" s="173"/>
+      <c r="I7" s="205"/>
+      <c r="J7" s="205"/>
+      <c r="K7" s="205"/>
     </row>
     <row r="8" spans="1:11" ht="14.25">
-      <c r="A8" s="181"/>
-      <c r="B8" s="181"/>
-      <c r="C8" s="181"/>
-      <c r="D8" s="181"/>
+      <c r="A8" s="206"/>
+      <c r="B8" s="206"/>
+      <c r="C8" s="206"/>
+      <c r="D8" s="206"/>
       <c r="E8" s="72"/>
       <c r="F8" s="72"/>
       <c r="G8" s="72"/>
@@ -9022,74 +9022,74 @@
       <c r="K8" s="86"/>
     </row>
     <row r="9" spans="1:11" ht="13.5" customHeight="1">
-      <c r="A9" s="187" t="s">
+      <c r="A9" s="209" t="s">
         <v>71</v>
       </c>
-      <c r="B9" s="189" t="s">
+      <c r="B9" s="211" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="187" t="s">
+      <c r="C9" s="209" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="193" t="s">
+      <c r="D9" s="215" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="194"/>
-      <c r="F9" s="194"/>
-      <c r="G9" s="195"/>
-      <c r="H9" s="191" t="s">
+      <c r="E9" s="216"/>
+      <c r="F9" s="216"/>
+      <c r="G9" s="217"/>
+      <c r="H9" s="213" t="s">
         <v>75</v>
       </c>
-      <c r="I9" s="192" t="s">
+      <c r="I9" s="214" t="s">
         <v>76</v>
       </c>
-      <c r="J9" s="192" t="s">
+      <c r="J9" s="214" t="s">
         <v>77</v>
       </c>
-      <c r="K9" s="192" t="s">
+      <c r="K9" s="214" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="188"/>
-      <c r="B10" s="190"/>
-      <c r="C10" s="188"/>
-      <c r="D10" s="196"/>
-      <c r="E10" s="197"/>
-      <c r="F10" s="197"/>
-      <c r="G10" s="198"/>
-      <c r="H10" s="187"/>
-      <c r="I10" s="187"/>
-      <c r="J10" s="187"/>
-      <c r="K10" s="187"/>
+      <c r="A10" s="210"/>
+      <c r="B10" s="212"/>
+      <c r="C10" s="210"/>
+      <c r="D10" s="218"/>
+      <c r="E10" s="219"/>
+      <c r="F10" s="219"/>
+      <c r="G10" s="220"/>
+      <c r="H10" s="209"/>
+      <c r="I10" s="209"/>
+      <c r="J10" s="209"/>
+      <c r="K10" s="209"/>
     </row>
     <row r="11" spans="1:11" ht="15">
-      <c r="A11" s="182"/>
-      <c r="B11" s="182"/>
-      <c r="C11" s="182"/>
-      <c r="D11" s="182"/>
-      <c r="E11" s="182"/>
-      <c r="F11" s="182"/>
-      <c r="G11" s="182"/>
-      <c r="H11" s="182"/>
-      <c r="I11" s="182"/>
-      <c r="J11" s="182"/>
-      <c r="K11" s="183"/>
+      <c r="A11" s="207"/>
+      <c r="B11" s="207"/>
+      <c r="C11" s="207"/>
+      <c r="D11" s="207"/>
+      <c r="E11" s="207"/>
+      <c r="F11" s="207"/>
+      <c r="G11" s="207"/>
+      <c r="H11" s="207"/>
+      <c r="I11" s="207"/>
+      <c r="J11" s="207"/>
+      <c r="K11" s="208"/>
     </row>
     <row r="12" spans="1:11" ht="16.5" customHeight="1">
-      <c r="A12" s="184" t="s">
+      <c r="A12" s="196" t="s">
         <v>222</v>
       </c>
-      <c r="B12" s="185"/>
-      <c r="C12" s="185"/>
-      <c r="D12" s="185"/>
-      <c r="E12" s="185"/>
-      <c r="F12" s="185"/>
-      <c r="G12" s="185"/>
-      <c r="H12" s="185"/>
-      <c r="I12" s="185"/>
-      <c r="J12" s="185"/>
-      <c r="K12" s="186"/>
+      <c r="B12" s="197"/>
+      <c r="C12" s="197"/>
+      <c r="D12" s="197"/>
+      <c r="E12" s="197"/>
+      <c r="F12" s="197"/>
+      <c r="G12" s="197"/>
+      <c r="H12" s="197"/>
+      <c r="I12" s="197"/>
+      <c r="J12" s="197"/>
+      <c r="K12" s="198"/>
     </row>
     <row r="13" spans="1:11" ht="54" customHeight="1">
       <c r="A13" s="90" t="s">
@@ -9101,11 +9101,11 @@
       <c r="C13" s="92" t="s">
         <v>224</v>
       </c>
-      <c r="D13" s="221" t="s">
+      <c r="D13" s="233" t="s">
         <v>225</v>
       </c>
-      <c r="E13" s="222"/>
-      <c r="F13" s="222"/>
+      <c r="E13" s="234"/>
+      <c r="F13" s="234"/>
       <c r="G13" s="124"/>
       <c r="H13" s="94"/>
       <c r="I13" s="96"/>
@@ -9124,11 +9124,11 @@
       <c r="C14" s="92" t="s">
         <v>227</v>
       </c>
-      <c r="D14" s="207" t="s">
+      <c r="D14" s="187" t="s">
         <v>228</v>
       </c>
-      <c r="E14" s="200"/>
-      <c r="F14" s="200"/>
+      <c r="E14" s="188"/>
+      <c r="F14" s="188"/>
       <c r="G14" s="124"/>
       <c r="H14" s="94"/>
       <c r="I14" s="96"/>
@@ -9147,11 +9147,11 @@
       <c r="C15" s="93" t="s">
         <v>230</v>
       </c>
-      <c r="D15" s="207" t="s">
+      <c r="D15" s="187" t="s">
         <v>231</v>
       </c>
-      <c r="E15" s="200"/>
-      <c r="F15" s="200"/>
+      <c r="E15" s="188"/>
+      <c r="F15" s="188"/>
       <c r="G15" s="95"/>
       <c r="H15" s="95"/>
       <c r="I15" s="125"/>
@@ -9161,11 +9161,11 @@
       <c r="K15" s="92"/>
     </row>
     <row r="16" spans="1:11" ht="18" customHeight="1">
-      <c r="A16" s="184" t="s">
+      <c r="A16" s="196" t="s">
         <v>232</v>
       </c>
-      <c r="B16" s="185"/>
-      <c r="C16" s="185"/>
+      <c r="B16" s="197"/>
+      <c r="C16" s="197"/>
       <c r="D16" s="126"/>
       <c r="E16" s="126"/>
       <c r="F16" s="126"/>
@@ -9185,11 +9185,11 @@
       <c r="C17" s="98" t="s">
         <v>234</v>
       </c>
-      <c r="D17" s="221" t="s">
+      <c r="D17" s="233" t="s">
         <v>235</v>
       </c>
-      <c r="E17" s="222"/>
-      <c r="F17" s="222"/>
+      <c r="E17" s="234"/>
+      <c r="F17" s="234"/>
       <c r="G17" s="124"/>
       <c r="H17" s="94"/>
       <c r="I17" s="93"/>
@@ -9208,11 +9208,11 @@
       <c r="C18" s="93" t="s">
         <v>237</v>
       </c>
-      <c r="D18" s="207" t="s">
+      <c r="D18" s="187" t="s">
         <v>238</v>
       </c>
-      <c r="E18" s="200"/>
-      <c r="F18" s="200"/>
+      <c r="E18" s="188"/>
+      <c r="F18" s="188"/>
       <c r="G18" s="95"/>
       <c r="H18" s="95"/>
       <c r="I18" s="92"/>
@@ -9231,11 +9231,11 @@
       <c r="C19" s="93" t="s">
         <v>240</v>
       </c>
-      <c r="D19" s="207" t="s">
+      <c r="D19" s="187" t="s">
         <v>238</v>
       </c>
-      <c r="E19" s="200"/>
-      <c r="F19" s="200"/>
+      <c r="E19" s="188"/>
+      <c r="F19" s="188"/>
       <c r="G19" s="95"/>
       <c r="H19" s="95"/>
       <c r="I19" s="92"/>
@@ -9245,11 +9245,11 @@
       <c r="K19" s="92"/>
     </row>
     <row r="20" spans="1:11" ht="19.5" customHeight="1">
-      <c r="A20" s="184" t="s">
+      <c r="A20" s="196" t="s">
         <v>241</v>
       </c>
-      <c r="B20" s="185"/>
-      <c r="C20" s="185"/>
+      <c r="B20" s="197"/>
+      <c r="C20" s="197"/>
       <c r="D20" s="126"/>
       <c r="E20" s="126"/>
       <c r="F20" s="126"/>
@@ -9269,11 +9269,11 @@
       <c r="C21" s="98" t="s">
         <v>243</v>
       </c>
-      <c r="D21" s="207" t="s">
+      <c r="D21" s="187" t="s">
         <v>244</v>
       </c>
-      <c r="E21" s="200"/>
-      <c r="F21" s="200"/>
+      <c r="E21" s="188"/>
+      <c r="F21" s="188"/>
       <c r="G21" s="95"/>
       <c r="H21" s="94"/>
       <c r="I21" s="93"/>
@@ -9292,11 +9292,11 @@
       <c r="C22" s="92" t="s">
         <v>246</v>
       </c>
-      <c r="D22" s="207" t="s">
+      <c r="D22" s="187" t="s">
         <v>247</v>
       </c>
-      <c r="E22" s="200"/>
-      <c r="F22" s="200"/>
+      <c r="E22" s="188"/>
+      <c r="F22" s="188"/>
       <c r="G22" s="95"/>
       <c r="H22" s="92"/>
       <c r="I22" s="92"/>
@@ -9315,11 +9315,11 @@
       <c r="C23" s="92" t="s">
         <v>249</v>
       </c>
-      <c r="D23" s="221" t="s">
+      <c r="D23" s="233" t="s">
         <v>247</v>
       </c>
-      <c r="E23" s="222"/>
-      <c r="F23" s="222"/>
+      <c r="E23" s="234"/>
+      <c r="F23" s="234"/>
       <c r="G23" s="124"/>
       <c r="H23" s="98"/>
       <c r="I23" s="98"/>
@@ -9329,14 +9329,14 @@
       <c r="K23" s="98"/>
     </row>
     <row r="24" spans="1:11" ht="18" customHeight="1">
-      <c r="A24" s="184" t="s">
+      <c r="A24" s="196" t="s">
         <v>250</v>
       </c>
-      <c r="B24" s="185"/>
-      <c r="C24" s="185"/>
-      <c r="D24" s="223"/>
-      <c r="E24" s="223"/>
-      <c r="F24" s="223"/>
+      <c r="B24" s="197"/>
+      <c r="C24" s="197"/>
+      <c r="D24" s="235"/>
+      <c r="E24" s="235"/>
+      <c r="F24" s="235"/>
       <c r="G24" s="88"/>
       <c r="H24" s="88"/>
       <c r="I24" s="88"/>
@@ -9353,11 +9353,11 @@
       <c r="C25" s="92" t="s">
         <v>252</v>
       </c>
-      <c r="D25" s="221" t="s">
+      <c r="D25" s="233" t="s">
         <v>253</v>
       </c>
-      <c r="E25" s="222"/>
-      <c r="F25" s="222"/>
+      <c r="E25" s="234"/>
+      <c r="F25" s="234"/>
       <c r="G25" s="124"/>
       <c r="H25" s="98"/>
       <c r="I25" s="98"/>
@@ -9376,11 +9376,11 @@
       <c r="C26" s="92" t="s">
         <v>255</v>
       </c>
-      <c r="D26" s="212" t="s">
+      <c r="D26" s="186" t="s">
         <v>256</v>
       </c>
-      <c r="E26" s="212"/>
-      <c r="F26" s="207"/>
+      <c r="E26" s="186"/>
+      <c r="F26" s="187"/>
       <c r="G26" s="95"/>
       <c r="H26" s="95"/>
       <c r="I26" s="92"/>
@@ -9399,11 +9399,11 @@
       <c r="C27" s="92" t="s">
         <v>258</v>
       </c>
-      <c r="D27" s="212" t="s">
+      <c r="D27" s="186" t="s">
         <v>259</v>
       </c>
-      <c r="E27" s="212"/>
-      <c r="F27" s="207"/>
+      <c r="E27" s="186"/>
+      <c r="F27" s="187"/>
       <c r="G27" s="95"/>
       <c r="H27" s="92"/>
       <c r="I27" s="92"/>
@@ -9439,6 +9439,25 @@
     </row>
   </sheetData>
   <mergeCells count="35">
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A11:K11"/>
+    <mergeCell ref="A12:K12"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="K9:K10"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="D17:F17"/>
     <mergeCell ref="D27:F27"/>
     <mergeCell ref="A9:A10"/>
     <mergeCell ref="B9:B10"/>
@@ -9455,25 +9474,6 @@
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="D21:F21"/>
     <mergeCell ref="D22:F22"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A11:K11"/>
-    <mergeCell ref="A12:K12"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="K9:K10"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="I5:K5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -9532,54 +9532,54 @@
       <c r="A3" s="106" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="171" t="s">
+      <c r="B3" s="221" t="s">
         <v>62</v>
       </c>
-      <c r="C3" s="171"/>
-      <c r="D3" s="172"/>
+      <c r="C3" s="221"/>
+      <c r="D3" s="222"/>
       <c r="E3" s="71"/>
       <c r="F3" s="71"/>
       <c r="G3" s="71"/>
       <c r="H3" s="71"/>
-      <c r="I3" s="173"/>
-      <c r="J3" s="173"/>
-      <c r="K3" s="173"/>
+      <c r="I3" s="205"/>
+      <c r="J3" s="205"/>
+      <c r="K3" s="205"/>
       <c r="L3" s="73"/>
     </row>
     <row r="4" spans="1:12" s="61" customFormat="1" ht="13.15" customHeight="1">
       <c r="A4" s="74" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="174" t="s">
+      <c r="B4" s="223" t="s">
         <v>260</v>
       </c>
-      <c r="C4" s="175"/>
-      <c r="D4" s="176"/>
+      <c r="C4" s="224"/>
+      <c r="D4" s="225"/>
       <c r="E4" s="71"/>
       <c r="F4" s="71"/>
       <c r="G4" s="71"/>
       <c r="H4" s="71"/>
-      <c r="I4" s="173"/>
-      <c r="J4" s="173"/>
-      <c r="K4" s="173"/>
+      <c r="I4" s="205"/>
+      <c r="J4" s="205"/>
+      <c r="K4" s="205"/>
       <c r="L4" s="73"/>
     </row>
     <row r="5" spans="1:12" s="62" customFormat="1" ht="12.75">
       <c r="A5" s="107" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="177" t="s">
+      <c r="B5" s="226" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="178"/>
-      <c r="D5" s="179"/>
+      <c r="C5" s="227"/>
+      <c r="D5" s="228"/>
       <c r="E5" s="75"/>
       <c r="F5" s="75"/>
       <c r="G5" s="75"/>
       <c r="H5" s="75"/>
-      <c r="I5" s="180"/>
-      <c r="J5" s="180"/>
-      <c r="K5" s="180"/>
+      <c r="I5" s="229"/>
+      <c r="J5" s="229"/>
+      <c r="K5" s="229"/>
       <c r="L5" s="76"/>
     </row>
     <row r="6" spans="1:12" s="61" customFormat="1" ht="15" customHeight="1">
@@ -9601,9 +9601,9 @@
       <c r="F6" s="72"/>
       <c r="G6" s="72"/>
       <c r="H6" s="72"/>
-      <c r="I6" s="173"/>
-      <c r="J6" s="173"/>
-      <c r="K6" s="173"/>
+      <c r="I6" s="205"/>
+      <c r="J6" s="205"/>
+      <c r="K6" s="205"/>
       <c r="L6" s="73"/>
     </row>
     <row r="7" spans="1:12" s="61" customFormat="1" ht="15" customHeight="1">
@@ -9625,16 +9625,16 @@
       <c r="F7" s="85"/>
       <c r="G7" s="85"/>
       <c r="H7" s="85"/>
-      <c r="I7" s="173"/>
-      <c r="J7" s="173"/>
-      <c r="K7" s="173"/>
+      <c r="I7" s="205"/>
+      <c r="J7" s="205"/>
+      <c r="K7" s="205"/>
       <c r="L7" s="73"/>
     </row>
     <row r="8" spans="1:12" s="61" customFormat="1" ht="15" customHeight="1">
-      <c r="A8" s="181"/>
-      <c r="B8" s="181"/>
-      <c r="C8" s="181"/>
-      <c r="D8" s="181"/>
+      <c r="A8" s="206"/>
+      <c r="B8" s="206"/>
+      <c r="C8" s="206"/>
+      <c r="D8" s="206"/>
       <c r="E8" s="72"/>
       <c r="F8" s="72"/>
       <c r="G8" s="72"/>
@@ -9645,76 +9645,76 @@
       <c r="L8" s="73"/>
     </row>
     <row r="9" spans="1:12" s="63" customFormat="1" ht="12" customHeight="1">
-      <c r="A9" s="187" t="s">
+      <c r="A9" s="209" t="s">
         <v>71</v>
       </c>
-      <c r="B9" s="189" t="s">
+      <c r="B9" s="211" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="187" t="s">
+      <c r="C9" s="209" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="193" t="s">
+      <c r="D9" s="215" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="194"/>
-      <c r="F9" s="194"/>
-      <c r="G9" s="195"/>
-      <c r="H9" s="191" t="s">
+      <c r="E9" s="216"/>
+      <c r="F9" s="216"/>
+      <c r="G9" s="217"/>
+      <c r="H9" s="213" t="s">
         <v>75</v>
       </c>
-      <c r="I9" s="192" t="s">
+      <c r="I9" s="214" t="s">
         <v>76</v>
       </c>
-      <c r="J9" s="192" t="s">
+      <c r="J9" s="214" t="s">
         <v>77</v>
       </c>
-      <c r="K9" s="192" t="s">
+      <c r="K9" s="214" t="s">
         <v>78</v>
       </c>
       <c r="L9" s="87"/>
     </row>
     <row r="10" spans="1:12" s="61" customFormat="1" ht="12" customHeight="1">
-      <c r="A10" s="188"/>
-      <c r="B10" s="190"/>
-      <c r="C10" s="188"/>
-      <c r="D10" s="196"/>
-      <c r="E10" s="197"/>
-      <c r="F10" s="197"/>
-      <c r="G10" s="198"/>
-      <c r="H10" s="187"/>
-      <c r="I10" s="187"/>
-      <c r="J10" s="187"/>
-      <c r="K10" s="187"/>
+      <c r="A10" s="210"/>
+      <c r="B10" s="212"/>
+      <c r="C10" s="210"/>
+      <c r="D10" s="218"/>
+      <c r="E10" s="219"/>
+      <c r="F10" s="219"/>
+      <c r="G10" s="220"/>
+      <c r="H10" s="209"/>
+      <c r="I10" s="209"/>
+      <c r="J10" s="209"/>
+      <c r="K10" s="209"/>
       <c r="L10" s="73"/>
     </row>
     <row r="11" spans="1:12" s="64" customFormat="1" ht="15">
-      <c r="A11" s="182"/>
-      <c r="B11" s="182"/>
-      <c r="C11" s="182"/>
-      <c r="D11" s="182"/>
-      <c r="E11" s="182"/>
-      <c r="F11" s="182"/>
-      <c r="G11" s="182"/>
-      <c r="H11" s="182"/>
-      <c r="I11" s="182"/>
-      <c r="J11" s="182"/>
-      <c r="K11" s="183"/>
+      <c r="A11" s="207"/>
+      <c r="B11" s="207"/>
+      <c r="C11" s="207"/>
+      <c r="D11" s="207"/>
+      <c r="E11" s="207"/>
+      <c r="F11" s="207"/>
+      <c r="G11" s="207"/>
+      <c r="H11" s="207"/>
+      <c r="I11" s="207"/>
+      <c r="J11" s="207"/>
+      <c r="K11" s="208"/>
     </row>
     <row r="12" spans="1:12" s="65" customFormat="1" ht="24.6" customHeight="1">
-      <c r="A12" s="224" t="s">
+      <c r="A12" s="239" t="s">
         <v>261</v>
       </c>
-      <c r="B12" s="225"/>
-      <c r="C12" s="225"/>
-      <c r="D12" s="225"/>
-      <c r="E12" s="225"/>
-      <c r="F12" s="225"/>
-      <c r="G12" s="225"/>
-      <c r="H12" s="225"/>
-      <c r="I12" s="225"/>
-      <c r="J12" s="225"/>
-      <c r="K12" s="226"/>
+      <c r="B12" s="240"/>
+      <c r="C12" s="240"/>
+      <c r="D12" s="240"/>
+      <c r="E12" s="240"/>
+      <c r="F12" s="240"/>
+      <c r="G12" s="240"/>
+      <c r="H12" s="240"/>
+      <c r="I12" s="240"/>
+      <c r="J12" s="240"/>
+      <c r="K12" s="241"/>
     </row>
     <row r="13" spans="1:12" s="65" customFormat="1" ht="81.599999999999994" customHeight="1" outlineLevel="1">
       <c r="A13" s="108" t="s">
@@ -9726,11 +9726,11 @@
       <c r="C13" s="109" t="s">
         <v>263</v>
       </c>
-      <c r="D13" s="207" t="s">
+      <c r="D13" s="187" t="s">
         <v>264</v>
       </c>
-      <c r="E13" s="200"/>
-      <c r="F13" s="200"/>
+      <c r="E13" s="188"/>
+      <c r="F13" s="188"/>
       <c r="G13" s="95"/>
       <c r="H13" s="94"/>
       <c r="I13" s="96"/>
@@ -9747,11 +9747,11 @@
       <c r="C14" s="111" t="s">
         <v>266</v>
       </c>
-      <c r="D14" s="207" t="s">
+      <c r="D14" s="187" t="s">
         <v>267</v>
       </c>
-      <c r="E14" s="200"/>
-      <c r="F14" s="200"/>
+      <c r="E14" s="188"/>
+      <c r="F14" s="188"/>
       <c r="G14" s="95"/>
       <c r="H14" s="94"/>
       <c r="I14" s="93"/>
@@ -9768,11 +9768,11 @@
       <c r="C15" s="109" t="s">
         <v>269</v>
       </c>
-      <c r="D15" s="207" t="s">
+      <c r="D15" s="187" t="s">
         <v>270</v>
       </c>
-      <c r="E15" s="200"/>
-      <c r="F15" s="200"/>
+      <c r="E15" s="188"/>
+      <c r="F15" s="188"/>
       <c r="G15" s="95"/>
       <c r="H15" s="94"/>
       <c r="I15" s="93"/>
@@ -9789,11 +9789,11 @@
       <c r="C16" s="111" t="s">
         <v>272</v>
       </c>
-      <c r="D16" s="207" t="s">
+      <c r="D16" s="187" t="s">
         <v>273</v>
       </c>
-      <c r="E16" s="200"/>
-      <c r="F16" s="200"/>
+      <c r="E16" s="188"/>
+      <c r="F16" s="188"/>
       <c r="G16" s="95"/>
       <c r="H16" s="94"/>
       <c r="I16" s="93"/>
@@ -9810,11 +9810,11 @@
       <c r="C17" s="109" t="s">
         <v>275</v>
       </c>
-      <c r="D17" s="207" t="s">
+      <c r="D17" s="187" t="s">
         <v>276</v>
       </c>
-      <c r="E17" s="200"/>
-      <c r="F17" s="200"/>
+      <c r="E17" s="188"/>
+      <c r="F17" s="188"/>
       <c r="G17" s="95"/>
       <c r="H17" s="94"/>
       <c r="I17" s="93"/>
@@ -9831,11 +9831,11 @@
       <c r="C18" s="111" t="s">
         <v>278</v>
       </c>
-      <c r="D18" s="207" t="s">
+      <c r="D18" s="187" t="s">
         <v>279</v>
       </c>
-      <c r="E18" s="200"/>
-      <c r="F18" s="200"/>
+      <c r="E18" s="188"/>
+      <c r="F18" s="188"/>
       <c r="G18" s="95"/>
       <c r="H18" s="94"/>
       <c r="I18" s="96"/>
@@ -9852,11 +9852,11 @@
       <c r="C19" s="109" t="s">
         <v>281</v>
       </c>
-      <c r="D19" s="207" t="s">
+      <c r="D19" s="187" t="s">
         <v>282</v>
       </c>
-      <c r="E19" s="200"/>
-      <c r="F19" s="200"/>
+      <c r="E19" s="188"/>
+      <c r="F19" s="188"/>
       <c r="G19" s="95"/>
       <c r="H19" s="94"/>
       <c r="I19" s="93"/>
@@ -9873,11 +9873,11 @@
       <c r="C20" s="111" t="s">
         <v>284</v>
       </c>
-      <c r="D20" s="207" t="s">
+      <c r="D20" s="187" t="s">
         <v>285</v>
       </c>
-      <c r="E20" s="200"/>
-      <c r="F20" s="200"/>
+      <c r="E20" s="188"/>
+      <c r="F20" s="188"/>
       <c r="G20" s="95"/>
       <c r="H20" s="94"/>
       <c r="I20" s="93"/>
@@ -9894,11 +9894,11 @@
       <c r="C21" s="109" t="s">
         <v>287</v>
       </c>
-      <c r="D21" s="207" t="s">
+      <c r="D21" s="187" t="s">
         <v>288</v>
       </c>
-      <c r="E21" s="200"/>
-      <c r="F21" s="200"/>
+      <c r="E21" s="188"/>
+      <c r="F21" s="188"/>
       <c r="G21" s="95"/>
       <c r="H21" s="94"/>
       <c r="I21" s="93"/>
@@ -9915,11 +9915,11 @@
       <c r="C22" s="111" t="s">
         <v>290</v>
       </c>
-      <c r="D22" s="207" t="s">
+      <c r="D22" s="187" t="s">
         <v>291</v>
       </c>
-      <c r="E22" s="200"/>
-      <c r="F22" s="200"/>
+      <c r="E22" s="188"/>
+      <c r="F22" s="188"/>
       <c r="G22" s="95"/>
       <c r="H22" s="94"/>
       <c r="I22" s="93"/>
@@ -9936,11 +9936,11 @@
       <c r="C23" s="109" t="s">
         <v>293</v>
       </c>
-      <c r="D23" s="207" t="s">
+      <c r="D23" s="187" t="s">
         <v>294</v>
       </c>
-      <c r="E23" s="200"/>
-      <c r="F23" s="200"/>
+      <c r="E23" s="188"/>
+      <c r="F23" s="188"/>
       <c r="G23" s="95"/>
       <c r="H23" s="94"/>
       <c r="I23" s="96"/>
@@ -9957,11 +9957,11 @@
       <c r="C24" s="111" t="s">
         <v>296</v>
       </c>
-      <c r="D24" s="207" t="s">
+      <c r="D24" s="187" t="s">
         <v>297</v>
       </c>
-      <c r="E24" s="200"/>
-      <c r="F24" s="200"/>
+      <c r="E24" s="188"/>
+      <c r="F24" s="188"/>
       <c r="G24" s="95"/>
       <c r="H24" s="94"/>
       <c r="I24" s="93"/>
@@ -9978,11 +9978,11 @@
       <c r="C25" s="109" t="s">
         <v>300</v>
       </c>
-      <c r="D25" s="207" t="s">
+      <c r="D25" s="187" t="s">
         <v>301</v>
       </c>
-      <c r="E25" s="200"/>
-      <c r="F25" s="200"/>
+      <c r="E25" s="188"/>
+      <c r="F25" s="188"/>
       <c r="G25" s="95"/>
       <c r="H25" s="94"/>
       <c r="I25" s="93"/>
@@ -9999,11 +9999,11 @@
       <c r="C26" s="111" t="s">
         <v>304</v>
       </c>
-      <c r="D26" s="207" t="s">
+      <c r="D26" s="187" t="s">
         <v>305</v>
       </c>
-      <c r="E26" s="200"/>
-      <c r="F26" s="200"/>
+      <c r="E26" s="188"/>
+      <c r="F26" s="188"/>
       <c r="G26" s="95"/>
       <c r="H26" s="94"/>
       <c r="I26" s="93"/>
@@ -10011,19 +10011,19 @@
       <c r="K26" s="92"/>
     </row>
     <row r="27" spans="1:11" ht="25.15" customHeight="1">
-      <c r="A27" s="227" t="s">
+      <c r="A27" s="238" t="s">
         <v>306</v>
       </c>
-      <c r="B27" s="185"/>
-      <c r="C27" s="185"/>
-      <c r="D27" s="185"/>
-      <c r="E27" s="185"/>
-      <c r="F27" s="185"/>
-      <c r="G27" s="185"/>
-      <c r="H27" s="185"/>
-      <c r="I27" s="185"/>
-      <c r="J27" s="185"/>
-      <c r="K27" s="186"/>
+      <c r="B27" s="197"/>
+      <c r="C27" s="197"/>
+      <c r="D27" s="197"/>
+      <c r="E27" s="197"/>
+      <c r="F27" s="197"/>
+      <c r="G27" s="197"/>
+      <c r="H27" s="197"/>
+      <c r="I27" s="197"/>
+      <c r="J27" s="197"/>
+      <c r="K27" s="198"/>
     </row>
     <row r="28" spans="1:11" ht="70.150000000000006" customHeight="1">
       <c r="A28" s="108" t="s">
@@ -10035,11 +10035,11 @@
       <c r="C28" s="109" t="s">
         <v>309</v>
       </c>
-      <c r="D28" s="207" t="s">
+      <c r="D28" s="187" t="s">
         <v>310</v>
       </c>
-      <c r="E28" s="200"/>
-      <c r="F28" s="200"/>
+      <c r="E28" s="188"/>
+      <c r="F28" s="188"/>
       <c r="G28" s="95"/>
       <c r="H28" s="94"/>
       <c r="I28" s="96"/>
@@ -10056,11 +10056,11 @@
       <c r="C29" s="111" t="s">
         <v>313</v>
       </c>
-      <c r="D29" s="207" t="s">
+      <c r="D29" s="187" t="s">
         <v>314</v>
       </c>
-      <c r="E29" s="200"/>
-      <c r="F29" s="200"/>
+      <c r="E29" s="188"/>
+      <c r="F29" s="188"/>
       <c r="G29" s="95"/>
       <c r="H29" s="94"/>
       <c r="I29" s="93"/>
@@ -10077,11 +10077,11 @@
       <c r="C30" s="109" t="s">
         <v>317</v>
       </c>
-      <c r="D30" s="207" t="s">
+      <c r="D30" s="187" t="s">
         <v>318</v>
       </c>
-      <c r="E30" s="200"/>
-      <c r="F30" s="200"/>
+      <c r="E30" s="188"/>
+      <c r="F30" s="188"/>
       <c r="G30" s="95"/>
       <c r="H30" s="94"/>
       <c r="I30" s="93"/>
@@ -10098,11 +10098,11 @@
       <c r="C31" s="111" t="s">
         <v>321</v>
       </c>
-      <c r="D31" s="207" t="s">
+      <c r="D31" s="187" t="s">
         <v>322</v>
       </c>
-      <c r="E31" s="200"/>
-      <c r="F31" s="200"/>
+      <c r="E31" s="188"/>
+      <c r="F31" s="188"/>
       <c r="G31" s="95"/>
       <c r="H31" s="94"/>
       <c r="I31" s="93"/>
@@ -10119,11 +10119,11 @@
       <c r="C32" s="109" t="s">
         <v>325</v>
       </c>
-      <c r="D32" s="207" t="s">
+      <c r="D32" s="187" t="s">
         <v>326</v>
       </c>
-      <c r="E32" s="200"/>
-      <c r="F32" s="200"/>
+      <c r="E32" s="188"/>
+      <c r="F32" s="188"/>
       <c r="G32" s="95"/>
       <c r="H32" s="94"/>
       <c r="I32" s="93"/>
@@ -10140,11 +10140,11 @@
       <c r="C33" s="111" t="s">
         <v>329</v>
       </c>
-      <c r="D33" s="207" t="s">
+      <c r="D33" s="187" t="s">
         <v>322</v>
       </c>
-      <c r="E33" s="200"/>
-      <c r="F33" s="200"/>
+      <c r="E33" s="188"/>
+      <c r="F33" s="188"/>
       <c r="G33" s="95"/>
       <c r="H33" s="94"/>
       <c r="I33" s="93"/>
@@ -10161,11 +10161,11 @@
       <c r="C34" s="109" t="s">
         <v>332</v>
       </c>
-      <c r="D34" s="207" t="s">
+      <c r="D34" s="187" t="s">
         <v>333</v>
       </c>
-      <c r="E34" s="200"/>
-      <c r="F34" s="200"/>
+      <c r="E34" s="188"/>
+      <c r="F34" s="188"/>
       <c r="G34" s="95"/>
       <c r="H34" s="94"/>
       <c r="I34" s="93"/>
@@ -10182,11 +10182,11 @@
       <c r="C35" s="111" t="s">
         <v>336</v>
       </c>
-      <c r="D35" s="207" t="s">
+      <c r="D35" s="187" t="s">
         <v>337</v>
       </c>
-      <c r="E35" s="200"/>
-      <c r="F35" s="200"/>
+      <c r="E35" s="188"/>
+      <c r="F35" s="188"/>
       <c r="G35" s="95"/>
       <c r="H35" s="94"/>
       <c r="I35" s="93"/>
@@ -10194,19 +10194,19 @@
       <c r="K35" s="92"/>
     </row>
     <row r="36" spans="1:11" ht="28.15" customHeight="1">
-      <c r="A36" s="227" t="s">
+      <c r="A36" s="238" t="s">
         <v>338</v>
       </c>
-      <c r="B36" s="185"/>
-      <c r="C36" s="185"/>
-      <c r="D36" s="185"/>
-      <c r="E36" s="185"/>
-      <c r="F36" s="185"/>
-      <c r="G36" s="185"/>
-      <c r="H36" s="185"/>
-      <c r="I36" s="185"/>
-      <c r="J36" s="185"/>
-      <c r="K36" s="186"/>
+      <c r="B36" s="197"/>
+      <c r="C36" s="197"/>
+      <c r="D36" s="197"/>
+      <c r="E36" s="197"/>
+      <c r="F36" s="197"/>
+      <c r="G36" s="197"/>
+      <c r="H36" s="197"/>
+      <c r="I36" s="197"/>
+      <c r="J36" s="197"/>
+      <c r="K36" s="198"/>
     </row>
     <row r="37" spans="1:11" ht="70.150000000000006" customHeight="1">
       <c r="A37" s="108" t="s">
@@ -10218,11 +10218,11 @@
       <c r="C37" s="109" t="s">
         <v>341</v>
       </c>
-      <c r="D37" s="207" t="s">
+      <c r="D37" s="187" t="s">
         <v>342</v>
       </c>
-      <c r="E37" s="200"/>
-      <c r="F37" s="200"/>
+      <c r="E37" s="188"/>
+      <c r="F37" s="188"/>
       <c r="G37" s="95"/>
       <c r="H37" s="94"/>
       <c r="I37" s="93"/>
@@ -10239,11 +10239,11 @@
       <c r="C38" s="111" t="s">
         <v>345</v>
       </c>
-      <c r="D38" s="207" t="s">
+      <c r="D38" s="187" t="s">
         <v>346</v>
       </c>
-      <c r="E38" s="200"/>
-      <c r="F38" s="200"/>
+      <c r="E38" s="188"/>
+      <c r="F38" s="188"/>
       <c r="G38" s="95"/>
       <c r="H38" s="94"/>
       <c r="I38" s="93"/>
@@ -10251,19 +10251,19 @@
       <c r="K38" s="92"/>
     </row>
     <row r="39" spans="1:11" ht="28.9" customHeight="1">
-      <c r="A39" s="227" t="s">
+      <c r="A39" s="238" t="s">
         <v>347</v>
       </c>
-      <c r="B39" s="185"/>
-      <c r="C39" s="185"/>
-      <c r="D39" s="185"/>
-      <c r="E39" s="185"/>
-      <c r="F39" s="185"/>
-      <c r="G39" s="185"/>
-      <c r="H39" s="185"/>
-      <c r="I39" s="185"/>
-      <c r="J39" s="185"/>
-      <c r="K39" s="186"/>
+      <c r="B39" s="197"/>
+      <c r="C39" s="197"/>
+      <c r="D39" s="197"/>
+      <c r="E39" s="197"/>
+      <c r="F39" s="197"/>
+      <c r="G39" s="197"/>
+      <c r="H39" s="197"/>
+      <c r="I39" s="197"/>
+      <c r="J39" s="197"/>
+      <c r="K39" s="198"/>
     </row>
     <row r="40" spans="1:11" ht="70.150000000000006" customHeight="1">
       <c r="A40" s="108" t="s">
@@ -10275,11 +10275,11 @@
       <c r="C40" s="109" t="s">
         <v>350</v>
       </c>
-      <c r="D40" s="207" t="s">
+      <c r="D40" s="187" t="s">
         <v>351</v>
       </c>
-      <c r="E40" s="200"/>
-      <c r="F40" s="200"/>
+      <c r="E40" s="188"/>
+      <c r="F40" s="188"/>
       <c r="G40" s="95"/>
       <c r="H40" s="94"/>
       <c r="I40" s="93"/>
@@ -10296,11 +10296,11 @@
       <c r="C41" s="111" t="s">
         <v>354</v>
       </c>
-      <c r="D41" s="207" t="s">
+      <c r="D41" s="187" t="s">
         <v>355</v>
       </c>
-      <c r="E41" s="200"/>
-      <c r="F41" s="200"/>
+      <c r="E41" s="188"/>
+      <c r="F41" s="188"/>
       <c r="G41" s="95"/>
       <c r="H41" s="94"/>
       <c r="I41" s="93"/>
@@ -10311,9 +10311,9 @@
       <c r="A42" s="90"/>
       <c r="B42" s="99"/>
       <c r="C42" s="92"/>
-      <c r="D42" s="228"/>
-      <c r="E42" s="229"/>
-      <c r="F42" s="229"/>
+      <c r="D42" s="236"/>
+      <c r="E42" s="237"/>
+      <c r="F42" s="237"/>
       <c r="G42" s="95"/>
       <c r="H42" s="94"/>
       <c r="I42" s="93"/>
@@ -10324,9 +10324,9 @@
       <c r="A43" s="90"/>
       <c r="B43" s="97"/>
       <c r="C43" s="98"/>
-      <c r="D43" s="228"/>
-      <c r="E43" s="200"/>
-      <c r="F43" s="200"/>
+      <c r="D43" s="236"/>
+      <c r="E43" s="188"/>
+      <c r="F43" s="188"/>
       <c r="G43" s="95"/>
       <c r="H43" s="94"/>
       <c r="I43" s="93"/>
@@ -10337,9 +10337,9 @@
       <c r="A44" s="90"/>
       <c r="B44" s="99"/>
       <c r="C44" s="92"/>
-      <c r="D44" s="228"/>
-      <c r="E44" s="229"/>
-      <c r="F44" s="229"/>
+      <c r="D44" s="236"/>
+      <c r="E44" s="237"/>
+      <c r="F44" s="237"/>
       <c r="G44" s="95"/>
       <c r="H44" s="94"/>
       <c r="I44" s="93"/>
@@ -10350,9 +10350,9 @@
       <c r="A45" s="90"/>
       <c r="B45" s="97"/>
       <c r="C45" s="98"/>
-      <c r="D45" s="228"/>
-      <c r="E45" s="200"/>
-      <c r="F45" s="200"/>
+      <c r="D45" s="236"/>
+      <c r="E45" s="188"/>
+      <c r="F45" s="188"/>
       <c r="G45" s="95"/>
       <c r="H45" s="94"/>
       <c r="I45" s="93"/>
@@ -10363,9 +10363,9 @@
       <c r="A46" s="90"/>
       <c r="B46" s="99"/>
       <c r="C46" s="92"/>
-      <c r="D46" s="228"/>
-      <c r="E46" s="229"/>
-      <c r="F46" s="229"/>
+      <c r="D46" s="236"/>
+      <c r="E46" s="237"/>
+      <c r="F46" s="237"/>
       <c r="G46" s="95"/>
       <c r="H46" s="94"/>
       <c r="I46" s="93"/>
@@ -10376,9 +10376,9 @@
       <c r="A47" s="90"/>
       <c r="B47" s="97"/>
       <c r="C47" s="98"/>
-      <c r="D47" s="228"/>
-      <c r="E47" s="200"/>
-      <c r="F47" s="200"/>
+      <c r="D47" s="236"/>
+      <c r="E47" s="188"/>
+      <c r="F47" s="188"/>
       <c r="G47" s="95"/>
       <c r="H47" s="94"/>
       <c r="I47" s="93"/>
@@ -10389,9 +10389,9 @@
       <c r="A48" s="90"/>
       <c r="B48" s="99"/>
       <c r="C48" s="92"/>
-      <c r="D48" s="228"/>
-      <c r="E48" s="229"/>
-      <c r="F48" s="229"/>
+      <c r="D48" s="236"/>
+      <c r="E48" s="237"/>
+      <c r="F48" s="237"/>
       <c r="G48" s="95"/>
       <c r="H48" s="94"/>
       <c r="I48" s="93"/>
@@ -10402,9 +10402,9 @@
       <c r="A49" s="90"/>
       <c r="B49" s="97"/>
       <c r="C49" s="98"/>
-      <c r="D49" s="228"/>
-      <c r="E49" s="200"/>
-      <c r="F49" s="200"/>
+      <c r="D49" s="236"/>
+      <c r="E49" s="188"/>
+      <c r="F49" s="188"/>
       <c r="G49" s="95"/>
       <c r="H49" s="94"/>
       <c r="I49" s="93"/>
@@ -10415,9 +10415,9 @@
       <c r="A50" s="90"/>
       <c r="B50" s="99"/>
       <c r="C50" s="92"/>
-      <c r="D50" s="228"/>
-      <c r="E50" s="229"/>
-      <c r="F50" s="229"/>
+      <c r="D50" s="236"/>
+      <c r="E50" s="237"/>
+      <c r="F50" s="237"/>
       <c r="G50" s="95"/>
       <c r="H50" s="94"/>
       <c r="I50" s="93"/>
@@ -10429,6 +10429,47 @@
     <row r="53" spans="1:11" ht="12" customHeight="1"/>
   </sheetData>
   <mergeCells count="57">
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A11:K11"/>
+    <mergeCell ref="A12:K12"/>
+    <mergeCell ref="H9:H10"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="K9:K10"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="A27:K27"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="A36:K36"/>
+    <mergeCell ref="D37:F37"/>
     <mergeCell ref="D48:F48"/>
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="D50:F50"/>
@@ -10445,47 +10486,6 @@
     <mergeCell ref="A39:K39"/>
     <mergeCell ref="D40:F40"/>
     <mergeCell ref="D41:F41"/>
-    <mergeCell ref="D42:F42"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="A36:K36"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="A27:K27"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A11:K11"/>
-    <mergeCell ref="A12:K12"/>
-    <mergeCell ref="H9:H10"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="K9:K10"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="I5:K5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10543,54 +10543,54 @@
       <c r="A3" s="106" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="171" t="s">
+      <c r="B3" s="221" t="s">
         <v>62</v>
       </c>
-      <c r="C3" s="171"/>
-      <c r="D3" s="172"/>
+      <c r="C3" s="221"/>
+      <c r="D3" s="222"/>
       <c r="E3" s="71"/>
       <c r="F3" s="71"/>
       <c r="G3" s="71"/>
       <c r="H3" s="71"/>
-      <c r="I3" s="173"/>
-      <c r="J3" s="173"/>
-      <c r="K3" s="173"/>
+      <c r="I3" s="205"/>
+      <c r="J3" s="205"/>
+      <c r="K3" s="205"/>
       <c r="L3" s="73"/>
     </row>
     <row r="4" spans="1:12" s="61" customFormat="1" ht="13.15" customHeight="1">
       <c r="A4" s="74" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="174" t="s">
+      <c r="B4" s="223" t="s">
         <v>356</v>
       </c>
-      <c r="C4" s="175"/>
-      <c r="D4" s="176"/>
+      <c r="C4" s="224"/>
+      <c r="D4" s="225"/>
       <c r="E4" s="71"/>
       <c r="F4" s="71"/>
       <c r="G4" s="71"/>
       <c r="H4" s="71"/>
-      <c r="I4" s="173"/>
-      <c r="J4" s="173"/>
-      <c r="K4" s="173"/>
+      <c r="I4" s="205"/>
+      <c r="J4" s="205"/>
+      <c r="K4" s="205"/>
       <c r="L4" s="73"/>
     </row>
     <row r="5" spans="1:12" s="62" customFormat="1" ht="25.5">
       <c r="A5" s="107" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="177" t="s">
+      <c r="B5" s="226" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="178"/>
-      <c r="D5" s="179"/>
+      <c r="C5" s="227"/>
+      <c r="D5" s="228"/>
       <c r="E5" s="75"/>
       <c r="F5" s="75"/>
       <c r="G5" s="75"/>
       <c r="H5" s="75"/>
-      <c r="I5" s="180"/>
-      <c r="J5" s="180"/>
-      <c r="K5" s="180"/>
+      <c r="I5" s="229"/>
+      <c r="J5" s="229"/>
+      <c r="K5" s="229"/>
       <c r="L5" s="76"/>
     </row>
     <row r="6" spans="1:12" s="61" customFormat="1" ht="15" customHeight="1">
@@ -10612,9 +10612,9 @@
       <c r="F6" s="72"/>
       <c r="G6" s="72"/>
       <c r="H6" s="72"/>
-      <c r="I6" s="173"/>
-      <c r="J6" s="173"/>
-      <c r="K6" s="173"/>
+      <c r="I6" s="205"/>
+      <c r="J6" s="205"/>
+      <c r="K6" s="205"/>
       <c r="L6" s="73"/>
     </row>
     <row r="7" spans="1:12" s="61" customFormat="1" ht="15" customHeight="1">
@@ -10636,16 +10636,16 @@
       <c r="F7" s="85"/>
       <c r="G7" s="85"/>
       <c r="H7" s="85"/>
-      <c r="I7" s="173"/>
-      <c r="J7" s="173"/>
-      <c r="K7" s="173"/>
+      <c r="I7" s="205"/>
+      <c r="J7" s="205"/>
+      <c r="K7" s="205"/>
       <c r="L7" s="73"/>
     </row>
     <row r="8" spans="1:12" s="61" customFormat="1" ht="15" customHeight="1">
-      <c r="A8" s="181"/>
-      <c r="B8" s="181"/>
-      <c r="C8" s="181"/>
-      <c r="D8" s="181"/>
+      <c r="A8" s="206"/>
+      <c r="B8" s="206"/>
+      <c r="C8" s="206"/>
+      <c r="D8" s="206"/>
       <c r="E8" s="72"/>
       <c r="F8" s="72"/>
       <c r="G8" s="72"/>
@@ -10656,76 +10656,76 @@
       <c r="L8" s="73"/>
     </row>
     <row r="9" spans="1:12" s="63" customFormat="1" ht="12" customHeight="1">
-      <c r="A9" s="187" t="s">
+      <c r="A9" s="209" t="s">
         <v>71</v>
       </c>
-      <c r="B9" s="189" t="s">
+      <c r="B9" s="211" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="187" t="s">
+      <c r="C9" s="209" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="193" t="s">
+      <c r="D9" s="215" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="194"/>
-      <c r="F9" s="194"/>
-      <c r="G9" s="195"/>
-      <c r="H9" s="191" t="s">
+      <c r="E9" s="216"/>
+      <c r="F9" s="216"/>
+      <c r="G9" s="217"/>
+      <c r="H9" s="213" t="s">
         <v>75</v>
       </c>
-      <c r="I9" s="192" t="s">
+      <c r="I9" s="214" t="s">
         <v>76</v>
       </c>
-      <c r="J9" s="192" t="s">
+      <c r="J9" s="214" t="s">
         <v>77</v>
       </c>
-      <c r="K9" s="192" t="s">
+      <c r="K9" s="214" t="s">
         <v>78</v>
       </c>
       <c r="L9" s="87"/>
     </row>
     <row r="10" spans="1:12" s="61" customFormat="1" ht="12" customHeight="1">
-      <c r="A10" s="188"/>
-      <c r="B10" s="190"/>
-      <c r="C10" s="188"/>
-      <c r="D10" s="196"/>
-      <c r="E10" s="197"/>
-      <c r="F10" s="197"/>
-      <c r="G10" s="198"/>
-      <c r="H10" s="187"/>
-      <c r="I10" s="187"/>
-      <c r="J10" s="187"/>
-      <c r="K10" s="187"/>
+      <c r="A10" s="210"/>
+      <c r="B10" s="212"/>
+      <c r="C10" s="210"/>
+      <c r="D10" s="218"/>
+      <c r="E10" s="219"/>
+      <c r="F10" s="219"/>
+      <c r="G10" s="220"/>
+      <c r="H10" s="209"/>
+      <c r="I10" s="209"/>
+      <c r="J10" s="209"/>
+      <c r="K10" s="209"/>
       <c r="L10" s="73"/>
     </row>
     <row r="11" spans="1:12" s="64" customFormat="1" ht="15">
-      <c r="A11" s="182"/>
-      <c r="B11" s="182"/>
-      <c r="C11" s="182"/>
-      <c r="D11" s="182"/>
-      <c r="E11" s="182"/>
-      <c r="F11" s="182"/>
-      <c r="G11" s="182"/>
-      <c r="H11" s="182"/>
-      <c r="I11" s="182"/>
-      <c r="J11" s="182"/>
-      <c r="K11" s="183"/>
+      <c r="A11" s="207"/>
+      <c r="B11" s="207"/>
+      <c r="C11" s="207"/>
+      <c r="D11" s="207"/>
+      <c r="E11" s="207"/>
+      <c r="F11" s="207"/>
+      <c r="G11" s="207"/>
+      <c r="H11" s="207"/>
+      <c r="I11" s="207"/>
+      <c r="J11" s="207"/>
+      <c r="K11" s="208"/>
     </row>
     <row r="12" spans="1:12" s="65" customFormat="1" ht="22.9" customHeight="1">
-      <c r="A12" s="227" t="s">
+      <c r="A12" s="238" t="s">
         <v>357</v>
       </c>
-      <c r="B12" s="230"/>
-      <c r="C12" s="230"/>
-      <c r="D12" s="230"/>
-      <c r="E12" s="230"/>
-      <c r="F12" s="230"/>
-      <c r="G12" s="230"/>
-      <c r="H12" s="230"/>
-      <c r="I12" s="230"/>
-      <c r="J12" s="230"/>
-      <c r="K12" s="231"/>
+      <c r="B12" s="242"/>
+      <c r="C12" s="242"/>
+      <c r="D12" s="242"/>
+      <c r="E12" s="242"/>
+      <c r="F12" s="242"/>
+      <c r="G12" s="242"/>
+      <c r="H12" s="242"/>
+      <c r="I12" s="242"/>
+      <c r="J12" s="242"/>
+      <c r="K12" s="243"/>
     </row>
     <row r="13" spans="1:12" s="65" customFormat="1" ht="66.599999999999994" customHeight="1" outlineLevel="1">
       <c r="A13" s="108" t="s">
@@ -10737,11 +10737,11 @@
       <c r="C13" s="109" t="s">
         <v>359</v>
       </c>
-      <c r="D13" s="207" t="s">
+      <c r="D13" s="187" t="s">
         <v>360</v>
       </c>
-      <c r="E13" s="200"/>
-      <c r="F13" s="200"/>
+      <c r="E13" s="188"/>
+      <c r="F13" s="188"/>
       <c r="G13" s="95"/>
       <c r="H13" s="94"/>
       <c r="I13" s="96"/>
@@ -10758,11 +10758,11 @@
       <c r="C14" s="111" t="s">
         <v>362</v>
       </c>
-      <c r="D14" s="207" t="s">
+      <c r="D14" s="187" t="s">
         <v>363</v>
       </c>
-      <c r="E14" s="200"/>
-      <c r="F14" s="200"/>
+      <c r="E14" s="188"/>
+      <c r="F14" s="188"/>
       <c r="G14" s="95"/>
       <c r="H14" s="94"/>
       <c r="I14" s="93"/>
@@ -10779,11 +10779,11 @@
       <c r="C15" s="109" t="s">
         <v>365</v>
       </c>
-      <c r="D15" s="207" t="s">
+      <c r="D15" s="187" t="s">
         <v>366</v>
       </c>
-      <c r="E15" s="200"/>
-      <c r="F15" s="200"/>
+      <c r="E15" s="188"/>
+      <c r="F15" s="188"/>
       <c r="G15" s="95"/>
       <c r="H15" s="94"/>
       <c r="I15" s="93"/>
@@ -10791,19 +10791,19 @@
       <c r="K15" s="92"/>
     </row>
     <row r="16" spans="1:12" ht="27" customHeight="1">
-      <c r="A16" s="227" t="s">
+      <c r="A16" s="238" t="s">
         <v>367</v>
       </c>
-      <c r="B16" s="185"/>
-      <c r="C16" s="185"/>
-      <c r="D16" s="185"/>
-      <c r="E16" s="185"/>
-      <c r="F16" s="185"/>
-      <c r="G16" s="185"/>
-      <c r="H16" s="185"/>
-      <c r="I16" s="185"/>
-      <c r="J16" s="185"/>
-      <c r="K16" s="186"/>
+      <c r="B16" s="197"/>
+      <c r="C16" s="197"/>
+      <c r="D16" s="197"/>
+      <c r="E16" s="197"/>
+      <c r="F16" s="197"/>
+      <c r="G16" s="197"/>
+      <c r="H16" s="197"/>
+      <c r="I16" s="197"/>
+      <c r="J16" s="197"/>
+      <c r="K16" s="198"/>
     </row>
     <row r="17" spans="1:11" ht="70.150000000000006" customHeight="1">
       <c r="A17" s="110" t="s">
@@ -10815,11 +10815,11 @@
       <c r="C17" s="111" t="s">
         <v>369</v>
       </c>
-      <c r="D17" s="207" t="s">
+      <c r="D17" s="187" t="s">
         <v>370</v>
       </c>
-      <c r="E17" s="200"/>
-      <c r="F17" s="200"/>
+      <c r="E17" s="188"/>
+      <c r="F17" s="188"/>
       <c r="G17" s="95"/>
       <c r="H17" s="94"/>
       <c r="I17" s="93"/>
@@ -10836,11 +10836,11 @@
       <c r="C18" s="109" t="s">
         <v>372</v>
       </c>
-      <c r="D18" s="207" t="s">
+      <c r="D18" s="187" t="s">
         <v>373</v>
       </c>
-      <c r="E18" s="200"/>
-      <c r="F18" s="200"/>
+      <c r="E18" s="188"/>
+      <c r="F18" s="188"/>
       <c r="G18" s="95"/>
       <c r="H18" s="94"/>
       <c r="I18" s="93"/>
@@ -10857,11 +10857,11 @@
       <c r="C19" s="111" t="s">
         <v>375</v>
       </c>
-      <c r="D19" s="207" t="s">
+      <c r="D19" s="187" t="s">
         <v>376</v>
       </c>
-      <c r="E19" s="200"/>
-      <c r="F19" s="200"/>
+      <c r="E19" s="188"/>
+      <c r="F19" s="188"/>
       <c r="G19" s="95"/>
       <c r="H19" s="94"/>
       <c r="I19" s="93"/>
@@ -10869,19 +10869,19 @@
       <c r="K19" s="92"/>
     </row>
     <row r="20" spans="1:11" ht="28.15" customHeight="1">
-      <c r="A20" s="224" t="s">
+      <c r="A20" s="239" t="s">
         <v>377</v>
       </c>
-      <c r="B20" s="225"/>
-      <c r="C20" s="225"/>
-      <c r="D20" s="225"/>
-      <c r="E20" s="225"/>
-      <c r="F20" s="225"/>
-      <c r="G20" s="225"/>
-      <c r="H20" s="225"/>
-      <c r="I20" s="225"/>
-      <c r="J20" s="225"/>
-      <c r="K20" s="226"/>
+      <c r="B20" s="240"/>
+      <c r="C20" s="240"/>
+      <c r="D20" s="240"/>
+      <c r="E20" s="240"/>
+      <c r="F20" s="240"/>
+      <c r="G20" s="240"/>
+      <c r="H20" s="240"/>
+      <c r="I20" s="240"/>
+      <c r="J20" s="240"/>
+      <c r="K20" s="241"/>
     </row>
     <row r="21" spans="1:11" ht="70.150000000000006" customHeight="1">
       <c r="A21" s="108" t="s">
@@ -10893,11 +10893,11 @@
       <c r="C21" s="109" t="s">
         <v>379</v>
       </c>
-      <c r="D21" s="207" t="s">
+      <c r="D21" s="187" t="s">
         <v>380</v>
       </c>
-      <c r="E21" s="200"/>
-      <c r="F21" s="200"/>
+      <c r="E21" s="188"/>
+      <c r="F21" s="188"/>
       <c r="G21" s="95"/>
       <c r="H21" s="94"/>
       <c r="I21" s="93"/>
@@ -10914,11 +10914,11 @@
       <c r="C22" s="111" t="s">
         <v>382</v>
       </c>
-      <c r="D22" s="207" t="s">
+      <c r="D22" s="187" t="s">
         <v>383</v>
       </c>
-      <c r="E22" s="200"/>
-      <c r="F22" s="200"/>
+      <c r="E22" s="188"/>
+      <c r="F22" s="188"/>
       <c r="G22" s="95"/>
       <c r="H22" s="94"/>
       <c r="I22" s="93"/>
@@ -10935,11 +10935,11 @@
       <c r="C23" s="109" t="s">
         <v>385</v>
       </c>
-      <c r="D23" s="207" t="s">
+      <c r="D23" s="187" t="s">
         <v>386</v>
       </c>
-      <c r="E23" s="200"/>
-      <c r="F23" s="200"/>
+      <c r="E23" s="188"/>
+      <c r="F23" s="188"/>
       <c r="G23" s="95"/>
       <c r="H23" s="94"/>
       <c r="I23" s="93"/>
@@ -10956,11 +10956,11 @@
       <c r="C24" s="111" t="s">
         <v>388</v>
       </c>
-      <c r="D24" s="207" t="s">
+      <c r="D24" s="187" t="s">
         <v>389</v>
       </c>
-      <c r="E24" s="200"/>
-      <c r="F24" s="200"/>
+      <c r="E24" s="188"/>
+      <c r="F24" s="188"/>
       <c r="G24" s="95"/>
       <c r="H24" s="94"/>
       <c r="I24" s="93"/>
@@ -10968,19 +10968,19 @@
       <c r="K24" s="92"/>
     </row>
     <row r="25" spans="1:11" ht="31.15" customHeight="1">
-      <c r="A25" s="224" t="s">
+      <c r="A25" s="239" t="s">
         <v>390</v>
       </c>
-      <c r="B25" s="225"/>
-      <c r="C25" s="225"/>
-      <c r="D25" s="225"/>
-      <c r="E25" s="225"/>
-      <c r="F25" s="225"/>
-      <c r="G25" s="225"/>
-      <c r="H25" s="225"/>
-      <c r="I25" s="225"/>
-      <c r="J25" s="225"/>
-      <c r="K25" s="226"/>
+      <c r="B25" s="240"/>
+      <c r="C25" s="240"/>
+      <c r="D25" s="240"/>
+      <c r="E25" s="240"/>
+      <c r="F25" s="240"/>
+      <c r="G25" s="240"/>
+      <c r="H25" s="240"/>
+      <c r="I25" s="240"/>
+      <c r="J25" s="240"/>
+      <c r="K25" s="241"/>
     </row>
     <row r="26" spans="1:11" ht="70.150000000000006" customHeight="1">
       <c r="A26" s="108" t="s">
@@ -10992,11 +10992,11 @@
       <c r="C26" s="109" t="s">
         <v>392</v>
       </c>
-      <c r="D26" s="207" t="s">
+      <c r="D26" s="187" t="s">
         <v>393</v>
       </c>
-      <c r="E26" s="200"/>
-      <c r="F26" s="200"/>
+      <c r="E26" s="188"/>
+      <c r="F26" s="188"/>
       <c r="G26" s="95"/>
       <c r="H26" s="94"/>
       <c r="I26" s="93"/>
@@ -11013,11 +11013,11 @@
       <c r="C27" s="111" t="s">
         <v>395</v>
       </c>
-      <c r="D27" s="207" t="s">
+      <c r="D27" s="187" t="s">
         <v>396</v>
       </c>
-      <c r="E27" s="200"/>
-      <c r="F27" s="200"/>
+      <c r="E27" s="188"/>
+      <c r="F27" s="188"/>
       <c r="G27" s="95"/>
       <c r="H27" s="94"/>
       <c r="I27" s="93"/>
@@ -11034,11 +11034,11 @@
       <c r="C28" s="109" t="s">
         <v>398</v>
       </c>
-      <c r="D28" s="207" t="s">
+      <c r="D28" s="187" t="s">
         <v>399</v>
       </c>
-      <c r="E28" s="200"/>
-      <c r="F28" s="200"/>
+      <c r="E28" s="188"/>
+      <c r="F28" s="188"/>
       <c r="G28" s="95"/>
       <c r="H28" s="94"/>
       <c r="I28" s="93"/>
@@ -11055,11 +11055,11 @@
       <c r="C29" s="111" t="s">
         <v>401</v>
       </c>
-      <c r="D29" s="207" t="s">
+      <c r="D29" s="187" t="s">
         <v>402</v>
       </c>
-      <c r="E29" s="200"/>
-      <c r="F29" s="200"/>
+      <c r="E29" s="188"/>
+      <c r="F29" s="188"/>
       <c r="G29" s="95"/>
       <c r="H29" s="94"/>
       <c r="I29" s="93"/>
@@ -11070,9 +11070,9 @@
       <c r="A30" s="108"/>
       <c r="B30" s="109"/>
       <c r="C30" s="109"/>
-      <c r="D30" s="207"/>
-      <c r="E30" s="200"/>
-      <c r="F30" s="200"/>
+      <c r="D30" s="187"/>
+      <c r="E30" s="188"/>
+      <c r="F30" s="188"/>
       <c r="G30" s="95"/>
       <c r="H30" s="94"/>
       <c r="I30" s="93"/>
@@ -11083,9 +11083,9 @@
       <c r="A31" s="110"/>
       <c r="B31" s="120"/>
       <c r="C31" s="111"/>
-      <c r="D31" s="207"/>
-      <c r="E31" s="200"/>
-      <c r="F31" s="200"/>
+      <c r="D31" s="187"/>
+      <c r="E31" s="188"/>
+      <c r="F31" s="188"/>
       <c r="G31" s="95"/>
       <c r="H31" s="94"/>
       <c r="I31" s="93"/>
@@ -11096,9 +11096,9 @@
       <c r="A32" s="121"/>
       <c r="B32" s="122"/>
       <c r="C32" s="123"/>
-      <c r="D32" s="228"/>
-      <c r="E32" s="229"/>
-      <c r="F32" s="229"/>
+      <c r="D32" s="236"/>
+      <c r="E32" s="237"/>
+      <c r="F32" s="237"/>
       <c r="G32" s="95"/>
       <c r="H32" s="94"/>
       <c r="I32" s="93"/>
@@ -11109,9 +11109,9 @@
       <c r="A33" s="90"/>
       <c r="B33" s="99"/>
       <c r="C33" s="92"/>
-      <c r="D33" s="228"/>
-      <c r="E33" s="229"/>
-      <c r="F33" s="229"/>
+      <c r="D33" s="236"/>
+      <c r="E33" s="237"/>
+      <c r="F33" s="237"/>
       <c r="G33" s="95"/>
       <c r="H33" s="94"/>
       <c r="I33" s="93"/>
@@ -11122,9 +11122,9 @@
       <c r="A34" s="90"/>
       <c r="B34" s="99"/>
       <c r="C34" s="92"/>
-      <c r="D34" s="228"/>
-      <c r="E34" s="229"/>
-      <c r="F34" s="229"/>
+      <c r="D34" s="236"/>
+      <c r="E34" s="237"/>
+      <c r="F34" s="237"/>
       <c r="G34" s="95"/>
       <c r="H34" s="94"/>
       <c r="I34" s="93"/>
@@ -11135,9 +11135,9 @@
       <c r="A35" s="90"/>
       <c r="B35" s="99"/>
       <c r="C35" s="92"/>
-      <c r="D35" s="228"/>
-      <c r="E35" s="229"/>
-      <c r="F35" s="229"/>
+      <c r="D35" s="236"/>
+      <c r="E35" s="237"/>
+      <c r="F35" s="237"/>
       <c r="G35" s="95"/>
       <c r="H35" s="94"/>
       <c r="I35" s="93"/>
@@ -11148,9 +11148,9 @@
       <c r="A36" s="90"/>
       <c r="B36" s="99"/>
       <c r="C36" s="92"/>
-      <c r="D36" s="228"/>
-      <c r="E36" s="229"/>
-      <c r="F36" s="229"/>
+      <c r="D36" s="236"/>
+      <c r="E36" s="237"/>
+      <c r="F36" s="237"/>
       <c r="G36" s="95"/>
       <c r="H36" s="94"/>
       <c r="I36" s="93"/>
@@ -11161,9 +11161,9 @@
       <c r="A37" s="90"/>
       <c r="B37" s="99"/>
       <c r="C37" s="92"/>
-      <c r="D37" s="228"/>
-      <c r="E37" s="229"/>
-      <c r="F37" s="229"/>
+      <c r="D37" s="236"/>
+      <c r="E37" s="237"/>
+      <c r="F37" s="237"/>
       <c r="G37" s="95"/>
       <c r="H37" s="94"/>
       <c r="I37" s="93"/>
@@ -11174,9 +11174,9 @@
       <c r="A38" s="90"/>
       <c r="B38" s="99"/>
       <c r="C38" s="92"/>
-      <c r="D38" s="228"/>
-      <c r="E38" s="229"/>
-      <c r="F38" s="229"/>
+      <c r="D38" s="236"/>
+      <c r="E38" s="237"/>
+      <c r="F38" s="237"/>
       <c r="G38" s="95"/>
       <c r="H38" s="94"/>
       <c r="I38" s="93"/>
@@ -11187,9 +11187,9 @@
       <c r="A39" s="90"/>
       <c r="B39" s="99"/>
       <c r="C39" s="92"/>
-      <c r="D39" s="228"/>
-      <c r="E39" s="229"/>
-      <c r="F39" s="229"/>
+      <c r="D39" s="236"/>
+      <c r="E39" s="237"/>
+      <c r="F39" s="237"/>
       <c r="G39" s="95"/>
       <c r="H39" s="94"/>
       <c r="I39" s="93"/>
@@ -11200,9 +11200,9 @@
       <c r="A40" s="90"/>
       <c r="B40" s="99"/>
       <c r="C40" s="92"/>
-      <c r="D40" s="228"/>
-      <c r="E40" s="229"/>
-      <c r="F40" s="229"/>
+      <c r="D40" s="236"/>
+      <c r="E40" s="237"/>
+      <c r="F40" s="237"/>
       <c r="G40" s="95"/>
       <c r="H40" s="94"/>
       <c r="I40" s="93"/>
@@ -11213,9 +11213,9 @@
       <c r="A41" s="90"/>
       <c r="B41" s="99"/>
       <c r="C41" s="92"/>
-      <c r="D41" s="228"/>
-      <c r="E41" s="229"/>
-      <c r="F41" s="229"/>
+      <c r="D41" s="236"/>
+      <c r="E41" s="237"/>
+      <c r="F41" s="237"/>
       <c r="G41" s="95"/>
       <c r="H41" s="94"/>
       <c r="I41" s="93"/>
@@ -11226,9 +11226,9 @@
       <c r="A42" s="90"/>
       <c r="B42" s="99"/>
       <c r="C42" s="92"/>
-      <c r="D42" s="228"/>
-      <c r="E42" s="229"/>
-      <c r="F42" s="229"/>
+      <c r="D42" s="236"/>
+      <c r="E42" s="237"/>
+      <c r="F42" s="237"/>
       <c r="G42" s="95"/>
       <c r="H42" s="94"/>
       <c r="I42" s="93"/>
@@ -11239,9 +11239,9 @@
       <c r="A43" s="90"/>
       <c r="B43" s="99"/>
       <c r="C43" s="92"/>
-      <c r="D43" s="228"/>
-      <c r="E43" s="229"/>
-      <c r="F43" s="229"/>
+      <c r="D43" s="236"/>
+      <c r="E43" s="237"/>
+      <c r="F43" s="237"/>
       <c r="G43" s="95"/>
       <c r="H43" s="94"/>
       <c r="I43" s="93"/>
@@ -11252,9 +11252,9 @@
       <c r="A44" s="90"/>
       <c r="B44" s="99"/>
       <c r="C44" s="92"/>
-      <c r="D44" s="228"/>
-      <c r="E44" s="229"/>
-      <c r="F44" s="229"/>
+      <c r="D44" s="236"/>
+      <c r="E44" s="237"/>
+      <c r="F44" s="237"/>
       <c r="G44" s="95"/>
       <c r="H44" s="94"/>
       <c r="I44" s="93"/>
@@ -11265,9 +11265,9 @@
       <c r="A45" s="90"/>
       <c r="B45" s="99"/>
       <c r="C45" s="92"/>
-      <c r="D45" s="228"/>
-      <c r="E45" s="229"/>
-      <c r="F45" s="229"/>
+      <c r="D45" s="236"/>
+      <c r="E45" s="237"/>
+      <c r="F45" s="237"/>
       <c r="G45" s="95"/>
       <c r="H45" s="94"/>
       <c r="I45" s="93"/>
@@ -11278,9 +11278,9 @@
       <c r="A46" s="90"/>
       <c r="B46" s="99"/>
       <c r="C46" s="92"/>
-      <c r="D46" s="228"/>
-      <c r="E46" s="229"/>
-      <c r="F46" s="229"/>
+      <c r="D46" s="236"/>
+      <c r="E46" s="237"/>
+      <c r="F46" s="237"/>
       <c r="G46" s="95"/>
       <c r="H46" s="94"/>
       <c r="I46" s="93"/>
@@ -11291,9 +11291,9 @@
       <c r="A47" s="90"/>
       <c r="B47" s="99"/>
       <c r="C47" s="92"/>
-      <c r="D47" s="228"/>
-      <c r="E47" s="229"/>
-      <c r="F47" s="229"/>
+      <c r="D47" s="236"/>
+      <c r="E47" s="237"/>
+      <c r="F47" s="237"/>
       <c r="G47" s="95"/>
       <c r="H47" s="94"/>
       <c r="I47" s="93"/>
@@ -11304,9 +11304,9 @@
       <c r="A48" s="90"/>
       <c r="B48" s="99"/>
       <c r="C48" s="92"/>
-      <c r="D48" s="228"/>
-      <c r="E48" s="229"/>
-      <c r="F48" s="229"/>
+      <c r="D48" s="236"/>
+      <c r="E48" s="237"/>
+      <c r="F48" s="237"/>
       <c r="G48" s="95"/>
       <c r="H48" s="94"/>
       <c r="I48" s="93"/>
@@ -11319,6 +11319,45 @@
     <row r="52" ht="12" customHeight="1"/>
   </sheetData>
   <mergeCells count="55">
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A11:K11"/>
+    <mergeCell ref="A12:K12"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="K9:K10"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="A16:K16"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="A20:K20"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="A25:K25"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="D37:F37"/>
     <mergeCell ref="D48:F48"/>
     <mergeCell ref="A9:A10"/>
     <mergeCell ref="B9:B10"/>
@@ -11335,45 +11374,6 @@
     <mergeCell ref="D40:F40"/>
     <mergeCell ref="D41:F41"/>
     <mergeCell ref="D42:F42"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="D36:F36"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="A25:K25"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="A20:K20"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="A16:K16"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A11:K11"/>
-    <mergeCell ref="A12:K12"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="K9:K10"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="I5:K5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -11426,52 +11426,52 @@
       <c r="A3" s="70" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="171" t="s">
+      <c r="B3" s="221" t="s">
         <v>62</v>
       </c>
-      <c r="C3" s="171"/>
-      <c r="D3" s="172"/>
+      <c r="C3" s="221"/>
+      <c r="D3" s="222"/>
       <c r="E3" s="71"/>
       <c r="F3" s="71"/>
       <c r="G3" s="71"/>
       <c r="H3" s="71"/>
-      <c r="I3" s="173"/>
-      <c r="J3" s="173"/>
-      <c r="K3" s="173"/>
+      <c r="I3" s="205"/>
+      <c r="J3" s="205"/>
+      <c r="K3" s="205"/>
     </row>
     <row r="4" spans="1:11" ht="13.5" customHeight="1">
       <c r="A4" s="74" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="174" t="s">
+      <c r="B4" s="223" t="s">
         <v>404</v>
       </c>
-      <c r="C4" s="175"/>
-      <c r="D4" s="176"/>
+      <c r="C4" s="224"/>
+      <c r="D4" s="225"/>
       <c r="E4" s="71"/>
       <c r="F4" s="71"/>
       <c r="G4" s="71"/>
       <c r="H4" s="71"/>
-      <c r="I4" s="173"/>
-      <c r="J4" s="173"/>
-      <c r="K4" s="173"/>
+      <c r="I4" s="205"/>
+      <c r="J4" s="205"/>
+      <c r="K4" s="205"/>
     </row>
     <row r="5" spans="1:11" ht="12.75" customHeight="1">
       <c r="A5" s="74" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="177" t="s">
+      <c r="B5" s="226" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="178"/>
-      <c r="D5" s="179"/>
+      <c r="C5" s="227"/>
+      <c r="D5" s="228"/>
       <c r="E5" s="75"/>
       <c r="F5" s="75"/>
       <c r="G5" s="75"/>
       <c r="H5" s="75"/>
-      <c r="I5" s="180"/>
-      <c r="J5" s="180"/>
-      <c r="K5" s="180"/>
+      <c r="I5" s="229"/>
+      <c r="J5" s="229"/>
+      <c r="K5" s="229"/>
     </row>
     <row r="6" spans="1:11" ht="14.25">
       <c r="A6" s="77" t="s">
@@ -11492,9 +11492,9 @@
       <c r="F6" s="72"/>
       <c r="G6" s="72"/>
       <c r="H6" s="72"/>
-      <c r="I6" s="173"/>
-      <c r="J6" s="173"/>
-      <c r="K6" s="173"/>
+      <c r="I6" s="205"/>
+      <c r="J6" s="205"/>
+      <c r="K6" s="205"/>
     </row>
     <row r="7" spans="1:11" ht="14.25">
       <c r="A7" s="81" t="s">
@@ -11515,15 +11515,15 @@
       <c r="F7" s="85"/>
       <c r="G7" s="85"/>
       <c r="H7" s="85"/>
-      <c r="I7" s="173"/>
-      <c r="J7" s="173"/>
-      <c r="K7" s="173"/>
+      <c r="I7" s="205"/>
+      <c r="J7" s="205"/>
+      <c r="K7" s="205"/>
     </row>
     <row r="8" spans="1:11" ht="14.25">
-      <c r="A8" s="181"/>
-      <c r="B8" s="181"/>
-      <c r="C8" s="181"/>
-      <c r="D8" s="181"/>
+      <c r="A8" s="206"/>
+      <c r="B8" s="206"/>
+      <c r="C8" s="206"/>
+      <c r="D8" s="206"/>
       <c r="E8" s="72"/>
       <c r="F8" s="72"/>
       <c r="G8" s="72"/>
@@ -11533,74 +11533,74 @@
       <c r="K8" s="86"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="187" t="s">
+      <c r="A9" s="209" t="s">
         <v>71</v>
       </c>
-      <c r="B9" s="189" t="s">
+      <c r="B9" s="211" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="187" t="s">
+      <c r="C9" s="209" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="193" t="s">
+      <c r="D9" s="215" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="194"/>
-      <c r="F9" s="194"/>
-      <c r="G9" s="195"/>
-      <c r="H9" s="191" t="s">
+      <c r="E9" s="216"/>
+      <c r="F9" s="216"/>
+      <c r="G9" s="217"/>
+      <c r="H9" s="213" t="s">
         <v>75</v>
       </c>
-      <c r="I9" s="192" t="s">
+      <c r="I9" s="214" t="s">
         <v>76</v>
       </c>
-      <c r="J9" s="192" t="s">
+      <c r="J9" s="214" t="s">
         <v>77</v>
       </c>
-      <c r="K9" s="192" t="s">
+      <c r="K9" s="214" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="188"/>
-      <c r="B10" s="190"/>
-      <c r="C10" s="188"/>
-      <c r="D10" s="196"/>
-      <c r="E10" s="197"/>
-      <c r="F10" s="197"/>
-      <c r="G10" s="198"/>
-      <c r="H10" s="187"/>
-      <c r="I10" s="187"/>
-      <c r="J10" s="187"/>
-      <c r="K10" s="187"/>
+      <c r="A10" s="210"/>
+      <c r="B10" s="212"/>
+      <c r="C10" s="210"/>
+      <c r="D10" s="218"/>
+      <c r="E10" s="219"/>
+      <c r="F10" s="219"/>
+      <c r="G10" s="220"/>
+      <c r="H10" s="209"/>
+      <c r="I10" s="209"/>
+      <c r="J10" s="209"/>
+      <c r="K10" s="209"/>
     </row>
     <row r="11" spans="1:11" ht="15">
-      <c r="A11" s="182"/>
-      <c r="B11" s="182"/>
-      <c r="C11" s="182"/>
-      <c r="D11" s="182"/>
-      <c r="E11" s="182"/>
-      <c r="F11" s="182"/>
-      <c r="G11" s="182"/>
-      <c r="H11" s="182"/>
-      <c r="I11" s="182"/>
-      <c r="J11" s="182"/>
-      <c r="K11" s="183"/>
+      <c r="A11" s="207"/>
+      <c r="B11" s="207"/>
+      <c r="C11" s="207"/>
+      <c r="D11" s="207"/>
+      <c r="E11" s="207"/>
+      <c r="F11" s="207"/>
+      <c r="G11" s="207"/>
+      <c r="H11" s="207"/>
+      <c r="I11" s="207"/>
+      <c r="J11" s="207"/>
+      <c r="K11" s="208"/>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="184" t="s">
+      <c r="A12" s="196" t="s">
         <v>405</v>
       </c>
-      <c r="B12" s="185"/>
-      <c r="C12" s="185"/>
-      <c r="D12" s="185"/>
-      <c r="E12" s="185"/>
-      <c r="F12" s="185"/>
-      <c r="G12" s="185"/>
-      <c r="H12" s="185"/>
-      <c r="I12" s="185"/>
-      <c r="J12" s="185"/>
-      <c r="K12" s="186"/>
+      <c r="B12" s="197"/>
+      <c r="C12" s="197"/>
+      <c r="D12" s="197"/>
+      <c r="E12" s="197"/>
+      <c r="F12" s="197"/>
+      <c r="G12" s="197"/>
+      <c r="H12" s="197"/>
+      <c r="I12" s="197"/>
+      <c r="J12" s="197"/>
+      <c r="K12" s="198"/>
     </row>
     <row r="13" spans="1:11" ht="52.5" customHeight="1">
       <c r="A13" s="112" t="s">
@@ -11612,11 +11612,11 @@
       <c r="C13" s="91" t="s">
         <v>407</v>
       </c>
-      <c r="D13" s="232" t="s">
+      <c r="D13" s="244" t="s">
         <v>408</v>
       </c>
-      <c r="E13" s="233"/>
-      <c r="F13" s="233"/>
+      <c r="E13" s="245"/>
+      <c r="F13" s="245"/>
       <c r="G13" s="115"/>
       <c r="H13" s="114"/>
       <c r="I13" s="116"/>
@@ -11635,11 +11635,11 @@
       <c r="C14" s="91" t="s">
         <v>407</v>
       </c>
-      <c r="D14" s="232" t="s">
+      <c r="D14" s="244" t="s">
         <v>410</v>
       </c>
-      <c r="E14" s="233"/>
-      <c r="F14" s="233"/>
+      <c r="E14" s="245"/>
+      <c r="F14" s="245"/>
       <c r="G14" s="115"/>
       <c r="H14" s="114"/>
       <c r="I14" s="116"/>
@@ -11649,11 +11649,11 @@
       <c r="K14" s="91"/>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="234" t="s">
+      <c r="A15" s="246" t="s">
         <v>411</v>
       </c>
-      <c r="B15" s="235"/>
-      <c r="C15" s="235"/>
+      <c r="B15" s="247"/>
+      <c r="C15" s="247"/>
       <c r="D15" s="117"/>
       <c r="E15" s="117"/>
       <c r="F15" s="117"/>
@@ -11673,11 +11673,11 @@
       <c r="C16" s="119" t="s">
         <v>413</v>
       </c>
-      <c r="D16" s="232" t="s">
+      <c r="D16" s="244" t="s">
         <v>414</v>
       </c>
-      <c r="E16" s="233"/>
-      <c r="F16" s="233"/>
+      <c r="E16" s="245"/>
+      <c r="F16" s="245"/>
       <c r="G16" s="115"/>
       <c r="H16" s="114"/>
       <c r="I16" s="113"/>
@@ -11696,11 +11696,11 @@
       <c r="C17" s="119" t="s">
         <v>416</v>
       </c>
-      <c r="D17" s="232" t="s">
+      <c r="D17" s="244" t="s">
         <v>417</v>
       </c>
-      <c r="E17" s="233"/>
-      <c r="F17" s="233"/>
+      <c r="E17" s="245"/>
+      <c r="F17" s="245"/>
       <c r="G17" s="115"/>
       <c r="H17" s="114"/>
       <c r="I17" s="113"/>
@@ -11719,11 +11719,11 @@
       <c r="C18" s="119" t="s">
         <v>419</v>
       </c>
-      <c r="D18" s="232" t="s">
+      <c r="D18" s="244" t="s">
         <v>420</v>
       </c>
-      <c r="E18" s="233"/>
-      <c r="F18" s="233"/>
+      <c r="E18" s="245"/>
+      <c r="F18" s="245"/>
       <c r="G18" s="115"/>
       <c r="H18" s="114"/>
       <c r="I18" s="113"/>
@@ -11742,11 +11742,11 @@
       <c r="C19" s="119" t="s">
         <v>422</v>
       </c>
-      <c r="D19" s="232" t="s">
+      <c r="D19" s="244" t="s">
         <v>423</v>
       </c>
-      <c r="E19" s="233"/>
-      <c r="F19" s="233"/>
+      <c r="E19" s="245"/>
+      <c r="F19" s="245"/>
       <c r="G19" s="115"/>
       <c r="H19" s="114"/>
       <c r="I19" s="113"/>
@@ -11756,11 +11756,11 @@
       <c r="K19" s="91"/>
     </row>
     <row r="20" spans="1:11">
-      <c r="A20" s="234" t="s">
+      <c r="A20" s="246" t="s">
         <v>424</v>
       </c>
-      <c r="B20" s="235"/>
-      <c r="C20" s="235"/>
+      <c r="B20" s="247"/>
+      <c r="C20" s="247"/>
       <c r="D20" s="117"/>
       <c r="E20" s="117"/>
       <c r="F20" s="117"/>
@@ -11780,11 +11780,11 @@
       <c r="C21" s="91" t="s">
         <v>426</v>
       </c>
-      <c r="D21" s="232" t="s">
+      <c r="D21" s="244" t="s">
         <v>427</v>
       </c>
-      <c r="E21" s="236"/>
-      <c r="F21" s="236"/>
+      <c r="E21" s="248"/>
+      <c r="F21" s="248"/>
       <c r="G21" s="115"/>
       <c r="H21" s="114"/>
       <c r="I21" s="113"/>
@@ -11803,11 +11803,11 @@
       <c r="C22" s="91" t="s">
         <v>429</v>
       </c>
-      <c r="D22" s="232" t="s">
+      <c r="D22" s="244" t="s">
         <v>430</v>
       </c>
-      <c r="E22" s="236"/>
-      <c r="F22" s="236"/>
+      <c r="E22" s="248"/>
+      <c r="F22" s="248"/>
       <c r="G22" s="115"/>
       <c r="H22" s="114"/>
       <c r="I22" s="113"/>
@@ -11818,16 +11818,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="I5:K5"/>
     <mergeCell ref="I6:K6"/>
     <mergeCell ref="I7:K7"/>
     <mergeCell ref="A8:D8"/>
@@ -11841,12 +11837,16 @@
     <mergeCell ref="J9:J10"/>
     <mergeCell ref="K9:K10"/>
     <mergeCell ref="D9:G10"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="D22:F22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -11904,54 +11904,54 @@
       <c r="A3" s="106" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="171" t="s">
+      <c r="B3" s="221" t="s">
         <v>62</v>
       </c>
-      <c r="C3" s="171"/>
-      <c r="D3" s="172"/>
+      <c r="C3" s="221"/>
+      <c r="D3" s="222"/>
       <c r="E3" s="71"/>
       <c r="F3" s="71"/>
       <c r="G3" s="71"/>
       <c r="H3" s="71"/>
-      <c r="I3" s="173"/>
-      <c r="J3" s="173"/>
-      <c r="K3" s="173"/>
+      <c r="I3" s="205"/>
+      <c r="J3" s="205"/>
+      <c r="K3" s="205"/>
       <c r="L3" s="73"/>
     </row>
     <row r="4" spans="1:12" s="61" customFormat="1" ht="13.15" customHeight="1">
       <c r="A4" s="74" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="174" t="s">
+      <c r="B4" s="223" t="s">
         <v>431</v>
       </c>
-      <c r="C4" s="175"/>
-      <c r="D4" s="176"/>
+      <c r="C4" s="224"/>
+      <c r="D4" s="225"/>
       <c r="E4" s="71"/>
       <c r="F4" s="71"/>
       <c r="G4" s="71"/>
       <c r="H4" s="71"/>
-      <c r="I4" s="173"/>
-      <c r="J4" s="173"/>
-      <c r="K4" s="173"/>
+      <c r="I4" s="205"/>
+      <c r="J4" s="205"/>
+      <c r="K4" s="205"/>
       <c r="L4" s="73"/>
     </row>
     <row r="5" spans="1:12" s="62" customFormat="1" ht="25.5">
       <c r="A5" s="107" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="177" t="s">
+      <c r="B5" s="226" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="178"/>
-      <c r="D5" s="179"/>
+      <c r="C5" s="227"/>
+      <c r="D5" s="228"/>
       <c r="E5" s="75"/>
       <c r="F5" s="75"/>
       <c r="G5" s="75"/>
       <c r="H5" s="75"/>
-      <c r="I5" s="180"/>
-      <c r="J5" s="180"/>
-      <c r="K5" s="180"/>
+      <c r="I5" s="229"/>
+      <c r="J5" s="229"/>
+      <c r="K5" s="229"/>
       <c r="L5" s="76"/>
     </row>
     <row r="6" spans="1:12" s="61" customFormat="1" ht="15" customHeight="1">
@@ -11973,9 +11973,9 @@
       <c r="F6" s="72"/>
       <c r="G6" s="72"/>
       <c r="H6" s="72"/>
-      <c r="I6" s="173"/>
-      <c r="J6" s="173"/>
-      <c r="K6" s="173"/>
+      <c r="I6" s="205"/>
+      <c r="J6" s="205"/>
+      <c r="K6" s="205"/>
       <c r="L6" s="73"/>
     </row>
     <row r="7" spans="1:12" s="61" customFormat="1" ht="15" customHeight="1">
@@ -11997,16 +11997,16 @@
       <c r="F7" s="85"/>
       <c r="G7" s="85"/>
       <c r="H7" s="85"/>
-      <c r="I7" s="173"/>
-      <c r="J7" s="173"/>
-      <c r="K7" s="173"/>
+      <c r="I7" s="205"/>
+      <c r="J7" s="205"/>
+      <c r="K7" s="205"/>
       <c r="L7" s="73"/>
     </row>
     <row r="8" spans="1:12" s="61" customFormat="1" ht="15" customHeight="1">
-      <c r="A8" s="181"/>
-      <c r="B8" s="181"/>
-      <c r="C8" s="181"/>
-      <c r="D8" s="181"/>
+      <c r="A8" s="206"/>
+      <c r="B8" s="206"/>
+      <c r="C8" s="206"/>
+      <c r="D8" s="206"/>
       <c r="F8" s="72"/>
       <c r="G8" s="72"/>
       <c r="H8" s="72"/>
@@ -12016,76 +12016,76 @@
       <c r="L8" s="73"/>
     </row>
     <row r="9" spans="1:12" s="63" customFormat="1" ht="12" customHeight="1">
-      <c r="A9" s="187" t="s">
+      <c r="A9" s="209" t="s">
         <v>71</v>
       </c>
-      <c r="B9" s="189" t="s">
+      <c r="B9" s="211" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="187" t="s">
+      <c r="C9" s="209" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="193" t="s">
+      <c r="D9" s="215" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="194"/>
-      <c r="F9" s="194"/>
-      <c r="G9" s="195"/>
-      <c r="H9" s="191" t="s">
+      <c r="E9" s="216"/>
+      <c r="F9" s="216"/>
+      <c r="G9" s="217"/>
+      <c r="H9" s="213" t="s">
         <v>75</v>
       </c>
-      <c r="I9" s="192" t="s">
+      <c r="I9" s="214" t="s">
         <v>76</v>
       </c>
-      <c r="J9" s="192" t="s">
+      <c r="J9" s="214" t="s">
         <v>77</v>
       </c>
-      <c r="K9" s="192" t="s">
+      <c r="K9" s="214" t="s">
         <v>78</v>
       </c>
       <c r="L9" s="87"/>
     </row>
     <row r="10" spans="1:12" s="61" customFormat="1" ht="12" customHeight="1">
-      <c r="A10" s="188"/>
-      <c r="B10" s="190"/>
-      <c r="C10" s="188"/>
-      <c r="D10" s="196"/>
-      <c r="E10" s="197"/>
-      <c r="F10" s="197"/>
-      <c r="G10" s="198"/>
-      <c r="H10" s="187"/>
-      <c r="I10" s="187"/>
-      <c r="J10" s="187"/>
-      <c r="K10" s="187"/>
+      <c r="A10" s="210"/>
+      <c r="B10" s="212"/>
+      <c r="C10" s="210"/>
+      <c r="D10" s="218"/>
+      <c r="E10" s="219"/>
+      <c r="F10" s="219"/>
+      <c r="G10" s="220"/>
+      <c r="H10" s="209"/>
+      <c r="I10" s="209"/>
+      <c r="J10" s="209"/>
+      <c r="K10" s="209"/>
       <c r="L10" s="73"/>
     </row>
     <row r="11" spans="1:12" s="64" customFormat="1" ht="15">
-      <c r="A11" s="182"/>
-      <c r="B11" s="182"/>
-      <c r="C11" s="182"/>
-      <c r="D11" s="182"/>
-      <c r="E11" s="182"/>
-      <c r="F11" s="182"/>
-      <c r="G11" s="182"/>
-      <c r="H11" s="182"/>
-      <c r="I11" s="182"/>
-      <c r="J11" s="182"/>
-      <c r="K11" s="183"/>
+      <c r="A11" s="207"/>
+      <c r="B11" s="207"/>
+      <c r="C11" s="207"/>
+      <c r="D11" s="207"/>
+      <c r="E11" s="207"/>
+      <c r="F11" s="207"/>
+      <c r="G11" s="207"/>
+      <c r="H11" s="207"/>
+      <c r="I11" s="207"/>
+      <c r="J11" s="207"/>
+      <c r="K11" s="208"/>
     </row>
     <row r="12" spans="1:12" s="65" customFormat="1" ht="29.45" customHeight="1">
-      <c r="A12" s="237" t="s">
+      <c r="A12" s="249" t="s">
         <v>432</v>
       </c>
-      <c r="B12" s="185"/>
-      <c r="C12" s="185"/>
-      <c r="D12" s="185"/>
-      <c r="E12" s="185"/>
-      <c r="F12" s="185"/>
-      <c r="G12" s="185"/>
-      <c r="H12" s="185"/>
-      <c r="I12" s="185"/>
-      <c r="J12" s="185"/>
-      <c r="K12" s="186"/>
+      <c r="B12" s="197"/>
+      <c r="C12" s="197"/>
+      <c r="D12" s="197"/>
+      <c r="E12" s="197"/>
+      <c r="F12" s="197"/>
+      <c r="G12" s="197"/>
+      <c r="H12" s="197"/>
+      <c r="I12" s="197"/>
+      <c r="J12" s="197"/>
+      <c r="K12" s="198"/>
     </row>
     <row r="13" spans="1:12" s="65" customFormat="1" ht="69" customHeight="1" outlineLevel="1">
       <c r="A13" s="108" t="s">
@@ -12097,11 +12097,11 @@
       <c r="C13" s="109" t="s">
         <v>434</v>
       </c>
-      <c r="D13" s="207" t="s">
+      <c r="D13" s="187" t="s">
         <v>435</v>
       </c>
-      <c r="E13" s="200"/>
-      <c r="F13" s="200"/>
+      <c r="E13" s="188"/>
+      <c r="F13" s="188"/>
       <c r="G13" s="95"/>
       <c r="H13" s="94"/>
       <c r="I13" s="96"/>
@@ -12118,11 +12118,11 @@
       <c r="C14" s="111" t="s">
         <v>437</v>
       </c>
-      <c r="D14" s="207" t="s">
+      <c r="D14" s="187" t="s">
         <v>438</v>
       </c>
-      <c r="E14" s="200"/>
-      <c r="F14" s="200"/>
+      <c r="E14" s="188"/>
+      <c r="F14" s="188"/>
       <c r="G14" s="95"/>
       <c r="H14" s="94"/>
       <c r="I14" s="93"/>
@@ -12139,11 +12139,11 @@
       <c r="C15" s="109" t="s">
         <v>440</v>
       </c>
-      <c r="D15" s="207" t="s">
+      <c r="D15" s="187" t="s">
         <v>441</v>
       </c>
-      <c r="E15" s="200"/>
-      <c r="F15" s="200"/>
+      <c r="E15" s="188"/>
+      <c r="F15" s="188"/>
       <c r="G15" s="95"/>
       <c r="H15" s="94"/>
       <c r="I15" s="93"/>
@@ -12151,19 +12151,19 @@
       <c r="K15" s="92"/>
     </row>
     <row r="16" spans="1:12" ht="32.450000000000003" customHeight="1">
-      <c r="A16" s="237" t="s">
+      <c r="A16" s="249" t="s">
         <v>442</v>
       </c>
-      <c r="B16" s="185"/>
-      <c r="C16" s="185"/>
-      <c r="D16" s="185"/>
-      <c r="E16" s="185"/>
-      <c r="F16" s="185"/>
-      <c r="G16" s="185"/>
-      <c r="H16" s="185"/>
-      <c r="I16" s="185"/>
-      <c r="J16" s="185"/>
-      <c r="K16" s="186"/>
+      <c r="B16" s="197"/>
+      <c r="C16" s="197"/>
+      <c r="D16" s="197"/>
+      <c r="E16" s="197"/>
+      <c r="F16" s="197"/>
+      <c r="G16" s="197"/>
+      <c r="H16" s="197"/>
+      <c r="I16" s="197"/>
+      <c r="J16" s="197"/>
+      <c r="K16" s="198"/>
     </row>
     <row r="17" spans="1:11" ht="70.150000000000006" customHeight="1">
       <c r="A17" s="110" t="s">
@@ -12175,11 +12175,11 @@
       <c r="C17" s="111" t="s">
         <v>444</v>
       </c>
-      <c r="D17" s="207" t="s">
+      <c r="D17" s="187" t="s">
         <v>445</v>
       </c>
-      <c r="E17" s="200"/>
-      <c r="F17" s="200"/>
+      <c r="E17" s="188"/>
+      <c r="F17" s="188"/>
       <c r="G17" s="95"/>
       <c r="H17" s="94"/>
       <c r="I17" s="93"/>
@@ -12196,11 +12196,11 @@
       <c r="C18" s="109" t="s">
         <v>447</v>
       </c>
-      <c r="D18" s="207" t="s">
+      <c r="D18" s="187" t="s">
         <v>448</v>
       </c>
-      <c r="E18" s="200"/>
-      <c r="F18" s="200"/>
+      <c r="E18" s="188"/>
+      <c r="F18" s="188"/>
       <c r="G18" s="95"/>
       <c r="H18" s="94"/>
       <c r="I18" s="93"/>
@@ -12217,11 +12217,11 @@
       <c r="C19" s="111" t="s">
         <v>450</v>
       </c>
-      <c r="D19" s="207" t="s">
+      <c r="D19" s="187" t="s">
         <v>451</v>
       </c>
-      <c r="E19" s="200"/>
-      <c r="F19" s="200"/>
+      <c r="E19" s="188"/>
+      <c r="F19" s="188"/>
       <c r="G19" s="95"/>
       <c r="H19" s="94"/>
       <c r="I19" s="93"/>
@@ -12238,11 +12238,11 @@
       <c r="C20" s="109" t="s">
         <v>453</v>
       </c>
-      <c r="D20" s="207" t="s">
+      <c r="D20" s="187" t="s">
         <v>454</v>
       </c>
-      <c r="E20" s="200"/>
-      <c r="F20" s="200"/>
+      <c r="E20" s="188"/>
+      <c r="F20" s="188"/>
       <c r="G20" s="95"/>
       <c r="H20" s="94"/>
       <c r="I20" s="93"/>
@@ -12259,11 +12259,11 @@
       <c r="C21" s="111" t="s">
         <v>456</v>
       </c>
-      <c r="D21" s="207" t="s">
+      <c r="D21" s="187" t="s">
         <v>457</v>
       </c>
-      <c r="E21" s="200"/>
-      <c r="F21" s="200"/>
+      <c r="E21" s="188"/>
+      <c r="F21" s="188"/>
       <c r="G21" s="95"/>
       <c r="H21" s="94"/>
       <c r="I21" s="93"/>
@@ -12271,19 +12271,19 @@
       <c r="K21" s="92"/>
     </row>
     <row r="22" spans="1:11" ht="31.9" customHeight="1">
-      <c r="A22" s="237" t="s">
+      <c r="A22" s="249" t="s">
         <v>458</v>
       </c>
-      <c r="B22" s="185"/>
-      <c r="C22" s="185"/>
-      <c r="D22" s="185"/>
-      <c r="E22" s="185"/>
-      <c r="F22" s="185"/>
-      <c r="G22" s="185"/>
-      <c r="H22" s="185"/>
-      <c r="I22" s="185"/>
-      <c r="J22" s="185"/>
-      <c r="K22" s="186"/>
+      <c r="B22" s="197"/>
+      <c r="C22" s="197"/>
+      <c r="D22" s="197"/>
+      <c r="E22" s="197"/>
+      <c r="F22" s="197"/>
+      <c r="G22" s="197"/>
+      <c r="H22" s="197"/>
+      <c r="I22" s="197"/>
+      <c r="J22" s="197"/>
+      <c r="K22" s="198"/>
     </row>
     <row r="23" spans="1:11" ht="70.150000000000006" customHeight="1">
       <c r="A23" s="108" t="s">
@@ -12295,11 +12295,11 @@
       <c r="C23" s="109" t="s">
         <v>460</v>
       </c>
-      <c r="D23" s="207" t="s">
+      <c r="D23" s="187" t="s">
         <v>461</v>
       </c>
-      <c r="E23" s="200"/>
-      <c r="F23" s="200"/>
+      <c r="E23" s="188"/>
+      <c r="F23" s="188"/>
       <c r="G23" s="95"/>
       <c r="H23" s="94"/>
       <c r="I23" s="93"/>
@@ -12316,11 +12316,11 @@
       <c r="C24" s="111" t="s">
         <v>463</v>
       </c>
-      <c r="D24" s="207" t="s">
+      <c r="D24" s="187" t="s">
         <v>464</v>
       </c>
-      <c r="E24" s="200"/>
-      <c r="F24" s="200"/>
+      <c r="E24" s="188"/>
+      <c r="F24" s="188"/>
       <c r="G24" s="95"/>
       <c r="H24" s="94"/>
       <c r="I24" s="93"/>
@@ -12337,11 +12337,11 @@
       <c r="C25" s="109" t="s">
         <v>466</v>
       </c>
-      <c r="D25" s="207" t="s">
+      <c r="D25" s="187" t="s">
         <v>467</v>
       </c>
-      <c r="E25" s="200"/>
-      <c r="F25" s="200"/>
+      <c r="E25" s="188"/>
+      <c r="F25" s="188"/>
       <c r="G25" s="95"/>
       <c r="H25" s="94"/>
       <c r="I25" s="93"/>
@@ -12358,11 +12358,11 @@
       <c r="C26" s="111" t="s">
         <v>469</v>
       </c>
-      <c r="D26" s="207" t="s">
+      <c r="D26" s="187" t="s">
         <v>470</v>
       </c>
-      <c r="E26" s="200"/>
-      <c r="F26" s="200"/>
+      <c r="E26" s="188"/>
+      <c r="F26" s="188"/>
       <c r="G26" s="95"/>
       <c r="H26" s="94"/>
       <c r="I26" s="93"/>
@@ -12379,11 +12379,11 @@
       <c r="C27" s="109" t="s">
         <v>472</v>
       </c>
-      <c r="D27" s="207" t="s">
+      <c r="D27" s="187" t="s">
         <v>473</v>
       </c>
-      <c r="E27" s="200"/>
-      <c r="F27" s="200"/>
+      <c r="E27" s="188"/>
+      <c r="F27" s="188"/>
       <c r="G27" s="95"/>
       <c r="H27" s="94"/>
       <c r="I27" s="93"/>
@@ -12400,11 +12400,11 @@
       <c r="C28" s="111" t="s">
         <v>475</v>
       </c>
-      <c r="D28" s="207" t="s">
+      <c r="D28" s="187" t="s">
         <v>476</v>
       </c>
-      <c r="E28" s="200"/>
-      <c r="F28" s="200"/>
+      <c r="E28" s="188"/>
+      <c r="F28" s="188"/>
       <c r="G28" s="95"/>
       <c r="H28" s="94"/>
       <c r="I28" s="93"/>
@@ -12421,11 +12421,11 @@
       <c r="C29" s="109" t="s">
         <v>478</v>
       </c>
-      <c r="D29" s="207" t="s">
+      <c r="D29" s="187" t="s">
         <v>479</v>
       </c>
-      <c r="E29" s="200"/>
-      <c r="F29" s="200"/>
+      <c r="E29" s="188"/>
+      <c r="F29" s="188"/>
       <c r="G29" s="95"/>
       <c r="H29" s="94"/>
       <c r="I29" s="93"/>
@@ -12433,19 +12433,19 @@
       <c r="K29" s="92"/>
     </row>
     <row r="30" spans="1:11" ht="31.9" customHeight="1">
-      <c r="A30" s="237" t="s">
+      <c r="A30" s="249" t="s">
         <v>480</v>
       </c>
-      <c r="B30" s="185"/>
-      <c r="C30" s="185"/>
-      <c r="D30" s="185"/>
-      <c r="E30" s="185"/>
-      <c r="F30" s="185"/>
-      <c r="G30" s="185"/>
-      <c r="H30" s="185"/>
-      <c r="I30" s="185"/>
-      <c r="J30" s="185"/>
-      <c r="K30" s="186"/>
+      <c r="B30" s="197"/>
+      <c r="C30" s="197"/>
+      <c r="D30" s="197"/>
+      <c r="E30" s="197"/>
+      <c r="F30" s="197"/>
+      <c r="G30" s="197"/>
+      <c r="H30" s="197"/>
+      <c r="I30" s="197"/>
+      <c r="J30" s="197"/>
+      <c r="K30" s="198"/>
     </row>
     <row r="31" spans="1:11" ht="70.150000000000006" customHeight="1">
       <c r="A31" s="110" t="s">
@@ -12457,11 +12457,11 @@
       <c r="C31" s="111" t="s">
         <v>482</v>
       </c>
-      <c r="D31" s="207" t="s">
+      <c r="D31" s="187" t="s">
         <v>483</v>
       </c>
-      <c r="E31" s="200"/>
-      <c r="F31" s="200"/>
+      <c r="E31" s="188"/>
+      <c r="F31" s="188"/>
       <c r="G31" s="95"/>
       <c r="H31" s="94"/>
       <c r="I31" s="93"/>
@@ -12478,11 +12478,11 @@
       <c r="C32" s="109" t="s">
         <v>485</v>
       </c>
-      <c r="D32" s="207" t="s">
+      <c r="D32" s="187" t="s">
         <v>486</v>
       </c>
-      <c r="E32" s="200"/>
-      <c r="F32" s="200"/>
+      <c r="E32" s="188"/>
+      <c r="F32" s="188"/>
       <c r="G32" s="95"/>
       <c r="H32" s="94"/>
       <c r="I32" s="93"/>
@@ -12493,9 +12493,9 @@
       <c r="A33" s="90"/>
       <c r="B33" s="99"/>
       <c r="C33" s="92"/>
-      <c r="D33" s="228"/>
-      <c r="E33" s="229"/>
-      <c r="F33" s="229"/>
+      <c r="D33" s="236"/>
+      <c r="E33" s="237"/>
+      <c r="F33" s="237"/>
       <c r="G33" s="95"/>
       <c r="H33" s="94"/>
       <c r="I33" s="93"/>
@@ -12506,9 +12506,9 @@
       <c r="A34" s="90"/>
       <c r="B34" s="99"/>
       <c r="C34" s="92"/>
-      <c r="D34" s="228"/>
-      <c r="E34" s="229"/>
-      <c r="F34" s="229"/>
+      <c r="D34" s="236"/>
+      <c r="E34" s="237"/>
+      <c r="F34" s="237"/>
       <c r="G34" s="95"/>
       <c r="H34" s="94"/>
       <c r="I34" s="93"/>
@@ -12519,9 +12519,9 @@
       <c r="A35" s="90"/>
       <c r="B35" s="99"/>
       <c r="C35" s="92"/>
-      <c r="D35" s="228"/>
-      <c r="E35" s="229"/>
-      <c r="F35" s="229"/>
+      <c r="D35" s="236"/>
+      <c r="E35" s="237"/>
+      <c r="F35" s="237"/>
       <c r="G35" s="95"/>
       <c r="H35" s="94"/>
       <c r="I35" s="93"/>
@@ -12532,9 +12532,9 @@
       <c r="A36" s="90"/>
       <c r="B36" s="99"/>
       <c r="C36" s="92"/>
-      <c r="D36" s="228"/>
-      <c r="E36" s="229"/>
-      <c r="F36" s="229"/>
+      <c r="D36" s="236"/>
+      <c r="E36" s="237"/>
+      <c r="F36" s="237"/>
       <c r="G36" s="95"/>
       <c r="H36" s="94"/>
       <c r="I36" s="93"/>
@@ -12545,9 +12545,9 @@
       <c r="A37" s="90"/>
       <c r="B37" s="99"/>
       <c r="C37" s="92"/>
-      <c r="D37" s="228"/>
-      <c r="E37" s="229"/>
-      <c r="F37" s="229"/>
+      <c r="D37" s="236"/>
+      <c r="E37" s="237"/>
+      <c r="F37" s="237"/>
       <c r="G37" s="95"/>
       <c r="H37" s="94"/>
       <c r="I37" s="93"/>
@@ -12558,9 +12558,9 @@
       <c r="A38" s="90"/>
       <c r="B38" s="99"/>
       <c r="C38" s="92"/>
-      <c r="D38" s="228"/>
-      <c r="E38" s="229"/>
-      <c r="F38" s="229"/>
+      <c r="D38" s="236"/>
+      <c r="E38" s="237"/>
+      <c r="F38" s="237"/>
       <c r="G38" s="95"/>
       <c r="H38" s="94"/>
       <c r="I38" s="93"/>
@@ -12571,9 +12571,9 @@
       <c r="A39" s="90"/>
       <c r="B39" s="99"/>
       <c r="C39" s="92"/>
-      <c r="D39" s="228"/>
-      <c r="E39" s="229"/>
-      <c r="F39" s="229"/>
+      <c r="D39" s="236"/>
+      <c r="E39" s="237"/>
+      <c r="F39" s="237"/>
       <c r="G39" s="95"/>
       <c r="H39" s="94"/>
       <c r="I39" s="93"/>
@@ -12584,9 +12584,9 @@
       <c r="A40" s="90"/>
       <c r="B40" s="99"/>
       <c r="C40" s="92"/>
-      <c r="D40" s="228"/>
-      <c r="E40" s="229"/>
-      <c r="F40" s="229"/>
+      <c r="D40" s="236"/>
+      <c r="E40" s="237"/>
+      <c r="F40" s="237"/>
       <c r="G40" s="95"/>
       <c r="H40" s="94"/>
       <c r="I40" s="93"/>
@@ -12597,9 +12597,9 @@
       <c r="A41" s="90"/>
       <c r="B41" s="99"/>
       <c r="C41" s="92"/>
-      <c r="D41" s="228"/>
-      <c r="E41" s="229"/>
-      <c r="F41" s="229"/>
+      <c r="D41" s="236"/>
+      <c r="E41" s="237"/>
+      <c r="F41" s="237"/>
       <c r="G41" s="95"/>
       <c r="H41" s="94"/>
       <c r="I41" s="93"/>
@@ -12610,9 +12610,9 @@
       <c r="A42" s="90"/>
       <c r="B42" s="99"/>
       <c r="C42" s="92"/>
-      <c r="D42" s="228"/>
-      <c r="E42" s="229"/>
-      <c r="F42" s="229"/>
+      <c r="D42" s="236"/>
+      <c r="E42" s="237"/>
+      <c r="F42" s="237"/>
       <c r="G42" s="95"/>
       <c r="H42" s="94"/>
       <c r="I42" s="93"/>
@@ -12623,9 +12623,9 @@
       <c r="A43" s="90"/>
       <c r="B43" s="99"/>
       <c r="C43" s="92"/>
-      <c r="D43" s="228"/>
-      <c r="E43" s="229"/>
-      <c r="F43" s="229"/>
+      <c r="D43" s="236"/>
+      <c r="E43" s="237"/>
+      <c r="F43" s="237"/>
       <c r="G43" s="95"/>
       <c r="H43" s="94"/>
       <c r="I43" s="93"/>
@@ -12636,9 +12636,9 @@
       <c r="A44" s="90"/>
       <c r="B44" s="99"/>
       <c r="C44" s="92"/>
-      <c r="D44" s="228"/>
-      <c r="E44" s="229"/>
-      <c r="F44" s="229"/>
+      <c r="D44" s="236"/>
+      <c r="E44" s="237"/>
+      <c r="F44" s="237"/>
       <c r="G44" s="95"/>
       <c r="H44" s="94"/>
       <c r="I44" s="93"/>
@@ -12649,9 +12649,9 @@
       <c r="A45" s="90"/>
       <c r="B45" s="99"/>
       <c r="C45" s="92"/>
-      <c r="D45" s="228"/>
-      <c r="E45" s="229"/>
-      <c r="F45" s="229"/>
+      <c r="D45" s="236"/>
+      <c r="E45" s="237"/>
+      <c r="F45" s="237"/>
       <c r="G45" s="95"/>
       <c r="H45" s="94"/>
       <c r="I45" s="93"/>
@@ -12662,9 +12662,9 @@
       <c r="A46" s="90"/>
       <c r="B46" s="99"/>
       <c r="C46" s="92"/>
-      <c r="D46" s="228"/>
-      <c r="E46" s="229"/>
-      <c r="F46" s="229"/>
+      <c r="D46" s="236"/>
+      <c r="E46" s="237"/>
+      <c r="F46" s="237"/>
       <c r="G46" s="95"/>
       <c r="H46" s="94"/>
       <c r="I46" s="93"/>
@@ -12675,9 +12675,9 @@
       <c r="A47" s="90"/>
       <c r="B47" s="99"/>
       <c r="C47" s="92"/>
-      <c r="D47" s="228"/>
-      <c r="E47" s="229"/>
-      <c r="F47" s="229"/>
+      <c r="D47" s="236"/>
+      <c r="E47" s="237"/>
+      <c r="F47" s="237"/>
       <c r="G47" s="95"/>
       <c r="H47" s="94"/>
       <c r="I47" s="93"/>
@@ -12688,9 +12688,9 @@
       <c r="A48" s="90"/>
       <c r="B48" s="99"/>
       <c r="C48" s="92"/>
-      <c r="D48" s="228"/>
-      <c r="E48" s="229"/>
-      <c r="F48" s="229"/>
+      <c r="D48" s="236"/>
+      <c r="E48" s="237"/>
+      <c r="F48" s="237"/>
       <c r="G48" s="95"/>
       <c r="H48" s="94"/>
       <c r="I48" s="93"/>
@@ -12701,9 +12701,9 @@
       <c r="A49" s="90"/>
       <c r="B49" s="99"/>
       <c r="C49" s="92"/>
-      <c r="D49" s="228"/>
-      <c r="E49" s="229"/>
-      <c r="F49" s="229"/>
+      <c r="D49" s="236"/>
+      <c r="E49" s="237"/>
+      <c r="F49" s="237"/>
       <c r="G49" s="95"/>
       <c r="H49" s="94"/>
       <c r="I49" s="93"/>
@@ -12714,9 +12714,9 @@
       <c r="A50" s="90"/>
       <c r="B50" s="99"/>
       <c r="C50" s="92"/>
-      <c r="D50" s="228"/>
-      <c r="E50" s="229"/>
-      <c r="F50" s="229"/>
+      <c r="D50" s="236"/>
+      <c r="E50" s="237"/>
+      <c r="F50" s="237"/>
       <c r="G50" s="95"/>
       <c r="H50" s="94"/>
       <c r="I50" s="93"/>
@@ -12727,9 +12727,9 @@
       <c r="A51" s="90"/>
       <c r="B51" s="99"/>
       <c r="C51" s="92"/>
-      <c r="D51" s="228"/>
-      <c r="E51" s="229"/>
-      <c r="F51" s="229"/>
+      <c r="D51" s="236"/>
+      <c r="E51" s="237"/>
+      <c r="F51" s="237"/>
       <c r="G51" s="95"/>
       <c r="H51" s="94"/>
       <c r="I51" s="93"/>
@@ -12740,9 +12740,9 @@
       <c r="A52" s="90"/>
       <c r="B52" s="99"/>
       <c r="C52" s="92"/>
-      <c r="D52" s="228"/>
-      <c r="E52" s="229"/>
-      <c r="F52" s="229"/>
+      <c r="D52" s="236"/>
+      <c r="E52" s="237"/>
+      <c r="F52" s="237"/>
       <c r="G52" s="95"/>
       <c r="H52" s="94"/>
       <c r="I52" s="93"/>
@@ -12753,9 +12753,9 @@
       <c r="A53" s="90"/>
       <c r="B53" s="99"/>
       <c r="C53" s="92"/>
-      <c r="D53" s="228"/>
-      <c r="E53" s="229"/>
-      <c r="F53" s="229"/>
+      <c r="D53" s="236"/>
+      <c r="E53" s="237"/>
+      <c r="F53" s="237"/>
       <c r="G53" s="95"/>
       <c r="H53" s="94"/>
       <c r="I53" s="93"/>
@@ -12766,9 +12766,9 @@
       <c r="A54" s="90"/>
       <c r="B54" s="99"/>
       <c r="C54" s="92"/>
-      <c r="D54" s="228"/>
-      <c r="E54" s="229"/>
-      <c r="F54" s="229"/>
+      <c r="D54" s="236"/>
+      <c r="E54" s="237"/>
+      <c r="F54" s="237"/>
       <c r="G54" s="95"/>
       <c r="H54" s="94"/>
       <c r="I54" s="93"/>
@@ -12779,9 +12779,9 @@
       <c r="A55" s="90"/>
       <c r="B55" s="99"/>
       <c r="C55" s="92"/>
-      <c r="D55" s="228"/>
-      <c r="E55" s="229"/>
-      <c r="F55" s="229"/>
+      <c r="D55" s="236"/>
+      <c r="E55" s="237"/>
+      <c r="F55" s="237"/>
       <c r="G55" s="95"/>
       <c r="H55" s="94"/>
       <c r="I55" s="93"/>
@@ -12792,9 +12792,9 @@
       <c r="A56" s="90"/>
       <c r="B56" s="99"/>
       <c r="C56" s="92"/>
-      <c r="D56" s="228"/>
-      <c r="E56" s="229"/>
-      <c r="F56" s="229"/>
+      <c r="D56" s="236"/>
+      <c r="E56" s="237"/>
+      <c r="F56" s="237"/>
       <c r="G56" s="95"/>
       <c r="H56" s="94"/>
       <c r="I56" s="93"/>
@@ -12805,9 +12805,9 @@
       <c r="A57" s="90"/>
       <c r="B57" s="99"/>
       <c r="C57" s="92"/>
-      <c r="D57" s="228"/>
-      <c r="E57" s="229"/>
-      <c r="F57" s="229"/>
+      <c r="D57" s="236"/>
+      <c r="E57" s="237"/>
+      <c r="F57" s="237"/>
       <c r="G57" s="95"/>
       <c r="H57" s="94"/>
       <c r="I57" s="93"/>
@@ -12818,9 +12818,9 @@
       <c r="A58" s="90"/>
       <c r="B58" s="99"/>
       <c r="C58" s="92"/>
-      <c r="D58" s="228"/>
-      <c r="E58" s="229"/>
-      <c r="F58" s="229"/>
+      <c r="D58" s="236"/>
+      <c r="E58" s="237"/>
+      <c r="F58" s="237"/>
       <c r="G58" s="95"/>
       <c r="H58" s="94"/>
       <c r="I58" s="93"/>
@@ -12831,9 +12831,9 @@
       <c r="A59" s="90"/>
       <c r="B59" s="99"/>
       <c r="C59" s="92"/>
-      <c r="D59" s="228"/>
-      <c r="E59" s="229"/>
-      <c r="F59" s="229"/>
+      <c r="D59" s="236"/>
+      <c r="E59" s="237"/>
+      <c r="F59" s="237"/>
       <c r="G59" s="95"/>
       <c r="H59" s="94"/>
       <c r="I59" s="93"/>
@@ -12844,9 +12844,9 @@
       <c r="A60" s="90"/>
       <c r="B60" s="99"/>
       <c r="C60" s="92"/>
-      <c r="D60" s="228"/>
-      <c r="E60" s="229"/>
-      <c r="F60" s="229"/>
+      <c r="D60" s="236"/>
+      <c r="E60" s="237"/>
+      <c r="F60" s="237"/>
       <c r="G60" s="95"/>
       <c r="H60" s="94"/>
       <c r="I60" s="93"/>
@@ -12857,9 +12857,9 @@
       <c r="A61" s="90"/>
       <c r="B61" s="99"/>
       <c r="C61" s="92"/>
-      <c r="D61" s="228"/>
-      <c r="E61" s="229"/>
-      <c r="F61" s="229"/>
+      <c r="D61" s="236"/>
+      <c r="E61" s="237"/>
+      <c r="F61" s="237"/>
       <c r="G61" s="95"/>
       <c r="H61" s="94"/>
       <c r="I61" s="93"/>
@@ -12870,9 +12870,9 @@
       <c r="A62" s="90"/>
       <c r="B62" s="99"/>
       <c r="C62" s="92"/>
-      <c r="D62" s="228"/>
-      <c r="E62" s="229"/>
-      <c r="F62" s="229"/>
+      <c r="D62" s="236"/>
+      <c r="E62" s="237"/>
+      <c r="F62" s="237"/>
       <c r="G62" s="95"/>
       <c r="H62" s="94"/>
       <c r="I62" s="93"/>
@@ -12883,9 +12883,9 @@
       <c r="A63" s="90"/>
       <c r="B63" s="99"/>
       <c r="C63" s="92"/>
-      <c r="D63" s="228"/>
-      <c r="E63" s="229"/>
-      <c r="F63" s="229"/>
+      <c r="D63" s="236"/>
+      <c r="E63" s="237"/>
+      <c r="F63" s="237"/>
       <c r="G63" s="95"/>
       <c r="H63" s="94"/>
       <c r="I63" s="93"/>
@@ -12896,9 +12896,9 @@
       <c r="A64" s="90"/>
       <c r="B64" s="99"/>
       <c r="C64" s="92"/>
-      <c r="D64" s="228"/>
-      <c r="E64" s="229"/>
-      <c r="F64" s="229"/>
+      <c r="D64" s="236"/>
+      <c r="E64" s="237"/>
+      <c r="F64" s="237"/>
       <c r="G64" s="95"/>
       <c r="H64" s="94"/>
       <c r="I64" s="93"/>
@@ -12909,9 +12909,9 @@
       <c r="A65" s="90"/>
       <c r="B65" s="99"/>
       <c r="C65" s="92"/>
-      <c r="D65" s="228"/>
-      <c r="E65" s="229"/>
-      <c r="F65" s="229"/>
+      <c r="D65" s="236"/>
+      <c r="E65" s="237"/>
+      <c r="F65" s="237"/>
       <c r="G65" s="95"/>
       <c r="H65" s="94"/>
       <c r="I65" s="93"/>
@@ -12922,9 +12922,9 @@
       <c r="A66" s="90"/>
       <c r="B66" s="99"/>
       <c r="C66" s="92"/>
-      <c r="D66" s="228"/>
-      <c r="E66" s="229"/>
-      <c r="F66" s="229"/>
+      <c r="D66" s="236"/>
+      <c r="E66" s="237"/>
+      <c r="F66" s="237"/>
       <c r="G66" s="95"/>
       <c r="H66" s="94"/>
       <c r="I66" s="93"/>
@@ -12935,9 +12935,9 @@
       <c r="A67" s="90"/>
       <c r="B67" s="99"/>
       <c r="C67" s="92"/>
-      <c r="D67" s="228"/>
-      <c r="E67" s="229"/>
-      <c r="F67" s="229"/>
+      <c r="D67" s="236"/>
+      <c r="E67" s="237"/>
+      <c r="F67" s="237"/>
       <c r="G67" s="95"/>
       <c r="H67" s="94"/>
       <c r="I67" s="93"/>
@@ -12948,9 +12948,9 @@
       <c r="A68" s="90"/>
       <c r="B68" s="99"/>
       <c r="C68" s="92"/>
-      <c r="D68" s="228"/>
-      <c r="E68" s="229"/>
-      <c r="F68" s="229"/>
+      <c r="D68" s="236"/>
+      <c r="E68" s="237"/>
+      <c r="F68" s="237"/>
       <c r="G68" s="95"/>
       <c r="H68" s="94"/>
       <c r="I68" s="93"/>
@@ -12961,9 +12961,9 @@
       <c r="A69" s="90"/>
       <c r="B69" s="99"/>
       <c r="C69" s="92"/>
-      <c r="D69" s="228"/>
-      <c r="E69" s="229"/>
-      <c r="F69" s="229"/>
+      <c r="D69" s="236"/>
+      <c r="E69" s="237"/>
+      <c r="F69" s="237"/>
       <c r="G69" s="95"/>
       <c r="H69" s="94"/>
       <c r="I69" s="93"/>
@@ -12974,9 +12974,9 @@
       <c r="A70" s="90"/>
       <c r="B70" s="99"/>
       <c r="C70" s="92"/>
-      <c r="D70" s="228"/>
-      <c r="E70" s="229"/>
-      <c r="F70" s="229"/>
+      <c r="D70" s="236"/>
+      <c r="E70" s="237"/>
+      <c r="F70" s="237"/>
       <c r="G70" s="95"/>
       <c r="H70" s="94"/>
       <c r="I70" s="93"/>
@@ -12987,9 +12987,9 @@
       <c r="A71" s="90"/>
       <c r="B71" s="99"/>
       <c r="C71" s="92"/>
-      <c r="D71" s="228"/>
-      <c r="E71" s="229"/>
-      <c r="F71" s="229"/>
+      <c r="D71" s="236"/>
+      <c r="E71" s="237"/>
+      <c r="F71" s="237"/>
       <c r="G71" s="95"/>
       <c r="H71" s="94"/>
       <c r="I71" s="93"/>
@@ -13000,9 +13000,9 @@
       <c r="A72" s="90"/>
       <c r="B72" s="99"/>
       <c r="C72" s="92"/>
-      <c r="D72" s="228"/>
-      <c r="E72" s="229"/>
-      <c r="F72" s="229"/>
+      <c r="D72" s="236"/>
+      <c r="E72" s="237"/>
+      <c r="F72" s="237"/>
       <c r="G72" s="95"/>
       <c r="H72" s="94"/>
       <c r="I72" s="93"/>
@@ -13013,9 +13013,9 @@
       <c r="A73" s="90"/>
       <c r="B73" s="99"/>
       <c r="C73" s="92"/>
-      <c r="D73" s="228"/>
-      <c r="E73" s="229"/>
-      <c r="F73" s="229"/>
+      <c r="D73" s="236"/>
+      <c r="E73" s="237"/>
+      <c r="F73" s="237"/>
       <c r="G73" s="95"/>
       <c r="H73" s="94"/>
       <c r="I73" s="93"/>
@@ -13026,9 +13026,9 @@
       <c r="A74" s="90"/>
       <c r="B74" s="99"/>
       <c r="C74" s="92"/>
-      <c r="D74" s="228"/>
-      <c r="E74" s="229"/>
-      <c r="F74" s="229"/>
+      <c r="D74" s="236"/>
+      <c r="E74" s="237"/>
+      <c r="F74" s="237"/>
       <c r="G74" s="95"/>
       <c r="H74" s="94"/>
       <c r="I74" s="93"/>
@@ -13039,9 +13039,9 @@
       <c r="A75" s="90"/>
       <c r="B75" s="99"/>
       <c r="C75" s="92"/>
-      <c r="D75" s="228"/>
-      <c r="E75" s="229"/>
-      <c r="F75" s="229"/>
+      <c r="D75" s="236"/>
+      <c r="E75" s="237"/>
+      <c r="F75" s="237"/>
       <c r="G75" s="95"/>
       <c r="H75" s="94"/>
       <c r="I75" s="93"/>
@@ -13052,9 +13052,9 @@
       <c r="A76" s="90"/>
       <c r="B76" s="99"/>
       <c r="C76" s="92"/>
-      <c r="D76" s="228"/>
-      <c r="E76" s="229"/>
-      <c r="F76" s="229"/>
+      <c r="D76" s="236"/>
+      <c r="E76" s="237"/>
+      <c r="F76" s="237"/>
       <c r="G76" s="95"/>
       <c r="H76" s="94"/>
       <c r="I76" s="93"/>
@@ -13065,9 +13065,9 @@
       <c r="A77" s="90"/>
       <c r="B77" s="99"/>
       <c r="C77" s="92"/>
-      <c r="D77" s="228"/>
-      <c r="E77" s="229"/>
-      <c r="F77" s="229"/>
+      <c r="D77" s="236"/>
+      <c r="E77" s="237"/>
+      <c r="F77" s="237"/>
       <c r="G77" s="95"/>
       <c r="H77" s="94"/>
       <c r="I77" s="93"/>
@@ -13078,9 +13078,9 @@
       <c r="A78" s="90"/>
       <c r="B78" s="99"/>
       <c r="C78" s="92"/>
-      <c r="D78" s="228"/>
-      <c r="E78" s="229"/>
-      <c r="F78" s="229"/>
+      <c r="D78" s="236"/>
+      <c r="E78" s="237"/>
+      <c r="F78" s="237"/>
       <c r="G78" s="95"/>
       <c r="H78" s="94"/>
       <c r="I78" s="93"/>
@@ -13091,9 +13091,9 @@
       <c r="A79" s="90"/>
       <c r="B79" s="99"/>
       <c r="C79" s="92"/>
-      <c r="D79" s="228"/>
-      <c r="E79" s="229"/>
-      <c r="F79" s="229"/>
+      <c r="D79" s="236"/>
+      <c r="E79" s="237"/>
+      <c r="F79" s="237"/>
       <c r="G79" s="95"/>
       <c r="H79" s="94"/>
       <c r="I79" s="93"/>
@@ -13104,9 +13104,9 @@
       <c r="A80" s="90"/>
       <c r="B80" s="99"/>
       <c r="C80" s="92"/>
-      <c r="D80" s="228"/>
-      <c r="E80" s="229"/>
-      <c r="F80" s="229"/>
+      <c r="D80" s="236"/>
+      <c r="E80" s="237"/>
+      <c r="F80" s="237"/>
       <c r="G80" s="95"/>
       <c r="H80" s="94"/>
       <c r="I80" s="93"/>
@@ -13117,9 +13117,9 @@
       <c r="A81" s="90"/>
       <c r="B81" s="99"/>
       <c r="C81" s="92"/>
-      <c r="D81" s="228"/>
-      <c r="E81" s="229"/>
-      <c r="F81" s="229"/>
+      <c r="D81" s="236"/>
+      <c r="E81" s="237"/>
+      <c r="F81" s="237"/>
       <c r="G81" s="95"/>
       <c r="H81" s="94"/>
       <c r="I81" s="93"/>
@@ -13130,9 +13130,9 @@
       <c r="A82" s="90"/>
       <c r="B82" s="99"/>
       <c r="C82" s="92"/>
-      <c r="D82" s="228"/>
-      <c r="E82" s="229"/>
-      <c r="F82" s="229"/>
+      <c r="D82" s="236"/>
+      <c r="E82" s="237"/>
+      <c r="F82" s="237"/>
       <c r="G82" s="95"/>
       <c r="H82" s="94"/>
       <c r="I82" s="93"/>
@@ -13143,9 +13143,9 @@
       <c r="A83" s="90"/>
       <c r="B83" s="99"/>
       <c r="C83" s="92"/>
-      <c r="D83" s="228"/>
-      <c r="E83" s="229"/>
-      <c r="F83" s="229"/>
+      <c r="D83" s="236"/>
+      <c r="E83" s="237"/>
+      <c r="F83" s="237"/>
       <c r="G83" s="95"/>
       <c r="H83" s="94"/>
       <c r="I83" s="93"/>
@@ -13156,9 +13156,9 @@
       <c r="A84" s="90"/>
       <c r="B84" s="99"/>
       <c r="C84" s="92"/>
-      <c r="D84" s="228"/>
-      <c r="E84" s="229"/>
-      <c r="F84" s="229"/>
+      <c r="D84" s="236"/>
+      <c r="E84" s="237"/>
+      <c r="F84" s="237"/>
       <c r="G84" s="95"/>
       <c r="H84" s="94"/>
       <c r="I84" s="93"/>
@@ -13169,9 +13169,9 @@
       <c r="A85" s="90"/>
       <c r="B85" s="99"/>
       <c r="C85" s="92"/>
-      <c r="D85" s="228"/>
-      <c r="E85" s="229"/>
-      <c r="F85" s="229"/>
+      <c r="D85" s="236"/>
+      <c r="E85" s="237"/>
+      <c r="F85" s="237"/>
       <c r="G85" s="95"/>
       <c r="H85" s="94"/>
       <c r="I85" s="93"/>
@@ -13182,9 +13182,9 @@
       <c r="A86" s="90"/>
       <c r="B86" s="99"/>
       <c r="C86" s="92"/>
-      <c r="D86" s="228"/>
-      <c r="E86" s="229"/>
-      <c r="F86" s="229"/>
+      <c r="D86" s="236"/>
+      <c r="E86" s="237"/>
+      <c r="F86" s="237"/>
       <c r="G86" s="95"/>
       <c r="H86" s="94"/>
       <c r="I86" s="93"/>
@@ -13195,9 +13195,9 @@
       <c r="A87" s="90"/>
       <c r="B87" s="99"/>
       <c r="C87" s="92"/>
-      <c r="D87" s="228"/>
-      <c r="E87" s="229"/>
-      <c r="F87" s="229"/>
+      <c r="D87" s="236"/>
+      <c r="E87" s="237"/>
+      <c r="F87" s="237"/>
       <c r="G87" s="95"/>
       <c r="H87" s="94"/>
       <c r="I87" s="93"/>
@@ -13206,81 +13206,12 @@
     </row>
   </sheetData>
   <mergeCells count="94">
-    <mergeCell ref="D83:F83"/>
-    <mergeCell ref="D84:F84"/>
-    <mergeCell ref="D85:F85"/>
-    <mergeCell ref="D86:F86"/>
-    <mergeCell ref="D87:F87"/>
-    <mergeCell ref="D78:F78"/>
-    <mergeCell ref="D79:F79"/>
-    <mergeCell ref="D80:F80"/>
-    <mergeCell ref="D81:F81"/>
-    <mergeCell ref="D82:F82"/>
-    <mergeCell ref="D73:F73"/>
-    <mergeCell ref="D74:F74"/>
-    <mergeCell ref="D75:F75"/>
-    <mergeCell ref="D76:F76"/>
-    <mergeCell ref="D77:F77"/>
-    <mergeCell ref="D68:F68"/>
-    <mergeCell ref="D69:F69"/>
-    <mergeCell ref="D70:F70"/>
-    <mergeCell ref="D71:F71"/>
-    <mergeCell ref="D72:F72"/>
-    <mergeCell ref="D63:F63"/>
-    <mergeCell ref="D64:F64"/>
-    <mergeCell ref="D65:F65"/>
-    <mergeCell ref="D66:F66"/>
-    <mergeCell ref="D67:F67"/>
-    <mergeCell ref="D58:F58"/>
-    <mergeCell ref="D59:F59"/>
-    <mergeCell ref="D60:F60"/>
-    <mergeCell ref="D61:F61"/>
-    <mergeCell ref="D62:F62"/>
-    <mergeCell ref="D53:F53"/>
-    <mergeCell ref="D54:F54"/>
-    <mergeCell ref="D55:F55"/>
-    <mergeCell ref="D56:F56"/>
-    <mergeCell ref="D57:F57"/>
-    <mergeCell ref="D48:F48"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="D50:F50"/>
-    <mergeCell ref="D51:F51"/>
-    <mergeCell ref="D52:F52"/>
-    <mergeCell ref="D43:F43"/>
-    <mergeCell ref="D44:F44"/>
-    <mergeCell ref="D45:F45"/>
-    <mergeCell ref="D46:F46"/>
-    <mergeCell ref="D47:F47"/>
-    <mergeCell ref="D38:F38"/>
-    <mergeCell ref="D39:F39"/>
-    <mergeCell ref="D40:F40"/>
-    <mergeCell ref="D41:F41"/>
-    <mergeCell ref="D42:F42"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="D36:F36"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="A30:K30"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="A22:K22"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="A16:K16"/>
-    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="I5:K5"/>
     <mergeCell ref="I6:K6"/>
     <mergeCell ref="I7:K7"/>
     <mergeCell ref="A8:D8"/>
@@ -13294,12 +13225,81 @@
     <mergeCell ref="J9:J10"/>
     <mergeCell ref="K9:K10"/>
     <mergeCell ref="D9:G10"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="A16:K16"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="A22:K22"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="A30:K30"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="D38:F38"/>
+    <mergeCell ref="D39:F39"/>
+    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="D44:F44"/>
+    <mergeCell ref="D45:F45"/>
+    <mergeCell ref="D46:F46"/>
+    <mergeCell ref="D47:F47"/>
+    <mergeCell ref="D48:F48"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="D50:F50"/>
+    <mergeCell ref="D51:F51"/>
+    <mergeCell ref="D52:F52"/>
+    <mergeCell ref="D53:F53"/>
+    <mergeCell ref="D54:F54"/>
+    <mergeCell ref="D55:F55"/>
+    <mergeCell ref="D56:F56"/>
+    <mergeCell ref="D57:F57"/>
+    <mergeCell ref="D58:F58"/>
+    <mergeCell ref="D59:F59"/>
+    <mergeCell ref="D60:F60"/>
+    <mergeCell ref="D61:F61"/>
+    <mergeCell ref="D62:F62"/>
+    <mergeCell ref="D63:F63"/>
+    <mergeCell ref="D64:F64"/>
+    <mergeCell ref="D65:F65"/>
+    <mergeCell ref="D66:F66"/>
+    <mergeCell ref="D67:F67"/>
+    <mergeCell ref="D68:F68"/>
+    <mergeCell ref="D69:F69"/>
+    <mergeCell ref="D70:F70"/>
+    <mergeCell ref="D71:F71"/>
+    <mergeCell ref="D72:F72"/>
+    <mergeCell ref="D73:F73"/>
+    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="D75:F75"/>
+    <mergeCell ref="D76:F76"/>
+    <mergeCell ref="D77:F77"/>
+    <mergeCell ref="D78:F78"/>
+    <mergeCell ref="D79:F79"/>
+    <mergeCell ref="D80:F80"/>
+    <mergeCell ref="D81:F81"/>
+    <mergeCell ref="D82:F82"/>
+    <mergeCell ref="D83:F83"/>
+    <mergeCell ref="D84:F84"/>
+    <mergeCell ref="D85:F85"/>
+    <mergeCell ref="D86:F86"/>
+    <mergeCell ref="D87:F87"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/test-case-example.xlsx
+++ b/test-case-example.xlsx
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="993" uniqueCount="589">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1009" uniqueCount="594">
   <si>
     <t>TEST CASE</t>
   </si>
@@ -2365,6 +2365,21 @@
   <si>
     <t>28/4/2026</t>
   </si>
+  <si>
+    <t>29/4/2026</t>
+  </si>
+  <si>
+    <t>822, 881 - 882</t>
+  </si>
+  <si>
+    <t>revenue_report (822)</t>
+  </si>
+  <si>
+    <t>182, 218 - 220</t>
+  </si>
+  <si>
+    <t>review (182)</t>
+  </si>
 </sst>
 </file>
 
@@ -2375,7 +2390,7 @@
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="47">
+  <fonts count="48">
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -2662,6 +2677,11 @@
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="13">
     <fill>
@@ -2737,7 +2757,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="76">
+  <borders count="83">
     <border>
       <left/>
       <right/>
@@ -3704,6 +3724,103 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="hair">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFAAAAAA"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFAAAAAA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFAAAAAA"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFAAAAAA"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -3715,7 +3832,7 @@
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="272">
+  <cellXfs count="290">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3" applyFont="1"/>
@@ -4208,15 +4325,126 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="75" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="54" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="55" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="56" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="52" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="35" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="36" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="52" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="35" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="36" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="52" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="45" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="38" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="45" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="38" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="48" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="49" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="46" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="47" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="50" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="44" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="51" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="32" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="33" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="35" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -4238,117 +4466,6 @@
     <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="35" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="36" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="52" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="45" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="38" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="45" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="38" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="48" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="49" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="46" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="47" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="50" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="44" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="51" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="35" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="36" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="52" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="54" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="55" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="56" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="52" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -4367,6 +4484,15 @@
     <xf numFmtId="0" fontId="18" fillId="9" borderId="36" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="35" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="25" fillId="9" borderId="35" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -4376,15 +4502,6 @@
     <xf numFmtId="0" fontId="25" fillId="9" borderId="52" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="35" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="9" borderId="36" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -4412,14 +4529,50 @@
     <xf numFmtId="0" fontId="13" fillId="6" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="9" borderId="35" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="1" fontId="9" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="10" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="74" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="3" borderId="66" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="3" borderId="67" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -4427,44 +4580,62 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="9" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="1" fontId="8" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="3" borderId="66" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="10" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="76" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="74" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="3" borderId="67" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="77" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="78" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="47" fillId="0" borderId="79" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="47" fillId="0" borderId="80" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="81" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="82" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -4555,6 +4726,44 @@
         <a:xfrm>
           <a:off x="8306457" y="9979244"/>
           <a:ext cx="3409949" cy="844666"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>87923</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>65942</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3516922</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>149468</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8294077" y="10975730"/>
+          <a:ext cx="3428999" cy="933450"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5435,11 +5644,11 @@
       <c r="A3" s="64" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="186" t="s">
+      <c r="B3" s="224" t="s">
         <v>62</v>
       </c>
-      <c r="C3" s="186"/>
-      <c r="D3" s="187"/>
+      <c r="C3" s="224"/>
+      <c r="D3" s="225"/>
       <c r="E3" s="65"/>
       <c r="F3" s="65"/>
       <c r="G3" s="65"/>
@@ -5448,11 +5657,11 @@
       <c r="A4" s="68" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="189" t="s">
+      <c r="B4" s="226" t="s">
         <v>488</v>
       </c>
-      <c r="C4" s="190"/>
-      <c r="D4" s="191"/>
+      <c r="C4" s="227"/>
+      <c r="D4" s="228"/>
       <c r="E4" s="65"/>
       <c r="F4" s="65"/>
       <c r="G4" s="65"/>
@@ -5461,11 +5670,11 @@
       <c r="A5" s="68" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="192" t="s">
+      <c r="B5" s="229" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="193"/>
-      <c r="D5" s="194"/>
+      <c r="C5" s="230"/>
+      <c r="D5" s="231"/>
       <c r="E5" s="69"/>
       <c r="F5" s="69"/>
       <c r="G5" s="69"/>
@@ -5514,59 +5723,59 @@
       <c r="G8" s="66"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="202" t="s">
+      <c r="A9" s="212" t="s">
         <v>71</v>
       </c>
-      <c r="B9" s="204" t="s">
+      <c r="B9" s="214" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="202" t="s">
+      <c r="C9" s="212" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="208" t="s">
+      <c r="D9" s="218" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="209"/>
-      <c r="F9" s="209"/>
-      <c r="G9" s="210"/>
-      <c r="H9" s="206" t="s">
+      <c r="E9" s="219"/>
+      <c r="F9" s="219"/>
+      <c r="G9" s="220"/>
+      <c r="H9" s="216" t="s">
         <v>75</v>
       </c>
-      <c r="I9" s="207" t="s">
+      <c r="I9" s="217" t="s">
         <v>76</v>
       </c>
-      <c r="J9" s="207" t="s">
+      <c r="J9" s="217" t="s">
         <v>77</v>
       </c>
-      <c r="K9" s="207" t="s">
+      <c r="K9" s="217" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="203"/>
-      <c r="B10" s="205"/>
-      <c r="C10" s="203"/>
-      <c r="D10" s="211"/>
-      <c r="E10" s="212"/>
-      <c r="F10" s="212"/>
-      <c r="G10" s="213"/>
-      <c r="H10" s="202"/>
-      <c r="I10" s="202"/>
-      <c r="J10" s="202"/>
-      <c r="K10" s="202"/>
+      <c r="A10" s="213"/>
+      <c r="B10" s="215"/>
+      <c r="C10" s="213"/>
+      <c r="D10" s="221"/>
+      <c r="E10" s="222"/>
+      <c r="F10" s="222"/>
+      <c r="G10" s="223"/>
+      <c r="H10" s="212"/>
+      <c r="I10" s="212"/>
+      <c r="J10" s="212"/>
+      <c r="K10" s="212"/>
     </row>
     <row r="11" spans="1:11" ht="15">
-      <c r="A11" s="197"/>
-      <c r="B11" s="197"/>
-      <c r="C11" s="197"/>
-      <c r="D11" s="197"/>
-      <c r="E11" s="197"/>
-      <c r="F11" s="197"/>
-      <c r="G11" s="197"/>
-      <c r="H11" s="197"/>
-      <c r="I11" s="197"/>
-      <c r="J11" s="197"/>
-      <c r="K11" s="198"/>
+      <c r="A11" s="210"/>
+      <c r="B11" s="210"/>
+      <c r="C11" s="210"/>
+      <c r="D11" s="210"/>
+      <c r="E11" s="210"/>
+      <c r="F11" s="210"/>
+      <c r="G11" s="210"/>
+      <c r="H11" s="210"/>
+      <c r="I11" s="210"/>
+      <c r="J11" s="210"/>
+      <c r="K11" s="211"/>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="199" t="s">
@@ -5593,12 +5802,12 @@
       <c r="C13" s="86" t="s">
         <v>491</v>
       </c>
-      <c r="D13" s="214" t="s">
+      <c r="D13" s="202" t="s">
         <v>492</v>
       </c>
-      <c r="E13" s="215"/>
-      <c r="F13" s="215"/>
-      <c r="G13" s="216"/>
+      <c r="E13" s="191"/>
+      <c r="F13" s="191"/>
+      <c r="G13" s="192"/>
       <c r="H13" s="88"/>
       <c r="I13" s="90"/>
       <c r="J13" s="86" t="s">
@@ -5631,12 +5840,12 @@
       <c r="C15" s="96" t="s">
         <v>495</v>
       </c>
-      <c r="D15" s="217" t="s">
+      <c r="D15" s="203" t="s">
         <v>496</v>
       </c>
-      <c r="E15" s="218"/>
-      <c r="F15" s="218"/>
-      <c r="G15" s="219"/>
+      <c r="E15" s="204"/>
+      <c r="F15" s="204"/>
+      <c r="G15" s="205"/>
       <c r="H15" s="97"/>
       <c r="I15" s="97"/>
       <c r="J15" s="98" t="s">
@@ -5669,12 +5878,12 @@
       <c r="C17" s="96" t="s">
         <v>499</v>
       </c>
-      <c r="D17" s="217" t="s">
+      <c r="D17" s="203" t="s">
         <v>500</v>
       </c>
-      <c r="E17" s="218"/>
-      <c r="F17" s="218"/>
-      <c r="G17" s="219"/>
+      <c r="E17" s="204"/>
+      <c r="F17" s="204"/>
+      <c r="G17" s="205"/>
       <c r="H17" s="97"/>
       <c r="I17" s="97"/>
       <c r="J17" s="98" t="s">
@@ -5707,12 +5916,12 @@
       <c r="C19" s="96" t="s">
         <v>503</v>
       </c>
-      <c r="D19" s="217" t="s">
+      <c r="D19" s="203" t="s">
         <v>504</v>
       </c>
-      <c r="E19" s="218"/>
-      <c r="F19" s="218"/>
-      <c r="G19" s="219"/>
+      <c r="E19" s="204"/>
+      <c r="F19" s="204"/>
+      <c r="G19" s="205"/>
       <c r="H19" s="97"/>
       <c r="I19" s="97"/>
       <c r="J19" s="98" t="s">
@@ -5745,12 +5954,12 @@
       <c r="C21" s="96" t="s">
         <v>507</v>
       </c>
-      <c r="D21" s="217" t="s">
+      <c r="D21" s="203" t="s">
         <v>508</v>
       </c>
-      <c r="E21" s="218"/>
-      <c r="F21" s="218"/>
-      <c r="G21" s="219"/>
+      <c r="E21" s="204"/>
+      <c r="F21" s="204"/>
+      <c r="G21" s="205"/>
       <c r="H21" s="97"/>
       <c r="I21" s="97"/>
       <c r="J21" s="98" t="s">
@@ -5783,12 +5992,12 @@
       <c r="C23" s="96" t="s">
         <v>511</v>
       </c>
-      <c r="D23" s="217" t="s">
+      <c r="D23" s="203" t="s">
         <v>512</v>
       </c>
-      <c r="E23" s="218"/>
-      <c r="F23" s="218"/>
-      <c r="G23" s="219"/>
+      <c r="E23" s="204"/>
+      <c r="F23" s="204"/>
+      <c r="G23" s="205"/>
       <c r="H23" s="97"/>
       <c r="I23" s="97"/>
       <c r="J23" s="98" t="s">
@@ -5821,12 +6030,12 @@
       <c r="C25" s="96" t="s">
         <v>515</v>
       </c>
-      <c r="D25" s="217" t="s">
+      <c r="D25" s="203" t="s">
         <v>516</v>
       </c>
-      <c r="E25" s="218"/>
-      <c r="F25" s="218"/>
-      <c r="G25" s="219"/>
+      <c r="E25" s="204"/>
+      <c r="F25" s="204"/>
+      <c r="G25" s="205"/>
       <c r="H25" s="97"/>
       <c r="I25" s="97"/>
       <c r="J25" s="98" t="s">
@@ -5859,12 +6068,12 @@
       <c r="C27" s="96" t="s">
         <v>519</v>
       </c>
-      <c r="D27" s="217" t="s">
+      <c r="D27" s="203" t="s">
         <v>520</v>
       </c>
-      <c r="E27" s="218"/>
-      <c r="F27" s="218"/>
-      <c r="G27" s="219"/>
+      <c r="E27" s="204"/>
+      <c r="F27" s="204"/>
+      <c r="G27" s="205"/>
       <c r="H27" s="97"/>
       <c r="I27" s="97"/>
       <c r="J27" s="98" t="s">
@@ -5897,12 +6106,12 @@
       <c r="C29" s="96" t="s">
         <v>523</v>
       </c>
-      <c r="D29" s="217" t="s">
+      <c r="D29" s="203" t="s">
         <v>524</v>
       </c>
-      <c r="E29" s="218"/>
-      <c r="F29" s="218"/>
-      <c r="G29" s="219"/>
+      <c r="E29" s="204"/>
+      <c r="F29" s="204"/>
+      <c r="G29" s="205"/>
       <c r="H29" s="97"/>
       <c r="I29" s="97"/>
       <c r="J29" s="98" t="s">
@@ -5935,12 +6144,12 @@
       <c r="C31" s="96" t="s">
         <v>527</v>
       </c>
-      <c r="D31" s="217" t="s">
+      <c r="D31" s="203" t="s">
         <v>528</v>
       </c>
-      <c r="E31" s="218"/>
-      <c r="F31" s="218"/>
-      <c r="G31" s="219"/>
+      <c r="E31" s="204"/>
+      <c r="F31" s="204"/>
+      <c r="G31" s="205"/>
       <c r="H31" s="97"/>
       <c r="I31" s="97"/>
       <c r="J31" s="98" t="s">
@@ -5973,12 +6182,12 @@
       <c r="C33" s="96" t="s">
         <v>531</v>
       </c>
-      <c r="D33" s="217" t="s">
+      <c r="D33" s="203" t="s">
         <v>524</v>
       </c>
-      <c r="E33" s="218"/>
-      <c r="F33" s="218"/>
-      <c r="G33" s="219"/>
+      <c r="E33" s="204"/>
+      <c r="F33" s="204"/>
+      <c r="G33" s="205"/>
       <c r="H33" s="97"/>
       <c r="I33" s="97"/>
       <c r="J33" s="98" t="s">
@@ -5988,6 +6197,25 @@
     </row>
   </sheetData>
   <mergeCells count="35">
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A11:K11"/>
+    <mergeCell ref="A12:K12"/>
+    <mergeCell ref="D13:G13"/>
+    <mergeCell ref="A14:K14"/>
+    <mergeCell ref="D15:G15"/>
+    <mergeCell ref="A16:K16"/>
+    <mergeCell ref="D23:G23"/>
+    <mergeCell ref="A24:K24"/>
+    <mergeCell ref="D25:G25"/>
+    <mergeCell ref="A26:K26"/>
+    <mergeCell ref="D17:G17"/>
+    <mergeCell ref="A18:K18"/>
+    <mergeCell ref="D19:G19"/>
+    <mergeCell ref="A20:K20"/>
+    <mergeCell ref="D21:G21"/>
     <mergeCell ref="A32:K32"/>
     <mergeCell ref="D33:G33"/>
     <mergeCell ref="A9:A10"/>
@@ -6004,25 +6232,6 @@
     <mergeCell ref="A30:K30"/>
     <mergeCell ref="D31:G31"/>
     <mergeCell ref="A22:K22"/>
-    <mergeCell ref="D23:G23"/>
-    <mergeCell ref="A24:K24"/>
-    <mergeCell ref="D25:G25"/>
-    <mergeCell ref="A26:K26"/>
-    <mergeCell ref="D17:G17"/>
-    <mergeCell ref="A18:K18"/>
-    <mergeCell ref="D19:G19"/>
-    <mergeCell ref="A20:K20"/>
-    <mergeCell ref="D21:G21"/>
-    <mergeCell ref="A12:K12"/>
-    <mergeCell ref="D13:G13"/>
-    <mergeCell ref="A14:K14"/>
-    <mergeCell ref="D15:G15"/>
-    <mergeCell ref="A16:K16"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A11:K11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6051,9 +6260,9 @@
       <c r="A1" s="60" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="255"/>
-      <c r="C1" s="255"/>
-      <c r="D1" s="255"/>
+      <c r="B1" s="254"/>
+      <c r="C1" s="254"/>
+      <c r="D1" s="254"/>
       <c r="E1" s="61"/>
       <c r="F1" s="61"/>
       <c r="G1" s="61"/>
@@ -6065,9 +6274,9 @@
     </row>
     <row r="2" spans="1:12" s="54" customFormat="1" ht="11.25" customHeight="1">
       <c r="A2" s="63"/>
-      <c r="B2" s="256"/>
-      <c r="C2" s="256"/>
-      <c r="D2" s="256"/>
+      <c r="B2" s="255"/>
+      <c r="C2" s="255"/>
+      <c r="D2" s="255"/>
       <c r="E2" s="61"/>
       <c r="F2" s="61"/>
       <c r="G2" s="61"/>
@@ -6081,54 +6290,54 @@
       <c r="A3" s="64" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="186" t="s">
+      <c r="B3" s="224" t="s">
         <v>532</v>
       </c>
-      <c r="C3" s="186"/>
-      <c r="D3" s="187"/>
+      <c r="C3" s="224"/>
+      <c r="D3" s="225"/>
       <c r="E3" s="65"/>
       <c r="F3" s="65"/>
       <c r="G3" s="65"/>
       <c r="H3" s="65"/>
-      <c r="I3" s="188"/>
-      <c r="J3" s="188"/>
-      <c r="K3" s="188"/>
+      <c r="I3" s="208"/>
+      <c r="J3" s="208"/>
+      <c r="K3" s="208"/>
       <c r="L3" s="67"/>
     </row>
     <row r="4" spans="1:12" s="55" customFormat="1" ht="12.75">
       <c r="A4" s="68" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="189" t="s">
+      <c r="B4" s="226" t="s">
         <v>533</v>
       </c>
-      <c r="C4" s="190"/>
-      <c r="D4" s="191"/>
+      <c r="C4" s="227"/>
+      <c r="D4" s="228"/>
       <c r="E4" s="65"/>
       <c r="F4" s="65"/>
       <c r="G4" s="65"/>
       <c r="H4" s="65"/>
-      <c r="I4" s="188"/>
-      <c r="J4" s="188"/>
-      <c r="K4" s="188"/>
+      <c r="I4" s="208"/>
+      <c r="J4" s="208"/>
+      <c r="K4" s="208"/>
       <c r="L4" s="67"/>
     </row>
     <row r="5" spans="1:12" s="56" customFormat="1" ht="25.5">
       <c r="A5" s="68" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="192" t="s">
+      <c r="B5" s="229" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="193"/>
-      <c r="D5" s="194"/>
+      <c r="C5" s="230"/>
+      <c r="D5" s="231"/>
       <c r="E5" s="69"/>
       <c r="F5" s="69"/>
       <c r="G5" s="69"/>
       <c r="H5" s="69"/>
-      <c r="I5" s="195"/>
-      <c r="J5" s="195"/>
-      <c r="K5" s="195"/>
+      <c r="I5" s="232"/>
+      <c r="J5" s="232"/>
+      <c r="K5" s="232"/>
       <c r="L5" s="70"/>
     </row>
     <row r="6" spans="1:12" s="55" customFormat="1" ht="15" customHeight="1">
@@ -6150,9 +6359,9 @@
       <c r="F6" s="66"/>
       <c r="G6" s="66"/>
       <c r="H6" s="66"/>
-      <c r="I6" s="188"/>
-      <c r="J6" s="188"/>
-      <c r="K6" s="188"/>
+      <c r="I6" s="208"/>
+      <c r="J6" s="208"/>
+      <c r="K6" s="208"/>
       <c r="L6" s="67"/>
     </row>
     <row r="7" spans="1:12" s="55" customFormat="1" ht="15" customHeight="1">
@@ -6174,16 +6383,16 @@
       <c r="F7" s="79"/>
       <c r="G7" s="79"/>
       <c r="H7" s="79"/>
-      <c r="I7" s="188"/>
-      <c r="J7" s="188"/>
-      <c r="K7" s="188"/>
+      <c r="I7" s="208"/>
+      <c r="J7" s="208"/>
+      <c r="K7" s="208"/>
       <c r="L7" s="67"/>
     </row>
     <row r="8" spans="1:12" s="55" customFormat="1" ht="15" customHeight="1">
-      <c r="A8" s="196"/>
-      <c r="B8" s="196"/>
-      <c r="C8" s="196"/>
-      <c r="D8" s="196"/>
+      <c r="A8" s="209"/>
+      <c r="B8" s="209"/>
+      <c r="C8" s="209"/>
+      <c r="D8" s="209"/>
       <c r="E8" s="66"/>
       <c r="F8" s="66"/>
       <c r="G8" s="66"/>
@@ -6194,61 +6403,61 @@
       <c r="L8" s="67"/>
     </row>
     <row r="9" spans="1:12" s="57" customFormat="1" ht="12" customHeight="1">
-      <c r="A9" s="202" t="s">
+      <c r="A9" s="212" t="s">
         <v>71</v>
       </c>
-      <c r="B9" s="204" t="s">
+      <c r="B9" s="214" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="202" t="s">
+      <c r="C9" s="212" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="208" t="s">
+      <c r="D9" s="218" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="209"/>
-      <c r="F9" s="209"/>
-      <c r="G9" s="210"/>
-      <c r="H9" s="206" t="s">
+      <c r="E9" s="219"/>
+      <c r="F9" s="219"/>
+      <c r="G9" s="220"/>
+      <c r="H9" s="216" t="s">
         <v>75</v>
       </c>
-      <c r="I9" s="207" t="s">
+      <c r="I9" s="217" t="s">
         <v>76</v>
       </c>
-      <c r="J9" s="207" t="s">
+      <c r="J9" s="217" t="s">
         <v>77</v>
       </c>
-      <c r="K9" s="207" t="s">
+      <c r="K9" s="217" t="s">
         <v>78</v>
       </c>
       <c r="L9" s="81"/>
     </row>
     <row r="10" spans="1:12" s="55" customFormat="1" ht="12" customHeight="1">
-      <c r="A10" s="203"/>
-      <c r="B10" s="205"/>
-      <c r="C10" s="203"/>
-      <c r="D10" s="211"/>
-      <c r="E10" s="212"/>
-      <c r="F10" s="212"/>
-      <c r="G10" s="213"/>
-      <c r="H10" s="202"/>
-      <c r="I10" s="202"/>
-      <c r="J10" s="202"/>
-      <c r="K10" s="202"/>
+      <c r="A10" s="213"/>
+      <c r="B10" s="215"/>
+      <c r="C10" s="213"/>
+      <c r="D10" s="221"/>
+      <c r="E10" s="222"/>
+      <c r="F10" s="222"/>
+      <c r="G10" s="223"/>
+      <c r="H10" s="212"/>
+      <c r="I10" s="212"/>
+      <c r="J10" s="212"/>
+      <c r="K10" s="212"/>
       <c r="L10" s="67"/>
     </row>
     <row r="11" spans="1:12" s="58" customFormat="1" ht="15">
-      <c r="A11" s="197"/>
-      <c r="B11" s="197"/>
-      <c r="C11" s="197"/>
-      <c r="D11" s="197"/>
-      <c r="E11" s="197"/>
-      <c r="F11" s="197"/>
-      <c r="G11" s="197"/>
-      <c r="H11" s="197"/>
-      <c r="I11" s="197"/>
-      <c r="J11" s="197"/>
-      <c r="K11" s="198"/>
+      <c r="A11" s="210"/>
+      <c r="B11" s="210"/>
+      <c r="C11" s="210"/>
+      <c r="D11" s="210"/>
+      <c r="E11" s="210"/>
+      <c r="F11" s="210"/>
+      <c r="G11" s="210"/>
+      <c r="H11" s="210"/>
+      <c r="I11" s="210"/>
+      <c r="J11" s="210"/>
+      <c r="K11" s="211"/>
     </row>
     <row r="12" spans="1:12" s="59" customFormat="1" ht="12.75">
       <c r="A12" s="199" t="s">
@@ -6275,11 +6484,11 @@
       <c r="C13" s="86" t="s">
         <v>536</v>
       </c>
-      <c r="D13" s="222" t="s">
+      <c r="D13" s="190" t="s">
         <v>537</v>
       </c>
-      <c r="E13" s="215"/>
-      <c r="F13" s="215"/>
+      <c r="E13" s="191"/>
+      <c r="F13" s="191"/>
       <c r="G13" s="89"/>
       <c r="H13" s="88"/>
       <c r="I13" s="90"/>
@@ -6289,7 +6498,7 @@
       <c r="K13" s="86"/>
     </row>
     <row r="14" spans="1:12" s="59" customFormat="1" ht="12.75" outlineLevel="1">
-      <c r="A14" s="254" t="s">
+      <c r="A14" s="256" t="s">
         <v>538</v>
       </c>
       <c r="B14" s="238"/>
@@ -6313,11 +6522,11 @@
       <c r="C15" s="92" t="s">
         <v>540</v>
       </c>
-      <c r="D15" s="243" t="s">
+      <c r="D15" s="239" t="s">
         <v>541</v>
       </c>
-      <c r="E15" s="215"/>
-      <c r="F15" s="215"/>
+      <c r="E15" s="191"/>
+      <c r="F15" s="191"/>
       <c r="G15" s="89"/>
       <c r="H15" s="88"/>
       <c r="I15" s="87"/>
@@ -6327,7 +6536,7 @@
       <c r="K15" s="86"/>
     </row>
     <row r="16" spans="1:12" s="59" customFormat="1" ht="12.75" outlineLevel="1">
-      <c r="A16" s="254" t="s">
+      <c r="A16" s="256" t="s">
         <v>542</v>
       </c>
       <c r="B16" s="238"/>
@@ -6351,11 +6560,11 @@
       <c r="C17" s="86" t="s">
         <v>543</v>
       </c>
-      <c r="D17" s="243" t="s">
+      <c r="D17" s="239" t="s">
         <v>544</v>
       </c>
-      <c r="E17" s="244"/>
-      <c r="F17" s="244"/>
+      <c r="E17" s="240"/>
+      <c r="F17" s="240"/>
       <c r="G17" s="89"/>
       <c r="H17" s="88"/>
       <c r="I17" s="87"/>
@@ -6404,12 +6613,11 @@
     <row r="55" ht="12" customHeight="1"/>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="B1:D2"/>
-    <mergeCell ref="D9:G10"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="I5:K5"/>
     <mergeCell ref="A16:C16"/>
     <mergeCell ref="D17:F17"/>
     <mergeCell ref="I6:K6"/>
@@ -6424,11 +6632,12 @@
     <mergeCell ref="I9:I10"/>
     <mergeCell ref="J9:J10"/>
     <mergeCell ref="K9:K10"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="B1:D2"/>
+    <mergeCell ref="D9:G10"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="B3:D3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -6438,7 +6647,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="13.5"/>
   <cols>
     <col min="3" max="3" width="22.75" customWidth="1"/>
@@ -6522,10 +6731,10 @@
       <c r="F7" s="47" t="s">
         <v>68</v>
       </c>
-      <c r="G7" s="257" t="s">
+      <c r="G7" s="269" t="s">
         <v>550</v>
       </c>
-      <c r="H7" s="258"/>
+      <c r="H7" s="270"/>
     </row>
     <row r="8" spans="1:8" s="43" customFormat="1" ht="40.15" customHeight="1">
       <c r="A8" s="15"/>
@@ -6547,11 +6756,11 @@
         <f>COUNTIF(Auth!J10:J29, "Pending")</f>
         <v>0</v>
       </c>
-      <c r="G8" s="259">
+      <c r="G8" s="257">
         <f>Auth!D7</f>
         <v>26</v>
       </c>
-      <c r="H8" s="260"/>
+      <c r="H8" s="258"/>
     </row>
     <row r="9" spans="1:8" s="43" customFormat="1" ht="40.15" customHeight="1">
       <c r="A9" s="15"/>
@@ -6573,11 +6782,11 @@
         <f>COUNTIF(Home!J10:J29, "Pending")</f>
         <v>0</v>
       </c>
-      <c r="G9" s="261">
+      <c r="G9" s="259">
         <f>Home!D7</f>
         <v>17</v>
       </c>
-      <c r="H9" s="262"/>
+      <c r="H9" s="260"/>
     </row>
     <row r="10" spans="1:8" s="43" customFormat="1" ht="40.15" customHeight="1">
       <c r="A10" s="15"/>
@@ -6599,11 +6808,11 @@
         <f>COUNTIF(Favorite!J10:J29, "Pending")</f>
         <v>8</v>
       </c>
-      <c r="G10" s="263">
+      <c r="G10" s="271">
         <f>Favorite!D7</f>
         <v>8</v>
       </c>
-      <c r="H10" s="260"/>
+      <c r="H10" s="258"/>
     </row>
     <row r="11" spans="1:8" s="43" customFormat="1" ht="40.15" customHeight="1">
       <c r="A11" s="15"/>
@@ -6625,11 +6834,11 @@
         <f>COUNTIF(Booking!J10:J42, "Pending")</f>
         <v>23</v>
       </c>
-      <c r="G11" s="261">
+      <c r="G11" s="259">
         <f>Booking!D7</f>
         <v>23</v>
       </c>
-      <c r="H11" s="262"/>
+      <c r="H11" s="260"/>
     </row>
     <row r="12" spans="1:8" s="43" customFormat="1" ht="40.15" customHeight="1">
       <c r="A12" s="15"/>
@@ -6651,11 +6860,11 @@
         <f>COUNTIF('Cancel Booking'!J10:J29, "Pending")</f>
         <v>12</v>
       </c>
-      <c r="G12" s="259">
+      <c r="G12" s="257">
         <f>'Cancel Booking'!D7</f>
         <v>12</v>
       </c>
-      <c r="H12" s="260"/>
+      <c r="H12" s="258"/>
     </row>
     <row r="13" spans="1:8" s="43" customFormat="1" ht="40.15" customHeight="1">
       <c r="A13" s="15"/>
@@ -6677,11 +6886,11 @@
         <f>COUNTIF(Review!J10:J29, "Pending")</f>
         <v>10</v>
       </c>
-      <c r="G13" s="261">
+      <c r="G13" s="259">
         <f>Review!D7</f>
         <v>10</v>
       </c>
-      <c r="H13" s="262"/>
+      <c r="H13" s="260"/>
     </row>
     <row r="14" spans="1:8" s="43" customFormat="1" ht="40.15" customHeight="1">
       <c r="A14" s="15"/>
@@ -6703,11 +6912,11 @@
         <f>COUNTIF(Admin!J10:J29, "Pending")</f>
         <v>0</v>
       </c>
-      <c r="G14" s="259">
+      <c r="G14" s="257">
         <f>Admin!D7</f>
         <v>14</v>
       </c>
-      <c r="H14" s="260"/>
+      <c r="H14" s="258"/>
     </row>
     <row r="15" spans="1:8" ht="40.15" customHeight="1">
       <c r="A15" s="5"/>
@@ -6729,11 +6938,11 @@
         <f>COUNTIF(Venue!J10:J29, "Pending")</f>
         <v>6</v>
       </c>
-      <c r="G15" s="261">
+      <c r="G15" s="259">
         <f>Venue!D7</f>
         <v>6</v>
       </c>
-      <c r="H15" s="262"/>
+      <c r="H15" s="260"/>
     </row>
     <row r="16" spans="1:8" ht="40.15" customHeight="1">
       <c r="A16" s="5"/>
@@ -6753,11 +6962,11 @@
         <f>SUM(F8:F15)</f>
         <v>59</v>
       </c>
-      <c r="G16" s="267">
+      <c r="G16" s="261">
         <f>SUM(G8:H15)</f>
         <v>116</v>
       </c>
-      <c r="H16" s="268"/>
+      <c r="H16" s="262"/>
     </row>
     <row r="17" spans="1:9" ht="14.25">
       <c r="A17" s="5"/>
@@ -6907,7 +7116,7 @@
     </row>
     <row r="30" spans="1:9" ht="14.25">
       <c r="A30" s="5"/>
-      <c r="B30" s="269" t="s">
+      <c r="B30" s="263" t="s">
         <v>44</v>
       </c>
       <c r="C30" s="182" t="s">
@@ -6932,7 +7141,7 @@
     </row>
     <row r="31" spans="1:9" ht="14.25">
       <c r="A31" s="5"/>
-      <c r="B31" s="265"/>
+      <c r="B31" s="264"/>
       <c r="C31" s="182" t="s">
         <v>573</v>
       </c>
@@ -6955,7 +7164,7 @@
     </row>
     <row r="32" spans="1:9" ht="17.25" customHeight="1">
       <c r="A32" s="5"/>
-      <c r="B32" s="265"/>
+      <c r="B32" s="264"/>
       <c r="C32" s="182" t="s">
         <v>576</v>
       </c>
@@ -6978,7 +7187,7 @@
     </row>
     <row r="33" spans="1:9" ht="17.25" customHeight="1">
       <c r="A33" s="5"/>
-      <c r="B33" s="265"/>
+      <c r="B33" s="264"/>
       <c r="C33" s="182" t="s">
         <v>578</v>
       </c>
@@ -7001,7 +7210,7 @@
     </row>
     <row r="34" spans="1:9" ht="16.5" customHeight="1">
       <c r="A34" s="5"/>
-      <c r="B34" s="270"/>
+      <c r="B34" s="265"/>
       <c r="C34" s="183" t="s">
         <v>579</v>
       </c>
@@ -7020,11 +7229,11 @@
       <c r="H34" s="174" t="s">
         <v>581</v>
       </c>
-      <c r="I34" s="271"/>
+      <c r="I34" s="267"/>
     </row>
     <row r="35" spans="1:9" ht="16.5" customHeight="1">
       <c r="A35" s="5"/>
-      <c r="B35" s="264" t="s">
+      <c r="B35" s="268" t="s">
         <v>588</v>
       </c>
       <c r="C35" s="184" t="s">
@@ -7049,7 +7258,7 @@
     </row>
     <row r="36" spans="1:9" ht="16.5" customHeight="1">
       <c r="A36" s="5"/>
-      <c r="B36" s="265"/>
+      <c r="B36" s="264"/>
       <c r="C36" s="185" t="s">
         <v>573</v>
       </c>
@@ -7072,7 +7281,7 @@
     </row>
     <row r="37" spans="1:9" ht="16.5" customHeight="1">
       <c r="A37" s="5"/>
-      <c r="B37" s="265"/>
+      <c r="B37" s="264"/>
       <c r="C37" s="182" t="s">
         <v>576</v>
       </c>
@@ -7095,7 +7304,7 @@
     </row>
     <row r="38" spans="1:9" ht="16.5" customHeight="1">
       <c r="A38" s="5"/>
-      <c r="B38" s="265"/>
+      <c r="B38" s="264"/>
       <c r="C38" s="182" t="s">
         <v>578</v>
       </c>
@@ -7118,7 +7327,7 @@
     </row>
     <row r="39" spans="1:9" ht="16.5" customHeight="1">
       <c r="A39" s="5"/>
-      <c r="B39" s="270"/>
+      <c r="B39" s="265"/>
       <c r="C39" s="183" t="s">
         <v>579</v>
       </c>
@@ -7139,46 +7348,160 @@
       </c>
       <c r="I39" s="181"/>
     </row>
-    <row r="40" spans="1:9" ht="14.25">
+    <row r="40" spans="1:9" ht="16.5" customHeight="1">
       <c r="A40" s="5"/>
-      <c r="B40" s="32"/>
-      <c r="C40" s="33" t="s">
+      <c r="B40" s="273" t="s">
+        <v>589</v>
+      </c>
+      <c r="C40" s="274" t="s">
+        <v>571</v>
+      </c>
+      <c r="D40" s="275">
+        <v>12</v>
+      </c>
+      <c r="E40" s="276">
+        <v>0</v>
+      </c>
+      <c r="F40" s="277">
+        <v>1</v>
+      </c>
+      <c r="G40" s="278" t="s">
+        <v>572</v>
+      </c>
+      <c r="H40" s="278" t="s">
+        <v>572</v>
+      </c>
+      <c r="I40" s="279"/>
+    </row>
+    <row r="41" spans="1:9" ht="16.5" customHeight="1">
+      <c r="A41" s="5"/>
+      <c r="B41" s="280"/>
+      <c r="C41" s="281" t="s">
+        <v>573</v>
+      </c>
+      <c r="D41" s="282">
+        <v>92</v>
+      </c>
+      <c r="E41" s="283">
+        <v>0</v>
+      </c>
+      <c r="F41" s="284">
+        <v>1</v>
+      </c>
+      <c r="G41" s="285" t="s">
+        <v>572</v>
+      </c>
+      <c r="H41" s="285" t="s">
+        <v>572</v>
+      </c>
+      <c r="I41" s="286"/>
+    </row>
+    <row r="42" spans="1:9" ht="16.5" customHeight="1">
+      <c r="A42" s="5"/>
+      <c r="B42" s="280"/>
+      <c r="C42" s="281" t="s">
+        <v>576</v>
+      </c>
+      <c r="D42" s="282">
+        <v>137</v>
+      </c>
+      <c r="E42" s="283">
+        <v>0</v>
+      </c>
+      <c r="F42" s="284">
+        <v>1</v>
+      </c>
+      <c r="G42" s="285" t="s">
+        <v>572</v>
+      </c>
+      <c r="H42" s="285" t="s">
+        <v>572</v>
+      </c>
+      <c r="I42" s="286"/>
+    </row>
+    <row r="43" spans="1:9" ht="16.5" customHeight="1">
+      <c r="A43" s="5"/>
+      <c r="B43" s="280"/>
+      <c r="C43" s="281" t="s">
+        <v>578</v>
+      </c>
+      <c r="D43" s="282">
+        <v>541</v>
+      </c>
+      <c r="E43" s="283">
+        <v>3</v>
+      </c>
+      <c r="F43" s="284">
+        <v>0.99</v>
+      </c>
+      <c r="G43" s="285" t="s">
+        <v>590</v>
+      </c>
+      <c r="H43" s="285" t="s">
+        <v>591</v>
+      </c>
+      <c r="I43" s="286"/>
+    </row>
+    <row r="44" spans="1:9" ht="16.5" customHeight="1">
+      <c r="A44" s="5"/>
+      <c r="B44" s="287"/>
+      <c r="C44" s="288" t="s">
+        <v>579</v>
+      </c>
+      <c r="D44" s="289">
+        <v>167</v>
+      </c>
+      <c r="E44" s="283">
+        <v>4</v>
+      </c>
+      <c r="F44" s="284">
+        <v>0.98</v>
+      </c>
+      <c r="G44" s="285" t="s">
+        <v>592</v>
+      </c>
+      <c r="H44" s="285" t="s">
+        <v>593</v>
+      </c>
+      <c r="I44" s="286"/>
+    </row>
+    <row r="45" spans="1:9" ht="14.25">
+      <c r="A45" s="5"/>
+      <c r="B45" s="272"/>
+      <c r="C45" s="33" t="s">
         <v>559</v>
       </c>
-      <c r="D40" s="34">
+      <c r="D45" s="34">
         <f>SUM(D28:D39)</f>
         <v>1898</v>
       </c>
-      <c r="E40" s="35">
+      <c r="E45" s="35">
         <f>SUM(E28:E39)</f>
         <v>322</v>
       </c>
-      <c r="F40" s="34"/>
-      <c r="G40" s="36"/>
-      <c r="H40" s="37"/>
-      <c r="I40" s="38"/>
-    </row>
-    <row r="41" spans="1:9" ht="14.25">
-      <c r="A41" s="5"/>
-      <c r="B41" s="39"/>
-      <c r="C41" s="5"/>
-      <c r="D41" s="40"/>
-      <c r="E41" s="41"/>
-      <c r="F41" s="41"/>
-      <c r="G41" s="41"/>
-      <c r="H41" s="41"/>
-      <c r="I41" s="41"/>
-    </row>
-    <row r="44" spans="1:9">
-      <c r="G44" s="170"/>
+      <c r="F45" s="34"/>
+      <c r="G45" s="36"/>
+      <c r="H45" s="37"/>
+      <c r="I45" s="38"/>
+    </row>
+    <row r="46" spans="1:9" ht="14.25">
+      <c r="A46" s="5"/>
+      <c r="B46" s="39"/>
+      <c r="C46" s="5"/>
+      <c r="D46" s="40"/>
+      <c r="E46" s="41"/>
+      <c r="F46" s="41"/>
+      <c r="G46" s="41"/>
+      <c r="H46" s="41"/>
+      <c r="I46" s="41"/>
+    </row>
+    <row r="49" spans="7:7">
+      <c r="G49" s="170"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="G16:H16"/>
+  <mergeCells count="15">
+    <mergeCell ref="B40:B44"/>
+    <mergeCell ref="I40:I44"/>
     <mergeCell ref="B30:B34"/>
     <mergeCell ref="I30:I34"/>
     <mergeCell ref="B35:B39"/>
@@ -7187,6 +7510,11 @@
     <mergeCell ref="G9:H9"/>
     <mergeCell ref="G10:H10"/>
     <mergeCell ref="G11:H11"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G16:H16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
@@ -7241,52 +7569,52 @@
       <c r="A3" s="64" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="186" t="s">
+      <c r="B3" s="224" t="s">
         <v>62</v>
       </c>
-      <c r="C3" s="186"/>
-      <c r="D3" s="187"/>
+      <c r="C3" s="224"/>
+      <c r="D3" s="225"/>
       <c r="E3" s="65"/>
       <c r="F3" s="65"/>
       <c r="G3" s="65"/>
       <c r="H3" s="65"/>
-      <c r="I3" s="188"/>
-      <c r="J3" s="188"/>
-      <c r="K3" s="188"/>
+      <c r="I3" s="208"/>
+      <c r="J3" s="208"/>
+      <c r="K3" s="208"/>
     </row>
     <row r="4" spans="1:11" ht="14.25">
       <c r="A4" s="68" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="189" t="s">
+      <c r="B4" s="226" t="s">
         <v>64</v>
       </c>
-      <c r="C4" s="190"/>
-      <c r="D4" s="191"/>
+      <c r="C4" s="227"/>
+      <c r="D4" s="228"/>
       <c r="E4" s="65"/>
       <c r="F4" s="65"/>
       <c r="G4" s="65"/>
       <c r="H4" s="65"/>
-      <c r="I4" s="188"/>
-      <c r="J4" s="188"/>
-      <c r="K4" s="188"/>
+      <c r="I4" s="208"/>
+      <c r="J4" s="208"/>
+      <c r="K4" s="208"/>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="68" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="192" t="s">
+      <c r="B5" s="229" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="193"/>
-      <c r="D5" s="194"/>
+      <c r="C5" s="230"/>
+      <c r="D5" s="231"/>
       <c r="E5" s="69"/>
       <c r="F5" s="69"/>
       <c r="G5" s="69"/>
       <c r="H5" s="69"/>
-      <c r="I5" s="195"/>
-      <c r="J5" s="195"/>
-      <c r="K5" s="195"/>
+      <c r="I5" s="232"/>
+      <c r="J5" s="232"/>
+      <c r="K5" s="232"/>
     </row>
     <row r="6" spans="1:11" ht="14.25">
       <c r="A6" s="71" t="s">
@@ -7305,9 +7633,9 @@
       <c r="F6" s="66"/>
       <c r="G6" s="66"/>
       <c r="H6" s="66"/>
-      <c r="I6" s="188"/>
-      <c r="J6" s="188"/>
-      <c r="K6" s="188"/>
+      <c r="I6" s="208"/>
+      <c r="J6" s="208"/>
+      <c r="K6" s="208"/>
     </row>
     <row r="7" spans="1:11" ht="14.25">
       <c r="A7" s="75" t="s">
@@ -7327,15 +7655,15 @@
       <c r="F7" s="79"/>
       <c r="G7" s="79"/>
       <c r="H7" s="79"/>
-      <c r="I7" s="188"/>
-      <c r="J7" s="188"/>
-      <c r="K7" s="188"/>
+      <c r="I7" s="208"/>
+      <c r="J7" s="208"/>
+      <c r="K7" s="208"/>
     </row>
     <row r="8" spans="1:11" ht="14.25">
-      <c r="A8" s="196"/>
-      <c r="B8" s="196"/>
-      <c r="C8" s="196"/>
-      <c r="D8" s="196"/>
+      <c r="A8" s="209"/>
+      <c r="B8" s="209"/>
+      <c r="C8" s="209"/>
+      <c r="D8" s="209"/>
       <c r="E8" s="66"/>
       <c r="F8" s="66"/>
       <c r="G8" s="66"/>
@@ -7345,59 +7673,59 @@
       <c r="K8" s="80"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="202" t="s">
+      <c r="A9" s="212" t="s">
         <v>71</v>
       </c>
-      <c r="B9" s="204" t="s">
+      <c r="B9" s="214" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="202" t="s">
+      <c r="C9" s="212" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="208" t="s">
+      <c r="D9" s="218" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="209"/>
-      <c r="F9" s="209"/>
-      <c r="G9" s="210"/>
-      <c r="H9" s="206" t="s">
+      <c r="E9" s="219"/>
+      <c r="F9" s="219"/>
+      <c r="G9" s="220"/>
+      <c r="H9" s="216" t="s">
         <v>75</v>
       </c>
-      <c r="I9" s="207" t="s">
+      <c r="I9" s="217" t="s">
         <v>76</v>
       </c>
-      <c r="J9" s="207" t="s">
+      <c r="J9" s="217" t="s">
         <v>77</v>
       </c>
-      <c r="K9" s="207" t="s">
+      <c r="K9" s="217" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="203"/>
-      <c r="B10" s="205"/>
-      <c r="C10" s="203"/>
-      <c r="D10" s="211"/>
-      <c r="E10" s="212"/>
-      <c r="F10" s="212"/>
-      <c r="G10" s="213"/>
-      <c r="H10" s="202"/>
-      <c r="I10" s="202"/>
-      <c r="J10" s="202"/>
-      <c r="K10" s="202"/>
+      <c r="A10" s="213"/>
+      <c r="B10" s="215"/>
+      <c r="C10" s="213"/>
+      <c r="D10" s="221"/>
+      <c r="E10" s="222"/>
+      <c r="F10" s="222"/>
+      <c r="G10" s="223"/>
+      <c r="H10" s="212"/>
+      <c r="I10" s="212"/>
+      <c r="J10" s="212"/>
+      <c r="K10" s="212"/>
     </row>
     <row r="11" spans="1:11" ht="15">
-      <c r="A11" s="197"/>
-      <c r="B11" s="197"/>
-      <c r="C11" s="197"/>
-      <c r="D11" s="197"/>
-      <c r="E11" s="197"/>
-      <c r="F11" s="197"/>
-      <c r="G11" s="197"/>
-      <c r="H11" s="197"/>
-      <c r="I11" s="197"/>
-      <c r="J11" s="197"/>
-      <c r="K11" s="198"/>
+      <c r="A11" s="210"/>
+      <c r="B11" s="210"/>
+      <c r="C11" s="210"/>
+      <c r="D11" s="210"/>
+      <c r="E11" s="210"/>
+      <c r="F11" s="210"/>
+      <c r="G11" s="210"/>
+      <c r="H11" s="210"/>
+      <c r="I11" s="210"/>
+      <c r="J11" s="210"/>
+      <c r="K11" s="211"/>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="199" t="s">
@@ -7424,12 +7752,12 @@
       <c r="C13" s="86" t="s">
         <v>82</v>
       </c>
-      <c r="D13" s="214" t="s">
+      <c r="D13" s="202" t="s">
         <v>83</v>
       </c>
-      <c r="E13" s="215"/>
-      <c r="F13" s="215"/>
-      <c r="G13" s="216"/>
+      <c r="E13" s="191"/>
+      <c r="F13" s="191"/>
+      <c r="G13" s="192"/>
       <c r="H13" s="88"/>
       <c r="I13" s="90"/>
       <c r="J13" s="86" t="s">
@@ -7462,12 +7790,12 @@
       <c r="C15" s="96" t="s">
         <v>87</v>
       </c>
-      <c r="D15" s="217" t="s">
+      <c r="D15" s="203" t="s">
         <v>88</v>
       </c>
-      <c r="E15" s="218"/>
-      <c r="F15" s="218"/>
-      <c r="G15" s="219"/>
+      <c r="E15" s="204"/>
+      <c r="F15" s="204"/>
+      <c r="G15" s="205"/>
       <c r="H15" s="97"/>
       <c r="I15" s="97"/>
       <c r="J15" s="98" t="s">
@@ -7500,12 +7828,12 @@
       <c r="C17" s="92" t="s">
         <v>92</v>
       </c>
-      <c r="D17" s="214" t="s">
+      <c r="D17" s="202" t="s">
         <v>93</v>
       </c>
-      <c r="E17" s="220"/>
-      <c r="F17" s="220"/>
-      <c r="G17" s="221"/>
+      <c r="E17" s="206"/>
+      <c r="F17" s="206"/>
+      <c r="G17" s="207"/>
       <c r="H17" s="88"/>
       <c r="I17" s="87"/>
       <c r="J17" s="86" t="s">
@@ -7538,12 +7866,12 @@
       <c r="C19" s="86" t="s">
         <v>97</v>
       </c>
-      <c r="D19" s="222" t="s">
+      <c r="D19" s="190" t="s">
         <v>98</v>
       </c>
-      <c r="E19" s="215"/>
-      <c r="F19" s="215"/>
-      <c r="G19" s="216"/>
+      <c r="E19" s="191"/>
+      <c r="F19" s="191"/>
+      <c r="G19" s="192"/>
       <c r="H19" s="88"/>
       <c r="I19" s="87"/>
       <c r="J19" s="86" t="s">
@@ -7576,12 +7904,12 @@
       <c r="C21" s="86" t="s">
         <v>102</v>
       </c>
-      <c r="D21" s="222" t="s">
+      <c r="D21" s="190" t="s">
         <v>103</v>
       </c>
-      <c r="E21" s="215"/>
-      <c r="F21" s="215"/>
-      <c r="G21" s="216"/>
+      <c r="E21" s="191"/>
+      <c r="F21" s="191"/>
+      <c r="G21" s="192"/>
       <c r="H21" s="88"/>
       <c r="I21" s="87"/>
       <c r="J21" s="86" t="s">
@@ -7599,12 +7927,12 @@
       <c r="C22" s="86" t="s">
         <v>106</v>
       </c>
-      <c r="D22" s="222" t="s">
+      <c r="D22" s="190" t="s">
         <v>107</v>
       </c>
-      <c r="E22" s="215"/>
-      <c r="F22" s="215"/>
-      <c r="G22" s="216"/>
+      <c r="E22" s="191"/>
+      <c r="F22" s="191"/>
+      <c r="G22" s="192"/>
       <c r="H22" s="86"/>
       <c r="I22" s="86"/>
       <c r="J22" s="86" t="s">
@@ -7637,12 +7965,12 @@
       <c r="C24" s="86" t="s">
         <v>111</v>
       </c>
-      <c r="D24" s="222" t="s">
+      <c r="D24" s="190" t="s">
         <v>112</v>
       </c>
-      <c r="E24" s="215"/>
-      <c r="F24" s="215"/>
-      <c r="G24" s="216"/>
+      <c r="E24" s="191"/>
+      <c r="F24" s="191"/>
+      <c r="G24" s="192"/>
       <c r="H24" s="86"/>
       <c r="I24" s="86"/>
       <c r="J24" s="86" t="s">
@@ -7660,12 +7988,12 @@
       <c r="C25" s="86" t="s">
         <v>115</v>
       </c>
-      <c r="D25" s="222" t="s">
+      <c r="D25" s="190" t="s">
         <v>116</v>
       </c>
-      <c r="E25" s="215"/>
-      <c r="F25" s="215"/>
-      <c r="G25" s="216"/>
+      <c r="E25" s="191"/>
+      <c r="F25" s="191"/>
+      <c r="G25" s="192"/>
       <c r="H25" s="86"/>
       <c r="I25" s="86"/>
       <c r="J25" s="86" t="s">
@@ -7698,12 +8026,12 @@
       <c r="C27" s="86" t="s">
         <v>120</v>
       </c>
-      <c r="D27" s="222" t="s">
+      <c r="D27" s="190" t="s">
         <v>121</v>
       </c>
-      <c r="E27" s="215"/>
-      <c r="F27" s="215"/>
-      <c r="G27" s="216"/>
+      <c r="E27" s="191"/>
+      <c r="F27" s="191"/>
+      <c r="G27" s="192"/>
       <c r="H27" s="86"/>
       <c r="I27" s="86"/>
       <c r="J27" s="86" t="s">
@@ -7721,12 +8049,12 @@
       <c r="C28" s="86" t="s">
         <v>124</v>
       </c>
-      <c r="D28" s="222" t="s">
+      <c r="D28" s="190" t="s">
         <v>125</v>
       </c>
-      <c r="E28" s="215"/>
-      <c r="F28" s="215"/>
-      <c r="G28" s="216"/>
+      <c r="E28" s="191"/>
+      <c r="F28" s="191"/>
+      <c r="G28" s="192"/>
       <c r="H28" s="86"/>
       <c r="I28" s="86"/>
       <c r="J28" s="86" t="s">
@@ -7744,12 +8072,12 @@
       <c r="C29" s="86" t="s">
         <v>128</v>
       </c>
-      <c r="D29" s="222" t="s">
+      <c r="D29" s="190" t="s">
         <v>129</v>
       </c>
-      <c r="E29" s="215"/>
-      <c r="F29" s="215"/>
-      <c r="G29" s="216"/>
+      <c r="E29" s="191"/>
+      <c r="F29" s="191"/>
+      <c r="G29" s="192"/>
       <c r="H29" s="133"/>
       <c r="I29" s="133"/>
       <c r="J29" s="86" t="s">
@@ -7758,19 +8086,19 @@
       <c r="K29" s="133"/>
     </row>
     <row r="30" spans="1:11">
-      <c r="A30" s="223" t="s">
+      <c r="A30" s="193" t="s">
         <v>130</v>
       </c>
-      <c r="B30" s="224"/>
-      <c r="C30" s="224"/>
-      <c r="D30" s="224"/>
-      <c r="E30" s="224"/>
-      <c r="F30" s="224"/>
-      <c r="G30" s="224"/>
-      <c r="H30" s="224"/>
-      <c r="I30" s="224"/>
-      <c r="J30" s="224"/>
-      <c r="K30" s="225"/>
+      <c r="B30" s="194"/>
+      <c r="C30" s="194"/>
+      <c r="D30" s="194"/>
+      <c r="E30" s="194"/>
+      <c r="F30" s="194"/>
+      <c r="G30" s="194"/>
+      <c r="H30" s="194"/>
+      <c r="I30" s="194"/>
+      <c r="J30" s="194"/>
+      <c r="K30" s="195"/>
     </row>
     <row r="31" spans="1:11" ht="102">
       <c r="A31" s="84" t="s">
@@ -7782,12 +8110,12 @@
       <c r="C31" s="86" t="s">
         <v>132</v>
       </c>
-      <c r="D31" s="226" t="s">
+      <c r="D31" s="188" t="s">
         <v>133</v>
       </c>
-      <c r="E31" s="227"/>
-      <c r="F31" s="227"/>
-      <c r="G31" s="227"/>
+      <c r="E31" s="189"/>
+      <c r="F31" s="189"/>
+      <c r="G31" s="189"/>
       <c r="H31" s="86"/>
       <c r="I31" s="119"/>
       <c r="J31" s="86" t="s">
@@ -7805,12 +8133,12 @@
       <c r="C32" s="135" t="s">
         <v>135</v>
       </c>
-      <c r="D32" s="228" t="s">
+      <c r="D32" s="196" t="s">
         <v>136</v>
       </c>
-      <c r="E32" s="229"/>
-      <c r="F32" s="229"/>
-      <c r="G32" s="230"/>
+      <c r="E32" s="197"/>
+      <c r="F32" s="197"/>
+      <c r="G32" s="198"/>
       <c r="H32" s="135"/>
       <c r="I32" s="135"/>
       <c r="J32" s="134" t="s">
@@ -7828,12 +8156,12 @@
       <c r="C33" s="86" t="s">
         <v>138</v>
       </c>
-      <c r="D33" s="226" t="s">
+      <c r="D33" s="188" t="s">
         <v>139</v>
       </c>
-      <c r="E33" s="227"/>
-      <c r="F33" s="227"/>
-      <c r="G33" s="227"/>
+      <c r="E33" s="189"/>
+      <c r="F33" s="189"/>
+      <c r="G33" s="189"/>
       <c r="H33" s="86"/>
       <c r="I33" s="119"/>
       <c r="J33" s="86" t="s">
@@ -7851,12 +8179,12 @@
       <c r="C34" s="86" t="s">
         <v>141</v>
       </c>
-      <c r="D34" s="226" t="s">
+      <c r="D34" s="188" t="s">
         <v>142</v>
       </c>
-      <c r="E34" s="227"/>
-      <c r="F34" s="227"/>
-      <c r="G34" s="227"/>
+      <c r="E34" s="189"/>
+      <c r="F34" s="189"/>
+      <c r="G34" s="189"/>
       <c r="H34" s="86"/>
       <c r="I34" s="119"/>
       <c r="J34" s="86" t="s">
@@ -7874,12 +8202,12 @@
       <c r="C35" s="86" t="s">
         <v>144</v>
       </c>
-      <c r="D35" s="226" t="s">
+      <c r="D35" s="188" t="s">
         <v>145</v>
       </c>
-      <c r="E35" s="227"/>
-      <c r="F35" s="227"/>
-      <c r="G35" s="227"/>
+      <c r="E35" s="189"/>
+      <c r="F35" s="189"/>
+      <c r="G35" s="189"/>
       <c r="H35" s="86"/>
       <c r="I35" s="119"/>
       <c r="J35" s="86" t="s">
@@ -7897,12 +8225,12 @@
       <c r="C36" s="86" t="s">
         <v>147</v>
       </c>
-      <c r="D36" s="226" t="s">
+      <c r="D36" s="188" t="s">
         <v>148</v>
       </c>
-      <c r="E36" s="227"/>
-      <c r="F36" s="227"/>
-      <c r="G36" s="227"/>
+      <c r="E36" s="189"/>
+      <c r="F36" s="189"/>
+      <c r="G36" s="189"/>
       <c r="H36" s="86"/>
       <c r="I36" s="119"/>
       <c r="J36" s="86" t="s">
@@ -7920,12 +8248,12 @@
       <c r="C37" s="92" t="s">
         <v>150</v>
       </c>
-      <c r="D37" s="231" t="s">
+      <c r="D37" s="186" t="s">
         <v>151</v>
       </c>
-      <c r="E37" s="232"/>
-      <c r="F37" s="232"/>
-      <c r="G37" s="232"/>
+      <c r="E37" s="187"/>
+      <c r="F37" s="187"/>
+      <c r="G37" s="187"/>
       <c r="H37" s="92"/>
       <c r="I37" s="136"/>
       <c r="J37" s="92" t="s">
@@ -7943,12 +8271,12 @@
       <c r="C38" s="92" t="s">
         <v>153</v>
       </c>
-      <c r="D38" s="231" t="s">
+      <c r="D38" s="186" t="s">
         <v>154</v>
       </c>
-      <c r="E38" s="232"/>
-      <c r="F38" s="232"/>
-      <c r="G38" s="232"/>
+      <c r="E38" s="187"/>
+      <c r="F38" s="187"/>
+      <c r="G38" s="187"/>
       <c r="H38" s="92"/>
       <c r="I38" s="136"/>
       <c r="J38" s="92" t="s">
@@ -7966,12 +8294,12 @@
       <c r="C39" s="86" t="s">
         <v>156</v>
       </c>
-      <c r="D39" s="226" t="s">
+      <c r="D39" s="188" t="s">
         <v>157</v>
       </c>
-      <c r="E39" s="227"/>
-      <c r="F39" s="227"/>
-      <c r="G39" s="227"/>
+      <c r="E39" s="189"/>
+      <c r="F39" s="189"/>
+      <c r="G39" s="189"/>
       <c r="H39" s="86"/>
       <c r="I39" s="119"/>
       <c r="J39" s="86" t="s">
@@ -7989,12 +8317,12 @@
       <c r="C40" s="86" t="s">
         <v>159</v>
       </c>
-      <c r="D40" s="226" t="s">
+      <c r="D40" s="188" t="s">
         <v>160</v>
       </c>
-      <c r="E40" s="227"/>
-      <c r="F40" s="227"/>
-      <c r="G40" s="227"/>
+      <c r="E40" s="189"/>
+      <c r="F40" s="189"/>
+      <c r="G40" s="189"/>
       <c r="H40" s="86"/>
       <c r="I40" s="119"/>
       <c r="J40" s="86" t="s">
@@ -8012,12 +8340,12 @@
       <c r="C41" s="86" t="s">
         <v>159</v>
       </c>
-      <c r="D41" s="226" t="s">
+      <c r="D41" s="188" t="s">
         <v>160</v>
       </c>
-      <c r="E41" s="227"/>
-      <c r="F41" s="227"/>
-      <c r="G41" s="227"/>
+      <c r="E41" s="189"/>
+      <c r="F41" s="189"/>
+      <c r="G41" s="189"/>
       <c r="H41" s="86"/>
       <c r="I41" s="119"/>
       <c r="J41" s="86" t="s">
@@ -8035,12 +8363,12 @@
       <c r="C42" s="86" t="s">
         <v>163</v>
       </c>
-      <c r="D42" s="226" t="s">
+      <c r="D42" s="188" t="s">
         <v>164</v>
       </c>
-      <c r="E42" s="227"/>
-      <c r="F42" s="227"/>
-      <c r="G42" s="227"/>
+      <c r="E42" s="189"/>
+      <c r="F42" s="189"/>
+      <c r="G42" s="189"/>
       <c r="H42" s="86"/>
       <c r="I42" s="119"/>
       <c r="J42" s="86" t="s">
@@ -8050,36 +8378,12 @@
     </row>
   </sheetData>
   <mergeCells count="49">
-    <mergeCell ref="D38:G38"/>
-    <mergeCell ref="D39:G39"/>
-    <mergeCell ref="D40:G40"/>
-    <mergeCell ref="D41:G41"/>
-    <mergeCell ref="D42:G42"/>
-    <mergeCell ref="D33:G33"/>
-    <mergeCell ref="D34:G34"/>
-    <mergeCell ref="D35:G35"/>
-    <mergeCell ref="D36:G36"/>
-    <mergeCell ref="D37:G37"/>
-    <mergeCell ref="D28:G28"/>
-    <mergeCell ref="D29:G29"/>
-    <mergeCell ref="A30:K30"/>
-    <mergeCell ref="D31:G31"/>
-    <mergeCell ref="D32:G32"/>
-    <mergeCell ref="A23:K23"/>
-    <mergeCell ref="D24:G24"/>
-    <mergeCell ref="D25:G25"/>
-    <mergeCell ref="A26:K26"/>
-    <mergeCell ref="D27:G27"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="D19:G19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="D21:G21"/>
-    <mergeCell ref="D22:G22"/>
-    <mergeCell ref="D13:G13"/>
-    <mergeCell ref="A14:K14"/>
-    <mergeCell ref="D15:G15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="D17:G17"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="I5:K5"/>
     <mergeCell ref="I6:K6"/>
     <mergeCell ref="I7:K7"/>
     <mergeCell ref="A8:D8"/>
@@ -8093,12 +8397,36 @@
     <mergeCell ref="J9:J10"/>
     <mergeCell ref="K9:K10"/>
     <mergeCell ref="D9:G10"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="D13:G13"/>
+    <mergeCell ref="A14:K14"/>
+    <mergeCell ref="D15:G15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="D17:G17"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="D19:G19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="D21:G21"/>
+    <mergeCell ref="D22:G22"/>
+    <mergeCell ref="A23:K23"/>
+    <mergeCell ref="D24:G24"/>
+    <mergeCell ref="D25:G25"/>
+    <mergeCell ref="A26:K26"/>
+    <mergeCell ref="D27:G27"/>
+    <mergeCell ref="D28:G28"/>
+    <mergeCell ref="D29:G29"/>
+    <mergeCell ref="A30:K30"/>
+    <mergeCell ref="D31:G31"/>
+    <mergeCell ref="D32:G32"/>
+    <mergeCell ref="D33:G33"/>
+    <mergeCell ref="D34:G34"/>
+    <mergeCell ref="D35:G35"/>
+    <mergeCell ref="D36:G36"/>
+    <mergeCell ref="D37:G37"/>
+    <mergeCell ref="D38:G38"/>
+    <mergeCell ref="D39:G39"/>
+    <mergeCell ref="D40:G40"/>
+    <mergeCell ref="D41:G41"/>
+    <mergeCell ref="D42:G42"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8134,31 +8462,31 @@
       <c r="A3" s="64" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="186" t="s">
+      <c r="B3" s="224" t="s">
         <v>62</v>
       </c>
-      <c r="C3" s="186"/>
-      <c r="D3" s="187"/>
+      <c r="C3" s="224"/>
+      <c r="D3" s="225"/>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="68" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="189" t="s">
+      <c r="B4" s="226" t="s">
         <v>166</v>
       </c>
-      <c r="C4" s="190"/>
-      <c r="D4" s="191"/>
+      <c r="C4" s="227"/>
+      <c r="D4" s="228"/>
     </row>
     <row r="5" spans="1:11" ht="25.5">
       <c r="A5" s="68" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="192" t="s">
+      <c r="B5" s="229" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="193"/>
-      <c r="D5" s="194"/>
+      <c r="C5" s="230"/>
+      <c r="D5" s="231"/>
     </row>
     <row r="6" spans="1:11" ht="14.25">
       <c r="A6" s="71" t="s">
@@ -8189,59 +8517,59 @@
       </c>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="202" t="s">
+      <c r="A9" s="212" t="s">
         <v>71</v>
       </c>
-      <c r="B9" s="204" t="s">
+      <c r="B9" s="214" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="202" t="s">
+      <c r="C9" s="212" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="208" t="s">
+      <c r="D9" s="218" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="209"/>
-      <c r="F9" s="209"/>
-      <c r="G9" s="210"/>
-      <c r="H9" s="206" t="s">
+      <c r="E9" s="219"/>
+      <c r="F9" s="219"/>
+      <c r="G9" s="220"/>
+      <c r="H9" s="216" t="s">
         <v>75</v>
       </c>
-      <c r="I9" s="207" t="s">
+      <c r="I9" s="217" t="s">
         <v>76</v>
       </c>
-      <c r="J9" s="207" t="s">
+      <c r="J9" s="217" t="s">
         <v>77</v>
       </c>
-      <c r="K9" s="207" t="s">
+      <c r="K9" s="217" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="203"/>
-      <c r="B10" s="205"/>
-      <c r="C10" s="203"/>
-      <c r="D10" s="211"/>
-      <c r="E10" s="212"/>
-      <c r="F10" s="212"/>
-      <c r="G10" s="213"/>
-      <c r="H10" s="202"/>
-      <c r="I10" s="202"/>
-      <c r="J10" s="202"/>
-      <c r="K10" s="202"/>
+      <c r="A10" s="213"/>
+      <c r="B10" s="215"/>
+      <c r="C10" s="213"/>
+      <c r="D10" s="221"/>
+      <c r="E10" s="222"/>
+      <c r="F10" s="222"/>
+      <c r="G10" s="223"/>
+      <c r="H10" s="212"/>
+      <c r="I10" s="212"/>
+      <c r="J10" s="212"/>
+      <c r="K10" s="212"/>
     </row>
     <row r="11" spans="1:11" ht="15">
-      <c r="A11" s="197"/>
-      <c r="B11" s="197"/>
-      <c r="C11" s="197"/>
-      <c r="D11" s="197"/>
-      <c r="E11" s="197"/>
-      <c r="F11" s="197"/>
-      <c r="G11" s="197"/>
-      <c r="H11" s="197"/>
-      <c r="I11" s="197"/>
-      <c r="J11" s="197"/>
-      <c r="K11" s="198"/>
+      <c r="A11" s="210"/>
+      <c r="B11" s="210"/>
+      <c r="C11" s="210"/>
+      <c r="D11" s="210"/>
+      <c r="E11" s="210"/>
+      <c r="F11" s="210"/>
+      <c r="G11" s="210"/>
+      <c r="H11" s="210"/>
+      <c r="I11" s="210"/>
+      <c r="J11" s="210"/>
+      <c r="K11" s="211"/>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="199" t="s">
@@ -8268,12 +8596,12 @@
       <c r="C13" s="86" t="s">
         <v>169</v>
       </c>
-      <c r="D13" s="214" t="s">
+      <c r="D13" s="202" t="s">
         <v>170</v>
       </c>
-      <c r="E13" s="215"/>
-      <c r="F13" s="215"/>
-      <c r="G13" s="216"/>
+      <c r="E13" s="191"/>
+      <c r="F13" s="191"/>
+      <c r="G13" s="192"/>
       <c r="H13" s="88"/>
       <c r="I13" s="90"/>
       <c r="J13" s="86" t="s">
@@ -8291,12 +8619,12 @@
       <c r="C14" s="86" t="s">
         <v>172</v>
       </c>
-      <c r="D14" s="214" t="s">
+      <c r="D14" s="202" t="s">
         <v>173</v>
       </c>
-      <c r="E14" s="215"/>
-      <c r="F14" s="215"/>
-      <c r="G14" s="216"/>
+      <c r="E14" s="191"/>
+      <c r="F14" s="191"/>
+      <c r="G14" s="192"/>
       <c r="H14" s="88"/>
       <c r="I14" s="90"/>
       <c r="J14" s="86" t="s">
@@ -8314,12 +8642,12 @@
       <c r="C15" s="86" t="s">
         <v>175</v>
       </c>
-      <c r="D15" s="214" t="s">
+      <c r="D15" s="202" t="s">
         <v>176</v>
       </c>
-      <c r="E15" s="215"/>
-      <c r="F15" s="215"/>
-      <c r="G15" s="216"/>
+      <c r="E15" s="191"/>
+      <c r="F15" s="191"/>
+      <c r="G15" s="192"/>
       <c r="H15" s="88"/>
       <c r="I15" s="90"/>
       <c r="J15" s="86" t="s">
@@ -8337,12 +8665,12 @@
       <c r="C16" s="86" t="s">
         <v>178</v>
       </c>
-      <c r="D16" s="214" t="s">
+      <c r="D16" s="202" t="s">
         <v>179</v>
       </c>
-      <c r="E16" s="215"/>
-      <c r="F16" s="215"/>
-      <c r="G16" s="216"/>
+      <c r="E16" s="191"/>
+      <c r="F16" s="191"/>
+      <c r="G16" s="192"/>
       <c r="H16" s="88"/>
       <c r="I16" s="90"/>
       <c r="J16" s="86" t="s">
@@ -8360,12 +8688,12 @@
       <c r="C17" s="86" t="s">
         <v>181</v>
       </c>
-      <c r="D17" s="214" t="s">
+      <c r="D17" s="202" t="s">
         <v>182</v>
       </c>
-      <c r="E17" s="215"/>
-      <c r="F17" s="215"/>
-      <c r="G17" s="216"/>
+      <c r="E17" s="191"/>
+      <c r="F17" s="191"/>
+      <c r="G17" s="192"/>
       <c r="H17" s="88"/>
       <c r="I17" s="90"/>
       <c r="J17" s="86" t="s">
@@ -8383,12 +8711,12 @@
       <c r="C18" s="86" t="s">
         <v>184</v>
       </c>
-      <c r="D18" s="214" t="s">
+      <c r="D18" s="202" t="s">
         <v>185</v>
       </c>
-      <c r="E18" s="215"/>
-      <c r="F18" s="215"/>
-      <c r="G18" s="216"/>
+      <c r="E18" s="191"/>
+      <c r="F18" s="191"/>
+      <c r="G18" s="192"/>
       <c r="H18" s="88"/>
       <c r="I18" s="90"/>
       <c r="J18" s="86" t="s">
@@ -8406,12 +8734,12 @@
       <c r="C19" s="86" t="s">
         <v>187</v>
       </c>
-      <c r="D19" s="214" t="s">
+      <c r="D19" s="202" t="s">
         <v>188</v>
       </c>
-      <c r="E19" s="215"/>
-      <c r="F19" s="215"/>
-      <c r="G19" s="216"/>
+      <c r="E19" s="191"/>
+      <c r="F19" s="191"/>
+      <c r="G19" s="192"/>
       <c r="H19" s="88"/>
       <c r="I19" s="90"/>
       <c r="J19" s="86" t="s">
@@ -8444,12 +8772,12 @@
       <c r="C21" s="86" t="s">
         <v>191</v>
       </c>
-      <c r="D21" s="214" t="s">
+      <c r="D21" s="202" t="s">
         <v>192</v>
       </c>
-      <c r="E21" s="215"/>
-      <c r="F21" s="215"/>
-      <c r="G21" s="216"/>
+      <c r="E21" s="191"/>
+      <c r="F21" s="191"/>
+      <c r="G21" s="192"/>
       <c r="H21" s="88"/>
       <c r="I21" s="90"/>
       <c r="J21" s="86" t="s">
@@ -8467,12 +8795,12 @@
       <c r="C22" s="86" t="s">
         <v>194</v>
       </c>
-      <c r="D22" s="214" t="s">
+      <c r="D22" s="202" t="s">
         <v>195</v>
       </c>
-      <c r="E22" s="215"/>
-      <c r="F22" s="215"/>
-      <c r="G22" s="216"/>
+      <c r="E22" s="191"/>
+      <c r="F22" s="191"/>
+      <c r="G22" s="192"/>
       <c r="H22" s="88"/>
       <c r="I22" s="90"/>
       <c r="J22" s="86" t="s">
@@ -8490,12 +8818,12 @@
       <c r="C23" s="86" t="s">
         <v>197</v>
       </c>
-      <c r="D23" s="214" t="s">
+      <c r="D23" s="202" t="s">
         <v>198</v>
       </c>
-      <c r="E23" s="215"/>
-      <c r="F23" s="215"/>
-      <c r="G23" s="216"/>
+      <c r="E23" s="191"/>
+      <c r="F23" s="191"/>
+      <c r="G23" s="192"/>
       <c r="H23" s="88"/>
       <c r="I23" s="90"/>
       <c r="J23" s="86" t="s">
@@ -8557,21 +8885,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="D23:G23"/>
-    <mergeCell ref="A24:K24"/>
-    <mergeCell ref="D25:G25"/>
-    <mergeCell ref="D26:G26"/>
-    <mergeCell ref="D27:G27"/>
-    <mergeCell ref="D18:G18"/>
-    <mergeCell ref="D19:G19"/>
-    <mergeCell ref="A20:K20"/>
-    <mergeCell ref="D21:G21"/>
-    <mergeCell ref="D22:G22"/>
-    <mergeCell ref="D13:G13"/>
-    <mergeCell ref="D14:G14"/>
-    <mergeCell ref="D15:G15"/>
-    <mergeCell ref="D16:G16"/>
-    <mergeCell ref="D17:G17"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B5:D5"/>
@@ -8585,6 +8898,21 @@
     <mergeCell ref="J9:J10"/>
     <mergeCell ref="K9:K10"/>
     <mergeCell ref="D9:G10"/>
+    <mergeCell ref="D13:G13"/>
+    <mergeCell ref="D14:G14"/>
+    <mergeCell ref="D15:G15"/>
+    <mergeCell ref="D16:G16"/>
+    <mergeCell ref="D17:G17"/>
+    <mergeCell ref="D18:G18"/>
+    <mergeCell ref="D19:G19"/>
+    <mergeCell ref="A20:K20"/>
+    <mergeCell ref="D21:G21"/>
+    <mergeCell ref="D22:G22"/>
+    <mergeCell ref="D23:G23"/>
+    <mergeCell ref="A24:K24"/>
+    <mergeCell ref="D25:G25"/>
+    <mergeCell ref="D26:G26"/>
+    <mergeCell ref="D27:G27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8621,31 +8949,31 @@
       <c r="A3" s="64" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="186" t="s">
+      <c r="B3" s="224" t="s">
         <v>62</v>
       </c>
-      <c r="C3" s="186"/>
-      <c r="D3" s="187"/>
+      <c r="C3" s="224"/>
+      <c r="D3" s="225"/>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="68" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="189" t="s">
+      <c r="B4" s="226" t="s">
         <v>200</v>
       </c>
-      <c r="C4" s="190"/>
-      <c r="D4" s="191"/>
+      <c r="C4" s="227"/>
+      <c r="D4" s="228"/>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="68" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="192" t="s">
+      <c r="B5" s="229" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="193"/>
-      <c r="D5" s="194"/>
+      <c r="C5" s="230"/>
+      <c r="D5" s="231"/>
     </row>
     <row r="6" spans="1:11" ht="14.25">
       <c r="A6" s="71" t="s">
@@ -8676,59 +9004,59 @@
       </c>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="202" t="s">
+      <c r="A9" s="212" t="s">
         <v>71</v>
       </c>
-      <c r="B9" s="204" t="s">
+      <c r="B9" s="214" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="202" t="s">
+      <c r="C9" s="212" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="208" t="s">
+      <c r="D9" s="218" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="209"/>
-      <c r="F9" s="209"/>
-      <c r="G9" s="210"/>
-      <c r="H9" s="206" t="s">
+      <c r="E9" s="219"/>
+      <c r="F9" s="219"/>
+      <c r="G9" s="220"/>
+      <c r="H9" s="216" t="s">
         <v>75</v>
       </c>
-      <c r="I9" s="207" t="s">
+      <c r="I9" s="217" t="s">
         <v>76</v>
       </c>
-      <c r="J9" s="207" t="s">
+      <c r="J9" s="217" t="s">
         <v>77</v>
       </c>
-      <c r="K9" s="207" t="s">
+      <c r="K9" s="217" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="203"/>
-      <c r="B10" s="205"/>
-      <c r="C10" s="203"/>
-      <c r="D10" s="211"/>
-      <c r="E10" s="212"/>
-      <c r="F10" s="212"/>
-      <c r="G10" s="213"/>
-      <c r="H10" s="202"/>
-      <c r="I10" s="202"/>
-      <c r="J10" s="202"/>
-      <c r="K10" s="202"/>
+      <c r="A10" s="213"/>
+      <c r="B10" s="215"/>
+      <c r="C10" s="213"/>
+      <c r="D10" s="221"/>
+      <c r="E10" s="222"/>
+      <c r="F10" s="222"/>
+      <c r="G10" s="223"/>
+      <c r="H10" s="212"/>
+      <c r="I10" s="212"/>
+      <c r="J10" s="212"/>
+      <c r="K10" s="212"/>
     </row>
     <row r="11" spans="1:11" ht="15">
-      <c r="A11" s="197"/>
-      <c r="B11" s="197"/>
-      <c r="C11" s="197"/>
-      <c r="D11" s="197"/>
-      <c r="E11" s="197"/>
-      <c r="F11" s="197"/>
-      <c r="G11" s="197"/>
-      <c r="H11" s="197"/>
-      <c r="I11" s="197"/>
-      <c r="J11" s="197"/>
-      <c r="K11" s="198"/>
+      <c r="A11" s="210"/>
+      <c r="B11" s="210"/>
+      <c r="C11" s="210"/>
+      <c r="D11" s="210"/>
+      <c r="E11" s="210"/>
+      <c r="F11" s="210"/>
+      <c r="G11" s="210"/>
+      <c r="H11" s="210"/>
+      <c r="I11" s="210"/>
+      <c r="J11" s="210"/>
+      <c r="K11" s="211"/>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="199" t="s">
@@ -8755,12 +9083,12 @@
       <c r="C13" s="86" t="s">
         <v>203</v>
       </c>
-      <c r="D13" s="214" t="s">
+      <c r="D13" s="202" t="s">
         <v>204</v>
       </c>
-      <c r="E13" s="215"/>
-      <c r="F13" s="215"/>
-      <c r="G13" s="216"/>
+      <c r="E13" s="191"/>
+      <c r="F13" s="191"/>
+      <c r="G13" s="192"/>
       <c r="H13" s="88"/>
       <c r="I13" s="90"/>
       <c r="J13" s="86" t="s">
@@ -8778,12 +9106,12 @@
       <c r="C14" s="86" t="s">
         <v>206</v>
       </c>
-      <c r="D14" s="214" t="s">
+      <c r="D14" s="202" t="s">
         <v>207</v>
       </c>
-      <c r="E14" s="215"/>
-      <c r="F14" s="215"/>
-      <c r="G14" s="216"/>
+      <c r="E14" s="191"/>
+      <c r="F14" s="191"/>
+      <c r="G14" s="192"/>
       <c r="H14" s="88"/>
       <c r="I14" s="90"/>
       <c r="J14" s="86" t="s">
@@ -8801,12 +9129,12 @@
       <c r="C15" s="86" t="s">
         <v>209</v>
       </c>
-      <c r="D15" s="214" t="s">
+      <c r="D15" s="202" t="s">
         <v>210</v>
       </c>
-      <c r="E15" s="215"/>
-      <c r="F15" s="215"/>
-      <c r="G15" s="216"/>
+      <c r="E15" s="191"/>
+      <c r="F15" s="191"/>
+      <c r="G15" s="192"/>
       <c r="H15" s="88"/>
       <c r="I15" s="90"/>
       <c r="J15" s="86" t="s">
@@ -8824,12 +9152,12 @@
       <c r="C16" s="86" t="s">
         <v>212</v>
       </c>
-      <c r="D16" s="214" t="s">
+      <c r="D16" s="202" t="s">
         <v>213</v>
       </c>
-      <c r="E16" s="215"/>
-      <c r="F16" s="215"/>
-      <c r="G16" s="216"/>
+      <c r="E16" s="191"/>
+      <c r="F16" s="191"/>
+      <c r="G16" s="192"/>
       <c r="H16" s="88"/>
       <c r="I16" s="90"/>
       <c r="J16" s="86" t="s">
@@ -8847,12 +9175,12 @@
       <c r="C17" s="86" t="s">
         <v>215</v>
       </c>
-      <c r="D17" s="214" t="s">
+      <c r="D17" s="202" t="s">
         <v>216</v>
       </c>
-      <c r="E17" s="215"/>
-      <c r="F17" s="215"/>
-      <c r="G17" s="216"/>
+      <c r="E17" s="191"/>
+      <c r="F17" s="191"/>
+      <c r="G17" s="192"/>
       <c r="H17" s="88"/>
       <c r="I17" s="90"/>
       <c r="J17" s="86" t="s">
@@ -8870,12 +9198,12 @@
       <c r="C18" s="86" t="s">
         <v>218</v>
       </c>
-      <c r="D18" s="214" t="s">
+      <c r="D18" s="202" t="s">
         <v>219</v>
       </c>
-      <c r="E18" s="215"/>
-      <c r="F18" s="215"/>
-      <c r="G18" s="216"/>
+      <c r="E18" s="191"/>
+      <c r="F18" s="191"/>
+      <c r="G18" s="192"/>
       <c r="H18" s="88"/>
       <c r="I18" s="90"/>
       <c r="J18" s="86" t="s">
@@ -8885,6 +9213,14 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="A11:K11"/>
+    <mergeCell ref="A12:K12"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="K9:K10"/>
     <mergeCell ref="D18:G18"/>
     <mergeCell ref="A9:A10"/>
     <mergeCell ref="B9:B10"/>
@@ -8896,14 +9232,6 @@
     <mergeCell ref="D15:G15"/>
     <mergeCell ref="D16:G16"/>
     <mergeCell ref="D17:G17"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="A11:K11"/>
-    <mergeCell ref="A12:K12"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="K9:K10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8955,52 +9283,52 @@
       <c r="A3" s="100" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="186" t="s">
+      <c r="B3" s="224" t="s">
         <v>62</v>
       </c>
-      <c r="C3" s="186"/>
-      <c r="D3" s="187"/>
+      <c r="C3" s="224"/>
+      <c r="D3" s="225"/>
       <c r="E3" s="65"/>
       <c r="F3" s="65"/>
       <c r="G3" s="65"/>
       <c r="H3" s="65"/>
-      <c r="I3" s="188"/>
-      <c r="J3" s="188"/>
-      <c r="K3" s="188"/>
+      <c r="I3" s="208"/>
+      <c r="J3" s="208"/>
+      <c r="K3" s="208"/>
     </row>
     <row r="4" spans="1:11" ht="14.25">
       <c r="A4" s="68" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="189" t="s">
+      <c r="B4" s="226" t="s">
         <v>221</v>
       </c>
-      <c r="C4" s="190"/>
-      <c r="D4" s="191"/>
+      <c r="C4" s="227"/>
+      <c r="D4" s="228"/>
       <c r="E4" s="65"/>
       <c r="F4" s="65"/>
       <c r="G4" s="65"/>
       <c r="H4" s="65"/>
-      <c r="I4" s="188"/>
-      <c r="J4" s="188"/>
-      <c r="K4" s="188"/>
+      <c r="I4" s="208"/>
+      <c r="J4" s="208"/>
+      <c r="K4" s="208"/>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="101" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="192" t="s">
+      <c r="B5" s="229" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="193"/>
-      <c r="D5" s="194"/>
+      <c r="C5" s="230"/>
+      <c r="D5" s="231"/>
       <c r="E5" s="69"/>
       <c r="F5" s="69"/>
       <c r="G5" s="69"/>
       <c r="H5" s="69"/>
-      <c r="I5" s="195"/>
-      <c r="J5" s="195"/>
-      <c r="K5" s="195"/>
+      <c r="I5" s="232"/>
+      <c r="J5" s="232"/>
+      <c r="K5" s="232"/>
     </row>
     <row r="6" spans="1:11" ht="14.25">
       <c r="A6" s="71" t="s">
@@ -9021,9 +9349,9 @@
       <c r="F6" s="66"/>
       <c r="G6" s="66"/>
       <c r="H6" s="66"/>
-      <c r="I6" s="188"/>
-      <c r="J6" s="188"/>
-      <c r="K6" s="188"/>
+      <c r="I6" s="208"/>
+      <c r="J6" s="208"/>
+      <c r="K6" s="208"/>
     </row>
     <row r="7" spans="1:11" ht="14.25">
       <c r="A7" s="75" t="s">
@@ -9044,15 +9372,15 @@
       <c r="F7" s="79"/>
       <c r="G7" s="79"/>
       <c r="H7" s="79"/>
-      <c r="I7" s="188"/>
-      <c r="J7" s="188"/>
-      <c r="K7" s="188"/>
+      <c r="I7" s="208"/>
+      <c r="J7" s="208"/>
+      <c r="K7" s="208"/>
     </row>
     <row r="8" spans="1:11" ht="14.25">
-      <c r="A8" s="196"/>
-      <c r="B8" s="196"/>
-      <c r="C8" s="196"/>
-      <c r="D8" s="196"/>
+      <c r="A8" s="209"/>
+      <c r="B8" s="209"/>
+      <c r="C8" s="209"/>
+      <c r="D8" s="209"/>
       <c r="E8" s="66"/>
       <c r="F8" s="66"/>
       <c r="G8" s="66"/>
@@ -9062,59 +9390,59 @@
       <c r="K8" s="80"/>
     </row>
     <row r="9" spans="1:11" ht="13.5" customHeight="1">
-      <c r="A9" s="202" t="s">
+      <c r="A9" s="212" t="s">
         <v>71</v>
       </c>
-      <c r="B9" s="204" t="s">
+      <c r="B9" s="214" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="202" t="s">
+      <c r="C9" s="212" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="208" t="s">
+      <c r="D9" s="218" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="209"/>
-      <c r="F9" s="209"/>
-      <c r="G9" s="210"/>
-      <c r="H9" s="206" t="s">
+      <c r="E9" s="219"/>
+      <c r="F9" s="219"/>
+      <c r="G9" s="220"/>
+      <c r="H9" s="216" t="s">
         <v>75</v>
       </c>
-      <c r="I9" s="207" t="s">
+      <c r="I9" s="217" t="s">
         <v>76</v>
       </c>
-      <c r="J9" s="207" t="s">
+      <c r="J9" s="217" t="s">
         <v>77</v>
       </c>
-      <c r="K9" s="207" t="s">
+      <c r="K9" s="217" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="203"/>
-      <c r="B10" s="205"/>
-      <c r="C10" s="203"/>
-      <c r="D10" s="211"/>
-      <c r="E10" s="212"/>
-      <c r="F10" s="212"/>
-      <c r="G10" s="213"/>
-      <c r="H10" s="202"/>
-      <c r="I10" s="202"/>
-      <c r="J10" s="202"/>
-      <c r="K10" s="202"/>
+      <c r="A10" s="213"/>
+      <c r="B10" s="215"/>
+      <c r="C10" s="213"/>
+      <c r="D10" s="221"/>
+      <c r="E10" s="222"/>
+      <c r="F10" s="222"/>
+      <c r="G10" s="223"/>
+      <c r="H10" s="212"/>
+      <c r="I10" s="212"/>
+      <c r="J10" s="212"/>
+      <c r="K10" s="212"/>
     </row>
     <row r="11" spans="1:11" ht="15">
-      <c r="A11" s="197"/>
-      <c r="B11" s="197"/>
-      <c r="C11" s="197"/>
-      <c r="D11" s="197"/>
-      <c r="E11" s="197"/>
-      <c r="F11" s="197"/>
-      <c r="G11" s="197"/>
-      <c r="H11" s="197"/>
-      <c r="I11" s="197"/>
-      <c r="J11" s="197"/>
-      <c r="K11" s="198"/>
+      <c r="A11" s="210"/>
+      <c r="B11" s="210"/>
+      <c r="C11" s="210"/>
+      <c r="D11" s="210"/>
+      <c r="E11" s="210"/>
+      <c r="F11" s="210"/>
+      <c r="G11" s="210"/>
+      <c r="H11" s="210"/>
+      <c r="I11" s="210"/>
+      <c r="J11" s="210"/>
+      <c r="K11" s="211"/>
     </row>
     <row r="12" spans="1:11" ht="16.5" customHeight="1">
       <c r="A12" s="199" t="s">
@@ -9164,11 +9492,11 @@
       <c r="C14" s="86" t="s">
         <v>227</v>
       </c>
-      <c r="D14" s="222" t="s">
+      <c r="D14" s="190" t="s">
         <v>228</v>
       </c>
-      <c r="E14" s="215"/>
-      <c r="F14" s="215"/>
+      <c r="E14" s="191"/>
+      <c r="F14" s="191"/>
       <c r="G14" s="118"/>
       <c r="H14" s="88"/>
       <c r="I14" s="90"/>
@@ -9187,11 +9515,11 @@
       <c r="C15" s="87" t="s">
         <v>230</v>
       </c>
-      <c r="D15" s="222" t="s">
+      <c r="D15" s="190" t="s">
         <v>231</v>
       </c>
-      <c r="E15" s="215"/>
-      <c r="F15" s="215"/>
+      <c r="E15" s="191"/>
+      <c r="F15" s="191"/>
       <c r="G15" s="89"/>
       <c r="H15" s="89"/>
       <c r="I15" s="119"/>
@@ -9248,11 +9576,11 @@
       <c r="C18" s="87" t="s">
         <v>237</v>
       </c>
-      <c r="D18" s="222" t="s">
+      <c r="D18" s="190" t="s">
         <v>238</v>
       </c>
-      <c r="E18" s="215"/>
-      <c r="F18" s="215"/>
+      <c r="E18" s="191"/>
+      <c r="F18" s="191"/>
       <c r="G18" s="89"/>
       <c r="H18" s="89"/>
       <c r="I18" s="86"/>
@@ -9271,11 +9599,11 @@
       <c r="C19" s="87" t="s">
         <v>240</v>
       </c>
-      <c r="D19" s="222" t="s">
+      <c r="D19" s="190" t="s">
         <v>238</v>
       </c>
-      <c r="E19" s="215"/>
-      <c r="F19" s="215"/>
+      <c r="E19" s="191"/>
+      <c r="F19" s="191"/>
       <c r="G19" s="89"/>
       <c r="H19" s="89"/>
       <c r="I19" s="86"/>
@@ -9309,11 +9637,11 @@
       <c r="C21" s="92" t="s">
         <v>243</v>
       </c>
-      <c r="D21" s="222" t="s">
+      <c r="D21" s="190" t="s">
         <v>244</v>
       </c>
-      <c r="E21" s="215"/>
-      <c r="F21" s="215"/>
+      <c r="E21" s="191"/>
+      <c r="F21" s="191"/>
       <c r="G21" s="89"/>
       <c r="H21" s="88"/>
       <c r="I21" s="87"/>
@@ -9332,11 +9660,11 @@
       <c r="C22" s="86" t="s">
         <v>246</v>
       </c>
-      <c r="D22" s="222" t="s">
+      <c r="D22" s="190" t="s">
         <v>247</v>
       </c>
-      <c r="E22" s="215"/>
-      <c r="F22" s="215"/>
+      <c r="E22" s="191"/>
+      <c r="F22" s="191"/>
       <c r="G22" s="89"/>
       <c r="H22" s="86"/>
       <c r="I22" s="86"/>
@@ -9416,11 +9744,11 @@
       <c r="C26" s="86" t="s">
         <v>255</v>
       </c>
-      <c r="D26" s="227" t="s">
+      <c r="D26" s="189" t="s">
         <v>256</v>
       </c>
-      <c r="E26" s="227"/>
-      <c r="F26" s="222"/>
+      <c r="E26" s="189"/>
+      <c r="F26" s="190"/>
       <c r="G26" s="89"/>
       <c r="H26" s="89"/>
       <c r="I26" s="86"/>
@@ -9439,11 +9767,11 @@
       <c r="C27" s="86" t="s">
         <v>258</v>
       </c>
-      <c r="D27" s="227" t="s">
+      <c r="D27" s="189" t="s">
         <v>259</v>
       </c>
-      <c r="E27" s="227"/>
-      <c r="F27" s="222"/>
+      <c r="E27" s="189"/>
+      <c r="F27" s="190"/>
       <c r="G27" s="89"/>
       <c r="H27" s="86"/>
       <c r="I27" s="86"/>
@@ -9479,6 +9807,25 @@
     </row>
   </sheetData>
   <mergeCells count="35">
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A11:K11"/>
+    <mergeCell ref="A12:K12"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="K9:K10"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="D17:F17"/>
     <mergeCell ref="D27:F27"/>
     <mergeCell ref="A9:A10"/>
     <mergeCell ref="B9:B10"/>
@@ -9495,25 +9842,6 @@
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="D21:F21"/>
     <mergeCell ref="D22:F22"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A11:K11"/>
-    <mergeCell ref="A12:K12"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="K9:K10"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="I5:K5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -9572,54 +9900,54 @@
       <c r="A3" s="100" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="186" t="s">
+      <c r="B3" s="224" t="s">
         <v>62</v>
       </c>
-      <c r="C3" s="186"/>
-      <c r="D3" s="187"/>
+      <c r="C3" s="224"/>
+      <c r="D3" s="225"/>
       <c r="E3" s="65"/>
       <c r="F3" s="65"/>
       <c r="G3" s="65"/>
       <c r="H3" s="65"/>
-      <c r="I3" s="188"/>
-      <c r="J3" s="188"/>
-      <c r="K3" s="188"/>
+      <c r="I3" s="208"/>
+      <c r="J3" s="208"/>
+      <c r="K3" s="208"/>
       <c r="L3" s="67"/>
     </row>
     <row r="4" spans="1:12" s="55" customFormat="1" ht="13.15" customHeight="1">
       <c r="A4" s="68" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="189" t="s">
+      <c r="B4" s="226" t="s">
         <v>260</v>
       </c>
-      <c r="C4" s="190"/>
-      <c r="D4" s="191"/>
+      <c r="C4" s="227"/>
+      <c r="D4" s="228"/>
       <c r="E4" s="65"/>
       <c r="F4" s="65"/>
       <c r="G4" s="65"/>
       <c r="H4" s="65"/>
-      <c r="I4" s="188"/>
-      <c r="J4" s="188"/>
-      <c r="K4" s="188"/>
+      <c r="I4" s="208"/>
+      <c r="J4" s="208"/>
+      <c r="K4" s="208"/>
       <c r="L4" s="67"/>
     </row>
     <row r="5" spans="1:12" s="56" customFormat="1" ht="12.75">
       <c r="A5" s="101" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="192" t="s">
+      <c r="B5" s="229" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="193"/>
-      <c r="D5" s="194"/>
+      <c r="C5" s="230"/>
+      <c r="D5" s="231"/>
       <c r="E5" s="69"/>
       <c r="F5" s="69"/>
       <c r="G5" s="69"/>
       <c r="H5" s="69"/>
-      <c r="I5" s="195"/>
-      <c r="J5" s="195"/>
-      <c r="K5" s="195"/>
+      <c r="I5" s="232"/>
+      <c r="J5" s="232"/>
+      <c r="K5" s="232"/>
       <c r="L5" s="70"/>
     </row>
     <row r="6" spans="1:12" s="55" customFormat="1" ht="15" customHeight="1">
@@ -9641,9 +9969,9 @@
       <c r="F6" s="66"/>
       <c r="G6" s="66"/>
       <c r="H6" s="66"/>
-      <c r="I6" s="188"/>
-      <c r="J6" s="188"/>
-      <c r="K6" s="188"/>
+      <c r="I6" s="208"/>
+      <c r="J6" s="208"/>
+      <c r="K6" s="208"/>
       <c r="L6" s="67"/>
     </row>
     <row r="7" spans="1:12" s="55" customFormat="1" ht="15" customHeight="1">
@@ -9665,16 +9993,16 @@
       <c r="F7" s="79"/>
       <c r="G7" s="79"/>
       <c r="H7" s="79"/>
-      <c r="I7" s="188"/>
-      <c r="J7" s="188"/>
-      <c r="K7" s="188"/>
+      <c r="I7" s="208"/>
+      <c r="J7" s="208"/>
+      <c r="K7" s="208"/>
       <c r="L7" s="67"/>
     </row>
     <row r="8" spans="1:12" s="55" customFormat="1" ht="15" customHeight="1">
-      <c r="A8" s="196"/>
-      <c r="B8" s="196"/>
-      <c r="C8" s="196"/>
-      <c r="D8" s="196"/>
+      <c r="A8" s="209"/>
+      <c r="B8" s="209"/>
+      <c r="C8" s="209"/>
+      <c r="D8" s="209"/>
       <c r="E8" s="66"/>
       <c r="F8" s="66"/>
       <c r="G8" s="66"/>
@@ -9685,76 +10013,76 @@
       <c r="L8" s="67"/>
     </row>
     <row r="9" spans="1:12" s="57" customFormat="1" ht="12" customHeight="1">
-      <c r="A9" s="202" t="s">
+      <c r="A9" s="212" t="s">
         <v>71</v>
       </c>
-      <c r="B9" s="204" t="s">
+      <c r="B9" s="214" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="202" t="s">
+      <c r="C9" s="212" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="208" t="s">
+      <c r="D9" s="218" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="209"/>
-      <c r="F9" s="209"/>
-      <c r="G9" s="210"/>
-      <c r="H9" s="206" t="s">
+      <c r="E9" s="219"/>
+      <c r="F9" s="219"/>
+      <c r="G9" s="220"/>
+      <c r="H9" s="216" t="s">
         <v>75</v>
       </c>
-      <c r="I9" s="207" t="s">
+      <c r="I9" s="217" t="s">
         <v>76</v>
       </c>
-      <c r="J9" s="207" t="s">
+      <c r="J9" s="217" t="s">
         <v>77</v>
       </c>
-      <c r="K9" s="207" t="s">
+      <c r="K9" s="217" t="s">
         <v>78</v>
       </c>
       <c r="L9" s="81"/>
     </row>
     <row r="10" spans="1:12" s="55" customFormat="1" ht="12" customHeight="1">
-      <c r="A10" s="203"/>
-      <c r="B10" s="205"/>
-      <c r="C10" s="203"/>
-      <c r="D10" s="211"/>
-      <c r="E10" s="212"/>
-      <c r="F10" s="212"/>
-      <c r="G10" s="213"/>
-      <c r="H10" s="202"/>
-      <c r="I10" s="202"/>
-      <c r="J10" s="202"/>
-      <c r="K10" s="202"/>
+      <c r="A10" s="213"/>
+      <c r="B10" s="215"/>
+      <c r="C10" s="213"/>
+      <c r="D10" s="221"/>
+      <c r="E10" s="222"/>
+      <c r="F10" s="222"/>
+      <c r="G10" s="223"/>
+      <c r="H10" s="212"/>
+      <c r="I10" s="212"/>
+      <c r="J10" s="212"/>
+      <c r="K10" s="212"/>
       <c r="L10" s="67"/>
     </row>
     <row r="11" spans="1:12" s="58" customFormat="1" ht="15">
-      <c r="A11" s="197"/>
-      <c r="B11" s="197"/>
-      <c r="C11" s="197"/>
-      <c r="D11" s="197"/>
-      <c r="E11" s="197"/>
-      <c r="F11" s="197"/>
-      <c r="G11" s="197"/>
-      <c r="H11" s="197"/>
-      <c r="I11" s="197"/>
-      <c r="J11" s="197"/>
-      <c r="K11" s="198"/>
+      <c r="A11" s="210"/>
+      <c r="B11" s="210"/>
+      <c r="C11" s="210"/>
+      <c r="D11" s="210"/>
+      <c r="E11" s="210"/>
+      <c r="F11" s="210"/>
+      <c r="G11" s="210"/>
+      <c r="H11" s="210"/>
+      <c r="I11" s="210"/>
+      <c r="J11" s="210"/>
+      <c r="K11" s="211"/>
     </row>
     <row r="12" spans="1:12" s="59" customFormat="1" ht="24.6" customHeight="1">
-      <c r="A12" s="239" t="s">
+      <c r="A12" s="242" t="s">
         <v>261</v>
       </c>
-      <c r="B12" s="240"/>
-      <c r="C12" s="240"/>
-      <c r="D12" s="240"/>
-      <c r="E12" s="240"/>
-      <c r="F12" s="240"/>
-      <c r="G12" s="240"/>
-      <c r="H12" s="240"/>
-      <c r="I12" s="240"/>
-      <c r="J12" s="240"/>
-      <c r="K12" s="241"/>
+      <c r="B12" s="243"/>
+      <c r="C12" s="243"/>
+      <c r="D12" s="243"/>
+      <c r="E12" s="243"/>
+      <c r="F12" s="243"/>
+      <c r="G12" s="243"/>
+      <c r="H12" s="243"/>
+      <c r="I12" s="243"/>
+      <c r="J12" s="243"/>
+      <c r="K12" s="244"/>
     </row>
     <row r="13" spans="1:12" s="59" customFormat="1" ht="81.599999999999994" customHeight="1" outlineLevel="1">
       <c r="A13" s="102" t="s">
@@ -9766,11 +10094,11 @@
       <c r="C13" s="103" t="s">
         <v>263</v>
       </c>
-      <c r="D13" s="222" t="s">
+      <c r="D13" s="190" t="s">
         <v>264</v>
       </c>
-      <c r="E13" s="215"/>
-      <c r="F13" s="215"/>
+      <c r="E13" s="191"/>
+      <c r="F13" s="191"/>
       <c r="G13" s="89"/>
       <c r="H13" s="88"/>
       <c r="I13" s="90"/>
@@ -9787,11 +10115,11 @@
       <c r="C14" s="105" t="s">
         <v>266</v>
       </c>
-      <c r="D14" s="222" t="s">
+      <c r="D14" s="190" t="s">
         <v>267</v>
       </c>
-      <c r="E14" s="215"/>
-      <c r="F14" s="215"/>
+      <c r="E14" s="191"/>
+      <c r="F14" s="191"/>
       <c r="G14" s="89"/>
       <c r="H14" s="88"/>
       <c r="I14" s="87"/>
@@ -9808,11 +10136,11 @@
       <c r="C15" s="103" t="s">
         <v>269</v>
       </c>
-      <c r="D15" s="222" t="s">
+      <c r="D15" s="190" t="s">
         <v>270</v>
       </c>
-      <c r="E15" s="215"/>
-      <c r="F15" s="215"/>
+      <c r="E15" s="191"/>
+      <c r="F15" s="191"/>
       <c r="G15" s="89"/>
       <c r="H15" s="88"/>
       <c r="I15" s="87"/>
@@ -9829,11 +10157,11 @@
       <c r="C16" s="105" t="s">
         <v>272</v>
       </c>
-      <c r="D16" s="222" t="s">
+      <c r="D16" s="190" t="s">
         <v>273</v>
       </c>
-      <c r="E16" s="215"/>
-      <c r="F16" s="215"/>
+      <c r="E16" s="191"/>
+      <c r="F16" s="191"/>
       <c r="G16" s="89"/>
       <c r="H16" s="88"/>
       <c r="I16" s="87"/>
@@ -9850,11 +10178,11 @@
       <c r="C17" s="103" t="s">
         <v>275</v>
       </c>
-      <c r="D17" s="222" t="s">
+      <c r="D17" s="190" t="s">
         <v>276</v>
       </c>
-      <c r="E17" s="215"/>
-      <c r="F17" s="215"/>
+      <c r="E17" s="191"/>
+      <c r="F17" s="191"/>
       <c r="G17" s="89"/>
       <c r="H17" s="88"/>
       <c r="I17" s="87"/>
@@ -9871,11 +10199,11 @@
       <c r="C18" s="105" t="s">
         <v>278</v>
       </c>
-      <c r="D18" s="222" t="s">
+      <c r="D18" s="190" t="s">
         <v>279</v>
       </c>
-      <c r="E18" s="215"/>
-      <c r="F18" s="215"/>
+      <c r="E18" s="191"/>
+      <c r="F18" s="191"/>
       <c r="G18" s="89"/>
       <c r="H18" s="88"/>
       <c r="I18" s="90"/>
@@ -9892,11 +10220,11 @@
       <c r="C19" s="103" t="s">
         <v>281</v>
       </c>
-      <c r="D19" s="222" t="s">
+      <c r="D19" s="190" t="s">
         <v>282</v>
       </c>
-      <c r="E19" s="215"/>
-      <c r="F19" s="215"/>
+      <c r="E19" s="191"/>
+      <c r="F19" s="191"/>
       <c r="G19" s="89"/>
       <c r="H19" s="88"/>
       <c r="I19" s="87"/>
@@ -9913,11 +10241,11 @@
       <c r="C20" s="105" t="s">
         <v>284</v>
       </c>
-      <c r="D20" s="222" t="s">
+      <c r="D20" s="190" t="s">
         <v>285</v>
       </c>
-      <c r="E20" s="215"/>
-      <c r="F20" s="215"/>
+      <c r="E20" s="191"/>
+      <c r="F20" s="191"/>
       <c r="G20" s="89"/>
       <c r="H20" s="88"/>
       <c r="I20" s="87"/>
@@ -9934,11 +10262,11 @@
       <c r="C21" s="103" t="s">
         <v>287</v>
       </c>
-      <c r="D21" s="222" t="s">
+      <c r="D21" s="190" t="s">
         <v>288</v>
       </c>
-      <c r="E21" s="215"/>
-      <c r="F21" s="215"/>
+      <c r="E21" s="191"/>
+      <c r="F21" s="191"/>
       <c r="G21" s="89"/>
       <c r="H21" s="88"/>
       <c r="I21" s="87"/>
@@ -9955,11 +10283,11 @@
       <c r="C22" s="105" t="s">
         <v>290</v>
       </c>
-      <c r="D22" s="222" t="s">
+      <c r="D22" s="190" t="s">
         <v>291</v>
       </c>
-      <c r="E22" s="215"/>
-      <c r="F22" s="215"/>
+      <c r="E22" s="191"/>
+      <c r="F22" s="191"/>
       <c r="G22" s="89"/>
       <c r="H22" s="88"/>
       <c r="I22" s="87"/>
@@ -9976,11 +10304,11 @@
       <c r="C23" s="103" t="s">
         <v>293</v>
       </c>
-      <c r="D23" s="222" t="s">
+      <c r="D23" s="190" t="s">
         <v>294</v>
       </c>
-      <c r="E23" s="215"/>
-      <c r="F23" s="215"/>
+      <c r="E23" s="191"/>
+      <c r="F23" s="191"/>
       <c r="G23" s="89"/>
       <c r="H23" s="88"/>
       <c r="I23" s="90"/>
@@ -9997,11 +10325,11 @@
       <c r="C24" s="105" t="s">
         <v>296</v>
       </c>
-      <c r="D24" s="222" t="s">
+      <c r="D24" s="190" t="s">
         <v>297</v>
       </c>
-      <c r="E24" s="215"/>
-      <c r="F24" s="215"/>
+      <c r="E24" s="191"/>
+      <c r="F24" s="191"/>
       <c r="G24" s="89"/>
       <c r="H24" s="88"/>
       <c r="I24" s="87"/>
@@ -10018,11 +10346,11 @@
       <c r="C25" s="103" t="s">
         <v>300</v>
       </c>
-      <c r="D25" s="222" t="s">
+      <c r="D25" s="190" t="s">
         <v>301</v>
       </c>
-      <c r="E25" s="215"/>
-      <c r="F25" s="215"/>
+      <c r="E25" s="191"/>
+      <c r="F25" s="191"/>
       <c r="G25" s="89"/>
       <c r="H25" s="88"/>
       <c r="I25" s="87"/>
@@ -10039,11 +10367,11 @@
       <c r="C26" s="105" t="s">
         <v>304</v>
       </c>
-      <c r="D26" s="222" t="s">
+      <c r="D26" s="190" t="s">
         <v>305</v>
       </c>
-      <c r="E26" s="215"/>
-      <c r="F26" s="215"/>
+      <c r="E26" s="191"/>
+      <c r="F26" s="191"/>
       <c r="G26" s="89"/>
       <c r="H26" s="88"/>
       <c r="I26" s="87"/>
@@ -10051,7 +10379,7 @@
       <c r="K26" s="86"/>
     </row>
     <row r="27" spans="1:11" ht="25.15" customHeight="1">
-      <c r="A27" s="242" t="s">
+      <c r="A27" s="241" t="s">
         <v>306</v>
       </c>
       <c r="B27" s="200"/>
@@ -10075,11 +10403,11 @@
       <c r="C28" s="103" t="s">
         <v>309</v>
       </c>
-      <c r="D28" s="222" t="s">
+      <c r="D28" s="190" t="s">
         <v>310</v>
       </c>
-      <c r="E28" s="215"/>
-      <c r="F28" s="215"/>
+      <c r="E28" s="191"/>
+      <c r="F28" s="191"/>
       <c r="G28" s="89"/>
       <c r="H28" s="88"/>
       <c r="I28" s="90"/>
@@ -10096,11 +10424,11 @@
       <c r="C29" s="105" t="s">
         <v>313</v>
       </c>
-      <c r="D29" s="222" t="s">
+      <c r="D29" s="190" t="s">
         <v>314</v>
       </c>
-      <c r="E29" s="215"/>
-      <c r="F29" s="215"/>
+      <c r="E29" s="191"/>
+      <c r="F29" s="191"/>
       <c r="G29" s="89"/>
       <c r="H29" s="88"/>
       <c r="I29" s="87"/>
@@ -10117,11 +10445,11 @@
       <c r="C30" s="103" t="s">
         <v>317</v>
       </c>
-      <c r="D30" s="222" t="s">
+      <c r="D30" s="190" t="s">
         <v>318</v>
       </c>
-      <c r="E30" s="215"/>
-      <c r="F30" s="215"/>
+      <c r="E30" s="191"/>
+      <c r="F30" s="191"/>
       <c r="G30" s="89"/>
       <c r="H30" s="88"/>
       <c r="I30" s="87"/>
@@ -10138,11 +10466,11 @@
       <c r="C31" s="105" t="s">
         <v>321</v>
       </c>
-      <c r="D31" s="222" t="s">
+      <c r="D31" s="190" t="s">
         <v>322</v>
       </c>
-      <c r="E31" s="215"/>
-      <c r="F31" s="215"/>
+      <c r="E31" s="191"/>
+      <c r="F31" s="191"/>
       <c r="G31" s="89"/>
       <c r="H31" s="88"/>
       <c r="I31" s="87"/>
@@ -10159,11 +10487,11 @@
       <c r="C32" s="103" t="s">
         <v>325</v>
       </c>
-      <c r="D32" s="222" t="s">
+      <c r="D32" s="190" t="s">
         <v>326</v>
       </c>
-      <c r="E32" s="215"/>
-      <c r="F32" s="215"/>
+      <c r="E32" s="191"/>
+      <c r="F32" s="191"/>
       <c r="G32" s="89"/>
       <c r="H32" s="88"/>
       <c r="I32" s="87"/>
@@ -10180,11 +10508,11 @@
       <c r="C33" s="105" t="s">
         <v>329</v>
       </c>
-      <c r="D33" s="222" t="s">
+      <c r="D33" s="190" t="s">
         <v>322</v>
       </c>
-      <c r="E33" s="215"/>
-      <c r="F33" s="215"/>
+      <c r="E33" s="191"/>
+      <c r="F33" s="191"/>
       <c r="G33" s="89"/>
       <c r="H33" s="88"/>
       <c r="I33" s="87"/>
@@ -10201,11 +10529,11 @@
       <c r="C34" s="103" t="s">
         <v>332</v>
       </c>
-      <c r="D34" s="222" t="s">
+      <c r="D34" s="190" t="s">
         <v>333</v>
       </c>
-      <c r="E34" s="215"/>
-      <c r="F34" s="215"/>
+      <c r="E34" s="191"/>
+      <c r="F34" s="191"/>
       <c r="G34" s="89"/>
       <c r="H34" s="88"/>
       <c r="I34" s="87"/>
@@ -10222,11 +10550,11 @@
       <c r="C35" s="105" t="s">
         <v>336</v>
       </c>
-      <c r="D35" s="222" t="s">
+      <c r="D35" s="190" t="s">
         <v>337</v>
       </c>
-      <c r="E35" s="215"/>
-      <c r="F35" s="215"/>
+      <c r="E35" s="191"/>
+      <c r="F35" s="191"/>
       <c r="G35" s="89"/>
       <c r="H35" s="88"/>
       <c r="I35" s="87"/>
@@ -10234,7 +10562,7 @@
       <c r="K35" s="86"/>
     </row>
     <row r="36" spans="1:11" ht="28.15" customHeight="1">
-      <c r="A36" s="242" t="s">
+      <c r="A36" s="241" t="s">
         <v>338</v>
       </c>
       <c r="B36" s="200"/>
@@ -10258,11 +10586,11 @@
       <c r="C37" s="103" t="s">
         <v>341</v>
       </c>
-      <c r="D37" s="222" t="s">
+      <c r="D37" s="190" t="s">
         <v>342</v>
       </c>
-      <c r="E37" s="215"/>
-      <c r="F37" s="215"/>
+      <c r="E37" s="191"/>
+      <c r="F37" s="191"/>
       <c r="G37" s="89"/>
       <c r="H37" s="88"/>
       <c r="I37" s="87"/>
@@ -10279,11 +10607,11 @@
       <c r="C38" s="105" t="s">
         <v>345</v>
       </c>
-      <c r="D38" s="222" t="s">
+      <c r="D38" s="190" t="s">
         <v>346</v>
       </c>
-      <c r="E38" s="215"/>
-      <c r="F38" s="215"/>
+      <c r="E38" s="191"/>
+      <c r="F38" s="191"/>
       <c r="G38" s="89"/>
       <c r="H38" s="88"/>
       <c r="I38" s="87"/>
@@ -10291,7 +10619,7 @@
       <c r="K38" s="86"/>
     </row>
     <row r="39" spans="1:11" ht="28.9" customHeight="1">
-      <c r="A39" s="242" t="s">
+      <c r="A39" s="241" t="s">
         <v>347</v>
       </c>
       <c r="B39" s="200"/>
@@ -10315,11 +10643,11 @@
       <c r="C40" s="103" t="s">
         <v>350</v>
       </c>
-      <c r="D40" s="222" t="s">
+      <c r="D40" s="190" t="s">
         <v>351</v>
       </c>
-      <c r="E40" s="215"/>
-      <c r="F40" s="215"/>
+      <c r="E40" s="191"/>
+      <c r="F40" s="191"/>
       <c r="G40" s="89"/>
       <c r="H40" s="88"/>
       <c r="I40" s="87"/>
@@ -10336,11 +10664,11 @@
       <c r="C41" s="105" t="s">
         <v>354</v>
       </c>
-      <c r="D41" s="222" t="s">
+      <c r="D41" s="190" t="s">
         <v>355</v>
       </c>
-      <c r="E41" s="215"/>
-      <c r="F41" s="215"/>
+      <c r="E41" s="191"/>
+      <c r="F41" s="191"/>
       <c r="G41" s="89"/>
       <c r="H41" s="88"/>
       <c r="I41" s="87"/>
@@ -10351,9 +10679,9 @@
       <c r="A42" s="84"/>
       <c r="B42" s="93"/>
       <c r="C42" s="86"/>
-      <c r="D42" s="243"/>
-      <c r="E42" s="244"/>
-      <c r="F42" s="244"/>
+      <c r="D42" s="239"/>
+      <c r="E42" s="240"/>
+      <c r="F42" s="240"/>
       <c r="G42" s="89"/>
       <c r="H42" s="88"/>
       <c r="I42" s="87"/>
@@ -10364,9 +10692,9 @@
       <c r="A43" s="84"/>
       <c r="B43" s="91"/>
       <c r="C43" s="92"/>
-      <c r="D43" s="243"/>
-      <c r="E43" s="215"/>
-      <c r="F43" s="215"/>
+      <c r="D43" s="239"/>
+      <c r="E43" s="191"/>
+      <c r="F43" s="191"/>
       <c r="G43" s="89"/>
       <c r="H43" s="88"/>
       <c r="I43" s="87"/>
@@ -10377,9 +10705,9 @@
       <c r="A44" s="84"/>
       <c r="B44" s="93"/>
       <c r="C44" s="86"/>
-      <c r="D44" s="243"/>
-      <c r="E44" s="244"/>
-      <c r="F44" s="244"/>
+      <c r="D44" s="239"/>
+      <c r="E44" s="240"/>
+      <c r="F44" s="240"/>
       <c r="G44" s="89"/>
       <c r="H44" s="88"/>
       <c r="I44" s="87"/>
@@ -10390,9 +10718,9 @@
       <c r="A45" s="84"/>
       <c r="B45" s="91"/>
       <c r="C45" s="92"/>
-      <c r="D45" s="243"/>
-      <c r="E45" s="215"/>
-      <c r="F45" s="215"/>
+      <c r="D45" s="239"/>
+      <c r="E45" s="191"/>
+      <c r="F45" s="191"/>
       <c r="G45" s="89"/>
       <c r="H45" s="88"/>
       <c r="I45" s="87"/>
@@ -10403,9 +10731,9 @@
       <c r="A46" s="84"/>
       <c r="B46" s="93"/>
       <c r="C46" s="86"/>
-      <c r="D46" s="243"/>
-      <c r="E46" s="244"/>
-      <c r="F46" s="244"/>
+      <c r="D46" s="239"/>
+      <c r="E46" s="240"/>
+      <c r="F46" s="240"/>
       <c r="G46" s="89"/>
       <c r="H46" s="88"/>
       <c r="I46" s="87"/>
@@ -10416,9 +10744,9 @@
       <c r="A47" s="84"/>
       <c r="B47" s="91"/>
       <c r="C47" s="92"/>
-      <c r="D47" s="243"/>
-      <c r="E47" s="215"/>
-      <c r="F47" s="215"/>
+      <c r="D47" s="239"/>
+      <c r="E47" s="191"/>
+      <c r="F47" s="191"/>
       <c r="G47" s="89"/>
       <c r="H47" s="88"/>
       <c r="I47" s="87"/>
@@ -10429,9 +10757,9 @@
       <c r="A48" s="84"/>
       <c r="B48" s="93"/>
       <c r="C48" s="86"/>
-      <c r="D48" s="243"/>
-      <c r="E48" s="244"/>
-      <c r="F48" s="244"/>
+      <c r="D48" s="239"/>
+      <c r="E48" s="240"/>
+      <c r="F48" s="240"/>
       <c r="G48" s="89"/>
       <c r="H48" s="88"/>
       <c r="I48" s="87"/>
@@ -10442,9 +10770,9 @@
       <c r="A49" s="84"/>
       <c r="B49" s="91"/>
       <c r="C49" s="92"/>
-      <c r="D49" s="243"/>
-      <c r="E49" s="215"/>
-      <c r="F49" s="215"/>
+      <c r="D49" s="239"/>
+      <c r="E49" s="191"/>
+      <c r="F49" s="191"/>
       <c r="G49" s="89"/>
       <c r="H49" s="88"/>
       <c r="I49" s="87"/>
@@ -10455,9 +10783,9 @@
       <c r="A50" s="84"/>
       <c r="B50" s="93"/>
       <c r="C50" s="86"/>
-      <c r="D50" s="243"/>
-      <c r="E50" s="244"/>
-      <c r="F50" s="244"/>
+      <c r="D50" s="239"/>
+      <c r="E50" s="240"/>
+      <c r="F50" s="240"/>
       <c r="G50" s="89"/>
       <c r="H50" s="88"/>
       <c r="I50" s="87"/>
@@ -10469,6 +10797,47 @@
     <row r="53" spans="1:11" ht="12" customHeight="1"/>
   </sheetData>
   <mergeCells count="57">
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A11:K11"/>
+    <mergeCell ref="A12:K12"/>
+    <mergeCell ref="H9:H10"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="K9:K10"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="A27:K27"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="A36:K36"/>
+    <mergeCell ref="D37:F37"/>
     <mergeCell ref="D48:F48"/>
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="D50:F50"/>
@@ -10485,47 +10854,6 @@
     <mergeCell ref="A39:K39"/>
     <mergeCell ref="D40:F40"/>
     <mergeCell ref="D41:F41"/>
-    <mergeCell ref="D42:F42"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="A36:K36"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="A27:K27"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A11:K11"/>
-    <mergeCell ref="A12:K12"/>
-    <mergeCell ref="H9:H10"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="K9:K10"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="I5:K5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10583,54 +10911,54 @@
       <c r="A3" s="100" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="186" t="s">
+      <c r="B3" s="224" t="s">
         <v>62</v>
       </c>
-      <c r="C3" s="186"/>
-      <c r="D3" s="187"/>
+      <c r="C3" s="224"/>
+      <c r="D3" s="225"/>
       <c r="E3" s="65"/>
       <c r="F3" s="65"/>
       <c r="G3" s="65"/>
       <c r="H3" s="65"/>
-      <c r="I3" s="188"/>
-      <c r="J3" s="188"/>
-      <c r="K3" s="188"/>
+      <c r="I3" s="208"/>
+      <c r="J3" s="208"/>
+      <c r="K3" s="208"/>
       <c r="L3" s="67"/>
     </row>
     <row r="4" spans="1:12" s="55" customFormat="1" ht="13.15" customHeight="1">
       <c r="A4" s="68" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="189" t="s">
+      <c r="B4" s="226" t="s">
         <v>356</v>
       </c>
-      <c r="C4" s="190"/>
-      <c r="D4" s="191"/>
+      <c r="C4" s="227"/>
+      <c r="D4" s="228"/>
       <c r="E4" s="65"/>
       <c r="F4" s="65"/>
       <c r="G4" s="65"/>
       <c r="H4" s="65"/>
-      <c r="I4" s="188"/>
-      <c r="J4" s="188"/>
-      <c r="K4" s="188"/>
+      <c r="I4" s="208"/>
+      <c r="J4" s="208"/>
+      <c r="K4" s="208"/>
       <c r="L4" s="67"/>
     </row>
     <row r="5" spans="1:12" s="56" customFormat="1" ht="25.5">
       <c r="A5" s="101" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="192" t="s">
+      <c r="B5" s="229" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="193"/>
-      <c r="D5" s="194"/>
+      <c r="C5" s="230"/>
+      <c r="D5" s="231"/>
       <c r="E5" s="69"/>
       <c r="F5" s="69"/>
       <c r="G5" s="69"/>
       <c r="H5" s="69"/>
-      <c r="I5" s="195"/>
-      <c r="J5" s="195"/>
-      <c r="K5" s="195"/>
+      <c r="I5" s="232"/>
+      <c r="J5" s="232"/>
+      <c r="K5" s="232"/>
       <c r="L5" s="70"/>
     </row>
     <row r="6" spans="1:12" s="55" customFormat="1" ht="15" customHeight="1">
@@ -10652,9 +10980,9 @@
       <c r="F6" s="66"/>
       <c r="G6" s="66"/>
       <c r="H6" s="66"/>
-      <c r="I6" s="188"/>
-      <c r="J6" s="188"/>
-      <c r="K6" s="188"/>
+      <c r="I6" s="208"/>
+      <c r="J6" s="208"/>
+      <c r="K6" s="208"/>
       <c r="L6" s="67"/>
     </row>
     <row r="7" spans="1:12" s="55" customFormat="1" ht="15" customHeight="1">
@@ -10676,16 +11004,16 @@
       <c r="F7" s="79"/>
       <c r="G7" s="79"/>
       <c r="H7" s="79"/>
-      <c r="I7" s="188"/>
-      <c r="J7" s="188"/>
-      <c r="K7" s="188"/>
+      <c r="I7" s="208"/>
+      <c r="J7" s="208"/>
+      <c r="K7" s="208"/>
       <c r="L7" s="67"/>
     </row>
     <row r="8" spans="1:12" s="55" customFormat="1" ht="15" customHeight="1">
-      <c r="A8" s="196"/>
-      <c r="B8" s="196"/>
-      <c r="C8" s="196"/>
-      <c r="D8" s="196"/>
+      <c r="A8" s="209"/>
+      <c r="B8" s="209"/>
+      <c r="C8" s="209"/>
+      <c r="D8" s="209"/>
       <c r="E8" s="66"/>
       <c r="F8" s="66"/>
       <c r="G8" s="66"/>
@@ -10696,64 +11024,64 @@
       <c r="L8" s="67"/>
     </row>
     <row r="9" spans="1:12" s="57" customFormat="1" ht="12" customHeight="1">
-      <c r="A9" s="202" t="s">
+      <c r="A9" s="212" t="s">
         <v>71</v>
       </c>
-      <c r="B9" s="204" t="s">
+      <c r="B9" s="214" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="202" t="s">
+      <c r="C9" s="212" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="208" t="s">
+      <c r="D9" s="218" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="209"/>
-      <c r="F9" s="209"/>
-      <c r="G9" s="210"/>
-      <c r="H9" s="206" t="s">
+      <c r="E9" s="219"/>
+      <c r="F9" s="219"/>
+      <c r="G9" s="220"/>
+      <c r="H9" s="216" t="s">
         <v>75</v>
       </c>
-      <c r="I9" s="207" t="s">
+      <c r="I9" s="217" t="s">
         <v>76</v>
       </c>
-      <c r="J9" s="207" t="s">
+      <c r="J9" s="217" t="s">
         <v>77</v>
       </c>
-      <c r="K9" s="207" t="s">
+      <c r="K9" s="217" t="s">
         <v>78</v>
       </c>
       <c r="L9" s="81"/>
     </row>
     <row r="10" spans="1:12" s="55" customFormat="1" ht="12" customHeight="1">
-      <c r="A10" s="203"/>
-      <c r="B10" s="205"/>
-      <c r="C10" s="203"/>
-      <c r="D10" s="211"/>
-      <c r="E10" s="212"/>
-      <c r="F10" s="212"/>
-      <c r="G10" s="213"/>
-      <c r="H10" s="202"/>
-      <c r="I10" s="202"/>
-      <c r="J10" s="202"/>
-      <c r="K10" s="202"/>
+      <c r="A10" s="213"/>
+      <c r="B10" s="215"/>
+      <c r="C10" s="213"/>
+      <c r="D10" s="221"/>
+      <c r="E10" s="222"/>
+      <c r="F10" s="222"/>
+      <c r="G10" s="223"/>
+      <c r="H10" s="212"/>
+      <c r="I10" s="212"/>
+      <c r="J10" s="212"/>
+      <c r="K10" s="212"/>
       <c r="L10" s="67"/>
     </row>
     <row r="11" spans="1:12" s="58" customFormat="1" ht="15">
-      <c r="A11" s="197"/>
-      <c r="B11" s="197"/>
-      <c r="C11" s="197"/>
-      <c r="D11" s="197"/>
-      <c r="E11" s="197"/>
-      <c r="F11" s="197"/>
-      <c r="G11" s="197"/>
-      <c r="H11" s="197"/>
-      <c r="I11" s="197"/>
-      <c r="J11" s="197"/>
-      <c r="K11" s="198"/>
+      <c r="A11" s="210"/>
+      <c r="B11" s="210"/>
+      <c r="C11" s="210"/>
+      <c r="D11" s="210"/>
+      <c r="E11" s="210"/>
+      <c r="F11" s="210"/>
+      <c r="G11" s="210"/>
+      <c r="H11" s="210"/>
+      <c r="I11" s="210"/>
+      <c r="J11" s="210"/>
+      <c r="K11" s="211"/>
     </row>
     <row r="12" spans="1:12" s="59" customFormat="1" ht="22.9" customHeight="1">
-      <c r="A12" s="242" t="s">
+      <c r="A12" s="241" t="s">
         <v>357</v>
       </c>
       <c r="B12" s="245"/>
@@ -10777,11 +11105,11 @@
       <c r="C13" s="103" t="s">
         <v>359</v>
       </c>
-      <c r="D13" s="222" t="s">
+      <c r="D13" s="190" t="s">
         <v>360</v>
       </c>
-      <c r="E13" s="215"/>
-      <c r="F13" s="215"/>
+      <c r="E13" s="191"/>
+      <c r="F13" s="191"/>
       <c r="G13" s="89"/>
       <c r="H13" s="88"/>
       <c r="I13" s="90"/>
@@ -10798,11 +11126,11 @@
       <c r="C14" s="105" t="s">
         <v>362</v>
       </c>
-      <c r="D14" s="222" t="s">
+      <c r="D14" s="190" t="s">
         <v>363</v>
       </c>
-      <c r="E14" s="215"/>
-      <c r="F14" s="215"/>
+      <c r="E14" s="191"/>
+      <c r="F14" s="191"/>
       <c r="G14" s="89"/>
       <c r="H14" s="88"/>
       <c r="I14" s="87"/>
@@ -10819,11 +11147,11 @@
       <c r="C15" s="103" t="s">
         <v>365</v>
       </c>
-      <c r="D15" s="222" t="s">
+      <c r="D15" s="190" t="s">
         <v>366</v>
       </c>
-      <c r="E15" s="215"/>
-      <c r="F15" s="215"/>
+      <c r="E15" s="191"/>
+      <c r="F15" s="191"/>
       <c r="G15" s="89"/>
       <c r="H15" s="88"/>
       <c r="I15" s="87"/>
@@ -10831,7 +11159,7 @@
       <c r="K15" s="86"/>
     </row>
     <row r="16" spans="1:12" ht="27" customHeight="1">
-      <c r="A16" s="242" t="s">
+      <c r="A16" s="241" t="s">
         <v>367</v>
       </c>
       <c r="B16" s="200"/>
@@ -10855,11 +11183,11 @@
       <c r="C17" s="105" t="s">
         <v>369</v>
       </c>
-      <c r="D17" s="222" t="s">
+      <c r="D17" s="190" t="s">
         <v>370</v>
       </c>
-      <c r="E17" s="215"/>
-      <c r="F17" s="215"/>
+      <c r="E17" s="191"/>
+      <c r="F17" s="191"/>
       <c r="G17" s="89"/>
       <c r="H17" s="88"/>
       <c r="I17" s="87"/>
@@ -10876,11 +11204,11 @@
       <c r="C18" s="103" t="s">
         <v>372</v>
       </c>
-      <c r="D18" s="222" t="s">
+      <c r="D18" s="190" t="s">
         <v>373</v>
       </c>
-      <c r="E18" s="215"/>
-      <c r="F18" s="215"/>
+      <c r="E18" s="191"/>
+      <c r="F18" s="191"/>
       <c r="G18" s="89"/>
       <c r="H18" s="88"/>
       <c r="I18" s="87"/>
@@ -10897,11 +11225,11 @@
       <c r="C19" s="105" t="s">
         <v>375</v>
       </c>
-      <c r="D19" s="222" t="s">
+      <c r="D19" s="190" t="s">
         <v>376</v>
       </c>
-      <c r="E19" s="215"/>
-      <c r="F19" s="215"/>
+      <c r="E19" s="191"/>
+      <c r="F19" s="191"/>
       <c r="G19" s="89"/>
       <c r="H19" s="88"/>
       <c r="I19" s="87"/>
@@ -10909,19 +11237,19 @@
       <c r="K19" s="86"/>
     </row>
     <row r="20" spans="1:11" ht="28.15" customHeight="1">
-      <c r="A20" s="239" t="s">
+      <c r="A20" s="242" t="s">
         <v>377</v>
       </c>
-      <c r="B20" s="240"/>
-      <c r="C20" s="240"/>
-      <c r="D20" s="240"/>
-      <c r="E20" s="240"/>
-      <c r="F20" s="240"/>
-      <c r="G20" s="240"/>
-      <c r="H20" s="240"/>
-      <c r="I20" s="240"/>
-      <c r="J20" s="240"/>
-      <c r="K20" s="241"/>
+      <c r="B20" s="243"/>
+      <c r="C20" s="243"/>
+      <c r="D20" s="243"/>
+      <c r="E20" s="243"/>
+      <c r="F20" s="243"/>
+      <c r="G20" s="243"/>
+      <c r="H20" s="243"/>
+      <c r="I20" s="243"/>
+      <c r="J20" s="243"/>
+      <c r="K20" s="244"/>
     </row>
     <row r="21" spans="1:11" ht="70.150000000000006" customHeight="1">
       <c r="A21" s="102" t="s">
@@ -10933,11 +11261,11 @@
       <c r="C21" s="103" t="s">
         <v>379</v>
       </c>
-      <c r="D21" s="222" t="s">
+      <c r="D21" s="190" t="s">
         <v>380</v>
       </c>
-      <c r="E21" s="215"/>
-      <c r="F21" s="215"/>
+      <c r="E21" s="191"/>
+      <c r="F21" s="191"/>
       <c r="G21" s="89"/>
       <c r="H21" s="88"/>
       <c r="I21" s="87"/>
@@ -10954,11 +11282,11 @@
       <c r="C22" s="105" t="s">
         <v>382</v>
       </c>
-      <c r="D22" s="222" t="s">
+      <c r="D22" s="190" t="s">
         <v>383</v>
       </c>
-      <c r="E22" s="215"/>
-      <c r="F22" s="215"/>
+      <c r="E22" s="191"/>
+      <c r="F22" s="191"/>
       <c r="G22" s="89"/>
       <c r="H22" s="88"/>
       <c r="I22" s="87"/>
@@ -10975,11 +11303,11 @@
       <c r="C23" s="103" t="s">
         <v>385</v>
       </c>
-      <c r="D23" s="222" t="s">
+      <c r="D23" s="190" t="s">
         <v>386</v>
       </c>
-      <c r="E23" s="215"/>
-      <c r="F23" s="215"/>
+      <c r="E23" s="191"/>
+      <c r="F23" s="191"/>
       <c r="G23" s="89"/>
       <c r="H23" s="88"/>
       <c r="I23" s="87"/>
@@ -10996,11 +11324,11 @@
       <c r="C24" s="105" t="s">
         <v>388</v>
       </c>
-      <c r="D24" s="222" t="s">
+      <c r="D24" s="190" t="s">
         <v>389</v>
       </c>
-      <c r="E24" s="215"/>
-      <c r="F24" s="215"/>
+      <c r="E24" s="191"/>
+      <c r="F24" s="191"/>
       <c r="G24" s="89"/>
       <c r="H24" s="88"/>
       <c r="I24" s="87"/>
@@ -11008,19 +11336,19 @@
       <c r="K24" s="86"/>
     </row>
     <row r="25" spans="1:11" ht="31.15" customHeight="1">
-      <c r="A25" s="239" t="s">
+      <c r="A25" s="242" t="s">
         <v>390</v>
       </c>
-      <c r="B25" s="240"/>
-      <c r="C25" s="240"/>
-      <c r="D25" s="240"/>
-      <c r="E25" s="240"/>
-      <c r="F25" s="240"/>
-      <c r="G25" s="240"/>
-      <c r="H25" s="240"/>
-      <c r="I25" s="240"/>
-      <c r="J25" s="240"/>
-      <c r="K25" s="241"/>
+      <c r="B25" s="243"/>
+      <c r="C25" s="243"/>
+      <c r="D25" s="243"/>
+      <c r="E25" s="243"/>
+      <c r="F25" s="243"/>
+      <c r="G25" s="243"/>
+      <c r="H25" s="243"/>
+      <c r="I25" s="243"/>
+      <c r="J25" s="243"/>
+      <c r="K25" s="244"/>
     </row>
     <row r="26" spans="1:11" ht="70.150000000000006" customHeight="1">
       <c r="A26" s="102" t="s">
@@ -11032,11 +11360,11 @@
       <c r="C26" s="103" t="s">
         <v>392</v>
       </c>
-      <c r="D26" s="222" t="s">
+      <c r="D26" s="190" t="s">
         <v>393</v>
       </c>
-      <c r="E26" s="215"/>
-      <c r="F26" s="215"/>
+      <c r="E26" s="191"/>
+      <c r="F26" s="191"/>
       <c r="G26" s="89"/>
       <c r="H26" s="88"/>
       <c r="I26" s="87"/>
@@ -11053,11 +11381,11 @@
       <c r="C27" s="105" t="s">
         <v>395</v>
       </c>
-      <c r="D27" s="222" t="s">
+      <c r="D27" s="190" t="s">
         <v>396</v>
       </c>
-      <c r="E27" s="215"/>
-      <c r="F27" s="215"/>
+      <c r="E27" s="191"/>
+      <c r="F27" s="191"/>
       <c r="G27" s="89"/>
       <c r="H27" s="88"/>
       <c r="I27" s="87"/>
@@ -11074,11 +11402,11 @@
       <c r="C28" s="103" t="s">
         <v>398</v>
       </c>
-      <c r="D28" s="222" t="s">
+      <c r="D28" s="190" t="s">
         <v>399</v>
       </c>
-      <c r="E28" s="215"/>
-      <c r="F28" s="215"/>
+      <c r="E28" s="191"/>
+      <c r="F28" s="191"/>
       <c r="G28" s="89"/>
       <c r="H28" s="88"/>
       <c r="I28" s="87"/>
@@ -11095,11 +11423,11 @@
       <c r="C29" s="105" t="s">
         <v>401</v>
       </c>
-      <c r="D29" s="222" t="s">
+      <c r="D29" s="190" t="s">
         <v>402</v>
       </c>
-      <c r="E29" s="215"/>
-      <c r="F29" s="215"/>
+      <c r="E29" s="191"/>
+      <c r="F29" s="191"/>
       <c r="G29" s="89"/>
       <c r="H29" s="88"/>
       <c r="I29" s="87"/>
@@ -11110,9 +11438,9 @@
       <c r="A30" s="102"/>
       <c r="B30" s="103"/>
       <c r="C30" s="103"/>
-      <c r="D30" s="222"/>
-      <c r="E30" s="215"/>
-      <c r="F30" s="215"/>
+      <c r="D30" s="190"/>
+      <c r="E30" s="191"/>
+      <c r="F30" s="191"/>
       <c r="G30" s="89"/>
       <c r="H30" s="88"/>
       <c r="I30" s="87"/>
@@ -11123,9 +11451,9 @@
       <c r="A31" s="104"/>
       <c r="B31" s="114"/>
       <c r="C31" s="105"/>
-      <c r="D31" s="222"/>
-      <c r="E31" s="215"/>
-      <c r="F31" s="215"/>
+      <c r="D31" s="190"/>
+      <c r="E31" s="191"/>
+      <c r="F31" s="191"/>
       <c r="G31" s="89"/>
       <c r="H31" s="88"/>
       <c r="I31" s="87"/>
@@ -11136,9 +11464,9 @@
       <c r="A32" s="115"/>
       <c r="B32" s="116"/>
       <c r="C32" s="117"/>
-      <c r="D32" s="243"/>
-      <c r="E32" s="244"/>
-      <c r="F32" s="244"/>
+      <c r="D32" s="239"/>
+      <c r="E32" s="240"/>
+      <c r="F32" s="240"/>
       <c r="G32" s="89"/>
       <c r="H32" s="88"/>
       <c r="I32" s="87"/>
@@ -11149,9 +11477,9 @@
       <c r="A33" s="84"/>
       <c r="B33" s="93"/>
       <c r="C33" s="86"/>
-      <c r="D33" s="243"/>
-      <c r="E33" s="244"/>
-      <c r="F33" s="244"/>
+      <c r="D33" s="239"/>
+      <c r="E33" s="240"/>
+      <c r="F33" s="240"/>
       <c r="G33" s="89"/>
       <c r="H33" s="88"/>
       <c r="I33" s="87"/>
@@ -11162,9 +11490,9 @@
       <c r="A34" s="84"/>
       <c r="B34" s="93"/>
       <c r="C34" s="86"/>
-      <c r="D34" s="243"/>
-      <c r="E34" s="244"/>
-      <c r="F34" s="244"/>
+      <c r="D34" s="239"/>
+      <c r="E34" s="240"/>
+      <c r="F34" s="240"/>
       <c r="G34" s="89"/>
       <c r="H34" s="88"/>
       <c r="I34" s="87"/>
@@ -11175,9 +11503,9 @@
       <c r="A35" s="84"/>
       <c r="B35" s="93"/>
       <c r="C35" s="86"/>
-      <c r="D35" s="243"/>
-      <c r="E35" s="244"/>
-      <c r="F35" s="244"/>
+      <c r="D35" s="239"/>
+      <c r="E35" s="240"/>
+      <c r="F35" s="240"/>
       <c r="G35" s="89"/>
       <c r="H35" s="88"/>
       <c r="I35" s="87"/>
@@ -11188,9 +11516,9 @@
       <c r="A36" s="84"/>
       <c r="B36" s="93"/>
       <c r="C36" s="86"/>
-      <c r="D36" s="243"/>
-      <c r="E36" s="244"/>
-      <c r="F36" s="244"/>
+      <c r="D36" s="239"/>
+      <c r="E36" s="240"/>
+      <c r="F36" s="240"/>
       <c r="G36" s="89"/>
       <c r="H36" s="88"/>
       <c r="I36" s="87"/>
@@ -11201,9 +11529,9 @@
       <c r="A37" s="84"/>
       <c r="B37" s="93"/>
       <c r="C37" s="86"/>
-      <c r="D37" s="243"/>
-      <c r="E37" s="244"/>
-      <c r="F37" s="244"/>
+      <c r="D37" s="239"/>
+      <c r="E37" s="240"/>
+      <c r="F37" s="240"/>
       <c r="G37" s="89"/>
       <c r="H37" s="88"/>
       <c r="I37" s="87"/>
@@ -11214,9 +11542,9 @@
       <c r="A38" s="84"/>
       <c r="B38" s="93"/>
       <c r="C38" s="86"/>
-      <c r="D38" s="243"/>
-      <c r="E38" s="244"/>
-      <c r="F38" s="244"/>
+      <c r="D38" s="239"/>
+      <c r="E38" s="240"/>
+      <c r="F38" s="240"/>
       <c r="G38" s="89"/>
       <c r="H38" s="88"/>
       <c r="I38" s="87"/>
@@ -11227,9 +11555,9 @@
       <c r="A39" s="84"/>
       <c r="B39" s="93"/>
       <c r="C39" s="86"/>
-      <c r="D39" s="243"/>
-      <c r="E39" s="244"/>
-      <c r="F39" s="244"/>
+      <c r="D39" s="239"/>
+      <c r="E39" s="240"/>
+      <c r="F39" s="240"/>
       <c r="G39" s="89"/>
       <c r="H39" s="88"/>
       <c r="I39" s="87"/>
@@ -11240,9 +11568,9 @@
       <c r="A40" s="84"/>
       <c r="B40" s="93"/>
       <c r="C40" s="86"/>
-      <c r="D40" s="243"/>
-      <c r="E40" s="244"/>
-      <c r="F40" s="244"/>
+      <c r="D40" s="239"/>
+      <c r="E40" s="240"/>
+      <c r="F40" s="240"/>
       <c r="G40" s="89"/>
       <c r="H40" s="88"/>
       <c r="I40" s="87"/>
@@ -11253,9 +11581,9 @@
       <c r="A41" s="84"/>
       <c r="B41" s="93"/>
       <c r="C41" s="86"/>
-      <c r="D41" s="243"/>
-      <c r="E41" s="244"/>
-      <c r="F41" s="244"/>
+      <c r="D41" s="239"/>
+      <c r="E41" s="240"/>
+      <c r="F41" s="240"/>
       <c r="G41" s="89"/>
       <c r="H41" s="88"/>
       <c r="I41" s="87"/>
@@ -11266,9 +11594,9 @@
       <c r="A42" s="84"/>
       <c r="B42" s="93"/>
       <c r="C42" s="86"/>
-      <c r="D42" s="243"/>
-      <c r="E42" s="244"/>
-      <c r="F42" s="244"/>
+      <c r="D42" s="239"/>
+      <c r="E42" s="240"/>
+      <c r="F42" s="240"/>
       <c r="G42" s="89"/>
       <c r="H42" s="88"/>
       <c r="I42" s="87"/>
@@ -11279,9 +11607,9 @@
       <c r="A43" s="84"/>
       <c r="B43" s="93"/>
       <c r="C43" s="86"/>
-      <c r="D43" s="243"/>
-      <c r="E43" s="244"/>
-      <c r="F43" s="244"/>
+      <c r="D43" s="239"/>
+      <c r="E43" s="240"/>
+      <c r="F43" s="240"/>
       <c r="G43" s="89"/>
       <c r="H43" s="88"/>
       <c r="I43" s="87"/>
@@ -11292,9 +11620,9 @@
       <c r="A44" s="84"/>
       <c r="B44" s="93"/>
       <c r="C44" s="86"/>
-      <c r="D44" s="243"/>
-      <c r="E44" s="244"/>
-      <c r="F44" s="244"/>
+      <c r="D44" s="239"/>
+      <c r="E44" s="240"/>
+      <c r="F44" s="240"/>
       <c r="G44" s="89"/>
       <c r="H44" s="88"/>
       <c r="I44" s="87"/>
@@ -11305,9 +11633,9 @@
       <c r="A45" s="84"/>
       <c r="B45" s="93"/>
       <c r="C45" s="86"/>
-      <c r="D45" s="243"/>
-      <c r="E45" s="244"/>
-      <c r="F45" s="244"/>
+      <c r="D45" s="239"/>
+      <c r="E45" s="240"/>
+      <c r="F45" s="240"/>
       <c r="G45" s="89"/>
       <c r="H45" s="88"/>
       <c r="I45" s="87"/>
@@ -11318,9 +11646,9 @@
       <c r="A46" s="84"/>
       <c r="B46" s="93"/>
       <c r="C46" s="86"/>
-      <c r="D46" s="243"/>
-      <c r="E46" s="244"/>
-      <c r="F46" s="244"/>
+      <c r="D46" s="239"/>
+      <c r="E46" s="240"/>
+      <c r="F46" s="240"/>
       <c r="G46" s="89"/>
       <c r="H46" s="88"/>
       <c r="I46" s="87"/>
@@ -11331,9 +11659,9 @@
       <c r="A47" s="84"/>
       <c r="B47" s="93"/>
       <c r="C47" s="86"/>
-      <c r="D47" s="243"/>
-      <c r="E47" s="244"/>
-      <c r="F47" s="244"/>
+      <c r="D47" s="239"/>
+      <c r="E47" s="240"/>
+      <c r="F47" s="240"/>
       <c r="G47" s="89"/>
       <c r="H47" s="88"/>
       <c r="I47" s="87"/>
@@ -11344,9 +11672,9 @@
       <c r="A48" s="84"/>
       <c r="B48" s="93"/>
       <c r="C48" s="86"/>
-      <c r="D48" s="243"/>
-      <c r="E48" s="244"/>
-      <c r="F48" s="244"/>
+      <c r="D48" s="239"/>
+      <c r="E48" s="240"/>
+      <c r="F48" s="240"/>
       <c r="G48" s="89"/>
       <c r="H48" s="88"/>
       <c r="I48" s="87"/>
@@ -11359,6 +11687,45 @@
     <row r="52" ht="12" customHeight="1"/>
   </sheetData>
   <mergeCells count="55">
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A11:K11"/>
+    <mergeCell ref="A12:K12"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="K9:K10"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="A16:K16"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="A20:K20"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="A25:K25"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="D37:F37"/>
     <mergeCell ref="D48:F48"/>
     <mergeCell ref="A9:A10"/>
     <mergeCell ref="B9:B10"/>
@@ -11375,45 +11742,6 @@
     <mergeCell ref="D40:F40"/>
     <mergeCell ref="D41:F41"/>
     <mergeCell ref="D42:F42"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="D36:F36"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="A25:K25"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="A20:K20"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="A16:K16"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A11:K11"/>
-    <mergeCell ref="A12:K12"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="K9:K10"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="I5:K5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -11466,52 +11794,52 @@
       <c r="A3" s="64" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="186" t="s">
+      <c r="B3" s="224" t="s">
         <v>62</v>
       </c>
-      <c r="C3" s="186"/>
-      <c r="D3" s="187"/>
+      <c r="C3" s="224"/>
+      <c r="D3" s="225"/>
       <c r="E3" s="65"/>
       <c r="F3" s="65"/>
       <c r="G3" s="65"/>
       <c r="H3" s="65"/>
-      <c r="I3" s="188"/>
-      <c r="J3" s="188"/>
-      <c r="K3" s="188"/>
+      <c r="I3" s="208"/>
+      <c r="J3" s="208"/>
+      <c r="K3" s="208"/>
     </row>
     <row r="4" spans="1:11" ht="13.5" customHeight="1">
       <c r="A4" s="68" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="189" t="s">
+      <c r="B4" s="226" t="s">
         <v>404</v>
       </c>
-      <c r="C4" s="190"/>
-      <c r="D4" s="191"/>
+      <c r="C4" s="227"/>
+      <c r="D4" s="228"/>
       <c r="E4" s="65"/>
       <c r="F4" s="65"/>
       <c r="G4" s="65"/>
       <c r="H4" s="65"/>
-      <c r="I4" s="188"/>
-      <c r="J4" s="188"/>
-      <c r="K4" s="188"/>
+      <c r="I4" s="208"/>
+      <c r="J4" s="208"/>
+      <c r="K4" s="208"/>
     </row>
     <row r="5" spans="1:11" ht="12.75" customHeight="1">
       <c r="A5" s="68" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="192" t="s">
+      <c r="B5" s="229" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="193"/>
-      <c r="D5" s="194"/>
+      <c r="C5" s="230"/>
+      <c r="D5" s="231"/>
       <c r="E5" s="69"/>
       <c r="F5" s="69"/>
       <c r="G5" s="69"/>
       <c r="H5" s="69"/>
-      <c r="I5" s="195"/>
-      <c r="J5" s="195"/>
-      <c r="K5" s="195"/>
+      <c r="I5" s="232"/>
+      <c r="J5" s="232"/>
+      <c r="K5" s="232"/>
     </row>
     <row r="6" spans="1:11" ht="14.25">
       <c r="A6" s="71" t="s">
@@ -11532,9 +11860,9 @@
       <c r="F6" s="66"/>
       <c r="G6" s="66"/>
       <c r="H6" s="66"/>
-      <c r="I6" s="188"/>
-      <c r="J6" s="188"/>
-      <c r="K6" s="188"/>
+      <c r="I6" s="208"/>
+      <c r="J6" s="208"/>
+      <c r="K6" s="208"/>
     </row>
     <row r="7" spans="1:11" ht="14.25">
       <c r="A7" s="75" t="s">
@@ -11555,15 +11883,15 @@
       <c r="F7" s="79"/>
       <c r="G7" s="79"/>
       <c r="H7" s="79"/>
-      <c r="I7" s="188"/>
-      <c r="J7" s="188"/>
-      <c r="K7" s="188"/>
+      <c r="I7" s="208"/>
+      <c r="J7" s="208"/>
+      <c r="K7" s="208"/>
     </row>
     <row r="8" spans="1:11" ht="14.25">
-      <c r="A8" s="196"/>
-      <c r="B8" s="196"/>
-      <c r="C8" s="196"/>
-      <c r="D8" s="196"/>
+      <c r="A8" s="209"/>
+      <c r="B8" s="209"/>
+      <c r="C8" s="209"/>
+      <c r="D8" s="209"/>
       <c r="E8" s="66"/>
       <c r="F8" s="66"/>
       <c r="G8" s="66"/>
@@ -11573,59 +11901,59 @@
       <c r="K8" s="80"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="202" t="s">
+      <c r="A9" s="212" t="s">
         <v>71</v>
       </c>
-      <c r="B9" s="204" t="s">
+      <c r="B9" s="214" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="202" t="s">
+      <c r="C9" s="212" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="208" t="s">
+      <c r="D9" s="218" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="209"/>
-      <c r="F9" s="209"/>
-      <c r="G9" s="210"/>
-      <c r="H9" s="206" t="s">
+      <c r="E9" s="219"/>
+      <c r="F9" s="219"/>
+      <c r="G9" s="220"/>
+      <c r="H9" s="216" t="s">
         <v>75</v>
       </c>
-      <c r="I9" s="207" t="s">
+      <c r="I9" s="217" t="s">
         <v>76</v>
       </c>
-      <c r="J9" s="207" t="s">
+      <c r="J9" s="217" t="s">
         <v>77</v>
       </c>
-      <c r="K9" s="207" t="s">
+      <c r="K9" s="217" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="203"/>
-      <c r="B10" s="205"/>
-      <c r="C10" s="203"/>
-      <c r="D10" s="211"/>
-      <c r="E10" s="212"/>
-      <c r="F10" s="212"/>
-      <c r="G10" s="213"/>
-      <c r="H10" s="202"/>
-      <c r="I10" s="202"/>
-      <c r="J10" s="202"/>
-      <c r="K10" s="202"/>
+      <c r="A10" s="213"/>
+      <c r="B10" s="215"/>
+      <c r="C10" s="213"/>
+      <c r="D10" s="221"/>
+      <c r="E10" s="222"/>
+      <c r="F10" s="222"/>
+      <c r="G10" s="223"/>
+      <c r="H10" s="212"/>
+      <c r="I10" s="212"/>
+      <c r="J10" s="212"/>
+      <c r="K10" s="212"/>
     </row>
     <row r="11" spans="1:11" ht="15">
-      <c r="A11" s="197"/>
-      <c r="B11" s="197"/>
-      <c r="C11" s="197"/>
-      <c r="D11" s="197"/>
-      <c r="E11" s="197"/>
-      <c r="F11" s="197"/>
-      <c r="G11" s="197"/>
-      <c r="H11" s="197"/>
-      <c r="I11" s="197"/>
-      <c r="J11" s="197"/>
-      <c r="K11" s="198"/>
+      <c r="A11" s="210"/>
+      <c r="B11" s="210"/>
+      <c r="C11" s="210"/>
+      <c r="D11" s="210"/>
+      <c r="E11" s="210"/>
+      <c r="F11" s="210"/>
+      <c r="G11" s="210"/>
+      <c r="H11" s="210"/>
+      <c r="I11" s="210"/>
+      <c r="J11" s="210"/>
+      <c r="K11" s="211"/>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="199" t="s">
@@ -11858,16 +12186,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="I5:K5"/>
     <mergeCell ref="I6:K6"/>
     <mergeCell ref="I7:K7"/>
     <mergeCell ref="A8:D8"/>
@@ -11881,12 +12205,16 @@
     <mergeCell ref="J9:J10"/>
     <mergeCell ref="K9:K10"/>
     <mergeCell ref="D9:G10"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="D22:F22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -11944,54 +12272,54 @@
       <c r="A3" s="100" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="186" t="s">
+      <c r="B3" s="224" t="s">
         <v>62</v>
       </c>
-      <c r="C3" s="186"/>
-      <c r="D3" s="187"/>
+      <c r="C3" s="224"/>
+      <c r="D3" s="225"/>
       <c r="E3" s="65"/>
       <c r="F3" s="65"/>
       <c r="G3" s="65"/>
       <c r="H3" s="65"/>
-      <c r="I3" s="188"/>
-      <c r="J3" s="188"/>
-      <c r="K3" s="188"/>
+      <c r="I3" s="208"/>
+      <c r="J3" s="208"/>
+      <c r="K3" s="208"/>
       <c r="L3" s="67"/>
     </row>
     <row r="4" spans="1:12" s="55" customFormat="1" ht="13.15" customHeight="1">
       <c r="A4" s="68" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="189" t="s">
+      <c r="B4" s="226" t="s">
         <v>431</v>
       </c>
-      <c r="C4" s="190"/>
-      <c r="D4" s="191"/>
+      <c r="C4" s="227"/>
+      <c r="D4" s="228"/>
       <c r="E4" s="65"/>
       <c r="F4" s="65"/>
       <c r="G4" s="65"/>
       <c r="H4" s="65"/>
-      <c r="I4" s="188"/>
-      <c r="J4" s="188"/>
-      <c r="K4" s="188"/>
+      <c r="I4" s="208"/>
+      <c r="J4" s="208"/>
+      <c r="K4" s="208"/>
       <c r="L4" s="67"/>
     </row>
     <row r="5" spans="1:12" s="56" customFormat="1" ht="25.5">
       <c r="A5" s="101" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="192" t="s">
+      <c r="B5" s="229" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="193"/>
-      <c r="D5" s="194"/>
+      <c r="C5" s="230"/>
+      <c r="D5" s="231"/>
       <c r="E5" s="69"/>
       <c r="F5" s="69"/>
       <c r="G5" s="69"/>
       <c r="H5" s="69"/>
-      <c r="I5" s="195"/>
-      <c r="J5" s="195"/>
-      <c r="K5" s="195"/>
+      <c r="I5" s="232"/>
+      <c r="J5" s="232"/>
+      <c r="K5" s="232"/>
       <c r="L5" s="70"/>
     </row>
     <row r="6" spans="1:12" s="55" customFormat="1" ht="15" customHeight="1">
@@ -12013,9 +12341,9 @@
       <c r="F6" s="66"/>
       <c r="G6" s="66"/>
       <c r="H6" s="66"/>
-      <c r="I6" s="188"/>
-      <c r="J6" s="188"/>
-      <c r="K6" s="188"/>
+      <c r="I6" s="208"/>
+      <c r="J6" s="208"/>
+      <c r="K6" s="208"/>
       <c r="L6" s="67"/>
     </row>
     <row r="7" spans="1:12" s="55" customFormat="1" ht="15" customHeight="1">
@@ -12037,16 +12365,16 @@
       <c r="F7" s="79"/>
       <c r="G7" s="79"/>
       <c r="H7" s="79"/>
-      <c r="I7" s="188"/>
-      <c r="J7" s="188"/>
-      <c r="K7" s="188"/>
+      <c r="I7" s="208"/>
+      <c r="J7" s="208"/>
+      <c r="K7" s="208"/>
       <c r="L7" s="67"/>
     </row>
     <row r="8" spans="1:12" s="55" customFormat="1" ht="15" customHeight="1">
-      <c r="A8" s="196"/>
-      <c r="B8" s="196"/>
-      <c r="C8" s="196"/>
-      <c r="D8" s="196"/>
+      <c r="A8" s="209"/>
+      <c r="B8" s="209"/>
+      <c r="C8" s="209"/>
+      <c r="D8" s="209"/>
       <c r="F8" s="66"/>
       <c r="G8" s="66"/>
       <c r="H8" s="66"/>
@@ -12056,61 +12384,61 @@
       <c r="L8" s="67"/>
     </row>
     <row r="9" spans="1:12" s="57" customFormat="1" ht="12" customHeight="1">
-      <c r="A9" s="202" t="s">
+      <c r="A9" s="212" t="s">
         <v>71</v>
       </c>
-      <c r="B9" s="204" t="s">
+      <c r="B9" s="214" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="202" t="s">
+      <c r="C9" s="212" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="208" t="s">
+      <c r="D9" s="218" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="209"/>
-      <c r="F9" s="209"/>
-      <c r="G9" s="210"/>
-      <c r="H9" s="206" t="s">
+      <c r="E9" s="219"/>
+      <c r="F9" s="219"/>
+      <c r="G9" s="220"/>
+      <c r="H9" s="216" t="s">
         <v>75</v>
       </c>
-      <c r="I9" s="207" t="s">
+      <c r="I9" s="217" t="s">
         <v>76</v>
       </c>
-      <c r="J9" s="207" t="s">
+      <c r="J9" s="217" t="s">
         <v>77</v>
       </c>
-      <c r="K9" s="207" t="s">
+      <c r="K9" s="217" t="s">
         <v>78</v>
       </c>
       <c r="L9" s="81"/>
     </row>
     <row r="10" spans="1:12" s="55" customFormat="1" ht="12" customHeight="1">
-      <c r="A10" s="203"/>
-      <c r="B10" s="205"/>
-      <c r="C10" s="203"/>
-      <c r="D10" s="211"/>
-      <c r="E10" s="212"/>
-      <c r="F10" s="212"/>
-      <c r="G10" s="213"/>
-      <c r="H10" s="202"/>
-      <c r="I10" s="202"/>
-      <c r="J10" s="202"/>
-      <c r="K10" s="202"/>
+      <c r="A10" s="213"/>
+      <c r="B10" s="215"/>
+      <c r="C10" s="213"/>
+      <c r="D10" s="221"/>
+      <c r="E10" s="222"/>
+      <c r="F10" s="222"/>
+      <c r="G10" s="223"/>
+      <c r="H10" s="212"/>
+      <c r="I10" s="212"/>
+      <c r="J10" s="212"/>
+      <c r="K10" s="212"/>
       <c r="L10" s="67"/>
     </row>
     <row r="11" spans="1:12" s="58" customFormat="1" ht="15">
-      <c r="A11" s="197"/>
-      <c r="B11" s="197"/>
-      <c r="C11" s="197"/>
-      <c r="D11" s="197"/>
-      <c r="E11" s="197"/>
-      <c r="F11" s="197"/>
-      <c r="G11" s="197"/>
-      <c r="H11" s="197"/>
-      <c r="I11" s="197"/>
-      <c r="J11" s="197"/>
-      <c r="K11" s="198"/>
+      <c r="A11" s="210"/>
+      <c r="B11" s="210"/>
+      <c r="C11" s="210"/>
+      <c r="D11" s="210"/>
+      <c r="E11" s="210"/>
+      <c r="F11" s="210"/>
+      <c r="G11" s="210"/>
+      <c r="H11" s="210"/>
+      <c r="I11" s="210"/>
+      <c r="J11" s="210"/>
+      <c r="K11" s="211"/>
     </row>
     <row r="12" spans="1:12" s="59" customFormat="1" ht="29.45" customHeight="1">
       <c r="A12" s="252" t="s">
@@ -12137,11 +12465,11 @@
       <c r="C13" s="103" t="s">
         <v>434</v>
       </c>
-      <c r="D13" s="222" t="s">
+      <c r="D13" s="190" t="s">
         <v>435</v>
       </c>
-      <c r="E13" s="215"/>
-      <c r="F13" s="215"/>
+      <c r="E13" s="191"/>
+      <c r="F13" s="191"/>
       <c r="G13" s="89"/>
       <c r="H13" s="88"/>
       <c r="I13" s="90"/>
@@ -12158,11 +12486,11 @@
       <c r="C14" s="105" t="s">
         <v>437</v>
       </c>
-      <c r="D14" s="222" t="s">
+      <c r="D14" s="190" t="s">
         <v>438</v>
       </c>
-      <c r="E14" s="215"/>
-      <c r="F14" s="215"/>
+      <c r="E14" s="191"/>
+      <c r="F14" s="191"/>
       <c r="G14" s="89"/>
       <c r="H14" s="88"/>
       <c r="I14" s="87"/>
@@ -12179,11 +12507,11 @@
       <c r="C15" s="103" t="s">
         <v>440</v>
       </c>
-      <c r="D15" s="222" t="s">
+      <c r="D15" s="190" t="s">
         <v>441</v>
       </c>
-      <c r="E15" s="215"/>
-      <c r="F15" s="215"/>
+      <c r="E15" s="191"/>
+      <c r="F15" s="191"/>
       <c r="G15" s="89"/>
       <c r="H15" s="88"/>
       <c r="I15" s="87"/>
@@ -12215,11 +12543,11 @@
       <c r="C17" s="105" t="s">
         <v>444</v>
       </c>
-      <c r="D17" s="222" t="s">
+      <c r="D17" s="190" t="s">
         <v>445</v>
       </c>
-      <c r="E17" s="215"/>
-      <c r="F17" s="215"/>
+      <c r="E17" s="191"/>
+      <c r="F17" s="191"/>
       <c r="G17" s="89"/>
       <c r="H17" s="88"/>
       <c r="I17" s="87"/>
@@ -12236,11 +12564,11 @@
       <c r="C18" s="103" t="s">
         <v>447</v>
       </c>
-      <c r="D18" s="222" t="s">
+      <c r="D18" s="190" t="s">
         <v>448</v>
       </c>
-      <c r="E18" s="215"/>
-      <c r="F18" s="215"/>
+      <c r="E18" s="191"/>
+      <c r="F18" s="191"/>
       <c r="G18" s="89"/>
       <c r="H18" s="88"/>
       <c r="I18" s="87"/>
@@ -12257,11 +12585,11 @@
       <c r="C19" s="105" t="s">
         <v>450</v>
       </c>
-      <c r="D19" s="222" t="s">
+      <c r="D19" s="190" t="s">
         <v>451</v>
       </c>
-      <c r="E19" s="215"/>
-      <c r="F19" s="215"/>
+      <c r="E19" s="191"/>
+      <c r="F19" s="191"/>
       <c r="G19" s="89"/>
       <c r="H19" s="88"/>
       <c r="I19" s="87"/>
@@ -12278,11 +12606,11 @@
       <c r="C20" s="103" t="s">
         <v>453</v>
       </c>
-      <c r="D20" s="222" t="s">
+      <c r="D20" s="190" t="s">
         <v>454</v>
       </c>
-      <c r="E20" s="215"/>
-      <c r="F20" s="215"/>
+      <c r="E20" s="191"/>
+      <c r="F20" s="191"/>
       <c r="G20" s="89"/>
       <c r="H20" s="88"/>
       <c r="I20" s="87"/>
@@ -12299,11 +12627,11 @@
       <c r="C21" s="105" t="s">
         <v>456</v>
       </c>
-      <c r="D21" s="222" t="s">
+      <c r="D21" s="190" t="s">
         <v>457</v>
       </c>
-      <c r="E21" s="215"/>
-      <c r="F21" s="215"/>
+      <c r="E21" s="191"/>
+      <c r="F21" s="191"/>
       <c r="G21" s="89"/>
       <c r="H21" s="88"/>
       <c r="I21" s="87"/>
@@ -12335,11 +12663,11 @@
       <c r="C23" s="103" t="s">
         <v>460</v>
       </c>
-      <c r="D23" s="222" t="s">
+      <c r="D23" s="190" t="s">
         <v>461</v>
       </c>
-      <c r="E23" s="215"/>
-      <c r="F23" s="215"/>
+      <c r="E23" s="191"/>
+      <c r="F23" s="191"/>
       <c r="G23" s="89"/>
       <c r="H23" s="88"/>
       <c r="I23" s="87"/>
@@ -12356,11 +12684,11 @@
       <c r="C24" s="105" t="s">
         <v>463</v>
       </c>
-      <c r="D24" s="222" t="s">
+      <c r="D24" s="190" t="s">
         <v>464</v>
       </c>
-      <c r="E24" s="215"/>
-      <c r="F24" s="215"/>
+      <c r="E24" s="191"/>
+      <c r="F24" s="191"/>
       <c r="G24" s="89"/>
       <c r="H24" s="88"/>
       <c r="I24" s="87"/>
@@ -12377,11 +12705,11 @@
       <c r="C25" s="103" t="s">
         <v>466</v>
       </c>
-      <c r="D25" s="222" t="s">
+      <c r="D25" s="190" t="s">
         <v>467</v>
       </c>
-      <c r="E25" s="215"/>
-      <c r="F25" s="215"/>
+      <c r="E25" s="191"/>
+      <c r="F25" s="191"/>
       <c r="G25" s="89"/>
       <c r="H25" s="88"/>
       <c r="I25" s="87"/>
@@ -12398,11 +12726,11 @@
       <c r="C26" s="105" t="s">
         <v>469</v>
       </c>
-      <c r="D26" s="222" t="s">
+      <c r="D26" s="190" t="s">
         <v>470</v>
       </c>
-      <c r="E26" s="215"/>
-      <c r="F26" s="215"/>
+      <c r="E26" s="191"/>
+      <c r="F26" s="191"/>
       <c r="G26" s="89"/>
       <c r="H26" s="88"/>
       <c r="I26" s="87"/>
@@ -12419,11 +12747,11 @@
       <c r="C27" s="103" t="s">
         <v>472</v>
       </c>
-      <c r="D27" s="222" t="s">
+      <c r="D27" s="190" t="s">
         <v>473</v>
       </c>
-      <c r="E27" s="215"/>
-      <c r="F27" s="215"/>
+      <c r="E27" s="191"/>
+      <c r="F27" s="191"/>
       <c r="G27" s="89"/>
       <c r="H27" s="88"/>
       <c r="I27" s="87"/>
@@ -12440,11 +12768,11 @@
       <c r="C28" s="105" t="s">
         <v>475</v>
       </c>
-      <c r="D28" s="222" t="s">
+      <c r="D28" s="190" t="s">
         <v>476</v>
       </c>
-      <c r="E28" s="215"/>
-      <c r="F28" s="215"/>
+      <c r="E28" s="191"/>
+      <c r="F28" s="191"/>
       <c r="G28" s="89"/>
       <c r="H28" s="88"/>
       <c r="I28" s="87"/>
@@ -12461,11 +12789,11 @@
       <c r="C29" s="103" t="s">
         <v>478</v>
       </c>
-      <c r="D29" s="222" t="s">
+      <c r="D29" s="190" t="s">
         <v>479</v>
       </c>
-      <c r="E29" s="215"/>
-      <c r="F29" s="215"/>
+      <c r="E29" s="191"/>
+      <c r="F29" s="191"/>
       <c r="G29" s="89"/>
       <c r="H29" s="88"/>
       <c r="I29" s="87"/>
@@ -12497,11 +12825,11 @@
       <c r="C31" s="105" t="s">
         <v>482</v>
       </c>
-      <c r="D31" s="222" t="s">
+      <c r="D31" s="190" t="s">
         <v>483</v>
       </c>
-      <c r="E31" s="215"/>
-      <c r="F31" s="215"/>
+      <c r="E31" s="191"/>
+      <c r="F31" s="191"/>
       <c r="G31" s="89"/>
       <c r="H31" s="88"/>
       <c r="I31" s="87"/>
@@ -12518,11 +12846,11 @@
       <c r="C32" s="103" t="s">
         <v>485</v>
       </c>
-      <c r="D32" s="222" t="s">
+      <c r="D32" s="190" t="s">
         <v>486</v>
       </c>
-      <c r="E32" s="215"/>
-      <c r="F32" s="215"/>
+      <c r="E32" s="191"/>
+      <c r="F32" s="191"/>
       <c r="G32" s="89"/>
       <c r="H32" s="88"/>
       <c r="I32" s="87"/>
@@ -12533,9 +12861,9 @@
       <c r="A33" s="84"/>
       <c r="B33" s="93"/>
       <c r="C33" s="86"/>
-      <c r="D33" s="243"/>
-      <c r="E33" s="244"/>
-      <c r="F33" s="244"/>
+      <c r="D33" s="239"/>
+      <c r="E33" s="240"/>
+      <c r="F33" s="240"/>
       <c r="G33" s="89"/>
       <c r="H33" s="88"/>
       <c r="I33" s="87"/>
@@ -12546,9 +12874,9 @@
       <c r="A34" s="84"/>
       <c r="B34" s="93"/>
       <c r="C34" s="86"/>
-      <c r="D34" s="243"/>
-      <c r="E34" s="244"/>
-      <c r="F34" s="244"/>
+      <c r="D34" s="239"/>
+      <c r="E34" s="240"/>
+      <c r="F34" s="240"/>
       <c r="G34" s="89"/>
       <c r="H34" s="88"/>
       <c r="I34" s="87"/>
@@ -12559,9 +12887,9 @@
       <c r="A35" s="84"/>
       <c r="B35" s="93"/>
       <c r="C35" s="86"/>
-      <c r="D35" s="243"/>
-      <c r="E35" s="244"/>
-      <c r="F35" s="244"/>
+      <c r="D35" s="239"/>
+      <c r="E35" s="240"/>
+      <c r="F35" s="240"/>
       <c r="G35" s="89"/>
       <c r="H35" s="88"/>
       <c r="I35" s="87"/>
@@ -12572,9 +12900,9 @@
       <c r="A36" s="84"/>
       <c r="B36" s="93"/>
       <c r="C36" s="86"/>
-      <c r="D36" s="243"/>
-      <c r="E36" s="244"/>
-      <c r="F36" s="244"/>
+      <c r="D36" s="239"/>
+      <c r="E36" s="240"/>
+      <c r="F36" s="240"/>
       <c r="G36" s="89"/>
       <c r="H36" s="88"/>
       <c r="I36" s="87"/>
@@ -12585,9 +12913,9 @@
       <c r="A37" s="84"/>
       <c r="B37" s="93"/>
       <c r="C37" s="86"/>
-      <c r="D37" s="243"/>
-      <c r="E37" s="244"/>
-      <c r="F37" s="244"/>
+      <c r="D37" s="239"/>
+      <c r="E37" s="240"/>
+      <c r="F37" s="240"/>
       <c r="G37" s="89"/>
       <c r="H37" s="88"/>
       <c r="I37" s="87"/>
@@ -12598,9 +12926,9 @@
       <c r="A38" s="84"/>
       <c r="B38" s="93"/>
       <c r="C38" s="86"/>
-      <c r="D38" s="243"/>
-      <c r="E38" s="244"/>
-      <c r="F38" s="244"/>
+      <c r="D38" s="239"/>
+      <c r="E38" s="240"/>
+      <c r="F38" s="240"/>
       <c r="G38" s="89"/>
       <c r="H38" s="88"/>
       <c r="I38" s="87"/>
@@ -12611,9 +12939,9 @@
       <c r="A39" s="84"/>
       <c r="B39" s="93"/>
       <c r="C39" s="86"/>
-      <c r="D39" s="243"/>
-      <c r="E39" s="244"/>
-      <c r="F39" s="244"/>
+      <c r="D39" s="239"/>
+      <c r="E39" s="240"/>
+      <c r="F39" s="240"/>
       <c r="G39" s="89"/>
       <c r="H39" s="88"/>
       <c r="I39" s="87"/>
@@ -12624,9 +12952,9 @@
       <c r="A40" s="84"/>
       <c r="B40" s="93"/>
       <c r="C40" s="86"/>
-      <c r="D40" s="243"/>
-      <c r="E40" s="244"/>
-      <c r="F40" s="244"/>
+      <c r="D40" s="239"/>
+      <c r="E40" s="240"/>
+      <c r="F40" s="240"/>
       <c r="G40" s="89"/>
       <c r="H40" s="88"/>
       <c r="I40" s="87"/>
@@ -12637,9 +12965,9 @@
       <c r="A41" s="84"/>
       <c r="B41" s="93"/>
       <c r="C41" s="86"/>
-      <c r="D41" s="243"/>
-      <c r="E41" s="244"/>
-      <c r="F41" s="244"/>
+      <c r="D41" s="239"/>
+      <c r="E41" s="240"/>
+      <c r="F41" s="240"/>
       <c r="G41" s="89"/>
       <c r="H41" s="88"/>
       <c r="I41" s="87"/>
@@ -12650,9 +12978,9 @@
       <c r="A42" s="84"/>
       <c r="B42" s="93"/>
       <c r="C42" s="86"/>
-      <c r="D42" s="243"/>
-      <c r="E42" s="244"/>
-      <c r="F42" s="244"/>
+      <c r="D42" s="239"/>
+      <c r="E42" s="240"/>
+      <c r="F42" s="240"/>
       <c r="G42" s="89"/>
       <c r="H42" s="88"/>
       <c r="I42" s="87"/>
@@ -12663,9 +12991,9 @@
       <c r="A43" s="84"/>
       <c r="B43" s="93"/>
       <c r="C43" s="86"/>
-      <c r="D43" s="243"/>
-      <c r="E43" s="244"/>
-      <c r="F43" s="244"/>
+      <c r="D43" s="239"/>
+      <c r="E43" s="240"/>
+      <c r="F43" s="240"/>
       <c r="G43" s="89"/>
       <c r="H43" s="88"/>
       <c r="I43" s="87"/>
@@ -12676,9 +13004,9 @@
       <c r="A44" s="84"/>
       <c r="B44" s="93"/>
       <c r="C44" s="86"/>
-      <c r="D44" s="243"/>
-      <c r="E44" s="244"/>
-      <c r="F44" s="244"/>
+      <c r="D44" s="239"/>
+      <c r="E44" s="240"/>
+      <c r="F44" s="240"/>
       <c r="G44" s="89"/>
       <c r="H44" s="88"/>
       <c r="I44" s="87"/>
@@ -12689,9 +13017,9 @@
       <c r="A45" s="84"/>
       <c r="B45" s="93"/>
       <c r="C45" s="86"/>
-      <c r="D45" s="243"/>
-      <c r="E45" s="244"/>
-      <c r="F45" s="244"/>
+      <c r="D45" s="239"/>
+      <c r="E45" s="240"/>
+      <c r="F45" s="240"/>
       <c r="G45" s="89"/>
       <c r="H45" s="88"/>
       <c r="I45" s="87"/>
@@ -12702,9 +13030,9 @@
       <c r="A46" s="84"/>
       <c r="B46" s="93"/>
       <c r="C46" s="86"/>
-      <c r="D46" s="243"/>
-      <c r="E46" s="244"/>
-      <c r="F46" s="244"/>
+      <c r="D46" s="239"/>
+      <c r="E46" s="240"/>
+      <c r="F46" s="240"/>
       <c r="G46" s="89"/>
       <c r="H46" s="88"/>
       <c r="I46" s="87"/>
@@ -12715,9 +13043,9 @@
       <c r="A47" s="84"/>
       <c r="B47" s="93"/>
       <c r="C47" s="86"/>
-      <c r="D47" s="243"/>
-      <c r="E47" s="244"/>
-      <c r="F47" s="244"/>
+      <c r="D47" s="239"/>
+      <c r="E47" s="240"/>
+      <c r="F47" s="240"/>
       <c r="G47" s="89"/>
       <c r="H47" s="88"/>
       <c r="I47" s="87"/>
@@ -12728,9 +13056,9 @@
       <c r="A48" s="84"/>
       <c r="B48" s="93"/>
       <c r="C48" s="86"/>
-      <c r="D48" s="243"/>
-      <c r="E48" s="244"/>
-      <c r="F48" s="244"/>
+      <c r="D48" s="239"/>
+      <c r="E48" s="240"/>
+      <c r="F48" s="240"/>
       <c r="G48" s="89"/>
       <c r="H48" s="88"/>
       <c r="I48" s="87"/>
@@ -12741,9 +13069,9 @@
       <c r="A49" s="84"/>
       <c r="B49" s="93"/>
       <c r="C49" s="86"/>
-      <c r="D49" s="243"/>
-      <c r="E49" s="244"/>
-      <c r="F49" s="244"/>
+      <c r="D49" s="239"/>
+      <c r="E49" s="240"/>
+      <c r="F49" s="240"/>
       <c r="G49" s="89"/>
       <c r="H49" s="88"/>
       <c r="I49" s="87"/>
@@ -12754,9 +13082,9 @@
       <c r="A50" s="84"/>
       <c r="B50" s="93"/>
       <c r="C50" s="86"/>
-      <c r="D50" s="243"/>
-      <c r="E50" s="244"/>
-      <c r="F50" s="244"/>
+      <c r="D50" s="239"/>
+      <c r="E50" s="240"/>
+      <c r="F50" s="240"/>
       <c r="G50" s="89"/>
       <c r="H50" s="88"/>
       <c r="I50" s="87"/>
@@ -12767,9 +13095,9 @@
       <c r="A51" s="84"/>
       <c r="B51" s="93"/>
       <c r="C51" s="86"/>
-      <c r="D51" s="243"/>
-      <c r="E51" s="244"/>
-      <c r="F51" s="244"/>
+      <c r="D51" s="239"/>
+      <c r="E51" s="240"/>
+      <c r="F51" s="240"/>
       <c r="G51" s="89"/>
       <c r="H51" s="88"/>
       <c r="I51" s="87"/>
@@ -12780,9 +13108,9 @@
       <c r="A52" s="84"/>
       <c r="B52" s="93"/>
       <c r="C52" s="86"/>
-      <c r="D52" s="243"/>
-      <c r="E52" s="244"/>
-      <c r="F52" s="244"/>
+      <c r="D52" s="239"/>
+      <c r="E52" s="240"/>
+      <c r="F52" s="240"/>
       <c r="G52" s="89"/>
       <c r="H52" s="88"/>
       <c r="I52" s="87"/>
@@ -12793,9 +13121,9 @@
       <c r="A53" s="84"/>
       <c r="B53" s="93"/>
       <c r="C53" s="86"/>
-      <c r="D53" s="243"/>
-      <c r="E53" s="244"/>
-      <c r="F53" s="244"/>
+      <c r="D53" s="239"/>
+      <c r="E53" s="240"/>
+      <c r="F53" s="240"/>
       <c r="G53" s="89"/>
       <c r="H53" s="88"/>
       <c r="I53" s="87"/>
@@ -12806,9 +13134,9 @@
       <c r="A54" s="84"/>
       <c r="B54" s="93"/>
       <c r="C54" s="86"/>
-      <c r="D54" s="243"/>
-      <c r="E54" s="244"/>
-      <c r="F54" s="244"/>
+      <c r="D54" s="239"/>
+      <c r="E54" s="240"/>
+      <c r="F54" s="240"/>
       <c r="G54" s="89"/>
       <c r="H54" s="88"/>
       <c r="I54" s="87"/>
@@ -12819,9 +13147,9 @@
       <c r="A55" s="84"/>
       <c r="B55" s="93"/>
       <c r="C55" s="86"/>
-      <c r="D55" s="243"/>
-      <c r="E55" s="244"/>
-      <c r="F55" s="244"/>
+      <c r="D55" s="239"/>
+      <c r="E55" s="240"/>
+      <c r="F55" s="240"/>
       <c r="G55" s="89"/>
       <c r="H55" s="88"/>
       <c r="I55" s="87"/>
@@ -12832,9 +13160,9 @@
       <c r="A56" s="84"/>
       <c r="B56" s="93"/>
       <c r="C56" s="86"/>
-      <c r="D56" s="243"/>
-      <c r="E56" s="244"/>
-      <c r="F56" s="244"/>
+      <c r="D56" s="239"/>
+      <c r="E56" s="240"/>
+      <c r="F56" s="240"/>
       <c r="G56" s="89"/>
       <c r="H56" s="88"/>
       <c r="I56" s="87"/>
@@ -12845,9 +13173,9 @@
       <c r="A57" s="84"/>
       <c r="B57" s="93"/>
       <c r="C57" s="86"/>
-      <c r="D57" s="243"/>
-      <c r="E57" s="244"/>
-      <c r="F57" s="244"/>
+      <c r="D57" s="239"/>
+      <c r="E57" s="240"/>
+      <c r="F57" s="240"/>
       <c r="G57" s="89"/>
       <c r="H57" s="88"/>
       <c r="I57" s="87"/>
@@ -12858,9 +13186,9 @@
       <c r="A58" s="84"/>
       <c r="B58" s="93"/>
       <c r="C58" s="86"/>
-      <c r="D58" s="243"/>
-      <c r="E58" s="244"/>
-      <c r="F58" s="244"/>
+      <c r="D58" s="239"/>
+      <c r="E58" s="240"/>
+      <c r="F58" s="240"/>
       <c r="G58" s="89"/>
       <c r="H58" s="88"/>
       <c r="I58" s="87"/>
@@ -12871,9 +13199,9 @@
       <c r="A59" s="84"/>
       <c r="B59" s="93"/>
       <c r="C59" s="86"/>
-      <c r="D59" s="243"/>
-      <c r="E59" s="244"/>
-      <c r="F59" s="244"/>
+      <c r="D59" s="239"/>
+      <c r="E59" s="240"/>
+      <c r="F59" s="240"/>
       <c r="G59" s="89"/>
       <c r="H59" s="88"/>
       <c r="I59" s="87"/>
@@ -12884,9 +13212,9 @@
       <c r="A60" s="84"/>
       <c r="B60" s="93"/>
       <c r="C60" s="86"/>
-      <c r="D60" s="243"/>
-      <c r="E60" s="244"/>
-      <c r="F60" s="244"/>
+      <c r="D60" s="239"/>
+      <c r="E60" s="240"/>
+      <c r="F60" s="240"/>
       <c r="G60" s="89"/>
       <c r="H60" s="88"/>
       <c r="I60" s="87"/>
@@ -12897,9 +13225,9 @@
       <c r="A61" s="84"/>
       <c r="B61" s="93"/>
       <c r="C61" s="86"/>
-      <c r="D61" s="243"/>
-      <c r="E61" s="244"/>
-      <c r="F61" s="244"/>
+      <c r="D61" s="239"/>
+      <c r="E61" s="240"/>
+      <c r="F61" s="240"/>
       <c r="G61" s="89"/>
       <c r="H61" s="88"/>
       <c r="I61" s="87"/>
@@ -12910,9 +13238,9 @@
       <c r="A62" s="84"/>
       <c r="B62" s="93"/>
       <c r="C62" s="86"/>
-      <c r="D62" s="243"/>
-      <c r="E62" s="244"/>
-      <c r="F62" s="244"/>
+      <c r="D62" s="239"/>
+      <c r="E62" s="240"/>
+      <c r="F62" s="240"/>
       <c r="G62" s="89"/>
       <c r="H62" s="88"/>
       <c r="I62" s="87"/>
@@ -12923,9 +13251,9 @@
       <c r="A63" s="84"/>
       <c r="B63" s="93"/>
       <c r="C63" s="86"/>
-      <c r="D63" s="243"/>
-      <c r="E63" s="244"/>
-      <c r="F63" s="244"/>
+      <c r="D63" s="239"/>
+      <c r="E63" s="240"/>
+      <c r="F63" s="240"/>
       <c r="G63" s="89"/>
       <c r="H63" s="88"/>
       <c r="I63" s="87"/>
@@ -12936,9 +13264,9 @@
       <c r="A64" s="84"/>
       <c r="B64" s="93"/>
       <c r="C64" s="86"/>
-      <c r="D64" s="243"/>
-      <c r="E64" s="244"/>
-      <c r="F64" s="244"/>
+      <c r="D64" s="239"/>
+      <c r="E64" s="240"/>
+      <c r="F64" s="240"/>
       <c r="G64" s="89"/>
       <c r="H64" s="88"/>
       <c r="I64" s="87"/>
@@ -12949,9 +13277,9 @@
       <c r="A65" s="84"/>
       <c r="B65" s="93"/>
       <c r="C65" s="86"/>
-      <c r="D65" s="243"/>
-      <c r="E65" s="244"/>
-      <c r="F65" s="244"/>
+      <c r="D65" s="239"/>
+      <c r="E65" s="240"/>
+      <c r="F65" s="240"/>
       <c r="G65" s="89"/>
       <c r="H65" s="88"/>
       <c r="I65" s="87"/>
@@ -12962,9 +13290,9 @@
       <c r="A66" s="84"/>
       <c r="B66" s="93"/>
       <c r="C66" s="86"/>
-      <c r="D66" s="243"/>
-      <c r="E66" s="244"/>
-      <c r="F66" s="244"/>
+      <c r="D66" s="239"/>
+      <c r="E66" s="240"/>
+      <c r="F66" s="240"/>
       <c r="G66" s="89"/>
       <c r="H66" s="88"/>
       <c r="I66" s="87"/>
@@ -12975,9 +13303,9 @@
       <c r="A67" s="84"/>
       <c r="B67" s="93"/>
       <c r="C67" s="86"/>
-      <c r="D67" s="243"/>
-      <c r="E67" s="244"/>
-      <c r="F67" s="244"/>
+      <c r="D67" s="239"/>
+      <c r="E67" s="240"/>
+      <c r="F67" s="240"/>
       <c r="G67" s="89"/>
       <c r="H67" s="88"/>
       <c r="I67" s="87"/>
@@ -12988,9 +13316,9 @@
       <c r="A68" s="84"/>
       <c r="B68" s="93"/>
       <c r="C68" s="86"/>
-      <c r="D68" s="243"/>
-      <c r="E68" s="244"/>
-      <c r="F68" s="244"/>
+      <c r="D68" s="239"/>
+      <c r="E68" s="240"/>
+      <c r="F68" s="240"/>
       <c r="G68" s="89"/>
       <c r="H68" s="88"/>
       <c r="I68" s="87"/>
@@ -13001,9 +13329,9 @@
       <c r="A69" s="84"/>
       <c r="B69" s="93"/>
       <c r="C69" s="86"/>
-      <c r="D69" s="243"/>
-      <c r="E69" s="244"/>
-      <c r="F69" s="244"/>
+      <c r="D69" s="239"/>
+      <c r="E69" s="240"/>
+      <c r="F69" s="240"/>
       <c r="G69" s="89"/>
       <c r="H69" s="88"/>
       <c r="I69" s="87"/>
@@ -13014,9 +13342,9 @@
       <c r="A70" s="84"/>
       <c r="B70" s="93"/>
       <c r="C70" s="86"/>
-      <c r="D70" s="243"/>
-      <c r="E70" s="244"/>
-      <c r="F70" s="244"/>
+      <c r="D70" s="239"/>
+      <c r="E70" s="240"/>
+      <c r="F70" s="240"/>
       <c r="G70" s="89"/>
       <c r="H70" s="88"/>
       <c r="I70" s="87"/>
@@ -13027,9 +13355,9 @@
       <c r="A71" s="84"/>
       <c r="B71" s="93"/>
       <c r="C71" s="86"/>
-      <c r="D71" s="243"/>
-      <c r="E71" s="244"/>
-      <c r="F71" s="244"/>
+      <c r="D71" s="239"/>
+      <c r="E71" s="240"/>
+      <c r="F71" s="240"/>
       <c r="G71" s="89"/>
       <c r="H71" s="88"/>
       <c r="I71" s="87"/>
@@ -13040,9 +13368,9 @@
       <c r="A72" s="84"/>
       <c r="B72" s="93"/>
       <c r="C72" s="86"/>
-      <c r="D72" s="243"/>
-      <c r="E72" s="244"/>
-      <c r="F72" s="244"/>
+      <c r="D72" s="239"/>
+      <c r="E72" s="240"/>
+      <c r="F72" s="240"/>
       <c r="G72" s="89"/>
       <c r="H72" s="88"/>
       <c r="I72" s="87"/>
@@ -13053,9 +13381,9 @@
       <c r="A73" s="84"/>
       <c r="B73" s="93"/>
       <c r="C73" s="86"/>
-      <c r="D73" s="243"/>
-      <c r="E73" s="244"/>
-      <c r="F73" s="244"/>
+      <c r="D73" s="239"/>
+      <c r="E73" s="240"/>
+      <c r="F73" s="240"/>
       <c r="G73" s="89"/>
       <c r="H73" s="88"/>
       <c r="I73" s="87"/>
@@ -13066,9 +13394,9 @@
       <c r="A74" s="84"/>
       <c r="B74" s="93"/>
       <c r="C74" s="86"/>
-      <c r="D74" s="243"/>
-      <c r="E74" s="244"/>
-      <c r="F74" s="244"/>
+      <c r="D74" s="239"/>
+      <c r="E74" s="240"/>
+      <c r="F74" s="240"/>
       <c r="G74" s="89"/>
       <c r="H74" s="88"/>
       <c r="I74" s="87"/>
@@ -13079,9 +13407,9 @@
       <c r="A75" s="84"/>
       <c r="B75" s="93"/>
       <c r="C75" s="86"/>
-      <c r="D75" s="243"/>
-      <c r="E75" s="244"/>
-      <c r="F75" s="244"/>
+      <c r="D75" s="239"/>
+      <c r="E75" s="240"/>
+      <c r="F75" s="240"/>
       <c r="G75" s="89"/>
       <c r="H75" s="88"/>
       <c r="I75" s="87"/>
@@ -13092,9 +13420,9 @@
       <c r="A76" s="84"/>
       <c r="B76" s="93"/>
       <c r="C76" s="86"/>
-      <c r="D76" s="243"/>
-      <c r="E76" s="244"/>
-      <c r="F76" s="244"/>
+      <c r="D76" s="239"/>
+      <c r="E76" s="240"/>
+      <c r="F76" s="240"/>
       <c r="G76" s="89"/>
       <c r="H76" s="88"/>
       <c r="I76" s="87"/>
@@ -13105,9 +13433,9 @@
       <c r="A77" s="84"/>
       <c r="B77" s="93"/>
       <c r="C77" s="86"/>
-      <c r="D77" s="243"/>
-      <c r="E77" s="244"/>
-      <c r="F77" s="244"/>
+      <c r="D77" s="239"/>
+      <c r="E77" s="240"/>
+      <c r="F77" s="240"/>
       <c r="G77" s="89"/>
       <c r="H77" s="88"/>
       <c r="I77" s="87"/>
@@ -13118,9 +13446,9 @@
       <c r="A78" s="84"/>
       <c r="B78" s="93"/>
       <c r="C78" s="86"/>
-      <c r="D78" s="243"/>
-      <c r="E78" s="244"/>
-      <c r="F78" s="244"/>
+      <c r="D78" s="239"/>
+      <c r="E78" s="240"/>
+      <c r="F78" s="240"/>
       <c r="G78" s="89"/>
       <c r="H78" s="88"/>
       <c r="I78" s="87"/>
@@ -13131,9 +13459,9 @@
       <c r="A79" s="84"/>
       <c r="B79" s="93"/>
       <c r="C79" s="86"/>
-      <c r="D79" s="243"/>
-      <c r="E79" s="244"/>
-      <c r="F79" s="244"/>
+      <c r="D79" s="239"/>
+      <c r="E79" s="240"/>
+      <c r="F79" s="240"/>
       <c r="G79" s="89"/>
       <c r="H79" s="88"/>
       <c r="I79" s="87"/>
@@ -13144,9 +13472,9 @@
       <c r="A80" s="84"/>
       <c r="B80" s="93"/>
       <c r="C80" s="86"/>
-      <c r="D80" s="243"/>
-      <c r="E80" s="244"/>
-      <c r="F80" s="244"/>
+      <c r="D80" s="239"/>
+      <c r="E80" s="240"/>
+      <c r="F80" s="240"/>
       <c r="G80" s="89"/>
       <c r="H80" s="88"/>
       <c r="I80" s="87"/>
@@ -13157,9 +13485,9 @@
       <c r="A81" s="84"/>
       <c r="B81" s="93"/>
       <c r="C81" s="86"/>
-      <c r="D81" s="243"/>
-      <c r="E81" s="244"/>
-      <c r="F81" s="244"/>
+      <c r="D81" s="239"/>
+      <c r="E81" s="240"/>
+      <c r="F81" s="240"/>
       <c r="G81" s="89"/>
       <c r="H81" s="88"/>
       <c r="I81" s="87"/>
@@ -13170,9 +13498,9 @@
       <c r="A82" s="84"/>
       <c r="B82" s="93"/>
       <c r="C82" s="86"/>
-      <c r="D82" s="243"/>
-      <c r="E82" s="244"/>
-      <c r="F82" s="244"/>
+      <c r="D82" s="239"/>
+      <c r="E82" s="240"/>
+      <c r="F82" s="240"/>
       <c r="G82" s="89"/>
       <c r="H82" s="88"/>
       <c r="I82" s="87"/>
@@ -13183,9 +13511,9 @@
       <c r="A83" s="84"/>
       <c r="B83" s="93"/>
       <c r="C83" s="86"/>
-      <c r="D83" s="243"/>
-      <c r="E83" s="244"/>
-      <c r="F83" s="244"/>
+      <c r="D83" s="239"/>
+      <c r="E83" s="240"/>
+      <c r="F83" s="240"/>
       <c r="G83" s="89"/>
       <c r="H83" s="88"/>
       <c r="I83" s="87"/>
@@ -13196,9 +13524,9 @@
       <c r="A84" s="84"/>
       <c r="B84" s="93"/>
       <c r="C84" s="86"/>
-      <c r="D84" s="243"/>
-      <c r="E84" s="244"/>
-      <c r="F84" s="244"/>
+      <c r="D84" s="239"/>
+      <c r="E84" s="240"/>
+      <c r="F84" s="240"/>
       <c r="G84" s="89"/>
       <c r="H84" s="88"/>
       <c r="I84" s="87"/>
@@ -13209,9 +13537,9 @@
       <c r="A85" s="84"/>
       <c r="B85" s="93"/>
       <c r="C85" s="86"/>
-      <c r="D85" s="243"/>
-      <c r="E85" s="244"/>
-      <c r="F85" s="244"/>
+      <c r="D85" s="239"/>
+      <c r="E85" s="240"/>
+      <c r="F85" s="240"/>
       <c r="G85" s="89"/>
       <c r="H85" s="88"/>
       <c r="I85" s="87"/>
@@ -13222,9 +13550,9 @@
       <c r="A86" s="84"/>
       <c r="B86" s="93"/>
       <c r="C86" s="86"/>
-      <c r="D86" s="243"/>
-      <c r="E86" s="244"/>
-      <c r="F86" s="244"/>
+      <c r="D86" s="239"/>
+      <c r="E86" s="240"/>
+      <c r="F86" s="240"/>
       <c r="G86" s="89"/>
       <c r="H86" s="88"/>
       <c r="I86" s="87"/>
@@ -13235,9 +13563,9 @@
       <c r="A87" s="84"/>
       <c r="B87" s="93"/>
       <c r="C87" s="86"/>
-      <c r="D87" s="243"/>
-      <c r="E87" s="244"/>
-      <c r="F87" s="244"/>
+      <c r="D87" s="239"/>
+      <c r="E87" s="240"/>
+      <c r="F87" s="240"/>
       <c r="G87" s="89"/>
       <c r="H87" s="88"/>
       <c r="I87" s="87"/>
@@ -13246,81 +13574,12 @@
     </row>
   </sheetData>
   <mergeCells count="94">
-    <mergeCell ref="D83:F83"/>
-    <mergeCell ref="D84:F84"/>
-    <mergeCell ref="D85:F85"/>
-    <mergeCell ref="D86:F86"/>
-    <mergeCell ref="D87:F87"/>
-    <mergeCell ref="D78:F78"/>
-    <mergeCell ref="D79:F79"/>
-    <mergeCell ref="D80:F80"/>
-    <mergeCell ref="D81:F81"/>
-    <mergeCell ref="D82:F82"/>
-    <mergeCell ref="D73:F73"/>
-    <mergeCell ref="D74:F74"/>
-    <mergeCell ref="D75:F75"/>
-    <mergeCell ref="D76:F76"/>
-    <mergeCell ref="D77:F77"/>
-    <mergeCell ref="D68:F68"/>
-    <mergeCell ref="D69:F69"/>
-    <mergeCell ref="D70:F70"/>
-    <mergeCell ref="D71:F71"/>
-    <mergeCell ref="D72:F72"/>
-    <mergeCell ref="D63:F63"/>
-    <mergeCell ref="D64:F64"/>
-    <mergeCell ref="D65:F65"/>
-    <mergeCell ref="D66:F66"/>
-    <mergeCell ref="D67:F67"/>
-    <mergeCell ref="D58:F58"/>
-    <mergeCell ref="D59:F59"/>
-    <mergeCell ref="D60:F60"/>
-    <mergeCell ref="D61:F61"/>
-    <mergeCell ref="D62:F62"/>
-    <mergeCell ref="D53:F53"/>
-    <mergeCell ref="D54:F54"/>
-    <mergeCell ref="D55:F55"/>
-    <mergeCell ref="D56:F56"/>
-    <mergeCell ref="D57:F57"/>
-    <mergeCell ref="D48:F48"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="D50:F50"/>
-    <mergeCell ref="D51:F51"/>
-    <mergeCell ref="D52:F52"/>
-    <mergeCell ref="D43:F43"/>
-    <mergeCell ref="D44:F44"/>
-    <mergeCell ref="D45:F45"/>
-    <mergeCell ref="D46:F46"/>
-    <mergeCell ref="D47:F47"/>
-    <mergeCell ref="D38:F38"/>
-    <mergeCell ref="D39:F39"/>
-    <mergeCell ref="D40:F40"/>
-    <mergeCell ref="D41:F41"/>
-    <mergeCell ref="D42:F42"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="D36:F36"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="A30:K30"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="A22:K22"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="A16:K16"/>
-    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="I5:K5"/>
     <mergeCell ref="I6:K6"/>
     <mergeCell ref="I7:K7"/>
     <mergeCell ref="A8:D8"/>
@@ -13334,12 +13593,81 @@
     <mergeCell ref="J9:J10"/>
     <mergeCell ref="K9:K10"/>
     <mergeCell ref="D9:G10"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="A16:K16"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="A22:K22"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="A30:K30"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="D38:F38"/>
+    <mergeCell ref="D39:F39"/>
+    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="D44:F44"/>
+    <mergeCell ref="D45:F45"/>
+    <mergeCell ref="D46:F46"/>
+    <mergeCell ref="D47:F47"/>
+    <mergeCell ref="D48:F48"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="D50:F50"/>
+    <mergeCell ref="D51:F51"/>
+    <mergeCell ref="D52:F52"/>
+    <mergeCell ref="D53:F53"/>
+    <mergeCell ref="D54:F54"/>
+    <mergeCell ref="D55:F55"/>
+    <mergeCell ref="D56:F56"/>
+    <mergeCell ref="D57:F57"/>
+    <mergeCell ref="D58:F58"/>
+    <mergeCell ref="D59:F59"/>
+    <mergeCell ref="D60:F60"/>
+    <mergeCell ref="D61:F61"/>
+    <mergeCell ref="D62:F62"/>
+    <mergeCell ref="D63:F63"/>
+    <mergeCell ref="D64:F64"/>
+    <mergeCell ref="D65:F65"/>
+    <mergeCell ref="D66:F66"/>
+    <mergeCell ref="D67:F67"/>
+    <mergeCell ref="D68:F68"/>
+    <mergeCell ref="D69:F69"/>
+    <mergeCell ref="D70:F70"/>
+    <mergeCell ref="D71:F71"/>
+    <mergeCell ref="D72:F72"/>
+    <mergeCell ref="D73:F73"/>
+    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="D75:F75"/>
+    <mergeCell ref="D76:F76"/>
+    <mergeCell ref="D77:F77"/>
+    <mergeCell ref="D78:F78"/>
+    <mergeCell ref="D79:F79"/>
+    <mergeCell ref="D80:F80"/>
+    <mergeCell ref="D81:F81"/>
+    <mergeCell ref="D82:F82"/>
+    <mergeCell ref="D83:F83"/>
+    <mergeCell ref="D84:F84"/>
+    <mergeCell ref="D85:F85"/>
+    <mergeCell ref="D86:F86"/>
+    <mergeCell ref="D87:F87"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
